--- a/data/corpus/HVB_003_parallel.xlsx
+++ b/data/corpus/HVB_003_parallel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C282"/>
+  <dimension ref="A1:C452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>公餘捷記南平日好古乃於公暇以己所素聞及求諸博識凡有所得輒擬事直書其稟以成篇各曰公餘攬記其詞意淺隔古人高文大筆雖不敢望其門牆然畧記之中有勸戒寓者無備間史覧大德君子勿以斥鷃見哂是荷世家纂譚武侯記漢書卷一〇六·列傳·卷之六言武韜每錄慕澤武侯其先祖福建人名澤唐武宗會昌元年武代韓鈞為交州刺史愛其鄕風水之異遂卜居焉</t>
+          <t>公餘捷記</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CÔNG-DƯ TIỆP-KÝ THẾ GIA Gia thế họ Võ ở làng Mộ-Trạch, Tiền tổ ngày xưa tên là Hồn vốn người ở tỉnh Phúc-Kiến bên Tâu, (vào thời Đường Kinh-Tông Bửu-Nguyên năm đầu, ông được thay chân Hàn-Thiếu sang làm Đô-hộ-Sứ bên An-Nam). Đến thời Đường Võ-Tông niên hiệu năm đầu Hồi-Xương (841), lại thay Hàn-Uốc sang làm Giao-châu Thư-Sứ (có chỗ chép là Kinh lược sứ). Vì thích phong thủy tốt đẹp của làng đó, ông bên tình kế đóng ở đây, nhân thế mới lấy 2 chữ Dương-An để đặt tên huyện, và chữ Khả-Mộ để đặt tên ấp (sau mỗi đời tên là Mộ-Trạch).</t>
+          <t>CÔNG-DƯ TIỆP-KÝ</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>因以唐安名其縣可謂各其色中間始改為暮澤至明宗當寧時竟佐其其弟農同登第大學並以文學稱官至內侍行遣左僕射始著宗門圖其世次科名壽爵秩自是可考</t>
+          <t>世家</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kế đến thời vua Minh-Tông (1314-23) nhà Trần thì ông Nghiêu-Lá và em là Nông cũng đều đã đạt, (chức Đại-học-sĩ đời ra Quốc-sử), cả hai cũng đều nói tiếng chữ tốt văn hay, dần dần được thăng đến chức Hành-khiển Tả-bộc-Xạ. Bấy giờ các ông mới dời lại họ hàng, xếp thành chi thứ, khoa danh phẩm trước, ghi chú phân minh, từ đó mới có thể khảo sát rõ được.</t>
+          <t>THẾ GIA</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>時有高王七世孫各問南來徧者我國各地至邑門外己亥科四名其二各一名者從來相屬同時登用至二十員通邑皆準後裔推諧公道聲同往北俟約以事清後請福延一往就認武家宗派會賊挾擷阻陸路不通因徙安廣水道囘執事遂不果達求治間稽距崇天施屬山南土黃土黃崙尚書黃公賓又奉北使有武老爺者邀諸途而問曰使君乃安南陪臣必知本國明王族不審武潭苗裔當今闊闊如何公無道其因言武氏在天朝亦稱世科各余亨連</t>
+          <t>慕澤武侯其先祖福建人名澤唐武宗會昌元年武代韓鈞為交州刺史愛其鄕風水之異遂卜居焉因以唐安名其縣可謂各其色中間始改為暮澤</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trong thời gian này có cháu 7 đời của Cao-Vương Hao Vương, tên gọi là Lư, khi sang nước ta. Ông đi xem tất cả những nơi danh thắng nước ta khi đến công lăng Mộ-Trạch, Ông chỉ tay, bảo mọi người rằng: Đây là cái Tô Tấn sĩ đó! Quả nhiên đến thời nhà Lê vào khoảng niên hiệu Thịnh - Đức (1653) và năm Vĩnh - Thọ (1658 - 1662) những kỳ xuân thì chiếm bằng rất nhiều, khoa bình-thân đã được 3 người, đến khoa kỷ hội đã được 4 người, còn một hai người thì chẳng khoa nào bổ trọng, đồng thời có đến 13 vị cùng ra làm quan một lúc! Toàn dân trong ấp đều là dòng dõi Ông Hồn, nguyên trước ông được tặng phong Phúc-thần, rồi sau tiếp tục được phong huy hiệu. Hiện nay sau đám rừng nhỏ, vẫn còn một năm đất, tức là ngôi mộ của ông Vũ-Hồn vậy. Khoảng năm Dương-Đức (1672-1674) thời vua Lê Gia-Tông, bọn ông Duy-Hải và Công-Đạo cùng sang sứ bên Tàu, các ông hẹn nhau sau khi xong việc sẽ xin 'qua thăm Phúc-Kiến một lần, để nhận dòng đội họ Vũ bên ấy! nhưng vì lúc ấy có loạn, đường bộ bị nghẽn, nên không thực hành được. Mãi đến thời vua Lê Hy-Tông khoảng niên hiệu Vĩnh-Trị (1676-80) có quan Thượng-thư là Hoàng-công-Bửu quê huyện Thổ-Hoàng thuộc phủ Thiên Thi, phượng mang sang sứ bên Tàu, hổng có ông gia họ Vũ đón ở doc đường hồi Công-Bửu rằng: Sứ thân là người An-nam biết rõ những họ có danh ở bên Quí quốc. Vây tôi xin hỏi dòng dõi của họ Vũ-Hồn hiện nay thế nào? Công-Bửu bên kè hết chuyện họ Vũ bên này cho ông gia nghe. Ông gia nghe xong bắt giác hoa chân múa tay, luôn miệng khen tốt, rồi lại kẻ rằng: Họ Vũ chúng tôi ở bên Thiên Triều, cũng đẳng khoa danh kẻ thế, ngày nay cũng vẫn phát đạt như thường! Thế rồi trước khi cáo biệt, ông gia đưa ra 10 hốt bạc và 10 tấm nhiều màu huyện để ghi làm quà tặng. Nhưng lúc trở về doc đường hổng gặp người vợ Đặng-Diệu nguyên là tướng của nhà Minh, năm trước bị chết tại trận Hồng-Đàm, ngày nay thị muốn báo thù cho chồng, nên mỗi đêm bọn gia nhân đón đường Sứ giả, cướp lột hết cả hành trang! Đến khi về nước, chỉ còn thuật lại câu chuyện thế thôi! Ngày nay người ta cho là: Khoa bảng nước nhà riêng làng Mộ-Trạch chiếm nhiều nhất, là nhờ vương khí của bắc phương tự tập ở đó vậy.</t>
+          <t>Gia thế họ Võ ở làng Mộ-Trạch, Tiền tổ ngày xưa tên là Hồn vốn người ở tỉnh Phúc-Kiến bên Tâu, (vào thời Đường Kinh-Tông Bửu-Nguyên năm đầu, ông được thay chân Hàn-Thiếu sang làm Đô-hộ-Sứ bên An-Nam). Đến thời Đường Võ-Tông niên hiệu năm đầu Hồi-Xương (841), lại thay Hàn-Uốc sang làm Giao-châu Thư-Sứ (có chỗ chép là Kinh lược sứ). Vì thích phong thủy tốt đẹp của làng đó, ông bên tình kế đóng ở đây, nhân thế mới lấy 2 chữ Dương-An để đặt tên huyện, và chữ Khả-Mộ để đặt tên ấp (sau mỗi đời tên là Mộ-Trạch).</t>
         </is>
       </c>
     </row>
@@ -492,12 +492,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>既而告別以銀子十笏玄絲十匹高贈但使還間忽遇將都婁俞念我國洪澤之役事見寧相為失報仇率其徒遮截回程行裝為其所掠歸國曰鏡見道來一徧而已人言天南科第慕都探花武賊撰文會賀幀有詩讚云八百年來通脹長各公願聖世相望高曾祖考勲賢緒綿爵科各蔭澤光八葉華門聲來歌三槐王氏適堪芳鋪張不盡君家事下筆時開翰墨香</t>
+          <t>至明宗當寧時竟佐其其弟農同登第大學並以文學稱官至內侍行遣左僕射始著宗門圖其世次科名壽爵秩自是可考</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vi thế khoảng niên hiệu Vĩnh-Thịnh, khoa thi Nhâm thin (1712) Đinh-Ân thi đồ Tấn-sĩ, lúc ấy có vị Thâm-hoa Võ-Thành, là người cùng huyện, soạn bức trưởng mừng cho Văn-hội, đã có bài thơ khen ngợi như sau: Ngàn năm đạo đức mạch truyền qua. Đời rồi vang lừng tiếng đại gia. Sự nghiệp Tô tiên đã kẻ thế, Văn chương cháu chất nói đăng khoa! Tiêu đình là ngọc khoẻ tròn tâm Vương thị sản hòe sánh đủ ba Cảnh đẹp nhà ông phó chẳng xưê. Ngạt ngào hương mực khắp gần xa.</t>
+          <t>Kế đến thời vua Minh-Tông (1314-23) nhà Trần thì ông Nghiêu-Lá và em là Nông cũng đều đã đạt, (chức Đại-học-sĩ đời ra Quốc-sử), cả hai cũng đều nói tiếng chữ tốt văn hay, dần dần được thăng đến chức Hành-khiển Tả-bộc-Xạ. Bấy giờ các ông mới dời lại họ hàng, xếp thành chi thứ, khoa danh phẩm trước, ghi chú phân minh, từ đó mới có thể khảo sát rõ được.</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>尚書曰試有記武有慕澤人也</t>
+          <t>時有高王七世孫各問南來徧者我國各地至邑門外</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>THƯỢNG-THƯ VÕ-HỮU KÝ</t>
+          <t>Trong thời gian này có cháu 7 đời của Cao-Vương Hao Vương, tên gọi là Lư, khi sang nước ta. Ông đi xem tất cả những nơi danh thắng nước ta khi đến công lăng Mộ-Trạch, Ông chỉ tay, bảo mọi người rằng: Đây là cái Tô Tấn sĩ đó!</t>
         </is>
       </c>
     </row>
@@ -526,12 +526,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>乃竟佐之曾孫其父伯謙頒歸代路安副使參有陰德生下五男一女竝以貴顯稱武有生時所居宅其後為追遠相堂堂踊有喬木古樹亭亭時立黃甲幹武詠詩云尚書武祖來遺種異風英香火堂前得地生翠華蓋參天滋粉代黑怒濤十里樹風聲高標挺特為人望大器軒昂爵晚成舊福綿洪培植厚故家喬木永醫書有為人好古執禮博學洽聞光順樣聖宗癸未科黃甲送任內外諸曹聲價盡無鹽隊五部尚書常浪吟自述詩云雀荊周年官盛踐寧牛曾有之牛耕其清介頗如此尤精於筆學能立大成等法徐田載新述書行于世將城內端門及大興東花等門自李朝營築久歷星霜漸致顔壞皇上特命增葺葺因召公謂曰爾鄉精於等術令諸門修築試等鴻尾數千完了推討規公郎相其高低廣狹等祭黃炎其陳皇上帝治任陶鎔尋命草草之依然完成不差尺寸上深嘉嘆賞日此神籌也</t>
+          <t>己亥科四名其二各一名者從來相屬同時登用至二十員通邑皆準後裔</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ông Võ-Hữu người làng Mộ-Trạch, là cháu 3 đời của Nghiêu-Tà, phụ thân ông tên là Bả-Khiêm, lãnh chức vạn-phủ-phó-Sứ tại Lộ Quy-Hóa, vì có nhiều âm đức nên sau sinh hạ được 5 con gai và 1 con gái đều hiện vinh cả! Còn ngôi nhà của ông sau khi mất, học trò đặt tên là Truy Viễn-Đường, trước nhà có cây tùng cao chót vót mà Tùng-hiên Tiên-sinh (biệt hiệu của cụ Hoàng Giáp Võ-Cán ) đã liệt nó vào 1 cành trong 8 cành của làng Mộ-Trạch và có vịnh bài thơ như sau: Cối phúc lưu lai tự thuở nào! Từ đường đứng trước đẹp làm sao! Một trời phủ kín cây tân biếc. Mười dặm kêu vang lớp sóng đảo. Chót vót mây xanh người vẫn nghến! Hiện ngang bóng cả tiết càng cao! Cho hay phúc hậu công bởi đắp. Nhà với cây chung chữ thế hào! Ông Vô-Hữu là người có tánh hiểu cờ thủ lẻ, học rộng lại kiến văn nhiều. Thi đồ Hoàng-Giáp khoa Quí-vị (1463) vào thời Lê Thánh-Tông niên hiệu Quang-Thuận, khi xuất chính trái khắp trong ngoài, tôi đầu dân cũng ca ngợi, dân dân thăng đến ngữ bộ Thượng-Thư. Ông thường ngâm bài tự thuật trong có những câu: nhầm nhiểm chu niên quan lịch tiền, Tề ngưu tằng hữu pháp ngưu canh?</t>
+          <t>Quả nhiên đến thời nhà Lê vào khoảng niên hiệu Thịnh - Đức (1653) và năm Vĩnh - Thọ (1658 - 1662) những kỳ xuân thì chiếm bằng rất nhiều, khoa bình-thân đã được 3 người, đến khoa kỷ hội đã được 4 người, còn một hai người thì chẳng khoa nào bổ trọng, đồng thời có đến 13 vị cùng ra làm quan một lúc! Toàn dân trong ấp đều là dòng dõi Ông Hồn, nguyên trước ông được tặng phong Phúc-thần, rồi sau tiếp tục được phong huy hiệu. Hiện nay sau đám rừng nhỏ, vẫn còn một năm đất, tức là ngôi mộ của ông Vũ-Hồn vậy.</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>仍賜肥田百餘畝以旌其能年七十來戶部尚書曰誠仕嘗作涼亭煥鬱優遊山水以樂大年所居之卷各曰鳳池後贈太保職光黃乃載六黎簿之子詠詩云豪傑初由進士科日勤日愼無他諸當逃試功各著同列威推德業加廣相守文歆宋璟普朝強物黃張花午門建青黃相暎映餘慶從知精善家其孫武穆為人坦蕩人少遊長安稱典兵一啟黎仁宗太祖時有通臣范屯潘般興諒山王宜氏踰牆紱逆公乃文裔謀典業者二國公假以相人之術攘刀殺得范也</t>
+          <t>推諧公道聲同往北俟約以事清後請福延一往就認武家宗派會賊挾擷阻陸路不通因徙安廣水道囘執事遂不果達</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nghĩa là: Thấm thoát năm tròn quan trái khắp! trâu mồ thi có, thiếu trâu cày, coi đó dủ biết là người thanh liêm đến như thế nào? Ngoại điểm văn chương chính sự, ông còn tinh cả toán học, đã lập ra 1 cuốn Toán pháp đại thành trong có chỉ dẫn phép tinh ruộng đất và phương pháp cấy cây, truyền bá trong khắp dân chúng. Giữa lúc ấy trong hoàng-thành có các cửa Đoan-môn, cửa Đại-hưng, và cửa Đông-hoa. Xây dựng từ thời nhà Lý, tới nay trải nhiều mưa nắng bị vỡ lở nhiều đoạn. Hoàng Thượng ra lệnh trùng tu, nhân triệu ông vào phân hỏi: — Trẫm nghe nhà người tinh về toán học, vậy nay công việc trùng tu, các cửa, người thử tinh xem gạch đã hết là bao nhiêu thì làm lại được.</t>
+          <t>Khoảng năm Dương-Đức (1672-1674) thời vua Lê Gia-Tông, bọn ông Duy-Hải và Công-Đạo cùng sang sứ bên Tàu, các ông hẹn nhau sau khi xong việc sẽ xin 'qua thăm Phúc-Kiến một lần, để nhận dòng đội họ Vũ bên ấy! nhưng vì lúc ấy có loạn, đường bộ bị nghẽn, nên không thực hành được.</t>
         </is>
       </c>
     </row>
@@ -560,12 +560,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>因急喚二稱引兵赴救收潘敬父其黨盡裁之宮庭為之南清乃遜立聖宗嗣統朝廷護其功進封明義功臣都督府左都督知禮伯尹賞肥田一百畝餘衣為世業光賁有詩六早貞才各一世豪唐安知礼擅稱廢卻承孔鯉廷趨訓長得曹彬世授韜許裴載武途曾至踐百年簡竹記動勞莫嫌世道多婉挾門望之巍巍，</t>
+          <t>求治間稽距崇天施屬山南土黃土黃崙尚書黃公賓又奉北使有武老爺者邀諸途而問曰使君乃安南陪臣必知本國明王族不審武潭苗裔當今闊闊如何</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ông lỉnh mang ra ngay các cửa do đặc tinh toán xong rồi lập thành đồ bản dâng lên. Hoàng-Thượng bèn sai thợ nung gạch ngói và các vật liệu, bắt đầu khởi công, đến lúc hoàn thành quả nhiên không thừa không thiếu! Hoàng-Thượng tẩm tắc ngợi khen là tay thân toán, rồi thưởng cho ông 100 mẫu ruộng tốt để làm tiêu biểu cho sự tài năng. Năm ông 70 tuổi, được lãnh chức Hộ bộ Thượng-thư về hưu. Trong lúc thư nhân, ông mới xây nhà nghỉ mát, ngao du sơn thủy, vui thú cảnh gia. Nơi am ông ở đặt tên là Phương-Tri.</t>
+          <t>Mãi đến thời vua Lê Hy-Tông khoảng niên hiệu Vĩnh-Trị (1676-80) có quan Thượng-thư là Hoàng-công-Bửu quê huyện Thổ-Hoàng thuộc phủ Thiên Thi, phượng mang sang sứ bên Tàu, hổng có ông gia họ Vũ đón ở doc đường hồi Công-Bửu rằng: Sứ thân là người An-nam biết rõ những họ có danh ở bên Quí quốc. Vây tôi xin hỏi dòng dõi của họ Vũ-Hồn hiện nay thế nào?</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>獨高。旁誦言唐安知禮，</t>
+          <t>公無道其因言武氏在天朝亦稱世科各余亨連</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sau ông được tặng lên chức Thái-bảo, ông Quang-Bôn có làm thơ mừng như sau: Hào kiệt nguyên trong Tán sĩ khoa. Chữ cần chữ thận chẳng sai qua. Ty Tạo thử khắp tài năng rỏ Liêu hữu suy tôn đức nghiệp gia. Đường Tướng thử văn so Tống-Cảnh Tân Triệu bác vật sánh Trương-Hoa Môn đinh rực rỡ màu xanh tía.</t>
+          <t>Công-Bửu bên kè hết chuyện họ Vũ bên này cho ông gia nghe. Ông gia nghe xong bắt giác hoa chân múa tay, luôn miệng khen tốt, rồi lại kẻ rằng: Họ Vũ chúng tôi ở bên Thiên Triều, cũng đẳng khoa danh kẻ thế, ngày nay cũng vẫn phát đạt như thường!</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>此之謂也。按武有之，</t>
+          <t>既而告別以銀子十笏玄絲十匹高贈但使還間忽遇將都婁俞念我國洪澤之役事見寧相為失報仇率其徒遮截回程行裝為其所掠歸國曰鏡見道來一徧而已人言天南科第慕</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tích thiện cho hay bởi những nhà. Cháu tên là Võ-Dư là người vũ dũng can đảm là thường! lúc còn niên thiếu qua chơi Tràng-An, ban đầu được bỗ một chức Điền-binh, đến thời Lê Nhân-Tông (1413-54) có tên Phạm-Đồn và Phan-Ban cùng với Lạng-Sơn Vương Nghi-Dân trèo tường vào cung toàn bài thi nghịch, ông bèn mật muru với Sùng, Kỷ hai vị quốc công, cải trang làm thầy coi tướng, ngầm đất dao vào đâm chết Phạm-Đồn, rồi mới hò hai tướng kéo quân vào bắt sống Phan-Ban và các đồng đảng đem ra chém hết! Sau khi tạo thanh trong cung cảm, bèn đón Thánh-Tông về nỗi ngôi. Sau Triệu đình luận công ban thưởng, ông được tấn phong Minh-Nghĩa Công-Thần, Đô-Đốc Phù-Tà Đô-Đốc, Tri-Lễ-Bá, và được thưởng 100 mẫu phi diễn làm ruộng thế nghiệp. Vì thế Quang-Bôn có thơ mừng rằng: Sớm đã tài ba nổi tiếng hào!</t>
+          <t>Thế rồi trước khi cáo biệt, ông gia đưa ra 10 hốt bạc và 10 tấm nhiều màu huyện để ghi làm quà tặng. Nhưng lúc trở về doc đường hổng gặp người vợ Đặng-Diệu nguyên là tướng của nhà Minh, năm trước bị chết tại trận Hồng-Đàm, ngày nay thị muốn báo thù cho chồng, nên mỗi đêm bọn gia nhân đón đường Sứ giả, cướp lột hết cả hành trang! Đến khi về nước, chỉ còn thuật lại câu chuyện thế thôi! Ngày nay người ta cho là: Khoa bảng nước nhà riêng làng Mộ-Trạch chiếm nhiều nhất, là nhờ vương khí của bắc phương tự tập ở đó vậy.</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>後子孫貴盛世生武將文臣永享贈太保武祿陞左府以題頒祗都督武良中進士武延臨中黃甲武仲程武延韶武延恩詭中進士武有之遠孫也</t>
+          <t>都探花武賊撰文會賀幀有詩讚云</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Đường-An Tri-Lễ kém ai nào? Nhỏ theo của Không nên thì giáo Lớn học Tào-Bản môn lục thao Mấy độ Liễu dinh từng xuất nhập. Ngàn năm sử bút nhỏ công lao. Gò ghè phó mặc đời nhiều ngả! Riêng một danh môn chót vót cao.</t>
+          <t>Vi thế khoảng niên hiệu Vĩnh-Thịnh, khoa thi Nhâm thin (1712) Đinh-Ân thi đồ Tấn-sĩ, lúc ấy có vị Thâm-hoa Võ-Thành, là người cùng huyện, soạn bức trưởng mừng cho Văn-hội, đã có bài thơ khen ngợi như sau:</t>
         </is>
       </c>
     </row>
@@ -628,12 +628,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>嘗考私譜父登科錄公以年十四二十二歲中癸未科至泰帝小安年共六十四年以公年紀備之已八十七歲使共為尚有亦在休閒無用之歲地先朝國史云遣松楊侯武有持節往古桑進封莫登庸為安國王這武有乃山西武人與公偶同姓字至胡公仕楊作越監據錄尋以文臣二字指為財利所喚後人因以為幕澤武公使各芳之臣久負深誚令故辨之以俟博達君子者校正焉</t>
+          <t>八百年來通脹長各公願聖世相望</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thời bấy giờ có câu ngắn gọn: Đường-An biết lễ tức là thế đó. Xét ra con cháu ông Võ-Hữu về sau nổi đời vinh hiển, mà đời nào cũng có danh tướng, còn khoa bảng thì phát rất nhiều: ông Vĩnh-Phu được tặng đến chức Thái-Bửu, ông Dư được thăng đến chức Tâ-Phú, ông Tiệm được thăng Đề-Lãnh, ông Sa được thăng chức Tham-Đốc, ông Lương thì đỗ Tấn-sĩ, ông Đinh-Lâm thì đỗ Hoàng-giáp, các ông Trọng-Trinh, Đinh-Thiệu, Đinh-Ân đều đỗ Tấn-sĩ, và đều là cháu xa đời của ông Võ-Hữu. Nay lại xét trong gia-phả riêng và trong Đặng-khoa-Lục thì ông sinh năm Tân-Dậu (1437), đến năm Quang-Thuận đời Lê-thành-Tông, thì đỗ Tấn-sĩ vào khóa Quí-vị năm ấy mới 23 tuổi, nếu tính đến khoa Đinh-hội thời Cung-Đế thì 61 năm nữa, thành ra lúc ấy đã 87 tuổi, với cái tuổi ấy mà Cụ còn sống thì cũng về hưu đã lâu. Thế mà cứ như quốc-sử Tiên-triệu đã chép: Vua sai Tùng-Dương Hầu Võ-Hữu mang Cờ Tiết về Cờ-Trai Tấn-phong Mạc-dăng-Dong làm An-Nam Quốc-Vương? thì Võ-Hữu ấy là người họ Võ ở tỉnh Sơn-Tây trung họ trung tên với Cụ, khiến cho ông Hò-sĩ-Dương khi soạn bộ Việt-Giám Tiệp-Lục cũng theo cái nhầm đó rồi thêm hai chữ Văn Thân, và bảo ông bị tài lợi cảm giỡ, để cho đời sau tưởng là Võ Công ở làng Mộ-Trạch. Thành ra một vị danh thần đạo đức phải chịu mỉa mai? Vậy nay chúng tôi mới khảo sát thấy, mong rằng các vị đại-nhân quân-tử sẽ định chánh cho.</t>
+          <t>Ngàn năm đạo đức mạch truyền qua. Đời rồi vang lừng tiếng đại gia.</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>圖景狀元記武昭唐安慕澤人武悼之短也</t>
+          <t>高曾祖考勲賢緒綿爵科各蔭澤光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TRẠNG-NGUYÊN CỜ, 3 VẤN ĐỀ TÊN Ông Võ-Huyên người làng Mộ-Trạch là châu quan Nghè Võ-Đôn nguyên trên đỉnh đầu có một ngổ xương gỗ lên như cái quan cờ, lúc nhỏ đã có chí lớn, khi lớn rất tinh về môn đánh cờ.</t>
+          <t>Sự nghiệp Tô tiên đã kẻ thế, Văn chương cháu chất nói đăng khoa!</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>天庭中有一骨突生如棗子少有大志及長精于棊特有北國使來亦以善棊自負求共我國王開勝期以連輸三局必動兵端我國王志在勝他勢求罷者自助時臣以其各應郎召試之的是吾同手因用計瞞過他約至日中於丹墀對句各番把帕一人餘悉算去北使依克我國王以青帕徵穿上一小吼可通日影適抱之傍侍每勝局輒隱影引綦子國王以此累勝花使不覺嘆服其能國王重其才號曰南國某紂元甚加寵幸暱自是得名人無敢與對其者諺云黃梅酒藥澤其蓋謂此也</t>
+          <t>八葉華門聲來歌三槐王氏適堪芳</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lúc ấy có Sư tâu sang, tự phụ là tay cao cờ, muốn cùng Quốc-Vương ta đấu thử, và có hẹn rằng: Nếu Quốc-Vương thua luôn 3 ván thì bên Bắc quốc sẽ đem quân sang đánh ngay. Vì thế Quốc-Vương cũng muốn làm cho y phải khuất phục, nên mới sai người đi tìm tay cao về giúp, lúc ấy định thân đều tiên cử ông, Vua sai triều vào đấu thử, thấy quả là một tay cao. Ngài bên dùng kế che mất Sư giả, hẹn sẽ cùng đấu vào lúc giữa trưa ở trong sân rồng, mỗi bên chỉ đề một tên vác lọng đứng hầu, còn thì phải tránh đi hết. Bắc-Sư nhận lời xong rồi bên ta mới đem chiếc lọng ra xuyên thủng một lỗ rất nhỏ có thể lọt được ánh nắng mặt trời, trao cho ông Huyên vác đề che cho vua, mỗi khi có nước hay, ông sẽ chiếu bóng nắng vào quân cờ đề chỉ nước đi, thành ra Quốc-Vương thắng luôn mấy bàn, Sư giả thán phục. Rồi sau cuộc này ông được nhà vua trọng đại đặc biệt, ban cho danh hiệu Đấu-Kỳ Trạng-Nguyên và cũng được từ đấy nổi danh không còn ai giám đối thử. Vì thế ngạn ngữ có câu: Rượu Hoàng-Mai cờ Mộ-Trạch là chỉ vào ông vậy.</t>
+          <t>Tiêu đình là ngọc khoẻ tròn tâm Vương thị sản hòe sánh đủ ba</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>交跌狀元記武豊慕澤人武有之弟也</t>
+          <t>鋪張不盡君家事下筆時開翰墨香</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GIAO TRẬT TRẠNG NGUYÊN Ông Võ-Phong người làng Mộ-Trạch là em quan Thượng Võ-Hữu,</t>
+          <t>Cảnh đẹp nhà ông phó chẳng xưê. Ngạt ngào hương mực khắp gần xa.</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>相五短少善交跌賴即生宗時並長安見皇上御朝有都力士捧銅柱蕭立氣覿楊楊公問諸交曰此其人有其英才融而昂然若是其友曰他繫是彊健的人其交踐一藝有甚於此乎</t>
+          <t>尚書曰試有記</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nguyên người có tướng ngũ-doàn (chân tay, tai, mắt, miệng, mũi, 5 thứ đều ngắn và nhỏ, còn người thì thấp) nhưng rất giỏi về môn đấu vật. Đời vua Lê Thánh-Tông (1460-70) nhân có một hôm ông ra kinh thành Tràng-An gặp lúc vua đương ngự triều, ông thấy có viên Đô-lực sĩ vac chiếc chày đồng dùng hầu có về đương đương tử đắc! Ông bèn quay lại hỏi bạn: này bác người kia là ai? có tài cán chi? mà giảm ngang nhiên như vậy.</t>
+          <t>THƯỢNG-THƯ VÕ-HỮU KÝ</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>？夫子曰：「富貴榮辱，</t>
+          <t>武有慕澤人也乃竟佐之曾孫其父伯謙頒歸代路安副使參有陰德生下五男一女竝以貴顯稱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bàn đáp: Người đó là một võ sĩ sở trường về môn đánh vật, hiện thời không ai địch nổi! như vậy cũng là một cách để tiến thân đó! Nghe bạn kề xong ông lại hỏi rằng: nếu vậy ngày nay tôi muốn cùng y so tài cao thấp phỏng có được không? Bàn nghe xong vội vàng can rằng: người ta cao lớn thế kia mà bác thì bé loắt choắt như vậy!</t>
+          <t>Ông Võ-Hữu người làng Mộ-Trạch, là cháu 3 đời của Nghiêu-Tà, phụ thân ông tên là Bả-Khiêm, lãnh chức vạn-phủ-phó-Sứ tại Lộ Quy-Hóa, vì có nhiều âm đức nên sau sinh hạ được 5 con gai và 1 con gái đều hiện vinh cả!</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>可以為進身之地。</t>
+          <t>武有生時所居宅其後為追遠相堂堂踊有喬木古樹亭亭時立黃甲幹武詠詩云</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sợ khi đối thủ lại làm trò cười cho thiên hạ đó thôi!</t>
+          <t>Còn ngôi nhà của ông sau khi mất, học trò đặt tên là Truy Viễn-Đường, trước nhà có cây tùng cao chót vót mà Tùng-hiên Tiên-sinh (biệt hiệu của cụ Hoàng Giáp Võ-Cán) đã liệt nó vào 1 cành trong 8 cành của làng Mộ-Trạch và có vịnh bài thơ như sau:</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>」公曰：「吾請較藝，</t>
+          <t>尚書武祖來遺種異風英香火堂前得地生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ông mỉm cười đáp: điều đó xin Bác đừng ngại?</t>
+          <t>Cối phúc lưu lai tự thuở nào! Từ đường đứng trước đẹp làm sao!</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>如何？」交曰：</t>
+          <t>翠華蓋參天滋粉代黑怒濤十里樹風聲</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tôi đây bản lĩnh rất là cao cường! từ trước đến giờ chưa ai thắng nổi. Còn y chẳng qua chưa gặp địch thủ nên mới nói danh, nhưng nay gặp tôi rồi Bác thử coi tôi sẽ thắng y một cách rất dễ đó! Nói xong ông bèn viết một bản tấu xin cùng lực sĩ so tài. Hoàng Thượng xem tấu phán rằng: lực sĩ của ta tuyên lừa trong muốn ngàn người mới dặng có một!</t>
+          <t>Một trời phủ kín cây tân biếc. Mười dặm kêu vang lớp sóng đảo.</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>「他是身材長大而公以短小較之只恐為闕場見笑公曰吾技藝耳</t>
+          <t>高標挺特為人望大器軒昂爵晚成</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>hỏi còn ai hơn được nữa? thế mà anh kia tài nghệ ra sao lại giám to gan lớn mật như vậy?</t>
+          <t>Chót vót mây xanh người vẫn nghến! Hiện ngang bóng cả tiết càng cao!</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>熟精無厭尚右他未逢對手故得各耳</t>
+          <t>舊福綿洪培植厚故家喬木永</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nhưng rồi Ngài cũng phê chuẩn và định ngày giờ tí thì để Ngài thân ngự ra coi. Thế rồi đến hôm tì thì, trong lúc đối bên còn dương vôn nhau biểu diễn, thì ông quờ ngay xuống đất lấy một ít cát nắm kín trong lòng bàn tay, thưa lúc vô tình ném thẳng vào mặt địch thủ. Lực sĩ vừa nhắm mắt lại thì nhanh như chớt, ông đã dùng miệng Xuyên Trừu, một tay thọc nách một chân đệm phía sau lưng, đẩy mạnh một cái khiên cho Lực sĩ mất đã bị nằm phơi bụng ngay trên mặt đất.</t>
+          <t>Cho hay phúc hậu công bởi đắp. Nhà với cây chung chữ thế hào!</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>使令當番吾勝之即具本奏聞請與力士較勝負皇上覧奏判曰吾之力士千萬中有一人耳</t>
+          <t>醫書有為人好古執禮博學洽聞光順樣聖宗癸未科黃甲送任內外諸曹聲價盡無鹽隊五部尚書常浪吟自述詩云雀荊周年官盛踐寧牛曾有之牛耕其清介頗如此</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(Theo lệ đưa vật, hễ ai bị nằm ngửa bụng mới gọi là thua, còn nằm sấp bụng thì không kề). Thế là ông đã thắng cuộc một cách dễ dàng!</t>
+          <t>Ông Vô-Hữu là người có tánh hiểu cờ thủ lẻ, học rộng lại kiến văn nhiều. Thi đồ Hoàng-Giáp khoa Quí-vị (1463) vào thời Lê Thánh-Tông niên hiệu Quang-Thuận, khi xuất chính trái khắp trong ngoài, tôi đầu dân cũng ca ngợi, dân dân thăng đến ngữ bộ Thượng-Thư. Ông thường ngâm bài tự thuật trong có những câu: nhầm nhiểm chu niên quan lịch tiền, Tề ngưu tằng hữu pháp ngưu canh? nghĩa là: Thấm thoát năm tròn quan trái khắp! trâu mồ thi có, thiếu trâu cày, coi đó dủ biết là người thanh liêm đến như thế nào?</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>世衆以加何人斯敵爾大膽郎六九其請試看力士如何約詞日親御視之爾邊相對公潛納沙手中揮手突八華放沙于力士面上力士喊不啟開措手弗及合用。</t>
+          <t>尤精於筆學能立大成等法徐田載新述書行于世</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>khán giả hoan họ nhiệt liệt. Lúc ấy Hoàng-Thượng ở trên đại trong xuống thấy ông quật đỏ Lực sĩ mau lẹ như vậy, Ngài cũng tấm tắc khen là một tay Thần dũng, rồi sai lột chức Đô Lực-sĩ để phong cho ông;</t>
+          <t>Ngoại điểm văn chương chính sự, ông còn tinh cả toán học, đã lập ra 1 cuốn Toán pháp đại thành trong có chỉ dẫn phép tinh ruộng đất và phương pháp cấy cây, truyền bá trong khắp dân chúng.</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>旁射格擲倒于地觀者齊聲相喝皇上加其勇郎以所封九士者授之官至錦衣衛廷尉屬指揮使以平允称人言葉澤四狀元蓋指穆傳字狀元又為顧狀元武暄為葉狀元公為交跌狀元是為四狀元公兄弟五人竝有爵祿而公與兄有兩枝貴顯繼世登科為族中之冠光黃有詩云也</t>
+          <t>將城內端門及大興東花等門自李朝營築久歷星霜漸致顔壞皇上特命增葺葺因召公謂曰爾鄉精於等術令諸門修築試等鴻尾數千完了推討規公郎相其高低廣狹等祭黃炎其陳皇上帝治任陶鎔尋命草草之依然完成不差尺寸上深嘉嘆賞日此神籌也仍賜肥田百餘畝以旌其能</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dần dần ông được thăng đến Cẩm-Y-Thị-Vệ Úy-ty-Chí-huy-Sứ, nỗi tiếng là người chính trực siêng năng. Còn như lúc ấy thiên hạ đồn rằng: 4 Trạng của huyện Đường-An, 1 làng Mộ-Trạch chiếm cả! là chi vào ông Lê-Đinh làm Trạng-nguyên Chữ và kiêm cả Trạng-nguyên Com (ăn khỏe)! Võ-Huyên làm Trạng Cờ! còn ông thì làm Trạng đô Vật!</t>
+          <t>Giữa lúc ấy trong hoàng-thành có các cửa Đoan-môn, cửa Đại-hưng, và cửa Đông-hoa. Xây dựng từ thời nhà Lý, tới nay trải nhiều mưa nắng bị vỡ lở nhiều đoạn. Hoàng Thượng ra lệnh trùng tu, nhân triệu ông vào phân hỏi: — Trẫm nghe nhà người tinh về toán học, vậy nay công việc trùng tu, các cửa, người thử tinh xem gạch đã hết là bao nhiêu thì làm lại được. Ông lỉnh mang ra ngay các cửa do đặc tinh toán xong rồi lập thành đồ bản dâng lên. Hoàng-Thượng bèn sai thợ nung gạch ngói và các vật liệu, bắt đầu khởi công, đến lúc hoàn thành quả nhiên không thừa không thiếu! Hoàng-Thượng tẩm tắc ngợi khen là tay thân toán, rồi thưởng cho ông 100 mẫu ruộng tốt để làm tiêu biểu cho sự tài năng.</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>短曾稱相顓奇、</t>
+          <t>年七十來戶部尚書曰誠仕嘗作涼亭煥鬱優遊山水以樂大年所居之卷各曰鳳池</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tức là 4 Trạng!</t>
+          <t>Năm ông 70 tuổi, được lãnh chức Hộ bộ Thượng-thư về hưu. Trong lúc thư nhân, ông mới xây nhà nghỉ mát, ngao du sơn thủy, vui thú cảnh gia. Nơi am ông ở đặt tên là Phương-Tri.</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>桑蓬孤矢行男兒一門伯神光前養子載明良結主知應變有才施達政稱乎</t>
+          <t>後贈太保職光黃乃載六黎簿之子詠詩云</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ông có 5 anh em thì ai cũng có phẩm tước, riêng Chi của ông và Chi anh cả thì phát đạt hơn, vì được khoa bằng nỗi đời, đứng vào hàng đầu của họ Vũ ở làng Mộ-Trạch! bởi thế nên ông Quang-Bôn mới tặng thơ rằng: Tương xem ngũ đoàn thực phi thường, Hồ thì làm giai chí bốn phương. Nếp cũ thêm tươi hàng bá trọng, Ngàn xưa dẳng gặp chúa mình lương. Khen tay chính trị tài thông biến. Giữ mực công minh tiếng chẳng nhường.</t>
+          <t>Sau ông được tặng lên chức Thái-bảo, ông Quang-Bôn có làm thơ mừng như sau:</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>各營檔于時無殊榮盛多非偶種德卑閥是我師</t>
+          <t>豪傑初由進士科日勤日愼無他諸</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Con cháu vinh hoa âu cũng bồi, Ai giống cây đức để làm gương.</t>
+          <t>Hào kiệt nguyên trong Tán sĩ khoa. Chữ cần chữ thận chẳng sai qua.</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>宰相武惟志記宰相武惟一，</t>
+          <t>當逃試功各著同列威推德業加</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mộ-Trạch Tề-tướng Ký. Tề-tướng Vô-duy-Chí người làng Mộ-Trạch,</t>
+          <t>Ty Tạo thử khắp tài năng rỏ Liêu hữu suy tôn đức nghiệp gia.</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>燕澤人也，曾祖刑部員外郎晚年二接鄰時舉社吳村教授性畏水蛭一日初有洛沂風雩庶意出村頭池塘清水麗濯綢童子五六尾之纔經伊村園處見一堆圓彙微高顧童生戲指之曰師百歲後當於此封墳則水煙不融近也</t>
+          <t>廣相守文歆宋璟普朝強物黃張花</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cự tam đại trước đã làm đến chức Hình-bộ Viên-ngoại-lang, đến khi già tuổi về hưu, Cự sang dạy học ở làng Thời-Cử Thôn-ngư bên cạnh làng Cự. Nguyên Cự có tính sọ địa, nhân có một hôm Cự nhớ đến cái thanh thú của đức Khổng-phu-Tử ngày trước cùng các món dẹ đi tắm sông Nghi rồi lên hông mát ở nền Vũ-Vu, Cự bên dã 5, 6 đồng sinh ra ngay cái hồ nước trong ở chỗ đầu làng, định để giặt áo, chẳng ngờ khi ra khỏi một đầm rừng cây thì thấy có một gò đất hình tròn và cũng khá cao. Cự bên trở vào mò đất nói bốn với học trò rằng: Nếu thấy trăm tuổi các anh nhớ đem tàng trên gò đất cao kia thì địa không sao lên được. Thế rồi cách mấy năm sau Cự mất, người nhà nhớ lại câu nói ngày trước, đem đi hai ra an táng tại đó. Ngày nay xét ra thì cái gò ấy có một con đất vuông vẫn mọc tại giữa hồ tức là khẩu ấn để làm tiền án, còn ở phía sau tức là hậu chẩm, thì có một con đất giống hình Đan phương hàm thư Chim phương ngậm thư, ngoài mộ ngồi vào chử Ất trong ra chử Tân, về sau các thầy Địa-lý bảo rằng: đó là cục đất trời cho, sau này sẽ phát Công hầu khanh tướng!</t>
+          <t>Đường Tướng thử văn so Tống-Cảnh Tân Triệu bác vật sánh Trương-Hoa</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>及卒家人追念其言郎將伊廣塗之今</t>
+          <t>午門建青黃相暎映餘慶從知精善家</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nhắc lại nhà ông Duy-Chí, bà cụ thân sinh người rất hiền lành phúc hậu! khi còn ít tuổi Cụ cũng tần tảo bán buôn ở các chợ búa, một hôm dương lúc chợ đông, thấy có một chị bán hàng to lụa trong khi vội vã xếp gánh đi rồi mà còn bỏ sót lại đó một cuộn.</t>
+          <t>Môn đinh rực rỡ màu xanh tía. Tích thiện cho hay bởi những nhà.</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>按此地前接有茆浮水面桃後有升鳯郵書坐乙向辛風水師以為天蓋吉司子孫必發公候之貴惟志之母素有陰德少時往市間販買適有鬻綿緯者於眾人喧鬧中遺棄綿一束而去志哥已按取藏之頃之見一婦前來吐號尋覓母盡因問端的盡以付還賣絹婦德之以二匹致謝志哥笑曰取此二匹寧為取一束之多耶</t>
+          <t>其孫武穆為人坦蕩人少遊長安稱典兵一啟黎仁宗太祖時有通臣范屯潘般興諒山王宜氏踰牆紱逆公乃文裔謀典業者二國公假以相人之術攘刀殺得范也因急喚二稱引兵赴救收潘敬父其黨盡裁之宮庭為之南清乃遜立聖宗嗣統朝廷護其功進封明義功臣都督府左都督知禮伯尹賞肥田一百畝餘衣為世業</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cụ bên nhặt lấy xếp vào gánh hàng của mình, rồi một lát sau thấy chị bán to quay lại tìm kiếm không được gào khóc rất thâm thương! Cụ gọi lại hỏi chị kia mặt mát thứ gì? Thấy chị hàng to khai đúng, Cụ bên tra trả cuộn hàng cho chị, chị rất cảm ơn, rút ra 2 tấm để tạ, nhưng Cụ mỉm cười bảo rằng: nếu tôi có lòng tham của, nhận 2 tấm này chẳng tha tôi lấy cả cuộn (súc) có nhiều hơn không. Chỉ vì tôi thấy cũng chở chị em bạn hàng nay bị mất của, tất nhiên lúc trở về nhà sẽ bị chồng đánh đập tội thân, nên tôi mới tra trả lại, chứ có mong gì, tạ ơn, rồi Cụ nhất định không nhận, khiến cho các người trong chợ ai cũng ngợi khen là người phúc hậu!</t>
+          <t>Cháu tên là Võ-Dư là người vũ dũng can đảm là thường! lúc còn niên thiếu qua chơi Tràng-An, ban đầu được bỗ một chức Điền-binh, đến thời Lê Nhân-Tông (1413-54) có tên Phạm-Đồn và Phan-Ban cùng với Lạng-Sơn Vương Nghi-Dân trèo tường vào cung toàn bài thi nghịch, ông bèn mật muru với Sùng, Kỷ hai vị quốc công, cải trang làm thầy coi tướng, ngầm đất dao vào đâm chết Phạm-Đồn, rồi mới hò hai tướng kéo quân vào bắt sống Phan-Ban và các đồng đảng đem ra chém hết! Sau khi tạo thanh trong cung cảm, bèn đón Thánh-Tông về nỗi ngôi. Sau Triệu đình luận công ban thưởng, ông được tấn phong Minh-Nghĩa Công-Thần, Đô-Đốc Phù-Tà Đô-Đốc, Tri-Lễ-Bá, và được thưởng 100 mẫu phi diễn làm ruộng thế nghiệp.</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>我憐汝失物囘歸必被夫兒痛責故見還耳</t>
+          <t>光賁有詩六</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hôm ấy Cụ trở về nhà, đêm nằm mơ thấy có 5 sắc mây hiện ra trước mắt.</t>
+          <t>Vì thế Quang-Bôn có thơ mừng rằng:</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>豈望謝耶一市環視者皆稱其賢世常愛堂前有五色雲現親自抱之俄而春紅雲光散後生五男其一自快少有大志年二十七適長安睹扶花公子為王所重愛人情廣明之而弘祖陽王深自韜晦每朝侍日公執就府竊視之見挾花華止言繚知其成之器一見而異之曰此聖才也</t>
+          <t>早貞才各一世豪唐安知礼擅稱廢</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cụ bên ôm cả vào lòng, nhưng chỉ giây phút thì thấy mây xanh mây hồng tan ngay tức khắc. Về sau Bà sinh đặng 5 con giai, ứng nghiệm với điểm 5 sắc mây trước; 5 con giai là: Người thứ nhất gọi Tự-Khoái, lúc còn thiếu niên đã có chí lớn; đến năm 17 tuổi ra thăm kinh thành Tràng-An, giữa lúc Công-lử Phù và Công-lử Hoa được Hoàng-Thượng yêu dấu đặc biệt, ai cũng trong vào. Nhưng mà Hoàng Tồ Dương-Vương thì rất kín đáo.</t>
+          <t>Sớm đã tài ba nổi tiếng hào! Đường-An Tri-Lễ kém ai nào?</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>即行下其後以潛邸功臣官至左侍郎忠都公其二校萃田戍科進士官至寺鄉其三両子皆功臣進用惟志至宰相方夫至尚書曰距封都爵其其五求諭又已亥科中進士仕至參政自快常通六囊惟志方大皆自功成各遍相繙引年其六校萃求謝出由青紫比途而宦秩書科不異一門倡伸始信青紅先敬之聽惟志達於吏事輔以文學侍陽玉潛印頗見親幸時廣南有阮賊高平有莫澤子公從鸞勒間多有熱勞有駕大海調糧有險高山齊舟有隔千里陳事累差稱旨以致寵遇日隆至拜參政宰相朝臣有吏道為言王聞之即歷敘蕭曹為趙事業依鮮疑論以示群臣焉</t>
+          <t>卻承孔鯉廷趨訓長得曹彬世授韜</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cứ mỗi phiên châu Cậu Khải thường vào công phủ ngô trộm, xét thấy cứ chỉ đáng điệu của hai công-tử thì Cậu đoàn biết không phải là người làm nên to tát, nhưng khi thoát nhìn thấy mặt Hoàng-Tồ thì Cậu đã lấy làm kỵ, biết rằng con người có tài thành trí, bèn xin vào làm môn hạ, rồi sau được dự vào hạng Tiêm-đề Công-Thần tức là công thần từ trong Tư thất. Người thứ hai tên gọi Bạt-Tuy, thì đồ Hoàng-giáp khoa Giáp thin (1484) làm quan đến chức Tự-khanh. Người thứ ba, tư cũng đều là bậc công thần tiến dụng; Duy-Chí làm đến Tề-tướng, Phương-Đại làm đến Thượng-thư, đều phong tước Quân. Người thứ năm tên gọi Cậu-Hối đồ Tấn-sĩ khoa Kỷ-hội, về sau làm đến Tham-chánh.</t>
+          <t>Nhỏ theo của Không nên thì giáo Lớn học Tào-Bản môn lục thao</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>公章厚質直時春天正旦日正有旨文武殿朝禮訖各仍朝服詣政府道身共天道日月有光正氣崇禮言一介言青吉衣為正不宜還用朝服恐違舊制王從其言華為中止蓋亦有爭臣之風焉</t>
+          <t>許裴載武途曾至踐百年簡竹記動勞</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Xét ra Tự-Khoái được vua tri ngộ ngay lúc thiếu thời, thế mà lương thọ cũng ngoài sáu chục (60), còn như Duy-Chí, Phương-Đại cũng đều công thành danh toại, vinh quang đến lúc tuổi già, riêng có Bạt-Tuy Cậu-Hối xuất thân trong hạng khoa cử áo tia đại xanh thì lại phẩm trước thọ khảo đều kém anh em, do đó người ta nhận thấy cái điểm mây xanh, mây vàng tan trước quả thiệt ứng nghiệm.</t>
+          <t>Mấy độ Liễu dinh từng xuất nhập. Ngàn năm sử bút nhỏ công lao.</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>後以央部尚書國者老火保致仕於彩旗對句有云一代尊臣蕭相國兩朝元老趙韓王詩七十五贈太傅公吳遼州太宰范公同時俗云慕澤寧相燕州國老蓋精權位之相軌也</t>
+          <t>莫嫌世道多婉挾門望之巍巍，獨高。</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nhắc lại Duy-Chí là người thông suốt việc quan và có biệt tài về văn-chương, nên khi vào giúp Dương-Vương ở trong tư phủ, được Vương tín nhiệm hơn người. Gặp lúc trong vùng Quảng-Nam có quân Chúa Nguyễn nỗi giây, trên vùng Cao-Băng thì có con cháu họ Mạc quấy rối, ông vẫn theo bên cạnh Vương, lập được rất nhiều công trạng.</t>
+          <t>Gò ghè phó mặc đời nhiều ngả! Riêng một danh môn chót vót cao.</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其子惟諧已亥科中進士父子同朝</t>
+          <t>旁誦言唐安知禮，此之謂也。</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Có khi vượt bê vận lương, có lúc lên rừng dốc chiến, lại còn những lúc ở xa ngàn dặm gửi kế sách về cũng đều hợp ý, nên ông lại được chúa ưu đãi hơn xưa. Chỉ sau mấy năm đã lên đến chức Tham-tung Tề-trương, khiến cho đình thần ghen tị, mà ông là Nha lại xuất thân. Chúa nghe thấy câu đó Ngài liền soạn lại những thiên tiêu sử nói về sự nghiệp Tiêu-Hà Tào-Tham ngày trước, để trao cho các đình-thần, cốt ý là muốn giải thích hộ ông về câu mỉa dọ.</t>
+          <t>Thời bấy giờ có câu ngắn gọn: Đường-An biết lễ tức là thế đó.</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>時有北國人將都鴛舟百餘艘來我國安廣之洪澤朝命宗子王都公頒水師往伐以公為勘戰官進討日公用出文手計編覲諸市庯花嬪有餘輩放下賊艘托為弄月醉花之歡歡陰教各犯來紅巾一幅浸之以水乘夜索艘問鏡口滴水濕之仍各依期從小舟囘去次日交戰我即陳船排開一字交射威戰艘賊賊惶怯敗鏡應發不覺已隨計兵射不啟發將郡因縱火燼揚帆遁去官軍大捷活捉得他一充子年十六姿色絕倫軍囗載還以獻</t>
+          <t>按武有之，後子孫貴盛世生武將文臣永享贈太保武祿陞左府以題頒祗都督武良中進士武延臨中黃甲武仲程武延韶武延恩詭中進士武有之遠孫也</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phụ chú: Tiêu-Hà Tào-Tham nguyên trước cũng làm nha lại ấp Bái, về sau giúp Hán Cao-Tổ làm nên sự nghiệp để vương. Nguyên ông là người có tính trung hậu thắng thân, một năm nhân gặp ngày tết nguyên đán, chúa xuống chỉ du cho hà quan làm lễ triều điện xong rồi thì cứ đề nguyên áo mũ như thế vào mùng Chính-phủ. Ông bên tâu rằng: từ trước đến nay Vương thượng vẫn giữ tắc đa tôn phu, vậy thì buổi lễ hôm nay chỉ nên vân đồ thường phục mới phải, nếu vân triều y sự nữa không hợp với chế độ cũ. Chúa khen là phải thành ra việc ấy lại thôi, coi đó ta thấy ông là một người có đủ phong độ tranh thân đời cờ vậy!</t>
+          <t>Xét ra con cháu ông Võ-Hữu về sau nổi đời vinh hiển, mà đời nào cũng có danh tướng, còn khoa bảng thì phát rất nhiều: ông Vĩnh-Phu được tặng đến chức Thái-Bửu, ông Dư được thăng đến chức Tâ-Phú, ông Tiệm được thăng Đề-Lãnh, ông Sa được thăng chức Tham-Đốc, ông Lương thì đỗ Tấn-sĩ, ông Đinh-Lâm thì đỗ Hoàng-giáp, các ông Trọng-Trinh, Đinh-Thiệu, Đinh-Ân đều đỗ Tấn-sĩ, và đều là cháu xa đời của ông Võ-Hữu.</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其後擇陪臣從北使奉領東牒公文公與族弟令道父會庵榜眼陶公正三名中格再者東書字一各其門下書寫武常存以楷法道義獨在優等時有朝士數指平民論事中裴公輔曰今日中東文有三而幕澤居其二選東字有一而幕澤之優綴饒考中攬金他有兼之平民不睦措乎</t>
+          <t>嘗考私譜父登科錄公以年十四二十二歲中癸未科至泰帝小安年共六十四年以公年紀備之已八十七歲使共為尚有亦在休閒無用之歲</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tránh thân là người bè tôi biết can gián vua, rồi sau ông được về hưu với chức Lại-bộ Thượng-thư Quốc-lão Thiếu-phó, trong lá cờ hiệu có theo một câu đối rằng: Nhất đại tôn thần Tiêu Tương quốc, Lưỡng triều nguyên-lão Triệu Hàn vương, để vì ông cũng như Tiêu Tương quốc với Triệu Hàn vương ngày xưa, sau ông hưởng thọ được 75 tuổi, lúc mất lại được tặng chức Thái-phó.</t>
+          <t>Nay lại xét trong gia-phả riêng và trong Đặng-khoa-Lục thì ông sinh năm Tân-Dậu (1437), đến năm Quang-Thuận đời Lê-thành-Tông, thì đỗ Tấn-sĩ vào khóa Quí-vị năm ấy mới 23 tuổi, nếu tính đến khoa Đinh-hội thời Cung-Đế thì 61 năm nữa, thành ra lúc ấy đã 87 tuổi, với cái tuổi ấy mà Cụ còn sống thì cũng về hưu đã lâu.</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>矣乎民俗頒廓還財物箕室公輔漸憤他日會朝密來社邑彼徒將朝士帽籠衣所盡陰攫之朝士不覺驚焉</t>
+          <t>地先朝國史云遣松楊侯武有持節往古桑進封莫登庸為安國王這武有乃山西武人與公偶同姓字至胡公仕楊作越監據錄尋以文臣二字指為財利所喚後人因以為幕澤武公使各芳之臣久負深蚚令故辨之以俟博達君子者校正焉</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ông cùng quan Thái-tề ở Liêu-Xuyên là Phạm-công-Trư cùng làm quan trong một triều đại, cho nên đời ấy có câu nói rằng: Tề-tướng Mộ-Trạch, Quốc-lão Liêu-Xuyên, là nói quyền vị tương đương với nhau vậy. Còn như gia thế của ông về sau thì có con là DUY-HẢI đỗ Tấn-sĩ khoa Kỷ-hội, cha con làm quan đông triều. Lúc ấy có bọn giặc Tàu tên là Đặng-Diệu kéo hơn 100 chiến thuyền vượt bể sang đánh Đầm-Hồng, Triệu đình bèn sai Vương-Tử là Ninh Quân-Công Thống lãnh Thủy sư đi đánh, còn ông thì được giữ chức Khâm chiến. Trước khi giao phong ông bèn dùng kế mỹ nhân, sai người đi khắp các nơi mộ được 300 ả đào, cho xuống thuyền giặc ca nhạc giúp vui, nhưng trước khi xuống, ông đã chỉ bảo kẻ hoặc, trao cho mỗi chi một tấm khăn hồng, đợi đến lúc nào bọn chúng say rượu ngủ kỹ, bấy giờ mới đem thấm nước rồi nhét vô trong miệng súng thần công, làm xong nhiệm vụ thì phải trở về báo tin v.v. Quả nhiên sáng sớm hôm sau các cô thiếu nữ trở về báo rằng Kế sách đã thi hành xong.</t>
+          <t>Thế mà cứ như quốc-sử Tiên-triệu đã chép: Vua sai Tùng-Dương Hầu Võ-Hữu mang Cờ Tiết về Cờ-Trai Tấn-phong Mạc-dăng-Dong làm An-Nam Quốc-Vương? thì Võ-Hữu ấy là người họ Võ ở tỉnh Sơn-Tây trung họ trung tên với Cụ, khiến cho ông Hò-sĩ-Dương khi soạn bộ Việt-Giám Tiệp-Lục cũng theo cái nhầm đó rồi thêm hai chữ Văn Thân, và bảo ông bị tài lợi cảm giỡ, để cho đời sau tưởng là Võ Công ở làng Mộ-Trạch. Thành ra một vị danh thần đạo đức phải chịu mỉa mai? Vậy nay chúng tôi mới khảo sát thấy, mong rằng các vị đại-nhân quân-tử sẽ định chánh cho.</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>評顧謂合稱曰今日相竊非乎</t>
+          <t>圖景狀元記</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bấy giờ ông mới hạ lệnh đem hết chiến thuyền bày thành mặt trận chư nhất, cấp tốc tiến lên, các khẩu đại bác đồng thời nhả đạn. Quân giặc thấy vậy cũng với đem súng ra bắn giả nhồi, nhưng súng đều bị tắc họng, chẳng bắn được một phát nào. Bọn giặc biết mình bị trúng kế với vàng đốt thuốc hỏa mù, rồi kéo buồm lên chạy trốn, quan quân thừa thắng rượt theo, bắt được một số tù binh trong có một thiếu nữ, tuổi mới cấp kệ thực là một trang quốc sắc, thế mà cũng đem về để hiển lên Vương chư không say dẫm (cấp kệ là đến tuổi 17-18).</t>
+          <t>TRẠNG-NGUYÊN CỜ, 3 VẤN ĐỀ TÊN</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>民而誰那睞者所言相戲耳</t>
+          <t>武昭唐安慕澤人武悼之短也天庭中有一骨突生如棗子少有大志及長精于棊特有北國使來亦以善棊自負求共我國王開勝期以連輸三局必動兵端</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sau một thời gian triều đình có cuộc bang giao, muốn chọn một vị bồi thần sang sứ Bắc quốc, Vương sai đình thần thảo thử một bức công điệp, kết quả cuộc thi, ông với em họ là Công-Trực và quan Bảng-nhơn Hội-Am là Đào-công-Chánh, chỉ có 3 người được dự trúng cách, lần sau lại tuyển một người chữ tốt để viết điệp văn, thì học trò ông là Võ-thường-Tôn viết lời chữ khải tốt nhất được xếp hạng ưu. Khiến cho Triều thần lúc ấy ghen tị, thường nói dồn quan Binh-dân-Cấp-Sự Bui-công-Phụ rằng: ngày nay có 3 người văn hay thì Mộ-Trạch chiếm mất 2 suất, tuyển có 1 người chữ tốt thì Mộ-Trạch lại đứng hạng ưu. Vì thử có mở kỳ thì cướp giật, để thường Mộ-Trạch cũng chiếm cả chẳng, chứ như Binh-dân thì còn trở tay sao kip. Về phần Công-Phụ thấy bạn đồng liệu chế điều như vậy lấy làm hổ giặn, ông bèn bí mật cho người mọ lấy mấy tay ăn cấp thật giỏi, đem về cho sung vào toàn linh hầu, đội phiên triều hội ông cho theo vô để chúng ăn cấp hết cả các hôm áo mũ của bá quan đem dẩu vào một xó kín, sau khi tan châu bá quan thấy mất hết cả hôm dựng, ai cũng nhao nhao hỏi nhau, mà chẳng ai hiểu duyên cớ. Nhưng rồi cách một giờ lâu ai nấy nhớ lại câu chuyện hôm trước, bèn quay lại phía Công-Phụ nói với ông rằng: Việc này nếu không phải Bác Bình-dân thì còn ai nữa, thời thì hôm trước chúng tôi nói bốn, Bác cũng bỏ quá đi cho.</t>
+          <t>Ông Võ-Huyên người làng Mộ-Trạch là châu quan Nghè Võ-Đôn nguyên trên đỉnh đầu có một ngổ xương gỗ lên như cái quan cờ, lúc nhỏ đã có chí lớn, khi lớn rất tinh về môn đánh cờ. Lúc ấy có Sư tâu sang, tự phụ là tay cao cờ, muốn cùng Quốc-Vương ta đấu thử, và có hẹn rằng: Nếu Quốc-Vương thua luôn 3 ván thì bên Bắc quốc sẽ đem quân sang đánh ngay.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>宜急見還公輔佯為不知日比必慕澤也</t>
+          <t>我國王志在勝他勢求罷者自助時臣以其各應郎召試之的是吾同手因用計瞞過他約至日中於丹墀對句各番把帕一人餘悉算去</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vậy hợp áo đầu xin Bác trả lại để ta cùng về một thề.</t>
+          <t>Vì thế Quốc-Vương cũng muốn làm cho y phải khuất phục, nên mới sai người đi tìm tay cao về giúp, lúc ấy định thân đều tiên cử ông, Vua sai triều vào đấu thử, thấy quả là một tay cao. Ngài bên dùng kế che mất Sư giả, hẹn sẽ cùng đấu vào lúc giữa trưa ở trong sân rồng, mỗi bên chỉ đề một tên vác lọng đứng hầu, còn thì phải tránh đi hết.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>乎民安能如是各大笑而去公奏使日與公道公正等倡和詩調頗多不嚴盡述陸夫部在侍師後曾禮部尚書</t>
+          <t>北使依克我國王以青帕徵穿上一小吼可通日影適抱之傍侍每勝局輒隱影引綦子國王以此累勝花使不覺嘆服其能</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Công-Phụ lúc ấy vẫn cứ thân nhiên như không biết chuyện, thấy bá quan hỏi thì ông giả vờ đáp rằng: Việc ấy tất nhiên cũng người Mộ-Trạch, chứ bọn Bình-dân chúng tôi thì làm sao nỗi, bấy giờ mọi người mới rõ câu chuyện, trong nhau cả cười rồi cùng giải tán. Thế rồi cách ít lâu sau, ông cùng các ông Công-Đạo, Công-Chính phượng mạng lên đường sang sứ Bắc-quốc, đi qua các nơi danh thắng, các ông cùng nhau xương họa văn thơ, không biết bao nhiêu mà kẻ, đến khi xong việc trở về ông được thăng chức Thị-lạng bộ Lại, khi mất được phong Bá-tước và chức Lễ-bộ Thượng-thư.</t>
+          <t>Bắc-Sư nhận lời xong rồi bên ta mới đem chiếc lọng ra xuyên thủng một lỗ rất nhỏ có thể lọt được ánh nắng mặt trời, trao cho ông Huyên vác đề che cho vua, mỗi khi có nước hay, ông sẽ chiếu bóng nắng vào quân cờ đề chỉ nước đi, thành ra Quốc-Vương thắng luôn mấy bàn, Sư giả thán phục.</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>尚書武恆斷記尚書武惟新幕澤人也</t>
+          <t>國王重其才號曰南國某紂元甚加寵幸暱自是得名人無敢與對其者</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>QUẾ-AM, VÕ-DUY-ĐOÁN THẦN KHAI TÂM VĂN CHƯƠNG DANH THIÊN HẠ Được thần khai tâm. Văn chương nỗi tiếng khắp thiên hạ. Ông Đoán người làng Mộ-Trạch là con giai quan Hoàng giáp Bạt-Tụy ngày trước, lúc thiếu thời tính rất lỗ độn, học suốt ngày đêm cũng không thuộc được một dòng chữ thành ra khi đã 17 tuổi đầu mà vẫn đốt đặc cán mai. Cậu thấy mình không có khiếu học nên định xoay sang nghề khác.</t>
+          <t>Rồi sau cuộc này ông được nhà vua trọng đại đặc biệt, ban cho danh hiệu Đấu-Kỳ Trạng-Nguyên và cũng được từ đấy nổi danh không còn ai giám đối thử.</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中堂甲武拔萃之子也火極蒙晴讀書不記一行年十七乙未識字欲改別藝云夜受見神人騰空而降為之剖心剖去其濁既醒腹中隱然貴痛次備札橋謝之父再開心教學自此日漸開明學大進蟲宜中元二刊文章各天下初昭祖康王為公子時公居門下適有間饑從星散公獨進隨迨王居節制府進徃留屯詰賊時以解元八侍帷帳事之大小王必密之當時謂之內相徵完詞中優須甲長科中會元王賜之綵衣待以不次六部到尚書言公忠剛慷慨遇事敢言常尊泰九斂之為人上金鑑錄大要勸以正心穀俗知人去讒言甚愜切王嘉納之奇以通臣自許時宮中有詞鷄之戲中官索鷄鷄奉進公適見問問鷄何從來中官以鷄答公作色曰昔在潛師時主上惟知有我寧知爾輩為何人今乃導之以戲樂郎立執鷄喉鷄應手而死中官馳八具告王默然而起為罷詞鷄事陽德年間繫嘉宗年號有北使至公為接伴使與北使途廣和自稱河津至于殲門詩凡二十餘首應答如響北使甚敬章之至禮部設宴北使富筵索酒公應口吟曰飽吾宁道真佳味何必江亭問一盞北使稱賞覲成禮而去後差往高平公幹以爲臣漢都公各居公上公杭言曰臣承嚴之備位尚書奇意主上南牙各軍不調今日使漢都公居其右臣敬不奉命時府僚或在都臺令道乃孫弟方覲奏見此命若行三都不敢秉筆王怒曰若不知命且審此日向暮之黃門智俛之公道知上意不囧即以顗整柱公勃然曰王欲殺諫臣請即納還勅命黃門以聞王怒曰他前日斃吾良鷄我亦含忍今乃爾何疆耶</t>
+          <t>諺云黃梅酒藥澤其蓋謂此也</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chẳng ngỡ bỗng có một đêm Cậu nằm mơ thấy một vị thần nhân từ lung chùng giới giáng xuống, lấy dao rạch vào bụng Cậu, mọi trái tim ra nào hết những chất văn dục, đến khi giặt mình tỉnh giây bụng vẫn còn thấy hơi đau, nhưng Cậu cho là điểm tốt nên sáng hôm sau Cậu liền sửa lễ bài tạ, rồi cha mẹ cũng sửa lễ khai tâm để dạy Cậu học. Là thay từ đấy trở đi thì Cậu học một biết mươi, dần dần nỗi tiếng là người hay chữ, rồi gặp khoa thì Cậu lại chiếm luôn cờ biên Nhi-nguyên ( là 2 lần đỗ đầu), ai cũng cho rằng chuyện lạ. Nguyên trước khi Chiêu-Tổ Khang-Vương còn làm Công-tử, thì ông giúp việc ở trong phủ, gặp lúc hữu sự bao nhiêu thuốc hạ đều hổ chạy hết, riêng có mình ông lúc nào cũng ở bên cạnh Vương, đến khi Vương được phong chức Tiết-chế tức là Trịnh-Cần 1682-1709 đem quân vào đóng ở Luru-đồn thì ông đã đã Giải-nguyên theo giúp ở nơi quân thứ, bất luận việc lớn hay nhỏ Vương cũng hỏi qua ý kiến rồi mới thi-hành, bởi thế người đời mới gọi là quan Nội-tướng, rồi sau thì khoa Hoành-từ ông lại được trưng ưu hạng, đến năm Giáp-thìn lại đổ Hội-nguyên, Vương ban áo mũ và trọng đài hơn mọi người. Vì thế 6 năm giới mà ông đã thăng đến chức Thượng-thư. Xét thấy ông là người rất kiên trung và khẳng khái, gặp việc gì không hợp cũng có can đảm nói ngay. Vì ông rất hàm mộ tư cách của Trương-Cừu-Linh ngày trước cũng giống như thế. Cho nên có dáng bộ Kim-giám-lục trong đó toàn là những câu nói về Chính tâm, hậu tục biết người, xa kẻ siềm nịnh v.v. lời lẽ cực kỳ thiết đáng, được Vương khen là một vị Trực thần. Trong thời gian ấy ở nơi cung trung thường hay có cuộc chơi gà, các vị trung - quan thấy vậy bèn sai người đi khắp các nơi để mua gà tốt về hiến, một hôm bắt gặp, ông liên quát hỏi gà này từ đâu đem đến.</t>
+          <t>Vì thế ngạn ngữ có câu: Rượu Hoàng-Mai cờ Mộ-Trạch là chỉ vào ông vậy.</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>誰殺諫臣而卻知此說立耶</t>
+          <t>交跌狀元記</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trung quan cứ thực trả nhồi;</t>
+          <t>GIAO TRẬT TRẠNG NGUYÊN</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>罷歸公道像他黨亦罷隨耶</t>
+          <t>武豊慕澤人武有之弟也相五短少善交跌賴即生宗時並長安見皇上御朝有都力士捧銅柱蕭立氣覿楊楊公問諸交曰此其人有其英才融而昂然若是</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ông tỏ vẻ giận dữ mắng rằng: trước kia khi còn ở nơi Tiềm-đề (tư định) Vương thượng chỉ biết có một mình ta chứ có biết đâu bọn chúng, thế mà ngày nay chúng toàn bày trò du hi để làm mê hoặc Chúa thượng hay sao, mắng xong ông bên giang lấy con gà chơi rồi bè gậy cò cho nó chết tươi. Trung-quan chạy vào trong cung tấu bày cáo, Vương lãng lăng không nói gì, rồi từ đấy về sau trò chơi chơi gà cũng không còn nữa. Đến năm Dương-Đức triều Lê Gia-Tông (1672-74) có sứ Tàu sang, ông được sung chức Tiếp sử, trên quãng đường trường từ ải Nam-Quan trở về, đối bên xướng họa văn thơ không biết bao nhiêu mà kẻ, ngay từ bên sông Nhi-Hà vào đến Điện-môn, Bắc-Sử cũng xướng hơn 20 bài, bài nào ông cũng họa ngay. Sư giả lấy làm kinh ngạc, đến khi Lễ-bộ thết yến Sư giả hạch sách rượu dầu, ông lại ứng khẩu ngâm rằng: Bảo ngô cá đực chân nhai vị, Hà tất Giang đinh vấn nhất bồi nghĩa là Rượu ngon là đực ta say nhi, còn hỏi Giang đinh một chén chi, Sư giả nghe xong tấm tắc khen ngợi rồi buổi đại lễ được hoàn thành ngay. (Giang đinh là quán rượu). Cách ít lâu ông được lên công cán Cao-bằng, nhưng Vương lại cho nội thân là Hán Quân - công được ở quyền trên, nên ông kháng nghị rằng: Thần đây làm dự chức vị Thượng-thư, tưởng rằng Vương thượng cũng coi Nam nhà làm trọng, chứ có ngờ đâu Hán-Quân lại ở trên thân, vậy thân không dám phung mạng. Giữa lúc ấy các quan đều có mặt tại phủ, Đô-Đại Công Đạo là em họ ông cũng kháng nghị rằng: Vì thử Vương bất thi hành lệnh ấy, thì Tam Đô-thân không giảm cầm bút đề ghi. Vương cả giận phân rằng: Nếu không tuân lệnh thì cứ ở lại đây, thành ra bá quan phải ở lại đến lúc gần tới.</t>
+          <t>Ông Võ-Phong người làng Mộ-Trạch là em quan Thượng Võ-Hữu, nguyên người có tướng ngũ-doàn (chân tay, tai, mắt, miệng, mũi, 5 thứ đều ngắn và nhỏ, còn người thì thấp) nhưng rất giỏi về môn đấu vật. Đời vua Lê Thánh-Tông (1460-70) nhân có một hôm ông ra kinh thành Tràng-An gặp lúc vua đương ngự triều, ông thấy có viên Đô-lực sĩ vac chiếc chày đồng dùng hầu có về đương đương tử đắc! Ông bèn quay lại hỏi bạn: này bác người kia là ai? có tài cán chi? mà giảm ngang nhiên như vậy.</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>差往公道家追收勅命其進士科字一道公不肖納奉差索取之公堅執曰諸勅皆王之賜謹當奉還至如科字乃我才學做成不敬併納奉差不勝為而回時公子推匡由庚茂科中進士同北鎮勘制司王郎召還許以少師陪從意欲用之蓋公難以舊臣然數犯顏觸諦頻見嚴憚故因忤言麗之而用其子其後公道復召用居職如原而公優游桑梓遂無意於當世常有范蠡五湖賦父業澤風景農家考績異聞等作皆用國音人多傳誦其詩詞銘記頗多世稱中興以前詠橋候中興以後唐川子蓋言國音文體得之清高而其學問該博故耳</t>
+          <t>其友曰他繫是彊健的人其交踐一藝有甚於此乎？</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vương sai Hoàng-môn quan ra dực, Công-Đạo xem chúng Vương không chịu thay đổi ý kiến, bèn đập đầu vào cột trụ, ông thì nói lớn lên rằng: Vương Thượng đã giết Gián Thần, vậy Thần xin nạp lại sắc lệnh! Hoàng-môn Quan thấy vậy vội vàng vào tàu: Vương càng giận thêm! à! hôm trước đã giết gà chơi của ta, ta cũng ẩn nhẫn, chẳng ngờ ngày nay y lại quật cương đến thế thì thôi! thử hỏi ai giết Gián Thần mà y dám nói như vậy, rồi Vương hạ lệnh bãi chức ông và Công-Đạo, sau lại sai quan đến nhà thu về sắc mạng từ xưa đến nay, thử gi lòng cũng giao trả, riêng có đạo sắc Tấn-sĩ về khoa thì chữ tốt thì ông giữ lại, sai quan cố tình đời cả, ông viện lẽ rằng: những sắc lệnh kia là của Thượng ban thì tôi vàng mệnh giả về, còn đạo thì chữ là do tài tôi làm được thì tôi có quyền giữ lại làm ghi, Sai quan thấy nói hợp lẽ đánh phải trở về phục mạng.</t>
+          <t>Bàn đáp: Người đó là một võ sĩ sở trường về môn đánh vật, hiện thời không ai địch nổi!</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>公雖去國而朝野皆重其各漂然起敬</t>
+          <t>夫子曰：「富貴榮辱，可以為進身之地。」</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nhắc lại khi ông lui về vườn cũ bạn với cúc tùng, được hơn 4 tháng thì con giai là Công-Tử Duy-Khuông đỗ Tấn-sĩ tự khoa Canh-thin, hiện đương giữ chức Đông-Bắc-Trấn Khám-Chế-Ty, được Vương cho triệu về Kinh sung chức Bồi - Tung Thủy - Sur có ý muốn trọng dụng. Bởi vì ông dẫu là bậc cựu thần, nhưng đã nhiều lần làm Vương phạt ý, nên Vương mới phải xuống chỉ trực hồi, ngày nay lại muốn dùng con để tỏ ra lòng ưu đãi. Tiếc rằng Duy-Khuông vào trong Chính-phủ cũng chẳng được lâu, sự nghiệp cũng chưa thành tựu. Còn như ông Công-Đạo thì sau cũng được triệu về phục chức như xưa. Riêng về phần ông thì vẫn ngao du ở nơi phần tư, không đề ý đến việc đời, nhân buổi thư nhân ông có soạn ra rất nhiều thơ phú Phạm-Lãi-du-Ngũ-Hồ và cuốn Trạch-hương phong-cảnh tập Nông-gia-khảo-tích dị-văn, v.v. đặc biệt nhất là những cuốn văn ấy toàn dùng Quốc-âm, cho nên được rất nhiều người truyền tụng, ngoài ra lại còn biết bao bài mình, bài kỳ rất hay, người đời đã phải ca tụng những câu: Trung hung về trước có Vĩnh-Kiều Hầu, Trung-hung về sau có Đường Xuyên-Tử là nói thề văn quốc âm đều đã đến chỗ thanh cao lắm vậy. Lại như quan Trang họ Đặng ở làng Phù-Đồng soạn bức trướng mừng Võ Tề-Tương khi về hưu cũng có câu rằng: Châu Tương-Công có Đường-Xuyên là người đã nuốt hai kho sách Thiên-lộc Thạch-Cừ, của nhà Hán vào bụng, nghĩa là khen sức học uyên bác vậy.</t>
+          <t>như vậy cũng là một cách để tiến thân đó!</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>時有之南處意副在憲司日有武職一員以苛過被訴論失民兵其後奉侍內閣意副預焉</t>
+          <t>公曰：「吾請較藝，如何？」</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Còn ông thì đầu thời làm quan nhưng trong triều ngoại quan thấy đều trọng danh, lúc ấy có quan Phó-hiến đến nhận chức ở Sơn-Nam, thấy có một viên quan vô bị cáo về việc hà lâm. Ông kết vào tội làm mất dân binh, đến khi ông được bỏ vào Nội-các thấy người vác kiểm đứng hầu lại chính là viên chức bị tội ngày trước. Ông liền quy xuống tàu rằng: Hạ thân thấy quan Thương-thư Võ-duy-Đoán. trước kia vi trái ý Thượng nên phải bãi chức về vườn, tôi nay chưa được phục chức, mà viên võ kia là chức cai quản hà làm, Thân đã kết tôi làm mất quân dân, có sao nay lại phục chức như cũ. Vậy nên Thân phải chất vấn đề cho quốc pháp đẳng nghiêm v.v. Giữa lúc ông kêu việc đó thì các quan hầu thấy đều đông đủ, ai cũng nhìn nhau bằng đôi con mắt kinh ngạc!</t>
+          <t>Nghe bạn kề xong ông lại hỏi rằng: nếu vậy ngày nay tôi muốn cùng y so tài cao thấp phỏng có được không?</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>見武官奉勵武惟斷以事忤旨囂歸至今不見召用而武職其員由該官並可濫臣等已論失民兵今復居職知原小臣敬不彈奏以嚴國典時侍臣見之無不相顧駭愕至上疑意司是公之黨為之遊說命參訊之始知共公無干郎有旨云意副小臣何敢越職言事今姑原之自後不得知此意副奉命而退蓋公以正言被黜故有忠憤者亦為不平其祭文乃全平日所自作如致君期竟舜唐虞自任以身受變綫契去素蘊胸中平治欲大屢施至玄幾裏覓虛且取難宣世其盈虛付之玄機而不流於惑亦得古人忠厚之意兵壽六十四歲贈左侍郎公三世登科為武族世科之冠之始歟</t>
+          <t>交曰：「他是身材長大而公以短小較之只恐為闕場見笑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Còn Vương thượng thì lại ngỏ ông về bè với Võ-Thượng-thư, nên Ngải giao cho đình thần tra xét, sau biết là không, nên được miễn nghị, nhưng Vương lại hạ dụ rằng: Hiến-ty là hạng quan nhỏ sao được nói leo. Vậy nay hãy tạm tha thứ, còn từ đây về sau thì cảm không được giữ thói ấy nữa v.v. Xét thấy ông Phó-hiến đây vì giữ chính khi mà bị truất oan, khiến cho những người có lòng ngay thẳng cũng bất bình thay, còn bài văn tế là do ông thảo tự lúc sinh thời như câu: Thờ vua thì mong Vua như Nghiêu Thuấn, sửa mình thì phải theo dấu Cao-Quy. Sẵn tấm lòng ngay, muốn đem trị bình thì thô, xem cơ tạo hóa, dám đầu tiết lộ huyền vi, câu văn thực là kín đáo nhưng mà trung hậu biết bao. Về sau ông hưởng thọ được 61 tuổi, sau khi tạ thế được tặng chức Thi-lạng, như vậy thì nhà ông đã được 3 đời đăng khoa kế tiếp, và mở đầu 4 chữ kế thế đăng khoa cho họ Vũ làng Mộ-Trạch vậy. (nguyên bản có chú rằng còn thiếu một đoạn.)</t>
+          <t>Bàn nghe xong vội vàng can rằng: người ta cao lớn thế kia mà bác thì bé loắt choắt như vậy! sợ khi đối thủ lại làm trò cười cho thiên hạ đó thôi!</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>尚書武公道記武公道一蒙澤人也</t>
+          <t>公曰吾技藝耳熟精無厭尚右他未逢對手故得各耳使令當番吾勝之</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vũ-Công-Đạo người làng Mộ-Trạch phụ thân là An-phủ-Hậu.</t>
+          <t>Ông mỉm cười đáp: điều đó xin Bác đừng ngại? tôi đây bản lĩnh rất là cao cường! từ trước đến giờ chưa ai thắng nổi. Còn y chẳng qua chưa gặp địch thủ nên mới nói danh, nhưng nay gặp tôi rồi Bác thử coi tôi sẽ thắng y một cách rất dễ đó!</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>其父安富侯少而總齊時有鄰右衰老儒指庭前甘燕葉取岀一曰云庭前有燕皆著紫衣父對曰池下生蓮同張青蓋來大稱賞識者知其子孫必有科第同登之兆後生公與亮公起以馮爽稱丙申科會試公完赴舉時村內東亭市有老嫗于稠人廣坐中粹面撻身躍立而言曰我是儉人降下茲料進士于吾我已知之爾澤邑文星正旺天帝簡知我故來相告爾等欲聞之乎</t>
+          <t>即具本奏聞請與力士較勝負</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thế rồi đến năm Binh-thân gặp khoa thi hội, Công-Lượng cũng vào thi, lúc ấy ở chợ Đông-Định trong thôn bổng có một bà lão tự trong đầm đồng nhảy ra, đứng sừng trước mặt mọi người, mặt thì đỏ gay, đầu thì lão đảo, lên tiếng bảo mọi người rằng: Ta đây vốn ở Tiên cung cho nên khoa thi này được bao Tấn-sĩ ta đã biết trước, hiện nay làng Mộ-Trạch người, vẫn tinh dương vượng, đức Ngọc-Hoàng đã tuyển sẵn rồi nên mới sai Ta xướng đây bảo cho các ngươi biết rõ!</t>
+          <t>Nói xong ông bèn viết một bản tấu xin cùng lực sĩ so tài.</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>村人奇之布席以坐四面還觀爭以美質當祈獻叩問之其人曰今科進士有六而幕澤居其三村人請問姓名曰登龍中再問之曰卓然牛中又問之曰公亮中眾人皆以為誣謗莫之信父後出榜率知其言識者自謂事有明定而天門放榜之事亦不託傳部說茲科未生試一年間有北地師經登第龍祖登觀者良久曰我纏到青池縣月蓋社者阮族舊墳以為來科必發首科今按這苟不讓月蓋地脈來春亦當得者科人以爲誣朝之曰龍競假真都亂說豈有一榜二首科之理乎</t>
+          <t>皇上覧奏判曰吾之力士千萬中有一人耳世衆以加何人斯敵爾大膽郎六九其請試看力士如何約詞日親御視之</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vậy thì các ngươi có muốn nghe không? Các ngươi trong thôn xóm thấy nói lạ lùng như vậy, họ bèn trái chiều mòi bà ấy ngời, rồi họ đứng bọc chung quanh và lại xô nhau đem trâu cau ra khấn vái để hỏi xem sao? Bà ấy đáp rằng: khoa này có 6 Tấn-sĩ thì làng Mộ-Trạch chiếm được 3 ngươi. Hỏi 3 ngươi ấy họ tên thế nào? Bà ấy đáp: Đặng - Long, hỏi lần thứ hai, đáp rằng: Trác-Lạc, hỏi lần thứ ba, đáp rằng: Công-Lượng. Mọi ngươi nghe xong vẫn yên trí là câu nói hoang đường chứ chẳng ai tin, nhưng rồi đến khi kéo bảng thấy đúng như vậy. Bấy giờ những ngươi thức giả mới tin là có tiền định, mà việc phóng bảng trên cửa nhà giới, cũng chẳng phải là câu nói ngoa vậy!</t>
+          <t>Hoàng Thượng xem tấu phán rằng: lực sĩ của ta tuyên lừa trong muốn ngàn người mới dặng có một! hỏi còn ai hơn được nữa? thế mà anh kia tài nghệ ra sao lại giám to gan lớn mật như vậy? nhưng rồi Ngài cũng phê chuẩn và định ngày giờ tí thì để Ngài thân ngự ra coi.</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>至是策題問以君道聖籠子敬天用人開國紀綱保功臣法度國用治道禮樂將帥賞罰中興功業國勛九十四目為問阮廷柱中會元簽籠中第二醜而八將王庭王上見簽龍相貌比廷模勝之有首判云此子不當首科耶</t>
+          <t>爾邊相對公潛納沙手中揮手突八華放沙于力士面上</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nhắc lại khoa này một năm về trước có thầy địa-lý Tàu khi qua ngôi mộ Tồ nhà ông Đặng-Long thấy Địa xem xét hồi lâu rồi bảo mọi ngươi rằng: Khi tôi mới đến xã Nguyệt-Áng thuộc huyện Thanh-Tri đó xem lại ngôi mộ Tồ họ Nguyễn thì tôi đoán rằng: khoa thì sang năm họ ấy sẽ có người đỗ Thủ-khoa, ngày nay xem cục đất này khi mạch cũng không kèm gì Nguyệt-Áng, sang xuân thế nào cũng phát Thủ-khoa. Lúc ấy ai cũng chê điều cho rằng: Long hồ thực hư đều là những câu nói hão, chứ có lẽ đầu cùng trong một bảng mà lại có hai Thủ-khoa! Nhưng rồi đến khoa thì ấy thì đề tài sách vẫn lại hỏi về quân đạo Thánh học v.v. công 14 mục. Thi xong Đinh-Quế được trúng Hội - nguyên, Đặng - Long được đỡ thứ nhi, đến khi cùng vào Vương phủ dự yến, Hoàng-Thương nhìn thấy diện mạo Đặng - Long có vẻ tuần tú hơn Đinh-Quế nhiều, nên Ngai phân ngay rằng: Gã này không đáng mặt Thủ-khoa hay sao, rồi Ngai ra lệnh cho Long được đứng ở bên tay phải Đinh-Quế.</t>
+          <t>Thế rồi đến hôm tì thì, trong lúc đối bên còn dương vôn nhau biểu diễn, thì ông quờ ngay xuống đất lấy một ít cát nắm kín trong lòng bàn tay, thưa lúc vô tình ném thẳng vào mặt địch thủ.</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>命在天柱王右故時人稱楚樑字首科餐龍觀首科方覺北師之書亦為高見時入道未第吹年彼孝事偽因他適鄉試場目次點心中真更問夜為交至唐豪縣無得社行過去外聞內有聲喚曰進士何之公郎馳至三闕見闊者二人載嘆因問之曰這裏某宮人在閣者曰正中黃衣乃玉皇上帝座兩旁青衣者南曹北斗是也</t>
+          <t>力士喊不啟開措手弗及合用。旁射格擲倒于地觀者齊聲相喝</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vi thế lúc ấy mới có câu rằng: Đinh - Quế là Thủ-khoa Chữ Đặng-Long là Thủ-khoa đẹp, bấy giờ người ta mới tin thấy Địa cao kiến hơn đời vậy. Còn như Công-Đạo lúc ấy cũng chưa dỡ đạt, rồi sang năm sau gặp việc đại tang, nhân lại có việc phải đi nơi khác, nên bị thiếu điểm ở trường thi hương, giữa lúc còn đương lo phiên thì bỗng một đêm ông nằm mơ thấy: mình đi đến xã Võ - Ngai thuộc huyện Đường-Hào, khi qua ngôi chùa chợt nghe bên trong có tiếng hỏi: Quan Nghè định đi đầu tá Ông vội chạy vào trước cửa Tam quan, thì thấy hai người cầm roi đứng canh hai bên, ông hỏi trong ấy có vị quan nào, họ đáp: Người mặc áo vàng ngồi ở chính giữa là Đức Ngọc-Hoàng, còn hai người mặc áo xanh hai bên tức là Nam-Tảo Bắc-đầu đó.</t>
+          <t>Lực sĩ vừa nhắm mắt lại thì nhanh như chớt, ông đã dùng miệng Xuyên Trừu, một tay thọc nách một chân đệm phía sau lưng, đẩy mạnh một cái khiên cho Lực sĩ mất đã bị nằm phơi bụng ngay trên mặt đất. (Theo lệ đưa vật, hễ ai bị nằm ngửa bụng mới gọi là thua, còn nằm sấp bụng thì không kề). Thế là ông đã thắng cuộc một cách dễ dàng! khán giả hoan họ nhiệt liệt.</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>公進八庭前跪請曰敬問員進士何科見在旁二員面問中正知幕間之狀俄聞曰許茲科公曰來春袁經未除何能望此闡有聲曰震公再請曰臣藥已欠點知何又聞曰訴見點入受中喜不自勝急喜起趨出跌躡于地見在內老人調清水一盃灌之既而醒覺口中猶有香臭笑已科春園以有事展誠又先是各處直士徃徃潛八鄉試場代試多致大顯至是昭祖判云凡為人顯者為人代試必是有所文字應一切藏之今以是范吳科公親舅來謝族兄惟誨同色公朝四各同榜自有科目以來未之有也</t>
+          <t>皇上加其勇郎以所封九士者授之官至錦衣衛廷尉屬指揮使以平允称</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ông nghe hai người bảo thế vội tiến vào sân quy gói hỏi rằng: Khoa nào hạ thần được đổ Tấn-sĩ? Hỏi xong thì thấy hai người nhìn vào vị ngồi ở giữa hình như bẩm vấn điều chi rồi sau phân bảo: Anh sẽ đổ ngay khoa này! ông lại hỏi tiếp: Nhưng mà sang xuân thì thân còn đương mặc áo sô gấu biết làm thế nào? đáp rằng: Triền, (tức triền hạn), ông lại hỏi trước kia thân đã thiếu điểm thì sao? đáp: Tha cho điểm đó! Nghè được mấy câu phân bảo ông rất vui mừng, vội vàng chạy ra, chẳng ngờ xảy chân té nhào xuống đất, bống thấy bên trong có một ông già đem chén nước lă ra đổ vào miệng, rồi một lát sau thì ông tỉnh dậy, trong miệng vẫn còn hương thơm. Thế rồi vừa bước sang năm Kỷ-hợi trong nước gặp lúc hữu sự, nên kỳ Xuân-thí lại phải hoãn đến mùa đông. Và lại trước kia Cống-sĩ các nơi thường hay đội quyền thì giúp trong kỳ thi hương, cho nên nhiều người thiếu điểm. Ngày nay Chiêu-Tô phán rằng: Những người đã đi thi họ tất nhiên là người học khá, vậy nay nhất thiết tha cho cái lối thiếu điểm năm xưa, vì thế ông cũng được miễn.</t>
+          <t>Lúc ấy Hoàng-Thượng ở trên đại trong xuống thấy ông quật đỏ Lực sĩ mau lẹ như vậy, Ngài cũng tấm tắc khen là một tay Thần dũng, rồi sai lột chức Đô Lực-sĩ để phong cho ông; dần dần ông được thăng đến Cẩm-Y-Thị-Vệ Úy-ty-Chí-huy-Sứ, nỗi tiếng là người chính trực siêng năng.</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>公在朝言論碌何不辟權貴常有諫闕鷄文奉進昭祖深嘉之陽德間奉往北使回至南亭遇賊依攬阻陸路不通上國給以大艘從安廣水道而回仕至都御史壹因執奏武惟斬與內臣漢都公之罪見武惟斬王不從公以頭顱系柱凜然有奸廷折楹之風時稱直御史罷歸未幾復得召用任至尚書郎八十義公之前程事築未第時一變已非見矣</t>
+          <t>人言葉澤四狀元蓋指穆傳字狀元又為顧狀元武暄為葉狀元公為交跌狀元是為四狀元</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rồi ngày khoa ấy ông cùng Bác ruột là Cầu-Hối, em họ là Duy-Hải người cùng ấp là Công-Triều, tất cả 4 người cùng được đề danh đồng bảng. Kể từ lúc có khoa mục cho tới ngày nay chưa bao giờ thịnh đến như vậy! (Kiểm điểm cũng như kiểm diện). Xét thấy khi ông làm quan tại triều, nghị luận rất là cũng cỏi, không hề kiêng nề những chỗ quyền môn, thường tiến bài văn can gián về việc chơi gà, rất được Chiêu-Tô khen ngợi.</t>
+          <t>Còn như lúc ấy thiên hạ đồn rằng: 4 Trạng của huyện Đường-An, 1 làng Mộ-Trạch chiếm cả! là chi vào ông Lê-Đinh làm Trạng-nguyên Chữ và kiêm cả Trạng-nguyên Com (ăn khỏe)! Võ-Huyên làm Trạng Cờ! còn ông thì làm Trạng đô Vật! tức là 4 Trạng!</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>公外自風流而為行統實初為山南督同時賜夫人不在有二門下人擕一絕艶歌兒來欲其買寵公曰我自少至長未常違非已之色汝以尤物殺我平拒而遣之離居貴顯不買群妾只有微時一夫人與之緒影交常對兒孫言我雖不逮古人而未常犯奸色之或是人之所難也</t>
+          <t>公兄弟五人竝有爵祿而公與兄有兩枝貴顯繼世登科為族中之冠</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vào khoảng năm Dương-Đức (1672-74) ông sang sứ bên Tàu, khi về đến tỉnh Nam-Ninh thì địa phương ấy có giặc, đương bộ bị ngễn, địa phương quan phải vất 1 chiếc thuyền lớn để dưa ông về đường thủy, rồi sau ông làm đến Đô-Ngư-Sử Đại, lúc ấy ông tâu về việc Duy-Đoàn và Hán Quần-Công, thấy Vương không nghe, ông bèn dập đầu vào cột, khi phách lâm liệt chẳng khác gì người níu gãy bao lan ngày trước.</t>
+          <t>Ông có 5 anh em thì ai cũng có phẩm tước, riêng Chi của ông và Chi anh cả thì phát đạt hơn, vì được khoa bằng nỗi đời, đứng vào hàng đầu của họ Vũ ở làng Mộ-Trạch!</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>其平生教習多得英才如東鄰撫眼公范光宅丹輪探花武成賊楊柳會元阮各譽誼以魁科望異代見推皆公之門弟也</t>
+          <t>光黃有詩云</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cho nên đời mới gọi ông là Trực Ngư-Sử. Tuy nhiên sau vụ ấy thì ông bị bãi chức trở về cố hương, nhưng chưa bao lâu lại được triệu dụng, rồi làm đến chức Thượng-Thư Trí-sĩ. Kể ra từ năm 18 cho đến 86 tuổi, năm nào ông cũng có thơ Tự-thuật, viết bằng quốc âm và thơ Đường-luật, thơ đều xuất khẩu thành chương, rất được nhiều người truyền tụng. (Thấy trong tập Lão-Hội) bởi vì sự nghiệp tương lai của ông thì một giấc mộng đã bảo từ trước khi đổ đạt vậy.</t>
+          <t>bởi thế nên ông Quang-Bôn mới tặng thơ rằng:</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>今之學者猶尊仰焉</t>
+          <t>也短曾稱相顓奇、桑蓬孤矢行男兒</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Người ta xét thấy ông là người bên ngoài có vẻ phong tình, nhưng mà trong tâm giữ rất thuận cần, thử coi khi ông còn làm Đốc-Đồng tại xứ Sơn-Nam có viên thuộc hạ dòm lúc phu-nhân đi vắng, bèn đem một ả ca nhi tuyệt sắc vào định toan sự cầu thân. Nhưng ông bảo rằng: Ta đây từ nhỏ đến lớn chưa hề xăng bày đến cái sắc đẹp không phải của mình, vậy người toan lấy vật là để chức lay chuyện ý chí của ta đó chẳng? Thời muốn tốt thì người phải đem ngay đi chỗ khác. Chả thế mà trong lúc phu quí như vậy ông vẫn chẳng mua nàng hầu, trong phòng chỉ có mỗi một phu-nhân là người xe to kết tóc từ lúc hàn vi thôi, bởi thế nên ông thường bảo con cháu: Ta dầu không theo kip cờ nhân, nhưng cũng chưa hề phạm điều sắc giới, giữ được như thế tướng cũng khó thay. Nói tóm lại, sĩ phu thời ấy nhớ sự học vấn và đạo dức của ông đã gây nên được biết bao nhân tài. Tí như quan Bảng-nhơn Phạm-quang-Trạch ở làng Đồng-Ngạc, quan Thám-hoa Vũ-Thanh ở làng Đan-Luân và quan Hội-nguyên Nguyễn-danh-Dự ở làng Dương-Liễu, đều là các bậc khôi khoa, được đời tôn trọng và cũng đều là học trò của ông, khiến cho đời nay người ta vẫn còn ngưỡng mộ, vậy.</t>
+          <t>Tương xem ngũ đoàn thực phi thường, Hồ thì làm giai chí bốn phương.</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>廉蔣公遺記武娶唐安穫澤人也</t>
+          <t>一門伯神光前養子載明良結主知</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VÕ-TU. — Ông Võ-Tu người làng Hoạch-Trạch huyện Đường-An thì đã Hoàng-Giáp khoa qui-sửu thời Lê Hồng-Đức, ông vốn có tánh liêm-khiết và ngay thẳng, ngay lúc làm quan cũng vẫn giữ nếp thanh bạch, không hề lấy lễ của ai, giữa lục ấy cái tệ tham những dương hoành hành. Hoàng-Đế muốn bắt chước Vua Đường Thái-Tông ngày trước, cũng sai người giả làm dân thường đem lễ đút lót các quan, quan nào cũng nhận, duy có mình ông nhất định cự tuyệt, người đưa lễ có nài nói rằng: hiện nay phong tục hối lộ đã thành thói quen, và lại một món quà đây cũng chẳng đáng giá bao nhiêu, nếu Ngài nhận cho thì cũng không hại gì đến tiếng liêm khiết.</t>
+          <t>Nếp cũ thêm tươi hàng bá trọng, Ngàn xưa dẳng gặp chúa mình lương.</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>浙陽省洪德韜聖宗癸丑科中黃甲公性顔廉直居官清儉未嘗妄取于人時頗尚賂遺用唐太宗故事使人懲誡試之他官従従受之公獨見拒饋請人固請曰今習尚如此寢以成風且這條菲物而相公不受為傷廉也</t>
+          <t>應變有才施達政稱乎各營檔于時</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ông thấy người kia cổ tinh nài ép thì nghiêm sắc mặt mắng rằng: nhà người nên nhớ: Thế gian đều trọc, chỉ có một mình ta thanh! nhẽ nào ta lại vi câu nói ngọt và món lễ hậu của người mà dồi tiết tháo, người phải đem đi tức khắc!</t>
+          <t>Khen tay chính trị tài thông biến. Giữ mực công minh tiếng chẳng nhường.</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>公作色曰世人比自而獨我独清豈以爾甘言而易其樑驅而出之其人固奏帝嘉其人有暮夜卻金之郎賜公廉二字許入朝黏于衣領以旌異之仕到刑部左侍郎廉節各良家無祖石之儲而怡然自適所得寸禄僅足代耕有薄田數高不以遺其子臨終嘆許本社為祀田蓋取白清遺子孫之意邑人重其義香火不絕至今猶存焉</t>
+          <t>無殊榮盛多非偶種德卑閥是我師</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Người đem lễ bị ông quát đuổi, đem lễ ra về, vào tàu với vua như thế. Vua khen là người biết trọng khí tiết cũng như các vị thanh liêm thời trước chẳng chịu nhận vàng trong lúc đêm khuya. Vì thế Ngai mới ban cho hai chữ Liêm tiết, và cho định vào cờ áo trong lúc vô triều cốt để nếu cao phẩm giá, rồi sau ông cũng làm đến chức Thị-lạng bộ Hình, thế mà bồng lộc cũng chỉ tạm đủ chứ không dư dật, ruộng nương cũng chỉ có được 3 sao, ông cũng chẳng chia cho con, đem cùng cho xã để làm tự điển, tỏ ý chỉ để hai chữ thanh bạch lại cho con cháu mà thôi. Vì thế nhân dân trong xã thấy đều tôn kính, lập đến phung sự hương khói ngát mãi đến nay.</t>
+          <t>Con cháu vinh hoa âu cũng bồi, Ai giống cây đức để làm gương.</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>陳瑋記陳佛璋慕澤人也</t>
+          <t>宰相武惟志記</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TRẦN-THƯƠNG.— Ông Thường người làng Hoạch - Trạch dỗ Tấn - sĩ khoa giáp-thin thời Lê-Kính-Tông 1600-1619 (niên-hiệu Hoàng-Định.) Ông vốn có tính liêm trục, khi làm Hiến-Sát-Sư Tỉnh Nghệ-An, trong xứ có vị Quốc-cữu ỷ thế làm can chẳng kiêng nề gi pháp luật, nhân dân bị khổ làm đơn kêu quan kẻ đến hàng tập, quan có mời đến cửa công phân xử thì ông Quốc-cữu quát tháo om xóm, Quan cũng phải nhận. Ngày nay ông vừa đảo nhậm, đã nhận được rất nhiều đơn, ông bèn thira dip bắt về công đường tra tấn đến phải bỏ mạng. Bọn gia nhân của Quốc-cữu nghe được tin này bèn kéo nhau đến vậy kín tư thất định bắt ông phải đến mạng.</t>
+          <t>MỘ-TRẠCH TÈ-TƯỚNG KÝ</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>弘禎檢中興後甲長科中進士為人廉直初為乂安憲察侯時本處有國舅舅恃勢驕橫無所畏避徑徑肆行不法人奏是之其訴章堆積每有公事到輒行欺侮他官亦無知之何自公到者任他尙黠愈滋訟牒交至耶</t>
+          <t>宰相武惟一，燕澤人也，曾祖刑部員外郎晚年二接鄰時舉社吳村教授性畏水蛭一日初有洛沂風雩庶意出村頭池塘清水麗濯綢童子五六尾之纔經伊村園處見一堆圓彙微高顧童生戲指之曰師百歲後當於此封墳則水煙不融近也</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ông với thoát xuống một chiếc xưởng đánh cá chạy về kinh sư, bỏ mũ xuống sàn chính đường khấu đầu tạ tội: Thân nay làm giữ chức vị Hiến-ty phải vi Triều-dinh thi hành pháp luật, thế mà Quốc-cữu lại dám ngang tàng khinh thường quốc pháp, vì thế trong lúc quá giận thân đã lỡ tay, vậy xin về nơi của quyết chịu tội dưới lưỡi riu búa thân cũng cam tâm!</t>
+          <t>Tè-tướng Vô-duy-Chí người làng Mộ-Trạch, Cự tam đại trước đã làm đến chức Hình-bộ Viên-ngoại-lang, đến khi già tuổi về hưu, Cự sang dạy học ở làng Thời-Cử Thôn-ngư bên cạnh làng Cự. Nguyên Cự có tính sọ địa, nhân có một hôm Cự nhớ đến cái thanh thú của đức Khổng-phu-Tử ngày trước cùng các món dẹ đi tắm sông Nghi rồi lên hông mát ở nền Vũ-Vu, Cự bên dã 5, 6 đồng sinh ra ngay cái hồ nước trong ở chỗ đầu làng, định để giặt áo, chẳng ngờ khi ra khỏi một đầm rừng cây thì thấy có một gò đất hình tròn và cũng khá cao. Cự bên trở vào mò đất nói bốn với học trò rằng: Nếu thấy trăm tuổi các anh nhớ đem tàng trên gò đất cao kia thì địa không sao lên được.</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>同世間清善拿回杳尋機殺之他黨聞知遂至公家圍過意欲報仇公急下漁舟倍道而去既至京師即自詣政堂免冠頓首謝曰臣誠忝意司為朝守法而國舅杭弄雖行臣一時憤激不覺已過手了今伏闕待罪斧鑕是甘錦上訊問之有知其事乃獎諭曰設官以爲民風憲祛除民害可謂稱職何罪之有公拜謝而長再歸任所自是豪彊畏服境南然後奉北使仕至吏部左待郎贈少保知都公</t>
+          <t>及卒家人追念其言郎將伊廣塗之</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hoàng-Thượng thấy ông tâu trình như vậy, lập tức tra hỏi nguyên do, về sau biết rõ công việc thì lại khen ngợi và dụ cho ông biết rằng: Triều đình đặt ra quan chức là để vì dân, ngày nay Hiến ty trù được mới hai cho dân thế là xưng đáng với chức vụ chứ còn tội gì. Nghè lời dụ xong ông liền bài ta lui ra rồi lại trở về Ty cũ, từ đấy về sau cương hào trong hạt thấy đều kiệp sợ, chẳng dám ho he, nhân dân nhờ được an cư lạc nghiệp, rồi cách ít lâu thì ông phượng mang sang sứ Bắc - quốc, rồi làm đến chức Tả Thị-lạng, lúc về hưu lại được tặng chức Thiếu-phó tước Hương-Quân-công.</t>
+          <t>Thế rồi cách mấy năm sau Cự mất, người nhà nhớ lại câu nói ngày trước, đem đi hai ra an táng tại đó.</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>狀元莫擬之記陳朝為國欲元首大擬之字節文至靈龐洞人也</t>
+          <t>今按此地前接有茆浮水面桃後有升鳯郵書坐乙向辛風水師以為天蓋吉司子孫必發公候之貴</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mạc-Công-Đinh-Chi, tên tự là Tiết-Phu, người xã Lũng-Đông thuộc huyện Chi-Linh.</t>
+          <t>Ngày nay xét ra thì cái gò ấy có một con đất vuông vẫn mọc tại giữa hồ tức là khẩu ấn để làm tiền án, còn ở phía sau tức là hậu chẩm, thì có một con đất giống hình Đan phương hàm thư Chim phương ngậm thư, ngoài mộ ngồi vào chử Ất trong ra chử Tân, về sau các thầy Địa-lý bảo rằng: đó là cục đất trời cho, sau này sẽ phát Công hầu khanh tướng!</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>史記旁河人李朝尚書莫令徵績之孫也</t>
+          <t>惟志之母素有陰德少時往市間販買適有鬻綿緯者於眾人喧鬧中遺棄綿一束而去</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sử-ký chép người xã Bàng-Hà, nhưng xét thấy từ đây Đột- Lãnh trở xuống, tất cả một dài ven sông, theo bản đồ cũ đều thuộc về xã Bàng-Hà, cho nên ngày nay ngôi chúa của làng Lễ-Xá cũng thấy kêu tên là chúa Bàng-Hà, đó cũng là một chứng có vậy. Ngải vón là cháu quan Thượng-Thư Mạc-hiền-Tích Triệu Lý ngày trước. Quan Thượng-thu thì đồ Tấn-Sĩ đệ nhất danh khoa Bình-Dân thời Lý Trung-Tông, làm đến Thượng-Thư bộ Lại và được nhà vua bán cho bộ áo kim-ngư (cả vàng), em là Kiến-Quan cũng đồ Tấn-Sĩ làm đến Công-bộ Thượng-Thư, còn ông Trang đây là cháu cụ Hiền-Tích, tên tục gọi là Sách-Tú, (vì xã Lũng- Đông quen gọi là Kẻ-Sách, cho nên mới có tục danh như thế). Nay cứ theo như tục truyền, thì nơi làng Ngải có một cái gò rất lớn, cây cối um tùm, tức là chỗ ở của loài khí độc. Một hôm, thân mẫu của Ngài lên đó kiếm cùi, bị con khí độc hãm hiếp, trở về thuật lại với ông (tức thân phụ Ngài), ông bèn cải trang dân bà, trong mình dẫu con dao nhọn, rồi cũng giả vờ lên núi hải cùi. Khí dục lại quen thói cũ nhảy ra, liền bị ông dâm cho một mũi dao chết ngay tại chỗ, rồi ông quay về. Sáng sớm hôm sau, ông ra coi thử thì thấy xác con khí độc đã bị mồi dùn thành một cái mò rất lớn. Ông rất lấy làm kỳ.</t>
+          <t>Nhắc lại nhà ông Duy-Chí, bà cụ thân sinh người rất hiền lành phúc hậu! khi còn ít tuổi Cụ cũng tần tảo bán buôn ở các chợ búa, một hôm dương lúc chợ đông, thấy có một chị bán hàng to lụa trong khi vội vã xếp gánh đi rồi mà còn bỏ sót lại đó một cuộn.</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>李仁宗廣祐二年徵績中進補翰林學士世傳鄉有大陵阜林木鬱茂沐猴居之其母常往刈薪為雄猴所脅歸諸其父父遂服婦人衣懷刀往焉</t>
+          <t>志哥已按取藏之頃之見一婦前來吐號尋覓母盡因問端的盡以付還</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Về phần mẫu thân, sau khi bị khí hãm hiếp chẳng ngò bà thụ thai, đủ ngày tháng sinh ra một cậu con trai, người thấp lè tè, tướng mạo trong rất xấu xí, ai cũng bảo là giống khí. Vi thế, đến lúc phụ thân sắp sửa làm chung, Cụ có di chức lại rằng: phải tàng Cụ lên trên mò con khí đó, chắc rằng Cụ cũng hiểu ngầm thiên cơ nên mới hẹn như vậy. (Rồi sau Tràng Mạc-Định-Chi, lúc mất, cũng tàng ở phía dưới chân, ngày nay vẫn còn đủ cả). Nói về Tràng Mạc-định-Chi, diện mạo tuy xấu nhưng rất thông minh, gặp lúc Hoàng-tử Chiêu-Quốc-Công mở rộng học đường để dạy sĩ tử, ông xin vào học, đến khi tuổi gần hai chục, thì đồ Tràng-nguyên vào khoa Giáp- Thìn đời Trần-Anh-Tông (1.304); tất cả Thái-học-sinh nội thư-gia được về đối sách, thì ông đồ đầu, chỉ vì nhà vua thấy ông tướng mạo thơ lỗ nên không muốn cho đồ Tràng. Vi thế ông mới soạn ra bài phu Ngọc-Tỉnh-Liên, để vì với mình, đại ý nói rằng: sen ở trong giếng, tuy rằng sinh ở chổ thấp nhưng nó vốn là quí vật. Nhà vua xem qua bài phu hiệu rõ thâm ý của ông, nên lại cắt lên dỡ đầu. Thi đỗ xong, ông bắt đầu xuất chính, lần lượt qua mấy chức vị, rồi phượng mang sang sứ nhà Nguyễn. Trước khi đăng trình, đã hẹn đúng ngày sẽ tới cửa ải, vì mưa gió thành sai hẹn, bị người coi giữ cửa ải chặn lại, ông phải hết sức bày tỏ duyên có, viên ấy mới thuận, nhưng bắt buộc phải đối ngay một câu thi mới mở cửa cho vào.</t>
+          <t>Cụ bên nhặt lấy xếp vào gánh hàng của mình, rồi một lát sau thấy chị bán to quay lại tìm kiếm không được gào khóc rất thâm thương! Cụ gọi lại hỏi chị kia mặt mát thứ gì? Thấy chị hàng to khai đúng, Cụ bên tra trả cuộn hàng cho chị,</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>猴狙故態以又遂提刀擊斬殺且長從視之見土虫已將假冤墳成一堆艾異之母尊受胎暮年生公資相卑陋人以為假精之聽其父臨終遺言百塗猴墳之上至亦默會天機也</t>
+          <t>賣絹婦德之以二匹致謝志哥笑曰取此二匹寧為取一束之多耶我憐汝失物囘歸必被夫兒痛責故見還耳豈望謝耶一市環視者皆稱其賢</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yế đối ấy tự trên cửa ải ném xuống như sau:. Quá quan tri, quan quan bế, nguyên quá khách quá quan. Ông liên đối lại rằng: Xuất đối di, đối đối nan, thính Tiên-sinh tiên đối. Nghĩa về trên: Tới quan chật, cửa quan đồng, mới quá khách qua cửa khác. Nghĩa về dưới: Ra đối dễ, đối lại khó, xin Tiên-sinh đối trước cho. Viên coi giữ cửa ải thấy ông ứng khẩu đối ngay, rất phục là nhanh, bèn sai mở rộng cửa ải đón tiếp sứ bộ. Sang qua cửa ải Nam-Quan, ông cùng sứ bộ tiếp tục lên đường, khi tới Bắc-kinh triều thần nhà Nguyễn thấy ông thấp bé có ý kinh thường. Một hôm Tề-Tướng cho mọi vào phủ, giữa lúc đương ngồi nói chuyện, ông thấy trên bức trường gấm có thêu một con chim trước sắc vàng, đậu trên cành trúc, trông hết như con chim thực, ông tiến lại gần gior tay toan bất, các quan nhà Nguyễn cả cười, chè là ngơ ngẩn. Ông bên xe nát con chim ấy ra, khiến cho mọi người kinh ngạc, hỏi có tại sao. Ông ung dung đáp: Tôi thấy cờ nhân chỉ về Mai-Tước, chứ chưa thấy về Trúc-Tước bao giờ. Có sao bức trưởng của quan Tề-Tướng ngày nay lại thêu cái hình Trúc-Tước.</t>
+          <t>chị rất cảm ơn, rút ra 2 tấm để tạ, nhưng Cụ mỉm cười bảo rằng: nếu tôi có lòng tham của, nhận 2 tấm này chẳng tha tôi lấy cả cuộn (súc) có nhiều hơn không. Chỉ vì tôi thấy cũng chở chị em bạn hàng nay bị mất của, tất nhiên lúc trở về nhà sẽ bị chồng đánh đập tội thân, nên tôi mới tra trả lại, chứ có mong gì, tạ ơn, rồi Cụ nhất định không nhận, khiến cho các người trong chợ ai cũng ngợi khen là người phúc hậu!</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>其後公沒附葬其下今猶存焉</t>
+          <t>世常愛堂前有五色雲現親自抱之俄而春紅雲光散</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>( Trúc-Tước, Mai-Tước). Ôi! Trúc là bản sắc của người quân-tử! Tước là hình dáng của kẻ tiêu-nhân. Ngày nay Tề-Tướng cho thêu như vậy, thì tiêu-nhân lại dẻ lên trên quân-tử? Tôi sợ đạo của tiêu nhân lớn, thì đạo quân-tử sẽ tiêu, nên tôi phải vi Thành-đế trù khứ đi ngay.</t>
+          <t>Hôm ấy Cụ trở về nhà, đêm nằm mơ thấy có 5 sắc mây hiện ra trước mắt. Cụ bên ôm cả vào lòng, nhưng chỉ giây phút thì thấy mây xanh mây hồng tan ngay tức khắc.</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>公生而穎異資稟過人年既冠登陳英宗甲辰科中狀元上以公資質贊卑陋不欲與狀元公乃作五井蓮華賦以自祝蓋謂蓮花井中雖卑而可貴上覽之而悟遠置上第歷任各職往北使與北人限日至交關阻風雨失期為北人所拒公婉辭致請北人寫對句自開上板揭有曰到關邏陽陽開願過客過關公立對云出對易對對難願光生光對北人服其敏開開賜進至北朝元人以卑小陋之一日宰相召八府與坐有薄帳綿黃雀在竹枝上公以為生雀都就摘之元人笑其鄙陋公遂裂之眾人驚怪公應曰我聞古有梅雀畫未開竹雀畫夫竹君子也</t>
+          <t>後生五男其一自快少有大志年二十七適長安睹扶花公子為王所重愛人情廣明之而弘祖陽王深自韜晦每朝侍日公執就府竊視之見挾花華止言繚知其成之器一見而異之曰此聖才也即行下其後以潛邸功臣官至左侍郎忠都公</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Câu giải thích đó làm cho ai cũng khiếp phục về tài hùng biện hơn đời. Lúc ấy lại có người ở ngoại quốc đem quạt vào dâng, Nguyên-đế bèn sai ông cùng Sứ-thần Cao-Ly mỗi người phải làm ngay một bài tán. Sứ Cao-Ly làm xong trước, có những câu rằng: Uân long trùng trùng. Y-Doãn Chu-Công; Vũ tuyêt thê thê, Bá-Di Thức-Tề. Nghĩa là: Khí nóng bùng bùng, Y-Doãn Chu-Công; Mưa tuyêt đầm dia, Bá-Di Thức-Tề. Ý nói mùa hạ nóng nực, thì cái quạt đắc dụng như hai ông Y-Doãn Chu-Công. Đến mùa đông giá rét thì cái quạt bị chết là như hai ông Bá-Di Thức-Tề. Giữa lúc ấy thì ông chưa nghĩ xong, nhưng khi liếc sang đầu quân bút của sứ Cao-Ly, ông đã biết rõ những câu như thế, ông bèn nhân cái ý đó để suy diễn thêm một bài rằng: Phiên âm: Luru kim thược thạch, thiên địa vi lò! Nhĩ ư tư thi hề, Y-Chu cự nho. Bắc phong kỳ lương, vũ tuyệt tái đồ, nhĩ ư tư thi hề, Di Tề nga phu.</t>
+          <t>Về sau Bà sinh đặng 5 con giai, ứng nghiệm với điểm 5 sắc mây trước; 5 con giai là: Người thứ nhất gọi Tự-Khoái, lúc còn thiếu niên đã có chí lớn; đến năm 17 tuổi ra thăm kinh thành Tràng-An, giữa lúc Công-lử Phù và Công-lử Hoa được Hoàng-Thượng yêu dấu đặc biệt, ai cũng trong vào. Nhưng mà Hoàng Tồ Dương-Vương thì rất kín đáo. Cứ mỗi phiên châu Cậu Khải thường vào công phủ ngô trộm, xét thấy cứ chỉ đáng điệu của hai công-tử thì Cậu đoàn biết không phải là người làm nên to tát, nhưng khi thoát nhìn thấy mặt Hoàng-Tồ thì Cậu đã lấy làm kỵ, biết rằng con người có tài thành trí, bèn xin vào làm môn hạ, rồi sau được dự vào hạng Tiêm-đề Công-Thần tức là công thần từ trong Tư thất.</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>雀小人也寫相續此是以小人加諸君子之士上恐小人道長君子道消故為聖朝除之耳</t>
+          <t>其二校萃田戍科進士官至寺鄉</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Y: dụng chi tắc hành, xả chi tắc tàng, duy ngã dữ nhĩ hữu thị phu? Nghĩa là: Nấu vàng nung đá, trời đất như lò, thì người lúc ấy khác gi Y-Chu nói tiếng bắc cự nho. Gió lạnh buốt xương, mưa tuyệt đầy đường! thì người lúc ấy cũng như Di Tề nhìn dồi trên núi Thu-Dương. Ôi! Dùng thì ra giúp đời, bỏ thì tạm ẩn để chờ thời, chỉ ta với người có thể ôi. Viết xong bài trên ông tiến trình lên, Thiên-Tử nhà Nguyên coi xong chợ là hay, cảm bút khuyên vào câu có chữ Y và phê 4 chữ Lưỡng-Quốc Trạng-Nguyên. Thế là bài tán đề quạt của ông dẫu rằng thoát ý và làm xong sau, nhưng mà lại được Thiên-Tử nhà Nguyên thường thức hơn bài của Sư Cao-Ly đã làm xong trước vậy. Trong thời gian còn ở Bắc. kinh, một hôm, ông cởi lừa đi đạo phố, chẳng may con lừa của ông xó vào con ngựa của quan nhà Nguyễn. Vị quan ấy bên đọc mấy câu như sau:?</t>
+          <t>Người thứ hai tên gọi Bạt-Tuy, thì đồ Hoàng-giáp khoa Giáp thin (1484) làm quan đến chức Tự-khanh.</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>眾服其能及進朝適外國進殤元帝命公與高麗使賛之高麗使先就其詞曰韞隆蟲蟲伊母周公涼雨淒淒伯夷叔齊公未哀體制望其他筆管遂因而推演之曰流金爍石天地為爐汝於斯時兮伊周臣儒北風其涼雨雪載途汝癸斯時兮夷齊戮夫隱用之則行舍之則藏惟我共爾有是夫既成竝進天子眷懷伊司嘆賞不已封兩國狀元其在北國與北人遇于途公乘驢觸其馬北人誦之曰觸我騎馬東夷之人也</t>
+          <t>其三両子皆功臣進用惟志至宰相方夫至尚書曰距封都爵其</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>? Xúc ngã ky mã, đồng di chi nhân dã? Tây di chi nhân dã? Nghĩa là: Xó vào ngựa ta? hỏi người ở Mán đồng đó hay người ở Mán tây đó? Ngài ứng khẩu đối:? Át dư thừa lư, Nam phương chi cương du? Bắc phương chi cương du? Nghĩa là: Ngáng đầu lừa của ta, hỏi phương Nam mạnh du, hay phương Bắc mạnh du? Lại có một hôm ông cùng các vị thân sĩ nhà Nguyễn bàn luận văn chương, vì muốn thử tài, họ thay phiên nhau để ra câu đối, câu thứ I là: Kỷ dĩ mộc, Bồi bất mộc, như hà dĩ kỷ vi bồi? Câu này thuộc lối chấp chữ: như chữ kỷ thì hợp 2 chữ: dĩ và mộc. Chữ Bồi thì hợp 2 chữ: bất và mộc, có sao lại dùng gố kỹ làm chén rượu, và họ ám chỉ ông cũng lùn như người nước Kỷ, có sao lại được trọng dụng?</t>
+          <t>Người thứ ba, tư cũng đều là bậc công thần tiến dụng; Duy-Chí làm đến Tề-tướng, Phương-Đại làm đến Thượng-thư, đều phong tước Quân.</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>西夷之人也公應之曰遇予乘驢南方之彊戰北方之彊歟又常共北人對答北人出對曰杞已木梧否木知何以就為稽公對曰僧曾人佛弟子人何如以僧奉佛安者安以來為家公對曰因與人他王成國北人批云後世子孫當有王者但單字享國不長北人尚對曰日火雲煙白旦燒殘玉魄公對曰月弓星彈黃育射落金烏北人批云後世子孫必有慕人國北人尙對云魑魅魍魎四十四鬼蓋陋其卑小也</t>
+          <t>其五求諭又已亥科中進士仕至參政</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ông đối rằng:,, Tăng tăng nhân, Phật phát nhân, vân hồ dĩ tăng sự phật. Nghĩa là: chữ Tăng thì hợp chữ Tăng với chữ nhân, chữ phật thì hợp chữ phát (là chẳng phải) với chữ nhân, có ý bảo các chú người Mông-Cổ con cháu nhà phật. Nhưng phật chẳng phải là người, nhẽ đâu lại bắt Tăng (tức chúng tôi) thờ phật. Câu thứ II là:. An khứ nữ, dĩ thi vi gia. Nghĩa là: chử An bồ chử nữ thay chử Thi là heo vào, thành chử gia là nhà. Ông đối lại:. Tự xuất nhân, nhập vương thành quốc. Nghĩa là: chử Tự bồ chử nhân ra, cho chử Vương là vua vào, thành chử quốc là nước.</t>
+          <t>Người thứ năm tên gọi Cậu-Hối đồ Tấn-sĩ khoa Kỷ-hội, về sau làm đến Tham-chánh.</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>公對曰髮鬢琵琶八大王北人北北云後世必為血食之神北人對云鳥呼枝頭談嘗論知為知爭知為不知是知蓋以默音譏南人也</t>
+          <t>自快常通六囊惟志方大皆自功成各遍相繙引年其六校萃求謝出由青紫比途而宦秩書科不異一門倡伸始信青紅先敬之聽</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Họ chịu phục câu đối này là tài, nhưng lại phê vào rằng: Con cháu sau này tất nhiên có đời làm vua. Chi hiềm chử quốc viết đơn, thì giữ nước cũng chẳng được lâu dài, (chử quốc viết kép viết đơn như ở trên). Câu thứ III:,. Nhật hỏa vàn yên, bạch trù thiếu tân ngọc thô. Nghĩa là: mặt trời là lừa, đàm mây là khói, tảng sáng đốt tan thô ngọc. Ông đối lại:,. Nguyệt cung tinh dạn, hoàng hôn xạ lạc kim ô. Nghĩa là: vành trăng là cung, sao là dạn, bóng hoàng hôn bắn rụng ác vàng. Câu này họ lại phê rằng: Đời sau con cháu tất nhiên có người cướp nước. Câu thứ IV:. Ly My Vọng Lạng từ tiêu quỉ. Nghĩa là: 4 con quỉ nhỏ trên đều có chử quỉ một bên.</t>
+          <t>Xét ra Tự-Khoái được vua tri ngộ ngay lúc thiếu thời, thế mà lương thọ cũng ngoài sáu chục (60), còn như Duy-Chí, Phương-Đại cũng đều công thành danh toại, vinh quang đến lúc tuổi già, riêng có Bạt-Tuy Cậu-Hối xuất thân trong hạng khoa cử áo tia đại xanh thì lại phẩm trước thọ khảo đều kém anh em, do đó người ta nhận thấy cái điểm mây xanh, mây vàng tan trước quả thiệt ứng nghiệm.</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>公以類蛙聲應之曰蛙鳴池上讀鄒書樂獨樂樂共飛樂樂亂樂北人吾對云洛水神邕單應兆天效五地效五也</t>
+          <t>惟志達於吏事輔以文學侍陽玉潛印頗見親幸</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ông đối lại:. Cầm sắt Tỳ-bà bát đại vương. Nghĩa là: 4 cây đàn trên đều có 8 chử vương. Câu này họ phê rằng: Về sau sẽ được làm phúc thần. Câu thứ V:. Quách tại tường đầu dâm lỗ luận: Tri chi vi tri chi, bất tri vi bất tri, thị tri. Nghĩa là: Con chim quách đậu ở đầu tường, nó học đòi nói những câu sách Luận-ngữ: Biết thì bảo là biết, không biết bảo là không biết, ấy là biết. (để ngụ ý chê ông cũng như con chim học nói). Ông liền mượn ngay mấy câu trong sách Mạnh-Tử cũng có những tiếng đối lại rằng:. Oa cư trì để độc Trâu thư: Nhạc dữ thiểu lạc nhạc, nhạc dữ chúng lạc nhạc thực lạc. Nghĩa là: Con ếch ngồi đáy giếng đọc sách của ông Mạnh-Đức (Trâu thư): Vui với người ít cũng vui, vui với người nhiều lại càng vui thực. (lấy tiếng ộp oạp của ếch để đối với tiếng lích chích của quách, thành ra âm thanh đối với âm thanh).</t>
+          <t>Nhắc lại Duy-Chí là người thông suốt việc quan và có biệt tài về văn-chương, nên khi vào giúp Dương-Vương ở trong tư phủ, được Vương tín nhiệm hơn người.</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>五十五效效威混三大道道合元始天尊一誠有感公對曰峻山靈鳳兩星神雄聲六雌聲十六聲徽九章大天生嘉靖皇帝萬壽節無疆其對答出只成章無少為者又北朝后妃薨臨簽命公讀祝就讀但見空紙紙上有遺一字公即哭而讀之其词曰天上一朶雲空中一點雲子閾苑一枝花廣寒一片月噫雲散雪消花殘月缺北人大談焉</t>
+          <t>時廣南有阮賊高平有莫澤子公從鸞勒間多有熱勞</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ông biết họ chực thử mình, nhưng văn trình trong đọc ngay lên rằng: Thanh-thiên nhất đóa vân, hồng-lò nhất điểm tuyết; Thượng-uyển nhất chi hoa, Quảng-hàn nhất phiên nguyệt. Y! Vân tán tuyêt tiêu, hoa tàn nguyệt khuyet. Dịch nghĩa: Trời xanh 1 đám mây, Lò hồng 1 điểm tuyệt; Thượng-uyên một cảnh họa, Cung quảng một vùng nguyệt. Ơi! Mây tân tuyệt tiêu, hoa tân, giăng khuyết. (Bốn câu trên đều có 4 chữ nhất là một). Đọc xong bài văn tế trên, tất cả vua tôi nhà Nguyễn đều phục là bức thiên tài!</t>
+          <t>Gặp lúc trong vùng Quảng-Nam có quân Chúa Nguyễn nỗi giây, trên vùng Cao-Băng thì có con cháu họ Mạc quấy rối, ông vẫn theo bên cạnh Vương, lập được rất nhiều công trạng.</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>異嘆服其文公在北朝北人大奇其才而察相貌無可責者乃直公出則潛往視之見便薺分方謂公有隱相所貴在此分還北人往我國認其墳塋稱公乃禀生之地但水不亭留故不富耳</t>
+          <t>有駕大海調糧有險高山齊舟有隔千里陳事累差稱旨以致寵遇日隆至拜參政宰相</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>(bài văn ấy vẫn còn ghi trong bắc-sử, thế mà về sau lại có người bảo: bài ấy là của Lý-Bạch, nhưng ta xét kỹ về lời và ý, thì thấy giống như văn thể của ông. Tuy thế chưa chắc đã phải, bởi vì bài thơ đề quạt dịch là của ông. Thế mà trong sách Thuyết-Linh lại chép là của Phương-hiệu-Nho, lấy đó suy ra, thì sử sách bên Tàu chép về việc ấy chắc gì đã dùng vậy). Nhắc lại trong khi ông ở bắc-triều thì người nhà Nguyễn thấy có kỳ tài, nhưng xét tướng mạo không thấy có gì đáng quí. Họ bèn đợi lúc ông đi sau xong trở vào, họ mới lên ra quan sát thấy những hòn phân, vuông như quan cơ, bấy giờ họ mới bảo nhau: đó là ẩn tướng rất quí. Nhưng rồi sau khi công việc xuất sứ hoàn hảo, ông trở về nước, họ còn phải thấy địa-lý theo sang để xem phong thủy đều ta, nhân tiện ông có dẫn họ xem lại phần mộ tò tiên, ngôi nào họ cũng lắc đầu bảo rằng không được, sau cùng dẫn đến ngôi mộ phụ thân, thì họ tấm tắc khen ngôi bảo rằng: đây mới chính là ngôi mộ phát tích. Nay ta xét lại hình thế, thì ngôi mộ ấy quả nhiên đẹp thực, đầu đến các thầy địa-lý tầm thường cũng biết là qui cách. (cục này chép kỹ ở sách địa-lý ông Hòa-Thúc ). Hiểm rằng thủy không tu mấy, nên chỉ phát quí mà thôi, chứ không phát phú. Xét thấy trong đời làm quan của ông rất trong sạch, về cách cư xử âm-thực cũng chỉ giữ mực thường thường, vua Trần Minh-Tông hiểu rõ tinh tinh của ông, nên có sai người đem 10 bó tiền, rinh lúc đêm khuya thanh vắng bỏ vào trong cửa, sáng sớm hôm sau, khi ông thức dậy không biết là tiền của ai, vội vàng vào triều tàu để vua biết. Vua phân rằng: Tiền không có chủ thì khanh cứ việc nhận lấy chứ có hề chi; đức tinh thanh liêm của ông đại đề là như thế đó. Cho nên về sau Văn-hiên tiên-sinh có làm bài thơ tứ tuyệt để ca ngợi rằng: Phiên âm Đệ nhất khôi nguyên tạo trí thân Cư quan bất cải cựu thanh bản Phiến minh hựu trọng Yên-dài dự Sử tiết phương tri quốc hữu nhân Dịch Chiếm giải khôi nguyên tự thiếu thời, Quan sang vẫn giữ nếp nghèo thời, Yên-kính đã trọng thơ để quạt, Cò Sứ nếu cao, nước có người. Nói về đức tánh thì trong lúc qui hiền, ông vẫn giữ được nếp thanh bần, nên mới dễ phước lại cho con cháu.</t>
+          <t>Có khi vượt bê vận lương, có lúc lên rừng dốc chiến, lại còn những lúc ở xa ngàn dặm gửi kế sách về cũng đều hợp ý, nên ông lại được chúa ưu đãi hơn xưa. Chỉ sau mấy năm đã lên đến chức Tham-tung Tề-trương, khiến cho đình thần ghen tị, mà ông là Nha lại xuất thân.</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>公為官廉潔薄於自奉故其慶番後人于各覩員外郎孫各迪各遂各遠皆有執力共列顯貴其後吳平亦不父難莫遂子孫綏濟青河廣漢三世乂綏居宜陽蘇古齋社生莫太祖登庸篆織而有天下實狀元五世孫也</t>
+          <t>朝臣有吏道為言王聞之即歷敘蕭曹為趙事業依鮮疑論以示群臣焉</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Con trai như các ông Khẩn và Trực; cũng đều làm đến Viên-ngoại. Cháu là Dịch, Toại, Viễn,, đều có sức khỏe, gặp lúc nhà Hỏ cướp ngôi, nhân thấy cha ông ngày trước làm tới nhà Trần, nên vẫn ôm chí phục thù, đến lúc Minh-đế sai Trương-Phụ đem binh sang đánh nhà Hỏ, đại binh đóng ở Bắc ngạn sông Phú-lương, họ Hỏ bắt hết nam phụ lão ấu trong nước ra để cố thủ. Trương-Phụ không rõ hư thực ra sao, nên không dám vượt sang sông. Lúc ấy anh em ông Dịch nhận thấy có cơ báo thù, bèn từ Nam-sách lên lên Tam-đôi-Châu, hiệp lực với viên Thiềm-phán Đặng-Kinh đơn hàng Trương-Phụ đề báo-cáo tình-hình họ Hỏ. Vì thế quân Minh mới dám qua sông tiến đánh, luôn luôn thắng lợi. Trương-Phụ bèn dùng làm Hướng-đạo quan, rồi sau cùng với viên Hạ-hòa-mục là Võ-Thạch-Khanh, bắt được Hán-Thương và con là Nhưế ở núi Cao-Vọng. (việc còn ghi rõ trong Bình Binh-Giao Nam-Lục của Khâu-văn-Tráng biên soạn, ). Vì có công lớn nên được nhà Minh phong cho quan trước, Toại làm Tham-chánh, Dịch làm Chi-huy-Sứ, Viễn làm Diệm-Thiết-Sứ, về sau vua Lê Thái-Tổ bình được Ngọ, các ông cũng không mắc nạn. Riêng về phần Toại sau khi mất rồi, con cháu di cư vào vùng Ma-Khê thuộc huyện Thanh-Hà,, đến đời thứ 3 lại đi về làng Cổ-Trai cổ xã thuộc huyện Nghi-Dương rồi sanh ra nguy Thái-Tổ là Mạc-đăng-Dong, tức là cháu 7 đời của Trạng-nguyên Mạc-định-Chi vậy.</t>
+          <t>Chúa nghe thấy câu đó Ngài liền soạn lại những thiên tiêu sử nói về sự nghiệp Tiêu-Hà Tào-Tham ngày trước, để trao cho các đình-thần, cốt ý là muốn giải thích hộ ông về câu mỉa dọ. Phụ chú: Tiêu-Hà Tào-Tham nguyên trước cũng làm nha lại ấp Bái, về sau giúp Hán Cao-Tổ làm nên sự nghiệp để vương.</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1852,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>樗眼鄭鐵長記鄭鐵安矣</t>
+          <t>公章厚質直時春天正旦日正有旨文武殿朝禮訖各仍朝服詣政府</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TRỊNH THIẾT-TRƯỜNG người làng Đông-Lý thuộc huyện An-Định về người coi rất dĩnh ngọ, lúc còn thơ ấu chơi dưa với trẻ, cậu biết nặn con voi đất, rồi lấy bướm bướm làm tai, lấy dìa làm voi, hoạt động như con voi thực. Lúc ấy có ông quan phủ đi qua cũng lấy làm kỳ, nhân tiện có ra cho cậu một về đối rằng: Ngũ lục đồng vò như nhi xảo? Cậu liền hỏi lại: Vậy Ngài là quan chức gì?</t>
+          <t>Nguyên ông là người có tính trung hậu thắng thân, một năm nhân gặp ngày tết nguyên đán, chúa xuống chỉ du cho hà quan làm lễ triều điện xong rồi thì cứ đề nguyên áo mũ như thế vào mùng Chính-phủ.</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>東十里人也生而顴異少蓄與五六童子戲作大眾公以詡蝶為耳</t>
+          <t>道身共天道日月有光正氣崇禮言一介言青吉衣為正不宜還用朝服恐違舊制</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Quan đáp: ta đây là dường kim Thái-thủ ăn lương 2000 thạch đó; nghe xong Cậu đối ngay rằng:.</t>
+          <t>Ông bên tâu rằng: từ trước đến nay Vương thượng vẫn giữ tắc đa tôn phu, vậy thì buổi lễ hôm nay chỉ nên vân đồ thường phục mới phải, nếu vân triều y sự nữa không hợp với chế độ cũ.</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>水蛭為鼻宛如真形適有府官經過而異之因出對云童子五人六無知汝巧公曰敢問公是何官府官曰我是當今太守也</t>
+          <t>王從其言華為中止蓋亦有爭臣之風焉</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nhị thiên thạch mạc nhược công: Quan hỏi sao còn thiếu một chữ cuối? Cậu thưa rằng xin quan thường tiên rồi con sẽ có đủ. Quan bảo my đối không chính còn thường nói gì.</t>
+          <t>Chúa khen là phải thành ra việc ấy lại thôi, coi đó ta thấy ông là một người có đủ phong độ tranh thân đời cờ vậy!. Tránh thân là người bè tôi biết can gián vua,</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>公郎對云太守二千石莫若公府官曰欠一字省請賞府官曰汝對不發至何賞之有公曰太守二千石莫若公貪府官命賜綺錢公即改對曰莫大公若廉府官大奇之因喚公母至曰此子俊才當勉以學業必中魁元母依教遂勤以刻意讀書父長博學多能以文章名天下太寶篤志崇子虞科中進士使人來迎母赴京母不肯曰我從來望汝帶得魁元二字來明令都在人下任汝自為之我決不往</t>
+          <t>後以央部尚書國者老火保致仕於彩旗對句有云一代尊臣蕭相國兩朝元老趙韓王</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cậu bèn thêm ngay chữ tham tức là mạc nhược công tham, thành ra câu đối như sau: Năm sáu bê con chi có mây khéo, hai ngàn thùng thóc quả thực ông tham. Quan phủ nghe xong bên thường cho một quan tiên thi cậu lập tức dời ngay chữ tham ra chữ liêm, Quan phủ càng lấy làm la! sai người đi gọi mẹ cậu đến bảo: Con bà là một đứa bé tuần tù thông minh! Bà nên có gắng cho cháu đi học sau này thế nào nó cũng chiếm bằng khôi nguyên đó. Bà mẹ thấy Quan bảo thế nên cũng tìm thấy cho cậu học hành, đến khi lớn lên học rộng lại nhiều tài năng, văn chương lừng lẫy khắp cả thiên hạ!</t>
+          <t>rồi sau ông được về hưu với chức Lại-bộ Thượng-thư Quốc-lão Thiếu-phó, trong lá cờ hiệu có theo một câu đối rằng: Nhất đại tôn thần Tiêu Tương quốc, Lưỡng triều nguyên-lão Triệu Hàn vương, để vì ông cũng như Tiêu Tương quốc với Triệu Hàn vương ngày xưa,</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>其後與狀元青威且溪人同往北使公郎辭歸固學太和橘仁戊辰科再試遂中榜眼其後與狀元青威且溪人同往北使適天朝有會試科命諸國陪臣與中國舉人一體應試公與阮直入試文漸至半篇乃私與阮直語曰今審舊得先篤時惟我與兄耳</t>
+          <t>詩七十五贈太傅公</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>rồi đến niên hiệu Đại-Bảo (1440-42 Lê-Thái-tông) khoa thi nhâm tuất ông dỡ Đồng Tấn-sĩ, sai người về đón thân mẫu ra kinh thành, bà không chịu đi, bảo rằng trước đây ta vẫn mong rằng nó sẽ đoạt lấy hai chữ Khôi-nguyên đem về. Chờ còn ngày nay lại phải ở dưới người khác, thì mặc y nó, ta đây còn ra làm chi? Ông thấy mẹ già nói nhẫn như vậy lập tức từ giã kinh thành trở về học thêm, thế rồi đến khoa mẫu thin (1448) niên-hiệu Thái-Hòa, ông vào thi lại được trúng Bảng-Nhữn, rồi sau cùng với Trạng-Nguyên Nguyễn-Trực (người ở Bối-Khê thuộc huyện Thanh-Oai ) đỗ trạng năm nhâm-tuất, (1442) vang mệnh sang sứ Bắc-quốc, gặp lúc bên ấy mở khoa thi Hội, có lệnh cho các Sư thần cũng được vào thi với các Cử-nhan, Trung-quốc, hai ông cũng vào dự thi. Trong khi làm được nửa bài, ông bèn nói nhỏ với Nguyễn-công rằng: Cử chỗ tôi biết, phen này đoạt được giải nhất thì chỉ có tôi và quan bác đó thôi, nhưng văn từ của tôi có về rồng bay phương mùa, khó lòng có ai địch nổi.</t>
+          <t>sau ông hưởng thọ được 75 tuổi, lúc mất lại được tặng chức Thái-phó.</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>觀我文辭有起鳳騰蛟之勢未易與爭第思本朝間兄是狀元我是榜眼今以壓倒得兄則我國王必有選擇不精之吾兄意料如何阮直曰仕公規之既有遜讓之誠乞減其力俾我復欲元公復次檮眼可也</t>
+          <t>吳遼州太宰范公同時俗云慕澤寧相燕州國老蓋精權位之相軌也</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tôi tự nghĩ rằng: khi ở nước nhà bác là Tràng-Nguyên Tôi đây chỉ là Băng - Nhơn, vì bẳng ngày nay tôi lại ở trên quan Bắc, thì chẳng hóa ra Quốc-Vương tuyển lựa không tinh! vậy Bác định liệu thế nào xin cho đệ biết? Nguyễn công đáp: Việc ấy tùy anh định đoạt.</t>
+          <t>Ông cùng quan Thái-tề ở Liêu-Xuyên là Phạm-công-Trư cùng làm quan trong một triều đại, cho nên đời ấy có câu nói rằng: Tề-tướng Mộ-Trạch, Quốc-lão Liêu-Xuyên, là nói quyền vị tương đương với nhau vậy.</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>鄭公首肯既而行文有南之舟北之馬之句都塗馬字改寫予外馬有四點只見三點盡有司衡文鄭公宣猷充院道宣場眼但見鄭公寫自一字以北為為三足是蹤焉</t>
+          <t>其子惟諧已亥科中進士父子同朝</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vi thì anh có thành tâm nhượng lại, thì anh nên giảm bớt sức văn, để cho Ta vẫn giữ được Tràng-Nguyên, còn Anh vẫn giữ Băng-Nhơn là được. Trịnh công thấy Trạng đã vui lòng nhận lời, ông bèn trở lại chỗ ngồi đem quyền ra viết, khi viết đến câu: Nam chi chu bắc chi mã, nghĩa là phương nam giới nghề bơi thuyền phương bắc giới nghề côi ngựa, ông bèn xóa nhoe chữ mã rồi viết chữ khác một bên, chữ ấy lại chỉ chấm có 3 nét. Đến khi chấm bài Quan trưởng xét thấy văn của Trịnh công đáng dỡ Trạng-Nguyên còn văn của Nguyễn công thì đáng Băng-Nhơn, nhưng vì chữ mã trong bài Trịnh công thiếu mất một nét chấm tức là ngựa có 3 chân, khác chi ngựa què, có ý coi thường Bắc - quốc nên bị truất xuống một bực, rồi cho Nguyễn công được làm Lưỡng quốc Tràng-Nguyên Trịnh công thì làm Lưỡng quốc Băng-Nhơn!</t>
+          <t>Còn như gia thế của ông về sau thì có con là DUY-HẢI đỗ Tấn-sĩ khoa Kỷ-hội, cha con làm quan đông triều.</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>也似有輕中國之意即點一次乃許阮君為兩國狀元鄭公為兩國榜眼並賜榮歸本國使回日頒賜錦袍金笏兩袖廝馬儀用榮觀命防直前道簽程鄭公競自馬字其所頒廝馬仍簽一尺任使上轄簽程否則責留中國公即生下一計急命行人造一片木狀如馬足毒加以鐵索穿一下用異條經之擇起蹶足仍痛加鞭打這馬三足奔馳一足與之相依賴以不墜繞過一里許、</t>
+          <t>時有北國人將都鴛舟百餘艘來我國安廣之洪澤朝命宗子王都公頒水師往伐以公為勘戰官</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>đều ban áo mũ vinh quí. Thế rồi đến hôm ra về, Vua Tàu lại còn ban thêm bào gấm hốt vàng và ngựa thiên lý, để cho tăng phần vinh diệu, và lại xuống lệnh cho Nguyễn công phải đăng trình trước, còn phần Trịnh công vì có chữ mã 3 châu, nên con ngựa ban cũng bị treo lên 1 cảng, buộc phải lên yên cởi về, nếu không cởi được thì phải ở lại thượng quốc. Tiếp được mệnh trên và thấy cơ sự như vậy, Trịnh công bèn nghĩ ngay một kế, sai người theo hầu chế tạo ngay một cái chân ngựa gỗ, ruồn dây thép vào rồi buộc chằng lên chỗ chân bị treo bằng sợi dây đen, đợi khi ông ngồi lên yên đang hoàng, rồi mới dùng roi vứt mạnh một cái, tức thì ngựa chạy như bay!</t>
+          <t>Lúc ấy có bọn giặc Tàu tên là Đặng-Diệu kéo hơn 100 chiến thuyền vượt bể sang đánh Đầm-Hồng, Triệu đình bèn sai Vương-Tử là Ninh Quân-Công Thống lãnh Thủy sư đi đánh, còn ông thì được giữ chức Khâm chiến.</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>天朝志務其有應命又機思客即命解其索定乃與阮公依次而行歸國後防公仕至尚書鄭公亦仕至尚書封濟國禽渾北朝題載南文獻之邦緯莫公疑之之後二公其次也</t>
+          <t>進討日公用出文手計編覲諸市庯花嬪有餘輩放下賊艘托為弄月醉花之歡歡陰教各犯來紅巾一幅浸之以水乘夜索艘問鏡口滴水濕之仍各依期從小舟囘去</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vì có chân nọ giữa vào chân kia nên không bị ngã. Rồi sau cứ thế đi được đến hơn một dặm, thiên triều thấy vậy khen ông có tài làm cơ ứng biến! lập tức hạ lệnh cho cởi chiếc chân treo, để cùng đi với Trạng-Nguyên một thề.</t>
+          <t>Trước khi giao phong ông bèn dùng kế mỹ nhân, sai người đi khắp các nơi mộ được 300 ả đào, cho xuống thuyền giặc ca nhạc giúp vui, nhưng trước khi xuống, ông đã chỉ bảo kẻ hoặc, trao cho mỗi chi một tấm khăn hồng, đợi đến lúc nào bọn chúng say rượu ngủ kỹ, bấy giờ mới đem thấm nước rồi nhét vô trong miệng súng thần công, làm xong nhiệm vụ thì phải trở về báo tin v.v..</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>為公克寬亦踵其後壘</t>
+          <t>次日交戰我即陳船排開一字交射威戰艘賊賊惶怯敗鏡應發不覺已隨計兵射不啟發將郡因縱火燼揚帆遁去官軍大捷</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rồi khi về nước hai ông làm đến chức Thượng-thư rồi mới chỉ sĩ, Trịnh công được phong là Nghi-Quốc-Công tiếng tăm lừng lẫy cả bên Bắc-Quốc! làm thêm rang về vấn hiến nước nhà! như vậy thì sau Mạc-Đinh-Chi ta thấy chỉ có hai ông, mà người kế tiếp được hai ông thì có Phùng Khắc-Khoan tức là Trạng Phùng vậy.</t>
+          <t>Quả nhiên sáng sớm hôm sau các cô thiếu nữ trở về báo rằng Kế sách đã thi hành xong. Bấy giờ ông mới hạ lệnh đem hết chiến thuyền bày thành mặt trận chư nhất, cấp tốc tiến lên, các khẩu đại bác đồng thời nhả đạn. Quân giặc thấy vậy cũng với đem súng ra bắn giả nhồi, nhưng súng đều bị tắc họng, chẳng bắn được một phát nào. Bọn giặc biết mình bị trúng kế với vàng đốt thuốc hỏa mù, rồi kéo buồm lên chạy trốn, quan quân thừa thắng rượt theo,</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>黃田武瓊記武瓊唐安慕澤人也</t>
+          <t>活捉得他一充子年十六姿色絕倫軍囗載還以獻</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VÕ - QUỲNH. — Ông vốn là người Mộ-Trạch thi đỗ Hoàng-Giáp khoa Mậu-tuất thời Lê Hồng-Đức (1478), là người học rộng có tánh hiểu cờ lại sở trường về soạn thuật, lúc làm quan thường được kiêm cả chức Sư-quán-Đô-Tông-tái, đã soạn ra các bộ Đại-Việt Thông-Giám, và Thông-Khảo, thuật lại từ đời Hồng-Bàng xuống đến đời Thập Nhị Sứ-quân, từ đây trở về trước gọi là Ngoại-kỷ, còn từ Đinh-tiên-Hoàng xuống đến Bồn Triều Lê Thái-Tổ đại định năm đầu, gọi là Bồn-kỷ, và lại biên kỷ những niên kỷ của từng Triều đại, hợp thành 26 quyển truyền bá cho đời. Ngoài ra ông lại cùng với Trần-thế-Pháp soạn tập Lãnh-Nam-Chích Quái rồi sau làm đến Binh-bộ Thượng-thư, chẳng may gặp thời loạn lạc nên ông bị chết, con rể là Trạng-Nguyễn Lê-Đình có văn tế rằng;</t>
+          <t>bắt được một số tù binh trong có một thiếu nữ, tuổi mới cấp kệ thực là một trang quốc sắc, thế mà cũng đem về để hiển lên Vương chư không say dẫm (cấp kệ là đến tuổi 17-18).</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>洪德縣聖宗戊戌科由三黃甲公博學好古為世導師在長於模迹嘗業曰大官都總裁有大越通鹽通考迹自洪厽氏至十二侯君以前為外紀自丁天皇至朝繙太祖大受初年為本紀异譯錄歷代紀年九十二卷行于世又嘗接蘋南摭卦集仕至兵部尚書時有賊至遇害其壻狀元黎鶴卿有祭文曰羅先生道大矣</t>
+          <t>其後擇陪臣從北使奉領東牒公文公與族弟令道父會庵榜眼陶公正三名中格</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nhớ Tiên - sinh xưa : Đạo đã cao siêu, học càng thông suốt, đứng đầu quân tử thiên nhân, định dạc tiên phong đạo cốt! làm nhiều nói ít, hiểu hành khôn chê, ôn hòa giống ông Huệ xưa, Thời Trung theo thánh Khổng trước, như Tăng-Sâm lỗ đọn mà chẳng ương gần như thê Trọng-Do. Đức hạnh giống thầy Nhiệm thầy Nhan, ngọc lành không vết, văn chương như Tử-Du Tử-Hạ chất ngọc chưa tan, gió mát giảng thanh hề đầy túi, vượt bề cội sống hề mệnh mang!</t>
+          <t>Sau một thời gian triều đình có cuộc bang giao, muốn chọn một vị bồi thần sang sứ Bắc quốc, Vương sai đình thần thảo thử một bức công điệp, kết quả cuộc thi, ông với em họ là Công-Trực và quan Bảng-nhơn Hội-Am là Đào-công-Chánh, chỉ có 3 người được dự trúng cách,</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>學統而貫擬像風道骨之姿為君子善人之冠躬行而口不言教稱而人無間行惠之和而合犯之時得參之曾而非由之噫意井顔之德行粹然知玉之無瑕游真文章渾然大櫟之未散光風霽月兮滿胸懷攬影翻江兮何影靜洪德間策舉追士時則先生峻危擢科馳名壹諫景綬纂宗詔初求遺逸時則先生首應義旗張聲史館窮通隨所遇而安著述異乎</t>
+          <t>再者東書字一各其門下書寫武常存以楷法道義獨在優等</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Khoa Tấn-sĩ năm Hồng-đức đã chiếm Khói-nguyen danh vang trong đại Ngự-Sử. Chiếu cầu hiện năm Cảnh-Thống kéo cờ khởi nghĩa công rạng trong viện tu-thư. Mới biết cùng Thông đầu phải theo thời, trước thuật không ai sánh kịp. Thứ coi : Thông Khảo-kỷ-Nguyên cựu sử chép đúng quy mô, lại như Canh-Tịch Thị học chư biên. Chia trường thề đoạn, sư nho suy tôn Dương-Chấn, Chánh-sự theo kip Lý-Hoàng, khi ra Đông-Hải khéo lấy án tín vỗ về, lúc đến Bắc-binh lại thì chính sách điểm tính.</t>
+          <t>lần sau lại tuyển một người chữ tốt để viết điệp văn, thì học trò ông là Võ-thường-Tôn viết lời chữ khải tốt nhất được xếp hạng ưu.</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>人之模通考紀元崔備史得經史之規模耕籍侍學諸書得史中經之體既師儒希楊震之鱉堂政事萬李宏之山判蒼東海則以恩信撫韓乎</t>
+          <t>時有朝士數指平民論事中裴公輔曰今日中東文有三而幕澤居其二選東字有一而幕澤之優綴饒考中攬金他有兼之平民不睦措乎矣乎民俗頒廓還財物箕室公輔漸憤</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Vua dùng người cũ, đặt lên chức cao, chống gây trúc vào trước sân rồng, nếu guong sáng trong nền Quốc-học, ở chức Kinh-Duyên gần gui, giúp vua thành dức như ông Trinh-Dy, ở nơi Quốc-sử Tông-tái, lại tu Xuan thu như ông Hồ-Đán.</t>
+          <t>Khiến cho Triều thần lúc ấy ghen tị, thường nói dồn quan Binh-dân-Cấp-Sự Bui-công-Phụ rằng: ngày nay có 3 người văn hay thì Mộ-Trạch chiếm mất 2 suất, tuyển có 1 người chữ tốt thì Mộ-Trạch lại đứng hạng ưu. Vì thử có mở kỳ thì cướp giật, để thường Mộ-Trạch cũng chiếm cả chẳng, chứ như Binh-dân thì còn trở tay sao kip. Về phần Công-Phụ thấy bạn đồng liệu chế điều như vậy lấy làm hổ giặn,</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>邊氓戮北乎則以恬靜鎮安平邊患醒聖王圖任舊人越朋背蹤登頭窟業曳履於楓宸作元龜於弈泮其八侍經筵也</t>
+          <t>他日會朝密來社邑彼徒將朝士帽籠衣所盡陰攫之</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Một tấm lòng son trời có biết? Muôn đời thịnh trị bút còn ghi, những tưởng âm công chưa chất, sẽ hưởng thọ toàn lâu dài. Cờ sao hoàng thiên chẳng dễ, khiến cho đêm tối làm nguy.</t>
+          <t>ông bèn bí mật cho người mọ lấy mấy tay ăn cấp thật giỏi, đem về cho sung vào toàn linh hầu, đội phiên triều hội ông cho theo vô để chúng ăn cấp hết cả các hôm áo mũ của bá quan đem dẩu vào một xó kín,</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>堂堂焉輔成君德之程頗其總裁國史也</t>
+          <t>朝士不覺驚焉評顧謂合稱曰今日相竊非乎民而誰那睞者所言相戲耳宜急見還</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hồn còn phảng phát đầu đây, bút khó điểm tò nên chử. Thái-Sơn khi dò sĩ phu lương những ngâm ngùi! cừu trùng xiết bao ta thân, sai quan thăm viếng sau trước mấy lần, ăn huệ ban cho bạc tiền hàng vạn.</t>
+          <t>sau khi tan châu bá quan thấy mất hết cả hôm dựng, ai cũng nhao nhao hỏi nhau, mà chẳng ai hiểu duyên cớ. Nhưng rồi cách một giờ lâu ai nấy nhớ lại câu chuyện hôm trước, bèn quay lại phía Công-Phụ nói với ông rằng: Việc này nếu không phải Bác Bình-dân thì còn ai nữa, thời thì hôm trước chúng tôi nói bốn, Bác cũng bỏ quá đi cho. Vậy hợp áo đầu xin Bác trả lại để ta cùng về một thề.</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>致成焉志春秋之胡旦心忠義兮有天知萬古太和子恩日賞險功多在於斯文陽報期年於京尊胡皇天不假於愁遺致暮夜垂懸於難受易纏柱下之魄筆寫難常中之讚顏梁興冬士之嗟之強起九壹之嘆聞哀之中侯甫三慰吊之金餞臣萬時先生之不幸乃史書之不幸必使天下之人見其目睹耳</t>
+          <t>公輔佯為不知日比必慕澤也乎民安能如是各大笑而去</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Than ôi! Tiên sinh bất hạnh là không may cho Sứ quân nước nhà, những người mất thấy tai nghe ai không thương tiếc! Hương chi tôi đây, nghĩa nặng nào khác cha sinh. Tinh sâu lại là con rẻ, biệt ly một phút, uất hận trăm năm! Cáo phó hôm nào may được y quan vào liệm, những ngày quan thần chẳng được giang rượu mấy tuần, làm nhà bên mộ khôn hay, gò đống ngồn ngang thêm cảm, cũng muốn thu thập di cảo, then mình nghiên bút sơ sai, cũng muốn diễn lại dư ba!</t>
+          <t>Công-Phụ lúc ấy vẫn cứ thân nhiên như không biết chuyện, thấy bá quan hỏi thì ông giả vờ đáp rằng: Việc ấy tất nhiên cũng người Mộ-Trạch, chứ bọn Bình-dân chúng tôi thì làm sao nỗi, bấy giờ mọi người mới rõ câu chuyện, trong nhau cả cười rồi cùng giải tán.</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>聞莫不痛心之扼腕況某也</t>
+          <t>公奏使日與公道公正等倡和詩調頗多不嚴盡述</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>thẹn mình kiến văn nồng cạn, nhớ nét bằng thanh thường : phảng phát.</t>
+          <t>Thế rồi cách ít lâu sau, ông cùng các ông Công-Đạo, Công-Chính phượng mạng lên đường sang sứ Bắc-quốc, đi qua các nơi danh thắng, các ông cùng nhau xương họa văn thơ, không biết bao nhiêu mà kẻ,</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>義重臣三情深于半愴一刑之長終恨百年莫換器聞此日僅得備會禮而正是衣冠在續權時不得設几筵而奠是酒鬱魯城靈墓兮恨無由從厚血壠兮增感嘆將欲收先生之遺篇則某也</t>
+          <t>陸夫部在侍師後曾禮部尚書</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Trong với Cáo - lý những bảng khuang, gọi là một chén kinh dâng, khôn tả trăm năm ai oán, bởi thế nên trong tập Lê-Triệu khiếu Vinh đã có thơ rằng : Sớm chiếm cao khoa buổi thịnh thi. Đạo cao quốc học bậc Tôn sư (si) Một Thiên Việt khảo phương châm đủ. Trích quái bản chi những truyện kỳ. QUANG-BÔN CÓ THƠ RẰNG :</t>
+          <t>đến khi xong việc trở về ông được thăng chức Thị-lạng bộ Lại, khi mất được phong Bá-tước và chức Lễ-bộ Thượng-thư.</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>以文章倥傯總覩筆夕踈不莊集昌樑之遺文而為唐李漢將欲紡先生之道派則某也</t>
+          <t>尚書武恆斷記</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Một vị hồng nho giữa Thánh trào. Tùy thời tần thoái tự do sao. Tiên còn thượng thế coi như đúc? Phật sống nhân gian ngầm khác nào? Ngôn hạnh đối đương ai sánh kịp. Văn chương muốn thuở giá càng cao.</t>
+          <t>QUẾ-AM, VÕ-DUY-ĐOÁN</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>以見聞淺陋政事紛紜不罷榻老亭之遺蹤而為泉之黃幹水清玉潤兮想無忘萬里接遲兮空望新惡一酌以將愧寫百年之哀怒魏朝嘆詠詩云儒科早擢際明時學道尊為國學師越考一為真可法休談撫怪謾傳奇繡光貢有詩云堂堂聖世一洪儒仕士隨時任自由天上麗儒稱。骨相人間話佛見心頭嘉言善行諸賢慈大典高文萬古彌斯道巍然山奇在後人無不企企前修傳奇唐安之武者是也</t>
+          <t>尚書武惟新幕澤人也中堂甲武拔萃之子也</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Non xanh cùng đạo nguy nga mãi Hậu thế ai người chẳng ước ao? Nay ta xét thấy trong tập Truyền - Kỷ có chép họ Vũ ở Đường-An, chính là họ Vũ này vậy. Còn những con giai của ông tên là Cán, lúc nhỏ cũng rất thông minh nói tiếng là người bác học, thì đồ Hoàng-giáp vào khoa nhâm tuất thời Lê-Cảnh-Thống năm ấy mới 28 tuổi vì tánh yêu tùng nên mới lấy hiệu là Tùng-Hiên, về phần văn chương đức hạnh người đời rất là kinh mến, nhà vốn thanh bản thế mà lúc nào ông cũng thân nhiên, gặp khi cao hứng xuất khẩu thành chương, ngày tháng tích lại đóng thành một tập.</t>
+          <t>Ông Đoán người làng Mộ-Trạch là con giai quan Hoàng giáp Bạt-Tụy ngày trước,</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>公子幹生而頴異博極群書景綿稱德士寅科中黃甲性愛松故以松軒自號文章行當代推尊雖家素清貧而恬然自適凡遇物即事輒隨意興吟矢口成章揮毫立就日積月累遂成一家機軸典永賴古庵程國公相善其詩詞偈經往復如懷鄉綠蒿艾虎等首見白雲庵詩集未澤鄉八景等首見品景詩集又有松軒詩集并四六備覧覧傳于世仕禮部尚書禮度伯光賁詩云早擢危科副上來文章德業依飾模半天載上扶興運三十年餘歷要途驚龜冕躬主新好爵青燈黃老舊寒儒清貧誰哉</t>
+          <t>火極蒙晴讀書不記一行年十七乙未識字欲改別藝云</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ngoài ra ông lại cùng với bạn thân là Trinh-quốc-Công ở Trung-Am thuộc huyện Vĩnh-Lại xướng họa rất nhiều, tỷ như các bài thơ Hoài-hương Chi-duyên Một - hở v.v. hiện nay có chép trong Bạch Vân-Am Thi tập và các bài Tiêu-Tương-bát-Thủ thấy ở trong tập Phẩm-Vưng, lại còn Tùng-hiên tập và Tập Tứ-lục-bị-lâm truyền bá cho đời, về sau ông cùng làm đến Lễ-bộ Thượng-thư và được phong tước Lễ-Độ-Bá. Cho nên ông Quang-Bồn có thơ vinh rằng: Sớm đỗ cao khoa đẹp ý vua. Văn chương đức nghiệp đang sư mô. Nửa ngàn năm trước phò hưng vạn. Ba chục niên sau trái hoàn đồ. Áo tía đại vàng Quan tốt phẩm.</t>
+          <t>lúc thiếu thời tính rất lỗ độn, học suốt ngày đêm cũng không thuộc được một dòng chữ thành ra khi đã 17 tuổi đầu mà vẫn đốt đặc cán mai. Cậu thấy mình không có khiếu học nên định xoay sang nghề khác.</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>為家計焦地詩書有道腹</t>
+          <t>夜受見神人騰空而降為之剖心剖去其濁既醒腹中隱然貴痛次備札橋謝之父再開心教學自此日漸開明學大進</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Đèn xanh Ấn tuyệt cảnh hàn nho. Phí gia kề ấy không mang tới, Rượng cấy thi thư chẳng mất mùa.</t>
+          <t>Chẳng ngỡ bỗng có một đêm Cậu nằm mơ thấy một vị thần nhân từ lung chùng giới giáng xuống, lấy dao rạch vào bụng Cậu, mọi trái tim ra nào hết những chất văn dục, đến khi giặt mình tỉnh giây bụng vẫn còn thấy hơi đau, nhưng Cậu cho là điểm tốt nên sáng hôm sau Cậu liền sửa lễ bài tạ, rồi cha mẹ cũng sửa lễ khai tâm để dạy Cậu học.</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>樗眼阮全安記阮全安唐安時舉人也</t>
+          <t>蟲宜中元二刊文章各天下</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nguyễn-Toàn-An, người làng Thời-Cử tham thuộc huyện Dương-An vào khoảng niên hiệu Lê-Hồng-đức ông phải sung vào ngạch lính, giữ việc cắt cỏ ở trong sân điện, một đêm gặp tiết trung thu, bá quan được vào thường giang trong điện, đêm ấy giáng mờ, Hoàng thượng bên lấy 4 chữ Trung thu vô Nguyệt làm đầu đề, bắt các văn thần vinh thi, giữa lúc mọi người còn dương thời xao, chẳng ngờ chú lính Toàn-An đã làm xong trước, qui gởi dâng lên!</t>
+          <t>Là thay từ đấy trở đi thì Cậu học một biết mươi, dần dần nỗi tiếng là người hay chữ, rồi gặp khoa thì Cậu lại chiếm luôn cờ biên Nhi-nguyên (là 2 lần đỗ đầu), ai cũng cho rằng chuyện lạ.</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>洪德間充另兵常守殿前判草適中秋朝侍間夜月昏曉御題中秋無月詩班列中吟咏未竟公詩先就跪而上之在坐笑曰另兵亦有詩乎</t>
+          <t>初昭祖康王為公子時公居門下適有間饑從星散公獨進隨</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>cứ tỏ ai cũng cười rằng: binh lính cũng biết làm thơ đó chẳng? rỡ thật đánh trọng qua cửa nhà sắm, Hoàng thượng thấy vậy phân bảo đưa lên Ngai coi. Thấy câu kết viết:. Chớ thấy phen này mà để nguyệt?</t>
+          <t>Nguyên trước khi Chiêu-Tổ Khang-Vương còn làm Công-tử, thì ông giúp việc ở trong phủ, gặp lúc hữu sự bao nhiêu thuốc hạ đều hổ chạy hết, riêng có mình ông lúc nào cũng ở bên cạnh Vương,</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>母乃雷門擊手鼓命取觀之落句若曰莫把今番閒視月來秋望月月彌高觀者嘆服仍具奏敬因全寅科貳拾歲一舉中鄉試會廷試中榜眼合菜歸</t>
+          <t>迨王居節制府進徃留屯詰賊時以解元八侍帷帳事之大小王必密之當時謂之內相</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Thu sau trông nguyệt nguyệt càng cao. ai cũng tóm tắc khen ngợi rồi tâu vua xá tội cho về, đến năm nhâm-thin thì ông mới 23 tuổi, gặp có khoa thì ông vào ứng cử đỗ thi Hương xong, lại đỗ cả thi Hội;</t>
+          <t>đến khi Vương được phong chức Tiết-chế tức là Trịnh-Cần 1682-1709 đem quân vào đóng ở Luru-đồn thì ông đã đã Giải-nguyên theo giúp ở nơi quân thứ, bất luận việc lớn hay nhỏ Vương cũng hỏi qua ý kiến rồi mới thi-hành, bởi thế người đời mới gọi là quan Nội-tướng,</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>未幾適值家憂時朝制孔嚴係憂中要憂孕者不盡仕刻公守制三年不敬近女色服闕尋卒無嗣皇上聞而憐之自是居喪言月之極亦始除之光真有詩云森然美玉為聖河莫狀良工妙琢磨辛苦十年劬勞九寅綠一拳權危科方施心上經綸用莫測裘中愁恨交地下修文知有命豐才普壽奈天何</t>
+          <t>徵完詞中優須甲長科中會元王賜之綵衣待以不次六部到尚書</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>lúc vào thì Đinh được đỗ Bảng-nhãn, vinh quí bài tỏ vừa xong chẳng may lại gặp gia biến, theo như chế độ hiện hành, nghiêm cấm những người trong lúc có tang cha mẹ mà vợ thụ thai, thì không được kẻ vào hàng thân sĩ, bởi thế trong vòng 3 năm cư tang, ông phải lánh xa thế thiếp, rồi khi hết tang ông bị ốm chết, thành ra vô tự! vì thế Quang-Bôn có thơ khóc rằng: Sáng choang ngọc bích giữa trần ai, Khôn tỏ lương công cách giữa mái. Đèn sách mười niên công chẳng quản, Khoa danh nhất cử gia chưa hai. Kinh luận mở túi toàn gia sức, Luật pháp cư tang cảm thụ thai. Này chức tu văn nọ địa hạ, Ông xanh bớt thọ bồi thêm lại.</t>
+          <t>rồi sau thì khoa Hoành-từ ông lại được trưng ưu hạng, đến năm Giáp-thìn lại đổ Hội-nguyên, Vương ban áo mũ và trọng đài hơn mọi người. Vì thế 6 năm giới mà ông đã thăng đến chức Thượng-thư.</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>狀元綬帶記敬賀眾唐安幕澤人也</t>
+          <t>言公忠剛慷慨遇事敢言常尊泰九斂之為人上金鑑錄大要勸以正心穀俗知人去讒言甚愜切王嘉納之奇以通臣自許</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HUYNH DƯ ĐỆ THI LÊ TRANG-NGUYÊN CÚC TÍNH ĐOẠT TRỪ Anh em cùng vào thi, Lê Trang-Nguyên nói khích để đoạt giải Tràng-Nguyên Lê-Nại. (có chỗ viết là Đinh) Ông Nại Người làng Mộ-Trạch lúc nhỏ rất chăm học, năm đỗ giải nguyên mới 27 tuổi, được quan Thượng Võ-Quỳnh là người cùng làng gà con gái cho, khi ở gùi rẽ ông chỉ thơ thân tới ngày không để ý gì đến sách vở. Cụ Thượng lấy làm là hỏi phụ thân ông rằng: Tôi thường nghe nói Cậu ấy chăm học, thế mà từ khi sang bên nhà tôi thì Cậu không hề nhìn đến sách vở là có làm sao? Thân phụ ông hỏi lại: Thưa Ngài vậy từ khi cháu sang ở bên quí phụ thì sự ẩm thực thế nào? Cụ Thượng đáp: Theo lời thanh đạm của nhà nho, thì mỗi bữa ăn cũng chẳng mấy tí! Phụ thân ông đáp: Sức ăn của cháu khác với người thường, thế mà Tương-Công cho ăn ít ỏi như vậy, hoặc giả châu không vừa lòng đó chăng? Cụ Thượng Quỳnh thấy ông dâu gia nói vậy bên bảo người nhà cứ mỗi bữa ăn của Cậu sẽ tăng gấp đôi, từ đấy Cậu mới cảm sách đọc vài lượt, tăng đến nỗi ba (3) thì Cậu học đến trống tư (4)!</t>
+          <t>Xét thấy ông là người rất kiên trung và khẳng khái, gặp việc gì không hợp cũng có can đảm nói ngay. Vì ông rất hàm mộ tư cách của Trương-Cừu-Linh ngày trước cũng giống như thế. Cho nên có dáng bộ Kim-giám-lục trong đó toàn là những câu nói về Chính tâm, hậu tục biết người, xa kẻ siềm nịnh v.v... lời lẽ cực kỳ thiết đáng, được Vương khen là một vị Trực thần.</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>少助于紫鮮元時二十七歲同邑尚書狄瓊以女妻之出贅復終日間居不以書籍意瑤文怪之以問於公之艾曰素問言吾瑤力學邇來無事不曾見讀書父曰兒自過貴庭相公每食之如何瓊曰儒家清淡所食者其肱幾何父曰老子異夫人之食而公以尋常視之安巧有不滿處璣間言食每飯必加飯倍之自是公始開卷讀一二篇尋加三歲謁飯公漸讀章三鼓又加以四歲錫公郎讀至四鼓還曰吾謂誠能過人矣</t>
+          <t>時宮中有詞鷄之戲中官索鷄鷄奉進公適見問問鷄何從來中官以鷄答公作色曰昔在潛師時主上惟知有我寧知爾輩為何人今乃導之以戲樂郎立執鷄喉鷄應手而死中官馳八具告王默然而起為罷詞鷄事</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>bấy giờ Cụ Thượng mới biết con rể của mình ăn khỏe quá xá! rồi sau mỗi bữa ăn cứ lấy nỗi 5 làm mục để thử xem sao? quả nhiên Cậu học suốt đêm không hề nhắm mắt! và thường tán tụng mình rằng: Mộ-Trạch Tiên-Sinh, ăn khỏe nỗi danh! mười tám bát cơm! mười hai bát canh! Khởi nguyên chiếm bảng, trên cả quân anh! bởi nhiều sức tích, nên phát tung hoành! Thế rồi đến khoa ất Sứu (1504) niên hiệu Đoan-Khánh Triều Lệ Uy-Mục-Đế ông vào thi hội, về văn Tự lục ông dùng thứ nhi, còn kinh nghĩa, phủ sách, thì đều.</t>
+          <t>Trong thời gian ấy ở nơi cung trung thường hay có cuộc chơi gà, các vị trung - quan thấy vậy bèn sai người đi khắp các nơi để mua gà tốt về hiến, một hôm bắt gặp, ông liên quát hỏi gà này từ đâu đem đến. Trung quan cứ thực trả nhồi; ông tỏ vẻ giận dữ mắng rằng: trước kia khi còn ở nơi Tiềm-đề (tư định) Vương thượng chỉ biết có một mình ta chứ có biết đâu bọn chúng, thế mà ngày nay chúng toàn bày trò du hi để làm mê hoặc Chúa thượng hay sao, mắng xong ông bên giang lấy con gà chơi rồi bè gậy cò cho nó chết tươi. Trung-quan chạy vào trong cung tấu bày cáo, Vương lãng lăng không nói gì, rồi từ đấy về sau trò chơi chơi gà cũng không còn nữa.</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2345,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>更加以五歲錫為度誠觀知何是後讀書終夜不絕微常有賛云曾來潭先生以食為名十八肆飯十二餌羹魅荒次第各冠群英富之也</t>
+          <t>陽德年間繫嘉宗年號有北使至公為接伴使與北使途廣和自稱河津至于殲門詩凡二十餘首應答如響北使甚敬章之</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>thứ nhất, khi vào thì Đinh liên đồ Trạng-Nguyễn, lúc ra làm quan dàn dàn đến chức Tả-thị-Lang bộ Hộ, con là Quang-Bôn có thơ vịnh rằng: Rộng rãi còn thêm tính nét thuần. Thiên tài muốn phát chắc mười phân.</t>
+          <t>Đến năm Dương-Đức triều Lê Gia-Tông (1672-74) có sứ Tàu sang, ông được sung chức Tiếp sử, trên quãng đường trường từ ải Nam-Quan trở về, đối bên xướng họa văn thơ không biết bao nhiêu mà kẻ, ngay từ bên sông Nhi-Hà vào đến Điện-môn, Bắc-Sử cũng xướng hơn 20 bài, bài nào ông cũng họa ngay. Sư giả lấy làm kinh ngạc,</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>鉅談之也宏端變年間乙丑科會試四六中第二義經賦文策並第一廷試文中狀元往至戶部左侍郎其子光貞有詩云、</t>
+          <t>至禮部設宴北使富筵索酒公應口吟曰</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Đã đem danh vọng trùm thiên hạ. Còn lấy thì thư hóa vạn dân. Cây đực tốt tươi đời hai quả. Bằng vàng nối đời của đầy xuân! Cho hay phúc trạch bao giờ can? Hán vi Vu-Công, Tống Đậu-Quân.</t>
+          <t>đến khi Lễ-bộ thết yến Sư giả hạch sách rượu dầu, ông lại ứng khẩu ngâm rằng:</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>局度寬洪操履純天才定賦晚逢長曾將各望魁天下又把詩書還萬民陰德足徵來世及危科繼擢一門春永垂者一無窮慶漢義於公宋當見嗣公第大調以袖童稱少年激發之氣公奇抑之乙丑科八第一場有錯誤處以問子公公答之曰今番與正第試若以相告更將誰誘郎鼎怒曰今科讓兄光簽討撤籠而出郎日歸本鄉乘夜而行致家時以三鼓不敵呵門因憇卧于軒之檐處是夜其母愛袖人謂軒前有黃甲在何不開門接入俄醒覧覽私自怵曰今日八會試場二子皆京城應舉部有何黨甲在我家軒誠尚親焉</t>
+          <t>飽吾宁道真佳味何必江亭問一盞</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nguyễn ông còn có một người em giai tên gọi là Tài Thần, lúc nhỏ nỗi tiếng thân đồng! nên hay có tánh tự phụ ông phải tìm cách để nên bớt đi! Vi thế nên khoa ất sử, anh em cùng vào ứng thí, giữa kỳ đệ nhất, ông Tài quên sách đến hồi thì ông bảo rằng: chuyện này tôi thi với chú, nếu lại bảo chú thì còn thì cử với ai? Ông Tài tức giận đáp: Thôi thì khoa này tôi để cho anh chiếm giải trước vậy nói xong giỡ phẳng lều chống ra về, đi thẳng một mạch đến trông canh ba thì về tới nhà, nhưng lại không giám gọi cửa, dành nằm ngủ ở ngoài hiên. Giữa lúc ấy thân mẫu ngủ trong nhà mờ thấy thân nhân đến báo: Ngoài hiên có Ông Hoàng-giáp, sao không mở cửa đón vào. Bà cụ sức tình nghĩ rằng: Ngày nay đương kỳ thi Hội, hai con của mình đều ở trong kinh, thử hội còn Hoàng-giáp nào ngủ ở ngoài hiên.</t>
+          <t>Bảo ngô cá đực chân nhai vị, Hà tất Giang đinh vấn nhất bồi nghĩa là Rượu ngon là đực ta say nhi, còn hỏi Giang đinh một chén chi,</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>見壚外有人熹睡喚而起之乃晨才鼎其母愕然問故才鼎以實對母曰曾學未到勸再加功才得郎點燈索書觀之母笑而言曰覆落第歸斯爾愼激只恐此志難持鼎曰自今而後母觀如何自是日夜攻書手不釋卷是科兄鶴中狀元帝以爲監司月講官作成人才鼎尋赴京邀訓學從謂曰經営司是我的有如問其書首從毛聽講來學者素聞其各試往觀才學知何至鄕市處士人特書來問才兼隨問答之滔滔不絕至有以外書諸子問之亦淡練應答人皆發為服爭來觀咱而盟胃為之一空兄鼐即歎諧之曰吾弟之才何直受於高選不宜如此孟浪邀學者義嚴談使譽席欲講這是有關風教焉</t>
+          <t>北使稱賞覲成禮而去</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nghĩ thế rồi bà mở cửa ra coi, bỗng thấy một người dương nằm ngủ lăn ra đó. Bà đánh thức đây thì lại chính là cậu Tài, làm bà hết sức ngạc nhiên! Cậu bèn kể lại câu chuyện như thế. Nghe xong bà mới báo rằng: Đó là tại con học chưa đến nơi đến chốn, vậy thì từ nay con phải gắng công v.v. Cậu nghe lời mẹ dạy bảo với theo vào ngay trong nhà, đốt đèn mở sách ra đọc. Bà cụ thấy vậy mỉm cười bảo rằng: vừa mới thì hồng cho nên phần khích nhất thôi, chỉ sợ không giữ mãi được như thế đó thôi Ông đáp: Thưa mẹ, từ này về sau rồi mẹ sẽ thấy, thế rồi từ đây ông học suốt cả ngày đêm, tay không hề rời quyển sách. Còn phần ông Nại lúc ấy đã đồ Trạng-Nguyên vua cho giữ chức Giảng-quan trong Quốc-tử-Giám, biết bao sĩ tử được ông tác thành, rồi ngay khi đó ông Tài cũng ra kinh đó, đón đường bảo các sĩ tử rằng: Ta đây tức là bồ chư? các anh muốn hỏi chư gi?</t>
+          <t>Sư giả nghe xong tấm tắc khen ngợi rồi buổi đại lễ được hoàn thành ngay. (Giang đinh là quán rượu).</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>。才眾郎輿歸至洪順三年，</t>
+          <t>後差往高平公幹以爲臣漢都公各居公上公杭言曰臣承嚴之備位尚書奇意主上南牙各軍不調今日使漢都公居其右臣敬不奉命</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>hãy cứ đem sách lại đây rồi ta sẽ bảo?</t>
+          <t>Cách ít lâu ông được lên công cán Cao-bằng, nhưng Vương lại cho nội thân là Hán Quân - công được ở quyền trên, nên ông kháng nghị rằng: Thần đây làm dự chức vị Thượng-thư, tưởng rằng Vương thượng cũng coi Nam nhà làm trọng, chứ có ngờ đâu Hán-Quân lại ở trên thân, vậy thân không dám phung mạng.</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>穆襄翼帝年號，</t>
+          <t>時府僚或在都臺令道乃孫弟方覲奏見此命若行三都不敢秉筆</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Về phần sĩ tử trước kia vẫn thường nghe tiếng, ngày nay cũng muốn xem tài học ra sao? nên họ rủ nhau đến chỗ chợ Dừa thị để hỏi nghĩa sách, hỏi đâu đáp đây, thao thao bất tuyệt! Có người đem cả ngoại thư và sách chư từ ra hỏi, ông cũng giảng giải rất là tinh tường! Khiến cho mọi người đều phải khấp phục, rồi sau kéo đến cảng đông thành ra trường Giám vãng teo. Ông Nại thấy vậy phải can em rằng: Cứ như tài học của chú lo gì chẳng đồ cao? mà đi làm việc vô ích, đón học giả về bàn suông để cho trường Giám không ai đến học. Tôi thấy việc này có quan hệ đến nên giáo hóa, vậy khuyên chú nên định chỉ thi hơn. Ông nghe lời anh lập tức trở về. Đến khoa Tân-Vị (1140) ông đồ Nhị-giáp, lấy làm uất hận vì không chiếm giải khối nguyên, sau ra làm quan cũng chỉ đến Lại Bộ Cấp Sự-Trung rồi mất!</t>
+          <t>Giữa lúc ấy các quan đều có mặt tại phủ, Đô-Đại Công Đạo là em họ ông cũng kháng nghị rằng: Vì thử Vương bất thi hành lệnh ấy, thì Tam Đô-thân không giảm cầm bút đề ghi.</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>辛未科果中黃甲嘗以不得大科為根仕經免部給事中短光責有詩云確句奇男的壯懷一門兄弟應花開青鐵萬中登高遠蘋案曾趨預密陪幼學壯行初得遂有才無壽盡堪哀九重莫謂三光滿已送文星八夜臺</t>
+          <t>王怒曰若不知命且審此日向暮之黃門智俛之公道知上意不囧即以顗整柱公勃然曰王欲殺諫臣請即納還勅命</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>vì thế Quang-Bôn là cháu có thơ rằng: Lỗi lạc nam nhi có đủ tài? Sao khuê ưng cả một nhà Ngài? Vẫn như tiên đúc luôn tranh giải? Chức cũng xu bồi thoát ghế vai? Ngầm sự học hành khi thiếu tráng? Xem cơ thọ đoàn thực bi ai? Cửu trùng chớ tưởng Tam quang đủ? Đã tiến sao vẫn xống Dạ-đài!</t>
+          <t>Vương cả giận phân rằng: Nếu không tuân lệnh thì cứ ở lại đây, thành ra bá quan phải ở lại đến lúc gần tới. Vương sai Hoàng-môn quan ra dực, Công-Đạo xem chúng Vương không chịu thay đổi ý kiến, bèn đập đầu vào cột trụ, ông thì nói lớn lên rằng: Vương Thượng đã giết Gián Thần, vậy Thần xin nạp lại sắc lệnh!</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2464,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>狀元程國公記公字秉謙道號自雲居士永賴中庵人也</t>
+          <t>黃門以聞王怒曰他前日斃吾良鷄我亦含忍今乃爾何疆耶誰殺諫臣而卻知此說立耶罷歸公道像他黨亦罷隨耶差往公道家追收勅命其進士科字一道公不肖納奉差索取之公堅執曰諸勅皆王之賜謹當奉還至如科字乃我才學做成不敬併納奉差不勝為而回</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ông Nguyễn-bỉnh-Khiêm đạo hiệu là Bạch-Vân cư-sĩ, người làng Trung-Am huyện Vĩnh-Lại, tiền tổ ngày xưa tu nhân tích đức đã nhiều, (nay không thể khảo cứu được) chỉ biết từ đời cụ Tổ thì được tập phong Thiếu-bảo Tư-quận-Công mĩ tự là Văn-Tính, Cụ bà được phong Chính phu-nhân Phạm-thị Trinh-Huệ, nguyên trước các cụ lập gia cư ở nơi có núi sông bao bọc, hợp với kiểu đất của Cao-Biền. Phụ-thân được tặng phong Thái-bửu Nghiêm Quận-Công, mĩ tự là Văn-Định, đạo hiệu là Cù-Xuyên Tiên-Sinh, nguyên người học rộng tài cao, lại có đức tốt, được sung chức Thái-học-sinh. Thân mẫu họ Nhữ được phong Từ-Thục phu-nhân, nguyên người ở An-Tử hạ thuộc huyện Tiên-Minh, là con gái quan Hộ-bộ Thượng-thư Nhữ-Văn-Lan.</t>
+          <t>Hoàng-môn Quan thấy vậy vội vàng vào tàu: Vương càng giận thêm! à! hôm trước đã giết gà chơi của ta, ta cũng ẩn nhẫn, chẳng ngờ ngày nay y lại quật cương đến thế thì thôi! thử hỏi ai giết Gián Thần mà y dám nói như vậy, rồi Vương hạ lệnh bãi chức ông và Công-Đạo, sau lại sai quan đến nhà thu về sắc mạng từ xưa đến nay, thử gi lòng cũng giao trả, riêng có đạo sắc Tấn-sĩ về khoa thì chữ tốt thì ông giữ lại, sai quan cố tình đời cả, ông viện lẽ rằng: những sắc lệnh kia là của Thượng ban thì tôi vàng mệnh giả về, còn đạo thì chữ là do tài tôi làm được thì tôi có quyền giữ lại làm ghi, Sai quan thấy nói hợp lẽ đánh phải trở về phục mạng.</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>先世皆有隱德不可考其祖文靖始卜陽宅山水週环暗兮高王錮記父文英有學行亮太學生母慈淑夫人光明妾子下人戶尚部書汝文瀾相公之女世聽聲通經史善文章尤精風鑑曉術戴方洪德盛時而知四十年後炎運當微慨然有大夫夫改物之志擇對不嫁幾十年一見文定知其有貴兒相逐歸焉</t>
+          <t>時公子推匡由庚茂科中進士同北鎮勘制司王郎召還許以少師陪從意欲用之蓋公難以舊臣然數犯顏觸諦頻見嚴憚故因忤言麗之而用其子其後公道復召用居職如原</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bà vốn là người thông minh, học rộng văn hay; lại tinh cả môn tướng số, ngay thời Hồng-Đức mà Bà đã tính được rằng; vận mệnh nhà Lê chỉ sau 40 năm nữa thì sẽ suy đồi. Vì có một chí hướng phò vua giúp nước của bậc trượng phu, muốn chọn một người vừa ý mới chịu kết duyên, nên đã chờ đợi đến ngót 20 năm trời, khi gặp Cù-Xuyên Tiên-sinh biết là có tướng sinh quý tử mới chịu lấy.</t>
+          <t>Nhắc lại khi ông lui về vườn cũ bạn với cúc tùng, được hơn 4 tháng thì con giai là Công-Tử Duy-Khuông đỗ Tấn-sĩ tự khoa Canh-thin, hiện đương giữ chức Đông-Bắc-Trấn Khám-Chế-Ty, được Vương cho triệu về Kinh sung chức Bồi - Tung Thủy - Sur có ý muốn trọng dụng. Bởi vì ông dẫu là bậc cựu thần, nhưng đã nhiều lần làm Vương phạt ý, nên Vương mới phải xuống chỉ trực hồi, ngày nay lại muốn dùng con để tỏ ra lòng ưu đãi. Tiếc rằng Duy-Khuông vào trong Chính-phủ cũng chẳng được lâu, sự nghiệp cũng chưa thành tựu. Còn như ông Công-Đạo thì sau cũng được triệu về phục chức như xưa.</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>後遇一少年過雪江寒度頭愕然嘆曰火時何不相遇今日到此何為從者比而顓之夫人徐詢姓名知是登庸恨悔者絞日公以洪德二十一年幸亥生身體長大容貌英偉未周歲能言一日昧爽文定抱諸卷忽語曰日出東方考大驚異年四歲夫人誦以經傳王義即能誦新口頭又暗讀諸國詩數十首時夫人他為文矣</t>
+          <t>而公優游桑梓遂無意於當世常有范蠡五湖賦父業澤風景農家考績異聞等作皆用國音人多傳誦其詩詞銘記頗多世稱中興以前詠橋候中興以後唐川子蓋言國音文體得之清高而其學問該博故耳</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sau bà gặp một thiếu niên đi qua bến đò Hàn bên sông Tuyết-giang, bà kinh ngạc than rằng: « Sao lúc trước không gặp, nay tới đây làm chi? » Người nhà nghe lén hỏi tên họ, mới biết đó là Mạc-Đăng-Dung, bà lấy làm tiếc nuối. Ông sinh năm Tân-Hợi niên hiệu Hồng-Đức thứ 22, thân hình cao lớn dung mạo khôi ngô, chưa đầy tuổi đã biết nói. Một hôm sáng sớm, thân phụ bế ông, bỗng ông cất tiếng: «Nhật xuất đông phương». Thân phụ rất kinh ngạc. Năm 4 tuổi, mẹ dạy kinh truyện, đọc đến đâu ông nhớ đến đó, lại đọc thuộc hàng chục bài thơ Nôm.</t>
+          <t>Riêng về phần ông thì vẫn ngao du ở nơi phần tư, không đề ý đến việc đời, nhân buổi thư nhân ông có soạn ra rất nhiều thơ phú Phạm-Lãi-du-Ngũ-Hồ và cuốn Trạch-hương phong-cảnh tập Nông-gia-khảo-tích dị-văn, v.v... đặc biệt nhất là những cuốn văn ấy toàn dùng Quốc-âm, cho nên được rất nhiều người truyền tụng, ngoài ra lại còn biết bao bài mình, bài kỳ rất hay, người đời đã phải ca tụng những câu: Trung hung về trước có Vĩnh-Kiều Hầu, Trung-hung về sau có Đường Xuyên-Tử là nói thề văn quốc âm đều đã đến chỗ thanh cao lắm vậy. Lại như quan Trang họ Đặng ở làng Phù-Đồng soạn bức trướng mừng Võ Tề-Tương khi về hưu cũng có câu rằng: Châu Tương-Công có Đường-Xuyên là người đã nuốt hai kho sách Thiên-lộc Thạch-Cừ, của nhà Hán vào bụng, nghĩa là khen sức học uyên bác vậy.</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>因拽竹權弄兒戲吟國語詩曰月撿弓月撿弓下句未就公在竹樞中郎和云撥魏例忍忍容文武喜以示夫人夫人恚曰月臣象也</t>
+          <t>公雖去國而朝野皆重其各漂然起敬時有之南處意副在憲司日有武職一員以苛過被訴論失民兵其後奉侍內閣意副預焉見武官奉勵武惟斷以事忤旨囂歸至今不見召用而武職其員由該官並可濫臣等已論失民兵今復居職知原小臣敬不彈奏以嚴國典時侍臣見之無不相顧駭愕至上疑意司是公之黨為之遊說命參訊之始知共公無干郎有旨云意副小臣何敢越職言事今姑原之自後不得知此意副奉命而退</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Một hôm mẹ kéo chiếc que tre chơi với ông, ngâm câu thơ Nôm: « Nguyệt như cung, nguyệt như cung », chưa kịp ngâm câu dưới thì ông ở trong cũi tre liền ứng khẩu họa lại: « Bát nguyệt sơ tam nguyệt lãng dung ».</t>
+          <t>Còn ông thì đầu thời làm quan nhưng trong triều ngoại quan thấy đều trọng danh, lúc ấy có quan Phó-hiến đến nhận chức ở Sơn-Nam, thấy có một viên quan vô bị cáo về việc hà lâm. Ông kết vào tội làm mất dân binh, đến khi ông được bỏ vào Nội-các thấy người vác kiểm đứng hầu lại chính là viên chức bị tội ngày trước. Ông liền quy xuống tàu rằng: Hạ thân thấy quan Thương-thư Võ-duy-Đoán.trước kia vi trái ý Thượng nên phải bãi chức về vườn, tôi nay chưa được phục chức, mà viên võ kia là chức cai quản hà làm, Thân đã kết tôi làm mất quân dân, có sao nay lại phục chức như cũ. Vậy nên Thân phải chất vấn đề cho quốc pháp đẳng nghiêm v.v... Giữa lúc ông kêu việc đó thì các quan hầu thấy đều đông đủ, ai cũng nhìn nhau bằng đôi con mắt kinh ngạc! Còn Vương thượng thì lại ngỏ ông về bè với Võ-Thượng-thư, nên Ngải giao cho đình thần tra xét, sau biết là không, nên được miễn nghị, nhưng Vương lại hạ dụ rằng: Hiến-ty là hạng quan nhỏ sao được nói leo. Vậy nay hãy tạm tha thứ, còn từ đây về sau thì cảm không được giữ thói ấy nữa v.v.</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>汝何以此命兒考大慚謝然恨終不釋竟辭歸於父家公總角時群見洛於寒度南艏北人始相之曰王及諦視又曰惜彼粗只存做狀元宰相故人皆知其為公韓器自少時講學家吏既長聞榜眼梁得交文章各世負笈從從之梁公弘化會朝人奉使如明得太乙神經族人梁汝笏之後仍以授公公既造諸玄理見道遂東後染師病篤嘆其子有慶於公公撫之如子教以成名光紹間兵變起公隱居教授抱道自樂不求聞達綿元帝皇初年鄭綾公莫登庸皆有挾天子会諸侯之志類年構兵境內大亂公感懸興詩云泰和宇宙不虞周五戰交爭笑商答川血山骸淵魚羊殼雀為誰驅重興巴下渡江馬後憲應防八室龜世事到頭休說著醉吟澤畔為閒這蓋知教民當復與始雖備安終必復興國而室韜其隱語也</t>
+          <t>蓋公以正言被黜故有忠憤者亦為不平其祭文乃全平日所自作如致君期竟舜唐虞自任以身受變綫契去素蘊胸中平治欲大屢施至玄幾裏覓虛且取難宣世其盈虛付之玄機而不流於惑亦得古人忠厚之意兵壽六十四歲贈左侍郎公三世登科為武族世科之冠之始歟</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Thân phụ mừng rỡ đem khoe với phu nhân, phu nhân giận bảo: « Trăng là tượng của bề tôi, sao ông lại dạy con như thế? » Thân phụ hổ thẹn tạ lỗi, nhưng bà giận không nguôi, bỏ về nhà cha đẻ. Thuở nhỏ ông chăn trâu ở bến đò Hàn, có khách phương Bắc trông thấy bảo rằng: Cậu bé này có tướng rất quý, chỉ hiềm một nỗi là da hơi thô, về sau chỉ làm đến Trạng-nguyên Tể-tướng mà thôi, vì thế nên ai cũng đoán chắc rằng: ông sẽ là bậc tể-phụ của quốc gia sau này. Như ông lúc còn niên thiếu, học văn sở đắc ngay từ gia đình, đến khi lớn tuổi, nghe nói có quan Bảng-nhãn Lương-đắc-Bằng, nổi tiếng văn chương quán thế, ông bèn tìm đến để xin nhập học. Lương-Công là người ở làng Hội-Trào thuộc huyện Hoằng-Hóa lúc Ngài phụng mệnh sang sứ nhà Minh, có học được phép Thái-ất-thần-kinh của người cùng họ, tức là dòng dõi của Lương-nhữ-Hốt. Lương-Công rất tinh thông về lẽ huyền vi, đem truyền lại cho ông, đến khi Ngài bị ốm nặng, lại đem con là Lương-hữu-Khánh ký thác với ông, ông săn sóc dạy dỗ chẳng khác con mình, sau này ông Khánh cũng được thành đạt.</t>
+          <t>Xét thấy ông Phó-hiến đây vì giữ chính khi mà bị truất oan, khiến cho những người có lòng ngay thẳng cũng bất bình thay, còn bài văn tế là do ông thảo tự lúc sinh thời như câu: Thờ vua thì mong Vua như Nghiêu Thuấn, sửa mình thì phải theo dấu Cao-Quy. Sẵn tấm lòng ngay, muốn đem trị bình thì thô, xem cơ tạo hóa, dám đầu tiết lộ huyền vi, câu văn thực là kín đáo nhưng mà trung hậu biết bao. Về sau ông hưởng thọ được 61 tuổi, sau khi tạ thế được tặng chức Thi-lạng, như vậy thì nhà ông đã được 3 đời đăng khoa kế tiếp, và mở đầu 4 chữ kế thế đăng khoa cho họ Vũ làng Mộ-Trạch vậy. (nguyên bản có chú rằng còn thiếu một đoạn.)</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>阮鼎革偸檄四方乎親明委勸之仕公元四十始就鄉試領首選莫大正六年癸巳未春公年四十五赴會試四場並第壹廷對擢進士及第授東閣校書和莫太宗所制表春天御講二詩皆頒優等刑部左侍郎俄遷吏部左侍郎業東閣大學士在朝八年疏劾弄臣阮世小者十八人請悉誅之其志欲使萬物各得其所微而致慧亦比自授以敬卜葉恐值壇防端貴橫恐累連姻遂托病致仕時公元五十二既歸田里起白雲庵於鄉之士仍號名士起逐風長春等橋歲時遊態築中津館於雪江之津作碑以記其父又修葺佛寺構老僧同遊時或扁舟泛金海郁海觀魚宴子卧雲散主塗山諸各山皆自杖履登臨適意嘆咏往來或徜徉終日每遇樹木青幽時鳥變聲輒欣然自得公雖在家莫事以師礼國有大政事輒遣使就訪或時徵至京詢以大計從容規畫禪蓋弘多尋復還庵頤志後以功封程川候累陞夫部尚書太傅程國公公博極聲書深明易理雨暘水旱禍福災祥存亡得喪之因無不前知常與門人張時舉卜易則乾卦而知八世之後起戈千其神祕淵奧不能盡述授徒甚眾惟馮克寬篤有慶阮璽張時舉最著初克寬假館遊學事既卒業公夜叩門語之曰鷄鳴矣</t>
+          <t>尚書武公道記</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Năm Quang-thiệu gặp lúc loạn lạc, ông về ẩn cư để dạy học trò, lấy đạo làm vui, chẳng cầu danh tiếng, nhưng sang đến thời đầu niên hiệu Thống-nguyên thì Trịnh-Tuy và Mạc-đăng-Dung cũng đều có ý hiệp chế Thiên tử để sai khiến chư hầu, hai bên gây cuộc nội chiến khiến cho trong nước chịu cảnh lầm than, lúc ấy ông có cảm hứng một bài thơ rằng: Thái hòa vũ trụ bất ngu chu, Ngũ chiến giao tranh tiếu thượng thu.</t>
+          <t>MẠO THỦ KHOA CỬU TRÙNG ĐẶC CHỈ</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>夜既明矣何不起而作食堅固何為寬悟遂請八清仕歸阮氏後扶樑中興為各臣興隱居不仕作傳奇謾錄公亥為斧正遂為千古奇筆時阮太祖曰我兵大振數戰神符讙王莫敬兵敗世祖因進兵由西山累京北中外皇皇誠獻以實虛計境內靳日寧我朝順平八年中宗崩無嗣太祖有特疑意詢之焉</t>
+          <t>武公道一蒙澤人也其父安富侯少而總齊時有鄰右衰老儒指庭前甘燕葉取岀一曰云庭前有燕皆著紫衣父對曰池下生蓮同張青蓋來大稱賞識者知其子孫必有科第同登之兆後生公與亮公起以馮爽稱</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Xuyên huyết sơn hài tùy xứ hữu, Uyên ngư tằng trước vị thùy khu? Trùng hưng Ba Hạ độ giang mã, Hậu hoạn ưng phòng nhập thất quy. Thế sự đáo đầu hưu thuyết trước, Túy ngâm trạch phán vị nhàn du. Sở dĩ có bài thơ trên, vì ông biết rõ nhà Lê sẽ được trung hưng, dẫu rằng ngày nay tạm phải tìm kế an thân, nhưng rồi sau đây tất nhiên sẽ lại khôi phục được nước.</t>
+          <t>Vũ-Công-Đạo người làng Mộ-Trạch phụ thân là An-phủ-Hậu. Ông vốn thông minh ngay từ thuở nhỏ, lúc ấy có một ông Đồ hàng xóm tên là Tả-Côn chỉ vào khóm mía ở trước sân ra một vẽ đối như sau: Đinh tiền hưu giá giai trước tử y, nghĩa là: mía ở trước sân đều mang áo tía. Ông đối ngay rằng: Địa hạ sinh liên đồng trương thanh cái, nghĩa là Sen sinh dưới đất cùng rán lộng xanh. Ông Đồ nghe xong tám tắc khen ngợi, còn người thức giả thì dự đoán rằng: đó là cái điểm mà con cháu về sau sẽ đổ đồng khoa, quả nhiên về sau Cụ sinh ra Ông và Công-Lượng cũng đều nổi tiếng tài hoa.</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>竟寘不詔決因使寬家人饗厚禮潛往海陽訪之公弗答但顧家童曰方今不穩在於粟穀不奸爾等可覓雀鴉穀種種之又命鳥遊寺僧童酒榼焚香餘無所及蓋徵示以事佛獎綿底意寬具馳苦太祖乃悟遂立英宗范舍人與公又同鄉誼嘗密使人請公為子求一條生路使者以銀一包為贄拜祈不已。</t>
+          <t>丙申科會試公完赴舉時村內東亭市有老嫗于稠人廣坐中粹面撻身躍立而言曰我是儉人降下茲料進士于吾我已知之爾澤邑文星正旺天帝簡知我故來相告爾等欲聞之乎</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Quả nhiên về sau nhà Lê trung-hưng, bốn phương trở lại yên tĩnh, bấy giờ bạn hữu đều khuyên ông ra làm quan, đến năm 44 tuổi ông mới chịu ra ứng thí, khoa hương thí ấy ông được đỗ đầu, rồi năm sau tức là năm thứ 6 đời nhà Mạc, lại ra tỉnh thi được đỗ thứ nhất, khi vào đình đối lại đỗ Tấn-sĩ đệ nhất danh, được bổ chức Đông-Các Hiệu-Thư, trong thời Thái-Tông nhà Mạc, ông có làm hai bài thơ Xuân-thiên ngự-tứ, đều dự hạng ưu, rồi thăng chức Hữu-Thị-Lang Hình-bộ, sau thời gian ngắn lại thăng chức Tả-Thị-Lang, kiêm chức Đông-Các Đại-học-sĩ.</t>
+          <t>Thế rồi đến năm Binh-thân gặp khoa thi hội, Công-Lượng cũng vào thi, lúc ấy ở chợ Đông-Định trong thôn bổng có một bà lão tự trong đầm đồng nhảy ra, đứng sừng trước mặt mọi người, mặt thì đỏ gay, đầu thì lão đảo, lên tiếng bảo mọi người rằng: Ta đây vốn ở Tiên cung cho nên khoa thi này được bao Tấn-sĩ ta đã biết trước, hiện nay làng Mộ-Trạch người, vẫn tinh dương vượng, đức Ngọc-Hoàng đã tuyển sẵn rồi nên mới sai Ta xướng đây bảo cho các ngươi biết rõ! Vậy thì các ngươi có muốn nghe không?</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>如適策杖後圍圍後有數十石塊答石嵌出橫繞軒前有群議縁石而行公徐目蟻而矢曰橫山一帶足以容身使者悟其意歸以告洪洪乃以計頴廣順遂蟠撫焉</t>
+          <t>村人奇之布席以坐四面還觀爭以美質當祈獻叩問之其人曰今科進士有六而幕澤居其三村人請問姓名曰登龍中再問之曰卓然牛中又問之曰公亮中眾人皆以為誣謗莫之信父後出榜率知其言識者自謂事有明定而天門放榜之事亦不託傳部說</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Trong 8 năm ở triều, ông có dâng sớ hạch tội 18 kẻ nịnh thần, xin đem chém để làm gương, nhưng rồi gặp phải sự cản trở, vì sợ liên lụy đến mình, nên ông cáo quan xin về trí sĩ.</t>
+          <t>Các ngươi trong thôn xóm thấy nói lạ lùng như vậy, họ bèn trái chiều mòi bà ấy ngời, rồi họ đứng bọc chung quanh và lại xô nhau đem trâu cau ra khấn vái để hỏi xem sao? Bà ấy đáp rằng: khoa này có 6 Tấn-sĩ thì làng Mộ-Trạch chiếm được 3 ngươi. Hỏi 3 ngươi ấy họ tên thế nào? Bà ấy đáp: Đặng - Long, hỏi lần thứ hai, đáp rằng: Trác-Lạc, hỏi lần thứ ba, đáp rằng: Công-Lượng. Mọi ngươi nghe xong vẫn yên trí là câu nói hoang đường chứ chẳng ai tin, nhưng rồi đến khi kéo bảng thấy đúng như vậy. Bấy giờ những ngươi thức giả mới tin là có tiền định, mà việc phóng bảng trên cửa nhà giới, cũng chẳng phải là câu nói ngoa vậy!</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>為隂氏莫延歲八年發洽年號乙酉十一月公寢疾莫蒼治使人心問且語以國事公但曰他日國有事故高平難小可延數世福他無所言後七年莫之乾統隆泰順德永昌退保高平歷三世四十七十年而後泯其言無不騐類如此是月二十八日公薨于家壽九十五學者尊為雪江夫子葬于鄉之原公胸依酒落天資極高而充養補裨渾然不露圭角人不問則不言言則必中從容就事不見其有為居家四十四年而其心未嘗一日而亡世憂時愼俗一發於詩文章出於自然天口輒成不事雕琢簡而暢淡而味皆有觀於世教所依國語詩賦甚多著日雲詩集未千餘首今行于世者百餘首父中津賦而止然觀其大略齊月光風千古猶可想見公嘗有詩云高潔誰為天一士安閒我是地行行傳蓋自言其志也</t>
+          <t>茲科未生試一年間有北地師經登第龍祖登觀者良久曰我纏到青池縣月蓋社者阮族舊墳以為來科必發首科今按這苟不讓月蓋地脈來春亦當得者科人以爲誣朝之曰龍競假真都亂說豈有一榜二首科之理乎</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Thế là giữa năm Quảng-Hòa thứ 2 ông mới 52 tuổi đã xin trí sĩ, treo mũ về làng, dựng am Bạch-Vân ở phía tả chỗ làng ông ở, và vẫn lấy hiệu là Bạch-Vân Cư-sĩ. Khi ấy ông có bắc hai chiếc cầu Nghinh-Phong và Trường-Xuân để khi hóng mát, dựng một ngôi quán gọi là Trung-Tân ở bên Tuyết-Giang, có bia để ghi sự thực. Ngoài ra ông còn tu bổ chùa chiền, có lúc cùng các lão tăng đàm luận, có khi thả một con thuyền dạo chơi Kim-hải Úc-hải để xem đánh cá. Còn chỗ danh sơn thắng cảnh, như núi An-Tử, Ngọa-Vân, Kính-Chủ, Đồ-Sơn, nơi nào ông cũng chống gậy trèo lên, thừa hứng ngâm vịnh quên cả sớm chiều, mỗi khi thấy chỗ rừng cây xanh tốt, chim đổi giọng ca, thì ông hớn hở tự đắc, quả là một vị Lục-địa Thần-tiên. Nhưng trong thời gian dưỡng lão ở chốn gia hương, tuy rằng không dự quốc chính, thế mà họ Mạc vẫn phải kính trọng như một ông thầy, những việc trọng đại thường sai sứ giả về hỏi, có khi lại đón lên kinh thành để hỏi, ông đều ung dung chỉ dẫn, nhờ được bổ ích rất nhiều.</t>
+          <t>Nhắc lại khoa này một năm về trước có thầy địa-lý Tàu khi qua ngôi mộ Tồ nhà ông Đặng-Long thấy Địa xem xét hồi lâu rồi bảo mọi ngươi rằng: Khi tôi mới đến xã Nguyệt-Áng thuộc huyện Thanh-Tri đó xem lại ngôi mộ Tồ họ Nguyễn thì tôi đoán rằng: khoa thì sang năm họ ấy sẽ có người đỗ Thủ-khoa, ngày nay xem cục đất này khi mạch cũng không kèm gì Nguyệt-Áng, sang xuân thế nào cũng phát Thủ-khoa. Lúc ấy ai cũng chê điều cho rằng: Long hồ thực hư đều là những câu nói hão, chứ có lẽ đầu cùng trong một bảng mà lại có hai Thủ-khoa!</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>妻二人子十六男女五長子號寒江魏士蔭受惠員夫大生切德切德生道進道進生道通道通生登瀛登瀛生時當時當年六院十五有男子效人皆八世孫也</t>
+          <t>至是策題問以君道聖籠子敬天用人開國紀綱保功臣法度國用治道禮樂將帥賞罰中興功業國勛九十四目為問阮廷柱中會元簽籠中第二醜而八將王庭王上見簽龍相貌比廷模勝之有首判云此子不當首科耶命在天柱王右故時人稱楚樑字首科餐龍觀首科方覺北師之書亦為高見</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Xong rồi ông lại trở về am cũ, về sau được phong tước là Trình-Tuyền-Hầu, dần dần thăng đến Lại-bộ Thượng-Thư Thái-phó Trình-Quốc-Công. Năm Thuận-bình thứ 8 Lê Trung-Tông mất, không có hoàng nam nối ngôi.</t>
+          <t>Nhưng rồi đến khoa thì ấy thì đề tài sách vẫn lại hỏi về quân đạo Thánh học v. v... công 14 mục. Thi xong Đinh-Quế được trúng Hội - nguyên, Đặng - Long được đỡ thứ nhi, đến khi cùng vào Vương phủ dự yến, Hoàng-Thương nhìn thấy diện mạo Đặng - Long có vẻ tuần tú hơn Đinh-Quế nhiều, nên Ngai phân ngay rằng: Gã này không đáng mặt Thủ-khoa hay sao, rồi Ngai ra lệnh cho Long được đứng ở bên tay phải Đinh-Quế. Vi thế lúc ấy mới có câu rằng: Đinh - Quế là Thủ-khoa Chữ Đặng-Long là Thủ-khoa đẹp, bấy giờ người ta mới tin thấy Địa cao kiến hơn đời vậy.</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>按廣鄉之西南潭淤四五聚高亦可數四敵深泓一大許同光照鍾秀毓英宜其達人者尚焉</t>
+          <t>時入道未第吹年彼孝事偽因他適鄉試場目次點心中真更問夜為交至唐豪縣無得社行過去外聞內有聲喚曰進士何之公郎馳至三闕見闊者二人載嘆因問之曰這裏某宮人在閣者曰正中黃衣乃玉皇上帝座兩旁青衣者南曹北斗是也公進八庭前跪請曰敬問員進士何科見在旁二員面問中正知幕間之狀俄聞曰許茲科公曰來春袁經未除何能望此闡有聲曰震公再請曰臣藥已欠點知何又聞曰訴見點入受中喜不自勝急喜起趨出跌躡于地見在內老人調清水一盃灌之既而醒覺口中猶有香臭</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Thế-Tổ do dự không biết lập ai, hỏi Trạng-nguyên Phùng-khắc-Khoan, cũng không quyết định nổi, nên mới phải sai gia nhân ngầm đem lễ vật về tận Hải-dương để hỏi, ông không trả lời mà chỉ quay lại bảo các gia nhân rằng: «Vụ này lúa không được mẩy, chỉ tại thóc giống không tốt, vậy các người phải đi tìm giống cũ để mà gieo mạ». Nói xong ông lại lên xe ra chùa, sai các chú tiểu quét dọn đốt nhang, ngoài ra không hề đả động gì đến chuyện khác, bởi vì ông đã hé mở cho biết cái thâm ý là «cứ việc thờ phật thì được ăn oản». Rồi Trạng Phùng thấy thế vội vàng về báo, Thế-Tổ hiểu ngay, bèn đón Anh-Tông về lập, tình thế trong nước mới được ổn định. Trong thời gian ấy Đoan Quốc-Công Nguyễn-Hoàng là con Chiêu-Huân Tĩnh-Vương, đương lúc ở trong tình thế nguy ngập vì sợ không thoát khỏi tay Trịnh-Kiểm, thân mẫu của người vốn là chỗ đồng hương, nên thường bí mật sai người về làng nhờ ông chỉ giúp cho con giai bà một đường sống. Sứ giả đặt gói bạc nén ở trước mặt ông, rồi bái lạy lia lịa. Ông thấy sứ giả năn nỉ xin mãi nhưng vẫn không nói gì, rồi đứng phắt lên, tay cầm chiếc gậy thủng thỉnh ra lối vườn sau, là nơi có hơn 10 tảng đá xanh xếp thành một dãy núi giả quanh co, trước núi lúc ấy có những đàn kiến đương men tảng đá leo lên, ông ngắm nghía chúng một lát rồi mỉm cười và đọc một câu: «Hoành-sơn nhất đới khả dĩ dung thân», nghĩa là một dãy Hoành-Sơn có thể dung thân được đó.</t>
+          <t>Còn như Công-Đạo lúc ấy cũng chưa dỡ đạt, rồi sang năm sau gặp việc đại tang, nhân lại có việc phải đi nơi khác, nên bị thiếu điểm ở trường thi hương, giữa lúc còn đương lo phiên thì bỗng một đêm ông nằm mơ thấy: mình đi đến xã Võ - Ngai thuộc huyện Đường-Hào, khi qua ngôi chùa chợt nghe bên trong có tiếng hỏi: Quan Nghè định đi đầu tá Ông vội chạy vào trước cửa Tam quan, thì thấy hai người cầm roi đứng canh hai bên, ông hỏi trong ấy có vị quan nào, họ đáp: Người mặc áo vàng ngồi ở chính giữa là Đức Ngọc-Hoàng, còn hai người mặc áo xanh hai bên tức là Nam-Tảo Bắc-đầu đó. Ông nghe hai người bảo thế vội tiến vào sân quy gói hỏi rằng: Khoa nào hạ thần được đổ Tấn-sĩ? Hỏi xong thì thấy hai người nhìn vào vị ngồi ở giữa hình như bẩm vấn điều chi rồi sau phân bảo: Anh sẽ đổ ngay khoa này! ông lại hỏi tiếp: Nhưng mà sang xuân thì thân còn đương mặc áo sô gấu biết làm thế nào? đáp rằng: Triền, (tức triền hạn), ông lại hỏi trước kia thân đã thiếu điểm thì sao? đáp: Tha cho điểm đó! Nghè được mấy câu phân bảo ông rất vui mừng, vội vàng chạy ra, chẳng ngờ xảy chân té nhào xuống đất, bống thấy bên trong có một ông già đem chén nước lă ra đổ vào miệng, rồi một lát sau thì ông tỉnh dậy, trong miệng vẫn còn hương thơm.</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>古鉗云研池水水暎豈不信然</t>
+          <t>笑已科春園以有事展誠又先是各處直士徃徃潛八鄉試場代試多致大顯至是昭祖判云凡為人顯者為人代試必是有所文字應一切藏之今以是范吳科公親舅來謝族兄惟誨同色公朝四各同榜自有科目以來未之有也</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sứ giả hiểu ý trở về thuật lại với Nguyễn-Hoàng, Hoàng bèn xin vào trấn thủ Quảng-Nam.</t>
+          <t>Thế rồi vừa bước sang năm Kỷ-hợi trong nước gặp lúc hữu sự, nên kỳ Xuân-thí lại phải hoãn đến mùa đông. Và lại trước kia Cống-sĩ các nơi thường hay đội quyền thì giúp trong kỳ thi hương, cho nên nhiều người thiếu điểm. Ngày nay Chiêu-Tô phán rằng: Những người đã đi thi họ tất nhiên là người học khá, vậy nay nhất thiết tha cho cái lối thiếu điểm năm xưa, vì thế ông cũng được miễn. Rồi ngày khoa ấy ông cùng Bác ruột là Cầu-Hối, em họ là Duy-Hải người cùng ấp là Công-Triều, tất cả 4 người cùng được đề danh đồng bảng. Kể từ lúc có khoa mục cho tới ngày nay chưa bao giờ thịnh đến như vậy! (Kiểm điểm cũng như kiểm diện).</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>其後清使周粲謂嶺南人物理學有程泉筆之於書而傳於中土公詡宮國</t>
+          <t>公在朝言論碌何不辟權貴常有諫闕鷄文奉進昭祖深嘉之陽德間奉往北使回至南亭遇賊依攬阻陸路不通上國給以大艘從安廣水道而回仕至都御史壹因執奏武惟斬與內臣漢都公之罪見武惟斬王不從公以頭顱系柱凜然有奸廷折楹之風時稱直御史罷歸未幾復得召用任至尚書郎八十義公之前程事築未第時一變已非見矣</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mạc Mậu-Hiệp năm Diên-Thành thứ 8 tức năm Ất Dậu tháng 11 thì ông lâm bệnh, Mậu-Hiệp sai sứ đến vấn an và hỏi về quốc sự. Ông chỉ trả lời rằng: «Sau này quốc gia hữu sự thì đất Cao-bằng tuy nhỏ cũng giữ thêm được mấy đời», ngoài ra không nói gì nữa. Quả nhiên cách 7 năm sau thì họ Mạc mất, rồi rút lui lên giữ Cao-bằng được 70 năm, nghĩa là sau 3, 4 đời thì mới hoàn toàn bị diệt, coi đó thì lời của ông dự đoán chẳng sai chút nào. Nhưng rồi trong tháng ấy giữa ngày 28 thì ông tạ thế, hưởng thọ 95 tuổi, học trò suy tôn hiệu là Tuyết-giang phu-tử phần mộ ở trên một cái gò đất trong làng. Nói về môn sinh của ông sự thực không biết bao nhiêu mà kể, nhưng nói riêng về những người đã có tiếng tăm lừng lẫy thì có những ông như Phùng-khắc-Khoan, như Lương-hữu-Khánh, Nguyễn-Dữ và Trương-thời-Cử, đều đã nhờ ơn truyền thụ. Nhắc lại khi Phùng-khắc-Khoan còn theo học Bạch-Vân Tiên-sinh, lúc thành tài rồi bỗng có một đêm Tiên-sinh đến chỗ nhà trọ của ông, gõ cửa bảo rằng: «Gà gáy rồi đây, sao anh chưa dậy nấu ăn, mà còn nằm ỳở đó», Khắc-Khoan hiểu rõ ý thầy nên vội thu xếp vào vùng Thanh-hóa, cùng ẩn cư với ông Nguyễn-Dữ, trong thời gian ấy Nguyễn-Dữ có soạn ra bộ Truyền-Kỳ-Mạn-Lục, được ông phủ chính rất nhiều, cho nên mới thành một cuốn Thiên cổ Kỳ bút.</t>
+          <t>Xét thấy khi ông làm quan tại triều, nghị luận rất là cũng cỏi, không hề kiêng nề những chỗ quyền môn, thường tiến bài văn can gián về việc chơi gà, rất được Chiêu-Tô khen ngợi. Vào khoảng năm Dương-Đức (1672-74) ông sang sứ bên Tàu, khi về đến tỉnh Nam-Ninh thì địa phương ấy có giặc, đương bộ bị ngễn, địa phương quan phải vất 1 chiếc thuyền lớn để dưa ông về đường thủy, rồi sau ông làm đến Đô-Ngư-Sử Đại, lúc ấy ông tâu về việc Duy-Đoàn và Hán Quần-Công, thấy Vương không nghe, ông bèn dập đầu vào cột, khi phách lâm liệt chẳng khác gì người níu gãy bao lan ngày trước. Cho nên đời mới gọi ông là Trực Ngư-Sử. Tuy nhiên sau vụ ấy thì ông bị bãi chức trở về cố hương, nhưng chưa bao lâu lại được triệu dụng, rồi làm đến chức Thượng-Thư Trí-sĩ. Kể ra từ năm 18 cho đến 86 tuổi, năm nào ông cũng có thơ Tự-thuật, viết bằng quốc âm và thơ Đường-luật, thơ đều xuất khẩu thành chương, rất được nhiều người truyền tụng. (Thấy trong tập Lão-Hội) bởi vì sự nghiệp tương lai của ông thì một giấc mộng đã bảo từ trước khi đổ đạt vậy.</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>進士繚如虎記黎胡燕仙侶仙洲人也</t>
+          <t>公外自風流而為行統實初為山南督同時賜夫人不在有二門下人擕一絕艶歌兒來欲其買寵公曰我自少至長未常違非已之色汝以尤物殺我平拒而遣之離居貴顯不買群妾只有微時一夫人與之緒影交常對兒孫言我雖不逮古人而未常犯奸色之或是人之所難也</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ông Lê-như-Hồ (triều nhà Mạc) người xã Tiên - Châu thuộc huyện Tiên-Lữ lúc mới sinh ra trong rất vạm vỡ, đến khi lớn lên, thì người cao tới 5 thước 5 tấc, khoảng lưng chu vi đến một thước năm, Ông vốn có tính chăm học chỉ phải cái tật ăn khố mà nhà thì nghèo. Mỗi bữa cha mẹ nấu cho đến nồi 7 cơn mà Ông cũng ăn hết nhẫn.</t>
+          <t>Người ta xét thấy ông là người bên ngoài có vẻ phong tình, nhưng mà trong tâm giữ rất thuận cần, thử coi khi ông còn làm Đốc-Đồng tại xứ Sơn-Nam có viên thuộc hạ dòm lúc phu-nhân đi vắng, bèn đem một ả ca nhi tuyệt sắc vào định toan sự cầu thân. Nhưng ông bảo rằng: Ta đây từ nhỏ đến lớn chưa hề xăng bày đến cái sắc đẹp không phải của mình, vậy người toan lấy vật là để chức lay chuyện ý chí của ta đó chẳng? Thời muốn tốt thì người phải đem ngay đi chỗ khác. Chả thế mà trong lúc phu quí như vậy ông vẫn chẳng mua nàng hầu, trong phòng chỉ có mỗi một phu-nhân là người xe to kết tóc từ lúc hàn vi thôi, bởi thế nên ông thường bảo con cháu: Ta dầu không theo kip cờ nhân, nhưng cũng chưa hề phạm điều sắc giới, giữ được như thế tướng cũng khó thay.</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>少南處生而岐嶷及長體大過人高五尺五寸家貧好學性善飯父母嘗羹七歲餳飯公食無餘學得半年以家計不贍出為善片社富家贅婦翁食以五歲鍋飯輒嗜臥廢學亦公疑之以問公之父曰聶聞君言有佳婿是好學的人而今懶廢不知有何緣故父曰兒自蒙托愛公毋食之知何翁曰飯五歲鍋矣</t>
+          <t>其平生教習多得英才如東鄰撫眼公范光宅丹輪探花武成賊楊柳會元阮各譽誼以魁科望異代見推皆公之門弟也今之學者猶尊仰焉</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Vì thế cha mẹ chỉ cho theo học được đến nửa năm thì hết lượng thực, đánh phải cho sang gửi rể ở nhà phù Ông bên xã Thiện - Phiên, cha vợ cho ăn một nồi 5 cơn, thì ông chỉ nằm suốt ngày không hề mò đến quyền sách. Cha vợ lấy làm nghi hoặc hỏi cha để rằng: Trước kia tôi thấy Ông bảo Cậu nó là người chăm học, mà nay lười biếng như vậy, là có làm sao? Cha để hỏi lại: Được Ông quá yêu cho cháu sang ở bên ấy, vậy thì mỗi bữa Ông cho cháu ăn bao nhiêu? Cha vợ đáp: Mỗi bữa một nồi 5 com cơ đấy!</t>
+          <t>Nói tóm lại, sĩ phu thời ấy nhớ sự học vấn và đạo dức của ông đã gây nên được biết bao nhân tài. Tí như quan Bảng-nhơn Phạm-quang-Trạch ở làng Đồng-Ngạc, quan Thám-hoa Vũ-Thanh ở làng Đan-Luân và quan Hội-nguyên Nguyễn-danh-Dự ở làng Dương-Liễu, đều là các bậc khôi khoa, được đời tôn trọng và cũng đều là học trò của ông, khiến cho đời nay người ta vẫn còn ngưỡng mộ,vậy.</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>父曰無雖家用不數此兒尚有七歲餌之食今如此相待其不學也</t>
+          <t>廉蔣公遺記</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cha để mỉm cười nói: nhà tôi dẫu tùng cũng phải cho cháu ăn 1 nồi 7 com! Ngày nay Ông cho ăn ít như thế thảo nào nó chả nhắc học.</t>
+          <t>DANH THẦN VÕ-TU.</t>
         </is>
       </c>
     </row>
@@ -2753,12 +2753,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>固宜爾聞言輒加倍焉公自是始索書目讀一二歲耳</t>
+          <t>武娶唐安穫澤人也浙陽省洪德韜聖宗癸丑科中黃甲公性顔廉直居官清儉未嘗妄取于人時頗尚賂遺用唐太宗故事使人懲誡試之他官従従受之公獨見拒饋請人固請曰今習尚如此寢以成風且這條菲物而相公不受為傷廉也公作色曰世人比自而獨我独清豈以爾甘言而易其樑驅而出之其人固奏帝嘉其人有暮夜卻金之郎賜公廉二字許入朝黏于衣領以旌異之</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cha vợ biết thế cho ăn tăng lên ti chút. Bấy giờ cậu mới tìm sách để đọc qua loa, mẹ vợ thấy vậy có ý bất mãn bảo với Ông rằng: Ông khéo kén chọn con rể, chỉ được cái nết ăn khỏe mà thôi, còn sự học hành như thế, thì sau nó làm nên được những trò trống gì. Ông giải thích rằng: Điều đó bà đừng lo ngại, vì nó ăn khỏe hơn người, tất nhiên nó cũng có sức hơn người đây chứ. Bà đáp ừ nếu quả như vậy, thì nhà ta đây hiện có mấy mẫu ruộng rẫm, thử bảo nó ra phát có xem sao. Cậu thấy cha mẹ vợ bàn mảnh với nhau như vậy, sáng sớm hôm sau Cậu liền vác một con dao thật lớn xin ra phát có ngoài đồng, nhưng ra đến nơi thì Cậu lại nằm giả ngủ dưới gốc cây bàng. Đến khi mẹ vợ đi chợ về trông thấy tức giận dấy ruột, chạy về la lối om xóm: Ông oi từ nay Ông còn bảo nấu thêm com cho nó ăn nữa hay thôi.</t>
+          <t>Ông Võ-Tu người làng Hoạch-Trạch huyện Đường-An thì đã Hoàng-Giáp khoa qui-sửu thời Lê Hồng-Đức, ông vốn có tánh liêm-khiết và ngay thẳng, ngay lúc làm quan cũng vẫn giữ nếp thanh bạch, không hề lấy lễ của ai, giữa lục ấy cái tệ tham những dương hoành hành. Hoàng-Đế muốn bắt chước Vua Đường Thái-Tông ngày trước, cũng sai người giả làm dân thường đem lễ đút lót các quan, quan nào cũng nhận, duy có mình ông nhất định cự tuyệt, người đưa lễ có nài nói rằng: hiện nay phong tục hối lộ đã thành thói quen, và lại một món quà đây cũng chẳng đáng giá bao nhiêu, nếu Ngài nhận cho thì cũng không hại gì đến tiếng liêm khiết. Ông thấy người kia cổ tinh nài ép thì nghiêm sắc mặt mắng rằng: nhà người nên nhớ: Thế gian đều trọc, chỉ có một mình ta thanh! nhẽ nào ta lại vi câu nói ngọt và món lễ hậu của người mà dồi tiết tháo, người phải đem đi tức khắc! Người đem lễ bị ông quát đuổi, đem lễ ra về, vào tàu với vua như thế. Vua khen là người biết trọng khí tiết cũng như các vị thanh liêm thời trước chẳng chịu nhận vàng trong lúc đêm khuya. Vì thế Ngai mới ban cho hai chữ Liêm tiết, và cho định vào cờ áo trong lúc vô triều cốt để nếu cao phẩm giá,</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>安世有不足處謂顧曰擇得一好婿來雖勉強讀書只要善食終焉</t>
+          <t>仕到刑部左侍郎廉節各良家無祖石之儲而怡然自適所得寸禄僅足代耕有薄田數高不以遺其子臨終嘆許本社為祀田蓋取白清遺子孫之意邑人重其義香火不絕至今猶存焉</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hôm nay nó muốn tiếng ra phát cổ, thế mà từ sáng sớm cho đến lúc tôi về chợ, nó vẫn còn nằm ngủ dài ở dưới gốc cây. Chá tin thì Ông ra mà coi thử.</t>
+          <t>rồi sau ông cũng làm đến chức Thị-lạng bộ Hình, thế mà bồng lộc cũng chỉ tạm đủ chứ không dư dật, ruộng nương cũng chỉ có được 3 sao, ông cũng chẳng chia cho con, đem cùng cho xã để làm tự điển, tỏ ý chỉ để hai chữ thanh bạch lại cho con cháu mà thôi. Vì thế nhân dân trong xã thấy đều tôn kính, lập đến phung sự hương khói ngát mãi đến nay.</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>做得何事辦鮮之曰他食兼人之食必有兼人之勇母曰苟如此我有田草始無試使他刲了公聞之郎取刀出林頭榕樹下假臥速象母牲市同見而嗔之郎歸告其六翁曰今猶多造飯與他吃否託言刈草自旦至歸市猶在一處打眼因橋翁手往想不意自岳母歸後公郎就田刈之神觀瞻息間效敵草間俱盡魚走之不及所浮邀收換不可勝計地舅媽來見之因嗟訝不已其後穀嘉時岳母使公往市喚傭工來公乍出輒囘報云其小已喚之無肯行者時家中已養二十歲鵠飯以待工人而無有二公輒取餌來食之殆盡吾母喚之曰這飯吃了不幾成賜破那腹耶</t>
+          <t>火保陳瑋記</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Thế rồi bà tóm lấy tay dẫm ông ra thẳng cánh đồng. Nhưng bà có biết đâu rằng con rể của Bà vẫn nằm giả ngủ, đợi Bà đi khuất thì Cậu lập tức vác dao xuống ruộng phát lấy phát đẻ, chỉ trong chốc lát thì mấy mẫu cỏ đều đã quang lăng! đến cả tôm cá đều không chạy kip nên bị chết nỗi nhan nhân vót được rất nhiều. Khi hai Ông bà tới nơi, cũng phải hết sức kinh ngạc. Rồi sau đến mùa lúa chín mẹ vợ sai Cậu đi mướn thợ gặt, Cậu đi một lát quay về bảo chẳng mướn được ai cả, nhưng mà lúc ấy nhà đã nấu sẵn nồi hai mươi com, Cậu bèn đón com ra ăn hết quen, mẹ vợ lắc đầu báo: Con ăn nhiều quá như vậy, chẳng sợ vỡ bụng hay sao, Cậu thưa: mà đừng ngại! công việc gặt thóc hôm nay con xin đảm đang hết thầy.</t>
+          <t>THỂ ĐÁO THỦ, PHONG HIẾN NHIỆP HÀO CƯỜNG TRẦN-THƯƠNG.</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>公曰媽媽不須委惱今番經刈某請獨當遂袖弄一大段為俗曰：</t>
+          <t>陳佛璋慕澤人也弘禎檢中興後甲長科中進士為人廉直初為乂安憲察侯時本處有國舅舅恃勢驕橫無所畏避徑徑肆行不法人奏是之其訴章堆積每有公事到輒行欺侮他官亦無知之何自公到者任他尙黠愈滋訟牒交至耶同世間清善拿回杳尋機殺之他黨聞知遂至公家圍過意欲報仇公急下漁舟倍道而去</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ăn uống xong rồi Cậu liền dẫn hai đoạn tre lớn để làm đòn xóc, và chẻ một bó lạt dài quầy ra ngoài ruộng, gặt đến quá trưa thì xong cả hai mẫu lúa!</t>
+          <t>Ông Thường người làng Hoạch - Trạch dỗ Tấn - sĩ khoa giáp-thin thời Lê-Kính-Tông 1600-1619 (niên-hiệu Hoàng-Định.) Ông vốn có tính liêm trục, khi làm Hiến-Sát-Sư Tỉnh Nghệ-An, trong xứ có vị Quốc-cữu ỷ thế làm can chẳng kiêng nề gi pháp luật, nhân dân bị khổ làm đơn kêu quan kẻ đến hàng tập, quan có mời đến cửa công phân xử thì ông Quốc-cữu quát tháo om xóm, Quan cũng phải nhận. Ngày nay ông vừa đảo nhậm, đã nhận được rất nhiều đơn, ông bèn thira dip bắt về công đường tra tấn đến phải bỏ mạng. Bọn gia nhân của Quốc-cữu nghe được tin này bèn kéo nhau đến vậy kín tư thất định bắt ông phải đến mạng. Ông với thoát xuống một chiếc xưởng đánh cá chạy về kinh sư,</t>
         </is>
       </c>
     </row>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>槴乾，幷參大繩以往繞半月，</t>
+          <t>既至京師即自詣政堂免冠頓首謝曰臣誠忝意司為朝守法而國舅杭弄雖行臣一時憤激不覺已過手了今伏闕待罪斧鑕是甘錦上訊問之有知其事乃獎諭曰設官以爲民風憲祛除民害可謂稱職何罪之有公拜謝而長再歸任所自是豪彊畏服境南然後奉北使仕至吏部左待郎贈少保知都公</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>bó thành bốn bó lững thừng quầy về!</t>
+          <t>bỏ mũ xuống sàn chính đường khấu đầu tạ tội: Thân nay làm giữ chức vị Hiến-ty phải vi Triều-dinh thi hành pháp luật, thế mà Quốc-cữu lại dám ngang tàng khinh thường quốc pháp, vì thế trong lúc quá giận thân đã lỡ tay, vậy xin về nơi của quyết chịu tội dưới lưỡi riu búa thân cũng cam tâm! Hoàng-Thượng thấy ông tâu trình như vậy, lập tức tra hỏi nguyên do, về sau biết rõ công việc thì lại khen ngợi và dụ cho ông biết rằng: Triều đình đặt ra quan chức là để vì dân, ngày nay Hiến ty trù được mới hai cho dân thế là xưng đáng với chức vụ chứ còn tội gì. Nghè lời dụ xong ông liền bài ta lui ra rồi lại trở về Ty cũ, từ đấy về sau cương hào trong hạt thấy đều kiệp sợ, chẳng dám ho he, nhân dân nhờ được an cư lạc nghiệp, rồi cách ít lâu thì ông phượng mang sang sứ Bắc - quốc, rồi làm đến chức Tả Thị-lạng, lúc về hưu lại được tặng chức Thiếu-phó tước Hương-Quân-công.</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>復餘二畝，殆盡，</t>
+          <t>狀元莫擬之記</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>từ đấy mẹ vợ mới tổ thực tình yêu mến, cho ăn đầy đủ để chuyên vào việc học hành, nhưng lạ thay! trong khi học tập, hễ Cậu viết xong trang nào, thì lại đốt ngay tức khắc. Trong thời gian ấy, các vùng lân cận thường hay mở đám hội hè, đám nào có treo giải vật, Cậu cũng xin giữ giải nhất, bao nhiêu lực sĩ đó vật, vi đã biết sức của Cậu nên chẳng ai dám so tài! cho nên người ta mới tặng tên là (Như-Hồ). Thế rồi cách mấy năm sau, khi vừa đúng 30 tuổi thì đã nổi tiếng văn chương, bấy giờ đương triều nhà Mạc niên hiệu Quảng-Hòa (1541 - 46), Ông ra ứng thí được đỗ Tán-sĩ vào khoa Tán-Sửu, lúc ấy có người đồng bảng là Nguyễn - Thanh Ẩn người xã Bột - Thái thuộc huyện Hoằng - Hóa thường khoe nhà mình giàu có. Ông nói bốn rằng: Gia tài của Ông, chỉ đủ dải tôi một tháng là cùng?</t>
+          <t>Mạc-Đinh-Chi, Lưỡng quốc Trang-Nguyễn, Trang-Nguyễn hai nước, (Việt-nam và Trung-quốc).</t>
         </is>
       </c>
     </row>
@@ -2855,12 +2855,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>各束為四捆而回，</t>
+          <t>陳朝為國欲元首大擬之字節文至靈龐洞人也史記旁河人李朝尚書莫令徵績之孫也李仁宗廣祐二年徵績中進補翰林學士</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Thanh đáp: Nếu vậy mời Bác quá bộ vào chơi, tôi xin cung phượng ba tháng là ít, Ông đáp: thời khởi cần nói chi ba tháng, hôm nào tiện dip xin Bác hãy tạm thiết tôi một bữa xem sao? Ông Thanh nhận lời, hẹn dùng hôm nào sẽ xin đón tiếp. Rồi ít lâu sau, đúng ngày ước hẹn, Ông cùng với 1 tiểu học tới nhà Ông Thanh, chẳng ngờ Ông Thanh đi vắng, ông bèn nói với phu nhân: Tôi là bạn cũ của Bác trai đây, nhân có việc đi qua ghế vào thăm Bác, chẳng may Bác lại đi khỏi, vậy nay có hơn 30 tùy tùng, phiền Bác cho ăn một bữa, phòng có được chẳng. Phu nhân thấy nói là bạn của chồng, với bảo người nhà nấu ngày 3 nồi 10 com và đóng 5, 6 mâm cỗ chính đón bụng ra. Ông bèn giả tăng bảo đưa tiểu học: my ra gọi chúng vào đây, nhưng rồi chẳng thấy có một tên nào.</t>
+          <t>Mạc-Công-Đinh-Chi, tên tự là Tiết-Phu, người xã Lũng-Đông thuộc huyện Chi-Linh. Sử-ký chép người xã Bàng-Hà, nhưng xét thấy từ đây Đột- Lãnh trở xuống, tất cả một dài ven sông, theo bản đồ cũ đều thuộc về xã Bàng-Hà, cho nên ngày nay ngôi chúa của làng Lễ-Xá cũng thấy kêu tên là chúa Bàng-Hà, đó cũng là một chứng có vậy. Ngải vón là cháu quan Thượng-Thư Mạc-hiền-Tích Triệu Lý ngày trước. Quan Thượng-thu thì đồ Tấn-Sĩ đệ nhất danh khoa Bình-Dân thời Lý Trung-Tông, làm đến Thượng-Thư bộ Lại và được nhà vua bán cho bộ áo kim-ngư (cả vàng), em là Kiến-Quan cũng đồ Tấn-Sĩ làm đến Công-bộ Thượng-Thư, còn ông Trang đây là cháu cụ Hiền-Tích, tên tục gọi là Sách-Tú, (vì xã Lũng- Đông quen gọi là Kẻ-Sách, cho nên mới có tục danh như thế).</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>每捆由是愛之仍許以飽食就學公當學時每得紙千張讀了即焚之傍縣有交跌場公郎往取第一標都力士亦不敵較以其有力故各知亮年立辛丑科一舉中進士時同科有同年阮清弘化人也</t>
+          <t>世傳鄉有大陵阜林木鬱茂沐猴居之其母常往刈薪為雄猴所脅歸諸其父父遂服婦人衣懷刀往焉猴狙故態以又遂提刀擊斬殺且長從視之見土虫已將假冤墳成一堆艾異之母尊受胎暮年生公資相卑陋人以為假精之聽其父臨終遺言百塗猴墳之上至亦默會天機也其後公沒附葬其下今猶存焉</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Duy chỉ có mỗi mình Ông ngồi ăn, ăn hết mâm này lại đến mâm khác, khi ăn quan cả bấy nhiêu mâm rồi Ông mới cáo biệt ra đi. Chiều hôm ấy Ông Thanh thoát về đến cửa, phu nhân với ra nói ngay: Cậu ơi: nhà ta hôm nay có một câu chuyện rất là buồn cười; Ông hỏi chuyện gì?</t>
+          <t>Nay cứ theo như tục truyền, thì nơi làng Ngải có một cái gò rất lớn, cây cối um tùm, tức là chỗ ở của loài khí độc. Một hôm, thân mẫu của Ngài lên đó kiếm cùi, bị con khí độc hãm hiếp, trở về thuật lại với ông (tức thân phụ Ngài), ông bèn cải trang dân bà, trong mình dẫu con dao nhọn, rồi cũng giả vờ lên núi hải cùi. Khí dục lại quen thói cũ nhảy ra, liền bị ông dâm cho một mũi dao chết ngay tại chỗ, rồi ông quay về. Sáng sớm hôm sau, ông ra coi thử thì thấy xác con khí độc đã bị mồi dùn thành một cái mò rất lớn. Ông rất lấy làm kỳ. Về phần mẫu thân, sau khi bị khí hãm hiếp chẳng ngò bà thụ thai, đủ ngày tháng sinh ra một cậu con trai, người thấp lè tè, tướng mạo trong rất xấu xí, ai cũng bảo là giống khí. Vi thế, đến lúc phụ thân sắp sửa làm chung, Cụ có di chức lại rằng: phải tàng Cụ lên trên mò con khí đó, chắc rằng Cụ cũng hiểu ngầm thiên cơ nên mới hẹn như vậy. (Rồi sau Tràng Mạc-Định-Chi, lúc mất, cũng tàng ở phía dưới chân, ngày nay vẫn còn đủ cả).</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>嘗與公語及家計公戲之曰兄之家資僅足供我一月粮清曰請供三月之頓會不須三月斬請許一頓如何清曰諾約以某日辰臨至公遂與一僕徒諳清家不意清有事他適公使達于夫人我與兄有舊偶因公事往過有隨從三十餘人須許一頓夫人即喚家童煮十歲鶴飯者三并物食五六盤聚了進之公佯謂其仆曰爾忘喚請從者來既而不見一人公就取盤鍋并物食吃都盡了因致謝而去逮暮清歸夫人語之曰我家今日有一事好笑請問故夫人笑道早有一人自稱與君相善多帶從人者來求獵予一頓妻發並辨以待不謂只有一酌人坐吃妄自竊視見一碗數口恰似風捲雲殘三盞飯並五六食盤一時俱盡不知是人是怪清悔之曰此必我同年儒洲人也</t>
+          <t>公生而穎異資稟過人年既冠登陳英宗甲辰科中狀元上以公資質贊卑陋不欲與狀元公乃作五井蓮華賦以自祝蓋謂蓮花井中雖卑而可貴上覽之而悟遠置上第歷任各職</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>phu nhân mỉm cười đáp: Sáng sớm hôm nay có một ông khách đến chơi, nói là bạn thân của Cậu, nhân đi công cán qua đây, hiện có đem theo mấy chục tùy tùng, nhờ tôi sửa giúp cho một bữa cơm. Chẳng ngờ đến khi làm xong bụng lên, thì lại chỉ có một mình ông ấy ngồi ăn hết cả. Lúc ấy tôi ở trong phòng nhìn ra thấy mỗi tò com lớn ông chỉ và có hai miếng! ăn mau như thế gió cuốn mấy bay! chỉ trong một lát, ăn hết cả ba nồi 10 com và 5, 6 mâm cỡ.</t>
+          <t>Nói về Tràng Mạc-định-Chi, diện mạo tuy xấu nhưng rất thông minh, gặp lúc Hoàng-tử Chiêu-Quốc-Công mở rộng học đường để dạy sĩ tử, ông xin vào học, đến khi tuổi gần hai chục, thì đồ Tràng-nguyên vào khoa Giáp- Thìn đời Trần-Anh-Tông (1.304); tất cả Thái-học-sinh nội thư-gia được về đối sách, thì ông đồ đầu, chỉ vì nhà vua thấy ông tướng mạo thơ lỗ nên không muốn cho đồ Tràng. Vi thế ông mới soạn ra bài phu Ngọc-Tỉnh-Liên, để vì với mình, đại ý nói rằng: sen ở trong giếng, tuy rằng sinh ở chổ thấp nhưng nó vốn là quí vật. Nhà vua xem qua bài phu hiệu rõ thâm ý của ông, nên lại cắt lên dỡ đầu... Thi đỗ xong, ông bắt đầu xuất chính, lần lượt qua mấy chức vị,</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>我昨日有約惠然肯來今卻忘之必被吾兄見責後清因回家途經像洲郎詣公訪舊公屬家人整燕肥豬二隻又資盛二盞同坐款待清契盡豬款各一角公契盡豬一隻又款一盤又契清新餘各一角只需其半以與狹人相吃溝大驚曰古稱慕澤先生以食為各但又于十八十二之數若與兄同時適避三舍矣</t>
+          <t>往北使與北人限日至交關阻風雨失期為北人所拒公婉辭致請北人寫對句自開上板揭有曰到關邏陽陽開願過客過關</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chẳng biết là người hay quí? mà lại ăn khỏe lạ lùng như vậy. Ông Thanh nghe vọ kề xong tỏ vẻ hối hận nói rằng: Thôi thôi! chính là Ông bạn quê ở Tiên-Châu, trước kia tôi có hẹn Ông vào chơi, chẳng ngờ ngày nay quên bằng đi mất, thế nào anh ấy cũng trách là kẻ vô tình? Thế rồi cách ít lâu sau, Ông Thanh nhân lúc về quê đi qua Tiên-Châu có ghé vào thăm Ông Hò, Ông bảo gia nhân giết hai con heo luộc chín, và 4 mâm xoi để thết đài bạn!</t>
+          <t>rồi phượng mang sang sứ nhà Nguyễn. Trước khi đăng trình, đã hẹn đúng ngày sẽ tới cửa ải, vì mưa gió thành sai hẹn, bị người coi giữ cửa ải chặn lại, ông phải hết sức bày tỏ duyên có, viên ấy mới thuận, nhưng bắt buộc phải đối ngay một câu thi mới mở cửa cho vào. Yế đối ấy tự trên cửa ải ném xuống như sau:. Quá quan tri, quan quan bế, nguyên quá khách quá quan.</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>公大笑其後官歷左侍郎奉往北使時同縣安照社署人頗有口辨使之從行至燕京北人聞公善食因作一具十八層召公赴宴架梯而食公每吃了一層輒取鉢擲下至最後層見一人頭在焉</t>
+          <t>公立對云出對易對對難願光生光對北人服其敏開開賜進至北朝元人以卑小陋之一日宰相召八府與坐有薄帳綿黃雀在竹枝上公以為生雀都就摘之元人笑其鄙陋公遂裂之眾人驚怪公應曰我聞古有梅雀畫未開竹雀畫夫竹君子也雀小人也寫相續此是以小人加諸君子之士上恐小人道長君子道消故為聖朝除之耳眾服其能</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>về phần Ông Thanh chỉ ăn hết có 1 góc, còn Ông Hò thì ăn hết cả 3 mâm xôi và một con heo, rồi lại ăn sang một góc của Ông Thanh, chỉ còn để lại một nĩa cho người theo hầu, khiến cho Ông Thanh hết sức kinh ngạc nói rằng: Đời trước khen Mộ-Trạch Tiên-Sinh là người ăn khỏe, nhưng chỉ đến số 12 (cạnh) 18 (cơm) mà thôi, vì thử đồng thời với Bác thì còn kém Bác đến 3 dặm vậy, Ông Hò dắc ý cả cười. Rồi sau Ông Hò làm đến chức Hữu-thị-Lang, phung mạng sang sứ Bắc quốc, lúc ấy có người lái buôn ở xã An-Chiều an cung huyện, vốn là một người có tài khẩu thiệt, Ông cho đi theo. Khi tới Yên Kinh, Bắc triều vốn đã nghe tiếng Ông ăn khỏe nhất, nên có sửa một mâm cỡ, chồng chất lên 18 từng rồi triệu Ông vào dự yến!</t>
+          <t>Ông liên đối lại rằng: Xuất đối di, đối đối nan, thính Tiên-sinh tiên đối. Nghĩa về trên: Tới quan chật, cửa quan đồng, mới quá khách qua cửa khác. Nghĩa về dưới: Ra đối dễ, đối lại khó, xin Tiên-sinh đối trước cho. Viên coi giữ cửa ải thấy ông ứng khẩu đối ngay, rất phục là nhanh, bèn sai mở rộng cửa ải đón tiếp sứ bộ.. Sang qua cửa ải Nam-Quan, ông cùng sứ bộ tiếp tục lên đường, khi tới Bắc-kinh triều thần nhà Nguyễn thấy ông thấp bé có ý kinh thường. Một hôm Tề-Tướng cho mọi vào phủ, giữa lúc đương ngồi nói chuyện, ông thấy trên bức trường gấm có thêu một con chim trước sắc vàng, đậu trên cành trúc, trông hết như con chim thực, ông tiến lại gần gior tay toan bất, các quan nhà Nguyễn cả cười, chè là ngơ ngẩn. Ông bên xe nát con chim ấy ra, khiến cho mọi người kinh ngạc, hỏi có tại sao. Ông ung dung đáp: Tôi thấy cờ nhân chỉ về Mai-Tước, chứ chưa thấy về Trúc-Tước bao giờ. Có sao bức trưởng của quan Tề-Tướng ngày nay lại thêu cái hình Trúc-Tước. (Trúc-Tước, Mai-Tước). Ôi! Trúc là bản sắc của người quân-tử! Tước là hình dáng của kẻ tiêu-nhân. Ngày nay Tề-Tướng cho thêu như vậy, thì tiêu-nhân lại dẻ lên trên quân-tử? Tôi sợ đạo của tiêu nhân lớn, thì đạo quân-tử sẽ tiêu, nên tôi phải vi Thành-đế trù khứ đi ngay. Câu giải thích đó làm cho ai cũng khiếp phục về tài hùng biện hơn đời.</t>
         </is>
       </c>
     </row>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>傷人皆掩目不敎正視公大聲喚從者來曰書我生不知滋味今皇帝賜我食北人頭最為佳品汝將取醋來我吃了蓋這頭乃魚人頭與人無異世所罕見故他以此怵公今見其不懾頗有侵渡之語即挈取頭去尋托以他爭篤其兩目使人撓之自曼所而往三日復就這賣因問公何賣否公已默記其心郎答云乃前日賜晏賣也</t>
+          <t>及進朝適外國進殤元帝命公與高麗使賛之高麗使先就其詞曰韞隆蟲蟲伊母周公涼雨淒淒伯夷叔齊</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>khi ăn phải treo lên thang, ăn hết từng trên thì quảng bát đã xuống đất rồi mới ăn đến từng dưới. Chẳng ngờ khi ăn đến từng dưới cùng thấy có một cái đầu người. Ông bèn lấy dưa xuyên vào hai mắt rồi giao cao lên, làm cho những người chung quanh đều phải bịt mắt chó không giám nhìn. Ông bèn thét bảo quân lính theo hầu: Ta đây là kẻ Thư sinh chưa nếm những món ăn là bao giờ, ngày nay Hoàng - Đế cho ăn số người Bắc quốc!</t>
+          <t>Lúc ấy lại có người ở ngoại quốc đem quạt vào dâng, Nguyên-đế bèn sai ông cùng Sứ-thần Cao-Ly mỗi người phải làm ngay một bài tán. Sứ Cao-Ly làm xong trước, có những câu rằng: Uân long trùng trùng. Y-Doãn Chu-Công; Vũ tuyêt thê thê, Bá-Di Thức-Tề. Nghĩa là: Khí nóng bùng bùng, Y-Doãn Chu-Công; Mưa tuyêt đầm dia, Bá-Di Thức-Tề. Ý nói mùa hạ nóng nực, thì cái quạt đắc dụng như hai ông Y-Doãn Chu-Công. Đến mùa đông giá rét thì cái quạt bị chết là như hai ông Bá-Di Thức-Tề.</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>北人謂公莊前知遂敬之時國上連月不雨仍命諸國陪臣修文橋雨公料知天象未雨因奏曰臣小國乞後讓大國先之已而祈之皆不應皇帝郎命公對曰有從人學得武公遺法嚴乎</t>
+          <t>公未哀體制望其他筆管遂因而推演之曰流金爍石天地為爐汝於斯時兮伊周臣儒北風其涼雨雪載途汝癸斯時兮夷齊戮夫隱用之則行舍之則藏惟我共爾有是夫既成竝進天子眷懷伊司嘆賞不已封兩國狀元</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>hẳn là món ăn rất ngon. Vậy thì các chủ kip đem tương dẫm lại đây để cho ta chén nghe. Nguyên cái số ấy tức là số con nhân ngư (cả người) trong y như số người thực, mà đời ít khi được thấy, cho nên họ mới dùng nó để thử thách Ông, nay thấy Ông đã chẳng sợ lại còn nói xược như vậy.</t>
+          <t>Giữa lúc ấy thì ông chưa nghĩ xong, nhưng khi liếc sang đầu quân bút của sứ Cao-Ly, ông đã biết rõ những câu như thế, ông bèn nhân cái ý đó để suy diễn thêm một bài rằng: Phiên âm: Luru kim thược thạch, thiên địa vi lò! Nhĩ ư tư thi hề, Y-Chu cự nho. Bắc phong kỳ lương, vũ tuyệt tái đồ, nhĩ ư tư thi hề, Di Tề nga phu. Y: dụng chi tắc hành, xả chi tắc tàng, duy ngã dữ nhĩ hữu thị phu? Nghĩa là: Nấu vàng nung đá, trời đất như lò, thì người lúc ấy khác gi Y-Chu nói tiếng bắc cự nho. Gió lạnh buốt xương, mưa tuyệt đầy đường! thì người lúc ấy cũng như Di Tề nhìn dồi trên núi Thu-Dương. Ôi! Dùng thì ra giúp đời, bỏ thì tạm ẩn để chờ thời, chỉ ta với người có thể ôi. Viết xong bài trên ông tiến trình lên, Thiên-Tử nhà Nguyên coi xong chợ là hay, cảm bút khuyên vào câu có chữ Y và phê 4 chữ Lưỡng-Quốc Trạng-Nguyên. Thế là bài tán đề quạt của ông dẫu rằng thoát ý và làm xong sau, nhưng mà lại được Thiên-Tử nhà Nguyên thường thức hơn bài của Sư Cao-Ly đã làm xong trước vậy.</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>風喚雨可遣皇帝郎召之其人奏曰臣有一法須得吉日方可用乃潛觀櫪木根俗曰已見白父鷄頸草俗曰鷄鵠有黠自知兩期將至即請設壇場禱之已而果得兩皇需大稱賞封為兩國之師封公為兩國尚書公善辭命應對名聞兩朝皇帝欲晉之使教太子公難之不敬遠奏請造一新堂并備鞭模教具皇子出有過輒痛加筆箋矣</t>
+          <t>其在北國與北人遇于途公乘驢觸其馬北人誦之曰觸我騎馬東夷之人也西夷之人也公應之曰遇予乘驢南方之彊戰北方之彊歟</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Họ liền xách ngay cái số ấy đi, rồi vùn vào một cờ khác để bịt mắt Ông lại, cho người công đi an trí một nơi, sau một vài hôm chúng lại đưa về chỗ cũ, hỏi Ông có biết đây là nơi nào. Vì Ông đã đề tâm từ trước, nên giả nhồi ngay rằng: Chính đây là chỗ ăn yến hôm trước chứ còn nơi nào. Người Tàu tưởng Ông là bậc tiên-tri, nên mới tha cho lối trước. Trong thời gian ấy Bắc quốc đương bị hạn hàn luôn mấy tháng giới! Vua Tàu ra lệnh cho Sư-Thần các nước đều phải viết văn đảo vỡ.</t>
+          <t>Trong thời gian còn ở Bắc.kinh, một hôm, ông cởi lừa đi đạo phố, chẳng may con lừa của ông xó vào con ngựa của quan nhà Nguyễn. Vị quan ấy bên đọc mấy câu như sau:?? Xúc ngã ky mã, đồng di chi nhân dã? Tây di chi nhân dã? Nghĩa là: Xó vào ngựa ta? hỏi người ở Mán đồng đó hay người ở Mán tây đó? Ngài ứng khẩu đối:?? Át dư thừa lư, Nam phương chi cương du? Bắc phương chi cương du? Nghĩa là: Ngáng đầu lừa của ta, hỏi phương Nam mạnh du, hay phương Bắc mạnh du?</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>曰先學禮後文學太後酷愛其子奏請擇導官公以是免歸國後任至尚書春江侯陸少保佀郡公致仕耳</t>
+          <t>又常共北人對答北人出對曰杞已木梧否木知何以就為稽公對曰僧曾人佛弟子人何如以僧奉佛</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ông thấy điểm giới còn lâu mới mưa nên tàu rằng: Nước Thần bé nhất xin cho làm lễ đảo sau, để nhường nước lớn đảo trước.</t>
+          <t>Lại có một hôm ông cùng các vị thân sĩ nhà Nguyễn bàn luận văn chương, vì muốn thử tài, họ thay phiên nhau để ra câu đối, câu thứ I là: Kỷ dĩ mộc, Bồi bất mộc, như hà dĩ kỷ vi bồi? Câu này thuộc lối chấp chữ: như chữ kỷ thì hợp 2 chữ: dĩ và mộc. Chữ Bồi thì hợp 2 chữ: bất và mộc, có sao lại dùng gố kỹ làm chén rượu, và họ ám chỉ ông cũng lùn như người nước Kỷ, có sao lại được trọng dụng? Ông đối rằng:,, Tăng tăng nhân, Phật phát nhân, vân hồ dĩ tăng sự phật. Nghĩa là: chữ Tăng thì hợp chữ Tăng với chữ nhân, chữ phật thì hợp chữ phát (là chẳng phải) với chữ nhân, có ý bảo các chú người Mông-Cổ con cháu nhà phật. Nhưng phật chẳng phải là người, nhẽ đâu lại bắt Tăng (tức chúng tôi) thờ phật.</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>傳公卒後國王頒以嗣棺差人會葬今村內猶有遺塚在焉</t>
+          <t>安者安以來為家公對曰因與人他王成國北人批云後世子孫當有王者但單字享國不長</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Quả nhiên Sư Thần các nước đảo mãi cũng đều vô hiệu, bấy giờ vua Tàu mới triệu đến Ông. Ông tàu rằng: Hạ thần có viên tùy tùng vốn học được phép hô phong hoán vỡ của Không-Minh ngày xưa, nếu sai người ấy cầu đảo tất nhiên sẽ có công biểu, vua bèn cho đi triệu ngay, người ấy (tức anh lái buôn chè) tàu rằng: Thần có một phép nhưng cần phải chọn ngày tốt thì mới ứng nghiệm. Rồi anh lên đi các nơi để xem triệu chúng ra sao. Sau khi nhìn thấy gốc si đã đâm rễ trắng, cỏ gà cũng điểm lóm đốm, biết rằng sập mưa đến nơi, bấy giờ anh mới tàu xin lập đàn câu đảo, quả nhiên mưa xuống âm âm, vua Tàu khen ngợi phong làm Lưỡng quốc Quốc - Sư. Còn Ông thì được phong làm Lưỡng quốc Thượng-thư.</t>
+          <t>Câu thứ II là:. An khứ nữ, dĩ thi vi gia. Nghĩa là: chử An bồ chử nữ thay chử Thi là heo vào, thành chử gia là nhà. Ông đối lại:. Tự xuất nhân, nhập vương thành quốc. Nghĩa là: chử Tự bồ chử nhân ra, cho chử Vương là vua vào, thành chử quốc là nước. Họ chịu phục câu đối này là tài, nhưng lại phê vào rằng: Con cháu sau này tất nhiên có đời làm vua. Chi hiềm chử quốc viết đơn, thì giữ nước cũng chẳng được lâu dài, (chử quốc viết kép viết đơn như ở trên).</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>其後人自北歸國王命築室于本社寺及平置庵于其側號國師寺至今香火猶存焉</t>
+          <t>北人尚對曰日火雲煙白旦燒殘玉魄公對曰月弓星彈黃育射落金烏北人批云後世子孫必有慕人國</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Riêng Ông sở trường về từ mạnh ứng đối, vua Tàu muốn giữ lại để dạy các Hoàng - tử; ý Ông không muốn nhưng không giám trái lệnh, nên mới tàu xin cho đặt học đường riêng ra một chỗ, rồi sai sắm sửa các thứ roi vọt, hễ Hoàng-tử nào có lỗi Ông đánh rất đau và bảo cho biết, trước phải học lễ rồi sau mới học văn! Hoàng-hậu vốn yêu dấu con, không thể nhận được bên xin vua chọn thầy giáo khác, thành ra Ông được trở về nước nhà, làm đến Thượng - thư phong Xuân-Giang-Hầu và trước Thiếu-Bảo-Lữ-Quận-Công rồi mới Tri-sĩ hưởng thọ 72 tuổi. Theo như tục truyền thì lúc Ông mất Vua ta có ban cho một cỗ áo quan bằng đồng, và vua bên Tàu cũng sai quan sang đưa dặm, hiện nay mồ mà vẫn còn thấy ở trong thôn. Còn anh lái buồn theo Ông khi ở Tàu về Vua ta cũng sai dựng nhà ở bên cạnh ch a của làng ấy, và lấy danh là chùa Quốc-sur, ngày nay nhang khói vẫn còn.</t>
+          <t>Câu thứ III:,. Nhật hỏa vàn yên, bạch trù thiếu tân ngọc thô. Nghĩa là: mặt trời là lừa, đàm mây là khói, tảng sáng đốt tan thô ngọc. Ông đối lại:,. Nguyệt cung tinh dạn, hoàng hôn xạ lạc kim ô. Nghĩa là: vành trăng là cung, sao là dạn, bóng hoàng hôn bắn rụng ác vàng. Câu này họ lại phê rằng: Đời sau con cháu tất nhiên có người cướp nước.</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>在曰營接這跡內有一二事頗淡訛傳但得子公族人之言且參諸村邑高年所道來無異故畧記之以俟大德君子焉</t>
+          <t>北人尙對云魑魅魍魎四十四鬼蓋陋其卑小也公對曰髮鬢琵琶八大王北人北北云後世必為血食之神</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Xét sự tích này bên trong cũng có vài việc hầu như ngoa truyền, nhưng đó là những câu của người trong họ Ông sau này thuật lại. Và các bô lão ở vùng lân cận cũng đều kể lại như thế. Cho nên mới ghi lại đây để đợi các vị quan tử sau này chấp chính.</t>
+          <t>Câu thứ IV:. Ly My Vọng Lạng từ tiêu quỉ. Nghĩa là: 4 con quỉ nhỏ trên đều có chử quỉ một bên. Ông đối lại:. Cầm sắt Tỳ-bà bát đại vương. Nghĩa là: 4 cây đàn trên đều có 8 chử vương. Câu này họ phê rằng: Về sau sẽ được làm phúc thần.</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>范鎮杜注記海陽之嘉福藍橋社范鎮阪林社杜汪里開相鄰舊傳杜汪邑中有女精者往往興大祟作變幻百出祈禱願有驗焉</t>
+          <t>北人對云鳥呼枝頭談嘗論知為知爭知為不知是知蓋以默音譏南人也公以類蛙聲應之曰蛙鳴池上讀鄒書樂獨樂樂共飛樂樂亂樂</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Phạm-Trần ở xã Lam-Kiều thuộc huyện Gia-Phúc và Đỗ - Uông ở xã Đoàn - Lâm hai làng giáp với nhau. Tục truyền rằng: trong ấp Ông Uông có một con nữ yêu tình thời thường hiện hiện, tác yêu tác quái biến ảo khôn lương! dân làng yểm đảo mãi mà vẫn vô hiệu.</t>
+          <t>Câu thứ V:. Quách tại tường đầu dâm lỗ luận: Tri chi vi tri chi, bất tri vi bất tri, thị tri. Nghĩa là: Con chim quách đậu ở đầu tường, nó học đòi nói những câu sách Luận-ngữ: Biết thì bảo là biết, không biết bảo là không biết, ấy là biết. (để ngụ ý chê ông cũng như con chim học nói). Ông liền mượn ngay mấy câu trong sách Mạnh-Tử cũng có những tiếng đối lại rằng:. Oa cư trì để độc Trâu thư: Nhạc dữ thiểu lạc nhạc, nhạc dữ chúng lạc nhạc thực lạc. Nghĩa là: Con ếch ngồi đáy giếng đọc sách của ông Mạnh-Đức (Trâu thư): Vui với người ít cũng vui, vui với người nhiều lại càng vui thực. (lấy tiếng ộp oạp của ếch để đối với tiếng lích chích của quách, thành ra âm thanh đối với âm thanh).</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>注少時臨窗閱書夜間常見一手自窺前伸八汪知其為妖就質諸同縣老法師法師夜間常見一手自應節伸入汪知其箋效就質詣何舉才之師注師手果不肐縮大將曉窻下哀訴曰公當大貴我眉戲耳</t>
+          <t>北人吾對云洛水神邕單應兆天效五地效五也五十五效效威混三大道道合元始天尊一誠有感公對曰峻山靈鳳兩星神雄聲六雌聲十六聲徽九章大天生嘉靖皇帝萬壽節無疆其對答出只成章無少為者</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Về phần Ông Uông lúc còn niên thiếu, một đêm đường ngời đọc sách ở trong cửa sổ, bỗng thấy phía ngoài có một cánh tay thò vào. Ông đoán biết là tay con nữ yêu, sáng sớm hôm sau đến hỏi Ông pháp sư già cùng làng. Pháp sư ấy bảo: Từ nay về sau hễ thấy nó thò tay vào thì cậu lấy chỉ ngũ sắc buộc lại, tất nhien nó không biến được. Uông nghe pháp sư bảo thế với về sắm sửa đội đến canh khuya lại thấy con yêu thò cánh tay vào. Cậu liên lấy chỉ ngũ sắc buộc ngay vào song cửa sổ, tư nhien tay nó cưng dò, không sao rút ra được nữa, cho mãi đến lúc gần sáng.</t>
+          <t>Câu thứ VI:,,,,,,. Lạc thủy thần qui đơn ứng triệu, thiên số cửu, địa số cửu, cửu cửu bát thập nhất số, số số hỗn thành tam đại đạo, đạo hợp nguyên thủy thiên tôn nhất thành hữu cảm. Nghĩa là: Thần qui ở sông Lạc hiện ra điểm tốt, số trời là 9, số đất là 9, 9 lần 9 là 81 số, số số hỗn thành 3 đạo lớn, đạo hợp với đức Nguyên-thủy Thiên-tôn do một tấm lòng thành cảm ứng. Đối lại rằng:,,,,,,. Kỳ-Sơn minh phượng lưỡng trình tường, hùng thanh lục, thư thanh lục, lục lục tam thập lục thanh, thanh thanh hưởng triệt cửu trùng thiên, thiên sinh gia tĩnh Hoàng-đế vạn thọ vô cương. Nghĩa là: Chim phượng hót ở núi Kỳ-Sơn hiện hai điểm tốt, tiếng chim đực là 6, tiếng chim cái là 6, 6 lần 6 là 36 tiếng, tiếng tiếng vang suốt chín từng trời, trời sinh vua Gia-tĩnh muôn tuổi khôn cùng. Trải qua bao câu đối đáp, Thân Sĩ triều Nguyên biết rằng không thể áp đảo được ông,</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3093,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>何忍至此極也汪曰以我之果做狀元否曰狀元已有范生公當次之汪曰汝有甚灵物即共我觀我便敵汝俄聞嘔吐聲忽見一物似玉在紋手中精光奪目汪有取吝之師解其繫線自是天邑中不聞怪而泣嘆曰精通舟詞章一出人以賞陳吐王稱之在場屋間甚有聲譽鑲常不逮光靈員員意崇年號丙辰科會試時年共二十四歲同年同榜至庭試日汪見全題皆素慣今番首選醫我無驗時鎮在籠中彷彿見傍有兩人一稱韓琦一稱東方朔附耳</t>
+          <t>又北朝后妃薨臨簽命公讀祝就讀但見空紙紙上有遺一字公即哭而讀之其词曰天上一朶雲空中一點雲子閾苑一枝花廣寒一片月噫雲散雪消花殘月缺北人大談焉異嘆服其文</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Nó đứng bên ngoài khóc lóc van lon. Tôi thấy ông sắp trở nên đại qui, nên mới đưa bốn thế thôi, sao mà ông lại nhẫn tâm như vậy? Ông hỏi: vậy như tài của Ta đây thì có dỡ được Trang-Nguyen hay không? Nó đáp: Trang-nguyen thì đã về họ Phạm, còn ông chỉ dỡ thứ hai mà thôi!</t>
+          <t>rồi sau mấy bữa, nhân gặp tang lễ bà Hậu phi, họ bèn tâu với vua nhà Nguyên cử ông vào đọc văn tế. Khi vào quỳ trước linh-vị, nghe tiếng xướng xong, mở tờ chúc văn ra đọc, chỉ thấy có 4 chữ nhất là một. Ông biết họ chực thử mình, nhưng văn trình trong đọc ngay lên rằng: Thanh-thiên nhất đóa vân, hồng-lò nhất điểm tuyết; Thượng-uyển nhất chi hoa, Quảng-hàn nhất phiên nguyệt. Y! Vân tán tuyêt tiêu, hoa tàn nguyệt khuyet. Dịch nghĩa: Trời xanh 1 đám mây, Lò hồng 1 điểm tuyệt; Thượng-uyên một cảnh họa, Cung quảng một vùng nguyệt. Ơi! Mây tân tuyệt tiêu, hoa tân, giăng khuyết. (Bốn câu trên đều có 4 chữ nhất là một). Đọc xong bài văn tế trên, tất cả vua tôi nhà Nguyễn đều phục là bức thiên tài! (bài văn ấy vẫn còn ghi trong bắc-sử, thế mà về sau lại có người bảo: bài ấy là của Lý-Bạch, nhưng ta xét kỹ về lời và ý, thì thấy giống như văn thể của ông. Tuy thế chưa chắc đã phải, bởi vì bài thơ đề quạt dịch là của ông. Thế mà trong sách Thuyết-Linh lại chép là của Phương-hiệu-Nho, lấy đó suy ra, thì sử sách bên Tàu chép về việc ấy chắc gì đã dùng vậy).</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>讀之滔滔不竭鎮寫之不發聞靜謂琦曰須使任致病以減其力俄見杜汪抱腹申吟不能下筆迨鑲過一段泣病方愈故習燕雖多而日力不足既而臚唱鎮中獄元酒中榜眼顯喜語人曰吾今壓倒杜注矣</t>
+          <t>公在北朝北人大奇其才而察相貌無可責者乃直公出則潛往視之見便薺分方謂公有隱相所貴在此分還北人往我國認其墳塋稱公乃禀生之地但水不亭留故不富耳</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Lại hỏi: vậy mi có vật gì thiêng liêng hãy đưa đây ta coi thử, rồi ta sẽ cởi trói cho. Ông vừa hỏi xong thì thấy nó thở ra một vật gì ở giữa bàn tay trong như viên ngọc sáng chói cả mắt. Ông liền cảm lấy bỏ ngay vào mồm nuốt trúng, rồi mới cởi trói cho nó biến đi. Về sau không thấy tác quái gì nữa, mà ông thì cũng từ đấy về sau học một biết mươi, vẫn chương lại càng xuất sắc, ai cũng khen tài nhà ngọc phun châu, khi cùng tập ở các trường ông Trần vẫn không theo kịp. Thế rồi đến năm Quang-Bửu thời Mạc Phúc-Nguyên ( 1554-61) gặp khoa thi hội năm Bình-thin, hai ông cùng 34 tuổi, là bạn đồng niên đồng bằng, đến hôm cùng vào thi đình, ông Uông nhận thấy đầu bài nào mình cũng thuộc lòng hết thấy, tin chắc phen này sẽ nắm vững giải khơi - nguyên. Còn phần ông Trần lúc đương viết bài ở trong lều, bồng thấy thấp thoáng có hai bóng người đứng ở bên cạnh, một người tự xưng là Đông - phương - Sóc một người tự xưng là Hán-Kỳ (có bốn chép là Phú bất và Phạm-trọng-Am ) ghé vào bên tai đọc lên thao thao bất tuyệt, khiến ông Trần không sao chép kịp.</t>
+          <t>Nhắc lại trong khi ông ở bắc-triều thì người nhà Nguyễn thấy có kỳ tài, nhưng xét tướng mạo không thấy có gì đáng quí. Họ bèn đợi lúc ông đi sau xong trở vào, họ mới lên ra quan sát thấy những hòn phân, vuông như quan cơ, bấy giờ họ mới bảo nhau: đó là ẩn tướng rất quí. Nhưng rồi sau khi công việc xuất sứ hoàn hảo, ông trở về nước, họ còn phải thấy địa-lý theo sang để xem phong thủy đều ta, nhân tiện ông có dẫn họ xem lại phần mộ tò tiên, ngôi nào họ cũng lắc đầu bảo rằng không được, sau cùng dẫn đến ngôi mộ phụ thân, thì họ tấm tắc khen ngôi bảo rằng: đây mới chính là ngôi mộ phát tích. Nay ta xét lại hình thế, thì ngôi mộ ấy quả nhiên đẹp thực, đầu đến các thầy địa-lý tầm thường cũng biết là qui cách. (cục này chép kỹ ở sách địa-lý ông Hòa-Thúc). Hiểm rằng thủy không tu mấy, nên chỉ phát quí mà thôi, chứ không phát phú.</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>。汪深愬之。榮歸日驅繾綣而行。</t>
+          <t>公為官廉潔薄於自奉故其慶番後人于各覩員外郎孫各迪各遂各遠皆有執力共列顯貴其後吳平亦不父難莫遂子孫綏濟青河廣漢三世乂綏居宜陽蘇古齋社生莫太祖登庸篆織而有天下實狀元五世孫也</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Thấy vậy ông Sóc bảo ông Kỳ rằng: chúng ta phải làm thế nào cho Uông bị ốm để giảm sức văn thì mới thắng nói. Thế rồi chỉ trong chớp mắt ông Uông ốm bụng kêu đau, không sao cảm được bút viết, cho mãi đến khi ông Trần viết xong một đoạn, bấy giờ ông Uông mới khỏi, thành ra sách vở văn thuốc, nhưng lại không đủ thì giờ, cho nên sức văn hơi kém. Đến khi truyền lò (xương danh) ông Trần đỗ Trạng-nguyen, Ông Uông phải đứng thứ nhì tức là Bảng-Nhơn.</t>
+          <t>Xét thấy trong đời làm quan của ông rất trong sạch, về cách cư xử âm-thực cũng chỉ giữ mực thường thường, vua Trần Minh-Tông hiểu rõ tinh tinh của ông, nên có sai người đem 10 bó tiền, rinh lúc đêm khuya thanh vắng bỏ vào trong cửa, sáng sớm hôm sau, khi ông thức dậy không biết là tiền của ai, vội vàng vào triều tàu để vua biết. Vua phân rằng: Tiền không có chủ thì khanh cứ việc nhận lấy chứ có hề chi; đức tinh thanh liêm của ông đại đề là như thế đó. Cho nên về sau Văn-hiên tiên-sinh có làm bài thơ tứ tuyệt để ca ngợi rằng: Phiên âm Đệ nhất khôi nguyên tạo trí thân Cư quan bất cải cựu thanh bản Phiến minh hựu trọng Yên-dài dự Sử tiết phương tri quốc hữu nhân Dịch Chiếm giải khôi nguyên tự thiếu thời, Quan sang vẫn giữ nếp nghèo thời, Yên-kính đã trọng thơ để quạt, Cò Sứ nếu cao, nước có người. Nói về đức tánh thì trong lúc qui hiền, ông vẫn giữ được nếp thanh bần, nên mới dễ phước lại cho con cháu. Con trai như các ông Khẩn và Trực; cũng đều làm đến Viên-ngoại. Cháu là Dịch, Toại, Viễn,, đều có sức khỏe, gặp lúc nhà Hỏ cướp ngôi, nhân thấy cha ông ngày trước làm tới nhà Trần, nên vẫn ôm chí phục thù, đến lúc Minh-đế sai Trương-Phụ đem binh sang đánh nhà Hỏ, đại binh đóng ở Bắc ngạn sông Phú-lương, họ Hỏ bắt hết nam phụ lão ấu trong nước ra để cố thủ. Trương-Phụ không rõ hư thực ra sao, nên không dám vượt sang sông. Lúc ấy anh em ông Dịch nhận thấy có cơ báo thù, bèn từ Nam-sách lên lên Tam-đôi-Châu, hiệp lực với viên Thiềm-phán Đặng-Kinh đơn hàng Trương-Phụ đề báo-cáo tình-hình họ Hỏ. Vì thế quân Minh mới dám qua sông tiến đánh, luôn luôn thắng lợi. Trương-Phụ bèn dùng làm Hướng-đạo quan, rồi sau cùng với viên Hạ-hòa-mục là Võ-Thạch-Khanh, bắt được Hán-Thương và con là Nhưế ở núi Cao-Vọng. (việc còn ghi rõ trong Bình Binh-Giao Nam-Lục của Khâu-văn-Tráng biên soạn,). Vì có công lớn nên được nhà Minh phong cho quan trước, Toại làm Tham-chánh, Dịch làm Chi-huy-Sứ, Viễn làm Diệm-Thiết-Sứ, về sau vua Lê Thái-Tổ bình được Ngọ, các ông cũng không mắc nạn... Riêng về phần Toại sau khi mất rồi, con cháu di cư vào vùng Ma-Khê thuộc huyện Thanh-Hà,, đến đời thứ 3 lại đi về làng Cổ-Trai cổ xã thuộc huyện Nghi-Dương rồi sanh ra nguy Thái-Tổ là Mạc-đăng-Dong, tức là cháu 7 đời của Trạng-nguyên Mạc-định-Chi vậy.</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>與鬩並驅爭先。</t>
+          <t>樗眼鄭鐵長記</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ông Trần tỏ vẻ hoan hỉ nói rằng: phen này ta đã đề nói Đỗ-Uông. Làm cho ông Uông tức bực vô cùng. Đến hôm hai người cùng về vinh quí bài tờ, Uông vẫn đóng ngựa đi ngang với Trần, chứ không chịu nhường, khi về đến chợ Bồng - Khê thuộc xã Hoạch-Trạch, người ở bên cầu thường vẫn nghe tiếng hai ông, ngày nay thấy cùng vinh quí, nên họ xin một bài thơ vinh cầu để làm kỷ niệm.</t>
+          <t>ĐA NĂNG TẠI HẠ TRỊNH BẰNG-NHỜN</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>不背公讓至獲澤杜蓮溪中橋人曰素聞杜范二公大各今見同日榮歸請詠橋詩一首頒汪相異曰橋屋十有餘間限過七間成詩詩用一句一禽先成者讓先行不得筆道直顯如約立就詩國語八句馬上讀之人皆藥服泣曰這詩已平日素成非臨時所張得吾何讓焉</t>
+          <t>鄭鐵安矣東十里人也生而顴異少蓄與五六童子戲作大眾公以詡蝶為耳水蛭為鼻宛如真形適有府官經過而異之因出對云</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hai ông thấy dân sở tại xin thơ, lập tức giao hẹn với nhau rằng: chiếc cầu có hơn 10 gian, vậy khi qua được 7 gian thì phải làm xong bài thơ, mà thể thơ thì mỗi câu có một giống cảm, nếu ai xong trước thì sẽ đi trước, còn xong sau thì không được phép tranh cạnh. Hai ông đặt điều kiện xong rồi cùng tiến bước, chẳng ngờ ông Trần ngồi trên lưng ngựa đọc luôn ngay được 8 câu, khiến cho ai cũng kinh phục, riêng có ông Uông thì lại bảo rằng: Thơ ấy làm sẵn từ lúc ngày thường, chứ lúc làm thời thì làm sao nỗi, tôi chẳng chiều nhường. Nói xong ông lại cứ đi ngang hàng, khi về đến xã Minh-Luân, trong xã có người vừa làm được ngôi nhà mới, đón đường thưa rằng: chúng tôi mới dùng xong nhà, may gặp được hai quý vị qua đây, giảm xin hai vị ban cho mấy câu để tặng về đẹp.</t>
+          <t>TRỊNH THIẾT-TRƯỜNG người làng Đông-Lý thuộc huyện An-Định về người coi rất dĩnh ngọ, lúc còn thơ ấu chơi dưa với trẻ, cậu biết nặn con voi đất, rồi lấy bướm bướm làm tai, lấy dìa làm voi, hoạt động như con voi thực. Lúc ấy có ông quan phủ đi qua cũng lấy làm kỳ, nhân tiện có ra cho cậu một về đối rằng: Ngũ lục đồng vò như nhi xảo?</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>又齊道而行至明倫社有伊社人屋字是新富途請曰鄙人再構新家幸逢兩貴台經過乞惠之佳句燕歌屋生輝鎮應曰年年增富貴日日壽榮花古人有此句今日賀新家洹吟沱曰賛羙之辭此等句盡之矣</t>
+          <t>童子五人六無知汝巧公曰敢問公是何官府官曰我是當今太守也</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ông Trần ứng khẩu đọc luôn: Năm năm tặng phu quý ngày ngày hưởng vinh hoa người xưa có câu ấy nay mừng mới làm nhà, ông Trần vừa mới ngâm xong, ông Uông nói chận ngay rằng: đó là những chữ tân tung, chỉ dùng nửa câu cũng đủ can chi mà phải làm nhiều, rồi ông cũng vẫn không phục, Nghè ông Trần ngâm xong bài thơ trên đây, ông Uông mới đặt này mình nói rằng: quả thực xuất khẩu thành chương, nếu không có quỉ thần trợ lực thì làm sao nổi, từ đấy chịu nhường để cho ông Trần đi trước chó không đi ngang hàng nữa. Nhưng rồi về sau ông Uông lên đến Lam-Kiều xem ngôi mộ tò của nhà ông Trần, thấy có hai cái gò đất ở sát hai bên, tục gọi là đống thần ẩn ẩn thần đồng phụ nhi, ông bên chi vào đống đất bảo rằng, trước đây y thằng nói ta mấy phen là nhờ cái đống đất này. Nói xong ông lấy gót chân nện vào hai đống đất ấy thế mà không biết tại sao cũng từ hôm ấy ông Trần bị chứng điếc tai, thuốc thang chạy chữa vẫn không công hiệu, về sau cò người dem viêc ông Uông dập vào gò đất thân đồng mách với ông Trần, ông bèn tố cáo lên vua. Vua bắt ông Uông phải làm lễ tạ long thần, bấy giờ ông Trần mới khỏi, rồi sau Triệu dinh có mở khoa thì Đông-Các, đầu đề tho là (Văn-Võ, Tinh-Dụng ), dùng thể ngữ ngôn, hạn 15 văn, trong thơ Ông Trần có hai câu rằng:.</t>
+          <t>Cậu liền hỏi lại: Vậy Ngài là quan chức gì? Quan đáp: ta đây là dường kim Thái-thủ ăn lương 2000 thạch đó;</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>豈復以加而頒矣口輒成自非神吟鬼助轟然若是自是始讓顱先行後潛至監來杜著鎮祖墓見有二土堆俗曰兩袖童附耳</t>
+          <t>公郎對云太守二千石莫若公府官曰欠一字省請賞府官曰汝對不發至何賞之有公曰太守二千石莫若公貪府官命賜綺錢公即改對曰莫大公若廉府官大奇之因喚公母至曰此子俊才當勉以學業必中魁元</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Xưng Cao phong tự khỏi.</t>
+          <t>nghe xong Cậu đối ngay rằng:. Nhị thiên thạch mạc nhược công: Quan hỏi sao còn thiếu một chữ cuối? Cậu thưa rằng xin quan thường tiên rồi con sẽ có đủ. Quan bảo my đối không chính còn thường nói gì. Cậu bèn thêm ngay chữ tham tức là mạc nhược công tham, thành ra câu đối như sau: Năm sáu bê con chi có mây khéo, hai ngàn thùng thóc quả thực ông tham. Quan phủ nghe xong bên thường cho một quan tiên thi cậu lập tức dời ngay chữ tham ra chữ liêm, Quan phủ càng lấy làm la! sai người đi gọi mẹ cậu đến bảo: Con bà là một đứa bé tuần tù thông minh! Bà nên có gắng cho cháu đi học sau này thế nào nó cũng chiếm bằng khôi nguyên đó.</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3212,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>泣致指之曰從來勝我數番以有那神童附耳</t>
+          <t>母依教遂勤以刻意讀書父長博學多能以文章名天下</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Diệt Hạng diuh năng giang, nghĩa là khen Cao-Tô giấy tư ấp phong, Diệp Hạng quân sức hay cử đỉnh.</t>
+          <t>Bà mẹ thấy Quan bảo thế nên cũng tìm thấy cho cậu học hành, đến khi lớn lên học rộng lại nhiều tài năng, văn chương lừng lẫy khắp cả thiên hạ!</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>之功即用腳跟擊手土堆自是顫從耳</t>
+          <t>太寶篤志崇子虞科中進士使人來迎母赴京母不肯曰我從來望汝帶得魁元二字來明令都在人下任汝自為之我決不往</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kỷ này Ông Trần lại được đứng hàng nhất, mà Ông Uông vẫn phải thứ hai. Nhắc lại lúc chưa đỗ đạt, có hôm hai Ông cùng ngồi uống rượu, khi đã giờ say, thách nhau làm bài. Từ-Tán, Ông Uông đọc trước: Hữu huynh dụng huynh, vô huynh dụng hòa. dụng tắc hàm nghi thì vô bất khả: Có huynh thì uống rượu huynh, không huynh thì uống rượu hòa, uống đều say xưa gặp chẳng hay chớ.</t>
+          <t>rồi đến niên hiệu Đại-Bảo (1440-42 Lê-Thái-tông) khoa thi nhâm tuất ông dỡ Đồng Tấn-sĩ, sai người về đón thân mẫu ra kinh thành, bà không chịu đi, bảo rằng trước đây ta vẫn mong rằng nó sẽ đoạt lấy hai chữ Khôi-nguyên đem về. Chờ còn ngày nay lại phải ở dưới người khác, thì mặc y nó, ta đây còn ra làm chi?</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>病廢商治弗效有人以汪轡車土堆之事語鎮者鎮即訢于朝署朝論汪謝鎮祖墓鎮病尋愈</t>
+          <t>其後與狀元青威且溪人同往北使公郎辭歸固學太和橘仁戊辰科再試遂中榜眼</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ông Trần lại đọc tiếp rằng:,, Từ hoang tắc âm, từ hòa tắc tuyệt, hữu vi thử ngôn thiên địa nhất nguyệt. Rượu vàng thì uống, rượu hòa thì thôi, vì chẳng như lời, có đất trời soi, xem hai bài tán trên người ta nhận thấy hai Ông lập chí vẫn khác nhau xa. Quả nhiên rồi sau họ Mạc mất rồi. Bản Triệu trung hung thì Ông Uông ra làm quan trước được thăng đến chức Hộ-Bộ Thượng-Thư và phong sắc phục Thần, còn Ông Trần thì không chịu ra cho nên chỉ làm đến chức Thừa-Chính-Sư mà thôi.</t>
+          <t>Ông thấy mẹ già nói nhẫn như vậy lập tức từ giã kinh thành trở về học thêm, thế rồi đến khoa mẫu thin (1448) niên-hiệu Thái-Hòa, ông vào thi lại được trúng Bảng-Nhữn,</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>其後試東閣以文武並用詩題用五言三江為韻取十五韻鐵復中第一泊第二始興徵時與江對飲酒至半酣相戲為酒賛酒先唱曰有潰用潰無潰用火所用咸宜無施不可頤續吟曰酒潰則歡火潰則絕有遠此言天地日月識者以是言其立志之珠</t>
+          <t>其後與狀元青威且溪人同往北使適天朝有會試科命諸國陪臣與中國舉人一體應試公與阮直入試文漸至半篇乃私與阮直語曰今審舊得先篤時惟我與兄耳觀我文辭有起鳳騰蛟之勢未易與爭第思本朝間兄是狀元我是榜眼今以壓倒得兄則我國王必有選擇不精之吾兄意料如何</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Phạm-Trần ở xã Lam-Kiều thuộc huyện Gia-Phúc và Đỗ - Uông ở xã Đoàn - Lâm hai làng giáp với nhau. Tục truyền rằng: trong ấp Ông Uông có một con nữ yêu tình thời thường hiện hiện, tác yêu tác quái biến ảo khôn lương! dân làng yểm đảo mãi mà vẫn vô hiệu.</t>
+          <t>rồi sau cùng với Trạng-Nguyên Nguyễn-Trực (người ở Bối-Khê thuộc huyện Thanh-Oai) đỗ trạng năm nhâm-tuất, (1442) vang mệnh sang sứ Bắc-quốc, gặp lúc bên ấy mở khoa thi Hội, có lệnh cho các Sư thần cũng được vào thi với các Cử-nhan, Trung-quốc, hai ông cũng vào dự thi. Trong khi làm được nửa bài, ông bèn nói nhỏ với Nguyễn-công rằng: Cử chỗ tôi biết, phen này đoạt được giải nhất thì chỉ có tôi và quan bác đó thôi, nhưng văn từ của tôi có về rồng bay phương mùa, khó lòng có ai địch nổi. Tôi tự nghĩ rằng: khi ở nước nhà bác là Tràng-Nguyên Tôi đây chỉ là Băng - Nhơn, vì bẳng ngày nay tôi lại ở trên quan Bắc, thì chẳng hóa ra Quốc-Vương tuyển lựa không tinh! vậy Bác định liệu thế nào xin cho đệ biết?</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>其後莫七我朝中興汪首出仕至戶部尚書封福神鎮辭歸不仕仕終承政使司</t>
+          <t>阮直曰仕公規之既有遜讓之誠乞減其力俾我復欲元公復次檮眼可也</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Về phần Ông Uông lúc còn niên thiếu, một đêm đường ngời đọc sách ở trong cửa sổ, bỗng thấy phía ngoài có một cánh tay thò vào. Ông đoán biết là tay con nữ yêu, sáng sớm hôm sau đến hỏi Ông pháp sư già cùng làng. Pháp sư ấy bảo: Từ nay về sau hễ thấy nó thò tay vào thì cậu lấy chỉ ngũ sắc buộc lại, tất nhien nó không biến được. Uông nghe pháp sư bảo thế với về sắm sửa đội đến canh khuya lại thấy con yêu thò cánh tay vào. Cậu liên lấy chỉ ngũ sắc buộc ngay vào song cửa sổ, tư nhien tay nó cưng dò, không sao rút ra được nữa, cho mãi đến lúc gần sáng.</t>
+          <t>Nguyễn công đáp: Việc ấy tùy anh định đoạt. Vi thì anh có thành tâm nhượng lại, thì anh nên giảm bớt sức văn, để cho Ta vẫn giữ được Tràng-Nguyên, còn Anh vẫn giữ Băng-Nhơn là được.</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>探花廓佳記未生時有接近人以慣偷盜為業一日就公邑內行盜會人未定時潛八廟祠後假卧不覺薰睡至鷄鳴方醒披衣徵起忽聞前回喧鬧有人自廟外而入在廟內有人迎問曰今番何事遲歸聞有聲曰答適朝士帝與諸曹會談夜命一探花即降伊社有員捧薄奏曰長按伊家福德薄恐不稱此帝命取薄觀之良久判曰雖然知此但業已許之不必換改如他德果薄來時更有定奪焉</t>
+          <t>鄭公首肯既而行文有南之舟北之馬之句都塗馬字改寫予外馬有四點只見三點盡有司衡文鄭公宣猷充院道宣場眼但見鄭公寫自一字以北為為三足是蹤焉也似有輕中國之意即點一次乃許阮君為兩國狀元鄭公為兩國榜眼並賜榮歸本國使回日頒賜錦袍金笏兩袖廝馬儀用榮觀命防直前道簽程鄭公競自馬字其所頒廝馬仍簽一尺任使上轄簽程否則責留中國</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CHƯ TÀO HỘI NGHI, PHÙ-KHÊ THIÊN GIÁNG THÁM-HOA NAM TÀO HỘI NGHI, CHO MỘT THÁM-HOA XƯỞNG LÀNG PHÙ-KHÊ QUÁCH-CHÚ. Người làng Phù-Khê thuộc huyện Đông-Ngan. Nói về lúc Ông chưa sinh ra đời, thì ở lân cận có một người chuyên nghề ăn trộm, bỗng có một lần mò sang bên làng Ông định kiếm một mẻ. Nhưng vì lúc ấy nhà nào cũng còn thức, nên anh lên vào nằm ở trong miếu, để đợi, chẳng ngòi lại ngủ thiếp đi. Đến lúc gà gáy anh mới sực tỉnh xốc áo toan di, chợt nghe ở trước mặt có tiếng xôn xao.</t>
+          <t>Trịnh công thấy Trạng đã vui lòng nhận lời, ông bèn trở lại chỗ ngồi đem quyền ra viết, khi viết đến câu: Nam chi chu bắc chi mã, nghĩa là phương nam giới nghề bơi thuyền phương bắc giới nghề côi ngựa, ông bèn xóa nhoe chữ mã rồi viết chữ khác một bên, chữ ấy lại chỉ chấm có 3 nét. Đến khi chấm bài Quan trưởng xét thấy văn của Trịnh công đáng dỡ Trạng-Nguyên còn văn của Nguyễn công thì đáng Băng-Nhơn, nhưng vì chữ mã trong bài Trịnh công thiếu mất một nét chấm tức là ngựa có 3 chân, khác chi ngựa què, có ý coi thường Bắc - quốc nên bị truất xuống một bực, rồi cho Nguyễn công được làm Lưỡng quốc Tràng-Nguyên Trịnh công thì làm Lưỡng quốc Băng-Nhơn! đều ban áo mũ vinh quí. Thế rồi đến hôm ra về, Vua Tàu lại còn ban thêm bào gấm hốt vàng và ngựa thiên lý, để cho tăng phần vinh diệu, và lại xuống lệnh cho Nguyễn công phải đăng trình trước, còn phần Trịnh công vì có chữ mã 3 châu, nên con ngựa ban cũng bị treo lên 1 cảng, buộc phải lên yên cởi về, nếu không cởi được thì phải ở lại thượng quốc.</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>以此故遂歸耳時人在廟後竊聞具得其詳當夜不以行為意因徧往邑中探聽何宋生子見公生於是夜災早即公家具導前事一通預以為賀生而頴異人稱袖童及長以文舉子各正和年號、</t>
+          <t>公即生下一計急命行人造一片木狀如馬足毒加以鐵索穿一下用異條經之擇起蹶足仍痛加鞭打這馬三足奔馳一足與之相依賴以不墜</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Và thấy có người từ ở phía ngoài đi vào trong miếu, bên trong có người ra đón hỏi rằng: Phiên này sao về trẻ thế, đáp: Vừa rời lên châu Thượng-Đế, hội nghị với các Nam - Tào, định rằng trong đêm hôm nay sẽ cho một vị Thám - Hoa giáng sinh ngay ở xã này.</t>
+          <t>Tiếp được mệnh trên và thấy cơ sự như vậy, Trịnh công bèn nghĩ ngay một kế, sai người theo hầu chế tạo ngay một cái chân ngựa gỗ, ruồn dây thép vào rồi buộc chằng lên chỗ chân bị treo bằng sợi dây đen, đợi khi ông ngồi lên yên đang hoàng, rồi mới dùng roi vứt mạnh một cái, tức thì ngựa chạy như bay! Vì có chân nọ giữa vào chân kia nên không bị ngã.</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>癸亥文科中進士第一甲三名公在朝適內閣談政事餘昭祖康王問侍臣曰韓信遺燕書曰有曰白鹿抱泉事跡何在卿等能知之乎</t>
+          <t>繞過一里許、天朝志務其有應命又機思客即命解其索定乃與阮公依次而行</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Rồi lại thấy một viên quan tay nàng quyền sở tàu rằng Hạ: thần xét thấy phúc đức nhà ấy mông lẫm sợ không xưng chút nào, giám xin Hoàng-Đế định lại. Hoàng-Đế nghe tàu bên cầm cuốn sở coi qua một lát rồi mới phân rằng: đầu thế nhưng mà đã cho rồi, nhẽ nào lại còn canh cãi. Vì thử nhà ấy quả nhiên phúc bạc, rồi sẽ định đoạt về sau v.v. Vì thế cho nên hôm nay tôi về hỏi trẻ một chút. Lúc ấy anh kẻ trộm ta hãy còn nụ ở trong miếu, nghe lồm được bấy nhiêu câu. Anh bên bỏ ngay ý định ăn trộm, rồi vào trong ấp để thám thính xem trong đêm ấy nhà nào sinh đẳng con trai. Khi thấy chỉ có nhà Ông, thì sáng hôm sau nữa anh đến tận nhà kẻ lại câu truyện như thế.</t>
+          <t>Rồi sau cứ thế đi được đến hơn một dặm, thiên triều thấy vậy khen ông có tài làm cơ ứng biến! lập tức hạ lệnh cho cởi chiếc chân treo, để cùng đi với Trạng-Nguyên một thề.</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>群臣皆莫能對公跪對曰跡詳見漢書王郎命索公家書來觀之稱其簿學時公方以事被遣</t>
+          <t>歸國後防公仕至尚書鄭公亦仕至尚書封濟國禽渾北朝題載南文獻之邦緯莫公疑之之後二公其次也為公克寬亦踵其後壘</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Còn về phần Ông ngay lúc mới sinh trong đã rình ngộ rồi sau nói tiếng Thần-đồng! Đến khi lớn lên vẫn học lại thêm lừng lẫy!</t>
+          <t>Rồi khi về nước hai ông làm đến chức Thượng-thư rồi mới chỉ sĩ, Trịnh công được phong là Nghi-Quốc-Công tiếng tăm lừng lẫy cả bên Bắc-Quốc! làm thêm rang về vấn hiến nước nhà! như vậy thì sau Mạc-Đinh-Chi ta thấy chỉ có hai ông, mà người kế tiếp được hai ông thì có Phùng Khắc-Khoan tức là Trạng Phùng vậy.</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>未幾除清花聲同仕至寺癖以風疾不視朝始信從日祠神對語之聽</t>
+          <t>黃田武瓊記</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Vào khoảng niên-hiệu Chính-Hòa (1680 - 1705) khoa thi năm Quí-Hợi, thì đồ Tấn-sĩ đệ Nhất giáp đệ Tam danh. Đến khi làm quan tại triều, nhân lúc nhân đàm ở trong Nội-các Chiêu-tổ Khang-Vương (Trinh-Cần) hỏi các quan hầu về việc ngày trước Hàn - Tín gởi thơ cho Yên-Vương trong có câu rằng: Bạch lộc bảo tuyên, thì sự tích ấy ra sao. Quân thần không ai đáp được, chỉ có một mình Ông đặt gởi tàu rằng: Diện tích ấy biên rỡ trong Hán-thư. Vương sai về lấy gia thư của Ông vào xem quả nhien có thực, Vương khen là người học rộng nhớ nhiều. Giữa lúc ấy Ông đương mắc phải việc gì nên bị khiên trách, nhưng rồi chỉ sau ít lâu thì được bổ chức Đốc-đông tại tỉnh Thanh - Hóa, tức là ưu thưởng cho Ông về điểm bác học. Rồi sau Ông làm đến chức Thị-lang, vì có bình phong nên không vào triều chính, bấy giờ mới rỡ câu chuyện trong miếu ngày trước quả nhien có ứng nghiệm vậy.</t>
+          <t>DANH NHO VÕ - QUỲNH.</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>參議武登顯記 多者至八九名少者不下四五十名連名覆中率以為常而午年科保提調 官其左夫阮澧性頗廉直以慕澤從來多中必有私巧者在乞為海陽提 調以察之朝延協議考至第四場公命攝地為安合士人坐在穴中籠 蓋其上防守其甚嚴迨同考院考訖送來公無嚴飾覆考官詳看文勢 精純全篇無瑕者方得挑取而覆考擇得十卷公親自評之汰去四卷只 取六卷既而呼各優頂一名皆來澤社武登顯首科纔十八歲第二名某 澤社人第四建亦慕澤社人其三名乃永賴古庵唐安王司青林樂實人也</t>
+          <t>武瓊唐安慕澤人也洪德縣聖宗戊戌科由三黃甲公博學好古為世導師在長於模迹嘗業曰大官都總裁有大越通鹽通考迹自洪厽氏至十二侯君以前為外紀自丁天皇至朝繙太祖大受初年為本紀异譯錄歷代紀年九十二卷行于世</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Mỗi khoa liên đăng, Mộ-Trạch đỗ đạt nhiều, có khoa đến 8, 9 người, ít nhất cũng 4, 5 người, chẳng khoa nào không có người đỗ, đó là việc thường. Đến khoa Bính-Ngọ, có quan Tả-phủ là Nguyễn-văn-Lễ, tính tình thanh liêm, thẳng thắn, thấy Mộ-Trạch khoa nào cũng đỗ nhiều, nghi là có mánh khoé, xin làm Đề-điệu Hải-Dương để tra xét. Triều đình chuẩn y. Đến kỳ thứ tư, ông sai đào lỗ cho sĩ tử ngồi, trên có lồng che, phòng thủ rất nghiêm. Khi các quan khảo hạch xong, ông lại cho phúc khảo, xem bài nào văn hay, không tì vết mới được chọn. Chọn được 10 bài, ông đích thân xem lại, bỏ 4 bài, chỉ lấy 6 bài. Rồi gọi những người đứng đầu mỗi bài đến. Võ-Đăng-Hiển ở Mộ-Trạch đỗ thủ khoa, mới 18 tuổi. Người thứ nhì và thứ tư cũng ở Mộ-Trạch. Người thứ ba, thứ năm, thứ sáu là người ở Cờ-Am, phủ Vĩnh-Lại, làng Ngọc-Cục, huyện Đường-An, xã Lạc-Thực, huyện Thanh-Lâm.</t>
+          <t>Ông vốn là người Mộ-Trạch thi đỗ Hoàng-Giáp khoa Mậu-tuất thời Lê Hồng-Đức (1478), là người học rộng có tánh hiểu cờ lại sở trường về soạn thuật, lúc làm quan thường được kiêm cả chức Sư-quán-Đô-Tông-tái, đã soạn ra các bộ Đại-Việt Thông-Giám, và Thông-Khảo, thuật lại từ đời Hồng-Bàng xuống đến đời Thập Nhị Sứ-quân, từ đây trở về trước gọi là Ngoại-kỷ, còn từ Đinh-tiên-Hoàng xuống đến Bồn Triều Lê Thái-Tổ đại định năm đầu, gọi là Bồn-kỷ, và lại biên kỷ những niên kỷ của từng Triều đại, hợp thành 26 quyển truyền bá cho đời.</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>一科續取六各而纂澤居其半同院取卷觀之見三卷文理各殊不相蹈襲深嘉嘆賞貞始細信慕澤為世尚儒流文物之地文衡公器初非本私</t>
+          <t>又嘗接蘋南摭卦集仕至兵部尚書時有賊至遇害其壻狀元黎鶴卿有祭文曰</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Khoa ấy lấy 6 người, Mộ-Trạch chiếm một nửa. Các quan cùng sở xem các bài văn, thấy 3 bài văn lý khác nhau, không bài nào giống bài nào, rất khen ngợi. Từ đó mới tin Mộ-Trạch là nơi danh nho, văn chương có quy mô chung, không phải do tư lợi. Sau này Võ-Đăng-Hiển lại đỗ cao ở khoa Hoành-từ, thi hội đỗ cao sĩ, nhưng chỉ đỗ 3 trường, cho là chưa thỏa chí.</t>
+          <t>Ngoài ra ông lại cùng với Trần-thế-Pháp soạn tập Lãnh-Nam-Chích Quái rồi sau làm đến Binh-bộ Thượng-thư, chẳng may gặp thời loạn lạc nên ông bị chết, con rể là Trạng-Nguyễn Lê-Đình có văn tế rằng;</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>其後武盞顒宏詞科中優一會試賦優士分但中三場嘗以未遊青雲為限 官至北京處參議以親老辭官歸養設場教授及其門生擢大科儒者者 稱為尊師至今猶歆為裳</t>
+          <t>羅先生道大矣學統而貫擬像風道骨之姿為君子善人之冠躬行而口不言教稱而人無間行惠之和而合犯之時得參之曾而非由之噫意井顔之德行粹然知玉之無瑕游真文章渾然大櫟之未散光風霽月兮滿胸懷攬影翻江兮何影靜</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sau này Võ-Đăng-Hiển lại đỗ cao ở khoa Hoành-từ, thi hội đỗ cao sĩ, nhưng chỉ đỗ 3 trường, cho là chưa thỏa chí. Ông làm quan đến Bắc-kinh Tham-nghị, vì cha mẹ già xin về nghỉ, mở trường dạy học, học trò đỗ đại khoa rất nhiều. Người đời bấy giờ gọi ông là Tôn-sư, đến nay vẫn còn kính trọng.</t>
+          <t>Nhớ Tiên - sinh xưa: Đạo đã cao siêu, học càng thông suốt, đứng đầu quân tử thiên nhân, định dạc tiên phong đạo cốt! làm nhiều nói ít, hiểu hành khôn chê, ôn hòa giống ông Huệ xưa, Thời Trung theo thánh Khổng trước, như Tăng-Sâm lỗ đọn mà chẳng ương gần như thê Trọng-Do. Đức hạnh giống thầy Nhiệm thầy Nhan, ngọc lành không vết, văn chương như Tử-Du Tử-Hạ chất ngọc chưa tan, gió mát giảng thanh hề đầy túi, vượt bề cội sống hề mệnh mang!</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>節義樑鼎景詢記附光貞陳朝樁景詞其祖汝猷淳祿老疎人也</t>
+          <t>洪德間策舉追士時則先生峻危擢科馳名壹諫</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TIẾT NGHĨA Lê-Cảnh-Tuân.— Triệu nhà Trần có Lê-Cảnh-Tuân, ông nội tên là Nhữ-Du người huyện Thuần-Phước xã Lão-Lạt; khi làm Tri-Phủ Lạng-Giang kết duyên với con gái họ Vũ của làng Mộ-Trạch thuộc huyện Đường-An, nhân thế, mới lập gia-cư ngay ở làng vợ, tức là Thê hương.</t>
+          <t>Khoa Tấn-sĩ năm Hồng-đức đã chiếm Khói-nguyen danh vang trong đại Ngự-Sử.</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>為諒江知府娶唐安慕澤武氏之女因以妻鄕居焉</t>
+          <t>景綬纂宗詔初求遺逸時則先生首應義旗張聲史館</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Đến thời ông Tuân, khi đã sung chức Đại-Học-Sĩ, vì lúc còn nhỏ có quen với Bùi-Bá-Kỳ người xã Phù-Nội thuộc huyện Thanh-Miện, gặp lúc cuối đời nhà Trần bị Hồ-Quý-Ly cướp ngôi, Bá-Kỳ sang bên Yên-Kinh xin quân về đánh họ Hổ. Nhà Minh bên sai Truong-Phu và Mộc-Thanh chia đường kéo sang, Bá-Kỳ nhận chức Tiên-phong để hướng đạo.</t>
+          <t>Chiếu cầu hiện năm Cảnh-Thống kéo cờ khởi nghĩa công rạng trong viện tu-thư.</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>詢覓太學生少與青沔縣扶助社內裴伯耆相善陳末胡墓位伯者如燕京乞師伐胡明遣張翰沐晟等分道而來伯耆為先鋒向道拾逆胡父子送同明人拜伯耆為參護諭郎上萬言書于伯耆其畧曰若能立陳為上策僕願為佐龍中藥物任足下所用為陳辭官為中策僕願執籩籩豆奔走任足下所使若貪其禄位斯為下矣</t>
+          <t>窮通隨所遇而安著述異乎人之模</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sau khi bắt sống được cha con họ Hồ đem về bên Bắc quốc, nhà Minh bên cho Bá-Kỳ giữ chức Tham-Nghi, lúc ấy ông Tuân có gửi cho Bá-Kỳ một bức Vạn ngôn thư (bức thư có hơn một vạn chữ) đại lược như sau: Nếu ông có thể lập lại dòng dõi nhà Trần? Đó là thượng sách, thì tôi xin làm các vị thuốc ở trong tử để ông sử dụng! Hai là: Nếu ông nghĩ đến nhà Trần, mà giả chức vị cho nhà Minh, đó là trung sách, thì tôi xin cầm trở đầu (dở thờ) chạy theo, để tùy ý ông sai khiến! Ba là: Nếu ông còn tham tước lộc nhà Minh, đó là hạ sách, thì tôi sẽ đi câu cá hoặc đi cày ruộng mà thôi! Bá-Kỳ chưa kịp dùng.</t>
+          <t>Mới biết cùng Thông đầu phải theo thời, trước thuật không ai sánh kịp.</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3484,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>則僕樂鈞耕間而已伯耆不聽父伯耆犯明法明人籍其家得其書目詢變姓各遊匿後明人於我國立學校諭往觀之明人見其才學以為教授饒而知萬言書日乃誨師依郡補師去其三子太顚少顚叔顚皆願從行送至開門詭語之曰一當從二次且囘已奉舉以報君父之答眾子慟哭拜別詢其太顯至北京明人訝之曰爾教伯耆立陳後陰國不軌何也</t>
+          <t>通考紀元崔備史得經史之規模耕籍侍學諸書得史中經之體</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cách ít lâu Bá-Kỳ phạm pháp bị quan nhà Minh tịch biên gia sản, bắt được bức thư ấy, nhưng ông đã thay đổi họ tên lánh đi nơi khác, về sau nhà Minh đặt xong nên thống trị nước ta, rồi mới thiết lập ra các học xã, bấy giờ ông mới ra để xem việc giáo hóa thế nào? Chẳng ngờ các quan nhà Minh thấy ông là người có tài văn học liên cho ông làm Giáo-Thụ, nhưng rồi chúng biết chính ông đã viết bức thư vạn ngôn, nên chúng bắt ông giải về bên Tàu. Lúc ấy ba người con trai của ông tên là Thái-Điên Thiếu-Đinh Thúc-Hiên đều xin đi theo, khi tiến đến Âi Nam-Quan, ông bảo các con: Thời để cho một mình con trưởng theo ta là đủ, còn hai con thứ thì nên trở về trong nom hướng khỏi để bảo thù cho Vua, cha!</t>
+          <t>Thứ coi: Thông Khảo-kỷ-Nguyên cựu sử chép đúng quy mô, lại như Canh-Tịch Thị học chư biên. Chia trường thề đoạn,</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>詢曰我南人志存南國跖狗吠非其主又何問明人怒送于金陵獄父子皆卒于獄中掾萬言書與朱安七斬疏皆忠誠所發陳樸宗先安上疏乞斬七侯臣時稱七斬疏後芸棠故胡公作越鑑有六萬言之書忠貫印月七斬之疏義動鬼神詠史詩云上庠琴劍一書生三策懐憐許國情萬里虜廷終不屈先忠十孝而成名曾孫光貞有詩云超延詩禮講明請自勵懸壯士餌寒蹇匪朝誠協一拳拳許國策陳三綱常自任他奚恤鼎饒知餡死亦酣累世亦蒙忠義報光弼盡業振天南其後明人姜黃福鎮安南設場教學以收我國人才穎題兄弟竝往受業黃福愛之認為己子忽一夜雨電壞牆發屋明日黃福出城南玩景口占一旬云照朝風雨家家額壞舊牆垣以喻南國被侵必致額壞額頸即對云今日乾坤震處發榮新草木黃輝是簡高見人聞此句望天嘆曰安南已有聖主出乾坤方南國復還南國我亦不久且歸矣</t>
+          <t>既師儒希楊震之鱉堂政事萬李宏之山判</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>hai con vàng lời bài biệt rồi quay trở lại. Khi ông cùng Thái-Điên sang tới Yên-Kinh, các quan nhà Minh hỏi rằng: My xui Bá-Kỷ lập lại con cháu nhà Trần, âm mưu làm việc phi pháp là cờ làm sao? Ông đáp: Ta đây là người nước Nam, nên phải quyết chí bảo tồn Nam quốc, con chó của tên Đạo-Chích (kẻ trộm) còn biết cẩn người không phải chủ nó? Vậy thì các ngươn còn hỏi làm chi. Quan Minh nghe xong lấy làm tức giận bên đem giam ông vào nơi ngục thất ở Thanh Kim-Lăng, rồi hai cha con bị chết ở đó!</t>
+          <t>sư nho suy tôn Dương-Chấn, Chánh-sự theo kip Lý-Hoàng,</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>二子盡往從之以圖立功穎顯遂依報尋至愛州已見我大祖蘇山奮勵兄弟皆來歸附未幾大破北兵沐晟黃福等投降之和太祖縱之北還顔顔等戲師歸國至交開相告別同跪請曰儀等蒙作育久矣</t>
+          <t>蒼東海則以恩信撫韓乎邊氓戮北乎則以恬靜鎮安平邊患</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Xét thấy bức Vạn-ngôn-Thư của ông cùng với bản Thất-Trầm-Sơ của Chu-Văn-An đều do một tấm trung thành phát biểu ra ngoài cho nên trong bộ Việt- Giám của Tương-Công mới có câu rằng:,! Vạn ngôn chi thư Trung quân nhật nguyệt. Thất-Trầm chi só nghĩa động quỉ thần. Nghĩa là: bức thư Vạn-ngôn lòng Trung soi thấu nhật nguyệt! Bồn só Thất-Trầm chữ nghĩa động tôi quỉ thần;</t>
+          <t>khi ra Đông-Hải khéo lấy án tín vỗ về, lúc đến Bắc-binh lại thì chính sách điểm tính.</t>
         </is>
       </c>
     </row>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>未審何時復頒教誨請指示陰憤吉昌歸塟先人是吾師之賜也</t>
+          <t>醒聖王圖任舊人越朋背蹤登頭窟業曳履於楓宸作元龜於弈泮</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>rồi sau Văn-Hiên Vinh-Sử cũng có thơ rằng: Gươm dân Tương bằng một thư sinh. Câu nước trong thơ đã hiền minh? Muốn dặm trước thù không chịu khuất? Cha trung con hiếu thấy lừng danh.</t>
+          <t>Vua dùng người cũ, đặt lên chức cao, chống gây trúc vào trước sân rồng, nếu guong sáng trong nền Quốc-học,</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>並福曰我非忘了試觀二子之志耳</t>
+          <t>其八侍經筵也堂堂焉輔成君德之程頗其總裁國史也致成焉志春秋之胡旦</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ông Quang-Bôn cũng có thơ rằng: Trước sân thì lẽ đã từng qua? Tráng chi say sưa tự nhủ mà? Bằng bằng quên mình thành giữ một? Luôn luôn vì nước kẻ đáng ba?</t>
+          <t>ở chức Kinh-Duyên gần gui, giúp vua thành dức như ông Trinh-Dy, ở nơi Quốc-sử Tông-tái, lại tu Xuan thu như ông Hồ-Đán.</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>前日噐心一穴在亦邑兌邊桃樸頭向銀帶日月扶裔天馬在其西旁正乎</t>
+          <t>心忠義兮有天知萬古太和子恩日賞險功多在於斯文</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cương thường phải nhớ, ngoài chi kẻ? Bình vạc như du, chết cũng thả? Trung nghĩa nói đời cơ bảo ưng? Về vang sự nghiệp nước Nam nhà. Thế rồi cách ít lâu sau nhà Minh sai Thượng-Thư Hoàng-Phúc sang làm Đô-hộ An-Nam, Phúc liên mở trường dạy học để thu nhân tài, bấy giờ anh em Thúc-Đinh cũng xin nhập học, được Phúc yêu mến nhận làm con nuôi. Rồi bỗng một đêm mưa bão làm đổ nhà cửa! sáng sớm hôm sau, Hoàng-Phúc thân ra ngoài thành để xem quang cảnh, buột miệng đọc một câu rằng:.</t>
+          <t>Một tấm lòng son trời có biết? Muôn đời thịnh trị bút còn ghi, những tưởng âm công chưa chất, sẽ hưởng thọ toàn lâu dài.</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>年我已埋下木板歸而尋之囑其子孫後有北使遲歸便可鑿這馬足郎當反轡二人拜辭而回時太祖已矣</t>
+          <t>陽報期年於京尊胡皇天不假於愁遺致暮夜垂懸於難受易纏柱下之魄筆寫難常中之讚顏梁興冬士之嗟之強起九壹之嘆聞哀之中侯甫三慰吊之金餞臣萬</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tác triều phong vũ gia gia đồi hoại cựu viên tường? Nghĩa là: hôm qua gió mưa, tường vách muốn nha cùng đổ la liệt. Xét thấy câu thơ ứng khẩu trên đây, Hoàng-Phúc có ý nói nước Nam ta đã bị xâm chiếm thế tất là phải tan hoang? vì thế Thúc-Hiên cũng ứng khẩu đối rằng:. Kim nhật càn khôn xử xử phát vinh tán thảo mộc. Nghĩa là: Hôm nay trời đất cô cây bốn mặt càng thêm tỏ vẻ tốt tươi. Hoàng-Phúc là người cao kiến khi nghe học trò đối lại như vậy, thốt nhiên ngửa mặt lên trời than rằng: Thôi!</t>
+          <t>Cờ sao hoàng thiên chẳng dễ, khiến cho đêm tối làm nguy. Hồn còn phảng phát đầu đây, bút khó điểm tò nên chử. Thái-Sơn khi dò sĩ phu lương những ngâm ngùi! cừu trùng xiết bao ta thân, sai quan thăm viếng sau trước mấy lần, ăn huệ ban cho bạc tiền hàng vạn.</t>
         </is>
       </c>
     </row>
@@ -3603,12 +3603,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>天下擇人北使無敢行者少頴以父兄之故敵然請往太祖許之拜審刑院事、</t>
+          <t>時先生之不幸乃史書之不幸必使天下之人見其目睹耳聞莫不痛心之扼腕</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>An-Nam đã có Thánh chúa giáng sinh tại phương càn khôn (dong nam) nước Nam lại được trả về cho người nước Nam, chẳng bao lâu nữa ta cũng trở về Bắc quốc? vậy thì hai con sao chả đi tìm người đó để lập công danh? Anh em Thúc-Hiên nghe lời Hoàng-Phúc chỉ giáo ưư vậy, bèn từ biệt thầy để vào Ái-Châu dăng tìm Thánh chúa? khi vào tới nơi thì Lê-Thái-Tổ đã khởi nghĩa ở Lam-Sơn rồi. Anh em bèn xin ở lại phò tá, rồi chẳng bao lâu, quân Minh bị bại, Mộc-Thanh Hoàng-Phúc xin hòa. Thái-Tổ tha cho trở về Bắc quốc, lúc ấy anh em Đinh-Hiên xin tiến chân thầy đến Ái Nam-Quan rồi mới thưa rằng: Chúng con nhớ ơn chỉ giáo đã lâu, ngày nay Tôn-sur trở về cớ quốc, chẳng biết bao giờ lại sang? vậy xin Tôn-sur chỉ bảo cho mấy người đất đề táng Tô tiên?</t>
+          <t>Than ôi! Tiên sinh bất hạnh là không may cho Sứ quân nước nhà, những người mất thấy tai nghe ai không thương tiếc!</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>秦陳情表于明其畧曰天地之於萬物雖有雷霆之怒而發生每行乎</t>
+          <t>況某也義重臣三情深于半愴一刑之長終恨百年莫換器</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>đó là cái ơn đặc biệt vậy. Hoàng-Phúc đáp rằng: Việc đó nhẽ nào Thầy lại không nhớ?</t>
+          <t>Hương chi tôi đây, nghĩa nặng nào khác cha sinh. Tinh sâu lại là con rẻ, biệt ly một phút, uất hận trăm năm!</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>其間父母之於眾子雖有笞檳之威而鞠育常存乎</t>
+          <t>聞此日僅得備會禮而正是衣冠在續權時不得設几筵而奠是酒鬱</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>chẳng qua là muốn thử gia các anh đó thôi? vậy nay Thầy bảo cho các anh biết, nguyên trước Thầy đã lưu tâm một huyết ở ngay phía bắc làng anh, cục ấy gởi vào chiếc mũ trong ra chiếc dai vàng, nhật nguyệt đóng ở hai vai, ngựa đi sứ đông tại phía Tây, còn mộ thì toạ chữ Tỷ hướng chữ ngo, phía dưới Thầy đã chọn sẵn một mảnh vân gỗ làm ghi, vậy khi trở về các anh nên tìm ngay đến chỗ đó, và nhớ hẹn con' cháu rằng: Sau này nếu có sang Sư mà lâu không trở về, thì cứ dục khoét vào chân con ngựa ấy, tự nhiên Sư giả sẽ được về ngay? Hai người nghe xong bài từ Hoàng-Phúc rồi quay trở lại. Lúc ấy Thái-Tổ đã bình định xong thiên hạ, Ngái muốn tuyển một Sư bộ sang Tâu nhưng chẳng ai dám xin đi, riêng có Thúc-Định vì muốn tiện thể thăm đó tin tức phụ huynh nên mới khẳng khái tình nguyện, Thái-Tổ bèn phong cho chức Thâm-Hình Viện-Sự để mang tờ biểu trần tình sang nộp tờ biểu đại lược như sau: Trời đất đối với muốn loài, mỗi khi giạn dữ đầu có ra oai sấm sét, nhưng mà bên trong vẫn ngụ sẵn đức hiểu sinh? Cha mẹ đối với các con, đầu có dùng đến roi vọt mà on cục dục vẫn dễ trong lòng, chả thể mà con người ta mỗi khi gặp sự đau đớn lại kêu trời đất cha mẹ? cho nên ngày nay Thần phải đem câu tâm huyết giải bày để mong soi xét v.v. (Tờ biểu này do quan Thừa-Chí Nguyễn-Trãi soạn). Kèm với tờ biểu kẻ trên lại còn một hộp vàng bạc thay thế hình nhân, bên trong có đựng mỗi thứ là 100 lượng, khi tới Yên-Kinh, vua tới nhà Minh cảm thù về việc sát hại Liễu-Thăng nên chỉ quát mắng chứ không thu nhận, rồi lại bắt giam Thiếu-Đinh ở ngoài công thành, và bồi son kín cả hai mắt không cho ăn uống gì cả.</t>
+          <t>Cáo phó hôm nào may được y quan vào liệm, những ngày quan thần chẳng được giang rượu mấy tuần,</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>其內是以人有疾病未常不呼天地父母此臣子之歷緬陳詞以伸表籲也</t>
+          <t>魯城靈墓兮恨無由從厚血壠兮增感嘆</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>May sao lúc ấy Hoàng-Phúc vào triều biết là Thiếu-Đinh, nên thường dẫu bánh mi ở trong mũi giầy, mỗi khi đạo qua hắt cho Thiếu - Đinh, vì thế nên không chết lả. Triều thân nhà Minh thấy hơn 3 tháng mà sao Thiếu-Đinh vẫn sống như thường, thì cho là bạc thân nhân hấy giờ mới chịu nhận lễ, và cho trở về báo tin. Về phần Thiếu-Đinh sau khi đã được trả lại tự-do, lập tức đi đạo các nơi hỏi thăm tin tức cha anh ngày trước, nhưng cũng chẳng biết mất ở nơi nào? Sau cùng đến một người chùa thì thấy có một tập thơ để lại, ông bên mang về bồn quốc và làm ma chay theo tục hư tàng (tàng bằng quan tài không) về sau nhân việc can ngăn làm vua phật ý phải giáng chức Viên-ngoại-lạng; vì thế Quang-Bôn có thơ vịnh rằng: Tên họ vang lừng lúc tuổi xanh, Gặp thời khai sáng, chúa anh mình!</t>
+          <t>làm nhà bên mộ khôn hay, gò đống ngồn ngang thêm cảm,</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>寫所作並替代金人二軀各重二百兩至燕京陳于關下懇訴明人恨我國徵殺柳昇之故甄唾罵不問物火頴于門下外漆其兩目不許飲食時黃福八朝見之知其少穎嘗取貓餅藏穀中每過即授之三月餘不死明人以為神始受貢禮使囘復命火穎因尋父兄不知沒處至于僧奇只見一詩一畫存焉</t>
+          <t>將欲收先生之遺篇則某也以文章倥傯總覩筆夕踈不莊集昌樑之遺文而為唐李漢</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cung loạn án ngọc hằng lui tới? Xe sứ đường mây sớm khởi hành. Nghĩa cả thờ vua trung với ái. Đạo trời qua vận bỉ sang hạnh. Ngày nay con cháu nơi đường cũ? Xây đắp công danh sự nghiệp mình? Xét thấy hai ông Đinh và Hiền đều có công to trong việc thống nhất của vua Lê-Thái-Tổ, chỉ vì một hôm bản việc gia-dinh, không vào triều kiến, bị phạm vào lối khiếm điểm, thành thử không được phong tước công thần đó thôi.</t>
+          <t>cũng muốn thu thập di cảo, then mình nghiên bút sơ sai,</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>即將固本鄉虛墓之後諫太祖忤旨降禮部員外郎光貢有詩云壯年表表頁高各開創寅緣際聖明詩草預陪寫掖運垂朝先擁使花行王臣襄惕忠兼孝天理昭明困復亨未商于今循故轍功成事濟是前程其孫孫襄中狀元生下共責五歲好學人號袖童統元年號、</t>
+          <t>將欲紡先生之道派則某也以見聞淺陋政事紛紜不罷榻老亭之遺蹤而為泉之黃幹</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nhắc lại khi trước ông làm Tri-phủ Tràng-An, nhân có một hôm vào yết miếu vua Đinh, ông thấy pho tượng Dương-Hậu cùng đặt ngòi chung với hai ông chồng, (tức là vua Đinh-Tiên-Hoàng và Lê-Đại-Hành) thì ông cho là hồn độn, nên có đáng bắn sỏ tàu, xin đặt Dương-Hậu vào chổ chồng sau. Nghi-luận táo bạo này được đức Thái-Tồ ban khen: Khanh quả là người trung trực, chẳng sợ quỉ thần.</t>
+          <t>cũng muốn diễn lại dư ba! thẹn mình kiến văn nồng cạn, nhớ nét bằng thanh thường: phảng phát.</t>
         </is>
       </c>
     </row>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>丙辰科中黃甲仕至戶部左侍郎奉往北使時有中使輔行等寧貴物假作金銀替代潛取原物公不知之比至南寧府總督啟發見其非真遂以事聞皇帝怒其無禮命拘晉于北那官仍以蛤蜊覆公兩目以漆粘之曰瓶氣馬角方得還期公怡然自樂不少動心書於冬日出時輒圓一小床曝于日下一明人問其故公即撫其腹曰我曝腹中經笥耳</t>
+          <t>水清玉潤兮想無忘萬里接遲兮空望新惡一酌以將愧寫百年之哀怒</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Rồi ngài hạ lệnh cho rước Đại-Hành và Dương-Hậu sang thờ tại ngôi miếu khác! Về sau ông được thăng chức Tuyên-Phủ-Sứ Trần Lạng - Giang châu là Tràng - Nguyễn Lê-Nại sinh ra Quang-Bôn, Quang-Bôn lúc mới lên 5 tuổi đã nỗi tiếng là thân-đồng thì đỗ Hoàng-Giáp khoa Binh-Tuất thời Lê Thống-Nguyễn, về sau làm đến Thị-Lang bộ Hộ, khi sang Sư Tẩu, có viên Trung-Sứ trong nom các thứ lễ vật đem vàng bạc giả đánh tráo mà ông không biết, khi sang đến phủ Nam-Ninh, viên Tông-Đốc bên đó mở ra kiểm điểm, biết là không phải vàng thực, lập tức báo cáo về triều, Minh triều cho là vô lễ, hạ lệnh giam cầm sứ thần, rồi viên Tông-Đốc sai lấy vở trai bịt kín hai mắt của ông, bên ngoài dùng son phủ lại, và báo cho biết: Bao giờ thấy ngựa mọc sừng thì người được trở về nước? Còn về phần ông đầu bị tai nạn bất thần như vậy, mà ông vẫn cứ thân nhiên không hề ta thân, gặp tiết mưa đông, lúc vùng Thái-dương vừa mọc ông thường nằm ngửa trên chiếc chồng, phơi dưới ánh nắng mặt trời, quan lại nhà Minh hỏi cô tại sao? thì ông vỗ bụng bảo rằng: Tôi phơi sách vở trong bụng đây mà?</t>
+          <t>Trong với Cáo - lý những bảng khuang, gọi là một chén kinh dâng, khôn tả trăm năm ai oán</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3722,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>明人使讀大演義公讀了一遍不差一字明人大奇之即去其粘目甚加禮重公客旅中有撲逃本社諸先靈詩集寄歸</t>
+          <t>魏朝嘆詠詩云</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bọn quan lại nhà Minh thấy ông trả lời một cách tự phụ như vậy, liền bảo ông đọc thử một quyền Đại-học Diễn-ngiha xem sao? Biết rằng chúng muốn thử mình? ông bèn lên giọng đọc ngay một lượt chẳng hề sai một chữ nào? bọn chúng thấy vậy đem lòng kinh phục? tức thì cởi bỏ những thứ gắn mắt và để ông được tự do chứ không hành hạ như trước, thế rồi trong khi còn ở lữ điểm, ông cô soạn tập được một cuốn thơ của các Tiên hiền trong xã, đặt tên là cuốn Tư-hương Vạn-Lục gửi về nước nhà, còn ông thì phải ở lại đợi lệnh. Nhắc lại trong khi ông còn ở lại bêu Tàu, bỗng có một vị Cử-Nhân nhà Minh tên gọi là Đặng-Hồng-Chấn, vẫn thường đi lại với viên Tùy-tông của ông là Thân-khắc-Tảo vì thấy ông là người học văn yêm bác, bèn xin thụ nghiệp để học hỏi thêm? rồi sau đến khoa Kỷ-Vị thì đỗ Tấn-Sĩ, được bờ Tri-huyện Quảng-Đông, dàn dàn thăng chức Yến-Kinh Chủ-sự, nhân mới nghĩ đến thấy học của mình còn bị đây ải ở chốn tha hương, bèn dâng bản tấu kẻ rõ tình hình, được vua nhà Minh xét lại, lập tức triệu ông về Kinh an ủi, rồi tháng 3 nhuận năm ấy cho ông trở về bản quốc.</t>
+          <t>bởi thế nên trong tập Lê-Triệu khiếu Vinh đã có thơ rằng:</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>時有葉人鄭洪震見公紫閣僕長郎八門受業癸未科中進士第除廣東知縣陞燕京重事以念其師淹晉不返即具本奏聞明帝始原之因召至京慰問二月遣還洪震即設愛買斂並綵銀致饒公出侯凡十八年其家黃橋福之言始鑿金為足王是歸國陸吏部尚書蘇川侯後贈少保蘇郡公人獸武前身蓋相類者</t>
+          <t>儒科早擢際明時學道尊為國學師</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Trước khi lên đường Hồng-Chấn có bảy tiệc tiến hành và biểu một số bạc cùng các thứ vài vóc v.v. Tình lại ông phung mang đi Sứ vừa dùng 18 năm trời, gia đình ở bên nước nhà thấy lâu được về, bên theo như lời Hoàng-Phúc hẹn trước, đem khoét vào chỗ chân ngựa. hóa nên ông được trở lại, rồi khi về nước được thăng chức Lại-Bộ Thượng-Thư, tặng tước Thiếu-Bảo Quân-Công. người đời bảo ông là kiếp sau ông Tô-Vũ, đời nhà Hán, vì thân thể cũng giống nhau vậy.</t>
+          <t>Sớm chiếm cao khoa buổi thịnh thi. Đạo cao quốc học bậc Tôn sư (si)</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>尚書張孚記 青沔金壤断慶帝年號乙酉科中黃甲公性頗剛直統元末莫登庸欲篡位時公為吏部尚書百官以其故臣使作禮詔公張目叱之曰此何義也</t>
+          <t>越考一為真可法休談撫怪謾傳奇</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ông Trương-phu-Thuyệt người làng Kim-Đầu thuộc huyện Thanh-Miện, thời Lê Uy-Mục niên hiệu Đoan-Khánh. 1505-1509 thì đã Hoàng-Giáp khoa Ất-Sửu. Ông là người có tinh cương trực cho nên vào cuối năm Thống-nguyên (1527) Mạc-Đăng-Dung muốn cướp ngôi nhà Lê, lúc ấy ông đương giữ chức Thượng-Thư bộ Lại, bá quan thấy ông là bậc nguyên lão đại-thần nhờ ông thảo cho bản chiêu nhường ngôi! Ông liên trọn mắt quát bảo: Như vậy là nghĩa lý gi?</t>
+          <t>Một Thiên Việt khảo phương châm đủ. Trích quái bản chi những truyện kỳ.</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>終不脹屈改命願公泰為之後公歸田里適間中館問野服乘涼與常人無異時則令偶經伊處人皆起立公獨靜坐矣</t>
+          <t>繡光貢有詩云</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bá quan biết rằng không thể bắt ép được ông, nên lại trao cho Nguyễn-văn-Thái (Đỗ Thám-Hoa khoa Nhâm-Tuất (1501), năm Cảnh-Thống thứ 5) đứng thảo. Ông bèn cáo quan trở về làng cũ, trong lúc thư nhân thường ra quán ngồi chơi hóng mát, chẳng khác một người dân quê? Bồng có một hôm quan Huyện sở tại đi qua, mọi người trong quán đều đứng cả dậy, chỉ có một mình ông là vẫn ngồi yên, linh hầu của quan thấy vậy quát mắng: Người kia sao dám vô lễ? và toàn đánh đập!</t>
+          <t>QUANG-BÔN CÓ THƠ RẰNG:</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>之從者叱曰何人無禮將欲攻之縣令望見公駿須之異急止從者曰吾觀此鬚美且認其體構必有識字試出對句若或不成打之未晚即出對六知縣青沔見無礼而欲攻公郎應之曰進士金燭幸有珍餚而得晚賂令始知其公即連遜趨拜自言途由錯誤過咎是耳</t>
+          <t>堂堂聖世一洪儒 仕士隨時任自由 天上麗儒稱。骨相人間話佛見心頭嘉言善行諸賢慈大典高文萬古彌斯道巍然山奇在後人無不企企前修傳奇唐安之武者是也</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Quan Huyện nhìn ông thấy có bộ râu rất đẹp! vội vàng quát bảo linh hầu: Ta coi người này râu ria đạo mạo, tất nhiên là người có học? vậy để ta ra cho một vẽ đối, nếu không đối được, hãy đánh cũng chưa muốn gì, nói xong quan bên ra một vẽ đối như sau:, Huyện quan Thanh-Miện kiến vờ lề nhi duc công. Ông liên ưng khâu đối rằng: Tấn-Sĩ Kim-Đầu vị hưu tu nhi đắc miễn.</t>
+          <t>Một vị hồng nho giữa Thánh trào. Tùy thời tần thoái tự do sao. Tiên còn thượng thế coi như đúc? Phật sống nhân gian ngầm khác nào? Ngôn hạnh đối đương ai sánh kịp. Văn chương muốn thuở giá càng cao. Non xanh cùng đạo nguy nga mãi Hậu thế ai người chẳng ước ao? Nay ta xét thấy trong tập Truyền - Kỷ có chép họ Vũ ở Đường-An, chính là họ Vũ này vậy.</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>幸大人見恕公笑而釋之公前不附偽莫後辭歸不仕蓋在節義之列云</t>
+          <t>公子幹生而頴異博極群書景綿稱德士寅科中黃甲性愛松故以松軒自號文章行當代推尊雖家素清貧而恬然自適凡遇物即事輒隨意興吟矢口成章揮毫立就日積月累遂成一家機軸</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Nghĩa là: Quan huyện Thanh-Miện thấy kẻ vờ lề mà muốn đánh. Đối với: Tấn-Sĩ Kim-Đầu may vì có râu mà được tha. Quan Huyện nghe xong câu đối mới biết chính là ông Nghè, vội vàng bài tạ, xin ông thứ lỗi, ông cũng cười xóa. Xét ông không phù Mạc, thực xứng là người biết trọng tiết nghĩa vậy.</t>
+          <t>Còn những con giai của ông tên là Cán, lúc nhỏ cũng rất thông minh nói tiếng là người bác học, thì đồ Hoàng-giáp vào khoa nhâm tuất thời Lê-Cảnh-Thống năm ấy mới 28 tuổi vì tánh yêu tùng nên mới lấy hiệu là Tùng-Hiên, về phần văn chương đức hạnh người đời rất là kinh mến, nhà vốn thanh bản thế mà lúc nào ông cũng thân nhiên, gặp khi cao hứng xuất khẩu thành chương, ngày tháng tích lại đóng thành một tập.</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>大興候記院世儀當泰澤社一下村人中官蒞國公世恩之第附焉</t>
+          <t>典永賴古庵程國公相善其詩詞偈經往復如懷鄉綠蒿艾虎等首見白雲庵詩集未澤鄉八景等首見品景詩集又有松軒詩集并四六備覧覧傳于世</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Đại Hưng-Hàu bằng huynh tử chi ĐẠI HUNG-HÀU VÌ CÓ THỂ LỰC CỦA ANH MÀ BUỘC PHÓNG TÚNG Nguyễn-Thế-Nghi người ở thôn hạ làng Mộ-Trạch, là em quan Đam-Quốc-Công Nguyễn-Thế-Án và là chủ họ của Phò-Mã Nguyễn-Thế-Từ, ông vốn có tính bừa bãi không giữ lễ độ, nhưng chỉ khi lại rất cao thượng, ngày từ lúc nhỏ đã giỏi văn-chương, mà lại sở trường về thế quốc âm thơ phú, khi 15 tuổi thì đã Hương-Tiến (Cử-Nhân) lúc ấy các người đồng bằng vào tạ quan trường ai cũng áo mũ màu xanh, riêng ông lại mặc màu hồng có thêu đuôi qua. Quan trường có vẻ bất mãn nhưng vì e sợ thể lực Quốc-Công, nên không phục vấn giả cả. Nguyễn ông ngày thường chơi thân với Mạc-Đăng-Dung, đến năm Thống-Nguyễn (1527) Đặng-Dung cướp ngôi nhà Lê thì ông đương lạc lõng ở ngày Kinh thành trù ngụ trong chùa Trưởng-An, nhưng không có ý cầu cảnh.</t>
+          <t>Ngoài ra ông lại cùng với bạn thân là Trinh-quốc-Công ở Trung-Am thuộc huyện Vĩnh-Lại xướng họa rất nhiều, tỷ như các bài thơ Hoài-hương Chi-duyên Một - hở v. v. hiện nay có chép trong Bạch Vân-Am Thi tập và các bài Tiêu-Tương-bát-Thủ thấy ở trong tập Phẩm-Vưng, lại còn Tùng-hiên tập và Tập Tứ-lục-bị-lâm truyền bá cho đời,</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>賜之叔也為人焉浪不循禮度而高尚志氣少善盈文尤長於文體十五歲頴鄉舉特同科諸貢士拜試場官皆用烏紗帽青吉衣公獨著紅色衣烏尾暢場官怖乃兄勢熖仍免覆問平日共奠登庸相有交善統元間也</t>
+          <t>仕禮部尚書禮度伯光賁詩云</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Thế mà một hôm họ Mạc biết tin muốn phong quan trước ông cũng từ chối; chỉ xin phong cho một danh hiệu mà thời. Đăng-Dung hỏi danh hiệu gi? Ông xin phong cho hai chữ Đại-Hưng, Đăng-Dung cũng bằng lòng cho để ông làm theo chí muốn, rồi sau ông thường ngâm mấy câu thơ nôm, và để vào phía tả của Đại-Hưng rằng:?</t>
+          <t>về sau ông cùng làm đến Lễ-bộ Thượng-thư và được phong tước Lễ-Độ-Bá. Cho nên ông Quang-Bồn có thơ vinh rằng:</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>音托不檢束也。</t>
+          <t>早擢危科副上來文章德業依飾模</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Anh hùng ai này nhung những?</t>
+          <t>Sớm đỗ cao khoa đẹp ý vua. Văn chương đức nghiệp đang sư mô.</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>出居京城外長生寺不求療達一月莫簽庸迫至欲加以好官公辭不受願得一爵為各稱足矣</t>
+          <t>半天載上扶興運三十年餘歷要途</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Nào ai đến cửa Đại-Hưng chẳng luôn? Có ý bảo mình ngồi bên trên, mà ai cũng phải luôn cùi bên dưới vậy? hai câu này đến cuối đời nhà Mạc vẫn thấy còn để chữ không bị xóa.</t>
+          <t>Nửa ngàn năm trước phò hưng vạn. Ba chục niên sau trái hoàn đồ.</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>因請以大興二字為號登庸許之即拜為大興侯任行高志儀嘗浪吟一句云英雄埃乃剝剝帝境鉅剎大興庄輪題于登龍城大興門左自謂己在其上而人皆出下之意歷歷莫大李尚存時莫氏荒怠政命著樂昌分鏡國語傳序陳隋奢欲事寫意諷論他亦不之悟也</t>
+          <t>驚龜冕躬主新好爵青燈黃老舊寒儒</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Thế rồi về sau nhà Mạc hoang dâm, trẻ nái về đường chính-trị. Ông bèn soạn ra truyện Nhạc-Xương phân kinh dùng toàn quốc âm, ngụ ý chê bài họ Mạc xa xi giống như nhà Trần nhà Tùy ngày xưa, thế mà họ Mạc vẫn không tỉnh ngộ, ông lại soạn ra bài phu Huyền-Quang-Tuyền cung nữ bằng quốc âm, rất được nhiều người truyền tụng.</t>
+          <t>Áo tía đại vàng Quan tốt phẩm. Đèn xanh Ấn tuyệt cảnh hàn nho.</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>又嘗有北侯至途經南門聞門上題字係我國臣子各號輒停車不進要以架梯從上而行時尚書武惟斬為援伴官伴應以知命部下生一計陰取送象來從後痛刺槪大吼衝突北人叱了一驚郎撓愕走過自知墜于計中不勝慙憤至今猶傳其事云</t>
+          <t>清貧誰哉為家計焦地詩書有道腹</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Đến thời Minh-Đức (1527-1529) có sứ Tàu sang, khi qua cửa Nam nhìn lên thấy có chữ đề bên trên, và là danh hiệu của một thần từ nước Nam, nên bắt dừng xe không chịu tiến nữa, và lại bắt ta phải đi lấy thang để bắc qua công thì mới chịu vào? Giữa lúc ấy có quan Thượng-Thư là Võ-Duy-Đoán hiện sung chức Bàn-Tiếp để dón sứ-giả, thấy sứ yêu sách như vậy, Ngại cũng giả ý tuân theo, nhưng mà trong tâm đã nghĩ ra được một kế, ngầm sai quan hầu di bảo quân-tượng xua voi đi qua, lúc gần đến chỗ sừ-giả thì lấy mũi nhọn chích vào lưng voi, voi bị đau buốt gãm lên rồi nhảy loạn xạ, làm cho ai này cũng phải hoảng hồn tim chở ăn nấp? chạy xô cả vào phía trong cửa nam, sừ-giả và đoàn tùy-tùng cũng thế, nhưng khi đã trót chạy vào mới biết rằng mình trúng mưu, đánh phải nuốt hận; việc ấy vẫn còn truyền ngọn cho mãi đến nay.</t>
+          <t>Phí gia kề ấy không mang tới, Rượng cấy thi thư chẳng mất mùa.</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>扶擁節婦記上洪唐安有范氏各援者自少通穎尙間頗有姿色既加笄即歸于唐豪令族之家生下男女四人值北兵南侵夫以病死婦撫幼育孤以不一庭不雨醮自誓言其悲酸情狀缺石心腸非言語形容所莊盡將當兵火人罕自全城或饑寒失守為盜賊所污者或道路流亡苟來生浩而婦周旋其間以死自誓言變容斂色不為隱暴所侵一方之人皆以故郡鄰目之造天日明基圖復舊朝之達官鄉之豪右屢欲奪其操詔求真烈有司以名聞仍表其問曰節義門賜奉事以旌揭之年八十而終子孫累世長冠為一鄉之明王族今扶櫨社有故碑存焉</t>
+          <t>樗眼阮全安記</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>LIỆT NỮ Tiết phụ món, nhất hương vọng tộc CỦA TIẾT-PHỤ, MỘT HỌ DANH VỌNG NHẤT LÂNG Xã Thượng-Hồng huyện Đường-An có người con gái tên là Phạm-Noãn, lúc còn niên thiếu người rất thông minh nhân nhà lại thêm có nhan sắc đẹp, khi đến tuổi cấp kẻ kết duyên với một người cùng dòng đối danh giá ở làng Phù-ùng thuộc huyện Đường-Hào, sinh hạ được 4 con, cả trai lẫn gái. Chẳng may gặp lúc quân Tàu kéo sang xâm chiếm, người chồng lại bị ốm chết, thế mà chỉ vẫn quyết chí ở vậy để nuôi các con chứ không bước qua cầu nữa, dù rằng phải chịu trăm đáng ngàn cay, mà tấm dạ sắt gan vàng không ai có thể hình dung hết được. Bởi vì trong con bình hòa, ít ai giữ được trong sạch tấm thân, nếu không vì cảnh cơ hàn, cũng bị giặc cướp hãm hiếp, hoặc giả trong bước lưu ly cũng phải bán liều danh tiết để cầu lấy sống. Thế mà riêng chị lại quyết làm cho hủy hoại nhan sắc, để bọn cưỡng đạo chẳng muốn nhìn mặt, nên mỗi giữ được trọn tấm kiên trình; vì thế cả vùng ai cũng khen là một người tiết-phụ hiếm có. Nhất là về sau giang-son đến hồi quang phục, các quan trong triều cựng như cương hào trong xã, vi yêu danh tiết cũng muốn ép duyên, nhưng nàng đem câu đại nghĩa ra để từ chối, thì ai cũng phải kinh nê. Thế rồi vào khoảng niên hiệu Thái-Hòa đời Lê-Nhân-Tông (1443-1454) nhà vua xuống chiếu hỏi đến những người trinh-tiết, các quan địa phương cử thực tấu trình, vua bèn ban cho chiếc biển treo của có đề chữ Tiết-Phụ-Môn? để nếu tấm gương tiết-liệt, về sau bà thọ 86 tuổi, con cháu vinh hiển nối đời, thành ra một họ danh vọng nhất xã, hiện nay tấm bia cũ ấy vẫn còn.</t>
+          <t>LÁNH HIỆU BAN THI, NGUYỄN BẢNG-NHÂN</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3943,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>陰境陳朝祖墓記陳朝之祖美禎，</t>
+          <t>阮全安唐安時舉人也洪德間充另兵常守殿前判草適中秋朝侍間夜月昏曉御題中秋無月詩班列中吟咏未竟公詩先就跪而上之在坐笑曰另兵亦有詩乎母乃雷門擊手鼓命取觀之落句若曰</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tô tiên nhà Trần ở làng Tức-Mặc p? thuộc huyện Mỹ-Lộc nỗi đời làm nghề chài lưới,</t>
+          <t>Nguyễn-Toàn-An, người làng Thời-Cử tham thuộc huyện Dương-An vào khoảng niên hiệu Lê-Hồng-đức ông phải sung vào ngạch lính, giữ việc cắt cỏ ở trong sân điện, một đêm gặp tiết trung thu, bá quan được vào thường giang trong điện, đêm ấy giáng mờ, Hoàng thượng bên lấy 4 chữ Trung thu vô Nguyệt làm đầu đề, bắt các văn thần vinh thi, giữa lúc mọi người còn dương thời xao, chẳng ngờ chú lính Toàn-An đã làm xong trước, qui gởi dâng lên! cứ tỏ ai cũng cười rằng: binh lính cũng biết làm thơ đó chẳng? rỡ thật đánh trọng qua cửa nhà sắm, Hoàng thượng thấy vậy phân bảo đưa lên Ngai coi. Thấy câu kết viết:</t>
         </is>
       </c>
     </row>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>即墨人也。世以魚為業，</t>
+          <t>莫把今番閒視月來秋望月月彌高</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>suốt cả một giải Tràng-giang ở nam đảo, tới đầu thì cũng là nhà, chừ không nhứt định. Lúc ấy có thấy địa lý chính tong ở bên Tàu sang nước ta tìm đất, bắt đầu từ đây tổ-son Tam-Đảo lần theo long mạch xướng khỏi Thăng-Long Cờ-Bi rồi đến các xã Kệ-Châu Cao-Xá thuộc huyện Kim-Động, thấy nhiều gò đồng tụ tập ở đó, thì thấy bảo rằng: đây là chỗ đóng bình nâu com; đi đến xã Phương-Trà thuộc huyện Nam-Xương, không thấy vết tích long mạch đâu nữa. Thấy địa dừng lại nhìn quanh một lúc, thì lại nhầm lầm nói một mình rằng: Nước sông chảy xiết thế kia, lẽ nào huyết lại chim dưới thủy đề. Rồi lại xướng đó sang sông, đi tới đến làng Hà-Liễu thuộc huyện Ngư-Thiên.</t>
+          <t>. Chớ thấy phen này mà để nguyệt? Thu sau trông nguyệt nguyệt càng cao.</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>南道長江一帶，</t>
+          <t>觀者嘆服仍具奏敬因全寅科貳拾歲一舉中鄉試會廷試中榜眼合菜歸</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>thấy một ngọn núi lù lù hiện lên.</t>
+          <t>ai cũng tóm tắc khen ngợi rồi tâu vua xá tội cho về, đến năm nhâm-thin thì ông mới 23 tuổi, gặp có khoa thì ông vào ứng cử đỗ thi Hương xong, lại đỗ cả thi Hội; lúc vào thì Đinh được đỗ Bảng-nhãn, vinh quí bài tỏ vừa xong</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>到處是家焉。</t>
+          <t>未幾適值家憂時朝制孔嚴係憂中要憂孕者不盡仕刻公守制三年不敬近女色服闕尋卒無嗣皇上聞而憐之自是居喪言月之極亦始除之</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Thấy địa tỏ về mừng rõ chỉ tay nói rằng: Nó đã ngóc đầu kia rồi, thế nào lại trốn được ta? Nhận rõ long mạch rồi thấy lại tìm đến xã Nhật-Cảo là nơi khởi điểm, và xã Đại-Dương là nơi kết cục, bấy giờ mới đặt địa bàn coi thử, rồi thấy cảm thấy say mê, quanh quần mãi ở nơi đó. Chẳng ngờ giữa lúc thấy dương trù trù nghĩ ngợi ở đó, thì có một người tên gọi Nguyễn-Cố Ẩn người xã Tây-Vệ xá đi qua nom thấy, tiến lại hỏi rằng: Địa Tiên chú ý ở đây, phải chẳng chở này có ngôi quí địa sao đó.</t>
+          <t>chẳng may lại gặp gia biến, theo như chế độ hiện hành, nghiêm cấm những người trong lúc có tang cha mẹ mà vợ thụ thai, thì không được kẻ vào hàng thân sĩ, bởi thế trong vòng 3 năm cư tang, ông phải lánh xa thế thiếp, rồi khi hết tang ông bị ốm chết, thành ra vô tự!</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>時有堪輿北客就我國相地自三島祖山從龍脈而來歷昇龍古碑至金洞縣偈州社高會社見土堆環聚即笑而言曰是也</t>
+          <t>光真有詩云</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Thầy địa nghe Cố hỏi vậy, có ý tự phụ ngửa mặt cả cười: Hừ hừ! Ai biết ngôi đất để vương lại lạc xuống quảng bình điền. Từ trước đến nay các thầy địa lý thực không có mất.</t>
+          <t>vì thế Quang-Bôn có thơ khóc rằng:</t>
         </is>
       </c>
     </row>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>駐兵造厭旁至南昌縣芳萊社江漢沒了臨江顧望良久曰江水急流豈有六藏水底耶</t>
+          <t>森然美玉為聖河莫狀良工妙琢磨</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Chú thầy địa nói xong, Nguyễn-Cố sừng sốt hỏi: Nếu quả như vậy, xin thầy làm ơn để lại cho tôi, tôi xin biên lễ hậu tạ, bao nhiêu cũng được. Chú thầy địa đáp: Ừ, nhà người có phước nên mới gặp ta, thì ta cũng để giúp cho. Nhưng có một điều là khi tàng xong thì phải đưa trước cho ta 100 quan tiền, còn sau đến khi chiếm được nước rồi thì phải chia đôi thiên hạ. Nguyễn-Cố thấy chú khách buộc hai điều kiện trên cũng chấp thuận ngay, rồi hốt ngôi mộ Tô lên để nhờ thầy địa an táng.</t>
+          <t>Sáng choang ngọc bích giữa trần ai, Khôn tỏ lương công cách giữa mái.</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>因過河而往至御天縣河柳社見星峯草立郎指之曰撞頭旁在是寧能適我耶</t>
+          <t>辛苦十年劬勞九寅綠一拳權危科</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Thầy địa sợ Cố lật lọng nên lại hẹn rằng: kiểu đất này sau khi tàng rồi phát đạt rất lớn.</t>
+          <t>Đèn sách mười niên công chẳng quản, Khoa danh nhất cử gia chưa hai.</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>遂尋至日果社起宗到太堂社阮固結苟旁續下盤針看了輒躊躇不敍去適西衙人阮固見之問曰地仙屬意于見不知這處有吉穴耶</t>
+          <t>方施心上經綸用莫測裘中愁恨交</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Nhưng mà trong khoảng 100 ngày, phải nên thời thường thám thính, nếu sau những trận gió mưa sấm sét, mà thấy có sự gì lạ, thì sự tốt lành có ít mà sự hung dữ lại nhiều, nên kịp đời đi chỗ khác.</t>
+          <t>Kinh luận mở túi toàn gia sức, Luật pháp cư tang cảm thụ thai.</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>客人仰面笑曰不謂奇王大地出平陽可笑聰勁時師都無眼力固曰果如此請以許我師謝禮如何我亦可辨客人曰爾既有福而遇我我則予之郎還謝我以百緡錢他時有國當分其半國許諾遂將祖墓葬之客人反覆謂之曰這誠大地登了必有嘉祥但於百日之內時常往來以探倘風雷之後見有異事便是剣多古少一可急殺塞之葬纔三日忽夜聞巨雷振起一聲所在地方人畜皆驚而次日視之見蜀會西衙太堂三社有石突出人稱貓耳</t>
+          <t>地下修文知有命豐才普壽奈天何</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Quả nhiên vừa mới táng được 3 ngày, thì đêm hôm ấy sấm sét nỗi dậy ầm ầm, nhân dân quanh vùng thấy đều nào động, sáng sớm hôm sau, người ta thấy đã ở dưới đất trời lên, trong như thứ đá tai mèo, nhan nhãn khắp vùng 3 xã Đăng-Xá, Tây-Vệ, Thái-Đường, tất cả hồ ao vườn được chỗ nào cũng có. Ngày nay dấu tích vẫn còn. Về phần Nguyễn-Cổ thấy có sự lạ như vậy, biết rằng ngôi mộ đã kết mùng rỗ vò cùng. Nhưng vợ anh thì lại nghĩ khác, nên chị bảo khẽ anh rằng: Ngôi mộ nhà ta đã được phát phục, nhưng mà hiện nay chạy đầu cho ra 100 quan tiền lễ tạ, và lại sau này còn phải chia đôi thiên hạ, thử hỏi phần mình còn được bao nhiêu.</t>
+          <t>Này chức tu văn nọ địa hạ, Ông xanh bớt thọ bồi thêm lại.</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>石園池在在有之時同自知得地喜不自勝其要謂之曰此地雖然然發福但今損百緡錢如何可得又來日半分天下其所得者幾何因以是無意還謝禮錢客人問之固約以某日具還至日客抵其家固即捉來縷定乘夜救之江中惶遠而歸不意這處乃浮沙水漲自他將投下忽然潮水漸涸圖在沙上適陳氏魚舟過聞有人喚聲急來救之上船觧去其縫換以新衣間故客人具道由來因謝曰感君子角生之恩當以此地相報陳氏謂這地他已葬了若將之何客人曰某已先葬此地必為公有陳氏遂畱之舟中不露人聲跡客人即教以多采調器鑄為霹靂斧形及蘇木樑煮湯待有授用處忽是夜雷雨交作數然有雷轂手之聲，</t>
+          <t>狀元綬帶記</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Cố nghe vợ nói như vậy, nghĩ cũng tiếc của, anh bèn tính ngày đến việc bội sư, nên khi thấy địa đến hỏi lễ tạ, anh hẹn đúng ngày nào đó mới thấy quá bộ lại chơi, vợ chồng tôi sẽ xin giao đủ số. Thế rồi đúng hôm ước hẹn, thấy địa yên trí đến nơi, chẳng ngờ khi bước vào đến nhà trong, anh liền nhét giè vào mồm, trói gò ngay lại, rồi đến đêm khuya anh vác ra quảng xưởng giữa dòng sông cái, thì hành xong thủ đoạn anh lại đứng đình ra về, tưởng rằng không ai hay biết. Chẳng ngờ chỗ anh quảng thấy địa-lý phía dưới lại có con bơn (bãi cát), vì lúc thủy trào tràn ngập, nên không thấy rõ, nhưng rồi sau lúc anh quay về nhà thì nước thủy trào cũng rút. Thành ra chú thấy địa ấy lại nằm lò kho ở trên bãi cát, chứ vẫn không bị chết chim. May mắn hơn nữa là ngày lúc ấy lại có chiếc thuyền ngư phủ họ Trần đi qua, thoáng nghe thấy tiếng cầu cứu, vội vàng chèo đến, ôm xuống dưới thuyền, cởi trói cho chú, rồi hỏi duyên cớ tại sao?</t>
+          <t>HUYNH DƯ ĐỆ THI LÊ TRANG-NGUYÊN</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>震師將雲辟雲蓋，</t>
+          <t>敬賀眾唐安幕澤人也少助于紫鮮元時二十七歲同邑尚書狄瓊以女妻之出贅復終日間居不以書籍意瑤文怪之以問於公之艾曰素問言吾瑤力學邇來無事不曾見讀書父曰兒自過貴庭相公每食之如何瓊曰儒家清淡所食者其肱幾何父曰老子異夫人的食而公以尋常視之安巧有不滿處璣間言食每飯必加飯倍之</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Chú bèn kề hết đầu đuôi câu truyện cho ngư-phủ nghe, rồi sau ngỏ lời cảm tạ: rằng tôi được ông cứu thoát, thực là ân đức tái sinh, vậy nay xin đem ngôi đất quý đó để bảo đáp lại v.v. Trần-Công hỏi: nhưng ngôi huyết ấy thầy đã đề cho người khác, biết làm thế nào? Chú thầy địa đáp: Tôi đã cân nhắc kỹ-lưỡng, biết rằng ngôi đất quý ấy, trời đã đề dành cho họ nhà ông, vậy nên tôi đã có cách xử trí. Trần-Công thấy nói vậy bèn lưu thấy địa ở ngay trong thuyền để cho khỏi lộ câu truyện, rồi chú bảo ông đi mua đồng đỏ về dúc một số lưỡi búa tâm sét, và mua Tô-mộc nấu nước để sẵn (nước vàng) đợi khi cần dùng.</t>
+          <t>Tràng-Nguyên Lê-Nại. (có chỗ viết là Đinh) Ông Nại Người làng Mộ-Trạch lúc nhỏ rất chăm học, năm đỗ giải nguyên mới 27 tuổi, được quan Thượng Võ-Quỳnh là người cùng làng gà con gái cho, khi ở gùi rẽ ông chỉ thơ thân tới ngày không để ý gì đến sách vở. Cụ Thượng lấy làm là hỏi phụ thân ông rằng: Tôi thường nghe nói Cậu ấy chăm học, thế mà từ khi sang bên nhà tôi thì Cậu không hề nhìn đến sách vở là có làm sao? Thân phụ ông hỏi lại: Thưa Ngài vậy từ khi cháu sang ở bên quí phụ thì sự ẩm thực thế nào? Cụ Thượng đáp: Theo lời thanh đạm của nhà nho, thì mỗi bữa ăn cũng chẳng mấy tí! Phụ thân ông đáp: Sức ăn của cháu khác với người thường, thế mà Tương-Công cho ăn ít ỏi như vậy, hoặc giả châu không vừa lòng đó chăng? Cụ Thượng Quỳnh thấy ông dâu gia nói vậy bên bảo người nhà cứ mỗi bữa ăn của Cậu sẽ tăng gấp đôi,</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>斧穿重於墓上，</t>
+          <t>自是公始開卷讀一二篇尋加三歲謁飯公漸讀章三鼓又加以四歲錫公郎讀至四鼓還曰吾謂誠能過人矣更加以五歲錫為度誠觀知何是後讀書終夜不絕微常有賛云</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Rồi ngay đêm ấy trời bỗng nổi cơn mưa gió.</t>
+          <t>từ đấy Cậu mới cảm sách đọc vài lượt, tăng đến nỗi ba (3) thì Cậu học đến trống tư (4)! bấy giờ Cụ Thượng mới biết con rể của mình ăn khỏe quá xá! rồi sau mỗi bữa ăn cứ lấy nỗi 5 làm mục để thử xem sao? quả nhiên Cậu học suốt đêm không hề nhắm mắt! và thường tán tụng mình rằng:</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>面透至棺，隨以蘇木水灌下明日固往探見之以為雷打墓中流血因惧而殺去客人遂將陳家祖墓就塟焉</t>
+          <t>曾來潭先生以食為名十八肆飯十二餌羹魅荒次第各冠群英富之也鉅談之也宏</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Sấm sét đánh xuống âm âm, mãi đến gần sáng trời tạnh thì chú thầy địa và ông ngư-phủ họ Trần vội vàng đem các thứ ra chỗ ngôi mộ Tồ nhà Nguyễn-Cổ, cắm lưỡi tâm sét xuống chạm đến quan tài rồi đổ nước lên trên. Sáng hôm sau Nguyễn-Cổ cũng ra thăm mộ, nhìn thấy những lưỡi tâm sét còn cắm chơm chơm, và thấy nước đỏ như máu đường ở dưới mộ trào lên, anh nghĩ là bị trời đánh, nên ngay hôm ấy anh phải đào lên để đem tàng ở chỗ khác, rồi ông thầy địa bèn đem mộ Tồ họ Trần tàng vào, mà chẳng ai biết gì cả.</t>
+          <t>Mộ-Trạch Tiên-Sinh, ăn khỏe nỗi danh! mười tám bát cơm! mười hai bát canh! Khởi nguyên chiếm bảng, trên cả quân anh! bởi nhiều sức tích, nên phát tung hoành!</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>。這句前望三陵大江在美樣縣有備社格曰新巡礦後拖伏象樓壹旌劍羅劉左右穴在土腹藏金坐乾向巽事襄客人有課云彩岱黑當堤照煙花對面坐必以顏色得天下陳氏曰果如其言當分民祿之半客人得奈景須如此但君家世世享國則我家世世給足衣糧可也</t>
+          <t>端變年間乙丑科會試四六中第二義經賦文策並第一廷試文中狀元往至戶部左侍郎</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Xét ra cục đất quỉ này, trước mặt trong ra ngã ba sông cái, thuộc xã Hữu-Bi tục gọi là của Tuần-Vàng hay Tuần-Vương, phía sau gối vào voi phục, lầu dài, cờ kiếm la liệt hai bên, huyết điểm vào chỗ Thổ-phúc Tăng-Kim tim đất giấu vàng, ngời phương can trống chư Tốn, công việc xong rồi chủ thấy địa có đoàn trước mấy câu rằng: phần đại yến hoa đối diện sinh, tất dĩ nhan sắc đặc thiên hạ, nghĩa là: Son phần yến hoa bày trước mặt, hẳn vi sắc đẹp lấy giang son.</t>
+          <t>Thế rồi đến khoa ất Sứu (1504) niên hiệu Đoan-Khánh Triều Lệ Uy-Mục-Đế ông vào thi hội, về văn Tự lục ông dùng thứ nhi, còn kinh nghĩa, phủ sách, thì đều. thứ nhất, khi vào thì Đinh liên đồ Trạng-Nguyễn, lúc ra làm quan dàn dàn đến chức Tả-thị-Lang bộ Hộ,</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>陳氏謹當書目伸各有書交為質部說客人心多機智又密寫識一道雷與彼子孫藏之嘯以異事特他如禮不替者便以冥告倘者背約即如此因與陳語曰某恐遺下二法有漆長遠來時便可造之陳氏不勝感謝至二世陳賜守度曰陳家皇族乎</t>
+          <t>其子光貞有詩云、</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Trần-Công thấy thấy địa đoàn trước như vậy liền nói với thầy: Nếu dùng như lời sau này xin chia đôi phần lợi lộc! Thầy đáp: chẳng cần phải thế, hễ mà sau này nhà ông lấy được quốc gia, thì con cháu tôi đời đời cấp cho dữ com áo, thế cũng được rồi. Trần-Công xin vàng, rồi hai bên cùng lập khoản ước để lưu chiếu. Nguyên chú thầy địa đây vốn người da mưu và rất kin đáo;</t>
+          <t>con là Quang-Bôn có thơ vịnh rằng:</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4198,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>陳家赤族乎後遂禪位、</t>
+          <t>局度寬洪操履純天才定賦晚逢長</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>sau khi viết xong, chú còn viết ra 2 đạo sấm thư, trao cho con cháu cắt kỹ một chỗ, và bảo chúng rằng: vì thử sau này Trần gia xử sự trung hậu, thì nên bảo thực với họ, nhược bằng họ định bội ước, thì nên như thế như thế. rồi trước khi ra về chú lại nói với Trần-Công: Mở còn quên mất một phép có thể giữ nước lâu dài, nhưng để sau này mở sẽ chỉ bảo, Trần-Công lấy làm hân hạnh, sắm sửa lễ tạ để tiến chân chú khách về Tàu. Nhắc lại họ Trần kể từ khi tàng ngôi mộ đó cho mãi đến đời thứ 3 tức là Trần-Thừa, vào năm Duyên-Phúc thứ 8 đời nhà Lý (1218) — (có lẽ năm Kiến-Gia mới dùng) thì mới dàn sinh ra Trần-Cảnh tức là người có tướng mũi rộng mắt phương, được Lý-Chiều-Hoàng nhượng ngơi, hiệu là Thái-Tông. Bấy giờ con cháu thấy địa mới từ bên Tàu tim sang, lần nào cũng được tiền tông rất hậu.</t>
+          <t>Rộng rãi còn thêm tính nét thuần. Thiên tài muốn phát chắc mười phân.</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>逮季世後禮日寢哀客人即進言臣先祖遺一譜囑以某年遂就黃國陳朝取讖者之見內言太堂發跡舊墳今將不旺當疏通水道遂信其言照識內書圖鑒自富初社大江而八紫囘至太堂蓋陳家享福該有此數是亦出於天命豈人力所能及或按陳家祖墓提生天下後生仁宗火時清秀面字號金仙童子明宗清秀非允時人稱為神仙人中蓋亦土地之壇客言信不誣矣</t>
+          <t>曾將各望魁天下又把詩書還萬民</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Nhưng rồi về sau họ Trần đối đãi có phần bạc bẽo, thì con cháu thấy địa mới hiển kể rằng: Ông Tồ của thân ngày xưa có đề lại một tờ sấm, hẹn rằng năm nay thì đưa sang trình, Trần vương cảm lấy tờ sấm coi qua, thấy có những câu Ngôi mộ ở Thái-Đường là nơi phát tích, nhưng từ năm nay trở đi thì không được vương, cần phải khai thông thủy đạo thì mới giữ được lâu dài, vì quá tin ở thấy địa, nhà vua liền sai bá quan chiếu theo họa đồ trong tờ sấm đó, để đào ngay một con sông từ cửa sông cái thuộc xã Phú-Xuân kéo quanh về xã Đại-Đường (hiện nay vẫn còn di tích), chẳng ngờ vì thế mà đứt long-mạch, khiến cho nhà Trần suy yếu để Xích-Chủy-Hầu tức Hỗ-Quý-Ly ăn cướp mất ngôi. Nhưng xét cho kỹ thì nhà Trần hưởng phúc chỉ được đến đây, cũng là do ở mạng trời, chứ như nhân lực thì làm sao nổi?</t>
+          <t>Đã đem danh vọng trùm thiên hạ. Còn lấy thì thư hóa vạn dân.</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>詠橋祖墓記東崖誄橋京北阮族之祖號福過平生樂善音築木千豐盈縣東蕃社以釀酒為業傍有菩提樹為風所拔因買供新爨適極至樹根見下有銀穴約三婁許即收囘晉貯之已而撤廬去經二年餘時有北客來取銀見雀跡不存只畫空穴即聞諸旁人知這銀已為公所得遂尋至家出雀識一道示之曰某為先人遺貨跋涉而來不想天已賜公今早覓歸程所望出資路費受賜不淺而公得銀藏之不知多少至是取識者之因熙熙銀數與記不差即疑得其人謂曰聊這銀繫我取的原來收時如故不曾取用既是公家原物當盡以付還</t>
+          <t>陰德足徵來世及危科繼擢一門春</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>VINH-KIỀU TÒ MỘ KÝ Ngàn Khách tâm địa báo hảo tâm nhân. Chú Tàu lấy lại được bạc, tìm nơi cát địa đáp lại on sâu. Thượng-thư(thời Mạc) Nguyễn-văn-Huy xã Vinh-Kiều thuộc huyện Đông-Ngàn, Cự tổ hiệu là Phước-Mại, trong lúc ngày thường hay làm điều thiện. Cự có dựng nhà tại xã Đông-Lâu thuộc huyện An-Phong làm nghề nấu rượu, ở bên nhà có cây Bồ-đề cỏ thụ, một hôm bị bão đánh dở, Cự mua để làm cui thời, khi đào dưới gốc cây bông thấy có 3 hũ bạc, Cự bèn lẳng lặng đem về đấu kín không cho ai biết, rồi cách ít lâu Cự lại giỡ nhà thiên đi chỗ khác. Chẳng ngờ ba bốn năm sau bông có một chú ở bên Tàu sang tìm đến địa điểm chôn bạc của Tồ-tiên xưa, thì thấy đấu cũ còn đó;</t>
+          <t>Cây đực tốt tươi đời hai quả. Bằng vàng nối đời của đầy xuân!</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>其人謂曰那物雖我家先遺一下今既為公所得是公家物倘蒙惠顧只願費路錢足矣</t>
+          <t>永垂者一無窮慶漢義於公宋當見</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>lỡ chôn còn đây; mà những hũ bạc đều biến đâu mất? Chú bên lân la hỏi đó những nhà bên cạnh, người ta mới đoán rằng ông nấu rượu năm trước đã lấy đi rồi.</t>
+          <t>Cho hay phúc trạch bao giờ can? Hán vi Vu-Công, Tống Đậu-Quân.</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4266,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>若更以相還豈敢如命公固執不可客人曰公既有是心願頒其半公曰我不穀人情之所欲第這銀非我之財天使我為公守耳故為此以待勿復牢辭客人恐遠其意輒頒銀歸國後嘗以其事對北人言時有風水師者聞之曰難如此人好心我今老矣</t>
+          <t>嗣公第大調以袖童稱少年激發之氣公奇抑之</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Chú bên đến thẳng nhà ông xuất trình gia phả cùng các giấy tờ, rồi mới nói để ông biết: Tồ-tiên chúng tôi ngày trước có chôn bạc ở đây, ngày nay chúng tôi sang lấy chẳng ngò bạc đó đã về tay ông. Chúng tôi không giám ươn thân chi cả, duy có một điều xin ông nghĩ lại, bởi vì nay mai chúng tôi cũng phải thu xếp trở lại cổ hương, mà túi tiền lương đã cạn, mong ông sẽ phát hàng tâm giúp cho ít chút để làm lộ phi, chúng tôi chẳng giám quên ơn. Nhắc lại ông Cụ từ khi đào được hổ bạc cho tôi ngày nay, ông vẫn dẫu kín một nơi chưa hề dùng tới, nên cũng chẳng rõ nhiều ít thế nào, nay được xem bản gia-phả Cụ mới đem ra kiểm lại, thấy đúng con số đã ghi. Cụ bèn giữ Chú ở lại cơn rượu thết dài ăn càn, rồi mới bảo thực cho các Chú biết: rằng số bạc kia quá nhiên tôi đã đào được, nhưng vẫn dẫu kín chưa hề tiêu mất ít nào, ngày nay các chú sang đây tức là chú nhân của nó, thì tôi xin tra trả hết chứ có để lại làm chi. Chú Khách nghe Cụ nói vậy, trong dạ đã thấy mờ cờ, nhưng vì chẳng dám nhận ngay nên cũng kiếm câu từ chối: Thưa Cụ mấy hũ bạc đây dẫu là bạc của Tiên Tỏ chúng tôi để lại, nhưng nay giới đã cho Cụ, tức là của Cụ, nếu Cụ ban cho ít chút để làm lộ phi, chúng tôi cũng đã hàn hạnh lắm rồi, chứ đâu lại giám nhận cả như vậy. Chú khách nói thế nhưng Cụ nhất định không nghe, về sau xin chia ra làm 2 phần Cụ cũng không thuận, bảo thực cho các Chú biết: Tôi đây hà phải con người không quí tiền bạc, chỉ vì bạc đó không phải của mình, chẳng qua giới sai giữ lại để đợi các ông đó thôi, vậy thì các ông cứ việc nhận lấy đủ số đem về thì hon.</t>
+          <t>Nguyễn ông còn có một người em giai tên gọi là Tài Thần, lúc nhỏ nỗi tiếng thân đồng! nên hay có tánh tự phụ ông phải tìm cách để nên bớt đi!</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>尚尚火時郎當往安南擇吉地以報其人懇之師曰我有二門弟一可遣遂與之偕往北客至詠橋社探問則念已於前年捐館矣</t>
+          <t>乙丑科八第一場有錯誤處以問子公公答之曰今番與正第試若以相告更將誰誘郎鼎怒曰今科讓兄光簽討撤籠而出郎日歸本鄉乘夜而行致家時以三鼓不敵呵門因憇卧于軒之檐處</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Chú khách biết chúng không thể nài ép được nữa, nên phải nhận lấy số bạc đem đi, sau khi về tới nước nhà, gặp ai Chú cũng kể lại câu chuyện ông Già nước Nam có lòng nhơn đức như vậy.</t>
+          <t>Vi thế nên khoa ất sử, anh em cùng vào ứng thí, giữa kỳ đệ nhất, ông Tài quên sách đến hồi thì ông bảo rằng: chuyện này tôi thi với chú, nếu lại bảo chú thì còn thì cử với ai? Ông Tài tức giận đáp: Thôi thì khoa này tôi để cho anh chiếm giải trước vậy nói xong giỡ phẳng lều chống ra về, đi thẳng một mạch đến trông canh ba thì về tới nhà, nhưng lại không giám gọi cửa, dành nằm ngủ ở ngoài hiên.</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>郎辨一購禮致祭而去二月餘復至謂公之子曰我感受先人之德無以相報今帶得地師來來尋告地以謝有一處群山供伏可做一代帝王又一處緒軸花畫可做一代駙馬於二者何擇其子曰我家村鄙野人何慼望比所望者世出文儒之地不慼二地師曰苟如此在貴邑內何事遠求按地自錦章社來龍屈勢如蛇形至詠橋社八首突起二小阜一阜稍大平坦一阜差小勢頗微科一地師認穴在大阜十次一地師不可即就前面澤澤處浸卧水中貼仰良久方起日我已驗之果然方在小阜二師爭辨不決因畫成一圖使人北還就諸老師取正老師曰這曷是黃鶴咱蛤其氣在耳</t>
+          <t>是夜其母愛袖人謂軒前有黃甲在何不開門接入俄醒覧覧私自怵曰今日八會試場二子皆京城應舉部有何黨甲在我家軒誠尚親焉見壚外有人熹睡喚而起之乃晨才鼎其母愕然問故才鼎以實對母曰曾學未到勸再加功才得郎點燈索書觀之母笑而言曰覆落第歸斯爾愼激只恐此志難持鼎曰自今而後母觀如何自是日夜攻書手不釋卷</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Lúc ấy có một ông thầy địa lý chánh tông nghe xong câu chuyện cũng khen là người hiềm có, tiếc rằng tôi nay đã già, vì thử đường lúc thiếu trang, thì tôi quyết sang bên ấy tìm họ một ngôi huyệt kết để bảo on sau. Chú khách nghe ông Thầy Địa nói thế, khẩn khoản mời ông sang ngay, vì ông yêu quá không giám đi xa, nhưng ông cho biết: Tôi có hai anh đồ đệ cũng đã học được bí truyền, au là tôi cho cùng đi với bác một thề. Thế rồi 3 người cùng sang An-Nam tìm đến nhà Cụ bán ruộng, thì Cụ đã mất được hơn một năm, các Chú biện lễ phúng viếng xong rồi cáo từ ra đi, không biết đi đâu mà hai tháng sau thấy quay trở lại, bảo với con giai Cụ rằng: Chúng tôi đã chịu ơn Cụ ngày trước rất nhiều mà không có cách gì để báo đáp lại, vậy nay có mời được hai thầy Địa-lý cùng sang, hiện đã tìm được mấy chỗ cát địa, ngôi thứ nhất có một dãy núi châu về, sau phát Đế Vương nhưng chỉ một đôi là hết; còn ngôi thứ hai ở đóa hoa sen cũng phát 1 đôi Phò-mã, vậy Cậu muốn chấm ngôi nào?</t>
+          <t>Giữa lúc ấy thân mẫu ngủ trong nhà mờ thấy thân nhân đến báo: Ngoài hiên có Ông Hoàng-giáp, sao không mở cửa đón vào. Bà cụ sức tình nghĩ rằng: Ngày nay đương kỳ thi Hội, hai con của mình đều ở trong kinh, thử hội còn Hoàng-giáp nào ngủ ở ngoài hiên. Nghĩ thế rồi bà mở cửa ra coi, bỗng thấy một người dương nằm ngủ lăn ra đó. Bà đánh thức đây thì lại chính là cậu Tài, làm bà hết sức ngạc nhiên! Cậu bèn kể lại câu chuyện như thế. Nghe xong bà mới báo rằng: Đó là tại con học chưa đến nơi đến chốn, vậy thì từ nay con phải gắng công v. v. Cậu nghe lời mẹ dạy bảo với theo vào ngay trong nhà, đốt đèn mở sách ra đọc. Bà cụ thấy vậy mỉm cười bảo rằng: vừa mới thì hồng cho nên phần khích nhất thôi, chỉ sợ không giữ mãi được như thế đó thôi Ông đáp: Thưa mẹ, từ này về sau rồi mẹ sẽ thấy, thế rồi từ đây ông học suốt cả ngày đêm, tay không hề rời quyển sách.</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>兩阜間兩耳也大耳是等小耳是微科有氣旁必在杳其子即依言移公藝之坐恩向坤至三世文徽以明德翼登庸乙丑科中探花官至尚書致仕其三子伸調以永定奠福原丁未科中黃甲官亦至尚書日達善以光寶員乙未科中黃甲仕以淳福年考乙丑科中進士至侍郎其孫教方</t>
+          <t>是科兄鶴中狀元帝以爲監司月講官作成人才鼎尋赴京邀訓學從謂曰經営司是我的有如問其書首從毛聽講來學者素聞其各試往觀才學知何至鄕市處士人特書來問才兼隨問答之滔滔不絕至有以外書諸子問之亦淡練應答人皆發為服爭來觀咱而盟胃為之一空</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Cậu con đáp: Chúng tôi là gia đình ở nơi thôn giã, chẳng giám hy vọng cao xa, chỉ muốn được một người nào kể thế văn nho là đủ. Hai thầy Địa đáp: nếu vậy thời có khó gi, chẳng phải tìm đâu cho mệt. Tôi thấy ở Thôn nhà đây cũng có một người, long mạch tự xã Cẩm-Chương kéo đến, nó đi ướn khúc như kiểu hoàng xà, đến xã Vĩnh-Kiều thì ngóc đầu dầy, đột khởi lên 2 cái gò, gò lớn bằng phẳng, gò nhỏ thì hơi cong cong. Theo ý thầy cả thì huyết kết ở gò lớn, nhưng mà thầy hai không tin, ra cái dẫm sâu phía trước, lăn xuống dưới đây để xét khí mạch rồi quyết đoán là huyết ở gò nhỏ. Hai thầy không ai chịu thua ai, về sau phải họa kiểu đất sai người đem về Bắc quốc hỏi lại Sư-phụ. Sư-phụ coi xét bản đồ, bảo nó là kiểu Hoàng Xà thính - cáp nghĩa là con Hoàng xà lăng tiếng con ngô, lúc lăng thì tinh thần nó chú trọng cả ở lỗ tai, như vậy thì huyết kết ở tai, mà hai gò đất tức là hai tai, duy cái gò lớn bằng phẳng tức là cái tai bị điếc, còn cái gò nhỏ hơi cong, thì có tự khí, tức là tai lành, thế nào huyết cũng kết ở gò nhỏ.</t>
+          <t>Còn phần ông Nại lúc ấy đã đồ Trạng-Nguyên vua cho giữ chức Giảng-quan trong Quốc-tử-Giám, biết bao sĩ tử được ông tác thành, rồi ngay khi đó ông Tài cũng ra kinh đó, đón đường bảo các sĩ tử rằng: Ta đây tức là bồ chư? các anh muốn hỏi chư gi? hãy cứ đem sách lại đây rồi ta sẽ bảo? Về phần sĩ tử trước kia vẫn thường nghe tiếng, ngày nay cũng muốn xem tài học ra sao? nên họ rủ nhau đến chỗ chợ Dừa thị để hỏi nghĩa sách, hỏi đâu đáp đây, thao thao bất tuyệt! Có người đem cả ngoại thư và sách chư từ ra hỏi, ông cũng giảng giải rất là tinh tường! Khiến cho mọi người đều phải khấp phục, rồi sau kéo đến cảng đông thành ra trường Giám vãng teo.</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>是微科有氣旁必在杳其子即依言移公藝之坐恩向坤至三世文徽以明德翼登庸乙丑科中探花官至尚書致仕其三子伸調以永定奠福原丁未科中黃甲官亦至尚書日達善以光寶員乙未科中黃甲仕以淳福年考乙丑科中進士至侍郎其孫教方之文知江漢之水愈出愈奇四代孫福胡王以陽德繼中興嘉慶末科中會元再中東閣仕至都臺公坦德敦國益相鄰緒北省其苗裔商今旋中相傳諸預登紳甲者面必微科蓋地氣之所鍾也</t>
+          <t>兄鼐即歎諧之曰吾弟之才何直受於高選不宜如此孟浪邀學者義嚴談使譽席欲講這是關風教焉。</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hai người đồ đệ sau khi nhận được tin của Sư-phụ lập tức bảo con ông Cụ đem đi hai cha táng ở gò nhỏ, ngồi ở chữ Cẩn trong ra chữ Khôn, rồi sau đến đời thứ 3 là ông Văn-Huy thì đổ Thám-hoa tại năm kỷ-hội trong thời nhà Mạc, làm quan đến chức Thượng-thư rồi mới trí sĩ, người con thứ ba tên là Trọng-Quỳnh thì đổ Hoàng-giáp trong năm định vị tức là niên hiệu Vĩnh-định của Mạc-phuc-Nguyên Mễ Phúc Nguyên, về sau cũng làm đến chức Thượng-thư, còn ông Đạt-Thiện tiến sĩ mới 18 tuổi cũng đỗ Hoàng-Giáp khoa kỳ-vị năm Quang-Bửu nhà Mạc, về sau cũng làm đến chức Đô-khoa và ông Hiền-Tích cũng đỗ Tấn-sĩ khoa ất-sửu, niên hiệu Thuần-phước thời Lê-trung-Hung, sau làm đến chức Thị-lạng.</t>
+          <t>Ông Nại thấy vậy phải can em rằng: Cứ như tài học của chú lo gì chẳng đồ cao? mà đi làm việc vô ích, đón học giả về bàn suông để cho trường Giám không ai đến học. Tôi thấy việc này có quan hệ đến nên giáo hóa, vậy khuyên chú nên định chỉ thi hơn.</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>卻說頭乃文微次子火領鄉舉惟善飲酒懶廢學業見海陽處隨號嘗往珥河竹木津邊明儔對飲通就河津濯行見竹筏上有紱字在焉拾而觀之乃是舊賦一箇因記之燕燭每飲酒後輒叩盤歌詠習以為常乙丑科八第一場得親朋友之助頸在中第至第二場携酒而入坐間醉酒睡著日已向暮忽大風驟至塵霧漫天續睡中驚為起輩目觀之見有數片紙字飛到其前收來紬認乃是四六體文續喜曰此天賜吾也</t>
+          <t>才眾郎輿歸至洪順三年，穆襄翼帝年號，辛未科果中黃甲嘗以不得大科為根仕經免部給事中短光責有詩云</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Nguyễn-danh-Nho đỗ Tấn-sĩ khoa canh-tuất, làm đến Đô-khoa. Trên đây là kẻ hàng con, còn hàng cháu thì có Giáo-phương cũng đỗ Hội-nguyên khoa bình-tuất niên-hiệu Đoan-Thái thời Mạc-mậu-Hiệp (1586) lúc vào thì dinh lại đỗ Thâm-hoa, trong bài đối sách được Vua khen ngợi phê rằng: Văn của Giáo-phương như nước sông Giang, sông Hán! càng viết càng lẫm thử lạ. Truyền đến hàng cháu bốn đời thì có Đức-Vọng thì đỗ Hội-nguyên khoa quí-sửu, sau lại trúng luôn Đông-các, làm quan đến chức Đô-dài. (Vào thời Lê Dương-Đức 1635-43) còn như Công-Viên, Đức-Đôn, Quốc-Ích cũng lại kế tiếp đăng khoa và cũng đều là dòng dõi họ ấy, ngày nay trong họ có truyền ngôn rằng: những người đỗ đạt nét mặt đều thót, hay là hơi lép một bên, là bởi mộ tổ nằm trên gò đất hơi cong, cho nên khí mạch chung đúc như vậy. Nhắc lại Hiền-Tích là con thứ của Văn-Huy, ngay lúc niên thiếu đã đỗ thi hương, chỉ vì nghiên rượu sinh ra lười biếng chẳng chịu học thêm, đến khi được sung một chức Tùy-hiệu ở xứ Hải-Dương, thời thường kéo bạn ra bãi nhà bè bên sông Nghi-hà cùng nhau chè chén, nhân có một hôm ông xuống bên tắm chợt trong thấy có một quyền vở đề ở trên bê, ông bên mở ra xem thử, thì thấy bên trong có chép một thiên phú cờ rất hay.</t>
+          <t>Ông nghe lời anh lập tức trở về. Đến khoa Tân-Vị (1140) ông đồ Nhị-giáp, lấy làm uất hận vì không chiếm giải khối nguyên, sau ra làm quan cũng chỉ đến Lại Bộ Cấp Sự-Trung rồi mất! vì thế Quang-Bôn là cháu có thơ rằng:</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>依樣寫之已而果中至第三場賦題乃前日所得舊賦者更預中第追至四場日學業文廢不能措一辭因取晉侯國語舊傳凡諸鄙俚者換以新聲每句撥成輒需乘醉吟詠采察官見之謂曰天日已晚入皆行文過半而新進士何乃尚番空卷而放浪酣歌乎</t>
+          <t>確句奇男的壯懷一門兄弟應花開</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ông rất lấy làm thích chí, ngâm đi ngâm lại thành ra thuộc lòng. Thế rồi đến khoa ất sừ ông cũng đi thi, may sao kỳ đầu gặp bạn giúp sức nên đăng trôi chảy, đến kỳ thứ hai, ông mang theo một hồ rượu, trước khi làm bài ông đã uống say tùy lý, nằm vật xướng chống đánh một giấc ngủ cho đến xế chiều. Lúc ấy giới bồng nỗi con giống tổ, sấm chớp ầm ầm.</t>
+          <t>Lỗi lạc nam nhi có đủ tài? Sao khuê ưng cả một nhà Ngài?</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>續酩酊音落頃答之日欲寫郎寫何難遂寫了這傳授納時同考院有知音者見其詞調清遠每得佳句郎援筆闋之因語諸同院曰這卷寧為我院獨私當送與亞覆考獻笑既而覆考官會者以為戲談大笑周一場聲聞于外采察官見問全院具道其事考訖即擇諸中卷者適同候旨時上以其取中頗少亟差往命增取之諸考官對諸中官曰申格之文這等卷已盡矣</t>
+          <t>青鐵萬中登高遠蘋案曾趨預密陪</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bấy giờ ông mới sực tỉnh, mở mắt nhìn quanh thấy có 4, 5 tờ giấy bay đến trước mặt, vội nhặt lấy coi, thì là một bài Tự lục (phủ) dùng với đề tài ấy, thì ông hết sức vui mừng, cảm ơn trời phật phù hộ nên mới có sự may mắn như vậy, rồi ông chép đúng nguyên văn đem nộp, thành ra kỳ ấy cũng được đồ cao. Đến kỳ thứ 3. là kỳ thi phủ, đầu đề lại trùng với bài phú cờ mà ông đã đọc thuộc lòng, nên ông lại được trùng luôn kỳ nữa.</t>
+          <t>Vẫn như tiên đúc luôn tranh giải? Chức cũng xu bồi thoát ghế vai?</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>續酩酊音落頃答之日欲寫郎寫何難遂寫了這傳授納時同考院有知音者見其詞調清遠每得佳句郎援筆闋之因語諸同院曰這卷寧為我院獨私當送與亞覆考獻笑既而覆考官會者以為戲談大笑周一場聲聞于外采察官見問全院具道其事考訖即擇諸中卷者適同候旨時上以其取中頗少亟差往命增取之諸考官對諸中官曰申格之文這等卷已盡矣</t>
+          <t>幼學壯行初得遂有才無壽盡堪哀</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Thế là do sự may mắn ông đã lọt được 3 kỳ, duy còn kỳ thứ tư (4) nữa, là kỳ khó nhất, mà ông bỏ học lâu ngày, thành ra không sao viết nổi, thế rồi nhân lúc ngồi bồn ông nhớ đến chuyện Luru-Hầu lưu, nguyên là bài phú quốc âm, ông bèn sửa lại những chữ quê kịch, sửa xong câu nào thì lại dắc ý ngâm vang cả lên, nhân viên kiểm soát thấy vậy đến hỏi: Kia quan Nghè Tân khoa, mặt giới đã xế bóng rồi, bài vô ai cũng sắp sửa viết xong, có sao Ngài còn để quyền trăng mà cứ uống rượu ngâm tràn như vậy. Ông nghe tiếng viên Giám-sát duc giả thì cũng gật gù đáp rằng: Ư muốn viết thì viết có khó chi, thế rồi ông đem quyền ra viết ngay bài phú Luru-Hâu đem nộp, rõ thực minh Sở dầu Ngọ. Nhưng mà may sao trong hàng Giám-khảo cũng có một vị cũng thích quốc âm, nhìn qua bài phú của ông nhận thấy lời lẽ tân kỳ, gặp những câu hay cảm bút khuyên lấy khuyên để, rồi lại nói với Khảo quan khác rằng: quyền này chúng ta không nên giữ riêng, tất phải để sang bên phòng phục-khảo để hiển các vị ấy một trận cười, quả nhiên các vị phục-khảo khi nhận được quyền của ông, tức khắc đỏ xô lại coi ai cũng ôm bụng cả cười, tưởng chúng đến vỡ cả đám! khiến cho các vị Giám-sát đương ở bên ngoài, tưởng rằng bên trong có chuyện cãi nhau chạy vào can thiệp, nhưng rồi sau khi rõ chuyện thì cũng không sao nên được trận cười. Thế là khoa thi ấy vào kỳ thứ tư, ông làm lạc đề nên phải bị rót, nhưng theo lệ thường, hễ chấm thi xong khảo quan phải chọn những quyền trung cách để cả về Kinh xét lại, khoa này Hoàng-Thượng thấy dở ít quá bèn hạ lệnh lấy thêm: Trung-quan mang lệnh ra trường thì, Khảo-quan cũng nói: Văn bài kỳ này kém quá, ngoài mấy chục quyền trung cách thì không còn quyền nào có thể lấy thêm được nữa, nhưng Trung-quan nhất định không nghe. Lúc ấy không biết vô tình hay hữu ý mà Khảo-quan lại giả nhồi rằng: Hiện đây chỉ còn 1 quyền Luru-Hầu mà thôi chứ chẳng còn quyền nào khá nữa.</t>
+          <t>Ngầm sự học hành khi thiếu tráng? Xem cơ thọ đoàn thực bi ai?</t>
         </is>
       </c>
     </row>
@@ -4419,12 +4419,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>其餘無足之取中官以內首見逼考官曰所存者晉侯一卷外此更無中官郎馳回具奏有首判云晉侯不取更取何人郎傳與考官批取饒而返同觀之葉已取中輒藏不匿以宣露後績仕至兵部左侍郎會我朝中興出首左遷宣光處承使魯任按自有科目以來諸預中格者必是文理可取茲以國語傳取中頗微訛傳或者是時莫朝取士無章故有此異爭亦以見其為學在人而中否之中有天數存焉</t>
+          <t>九重莫謂三光滿已送文星八夜臺</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Trung-quan thấy vậy bèn dẹ bắn tẩu về Triều, Hoàng-Thượng xem qua bản tẩu thấy có hai chữ Luru-Hầu, Ngại liền cảm bút phê ngay mấy chữ Luru-Hầu chẳng lấy thì còn lấy ai, Luru-Hầu bất thủ cánh thủ hà nhân. Phè xong Ngại bèn truyền lệnh cho Khảo-quan phải lấy quyền đó. Đến khi dẹ quyền về Kinh thì Ngại mới biết, nhưng đã cho đồ mất rồi nên cũng đánh phải bỏ qua để khỏi lộ chuyện, về sau ông Tích cũng làm đến Bình-bộ Thị-lạng gặp lúc Triều-đình trung hung ông phải dời lên Tuyên-Quang nhưng được lưu nhiệm.</t>
+          <t>Cửu trùng chớ tưởng Tam quang đủ? Đã tiến sao vẫn xống Dạ-đài!</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>近日有監生者八省試第四場文理不成卻寫國音雜技投納試場官論以無為行仍論失監生袁訢幸免是為效類準之戒為初學</t>
+          <t>狀元程國公記</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Xét thấy nước nhà từ khi có khoa mục cho đến ngày nay, những quyền đã được trưng cách văn lý cũng đều hay cả, thế mà khoa này lại thấy 1 quyền quốc ngữ! phải chẳng là chuyện bịa đặt, hay là thời đó về việc khoa cử chưa có chương trình nhất định, cho nên mới có truyền là như vậy, nhưng nó cũng tỏ cho ta thấy rằng: học văn rộng hẹp là do ở người, còn lúc thì cử đỗ đạt hay không, hoặc giả cũng có thiên số nằm trong đó vậy. Nhưng mà việc này biết đâu chả là sự thật, bởi vì sau đó cũng có một Giám-sinh trong ngày thì ở hàng Tinh, đến kỳ thứ 4 anh cũng không làm nổi bài, nên đã phải viết những câu quốc âm làm nhảm đem nộp, Quan trường cho là vô hạnh, định truật cả chức Giám-sinh, về sau van lấy thâm thiết mới được miễn nghi. Đó cũng là một tấm gương sáng cho kẻ chỉ toàn bất chước đề cầu may vậy.</t>
+          <t>BẠCH-VÂN-AM CƯ-SĨ NGUYỄN-CÔNG-VĂN-ĐẠT PHỔ-KÝ</t>
         </is>
       </c>
     </row>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>安陽中行記安陽中行有武姓者起世寒微而頗好學時有裴氏來風水師相地釋得地吉塗之亊襄其師謂曰之這曷世世公假未審我家能稱此否</t>
+          <t>公字秉謙道號自雲居士永賴中庵人也先世皆有隱德不可考其祖文靖始卜陽宅山水週环暗兮高王錮記父文英有學行亮太學生母慈淑夫人光明妾子下人戶尚部書汝文瀾相公之女世聽聲通經史善文章尤精風鑑曉術戴方洪德盛時而知四十年後炎運當微慨然有大夫夫改物之志擇對不嫁幾十年一見文定知其有貴兒相逐歸焉</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Huyện An-Dương, xã Trung-hàng có một họ Võ, nhà đầu bần hàn, nhưng tính thích làm điều thiện. Lúc ấy trong áp có một phu-gia thường đi đón thầy phong thủy về coi đất, khi tìm được đất đem tàng xong rồi đến đêm mơ thấy có một vị thần về bảo: Địa phương đây thuộc quyền của ta cai quản, vậy mi là hàng người nào, lại dám đem mộ tàng vào địa phận của ta, muốn tốt phải bốc đi ngay, bằng không thì sẽ có tai họa đó.</t>
+          <t>Ông Nguyễn-bỉnh-Khiêm đạo hiệu là Bạch-Vân cư-sĩ, người làng Trung-Am huyện Vĩnh-Lại, tiền tổ ngày xưa tu nhân tích đức đã nhiều, (nay không thể khảo cứu được) chỉ biết từ đời cụ Tổ thì được tập phong Thiếu-bảo Tư-quận-Công mĩ tự là Văn-Tính, Cụ bà được phong Chính phu-nhân Phạm-thị Trinh-Huệ, nguyên trước các cụ lập gia cư ở nơi có núi sông bao bọc, hợp với kiểu đất của Cao-Biền. Phụ-thân được tặng phong Thái-bửu Nghiêm Quận-Công, mĩ tự là Văn-Định, đạo hiệu là Cù-Xuyên Tiên-Sinh, nguyên người học rộng tài cao, lại có đức tốt, được sung chức Thái-học-sinh. Thân mẫu họ Nhữ được phong Từ-Thục phu-nhân, nguyên người ở An-Tử hạ thuộc huyện Tiên-Minh, là con gái quan Hộ-bộ Thượng-thư Nhữ-Văn-Lan. Bà vốn là người thông minh, học rộng văn hay; lại tinh cả môn tướng số, ngay thời Hồng-Đức mà Bà đã tính được rằng; vận mệnh nhà Lê chỉ sau 40 năm nữa thì sẽ suy đồi. Vì có một chí hướng phò vua giúp nước của bậc trượng phu, muốn chọn một người vừa ý mới chịu kết duyên, nên đã chờ đợi đến ngót 20 năm trời, khi gặp Cù-Xuyên Tiên-sinh biết là có tướng sinh quý tử mới chịu lấy.</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>既而受神人罵日本地係我管了汝何人來塗我地不穢必有災殃其人特疑不決未幾幾舉家病作族中不寧復變神人謂曰汝福淺不堪此命我晉後待武強汝當讓與他則汝子孫亦當享他之報其人如言即邀武氏告之曰我有吉地一穴今許與汝來日汝家發福當無忘我子孫</t>
+          <t>後遇一少年過雪江寒度頭愕然嘆曰火時何不相遇今日到此何為從者比而顓之夫人徐詢姓名知是登庸恨悔者絞日</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Nhưng mà phu ông sau khi tỉnh giấc thì lại du dự không muốn bốc đi, chẳng ngờ từ đấy người nhà bị ốm la liệt, và cả trong họ cũng mất an ninh, bấy giờ ông lại mơ thấy thần nhân về bảo: Nhà mi phước bạc không xứng đáng với ngôi đất quí ấy đâu. Vả lại ngôi ấy ta đã đề dành cho nhà họ Võ, vậy người nên nhường cho y, rồi sau con cháu nhà người cũng được y bảo đáp lại, chẳng cũng tốt hơn hay sao. Về phần phu ông khi thấy thần nhân bảo mộng đến lượt thứ hai, bấy giờ ông mới quyết định theo đúng như lời trong mộng, cho mọi họ Võ đến nhà bảo cho biết là: Tôi có tìm được một ngôi đất quí, nay muốn nhường cho quí ông, ví thử sau này kết phát thì nên nhớ đến con cháu nhà tôi, ông nghĩ thế nào?</t>
+          <t>Sau bà gặp một thiếu niên đi qua bến đò Hàn bên sông Tuyết-giang, bà kinh ngạc than rằng: «Sao lúc trước không gặp, nay tới đây làm chi?» Người nhà nghe lén hỏi tên họ, mới biết đó là Mạc-Đăng-Dung, bà lấy làm tiếc nuối.</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>武氏許諸郎將先人塟之其後武家興旺多產才藝健武的人中興問滅莫有向道功榮封功臣至今世襲典兵爵禄未次誘言安陽中行金誠璽淡蓋言世臣之多也</t>
+          <t>公以洪德二十一年幸亥生身體長大容貌英偉未周歲能言一日昧爽文定抱諸卷忽語曰日出東方考大驚異</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ho Võ thấy phu ông có tâm lòng tốt như vậy, nên cũng cảm tạ và nhận lời ngay, rồi đem phần mộ tiên nhân táng vào huyệt đó, quả nhiên từ đây về sau gia-dinh mỗi ngày một thêm thịnh vượng, trong họ sản xuất được lắm nhân tài, nhất là võ nghệ, lại có nhiều tay tri đồng hơn đời, trong thời trung-hung có công hướng đạo để diệt họ Mạc, nhiều người đã được phong trước công thần, con cháu cũng được kế thế nắm giữ bình quyền, đến nay vẫn còn thịnh vượng, vì thế ngạn ngữ có câu: An-Dương nhất xã trung-hàng, Kim-Thành nhất làng Quỳnh-Khê nghĩa là nói về những xã trâm anh kế thế vậy.</t>
+          <t>Ông sinh năm Tân-Hợi niên hiệu Hồng-Đức thứ 22, thân hình cao lớn dung mạo khôi ngô, chưa đầy tuổi đã biết nói. Một hôm sáng sớm, thân phụ bế ông, bỗng ông cất tiếng: «Nhật xuất đông phương». Thân phụ rất kinh ngạc.</t>
         </is>
       </c>
     </row>
@@ -4504,12 +4504,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>陽宅、紫泥鄧庭記安山縣北荒地之西有石嶺千餘峯盤桓一里許清奇可愛中有石洞舊傳有仕社人鄒庚家貧為人傭借適在田間校未有相客經過二言我有吉地一處如有何人請者我即與之度聞其言去禾而上前来拜請因邀北寒同只辨得一黍小鶴為禮前致辭曰僕候遇明師自知有福但家貧冷淡愧怍殊深倘吾師惠以福地幸來時發誓不忘恩拒人見其誠心即引在山傍蟾蜍又一指之曰此地最好當作陽宅居之必然大發富貴但得近君後急撤去之切不可要庚依言即構茅屋數間居之纔及三年</t>
+          <t>年四歲夫人誦以經傳王義即能誦新口頭又暗讀諸國詩數十首</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Huyệt tại thiềm thử ảnh, bạc nghệ nhân đắc nhập vương cung ĐỀ MÀ VÀO BÓNG THIỀM THỨ (CON CÓC), KẺ NGHỀ MỘN ĐƯỢC VÀO CUNG VUA Huyện An-Sơn địa phận xã Tứ-Trâm, có dãy núi đá cộng hơn mười ngọn quanh co hơn một dặm trường, trong rất thanh tú, bên trong có một cái động, dưới có ngôi chùa, Tiên thánh vương xây sẵn cung điện ở đó để ra ngoạn cảnh luôn luôn, nên mỗi đời tên là xã Long-Châu. Xét thấy phía đông dãy núi có một ngọn nhỏ nhỏ lên trong giống hết như con Thiềm-thứ. Tục truyền rằng xã ấy có người tên là Đặng-Canh nhà nghèo phải đi làm mướn, một hôm anh đương nhỏ mà ở trong dãy núi, bỗng thấy có một người Tàu đi qua bảo với anh rằng: Ta đây mới tìm được ngôi đất quí, nếu ai muốn xin- thì ta cũng cho. Canh nghe thấy Tàu nói thế liền bỏ mà dấy chạy lên quy xuống trước mặt xin thấy làm ơn, rồi dồn thấy về nhà, đi xoay vát mãi mới biện được có một niêu cơm nếp để làm dò lẻ, rồi anh thú thực với thấy địa rằng: Tôi nay được gặp mình sư tử biết rằng nhà có đại hồng phúc, chỉ vì gia cảnh nghèo nàn lấy làm vô cùng hổ thẹn. Nếu thấy ra ơn giúp cho ngời huyệt quí ấy, sau này có được phát đạt, xin thề chẳng dám quên ơn. Chủ thầy địa nghe xong nhận thấy anh quả có tấm lòng thành, lập tức dẫm anh ra chỗ chân núi thiêm thử, chỉ vào núi đó bảo đây là cục đất quí lắm, nhưng nó thuộc về dương-trạch, vậy anh nên làm nhà đề ở, tất nhiên sẽ phát giàu sang. Duy có một điều hễ đến khi nào được gần vua chúa, thì phải dỡ nhà đi ở chỗ khác, chứ đừng ở lại làm chi.</t>
+          <t>Năm 4 tuổi, mẹ dạy kinh truyện, đọc đến đâu ông nhớ đến đó, lại đọc thuộc hàng chục bài thơ Nôm.</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>時有打魚俗例其池在山傍宅之前長潤數大許邑人鑒網相下庚於池中忍值魚鬚斷其絕郎上池畔山邊取藤英接經束之腰間忽然陽事大舉壯硬異常原有敵樁一啟恐不敵敵因晉浸池中不敵上畔時打魚陸續而歸庭獨不見眾人意其得魚而藏匿者其母郎徙尋之見廣猶在池中仍聲以遲歸之故廣郎鮮魚共母將同襃解釋其藤陽事漸漸而倒既歸世問其故庾具以宴告母即取藤使試佩之陽輒勃起築安試箋驗母取曝乾置之灶上時陳裕宗陽爭不舉廢罔治弗效使人禰詣國中有能治者許天下民祿之半適詣至伊社庚丹聞之曰劣陽是世之病，</t>
+          <t>時夫人他為文矣因拽竹權弄兒戲吟國語詩曰月撿弓月撿弓下句未就公在竹樞中郎和云撥魏例忍忍容文武喜以示夫人夫人恚曰月臣象也汝何以此命兒考大慚謝然恨終不釋竟辭歸於父家</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Canh nghe thấy địa chỉ bảo như vậy, lập tức theo đúng như lời, dựng ngay mấy gian nhà là đề ở, mới ở được ba năm trời, thì gặp được ngày trong áp có lệ đánh cá, ao cá ở ngay cạnh núi và ở trước mặt nhà anh, ao rộng kẻ mấy chục trượng, chẳng ngờ giữa lúc dân làng kẻ nom người vô dương mãi bất cá ở dưới ao, thì Canh hị dứt đây buộc giỏ. Anh vội lên trên bờ rào bút một sợi dây Chia-với để buộc ngang lưng rồi lại lội xuống, thì ngay lúc ấy dương vật của anh bỗng thấy thượng lên và nó cũng dẫm là thường, một đoạn khổ rách của anh chẳng còn cách nào để che kín được, vì thế anh không dám lên, cho mãi đến lúc đánh cá xong rồi người làng đã kéo lên hết, chỉ còn có một mình anh lẩn quần dưới ao, ai cũng nghĩ rằng anh bắt được cá lớn nên còn đấu điểm chi đây. Giữa lúc ấy thân mẫu của anh ở nhà, nhìn thấy dân làng đã kéo về cả mà sao anh lại chưa về, nên bà sôt ruột chạy ra xem sao, khi ra tới nơi thấy anh còn dương mò mẩm dưới ao, thi bà quát tháo dục đã, bấy giờ anh mới cỏi chiếc giỏ cá trao cho mẹ đem về trước, thì lạ thay, cái đoạn giấy ấy vừa buông ra khỏi thắt lưng, dương vật của anh nó cũng từ từ cựp xuống! Khi về đến nhà mẹ hỏi duyên có tại sao? Anh cũng nói thực như vậy. Mẹ bên đi cắt một ít đây Chia-với đem về phơi khô, gác lên trốc bếp, muốn xem thực hư thế nào, bà mẹ thường bảo anh đem thứ đây ấy buộc vào lưng, lần nào cũng thấy hiệu nghiệm y như hôm trước. Dịp đầu may mắn là nhường!</t>
+          <t>Một hôm mẹ kéo chiếc que tre chơi với ông, ngâm câu thơ Nôm: «Nguyệt như cung, nguyệt như cung», chưa kịp ngâm câu dưới thì ông ở trong cũi tre liền ứng khẩu họa lại: «Bát nguyệt sơ tam nguyệt lãng dung». Thân phụ mừng rỡ đem khoe với phu nhân, phu nhân giận bảo: «Trăng là tượng của bề tôi, sao ông lại dạy con như thế?» Thân phụ hổ thẹn tạ lỗi, nhưng bà giận không nguôi, bỏ về nhà cha đẻ.</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>使者具道可其六詳母曰我家有一物必能治之母子即取而勝隨使者赴京獻上祿宗佩之忽然陽事雄壯生得二皇子以度為神醫畫之宮中侍藥賞資不可勝計寵幸無比廣既得君都忘客人之言不徹舊宅</t>
+          <t>公總角時群見洛於寒度南艏北人始相之曰王及諦視又曰惜彼粗只存做狀元宰相故人皆知其為公韓器</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>vì giữa lúc ấy vua Trần-Dụ-Tông cũng dương bị chứng liệt dương, các quan thầy thuốc ra công điều trị không có hiệu quả, triều định phái viên đi khắp trong nước hỏi xem ai có món gì chữa khỏi được bệnh nhà vua, thì chia đôi quyền lợi thiên hạ. Một hôm sứ-giả về đến Tử-Trần, tuyên bố mệnh lệnh cho dân làng biết về việc tìm thầy thuốc vân vân: Bà mẹ Đặng-Canh nghe nói biết rằng cơ hội đã sắp đến nơi, bà liên xin vào yết kiến sứ-giả hỏi bệnh dương liệt nó là bệnh gì? Sứ-giả kề rõ bệnh tình như thế. Bà liền thưa rằng: Nếu như vậy nhà chúng tôi cũng có món thuốc trị được bệnh đó. Sứ-giả thấy vậy liền đưa mẹ còn bà về kinh thành tàu với nhà vua: vua cho triệu vào, bà đem những sợi Chia-với khô ấy dâng lên, nhà vua buộc thử vào người, quả nhiên thấy có công hiệu ngoài sức tưởng tượng, rồi ngài sinh luôn được hai (2) Hoàng-Tử, khen mẹ con Canh là bậc thần-y, giữ ở trong cung hầu hạ thang thuốc, luôn luôn ban thưởng, sùng hành không ai sánh tầy. Riêng về phần Canh sau khi được vua sủng hành, anh liên quen bằng những lời thày địa chỉ bảo năm xưa, không chịu dỡ nhà đem đi nơi khác, rồi sau con trai của Canh, thông dâm với các cung-nữ, công việc phát giác, bị xử tử hình, và Canh cũng bị trực xuất, tịch thu hết cả gia tài, thành ra anh bị dôi rết như cũ. Xét thấy ngôi dương cơ này về phía trước mặt, có thửa ruộng cao ước chừng 3 mẫu, trong hình như chiếc dao câu thái thuốc, cho nên mới phát danh y. Còn chỗ nhà ở vì nó sát ngay chân núi, mặt trời mặt trăng mỗi khi ngả bóng chiếu tạt xuống nhà, trong như hình con Thiềm-thư ngồi ở trên nóc, vì như thân ở cung thêm, nên mới được ở bên cạnh quân vương, từ do ra vào cung cấm. Nhưng mà chỉ hiềm một nỗi: nhà ở bên non, địa thế bức bách, bên ngoài còn có biết bao ngọn núi phân lại, cho nên phù quái chẳng được lâu dài, đó là theo phương pháp địa lý mà nói đại khái như vậy.</t>
+          <t>Thuở nhỏ ông chăn trâu ở bến đò Hàn, có khách phương Bắc trông thấy bảo rằng: Cậu bé này có tướng rất quý, chỉ hiềm một nỗi là da hơi thô, về sau chỉ làm đến Trạng-nguyên Tể-tướng mà thôi, vì thế nên ai cũng đoán chắc rằng: ông sẽ là bậc tể-phụ của quốc gia sau này.</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>其後庚子通渙宮女事覺被刑庚被驅囘田產盡沒始曩時貧寒的人接這宅接外有高數武形如理藥刀盤以故贓得各又宅處與山相近每日月斜照山影隨下胡王之知蟾蜍在屋簷上當如身在蟾宮故得近君王出入宮掖但嫌宅在山傍地荒其適又前面卻山去來靡定以故富貴不久按國史記裕宗遊西湖墜水中鄒英齋之復生因陽事不舉廣請取童男肝和陽起石服之及通同胞女以助疑道乃通其端羅裕宗服之屢驗與此說不同未知孰是晚斬詠史詩云既因薄載云要君寵又啟滯風逞已私行險小人心似鬼當時謾說是神殿罔</t>
+          <t>自少時講學家吏既長聞榜眼梁得交文章各世負笈從從之梁公弘化會朝人奉使如明得太乙神經族人梁汝笏之後仍以授公公既造諸玄理見道遂東後染師病篤嘆其子有慶於公公撫之如子教以成名</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Còn như về phần sử-ký: thì trong quốc sử có chép rõ rằng: Khi vua Dụ-Tông ra chơi Tây-Hồ, đương người trên thuyền tự nhiên ngã nháo xuống nước, sau khi vót lên, Đặng-Canh dùng phép châm cứu nên ngài mới được hồi sinh, về sau ngài bị liệt dương, Đặng-Canh xin cho mở bung dựa trẻ con trai lấy gan hòa với vị Dương-khởi-Thạch để cho vua uống, và bảo vua phải thông dâm với chị em ruột để giúp thêm cho dương khi, nhà vua làm theo phương pháp quả có hiệu nghiệm, cho nên Canh mới được vua tin dùng. Nay đem sử liệu so với thuyết trên thì thấy khác hẳn, chưa rõ thực hư thế nào, vì thế nhà thơ Thoát-Hiên có vinh bài thơ tứ-tuyệt như sau: Đã đem nghề mọn mua tâm chúa! Lại mở lò dâm thỏa chí ma! Hiểm thực tiểu nhân loài quỉ quốc? Ai oì đứng với tướng Hoa-Đà.</t>
+          <t>Như ông lúc còn niên thiếu, học văn sở đắc ngay từ gia đình, đến khi lớn tuổi, nghe nói có quan Bảng-nhãn Lương-đắc-Bằng, nổi tiếng văn chương quán thế, ông bèn tìm đến để xin nhập học. Lương-Công là người ở làng Hội-Trào thuộc huyện Hoằng-Hóa lúc Ngài phụng mệnh sang sứ nhà Minh, có học được phép Thái-ất-thần-kinh của người cùng họ, tức là dòng dõi của Lương-nhữ-Hốt. Lương-Công rất tinh thông về lẽ huyền vi, đem truyền lại cho ông, đến khi Ngài bị ốm nặng, lại đem con là Lương-hữu-Khánh ký thác với ông, ông săn sóc dạy dỗ chẳng khác con mình, sau này ông Khánh cũng được thành đạt.</t>
         </is>
       </c>
     </row>
@@ -4572,12 +4572,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>神怪厚捧光明寺嘉福縣厚榛社屬海陽處有光明寺千重碧樹四面波濤里路通其前河水繞其左真禪門一勝槳也</t>
+          <t>光紹間兵變起公隱居教授抱道自樂不求聞達綿元帝皇初年鄭綾公莫登庸皆有挾天子会諸侯之志類年構兵境內大亂公感懸興詩云</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Huyện Gia-Phước xã Hậu-Bồng có ngôi chùa Quang-Minh từ, ngôi chùa ẩn giữa ngàn cây cổ-thụ xanh biếc, bốn bề đồng tráng nước trong, trước mặt có đường quan lộ, bên tả có sông Vĩnh-Hà, quả thực là một danh lam thắng cảnh.</t>
+          <t>Năm Quang-thiệu gặp lúc loạn lạc, ông về ẩn cư để dạy học trò, lấy đạo làm vui, chẳng cầu danh tiếng, nhưng sang đến thời đầu niên hiệu Thống-nguyên thì Trịnh-Tuy và Mạc-đăng-Dung cũng đều có ý hiệp chế Thiên tử để sai khiến chư hầu, hai bên gây cuộc nội chiến khiến cho trong nước chịu cảnh lầm than, lúc ấy ông có cảm hứng một bài thơ rằng:</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>舊傳有一婆蒼僧號玄真住持在此只誦經禮佛不營人間事業利欲卻意人皆以為禪處高僧稱許晚年于房後打眼忽愛彌陀伏降臨實殿邀來按前謂曰爾有功梵教委厥上有主且慈悲一點善心達于玄後劫富降生為胡王國皇帝爾其知之既醒乃召諸道場謂曰某自初出家飯依禦率每謂塵緣淨盡果福圓成寶座金蓮是我遂後身之報誼意他日迴輪都以累年或行三夫消也</t>
+          <t>泰和宇宙不虞周五戰交爭笑商答</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Chùa này nguyên trước có một nhà sư hiệu là Huyền-Chân trụ trì tại đó, ngày tháng chỉ mãi tụng kinh, lễ Phật, chẳng màng việc thế sự, lợi danh, ai cũng cho là nơi thiền định, các bậc cao tăng đều khen ngợi. Cuối đời, sau nhà nghỉ, Sư bỗng thấy Di-Đà Phật hiện xuống, mời vào điện, bảo rằng: Ngươi có công với Phật giáo, trên có chủ, lòng từ bi đã thấu đến trời cao, kiếp sau sẽ đầu thai làm Hoàng đế nước Hồ. Ngươi biết chưa?</t>
+          <t>Thái hòa vũ trụ bất ngu chu, Ngũ chiến giao tranh tiếu thượng thu.</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>得塵寰一大艱難且日月國君之哲言昔人所不願也</t>
+          <t>川血山骸淵魚羊殼雀為誰驅</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Vậy nên sau này hóa kiếp được làm Hoàng-Đế của một nước lớn.</t>
+          <t>Xuyên huyết sơn hài tùy xứ hữu, Uyên ngư tằng trước vị thùy khu?</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>不知生前葉障其未盡除去而然耶</t>
+          <t>重興巴下渡江馬後憲應防八室龜</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Người đã biết chưa?</t>
+          <t>Trùng hưng Ba Hạ độ giang mã, Hậu hoạn ưng phòng nhập thất quy.</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>這事現有問夜佛旨爾等同記吾言當於圓寂之後寫來數為詭以驗之也及卒後道場依其言乃朱書十字于肩上用佛家火藥法收舍利時銀瓶埋之尋藥以石庵時加供養焉都說永賴縣前烈社阮自隱家貪好學及長從師長安路經予此每往返間輒檢特休息或至登臨玩賞亦不知其光明奇焉</t>
+          <t>世事到頭休說著醉吟澤畔為閒這</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Về phần nhà Sư sau khi tỉnh dậy, nhớ đến những lời trong mộng, bèn triệu các Đạo tràng đến bảo rằng: Ta từ lúc xuất gia nương nhờ của Phật, tưởng rằng tẩy hết trần duyên, tu tròn quả phúc để lên Tòa Sen, đó là hậu báo cho lúc siêu sinh, ngòi đầu đến kiếp luân hồi, thì bao công phu khở hành, lại phải dời lấy các chức vị gian nan lớn nhất ở trong trân thế. Vả lại lời thề của vua nước Nhật-Nguyệt kia, người xưa cũng còn chẳng muốn, không rõ kiếp trước của ta còn có nghiệp chướng chi đây mà đến nổi thế? Thời thì việc này đêm qua đức Phật đã từng chỉ bảo, vậy thì các người hãy nên nhớ lấy những lời ta nói, đợi đến khi ta về châu Phật, các người sẽ ghi chớp lại, để xem ứng nghiệm ra sao? Các Đạo-Tràng theo lời di chúc trên đây, đến khi Sư mất, họ cũng lấy son viết đúng 10 chữ lên vai nhà Sư rồi theo phương pháp nhà Phật, đem xác ra thiêu, thiêu hóa xong mới lượm lấy năm than xương, dựng vào một chiếc bình bằng bạc để đem mai táng, rồi sau dựng một ngôi chùa bằng đá lên trên, tháng ngày gia công tung niệm. Lại nói về xã Tiền-Liệt thuộc huyện Vĩnh-Lại có quan Lễ-Bộ Thị-Lang là Nguyễn-tư-Cường, lúc nhỏ nhà nghèo nhưng rất chăm học, nhận một buổi sớm cậu vào khất thực nhà ông Đô-nho, ông thấy cậu học trò nhỏ, bèn đọc một câu ngạn ngữ để điều cậu rằng: Âm vị khai nhi dương đã lộ, nguyên câu chữ nôm là Cánh cửa Hồng-môn còn khép nếp, Ngọn cò xích xí đã lăm le, rồi lấy câu đó làm để tài bảo cậu vịnh một bài thơ nghe thử.</t>
+          <t>Thế sự đáo đầu hưu thuyết trước, Túy ngâm trạch phán vị nhàn du.</t>
         </is>
       </c>
     </row>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>及卒後道場依其言乃朱書十字于肩上用佛家火藥法收舍利時銀瓶埋之尋藥以石庵時加供養焉</t>
+          <t>蓋知教民當復與始雖備安終必復興國而室韜其隱語也</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Chỉ sau giây phút câu đã làm xong, câu trạng (thứ 3-4) viết rằng:,, Hồng-môn kiểm thuận do hoài nặc, xích xí kỳ mao dĩ chỉ huy, tức là dịch câu chữ nôm ở trên, quả đã thần tình, nên được nhiều người truyền tụng. Về sau đến tuổi trưởng thành cậu ra Tràng-An du học, mỗi khi qua chùa cậu vẫn vào chơi nghỉ mát, nhưng cũng không dễ ý nhận đó chính là chùa Quang-Minh tự rồi đến niên hiệu Hoàng-Định (1600-1619), cậu đồ Tiến-Sĩ vào khoa Giáp-Thin, cách mấy năm sau phượng mang sang sứ Bắc quốc, vua nhà Minh triều đến trước mặt hỏi rằng: Người là Sư-giả An-Nam chắc rằng biết hết những nơi danh lam bên đó. Vậy có chùa nào gọi tên là Quang-Minh tự hay không? Ông quí gọi tàu: Danh lam ở bên bồn quốc, thần biết rất nhiều, tỷ như các chùa Quỳnh-Lâm, Bão-Thiên, Phổ-Minh, Quy-Điền đều là những nơi cổ tích thần đều nghe tiếng, còn chùa Quang-Minh sự thực không biết ở đâu, thế mà ngày nay Hoàng-Đế phân hỏi, chẳng hay có duyên có gì, xin cho hạ thần được rõ?</t>
+          <t>Sở dĩ có bài thơ trên, vì ông biết rõ nhà Lê sẽ được trung hưng, dẫu rằng ngày nay tạm phải tìm kế an thân, nhưng rồi sau đây tất nhiên sẽ lại khôi phục được nước.</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>都說永賴縣前烈社阮自隱家貪好學及長從師長安路經予此每往返間輒檢特休息或至登臨玩賞亦不知其光明奇焉</t>
+          <t>阮鼎革偸檄四方乎親明委勸之仕公元四十始就鄉試領首選莫大正六年癸巳未春公年四十五赴會試四場並第壹廷對擢進士及第授東閣校書和莫太宗所制表春天御講二詩皆頒優等刑部左侍郎俄遷吏部左侍郎業東閣大學士在朝八年疏劾弄臣阮世小者十八人請悉誅之其志欲使萬物各得其所微而致慧亦比自授以敬卜葉恐值壇防端貴橫恐累連姻遂托病致仕時公元五十二</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Minh-Đế có về ngậm ngùi phân bảo: Trầm đây từ lúc mới sinh thấy ở bên vai có viết mấy chữ bằng son An-Nam quốc Quang-Minh tự Sa viết tự khẩu công là mươi chữ ngắn viết hãy còn rành rành.</t>
+          <t>Quả nhiên về sau nhà Lê trung-hưng, bốn phương trở lại yên tĩnh, bấy giờ bạn hữu đều khuyên ông ra làm quan, đến năm 44 tuổi ông mới chịu ra ứng thí, khoa hương thí ấy ông được đỗ đầu, rồi năm sau tức là năm thứ 6 đời nhà Mạc, lại ra tỉnh thi được đỗ thứ nhất, khi vào đình đối lại đỗ Tấn-sĩ đệ nhất danh, được bổ chức Đông-Các Hiệu-Thư, trong thời Thái-Tông nhà Mạc, ông có làm hai bài thơ Xuân-thiên ngự-tứ, đều dự hạng ưu, rồi thăng chức Hữu-Thị-Lang Hình-bộ, sau thời gian ngắn lại thăng chức Tả-Thị-Lang, kiêm chức Đông-Các Đại-học-sĩ. Trong 8 năm ở triều, ông có dâng sớ hạch tội 18 kẻ nịnh thần, xin đem chém để làm gương, nhưng rồi gặp phải sự cản trở, vì sợ liên lụy đến mình, nên ông cáo quan xin về trí sĩ. Thế là giữa năm Quảng-Hòa thứ 2 ông mới 52 tuổi đã xin trí sĩ, treo mũ về làng, dựng am Bạch-Vân ở phía tả chỗ làng ông ở, và vẫn lấy hiệu là Bạch-Vân Cư-sĩ.</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>弘寳稱敬崇甲長科中進士第仕至禮部左侍郎其後徙北使皇帝召問曰小南國陪臣未知南國各蓋何處是光明寺即跪奏曰臣本國各蓋甚矣</t>
+          <t>既歸田里起白雲庵於鄉之士仍號名士起逐風長春等橋歲時遊態築中津館於雪江之津作碑以記其父又修葺佛寺構老僧同遊時或扁舟泛金海郁海觀魚宴子卧雲散主塗山諸各山皆自杖履登臨適意嘆咏往來或徜徉終日每遇樹木青幽時鳥變聲輒欣然自得公雖在家莫事以師礼國有大政事輒遣使就訪或時徵至京詢以大計從容規畫禪蓋弘多尋復還庵頤志後以功封程川候累陞夫部尚書太傅程國公</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Trầm ngòi tiếp trước là một vị sư ở trong chùa đó mà sau giáng sanh sang đây; nay trầm muốn lấy những vết chữ đó, vậy người biết có phép gì màu nhiệm hay không?</t>
+          <t>Khi ấy ông có bắc hai chiếc cầu Nghinh-Phong và Trường-Xuân để khi hóng mát, dựng một ngôi quán gọi là Trung-Tân ở bên Tuyết-Giang, có bia để ghi sự thực. Ngoài ra ông còn tu bổ chùa chiền, có lúc cùng các lão tăng đàm luận, có khi thả một con thuyền dạo chơi Kim-hải Úc-hải để xem đánh cá. Còn chỗ danh sơn thắng cảnh, như núi An-Tử, Ngọa-Vân, Kính-Chủ, Đồ-Sơn, nơi nào ông cũng chống gậy trèo lên, thừa hứng ngâm vịnh quên cả sớm chiều, mỗi khi thấy chỗ rừng cây xanh tốt, chim đổi giọng ca, thì ông hớn hở tự đắc, quả là một vị Lục-địa Thần-tiên. Nhưng trong thời gian dưỡng lão ở chốn gia hương, tuy rằng không dự quốc chính, thế mà họ Mạc vẫn phải kính trọng như một ông thầy, những việc trọng đại thường sai sứ giả về hỏi, có khi lại đón lên kinh thành để hỏi, ông đều ung dung chỉ dẫn, nhờ được bổ ích rất nhiều. Xong rồi ông lại trở về am cũ, về sau được phong tước là Trình-Tuyền-Hầu, dần dần thăng đến Lại-bộ Thượng-Thư Thái-phó Trình-Quốc-Công.</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>如瓊林普明報天寵田諸古刺臣亦素聞至如光明寺各未知何處不審有何緣故願示其詳皇帝喟然曰朕生之始有上朱書痕迹冤然脫意脫是依奇僧令雖降生上國脫欲洗了字痕不知有何術公郎奏曰臣聞佛家有八水洗塵之法既是寺中降誕須取那寺中井水洗之方可耳</t>
+          <t>公博極聲書深明易理雨暘水旱禍福災祥存亡得喪之因無不前知常與門人張時舉卜易則乾卦而知八世之後起戈千其神祕淵奧不能盡述授徒甚眾惟馮克寬篤有慶阮璽張時舉最著</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Ông tàu rằng: Hạ thần nghe nói phương pháp tẩy trần của nhà Phật phải dùng đến dược thủy, ngày nay Hoàng-Đế biết rõ kiếp trước ở chùa, thì nên lấy thứ nước giếng ở trong chùa đó đem về để tẩy thì mới sạch được. Minh-đế khen phải rồi bảo ông về bồn quốc tìm lấy nước giếng chùa ấy đem sang, sẽ có hậu thưởng.</t>
+          <t>Nói về môn sinh của ông sự thực không biết bao nhiêu mà kể, nhưng nói riêng về những người đã có tiếng tăm lừng lẫy thì có những ông như Phùng-khắc-Khoan, như Lương-hữu-Khánh, Nguyễn-Dữ và Trương-thời-Cử, đều đã nhờ ơn truyền thụ.</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>皇帝曰爾言誠有理宜為朕亟還本國尋這奇的取井水來那時頗有授用公頒拜命謝而還且達於我國王因備行探訪不意乃原捧社寺平日素所休息處也</t>
+          <t>初克寬假館遊學事既卒業公夜叩門語之曰鷄鳴矣夜既明矣何不起而作食堅固何為寬悟遂請八清仕歸阮氏後扶樑中興為各臣興隱居不仕作傳奇謾錄公亥為斧正遂為千古奇筆</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Ông lỉnh mang bài tạ quay về, khi về tới nước nhà, bèn đem việc ấy tàu trinh vua ta, rồi đi thăm hỏi khắp nơi, chẳng ngờ lại chính là ngôi chùa của xã Hậu-Đồng mà ngày thường ông vẫn vào đó nghỉ mát.</t>
+          <t>Nhắc lại khi Phùng-khắc-Khoan còn theo học Bạch-Vân Tiên-sinh, lúc thành tài rồi bỗng có một đêm Tiên-sinh đến chỗ nhà trọ của ông, gõ cửa bảo rằng: «Gà gáy rồi đây, sao anh chưa dậy nấu ăn, mà còn nằm ỳ ở đó», Khắc-Khoan hiểu rõ ý thầy nên vội thu xếp vào vùng Thanh-hóa, cùng ẩn cư với ông Nguyễn-Dữ, trong thời gian ấy Nguyễn-Dữ có soạn ra bộ Truyền-Kỳ-Mạn-Lục, được ông phủ chính rất nhiều, cho nên mới thành một cuốn Thiên cổ Kỳ bút.</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>至來年貢部函奉命往仍取井水就京獻上皇命取來洗之果然消得舊痕書頁愈加光澤因大喜慰再召公至將大論諭曰朕得尓敵發頃悟首綠不亦終焉</t>
+          <t>時阮太祖曰我兵大振數戰神符讙王莫敬兵敗世祖因進兵由西山累京北中外皇皇誠獻以實虛計境內靳日寧我朝順平八年中宗崩無嗣太祖有特疑意詢之焉竟寘不詔決因使寬家人饗厚禮潛往海陽訪之公弗答但顧家童曰方今不穩在於粟穀不奸爾等可覓雀鴉穀種種之又命鳥遊寺僧童酒榼焚香餘無所及蓋徵示以事佛獎綿底意寬具馳苦太祖乃悟遂立英宗</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Thế rồi cách một năm sau đến hạn công hiến, ông lại phung mang sang sử, nhân tiện đem cả nước giếng ấy sang Yên-Kinh cùng hiến một thề. Hoàng-Đế nhà Minh cả mừng, lập tức đem ra tây ngay, quả nhiên vét cũ biển đi đầu hết, da để lại được sáng bóng thêm lên.</t>
+          <t>Năm Thuận-bình thứ 8 Lê Trung-Tông mất, không có hoàng nam nối ngôi. Thế-Tổ do dự không biết lập ai, hỏi Trạng-nguyên Phùng-khắc-Khoan, cũng không quyết định nổi, nên mới phải sai gia nhân ngầm đem lễ vật về tận Hải-dương để hỏi, ông không trả lời mà chỉ quay lại bảo các gia nhân rằng: «Vụ này lúa không được mẩy, chỉ tại thóc giống không tốt, vậy các người phải đi tìm giống cũ để mà gieo mạ». Nói xong ông lại lên xe ra chùa, sai các chú tiểu quét dọn đốt nhang, ngoài ra không hề đả động gì đến chuyện khác, bởi vì ông đã hé mở cho biết cái thâm ý là «cứ việc thờ phật thì được ăn oản». Rồi Trạng Phùng thấy thế vội vàng về báo, Thế-Tổ hiểu ngay, bèn đón Anh-Tông về lập, tình thế trong nước mới được ổn định.</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>浪度尓宜為朕重修梵字輪矣</t>
+          <t>范舍人與公又同鄉誼嘗密使人請公為子求一條生路使者以銀一包為贄拜祈不已。如適策杖後圍圍後有數十石塊答石嵌出橫繞軒前有群議縁石而行公徐目蟻而矢曰橫山一帶足以容身使者悟其意歸以告洪洪乃以計頴廣順遂蟠撫焉為隂氏</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Ngài rất lấy làm hài lòng, cho triều ông vào khen ngợi.</t>
+          <t>Trong thời gian ấy Đoan Quốc-Công Nguyễn-Hoàng là con Chiêu-Huân Tĩnh-Vương, đương lúc ở trong tình thế nguy ngập vì sợ không thoát khỏi tay Trịnh-Kiểm, thân mẫu của người vốn là chỗ đồng hương, nên thường bí mật sai người về làng nhờ ông chỉ giúp cho con giai bà một đường sống. Sứ giả đặt gói bạc nén ở trước mặt ông, rồi bái lạy lia lịa. Ông thấy sứ giả năn nỉ xin mãi nhưng vẫn không nói gì, rồi đứng phắt lên, tay cầm chiếc gậy thủng thỉnh ra lối vườn sau, là nơi có hơn 10 tảng đá xanh xếp thành một dãy núi giả quanh co, trước núi lúc ấy có những đàn kiến đương men tảng đá leo lên, ông ngắm nghía chúng một lát rồi mỉm cười và đọc một câu: «Hoành-sơn nhất đới khả dĩ dung thân», nghĩa là một dãy Hoành-Sơn có thể dung thân được đó. Sứ giả hiểu ý trở về thuật lại với Nguyễn-Hoàng, Hoàng bèn xin vào trấn thủ Quảng-Nam.</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4776,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>一新俾今春勝昔春非惟副朕心之誠耳</t>
+          <t>莫延歲八年發洽年號乙酉十一月公寢疾莫蒼治使人心問且語以國事公但曰他日國有事故高平難小可延數世福他無所言後七年莫之乾統隆泰順德永昌退保高平歷三世四十七十年而後泯其言無不騐類如此</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Trẫm vì có Khanh chỉ điểm chợt tình ngộ mới tiên duyên, nếu không thì thực bỏ phí cơ hội. Vậy Khanh nên vì trẫm gia sức trung tu, cửa Phật một phen đổi mới, xuân nay khác hẳn xuân xưa, làm được như thế chẳng những trọn được lòng thành bảo bồn của trẫm, mà lại còn biểu dương được rằng: nước người có cảnh linh thiêng chung đúc ra được một vị Trung-Hoa đại-đế, đối với phẩm giá thực là một việc ly kỳ. Vậy nay trẫm trao cho người 300 lạng vàng đem về xây dựng 36 tòa Phật tự và đèn cây bằng vàng bằng bạc mỗi thứ một cây để làm tự khi, sau khi về nước Khanh nên làm trọn cái công đức đó, cũng như trẫm được nhìn thấy tận nơi. Nếu không thì cơ báo ứng về sự hòa phục của Phật sẽ ở ngay bên thân của Khanh và con cháu Khanh đó nghe.</t>
+          <t>Mạc Mậu-Hiệp năm Diên-Thành thứ 8 tức năm Ất Dậu tháng 11 thì ông lâm bệnh, Mậu-Hiệp sai sứ đến vấn an và hỏi về quốc sự. Ông chỉ trả lời rằng: «Sau này quốc gia hữu sự thì đất Cao-bằng tuy nhỏ cũng giữ thêm được mấy đời», ngoài ra không nói gì nữa. Quả nhiên cách 7 năm sau thì họ Mạc mất, rồi rút lui lên giữ Cao-bằng được 70 năm, nghĩa là sau 3, 4 đời thì mới hoàn toàn bị diệt, coi đó thì lời của ông dự đoán chẳng sai chút nào.</t>
         </is>
       </c>
     </row>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>類尓國鐘靈為中花皇帝是品中之一奇也</t>
+          <t>是月二十八日公薨于家壽九十五學者尊為雪江夫子葬于鄉之原</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Ông nghe lời vua nhà Minh phân bảo xong lập tức bài tạ ra về, đem câu truyện đó tàu trinh quốc vương, vương cũng lấy làm kỳ di và hứa cho ông được phép làm theo mạng lệnh Minh triều. Được quốc vương nhà cho phép xong rồi, ông bèn dem số vàng bạc ấy ra sắm sửa vật liệu, thuê mướn nhân công, dựng một tòa chùa trước sau 36 nóc, nguy nga tráng lệ như cảnh Tây-thiên; lại còn xây thêm một tháp Phù-đồ gần một trăm bậc (cấp) chót vót từng máy, duy có cây đèn vàng bạc thì ông để lại nhà dùng, rồi đúc hai cây đèn sắt thay vào tự khi.</t>
+          <t>Nhưng rồi trong tháng ấy giữa ngày 28 thì ông tạ thế, hưởng thọ 95 tuổi, học trò suy tôn hiệu là Tuyết-giang phu-tử phần mộ ở trên một cái gò đất trong làng.</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>朕令付尔金三百兩銀三千兩帝同作仗奇並金銀燈擎各一樹番為奉佛之器還國之後當了此功德如朕親視否則佛家有得福果報之機須於身上與弟子孫上看公陛辭拜頒而歸再以這等情頭達于國王國王大奇仍許依天朝所命公即以所頒金銀市木鳴工崇修梵字一簽前後三十六連範巍哉</t>
+          <t>公胸依酒落天資極高而充養補裨渾然不露圭角人不問則不言言則必中從容就事不見其有為居家四十四年而其心未嘗一日而亡世憂時愼俗一發於詩文章出於自然天口輒成不事雕琢簡而暢淡而味皆有觀於世教所依國語詩賦甚多著日雲詩集未千餘首今行于世者百餘首父中津賦而止然觀其大略齊月光風千古猶可想見公嘗有詩云高潔誰為天一士安閒我是地行行傳蓋自言其志也妻二人子十六男女五長子號寒江魏士蔭受惠員夫大生切德切德生道進道進生道通道通生登瀛登瀛生時當時當年六院十五有男子效人皆八世孫也按廣鄉之西南潭淤四五聚高亦可數四敵深泓一大許同光照鍾秀毓英宜其達人者尚焉古鉗云研池水暎豈不信然其後清使周粲謂嶺南人物理學有程泉筆之於書而傳於中土公詡宮國</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Thế rồi cách mấy năm sau, vua Thành-Tổ nghe nói ông tình về môn xem tướng, nhân lúc nhân hạ mới hỏi ông rằng: Khanh thử coi tướng các con của trẫm, xem ai xứng đáng nói ngôi? Nguyên vì lúc ấy Vạn - Quân - Công được sủng ái nhất, rất có hy vọng lên ngôi sừ nhi, còn Thanh-Đô-Vương kẻ về vị thứ hãy còn kém xa, thế mà ông giám căn cứ vào tướng mạo tàu thẳng ngay rằng: Thần xem tướng các Hoàng-tử duy có Thanh-Đô-Vương là người sẽ được thiên hạ sau này đó thôi?</t>
+          <t>Xét thấy ông là người khơi ngoan tuấn, học hết các kinh sách lại rất tinh về lý thuyết kinh dịch, phạm việc mưa nắng, lụt hạn, hoa phúc, điểm dữ điểm lành cơ suy cơ thịnh v.v... việc gì ông cũng biết trước. Ngay trong lúc ông còn mở trường dạy học có một học sinh họ Bùi người xã Trung-hàng thuộc huyện An- dương, là người rất thạo về văn án. Ông bảo hậu vận của anh thế nào cũng được giàu sang. Nhưng mãi đến khi tuổi gần 70 mà bước công danh vẫn thấy chất vật như thường, nên anh nói nhỏ với các bạn rằng : Lý sở của thầy thân điều đến thế, mà cũng có chỗ sai nhầm hay sao. Ông thấy học trò bàn mảnh với nhau như vậy thì cũng mỉm cười chứ không nói gì. Nhưng rồi bỗng có một hôm ông bảo trò Bùi đi thuê lấy 10 chiếc thuyền đánh cá, kéo buồm vượt thắng ra cửa Vạn-Ninh rồi rẽ vào đầu ở trong khoảng Đàm-hồng, đợi đến đúng hôm nào đó, hễ thấy vật gì cứ vớt đem về, tất nhiên sẽ được trọng thưởng? (Mạn sự Tản , Vạn-Ninh, Đàm-hồng). Trò Bùi thấy thấy đây bảo như vậy hơn hổ vui mừng, theo đúng như lời, chuẩn bị thuyền ghe kéo ra Đàm- hồng chờ đợi. Bỗng thấy một chiếc thuyền dương bị sóng gió dồn dập. Anh với cùng đoàn thủy thủ lướt sóng tiến ra, nhìn vào trong khoang chỉ thấy có một bà lão ẩn vận ra dáng cung phi, đương nằm ngất xỉu! Anh bảo gia nhân đỡ sang thuyền mình đưa về tìm phương cứu tính rồi anh đưa về phượng sự như thế mẹ già. Sau một thời gian thì viên Tổng-đốc Quảng-dong có sai sứ giả sang ta nói rằng: Vì Thái-phu-nhân một hôm đáp thuyền ra bể, chẳng may bị nạn phong ba, nay coi thiên văn biết rằng Bà hãy còn sống, hiện ở địa phận nước Nam. Vậy xin qui quốc vì nghĩa lân bang, sai người tim hộ, bồn chức không giám quên ơn v.v.. Lúc ấy triều đình nhà Mạc tiếp được thư trên, cho thông sức đi khắp các nơi, hứa rằng hễ ai tìm thấy sẽ được hậu thưởng. Nhận thấy lệnh trên, anh liền sắm sửa xe vồng đưa Bà ra hiện tại kinh thành, Mạc chưa ban thường rất hậu, và lại được bồ quan chức, về sau phong tước đến Thao-Quốc-Công! . Năm Thuận-bình thứ 8 (1556) Lê Trung-Tông mất, không có hoàng nam nối ngôi. Thế-Tồ</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>壯麗恰似真明境界兼築浮屠一塔近百餘丈延望簷然惟金銀兩燈檠番為家用別鑄鐵器世方之其後八朝成祖哲王聞公相人之術乘間問曰我諸子誰啟闕守王基時萬都公得寵將有儲副之命而清都位次未及公以相術直對曰諸子惟清當有天下萬都公深愠佯乃問公以他事因投以毒藥尋卒後文祖王正位公贈封太保郡公其雲仍至今猶存率皆廣賤每以兩燈敬手報應為根其寺廢經兵火付之殘灰惟浮屠一嶺巍然獨存近曰官軍進討等賊亦曾於此住焉</t>
+          <t>進士繚如虎記</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chẳng ngờ câu truyện xem tướng lại lọt đến tai Quân-Công, Quân-Công biết thế, giả vờ triệu ông vào dinh để hỏi việc khác, nhưng rồi thừa cơ đầu độc nên ông bị chết. Đến sau Vãn-Tổ chính thức được lên ngôi vương, Ngài mới tặng phong cho ông trước Thái-Bửu Quân-Công và lại phong trước cho các cháu, đồng dõi họ ấy tới nay vẫn còn, nhưng đều nghèo khó, vì thế họ đều oán hận là bởi ngày trước ông đã đánh tráo hai cây đèn thơ, cho nên con cháu phải chiêu bảo ứng không hay. Còn như tòa chùa do ông xây dựng, trải qua bao cuộc binh hỏa, cái gì cũng biến ra tro, thế mà chỉ riêng cây tháp thì vẫn nguy nga tồn tại.</t>
+          <t>ĐỒNG NIÊN SONG TẤN THOẠI GIA TƯ?</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>因考僧人事跡以為慈悲中一傳奇也</t>
+          <t>黎胡燕仙侶仙洲人也少南處生而岐嶷及長體大過人高五尺五寸家貧好學性善飯父母嘗羹七歲餳飯公食無餘學得半年以家計不贍出為善片社富家贅婦翁食以五歲鍋飯輒嗜臥廢學亦公疑之以問公之父曰聶聞君言有佳婿是好學的人而今懶廢不知有何緣故父曰兒自蒙托愛公毋食之知何翁曰飯五歲鍋矣父曰無雖家用不數此兒尚有七歲餌之食今如此相待其不學也固宜爾聞言輒加倍焉</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Gần đây quan quân kéo đi chinh phạt cũng thường đóng quân tại đó, nhân thế mới hồi ra được sự tích cao tăng, thì ai cũng cho rằng một câu truyện lạ trong cảnh từ bi vậy.</t>
+          <t>Ông Lê-như-Hồ (triều nhà Mạc) người xã Tiên - Châu thuộc huyện Tiên-Lữ lúc mới sinh ra trong rất vạm vỡ, đến khi lớn lên, thì người cao tới 5 thước 5 tấc, khoảng lưng chu vi đến một thước năm, Ông vốn có tính chăm học chỉ phải cái tật ăn khố mà nhà thì nghèo. Mỗi bữa cha mẹ nấu cho đến nồi 7 cơn mà Ông cũng ăn hết nhẫn. Vì thế cha mẹ chỉ cho theo học được đến nửa năm thì hết lượng thực, đánh phải cho sang gửi rể ở nhà phù Ông bên xã Thiện - Phiên, cha vợ cho ăn một nồi 5 cơn, thì ông chỉ nằm suốt ngày không hề mò đến quyền sách. Cha vợ lấy làm nghi hoặc hỏi cha để rằng: Trước kia tôi thấy Ông bảo Cậu nó là người chăm học, mà nay lười biếng như vậy, là có làm sao? Cha để hỏi lại: Được Ông quá yêu cho cháu sang ở bên ấy, vậy thì mỗi bữa Ông cho cháu ăn bao nhiêu? Cha vợ đáp: Mỗi bữa một nồi 5 com cơ đấy! Cha để mỉm cười nói: nhà tôi dẫu tùng cũng phải cho cháu ăn 1 nồi 7 com! Ngày nay Ông cho ăn ít như thế thảo nào nó chả nhắc học. Cha vợ biết thế cho ăn tăng lên ti chút.</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>保伍冊郡公記細都公乃保母吳順妃之弟以故顯典兵永慶年間、</t>
+          <t>公自是始索書目讀一二歲耳安世有不足處謂顧曰擇得一好婿來雖勉強讀書只要善食終焉做得何事辦鮮之曰他食兼人之食必有兼人之勇母曰苟如此我有田草始無試使他刲了公聞之郎取刀出林頭榕樹下假臥速象母牲市同見而嗔之郎歸告其六翁曰今猶多造飯與他吃否託言刈草自旦至歸市猶在一處打眼因橋翁手往想不意自岳母歸後公郎就田刈之神觀瞻息間效敵草間俱盡魚走之不及所浮邀收換不可勝計地舅媽來見之因嗟訝不已</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Huyện Thiên-Bản, xã Bảo-Ngũ, có Điền-Quận-Công, vì là em ruột bà Bảo-mẫu Mạc-Thuận-Phi, cho nên được dự binh quyền. Vào khoảng niên hiệu Vĩnh-Khánh (1729-32),</t>
+          <t>Bấy giờ cậu mới tìm sách để đọc qua loa, mẹ vợ thấy vậy có ý bất mãn bảo với Ông rằng: Ông khéo kén chọn con rể, chỉ được cái nết ăn khỏe mà thôi, còn sự học hành như thế, thì sau nó làm nên được những trò trống gì. Ông giải thích rằng: Điều đó bà đừng lo ngại, vì nó ăn khỏe hơn người, tất nhiên nó cũng có sức hơn người đây chứ. Bà đáp ừ nếu quả như vậy, thì nhà ta đây hiện có mấy mẫu ruộng rẫm, thử bảo nó ra phát có xem sao. Cậu thấy cha mẹ vợ bàn mảnh với nhau như vậy, sáng sớm hôm sau Cậu liền vác một con dao thật lớn xin ra phát có ngoài đồng, nhưng ra đến nơi thì Cậu lại nằm giả ngủ dưới gốc cây bàng. Đến khi mẹ vợ đi chợ về trông thấy tức giận dấy ruột, chạy về la lối om xóm: Ông oi từ nay Ông còn bảo nấu thêm com cho nó ăn nữa hay thôi. Hôm nay nó muốn tiếng ra phát cổ, thế mà từ sáng sớm cho đến lúc tôi về chợ, nó vẫn còn nằm ngủ dài ở dưới gốc cây. Chá tin thì Ông ra mà coi thử. Thế rồi bà tóm lấy tay dẫm ông ra thẳng cánh đồng. Nhưng bà có biết đâu rằng con rể của Bà vẫn nằm giả ngủ, đợi Bà đi khuất thì Cậu lập tức vác dao xuống ruộng phát lấy phát đẻ, chỉ trong chốc lát thì mấy mẫu cỏ đều đã quang lăng! đến cả tôm cá đều không chạy kip nên bị chết nỗi nhan nhân vót được rất nhiều. Khi hai Ông bà tới nơi, cũng phải hết sức kinh ngạc.</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>公年號、大安縣、</t>
+          <t>其後穀嘉時岳母使公往市喚傭工來公乍出輒囘報云其小已喚之無肯行者時家中已養二十歲鵠飯以待工人而無有二公輒取餌來食之殆盡吾母喚之曰這飯吃了不幾成賜破那腹耶公曰媽媽不須委惱今番經刈某請獨當遂袖弄一大段為俗曰：槴乾，幷參大繩以往繞半月，復餘二畝，殆盡，各束為四捆而回，每捆由是愛之仍許以飽食就學</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>nhân có khúc đê ở xã Thọ. Triền thuộc huyện Đại-An bị nước xoáy vỡ. Điền-Quận được lệnh tới đó bồi đắp.</t>
+          <t>Rồi sau đến mùa lúa chín mẹ vợ sai Cậu đi mướn thợ gặt, Cậu đi một lát quay về bảo chẳng mướn được ai cả, nhưng mà lúc ấy nhà đã nấu sẵn nồi hai mươi com, Cậu bèn đón com ra ăn hết quen, mẹ vợ lắc đầu báo: Con ăn nhiều quá như vậy, chẳng sợ vỡ bụng hay sao, Cậu thưa: mà đừng ngại! công việc gặt thóc hôm nay con xin đảm đang hết thầy. Ăn uống xong rồi Cậu liền dẫn hai đoạn tre lớn để làm đòn xóc, và chẻ một bó lạt dài quầy ra ngoài ruộng, gặt đến quá trưa thì xong cả hai mẫu lúa! bó thành bốn bó lững thừng quầy về! từ đấy mẹ vợ mới tổ thực tình yêu mến, cho ăn đầy đủ để chuyên vào việc học hành,</t>
         </is>
       </c>
     </row>
@@ -4895,12 +4895,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>受雲社堤路水潰、珥都公奉命培築每行水次經縣內金錢河津上有水神原廟捻著靈應地方之人皆崇奉之時細郡公舟纔過廟輒不進若有沮截之者郡公指而罵曰爾在此不駐護一方之民使水常為民害今我往障頹波歇命至此尓今欲反沮我耶</t>
+          <t>公當學時每得紙千張讀了即焚之傍縣有交跌場公郎往取第一標都力士亦不敵較以其有力故各知亮年立辛丑科一舉中進士</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Khi thuyền qua bên Kim-Tông, trên bên có một miếu thờ Thủy-Thần rất là linh-trùng, địa-phương sùng bài kẻ đã lâu đời. Quận-Điền bỗng thấy thuyền mình tự nhiên dừng lại, tựa hồ có gì ngăn cản. Ông liên nói giận trở lên trên miếu mảng rằng: Nhà ngươn ở đây sao chẳng bảo hộ địa hạt, để cho nước lụt thường làm hại dân. Nay ta phung mạng tới đây bồi đắp, mà ngươn lại muốn ngăn cản là có làm sao? Lạ thay ông vừa quát mắng xong, thì thấy trước mặt hiện ra 5 chiếc thuyền lớn trong có quân-sĩ khi giới, xông tới ào ào như hình khiêu chiến. Nhưng ông cũng tinh về thuật phu thủy, đoán biết ngay là Thủy-Thần hóa phép để chống lại mình, nên cũng đứng ở trong thuyền, tuốt kiếm hò thần Thiên-Cương, thư phù niệm chú, rồi mới hạ lệnh cho các tướng-sĩ cầm sản giáo mác xông lên, hai bên đều dùng hỏa pháo bắn ra, khói đen mù một phủ khắp một vùng, đứng cách chỉ một gang tấc cũng chẳng trông rõ thứ gi. Trận chiến kéo dài độ một trống canh thì thuyền bên địch bồng biển đầu mất, thế là bên ông thắng lợi hoàn toàn.</t>
+          <t>nhưng lạ thay! trong khi học tập, hễ Cậu viết xong trang nào, thì lại đốt ngay tức khắc. Trong thời gian ấy, các vùng lân cận thường hay mở đám hội hè, đám nào có treo giải vật, Cậu cũng xin giữ giải nhất, bao nhiêu lực sĩ đó vật, vi đã biết sức của Cậu nên chẳng ai dám so tài! cho nên người ta mới tặng tên là (Như-Hồ). Thế rồi cách mấy năm sau, khi vừa đúng 30 tuổi thì đã nổi tiếng văn chương, bấy giờ đương triều nhà Mạc niên hiệu Quảng-Hòa (1541 - 46), Ông ra ứng thí được đỗ Tán-sĩ vào khoa Tán-Sửu,</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>大罵良久忽見前出舟五艘突來跳戰都細素精符法知是木神步見郎於船中內按劍步墨書符念呪已分而撥船夫刀搶併出兩邊鏡口對射煙霧昏黑咫尺不勝辨約一更許這出船先卻顧貯間已失所在細郡即順流而往至貢口誤路處與役築作土功將完問有巨魚楊鬱水次望似一小小帆以尾邀水大浪懷山堤路築復瀆裂隨難隨破如是者效次遍罰公無知之何郎暗祝于水神曰非者廟經過一時錯誤還亦衡撞神其勿以介意所胡玉餘灵默護使堤圓完一方之義受福不淺自是堪得堅實不復潰破獨自負戲之曰我築成此堤雖百靈神亦難壞了忽然河水無故翻動狂波怒浪衝激其問這堤裂表尚一叚原來這處貢口傍出沖淵與大河密通乃俗傳淵底有神常引河水透八以故難於障塞時細都已損了許多工夫因此會怒今斂取縣內竹木環剿樹柵再取民家敗臼破礎并一切舊石煉灰投下俄見淵底瀝沸魚浮而斃者不勝其數再加培築刻衣處復完纔半月間細都忍藥不火熟病知在青火黃無灼中廢同治弗效詭病而沒未幾保任邑內民富不寧邑人相與祈禱于本社廟中冀可捍災忽內有一人動而起放大聲曰我是細都公被水神黃乎</t>
+          <t>時同科有同年阮清弘化人也嘗與公語及家計公戲之曰兄之家資僅足供我一月粮清曰請供三月之頓會不須三月斬請許一頓如何清曰諾約以某日辰臨至</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Đánh tan được bọn âm binh âm tướng, ông bên hạ lệnh cho thuyền cứ việc thuận dòng thẳng tiến đến nơi cửa công, rồi sai quân-sĩ dắp lại quảng đê bị vỡ, chẳng -ngờ khi dấp gần xong, thì bồng thấy một con cá lớn bơi lại, to bằng một chiếc thuyền buồm, đuôi nó vẫy vùng thành những ngọn sóng cao như trái núi, làm cho đoạn đê vừa dắp lại bị vỡ tung, vỡ rồi ông lại sai dấp, dấp xong nó lại phá luôn, trải đến mấy lần như vậy. Chẳng biết đối phó ra sao, bấy giờ ông mới làm dám khẩn vãi như sau: Kinh thưa Thủy-Thần linh-vị: Mới rồi đi qua trước miếu, tôi đây một phen lầm lỡ trót đã xúc phạm oai linh, xin Thần cũng đừng để ý, ra sức ủng hộ cho cuộc bồi dắp sớm được hoàn thành, tức là Thần đã ban phúc cho dân địa phương không phải nhỏ vậy. Khẩn Thần xong rồi ông lại ra lệnh cho quân-sĩ bắt tay vào việc, hễ dấp đến đầu thì đất chắc nich đến đó, không bị vỡ lỗ chỗ nào. Nhưng rồi sau khi dấp xong ông lại tự phụ tuyên bố ngay rằng: Khúc đê của ta dấp đây dầu có 100 vị thần linh cũng không tài nào phá được. Lạ thay lúc ấy trời dương im lặng, thế mà ông vừa nói xong mấy câu thì trên mặt nước lại thấy chuyển động, sóng lại cuộn cuộn nổi lên, đập vào chân đê phá vỡ ngay một quãng lớn, làm ông hoàng sợ, vội vàng sắm sửa lễ vật để ta thân linh rồi sai dắp lại, nhưng mà dắp mãi cũng chỉ tôn công chư không thu được kết quả. Nhưng vì chổ cửa công đây là một khúc quẹo nằm cạnh đại hà, tục truyền ở dưới đây đầm có nhiều linh vật đục lỗ phía dưới đưa nước phù sa vào trong, cho nên rất khó hàn khẩu! Nhưng riêng về Quân-Điền với quãng đê này, ông đã tổn rất nhiều công mà chẳng thành sự, nên ông lấy làm cấm gián, sai quân đi khắp huyện hạt, chặt lấy tre gỗ, và đi thâu lượm vật liệu của dân để làm đà cồn, rồi lại nhào với với đà dỡ xuống lòng sông, chỉ trong chốc lát thì thấy rùa, cá, ba ba chết nổi lên trên mặt nước nhan nhản. Cứ thế làm luôn đến nửa tháng trời thì ông bị bệnh, thân thể nóng như nước sôi, chẳng có thuốc gì chữa được, rồi ông tử trần. Nhưng rồi sau khi ông mất chưa được bao lâu, thì các gia súc trong ấp Bảo-Ngũ lại bị chết dịch, nhân dân trong ấp bàn nhau sửa lễ kỳ-an, để mong tai qua nạn khỏi. Chẳng ngợ giữa lúc đương tế ở trong đình làng, thì thấy trong đầm nhân dân bỗng có một người đứng phất ngay đây, đầu tóc dựng ngược, hai mắt trọn trừng, khóc lớn lên rằng: Ta đây là Điền-Quân-Công mới bị Thủy-Thần ám hại, ôm hận về dưới suối vàng, nay muốn phục thù chỉ hiềm không có ngựa voi khí giới, thì dịch sao nổi với Thủy-Thần.</t>
+          <t>lúc ấy có người đồng bảng là Nguyễn - Thanh Ẩn người xã Bột - Thái thuộc huyện Hoằng - Hóa thường khoe nhà mình giàu có. Ông nói bốn rằng: Gia tài của Ông, chỉ đủ dải tôi một tháng là cùng? Thanh đáp: Nếu vậy mời Bác quá bộ vào chơi, tôi xin cung phượng ba tháng là ít, Ông đáp: thời khởi cần nói chi ba tháng, hôm nào tiện dip xin Bác hãy tạm thiết tôi một bữa xem sao? Ông Thanh nhận lời, hẹn dùng hôm nào sẽ xin đón tiếp.</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>抱恨而沒兮欲報仇第無象馬兵器難以相關寄達保母尊好為我辨送來不亦非推損物且將父人矣</t>
+          <t>公遂與一僕徒諳清家不意清有事他適公使達于夫人我與兄有舊偶因公事往過有隨從三十餘人須許一頓夫人即喚家童煮十歲鶴飯者三并物食五六盤聚了進之公佯謂其仆曰爾忘喚請從者來既而不見一人公就取盤鍋并物食吃都盡了因致謝而去</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Vậy xin nhẫn lời cho chị tức là Bảo-Mẫu chuẩn bị giúp cho. Nếu không thì chẳng những sức vật bị hại, mà cả nhân mạng cũng khó bảo toàn.</t>
+          <t>Rồi ít lâu sau, đúng ngày ước hẹn, Ông cùng với 1 tiểu học tới nhà Ông Thanh, chẳng ngờ Ông Thanh đi vắng, ông bèn nói với phu nhân: Tôi là bạn cũ của Bác trai đây, nhân có việc đi qua ghế vào thăm Bác, chẳng may Bác lại đi khỏi, vậy nay có hơn 30 tùy tùng, phiền Bác cho ăn một bữa, phòng có được chẳng. Phu nhân thấy nói là bạn của chồng, với bảo người nhà nấu ngày 3 nồi 10 com và đóng 5, 6 mâm cỗ chính đón bụng ra. Ông bèn giả tăng bảo đưa tiểu học: my ra gọi chúng vào đây, nhưng rồi chẳng thấy có một tên nào. Duy chỉ có mỗi mình Ông ngồi ăn, ăn hết mâm này lại đến mâm khác, khi ăn quan cả bấy nhiêu mâm rồi Ông mới cáo biệt ra đi.</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>保母聞言即合造與器一如珥郡公生特戰具完足焚之翌日見地方一帶河波濤淘湧如牛馬爭夫岸傍聽者似有于戈交戰之聲魚鬱魚紛然而驚保母聞之度必理郡與水神交戰因祝之曰吾弟今番共他戰勝負如何倘其有靈即以相報忽有一人搖動躍起言曰拜上尊姊贈以兵器戰具勢顓張皇但他族類宴聚已素練習我兵新習水戰未請兼以人形都非介胄薄弱之眾難與他鱗甲相鬩纏一交鋒更被挫了今後不可與鬩當於貢口處創一新綱讓他居之竟免積弊釁族人依言而材構作不日告成自是一方河道不聞有異事焉</t>
+          <t>逮暮清歸夫人語之曰我家今日有一事好笑請問故夫人笑道早有一人自稱與君相善多帶從人者來求獵予一頓妻發並辨以待不謂只有一酌人坐吃妄自竊視見一碗數口恰似風捲雲殘三盞飯並五六食盤一時俱盡不知是人是怪清悔之曰此必我同年儒洲人也我昨日有約惠然肯來今卻忘之必被吾兄見責</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Nói về bà chị tức là Bảo-Mẫu, sau khi nhận được tin ông hiện lên nhắn bảo, bà cũng theo đúng như lời, sắm sửa các thứ đồ mã, như voi, ngựa và các khí cụ bằng giấy đem đốt, rồi đến hôm sau thì một dài sông của địa phận đó, bỗng thấy sóng lớn nổi dậy như thể muốn ngựa giao tranh, nhân dân ở hai bên bờ nghe thấy những tiếng gươm giáo chạm nhau xoang-xoảng, cá tôm nổi lên mặt nước rất nhiều. Bảo-Mẫu đoán rằng: Em mình cùng Thủy-Thần giao chiến, nên bà cũng làm bảm khẩn: phen này giao chiến thắng phụ ra sao nếu em có thiêng thì báo tin ngay cho chị biết với. Lạ thay bà vừa khẩn xong, thì hồng có một người nhà dừng phất ngay lên vừa đảo la liệt vừa nói: Xin bài tạ Chị đã cho binh mã gươm dao. Nhưng vì quân địch quá nhiều và lại tinh nhuệ. Còn binh của ta toàn là lính mới, về phần thủy chiến chưa quen; gia đĩ các đồ bằng giấy không thể thắng nổi những quân có lăn gia vậy cũng dẫm, vì thế cho nên thoát mới giao phong liên bị tan rã. Thời thì từ đây về sau đừng nên đối địch với chúng mà thêm thiệt hại. Chi bằng hãy dựng một ngôi đền mới ở trên cửa Cống, nhường cho Thủy-Thần ở đó, để khỏi tích lũy hiểm thù v.v. Trong họ thấy ông hiện lên phân bảo như vậy, cũng theo dùng lời đi mua vật liệu xây dựng, sau khi dựng xong ngôi đền, thì quảng sông đó nghe không có truyền gì là nữa.</t>
+          <t>Chiều hôm ấy Ông Thanh thoát về đến cửa, phu nhân với ra nói ngay: Cậu ơi: nhà ta hôm nay có một câu chuyện rất là buồn cười; Ông hỏi chuyện gì? phu nhân mỉm cười đáp: Sáng sớm hôm nay có một ông khách đến chơi, nói là bạn thân của Cậu, nhân đi công cán qua đây, hiện có đem theo mấy chục tùy tùng, nhờ tôi sửa giúp cho một bữa cơm. Chẳng ngờ đến khi làm xong bụng lên, thì lại chỉ có một mình ông ấy ngồi ăn hết cả. Lúc ấy tôi ở trong phòng nhìn ra thấy mỗi tò com lớn ông chỉ và có hai miếng! ăn mau như thế gió cuốn mấy bay! chỉ trong một lát, ăn hết cả ba nồi 10 com và 5, 6 mâm cỡ. Chẳng biết là người hay quí? mà lại ăn khỏe lạ lùng như vậy. Ông Thanh nghe vọ kề xong tỏ vẻ hối hận nói rằng: Thôi thôi! chính là Ông bạn quê ở Tiên-Châu, trước kia tôi có hẹn Ông vào chơi, chẳng ngờ ngày nay quên bằng đi mất, thế nào anh ấy cũng trách là kẻ vô tình?</t>
         </is>
       </c>
     </row>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>族人依言而材構作不日告成自是一方河道不聞有異事焉</t>
+          <t>後清因回家途經像洲郎詣公訪舊公屬家人整燕肥豬二隻又資盛二盞同坐款待清契盡豬款各一角公契盡豬一隻又款一盤又契清新餘各一角只需其半以與狹人相吃溝大驚曰古稱慕澤先生以食為各但又于十八十二之數若與兄同時適避三舍矣公大笑</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Trong họ thấy ông hiện lên phân bảo như vậy, cũng theo dùng lời đi mua vật liệu xây dựng, sau khi dựng xong ngôi đền, thì quảng sông đó nghe không có truyền gì là nữa.</t>
+          <t>Thế rồi cách ít lâu sau, Ông Thanh nhân lúc về quê đi qua Tiên-Châu có ghé vào thăm Ông Hò, Ông bảo gia nhân giết hai con heo luộc chín, và 4 mâm xoi để thết đài bạn! về phần Ông Thanh chỉ ăn hết có 1 góc, còn Ông Hò thì ăn hết cả 3 mâm xôi và một con heo, rồi lại ăn sang một góc của Ông Thanh, chỉ còn để lại một nĩa cho người theo hầu, khiến cho Ông Thanh hết sức kinh ngạc nói rằng: Đời trước khen Mộ-Trạch Tiên-Sinh là người ăn khỏe, nhưng chỉ đến số 12 (cạnh) 18 (cơm) mà thôi, vì thử đồng thời với Bác thì còn kém Bác đến 3 dặm vậy, Ông Hò dắc ý cả cười.</t>
         </is>
       </c>
     </row>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>彊暴大王記</t>
+          <t>其後官歷左侍郎奉往北使時同縣安照社署人頗有口辨使之從行</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Cường-bạo vương, kẻ kháng Thiên Tướng</t>
+          <t>Rồi sau Ông Hò làm đến chức Hữu-thị-Lang, phung mạng sang sứ Bắc quốc, lúc ấy có người lái buôn ở xã An-Chiều an cung huyện, vốn là một người có tài khẩu thiệt, Ông cho đi theo.</t>
         </is>
       </c>
     </row>
@@ -4997,12 +4997,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>紂大王天本縣令改務 、</t>
+          <t>至燕京北人聞公善食因作一具十八層召公赴宴架梯而食公每吃了一層輒取鉢擲下至最後層見一人頭在焉傷人皆掩目不敎正視公大聲喚從者來曰書我生不知滋味今皇帝賜我食北人頭最為佳品汝將取醋來我吃了蓋這頭乃魚人頭與人無異世所罕見故他以此怵公今見其不懾頗有侵渡之語即挈取頭去</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>VUA CƯỜNG BẢO DŨNG MƯU KHÁNG CỰ TƯƠNG NHÀ TRỜI</t>
+          <t>Khi tới Yên Kinh, Bắc triều vốn đã nghe tiếng Ông ăn khỏe nhất, nên có sửa một mâm cỡ, chồng chất lên 18 từng rồi triệu Ông vào dự yến! khi ăn phải treo lên thang, ăn hết từng trên thì quảng bát đã xuống đất rồi mới ăn đến từng dưới. Chẳng ngờ khi ăn đến từng dưới cùng thấy có một cái đầu người. Ông bèn lấy dưa xuyên vào hai mắt rồi giao cao lên, làm cho những người chung quanh đều phải bịt mắt chó không giám nhìn. Ông bèn thét bảo quân lính theo hầu: Ta đây là kẻ Thư sinh chưa nếm những món ăn là bao giờ, ngày nay Hoàng - Đế cho ăn số người Bắc quốc! hẳn là món ăn rất ngon. Vậy thì các chủ kip đem tương dẫm lại đây để cho ta chén nghe. Nguyên cái số ấy tức là số con nhân ngư (cả người) trong y như số người thực, mà đời ít khi được thấy, cho nên họ mới dùng nó để thử thách Ông, nay thấy Ông đã chẳng sợ lại còn nói xược như vậy. Họ liền xách ngay cái số ấy đi,</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>見縝令改人也先其母愛黑漢神謂曰托生猴焉</t>
+          <t>尋托以他爭篤其兩目使人撓之自曼所而往三日復就這賣因問公何賣否公已默記其心郎答云乃前日賜晏賣也北人謂公莊前知遂敬之</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Cường-bạo đại-vương người làng Bối-Cẩm thuộc huyện Thiên-Bản , khi trước bà mẹ nằm mộng thấy có một người mặt đen bảo cho bà biết : Thần trên núi Nhạc sẽ giáng sinh xuống họ này đây, rồi bà thụ thai, dân sinh ra ông ; đến khi lớn tuổi ông rất ngổ ngưu, coi đời bằng nửa con mất, đến nỗi quên cả ngày giỗ cha mẹ, nhưng mà đối với Táo-quân thì lại sớm hôm khấn bài, dù khi bắt được một vài con tôm, cũng đem nấu nướng để cùng, cho nên thần Táo cũng thấu đến tâm lòng thành, thời thường ủng hộ. Thế rồi bỗng có một hôm cha mẹ đem hết tội trạng tố cáo ở trên thiên đình. Trời bên sai ngay lời thần xuống đánh. Ông Táo biết truyền xuống trước bảo khẽ với Vương : Vương xin Táo-quân, bày kế giúp đỡ. Táo-quân báo lấy chất tròn như mổ phết lên trên mái nhà, để cho Thiên-loi không có chỗ đứng, thì dẫu roi lừa búa đá cũng khó giữ trò v.v... Vương được Táo-quân dạy cho điều kế như vậy, lập tức đi kiếm Mông-toi đem về giả lấy nước giột, và sắm các thứ dầu mỡ để sẵn, đến hôm Thiên-loi xuống đánh, thì trước giờ đó Vương đem các thứ lên trát khắp mái nhà, rồi nắp phía dưới chờ xem động tĩnh ra sao ? Quả nhiên hôm ấy Vương vừa nắp được một lát, thì trời nôi con mưa gió sấm chớp ầm ầm !  Thiên-lợi phượng mang Ngọc-Hoàng cởi mây nhảy xuống nóc nhà, liền bị chất tron làm cho tuột chân té nháo xuống đất.</t>
+          <t>rồi vùn vào một cờ khác để bịt mắt Ông lại, cho người công đi an trí một nơi, sau một vài hôm chúng lại đưa về chỗ cũ, hỏi Ông có biết đây là nơi nào. Vì Ông đã đề tâm từ trước, nên giả nhồi ngay rằng: Chính đây là chỗ ăn yến hôm trước chứ còn nơi nào. Người Tàu tưởng Ông là bậc tiên-tri, nên mới tha cho lối trước.</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>族遂有娠而生時年將十五歲五為兒時好耕耘種樹吃然有巨人之性及長率性彊暴耿目一世都忘父母不有忘臘惟灶神朝祈又禱難得一鯨亦必熟而供之神亦知其心時加頸應一日父母以狀罪訢于天天郎命雷神降而打之灶神密先頭告王來計灶神曰以滑物塗屋上縱有火觀石斧其盛何施王依其言遂取箝夢條日揚攢與水油相和至日直于屋上偏洒之玉潜伏暗中候視俄而風雨驟至雷神從天而下繞躡星脊上滑而墜地王從中突步揮杖擊之雷神倏然不見奪得赤銅繩長丈餘郎於靜地埋之雷神歸具以事奏昊天天怒謂靈神曰三才我為之尊汝震我威所擊無不摧折者何等人物乃與霹靂抗衡潛報水神以某日引水而上北固彊暴亦為魚敞之餌灶神復告之玉遂結蕉為筏取葉為旗翌日水大至浸没蘆舍王郎乘筏而出擊手鼓鳴羅織橫水面設舟震于天大言我與天交戰時昊天方與群像論善惡聞之曰何處聲甚緊群像相視莫祛對雷神方候旨對曰是乃彊暴之賊向既逃罪令復于常恭望定奪昊天說思良久曰弗敬怒淪動輒抗拒是乃無天地的人今姑赦之任他長惡弗悛禍必將意至仍命水細縮水而下五竟免害即乃家人具道可以遙來得灶神之助允上帝一言一動必先顯告吾復何辜自是益橫其志復得一田雞自灸而食之不以獻灶神怒其忘己思中傷之一日顯告五曰來日雷神打汝五又問許灶神曰次早汝往耕于田如雷雨將至即於耕木夾處處穿車其中外用橫木裹鎖定自無事王不意一為其所賣依計而行既而雷雨漫天而至王欲斂之不脹竟被打斂頭間雨霽群牛觸土培之宛然成大阜鄉人即其土處封墳數年後方民夜勤畜類不寧一日有村翁早行過予墳處見立而言曰我彊暴靈神爾立廟祀之可保無虞不卒無遺類矣</t>
+          <t>時國上連月不雨仍命諸國陪臣修文橋雨公料知天象未雨因奏曰臣小國乞後讓大國先之已而祈之皆不應皇帝郎命公對曰有從人學得武公遺法嚴乎風喚雨可遣皇帝郎召之其人奏曰臣有一法須得吉日方可用乃潛觀櫪木根俗曰已見白父鷄頸草俗曰鷄鵠有黠自知兩期將至即請設壇場禱之已而果得兩皇需大稱賞封為兩國之師封公為兩國尚書</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Vương ở trong nhà ngó thấy, lập tức vác gậy xông ra, đánh ngay một đòn bồ thượng. Thiên-lợi loạng choạng chạy về Thiên-đình, Vương đoạt được sợi dây đồng đỏ dài hơn một trượng, bèn đem chôn ở một nơi cao ráo sạch sẽ. Còn phần Thiên-lợi sau khi chạy thoát trở lên tàu với Ngọc-Hoàng thì Ngài cả giận quơ mắng : Ta đây là bậc chí tôn trong hạng Tam-tái, nay cho nhà người xuống dưới hạ giới để làm vang đội oai danh, hỏi rằng đánh đầu mà chẳng nát gãy ? Vậy nay tên ấy là hạng người nào lại dám chống cự thiên oai ? Thế thì nhà người phải nên mặt báo với các Thủy-Thần, hẹn đúng ngày giờ, dâng nước lên bắt tên bạo tặc đó, để làm mời cho lũ cá giải, nghe ! Lần này Táo-quân nghe được lệnh trên, thì lại với vàng quay xuống báo tin cho Bạo-Vương biết. Vương bèn đi đóng bè chuỗi, lấy lá làm cờ, chuẩn bị vừa xong thì sáng hôm sau tự nhiên thấy nước dâng lên, ngập cả nhà cửa. Vương ngồi trên bè chuỗi đánh trống khua chiêng, tung hoành ở trên mặt nước, miệng thì thét lớn Ta lên giao chiến với trời ! Giữa lúc ấy trời đương cùng chư tiên phân đoàn những kẻ thiện ác ở dưới trần gian, bồng nghe phía dưới có tiếng om xóm, Ngái liên phân hỏi : Trống chiêng ở đâu mà thức dữ thế ? các Tiên chưa dám tàu qua, thì Lôi-thần đứng hầu bên cạnh đã vội thưa rằng : Đó là một tên cương bạo, trước đã tránh khỏi thiên hình, nên nay mới giám cần rỡ như vậy, cúi xin Hoàng-Đế định đoạt ra sao ? Ngọc-Hoàng nghe tàu xong thì Ngái trầm ngâm một lát rồi mới phân bảo : Hư ! Tên kia đã chẳng kinh nề lại còn kháng cự luôn luôn, thực là một kẻ vô thiên vô địa, âu là ngày nay hãy tạm tha thứ, để nó quen thói làm can, rồi sau tai và tự nhiên sẽ đến . Phán xong Ngái liền hạ lệnh cho Thủy-Thần hãy rút nước đi, Thế là Vương lại thoát nạn lần nữa. Nhưng thoát nạn xong rồi thì Vương có về tự đắc, cho gọi tất cả người nhà tập hợp chung quanh rồi bảo cho biết : từ trước đến nay nhờ có Táo-quân ủng-hộ, phàm trên Thượng-Đế nhất cử nhất động, Ngái cũng bảo trước cho hay, thì ta còn lo gì nữa. Thế rồi từ đây Vương lại hết sức kiêu ngạo. Có hôm bắt được một con cua bẻ đem nướng ăn ngay, không cùng Táo-quân như mọi lần trước, Táo-quân tức giận về nỗi vong ân, quyết tâm tìm kế hãm hại để cho bò ghét. Thế rồi bỗng có một hôm Táo-quân hiện lên bảo với Vương rằng : Ngày mai Thiên-lợi lại xuống đánh nhà người đó. Vương hỏi có kế gì không ? Táo-quân bảo : Sáng mai thì người cứ việc ra cây ngoài rương, hễ thấy trời sắp đổ mưa, sấm chớp nổ đây, thì người rủn tay vào trong chỗ kẽm chiếc cây, bên ngoài lấy đoạn cây ngang chân lên hai chân rồi khóa chặt lại, thế là sẽ được bình an. Vương thấy Táo-quân bày cho kẻ sách là lùng như vậy, cũng chẳng biết rằng Táo-quân đã nói đối mình, nên cứ lẳng lặng nghe theo. Ngờ đâu đến sáng hôm sau, lúc trời dỡ mưa, sấm chớp vang tai loe mắt !  Vương muốn tháo chân chạy trốn thì đã chẳng kịp, thành ra bị sét đánh chết tươi, rồi lúc tạnh mưa dân trâu lấy sừng húc đất dắp lên tử thi thành 1 cái gò rất lớn, người làng nhân đó dắp thành phần mộ, rồi mấy năm sau địa phương bị dịch trâu bò, nhân dân rất là xao xuyến, thì hổng một hôm trong thôn có một ông già, sáng sớm đi qua phần mộ, tự nhiên đứng lại quát to lên rằng : Ta đây tức là Cường-Bạo Linh-Thần. Chúng bay biết phép lập miếu phượng thờ, thì ta phù hộ chẳng có việc chi, vì bằng không nghe Ta sẽ giết hết.</t>
+          <t>Trong thời gian ấy Bắc quốc đương bị hạn hàn luôn mấy tháng giới! Vua Tàu ra lệnh cho Sư-Thần các nước đều phải viết văn đảo vỡ. Ông thấy điểm giới còn lâu mới mưa nên tàu rằng: Nước Thần bé nhất xin cho làm lễ đảo sau, để nhường nước lớn đảo trước. Quả nhiên Sư Thần các nước đảo mãi cũng đều vô hiệu, bấy giờ vua Tàu mới triệu đến Ông. Ông tàu rằng: Hạ thần có viên tùy tùng vốn học được phép hô phong hoán vỡ của Không-Minh ngày xưa, nếu sai người ấy cầu đảo tất nhiên sẽ có công biểu, vua bèn cho đi triệu ngay, người ấy (tức anh lái buôn chè) tàu rằng: Thần có một phép nhưng cần phải chọn ngày tốt thì mới ứng nghiệm. Rồi anh lên đi các nơi để xem triệu chúng ra sao. Sau khi nhìn thấy gốc si đã đâm rễ trắng, cỏ gà cũng điểm lóm đốm, biết rằng sập mưa đến nơi, bấy giờ anh mới tàu xin lập đàn câu đảo, quả nhiên mưa xuống âm âm, vua Tàu khen ngợi phong làm Lưỡng quốc Quốc - Sư. Còn Ông thì được phong làm Lưỡng quốc Thượng-thư.</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>將收牛者皆見之村翁歸而道其事鄕遂構祠崇奉自是始得寧居今至封為福神往年有騷客過祠下題詩云二五鍾靈象貫殊深霄黑漢應嘉符赤脂煉藥雷何畏白日乘桴水不虞香火永存光祿典泰盤默祻壯玉都古云敬遠今臣味君子休將辨有無</t>
+          <t>公善辭命應對名聞兩朝皇帝欲晉之使教太子公難之不敬遠奏請造一新堂并備鞭模教具皇子出有過輒痛加筆箋矣曰先學禮後文學太後酷愛其子奏請擇導官公以是免歸</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Giữa lúc ấy thì có một bọn chăn trâu nghe thấy như vậy, trở về thuật truyền lại với dân làng, nhân dân bên dựng đền thờ từ đấy mới được yên ổn, đến nay được phong sắc là Phúc-Thần, trước kia có một nhà thơ đi qua ngoài cửa cung vinh một bài thơ rằng : Lạ thay nhị ngũ khi hồn nhiều. Điểm bảo canh khuya tướng mặt đen. Mở nhốt, Thiên-lôi không hoảng sợ. Nước dâng, bê chuối khỏi lo phiền. Trải bao Tự điển còn hương khói. Giúp mãi hoàng đô được vững bền. Kinh viêng đối lời nên ngầm nghĩ. Có, không đứng với nói huyền thiên.</t>
+          <t>Riêng Ông sở trường về từ mạnh ứng đối, vua Tàu muốn giữ lại để dạy các Hoàng - tử; ý Ông không muốn nhưng không giám trái lệnh, nên mới tàu xin cho đặt học đường riêng ra một chỗ, rồi sai sắm sửa các thứ roi vọt, hễ Hoàng-tử nào có lỗi Ông đánh rất đau và bảo cho biết, trước phải học lễ rồi sau mới học văn! Hoàng-hậu vốn yêu dấu con, không thể nhận được bên xin vua chọn thầy giáo khác, thành ra Ông được trở về nước nhà,</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>羅山阮監生記羅山縣有阮姓者，</t>
+          <t>國後任至尚書春江侯陸少保佀郡公致仕耳</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Huyện La-Son có người họ Nguyễn, lúc mới sinh, trong phòng bồng thấy đỏ rực, người nhà tưởng rằng thất hỏa, nhưng lúc vào coi thì chẳng có gì.</t>
+          <t>làm đến Thượng - thư phong Xuân-Giang-Hầu và trước Thiếu-Bảo-Lữ-Quận-Công rồi mới Tri-sĩ hưởng thọ 72 tuổi...</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>生時赤光滿室，</t>
+          <t>傳公卒後國王頒以嗣棺差人會葬今村內猶有遺塚在焉其後人自北歸國王命築室于本社寺及平置庵于其側號國師寺至今香火猶存焉</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Rồi khi lớn lên coi rất đĩnh ngợ;</t>
+          <t>Theo như tục truyền thì lúc Ông mất Vua ta có ban cho một cỗ áo quan bằng đồng, và vua bên Tàu cũng sai quan sang đưa dặm, hiện nay mồ mà vẫn còn thấy ở trong thôn. Còn anh lái buồn theo Ông khi ở Tàu về Vua ta cũng sai dựng nhà ở bên cạnh ch a của làng ấy, và lấy danh là chùa Quốc-sur, ngày nay nhang khói vẫn còn.</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>人以為失火，父視之，卒無見火而賴異性謹愿端懿常受業于本社監生之門毎日輒先至酒掃學堂坐必別席不與諸生同坐是年近鄉試科其師與之就憲便官析出稍通一各意使官見立命坐日縱本處取中一各亦當取許但他時得志自蒙記憶</t>
+          <t>在曰營接這跡內有一二事頗淡訛傳但得子公族人之言且參諸村邑高年所道來無異故畧記之以俟大德君子焉</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>tính lại ôn hòa ngay thẳng, cha mẹ cho sang thụ nghiệp một vị Giám-sinh cũng làng, hôm nào cậu cũng đến trước, quét rửa nhà trường, đến lúc vào học thì cậu ngồi riêng biệt một chiếu, chứ không ngồi chung với bạn học trò, vì thế nên vẫn được thầy chú ý hơn hết. Thế rồi chẳng bao lâu nữa đến khoa thi hương, thấy dấn cầu sang giới thiệu với quan Hiến-Sư xin cho được dự một tên trong kỳ xảo-thông. Hiến-Sư trong thấy vội vàng vái chào mọi người, ôn tôn nói rằng: Bồn chúc lấy đồ một tên chẳng có ngại chi, mong rằng sau này đặc chi sẽ thơ đến cho.</t>
+          <t>Xét sự tích này bên trong cũng có vài việc hầu như ngoa truyền, nhưng đó là những câu của người trong họ Ông sau này thuật lại. Và các bô lão ở vùng lân cận cũng đều kể lại như thế. Cho nên mới ghi lại đây để đợi các vị quan tử sau này chấp chính.</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>憲官曰我昨日夜夢見一人來謁前道有銅柱斧鉞旌旗僕杖皆五者其隨從軍士約二萬人直至廳前謂曰今欲應考稍通不審官肯許一名否俄而醒覺想愛中所見端的是人不審將來做何等事業是科院公八場果中第一未幾無病而終但精氣不散家人常見倏然往來猶如平日每有求必應大著靈異其後有鄉人舟行至神海口於是舟中卒倒後時方頸因語人曰我見阮醫生乘舟一葉黃袍一帶侍衛甚嚴召至罰謂曰某原承上帝命降生人世作該帝王但方今收福旅方隆不可與竪立故復朝帝所別生他國今其從北去矣</t>
+          <t>范鎮杜注記</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Thời thì vị Công-Sinh mới hãy tạm ra ngoài, để thấy ở lại một lát cùng ta nói câu truyện riêng. Khi cậu lui ra ngoài rồi, Hiến-Sư bèn hỏi Giám-sinh về lai lịch của người đệ-tử, theo học đã bao lâu rồi? và sự học văn ra sao? Giám-sinh kể lại một lượt. Nghè Hiến-Sử kề lại giấc mơ kỳ quặc như thế, ông Đồ cũng lấy làm lạ, cáo biết ra về, rồi trong năm ấy cậu Nguyễn vào thi trúng ngay nhất cử; nhưng mà chẳng được bao lâu thì cậu ốm chết, chết rồi mà phần tình khi vẫn chẳng tiêu tan, người nhà vẫn thường trông thấy hình bóng đi lại như lúc sinh thời, cậu khấn việc gì cũng thấy ứng nghiệm. Thế rồi cách mấy năm sau có một người làng đi qua cửa bê Thân-phù, đương ngồi trong thuyền tự nhiên bị ngã thiếp đi hồi lâu, đến khi tỉnh dậy bảo người nhà rằng: Mới rồi ta gặp cậu Nguyễn Giám-Sinh ngồi trong một chiếc thuyền nhỏ, mình mặc hoàng-báo, lưng thắt đại ngọc, có đám thì về đi hầu, cho gọi ta đến bảo rằng: Mở đây ngày trước váng mạng Ngọc-Hoàng thác sinh xuống dưới tràn thế đẳng làm đế-vương nước này; nhưng vì quốc-vương hiện tại phục âm còn bền, vì lẽ anh hùng không thể lường lập, cho nên ta lại trở về Thiên-đình, ngày nay Ngọc-Hoàng lại sai thác sinh ở một nước khác.</t>
+          <t>LIÊN LUYẾN LƯỢNG KHÔI TRANH TỔ ĐẠO,</t>
         </is>
       </c>
     </row>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>既而謂曰新貢士第出其師當番別有說詰憲官即以問這弟子來歷與八門父近學業如何師具道其詳憲官曰我昨日夜夢見一人來謁前道有銅柱斧鉞旌旗僕杖皆五者其隨從軍士約二萬人直至廳前謂曰今欲應考稍通不審官肯許一名否俄而醒覺想愛中所見端的是人不審將來做何等事業是科院公八場果中第一</t>
+          <t>海陽之嘉福藍橋社范鎮阪林社杜汪里開相鄰舊傳杜汪邑中有女精者往往興大祟作變幻百出祈禱願有驗焉注少時臨窗閱書夜間常見一手自窺前伸八汪知其為妖就質諸同縣老法師法師夜間常見一手自應節伸入汪知其箋效就質詣何舉才之師注師手果不肐縮大將曉窻下哀訴曰公當大貴我眉戲耳何忍至此極也</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Hiến-Sư nghe xong bảo Giám-sinh rằng: Đêm trước tôi năm mơ thấy một người xin vào yết kiến, mà đoàn tiền đạo lại có quân sĩ vác phù việt bằng đồng, và có cờ quạt nghi về như một vương-giả, còn đoàn quân sĩ theo sau thì có đến hơn hai vạn, khi tiến vào cửa sảnh nói với tôi rằng: Muốn xin ưng cử kỳ thì xảo-thông, chẳng hay quan ngài có cho được dự một tên chẳng tá? Bây giờ nhớ lại cái người trong mộng, chính là cái cậu học sinh mới rồi, chẳng biết sau này cậu ấy làm nên sự nghiệp to tát đến đâu.</t>
+          <t>Phạm-Trần ở xã Lam-Kiều thuộc huyện Gia-Phúc và Đỗ - Uông ở xã Đoàn - Lâm hai làng giáp với nhau. Tục truyền rằng: trong ấp Ông Uông có một con nữ yêu tình thời thường hiện hiện, tác yêu tác quái biến ảo khôn lương! dân làng yểm đảo mãi mà vẫn vô hiệu. Về phần Ông Uông lúc còn niên thiếu, một đêm đường ngời đọc sách ở trong cửa sổ, bỗng thấy phía ngoài có một cánh tay thò vào. Ông đoán biết là tay con nữ yêu, sáng sớm hôm sau đến hỏi Ông pháp sư già cùng làng. Pháp sư ấy bảo: Từ nay về sau hễ thấy nó thò tay vào thì cậu lấy chỉ ngũ sắc buộc lại, tất nhien nó không biến được. Uông nghe pháp sư bảo thế với về sắm sửa đội đến canh khuya lại thấy con yêu thò cánh tay vào. Cậu liên lấy chỉ ngũ sắc buộc ngay vào song cửa sổ, tư nhien tay nó cưng dò, không sao rút ra được nữa, cho mãi đến lúc gần sáng. Nó đứng bên ngoài khóc lóc van lon. Tôi thấy ông sắp trở nên đại qui, nên mới đưa bốn thế thôi, sao mà ông lại nhẫn tâm như vậy?</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>煩為歸報家人不必思念言詭雝然而去瞧見來乃是一魚</t>
+          <t>汪曰以我之果做狀元否曰狀元已有范生公當次之汪曰汝有甚灵物即共我觀我便敵汝俄聞嘔吐聲忽見一物似玉在紋手中精光奪目汪有取吝之師解其繫線自是天邑中不聞怪而泣嘆曰精通舟詞章一出人以賞陳吐王稱之在場屋間甚有聲譽鑲常不逮</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Vậy phiền người về nói với gia-nhân của ta cũng đừng nên thương nhớ nữa.</t>
+          <t>Ông hỏi: vậy như tài của Ta đây thì có dỡ được Trang-Nguyen hay không? Nó đáp: Trang-nguyen thì đã về họ Phạm, còn ông chỉ dỡ thứ hai mà thôi! Lại hỏi: vậy mi có vật gì thiêng liêng hãy đưa đây ta coi thử, rồi ta sẽ cởi trói cho. Ông vừa hỏi xong thì thấy nó thở ra một vật gì ở giữa bàn tay trong như viên ngọc sáng chói cả mắt. Ông liền cảm lấy bỏ ngay vào mồm nuốt trúng, rồi mới cởi trói cho nó biến đi. Về sau không thấy tác quái gì nữa, mà ông thì cũng từ đấy về sau học một biết mươi, vẫn chương lại càng xuất sắc, ai cũng khen tài nhà ngọc phun châu, khi cùng tập ở các trường ông Trần vẫn không theo kịp.</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>既而振其家具以前事苦之自是不見頭應按此與亂鬚將見唐太宗而輒哀者乎</t>
+          <t>光靈員員意崇年號丙辰科會試時年共二十四歲同年同榜至庭試日汪見全題皆素慣今番首選醫我無驗</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Nói xong thì lại bay đi, đến khi người ấy chợt tỉnh mới biết là một giấc mộng, lúc về bên đêm truyền ấy kể lại cho nhà cậu nghe, rồi cũng từ đấy không thấy hiện linh như trước nữa. Xét ra truyện này cũng giống như truyện Cù-Tu Tướng-quân khi nhìn thấy Đường-Thái-Tông, tự nhien khóc rất thâm thiết (xuất xứ ở cuốn Hương-Đại? ) như vậy mới biết ngôi báu phải có mệnh trời, không thể đem tri lực ra mà cầu cạnh được, bởi vì theo dùng đạo-lý thì dẫu trời cho giáng sinh cũng phải nhượng người có đức.</t>
+          <t>Thế rồi đến năm Quang-Bửu thời Mạc Phúc-Nguyên (1554-61) gặp khoa thi hội năm Bình-thin, hai ông cùng 34 tuổi, là bạn đồng niên đồng bằng, đến hôm cùng vào thi đình, ông Uông nhận thấy đầu bài nào mình cũng thuộc lòng hết thấy, tin chắc phen này sẽ nắm vững giải khơi - nguyên.</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>亦相類是其神器有命不可以智力求蓋以道推之則雖天帝降生方且讓他一頭近世么麼之輩不自揣量卻于井底窺天晴圖望外亦有離身之禍世之亂賊可不成哉</t>
+          <t>時鎮在籠中彷彿見傍有兩人一稱韓琦一稱東方朔附耳讀之滔滔不竭鎮寫之不發聞靜謂琦曰須使任致病以減其力俄見杜汪抱腹申吟不能下筆迨鑲過一段泣病方愈故習燕雖多而日力不足既而臚唱鎮中獄元酒中榜眼顯喜語人曰吾今壓倒杜注矣。汪深愬之。</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Thế mà gần đây những bọn yêu quái, chẳng lượng sức mình, lại ngồi ở dưới đây giếng để tròng lên trời, lo toàn cướp ngôi tôn quỉ, chẳng sớm thì muộn rồi cũng mang lấy cái nạn diệt vong, sao chúng lại chẳng soi tấm gương đó để mà tu tỉnh vậy.</t>
+          <t>Còn phần ông Trần lúc đương viết bài ở trong lều, bồng thấy thấp thoáng có hai bóng người đứng ở bên cạnh, một người tự xưng là Đông - phương - Sóc một người tự xưng là Hán-Kỳ (có bốn chép là Phú bất và Phạm-trọng-Am) ghé vào bên tai đọc lên thao thao bất tuyệt, khiến ông Trần không sao chép kịp. Thấy vậy ông Sóc bảo ông Kỳ rằng: chúng ta phải làm thế nào cho Uông bị ốm để giảm sức văn thì mới thắng nói. Thế rồi chỉ trong chớp mắt ông Uông ốm bụng kêu đau, không sao cảm được bút viết, cho mãi đến khi ông Trần viết xong một đoạn, bấy giờ ông Uông mới khỏi, thành ra sách vở văn thuốc, nhưng lại không đủ thì giờ, cho nên sức văn hơi kém. Đến khi truyền lò (xương danh) ông Trần đỗ Trạng-nguyen, Ông Uông phải đứng thứ nhì tức là Bảng-Nhơn. Ông Trần tỏ vẻ hoan hỉ nói rằng: phen này ta đã đề nói Đỗ-Uông. Làm cho ông Uông tức bực vô cùng.</t>
         </is>
       </c>
     </row>
@@ -5201,12 +5201,2902 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>亦相類是其神器有命不可以智力求蓋以道推之則雖天帝降生方且讓他一頭近世么麼之輩不自揣量卻于井底窺天晴圖望外亦有離身之禍世之亂賊可不成哉</t>
+          <t>榮歸日驅繾綣而行。與鬩並驅爭先。不背公讓至獲澤杜蓮溪中橋人曰素聞杜范二公大各今見同日榮歸請詠橋詩一首頒汪相異曰橋屋十有餘間限過七間成詩詩用一句一禽先成者讓先行不得筆道直顯如約立就詩國語八句馬上讀之人皆藥服泣曰這詩已平日素成非臨時所張得吾何讓焉又齊道而行</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Thế mà gần đây những bọn yêu quái, chẳng lượng sức mình, lại ngồi ở dưới đây giếng để tròng lên trời, lo toàn cướp ngôi tôn quỉ, chẳng sớm thì muộn rồi cũng mang lấy cái nạn diệt vong, sao chúng lại chẳng soi tấm gương đó để mà tu tỉnh vậy.</t>
+          <t>Đến hôm hai người cùng về vinh quí bài tờ, Uông vẫn đóng ngựa đi ngang với Trần, chứ không chịu nhường, khi về đến chợ Bồng - Khê thuộc xã Hoạch-Trạch, người ở bên cầu thường vẫn nghe tiếng hai ông, ngày nay thấy cùng vinh quí, nên họ xin một bài thơ vinh cầu để làm kỷ niệm. Hai ông thấy dân sở tại xin thơ, lập tức giao hẹn với nhau rằng: chiếc cầu có hơn 10 gian, vậy khi qua được 7 gian thì phải làm xong bài thơ, mà thể thơ thì mỗi câu có một giống cảm, nếu ai xong trước thì sẽ đi trước, còn xong sau thì không được phép tranh cạnh. Hai ông đặt điều kiện xong rồi cùng tiến bước, chẳng ngờ ông Trần ngồi trên lưng ngựa đọc luôn ngay được 8 câu, khiến cho ai cũng kinh phục, riêng có ông Uông thì lại bảo rằng: Thơ ấy làm sẵn từ lúc ngày thường, chứ lúc làm thời thì làm sao nỗi, tôi chẳng chiều nhường. Nói xong ông lại cứ đi ngang hàng,</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>HVB_003_0281</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>至明倫社有伊社人屋字是新富途請曰鄙人再構新家幸逢兩貴台經過乞惠之佳句燕歌屋生輝鎮應曰</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>khi về đến xã Minh-Luân, trong xã có người vừa làm được ngôi nhà mới, đón đường thưa rằng: chúng tôi mới dùng xong nhà, may gặp được hai quý vị qua đây, giảm xin hai vị ban cho mấy câu để tặng về đẹp. Ông Trần ứng khẩu đọc luôn:</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>HVB_003_0282</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>年年增富貴日日壽榮花</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Năm năm tặng phu quý ngày ngày hưởng vinh hoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>HVB_003_0283</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>古人有此句今日賀新家</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>người xưa có câu ấy nay mừng mới làm nhà,</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>HVB_003_0284</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>洹吟沱曰賛羙之辭此等句盡之矣豈復以加而頒矣口輒成自非神吟鬼助轟然若是自是始讓顱先行</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ông Trần vừa mới ngâm xong, ông Uông nói chận ngay rằng: đó là những chữ tân tung, chỉ dùng nửa câu cũng đủ can chi mà phải làm nhiều, rồi ông cũng vẫn không phục, Nghè ông Trần ngâm xong bài thơ trên đây, ông Uông mới đặt này mình nói rằng: quả thực xuất khẩu thành chương, nếu không có quỉ thần trợ lực thì làm sao nổi, từ đấy chịu nhường để cho ông Trần đi trước chó không đi ngang hàng nữa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>HVB_003_0285</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>後潛至監來杜著鎮祖墓見有二土堆俗曰兩袖童附耳泣致指之曰從來勝我數番以有那神童附耳之功即用腳跟擊手土堆自是顫從耳病廢商治弗效有人以汪轡車土堆之事語鎮者鎮即訢于朝署朝論汪謝鎮祖墓鎮病尋愈</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Nhưng rồi về sau ông Uông lên đến Lam-Kiều xem ngôi mộ tò của nhà ông Trần, thấy có hai cái gò đất ở sát hai bên, tục gọi là đống thần ẩn ẩn thần đồng phụ nhi, ông bên chi vào đống đất bảo rằng, trước đây y thằng nói ta mấy phen là nhờ cái đống đất này. Nói xong ông lấy gót chân nện vào hai đống đất ấy thế mà không biết tại sao cũng từ hôm ấy ông Trần bị chứng điếc tai, thuốc thang chạy chữa vẫn không công hiệu, về sau cò người dem viêc ông Uông dập vào gò đất thân đồng mách với ông Trần, ông bèn tố cáo lên vua. Vua bắt ông Uông phải làm lễ tạ long thần, bấy giờ ông Trần mới khỏi,</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>HVB_003_0286</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>其後試東閣以文武並用詩題用五言三江為韻取十五韻鐵復中第一泊第二始興徵時與江對飲酒至半酣相戲為酒賛酒先唱曰</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>rồi sau Triệu dinh có mở khoa thì Đông-Các, đầu đề tho là (Văn-Võ,Tinh-Dụng), dùng thể ngữ ngôn, hạn 15 văn, trong thơ Ông Trần có hai câu rằng:. Xưng Cao phong tự khỏi. Diệt Hạng diuh năng giang, nghĩa là khen Cao-Tô giấy tư ấp phong, Diệp Hạng quân sức hay cử đỉnh. Kỷ này Ông Trần lại được đứng hàng nhất, mà Ông Uông vẫn phải thứ hai. Nhắc lại lúc chưa đỗ đạt, có hôm hai Ông cùng ngồi uống rượu, khi đã giờ say, thách nhau làm bài. Từ-Tán, Ông Uông đọc trước:</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>HVB_003_0287</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>有潰用潰無潰用火所用咸宜無施不可</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Hữu huynh dụng huynh, vô huynh dụng hòa. dụng tắc hàm nghi thì vô bất khả: Có huynh thì uống rượu huynh, không huynh thì uống rượu hòa, uống đều say xưa gặp chẳng hay chớ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>HVB_003_0288</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>頤續吟曰</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Ông Trần lại đọc tiếp rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>HVB_003_0289</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>酒潰則歡火潰則絕有遠此言天地日月</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>,, Từ hoang tắc âm, từ hòa tắc tuyệt, hữu vi thử ngôn thiên địa nhất nguyệt. Rượu vàng thì uống, rượu hòa thì thôi, vì chẳng như lời, có đất trời soi,</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>HVB_003_0290</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>識者以是言其立志之珠其後莫七我朝中興汪首出仕至戶部尚書封福神鎮辭歸不仕仕終承政使司</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>xem hai bài tán trên người ta nhận thấy hai Ông lập chí vẫn khác nhau xa. Quả nhiên rồi sau họ Mạc mất rồi. Bản Triệu trung hung thì Ông Uông ra làm quan trước được thăng đến chức Hộ-Bộ Thượng-Thư và phong sắc phục Thần, còn Ông Trần thì không chịu ra cho nên chỉ làm đến chức Thừa-Chính-Sư mà thôi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>HVB_003_0291</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>探花廓佳記</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>CHƯ TÀO HỘI NGHI, PHÙ-KHÊ THIÊN QUÁCH-CHÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>HVB_003_0292</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>未生時有接近人以慣偷盜為業一日就公邑內行盜會人未定時潛八廟祠後假卧不覺薰睡至鷄鳴方醒披衣徵起忽聞前回喧鬧有人自廟外而入在廟內有人迎問曰今番何事遲歸</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Người làng Phù-Khê thuộc huyện Đông-Ngan. Nói về lúc Ông chưa sinh ra đời, thì ở lân cận có một người chuyên nghề ăn trộm, bỗng có một lần mò sang bên làng Ông định kiếm một mẻ. Nhưng vì lúc ấy nhà nào cũng còn thức, nên anh lên vào nằm ở trong miếu, để đợi, chẳng ngòi lại ngủ thiếp đi. Đến lúc gà gáy anh mới sực tỉnh xốc áo toan di, chợt nghe ở trước mặt có tiếng xôn xao. Và thấy có người từ ở phía ngoài đi vào trong miếu, bên trong có người ra đón hỏi rằng: Phiên này sao về trẻ thế,</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>HVB_003_0293</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>聞有聲曰答適朝士帝與諸曹會談夜命一探花即降伊社有員捧薄奏曰長按伊家福德薄恐不稱此帝命取薄觀之良久判曰雖然知此但業已許之不必換改如他德果薄來時更有定奪焉以此故遂歸耳</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>đáp: Vừa rời lên châu Thượng-Đế, hội nghị với các Nam - Tào, định rằng trong đêm hôm nay sẽ cho một vị Thám - Hoa giáng sinh ngay ở xã này. Rồi lại thấy một viên quan tay nàng quyền sở tàu rằng Hạ: thần xét thấy phúc đức nhà ấy mông lẫm sợ không xưng chút nào, giám xin Hoàng-Đế định lại. Hoàng-Đế nghe tàu bên cầm cuốn sở coi qua một lát rồi mới phân rằng: đầu thế nhưng mà đã cho rồi, nhẽ nào lại còn canh cãi. Vì thử nhà ấy quả nhiên phúc bạc, rồi sẽ định đoạt về sau v. v. Vì thế cho nên hôm nay tôi về hỏi trẻ một chút.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>HVB_003_0294</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>時人在廟後竊聞具得其詳當夜不以行為意因徧往邑中探聽何宋生子見公生於是夜災早即公家具導前事一通預以為賀</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Lúc ấy anh kẻ trộm ta hãy còn nụ ở trong miếu, nghe lồm được bấy nhiêu câu. Anh bên bỏ ngay ý định ăn trộm, rồi vào trong ấp để thám thính xem trong đêm ấy nhà nào sinh đẳng con trai. Khi thấy chỉ có nhà Ông, thì sáng hôm sau nữa anh đến tận nhà kẻ lại câu truyện như thế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>HVB_003_0295</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>生而頴異人稱袖童及長以文舉子各正和年號、癸亥文科中進士第一甲三名</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Còn về phần Ông ngay lúc mới sinh trong đã rình ngộ rồi sau nói tiếng Thần-đồng! Đến khi lớn lên vẫn học lại thêm lừng lẫy! Vào khoảng niên-hiệu Chính-Hòa (1680 - 1705) khoa thi năm Quí-Hợi, thì đồ Tấn-sĩ đệ Nhất giáp đệ Tam danh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>HVB_003_0296</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>公在朝適內閣談政事餘昭祖康王問侍臣曰韓信遺燕書曰有曰白鹿抱泉事跡何在卿等能知之乎群臣皆莫能對公跪對曰跡詳見漢書王郎命索公家書來觀之稱其簿學</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Đến khi làm quan tại triều, nhân lúc nhân đàm ở trong Nội-các Chiêu-tổ Khang-Vương (Trinh-Cần) hỏi các quan hầu về việc ngày trước Hàn - Tín gởi thơ cho Yên-Vương trong có câu rằng: Bạch lộc bảo tuyên, thì sự tích ấy ra sao. Quân thần không ai đáp được, chỉ có một mình Ông đặt gởi tàu rằng: Diện tích ấy biên rỡ trong Hán-thư. Vương sai về lấy gia thư của Ông vào xem quả nhien có thực, Vương khen là người học rộng nhớ nhiều.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>HVB_003_0297</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>時公方以事被遣未幾除清花聲同仕至寺癖以風疾不視朝始信從日祠神對語之聽</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Giữa lúc ấy Ông đương mắc phải việc gì nên bị khiên trách, nhưng rồi chỉ sau ít lâu thì được bổ chức Đốc-đông tại tỉnh Thanh - Hóa, tức là ưu thưởng cho Ông về điểm bác học. Rồi sau Ông làm đến chức Thị-lang, vì có bình phong nên không vào triều chính, bấy giờ mới rỡ câu chuyện trong miếu ngày trước quả nhien có ứng nghiệm vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>HVB_003_0298</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>參議武登顯記</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>MỖI KHOA LIÊN ĐĂNG, MỘ-TRẠCH ĐẠI</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>HVB_003_0299</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>多者至八九名少者不下四五十名連名覆中率以為常而午年科保提調官其左夫阮澧性頗廉直以慕澤從來多中必有私巧者在乞為海陽提調以察之朝延協議考至第四場公命攝地為安合士人坐在穴中籠蓋其上防守其甚嚴</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Triệu vua Lê - Thánh - Tông vào khoảng niên hiệu Vĩnh-Thọ (1658-62 tức là thời Lê-Thần-Tông thì phải), văn học nho phong dương lúc thịnh hành, riêng các sĩ tử của lang Mộ-Trạch Hải-Dương, khoa thì Hương nào cũng đỗ đến 8, 9 người, ít nhất cũng 4, 5 người, chẳng một khoa nào bỏ trống; cho nên cũng lấy làm thường. Nhưng rồi đến khoa Binh-Ngo, có quan Tả-sử là Nguyễn-văn-Phong giữ chức Đề-diệu Trưởng thì, tính Ông thanh liêm và rất ngay thẳng, nay Ông xét thấy khoa nào Mộ-Trạch cũng đỗ đạt nhiều, ngòi rằng họ có mánh lới gì chẳng, nên khoa thì này Ông xin làm Đề-diệu Hải - Dương để kiểm soát thử. Được Triệu-đình chuẩn y, Ông ra tới nơi chấm xong 3 kỳ đến kỳ thứ 4, Ông sai đào riêng từng lỗ rồi dựng nhà lên trên, để cho sĩ-tư ngồi ở dưới lỗ, trên miệng lỗ đều có chụp chiếc lồng thưa, phòng thủ rất là nghiêm mật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>HVB_003_0300</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>迨同考院考訖送來公無嚴飾覆考官詳看文勢精純全篇無瑕者方得挑取而覆考擇得十卷公親自評之汰去四卷只取六卷</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Đợi khi các quan So-khảo chấm xong đệ văn bài đến, Ông lại trao cho Phúc - khảo kiểm lại, xem những quyền nào văn lý đặc sắc, toàn thiên không có vết tích mới phê cho đồ v. v. Các quan Phúc-khảo theo lệnh chọn lọc rất kỹ được có 10 quyền đệ lên Ông xem lại, rồi thái đi 4 quyền còn lấy được 6 quyền,</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>HVB_003_0301</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>既而呼各優頂一名皆來澤社武登顯首科纔十八歲第二名某澤社人第四建亦慕澤社人其三名乃永賴古庵唐安王司青林樂實人也一科續取六各而纂澤居其半同院取卷觀之見三卷文理各殊不相蹈襲深嘉嘆賞貞始細信慕澤為世尚儒流文物之地文衡公器初非本私</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>thế rồi đến khi họp phách chỉ có một người đứng vào ưu hàng là Võ-Đăng-Hiền ở làng Mộ-Trạch được đỗ Thủ - khoa, năm ấy mới 18 tuổi. Đến người được đỗ thứ nhi và người thứ tư cũng đều quê ở Mộ-Trạch. Còn người thứ 3 thứ 5 thứ 6, quê ở Cờ-Am thuộc phủ Vĩnh - Lại và làng Ngọc-Cục huyện Đường-An, cùng xã Lạc-Thực huyện Thanh-Lâm. Thế là Khoa ấy có 6 người đỗ thì làng Mộ-Trạch chiếm được 3! Khảo quan đem quyền xét lại thấy văn các quyền chẳng hề giống nhau chút nào. Bấy giờ Ông mới tin rằng Mộ - Trạch quả là một nơi danh nho kể thế, mà văn chương có mục thước chung, trước kia không hề tư vị,</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>HVB_003_0302</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>其後武盞顒宏詞科中優一會試賦優士分但中三場嘗以未遊青雲為限官至北京處參議以親老辭官歸養設場教授及其門生擢大科儒者者稱為尊師至今猶歆為裳</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>rồi sau Ông Đăng-Hiền lại trùng ưu hàng, khoa Hoành-từ, 10 khoa luôn trùng tam trường lấy làm chưa thỏa chí nguyện sau làm đến Kinh-Bắc Tham-nghi, rồi vi có cha mẹ già xin từ quan về phượng dưỡng, học trò rất đông mà đồ đại khoa cũng nhiều. Vi thế học giả lúc ấy đều coi như bậc Tôn-sư vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>HVB_003_0303</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>節義</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>TIẾT NGHĨA</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>HVB_003_0304</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>陳朝樁景詞其祖汝猷淳祿老疎人也為諒江知府娶唐安慕澤武氏之女因以妻鄕居焉</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Lê-Cảnh-Tuân.— Triệu nhà Trần có Lê-Cảnh-Tuân, ông nọi tên là Nhữ-Du người huyện Thuần-Phước xã Lão-Lạt; khi làm Tri-Phủ Lạng-Giang kết duyên với con gái họ Vũ của làng Mộ-Trạch thuộc huyện Đường-An, nhân thế, mới lập gia-cư ngay ở làng vợ, tức là Thê hương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>HVB_003_0305</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>詢覓太學生少與青沔縣扶助社內裴伯耆相善陳末胡墓位伯者如燕京乞師伐胡明遣張翰沐晟等分道而來伯耆為先鋒向道拾逆胡父子送同明人拜伯耆為參護</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Đến thời ông Tuân, khi đã sung chức Đại-Học-Sĩ, vì lúc còn nhỏ có quen với Bùi-Bá-Kỳ người xã Phù-Nội thuộc huyện Thanh-Miện, gặp lúc cuối đời nhà Trần bị Hổ-Quý-Ly cướp ngôi, Bá-Kỳ sang bên Yên-Kinh xin quân về đánh họ Hổ. Nhà Minh bên sai Truong-Phu và Mộc-Thanh chia đường kéo sang, Bá-Kỳ nhận chức Tiên-phong để hướng đạo. Sau khi bắt sống được cha con họ Hồ đem về bên Bắc quốc, nhà Minh bên cho Bá-Kỳ giữ chức Tham-Nghi,</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>HVB_003_0306</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>諭郎上萬言書于伯耆其畧曰</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>lúc ấy ông Tuân có gửi cho Bá-Kỳ một bức Vạn ngôn thư (bức thư có hơn một vạn chữ) đại lược như sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>HVB_003_0307</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>若能立陳為上策僕願為佐龍中藥物任足下所用</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Nếu ông có thể lập lại dòng dõi nhà Trần? Đó là thượng sách, thì tôi xin làm các vị thuốc ở trong tử để ông sử dụng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>HVB_003_0308</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>為陳辭官為中策僕願執籩籩豆奔走任足下所使</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Hai là: Nếu ông nghĩ đến nhà Trần, mà giả chức vị cho nhà Minh, đó là trung sách, thì tôi xin cầm trở đầu (dở thờ) chạy theo, để tùy ý ông sai khiến!</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>HVB_003_0309</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>若貪其禄位斯為下矣則僕樂鈞耕間而已</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Ba là: Nếu ông còn tham tước lộc nhà Minh, đó là hạ sách, thì tôi sẽ đi câu cá hoặc đi cày ruộng mà thôi!</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>HVB_003_0310</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>伯耆不聽父伯耆犯明法明人籍其家得其書目詢變姓各遊匿後明人於我國立學校諭往觀之明人見其才學以為教授饒而知萬言書日乃誨師依郡補師去其三子太顚少顚叔顚皆願從行送至開門詭語之曰一當從二次且囘已奉舉以報君父之答眾子慟哭拜別</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Bá-Kỳ chưa kịp dùng. Cách ít lâu Bá-Kỳ phạm pháp bị quan nhà Minh tịch biên gia sản, bắt được bức thư ấy, nhưng ông đã thay đổi họ tên lánh đi nơi khác, về sau nhà Minh đặt xong nên thống trị nước ta, rồi mới thiết lập ra các học xã, bấy giờ ông mới ra để xem việc giáo hóa thế nào? Chẳng ngờ các quan nhà Minh thấy ông là người có tài văn học liên cho ông làm Giáo-Thụ, nhưng rồi chúng biết chính ông đã viết bức thư vạn ngôn, nên chúng bắt ông giải về bên Tàu. Lúc ấy ba người con trai của ông tên là Thái-Điên Thiếu-Đinh Thúc-Hiên đều xin đi theo, khi tiến đến Âi Nam-Quan, ông bảo các con: Thời để cho một mình con trưởng theo ta là đủ, còn hai con thứ thì nên trở về trong nom hướng khỏi để bảo thù cho Vua, cha! hai con vàng lời bài biệt rồi quay trở lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>HVB_003_0311</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>詢其太顯至北京明人訝之曰爾教伯耆立陳後陰國不軌何也詢曰我南人志存南國跖狗吠非其主又何問明人怒送于金陵獄父子皆卒于獄中</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Khi ông cùng Thái-Điên sang tới Yên-Kinh, các quan nhà Minh hỏi rằng: My xui Bá-Kỷ lập lại con cháu nhà Trần, âm mưu làm việc phi pháp là cờ làm sao? Ông đáp: Ta đây là người nước Nam, nên phải quyết chí bảo tồn Nam quốc, con chó của tên Đạo-Chích (kẻ trộm) còn biết cẩn người không phải chủ nó? Vậy thì các ngươn còn hỏi làm chi. Quan Minh nghe xong lấy làm tức giận bên đem giam ông vào nơi ngục thất ở Thanh Kim-Lăng, rồi hai cha con bị chết ở đó!</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>HVB_003_0312</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>掾萬言書與朱安七斬疏皆忠誠所發陳樸宗先安上疏乞斬七侯臣時稱七斬疏後芸棠故胡公作越鑑有六萬言之書忠貫印月七斬之疏義動鬼神</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Xét thấy bức Vạn-ngôn-Thư của ông cùng với bản Thất-Trầm-Sơ của Chu-Văn-An đều do một tấm trung thành phát biểu ra ngoài cho nên trong bộ Việt- Giám của Tương-Công mới có câu rằng:,! Vạn ngôn chi thư Trung quân nhật nguyệt. Thất-Trầm chi só nghĩa động quỉ thần. Nghĩa là: bức thư Vạn-ngôn lòng Trung soi thấu nhật nguyệt! Bồn só Thất-Trầm chữ nghĩa động tôi quỉ thần;</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>HVB_003_0313</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>詠史詩云</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>rồi sau Văn-Hiên Vinh-Sử cũng có thơ rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>HVB_003_0314</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>上庠琴劍一書生三策懐憐許國情</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Gươm dân Tương bằng một thư sinh. Câu nước trong thơ đã hiền minh?</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>HVB_003_0315</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>萬里虜廷終不屈先忠十孝而成名</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Muốn dặm trước thù không chịu khuất? Cha trung con hiếu thấy lừng danh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>HVB_003_0316</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>曾孫光貞有詩云</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Ông Quang-Bôn cũng có thơ rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>HVB_003_0317</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>超延詩禮講明請自勵懸壯士餌寒蹇</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Trước sân thì lẽ đã từng qua? Tráng chi say sưa tự nhủ mà?</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>HVB_003_0318</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>匪朝誠協一拳拳許國策陳三綱常自任</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Bằng bằng quên mình thành giữ một? Luôn luôn vì nước kẻ đáng ba?</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>HVB_003_0319</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>他奚恤鼎饒知餡死亦酣累世亦蒙忠義報光弼盡業振天南</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Cương thường phải nhớ, ngoài chi kẻ? Bình vạc như du, chết cũng thả? Trung nghĩa nói đời cơ bảo ưng? Về vang sự nghiệp nước Nam nhà.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>HVB_003_0320</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>其後明人姜黃福鎮安南設場教學以收我國人才穎題兄弟竝往受業黃福愛之認為己子</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Thế rồi cách ít lâu sau nhà Minh sai Thượng-Thư Hoàng-Phúc sang làm Đô-hộ An-Nam, Phúc liên mở trường dạy học để thu nhân tài, bấy giờ anh em Thúc-Đinh cũng xin nhập học, được Phúc yêu mến nhận làm con nuôi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>HVB_003_0321</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>忽一夜雨電壞牆發屋明日黃福出城南玩景口占一旬云</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Rồi bỗng một đêm mưa bão làm đổ nhà cửa! sáng sớm hôm sau, Hoàng-Phúc thân ra ngoài thành để xem quang cảnh, buột miệng đọc một câu rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>HVB_003_0322</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>照朝風雨家家額壞舊牆垣</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>. Tác triều phong vũ gia gia đồi hoại cựu viên tường? Nghĩa là: hôm qua gió mưa, tường vách muốn nha cùng đổ la liệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>HVB_003_0323</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>以喻南國被侵必致額壞額頸即對云</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Xét thấy câu thơ ứng khẩu trên đây, Hoàng-Phúc có ý nói nước Nam ta đã bị xâm chiếm thế tất là phải tan hoang? vì thế Thúc-Hiên cũng ứng khẩu đối rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>HVB_003_0324</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>今日乾坤震處發榮新草木</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>. Kim nhật càn khôn xử xử phát vinh tán thảo mộc. Nghĩa là: Hôm nay trời đất cô cây bốn mặt càng thêm tỏ vẻ tốt tươi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>HVB_003_0325</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>黃輝是簡高見人聞此句望天嘆曰安南已有聖主出乾坤方南國復還南國我亦不久且歸矣二子盡往從之以圖立功穎顯遂依報尋至愛州已見我大祖蘇山奮勵兄弟皆來歸附未幾大破北兵沐晟黃福等投降之和太祖縱之北還</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Hoàng-Phúc là người cao kiến khi nghe học trò đối lại như vậy, thốt nhiên ngửa mặt lên trời than rằng: Thôi! An-Nam đã có Thánh chúa giáng sinh tại phương càn khôn (dong nam) nước Nam lại được trả về cho người nước Nam, chẳng bao lâu nữa ta cũng trở về Bắc quốc? vậy thì hai con sao chả đi tìm người đó để lập công danh? Anh em Thúc-Hiên nghe lời Hoàng-Phúc chỉ giáo ưư vậy, bèn từ biệt thầy để vào Ái-Châu dăng tìm Thánh chúa? khi vào tới nơi thì Lê-Thái-Tổ đã khởi nghĩa ở Lam-Sơn rồi. Anh em bèn xin ở lại phò tá, rồi chẳng bao lâu, quân Minh bị bại, Mộc-Thanh Hoàng-Phúc xin hòa. Thái-Tổ tha cho trở về Bắc quốc,</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>HVB_003_0326</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>顔顔等戲師歸國至交開相告別同跪請曰儀等蒙作育久矣未審何時復頒教誨請指示陰憤吉昌歸塟先人是吾師之賜也</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>lúc ấy anh em Đinh-Hiên xin tiến chân thầy đến Ái Nam-Quan rồi mới thưa rằng: Chúng con nhớ ơn chỉ giáo đã lâu, ngày nay Tôn-sur trở về cớ quốc, chẳng biết bao giờ lại sang? vậy xin Tôn-sur chỉ bảo cho mấy người đất đề táng Tô tiên? đó là cái ơn đặc biệt vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>HVB_003_0327</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>並福曰我非忘了試觀二子之志耳前日噐心一穴在亦邑兌邊桃樸頭向銀帶日月扶裔天馬在其西旁正乎年我已埋下木板歸而尋之囑其子孫後有北使遲歸便可鑿這馬足郎當反轡二人拜辭而回</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Hoàng-Phúc đáp rằng: Việc đó nhẽ nào Thầy lại không nhớ? chẳng qua là muốn thử gia các anh đó thôi? vậy nay Thầy bảo cho các anh biết, nguyên trước Thầy đã lưu tâm một huyết ở ngay phía bắc làng anh, cục ấy gởi vào chiếc mũ trong ra chiếc dai vàng, nhật nguyệt đóng ở hai vai, ngựa đi sứ đông tại phía Tây, còn mộ thì toạ chữ Tỷ hướng chữ ngo, phía dưới Thầy đã chọn sẵn một mảnh vân gỗ làm ghi, vậy khi trở về các anh nên tìm ngay đến chỗ đó, và nhớ hẹn con' cháu rằng: Sau này nếu có sang Sư mà lâu không trở về, thì cứ dục khoét vào chân con ngựa ấy, tự nhiên Sư giả sẽ được về ngay? Hai người nghe xong bài từ Hoàng-Phúc rồi quay trở lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>HVB_003_0328</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>時太祖已矣天下擇人北使無敢行者少頴以父兄之故敵然請往太祖許之拜審刑院事、秦陳情表于明其畧曰</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Lúc ấy Thái-Tổ đã bình định xong thiên hạ, Ngái muốn tuyển một Sư bộ sang Tâu nhưng chẳng ai dám xin đi, riêng có Thúc-Định vì muốn tiện thể thăm đó tin tức phụ huynh nên mới khẳng khái tình nguyện, Thái-Tổ bèn phong cho chức Thâm-Hình Viện-Sự để mang tờ biểu trần tình sang nộp tờ biểu đại lược như sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>HVB_003_0329</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>天地之於萬物雖有雷霆之怒而發生每行乎其間</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Trời đất đối với muốn loài, mỗi khi giạn dữ đầu có ra oai sấm sét, nhưng mà bên trong vẫn ngụ sẵn đức hiểu sinh?</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>HVB_003_0330</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>父母之於眾子雖有笞檳之威而鞠育常存乎其內</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Cha mẹ đối với các con, đầu có dùng đến roi vọt mà on cục dục vẫn dễ trong lòng,</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>HVB_003_0331</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>是以人有疾病未常不呼天地父母此臣子之歷緬陳詞以伸表籲也</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>chả thể mà con người ta mỗi khi gặp sự đau đớn lại kêu trời đất cha mẹ? cho nên ngày nay Thần phải đem câu tâm huyết giải bày để mong soi xét v.v... (Tờ biểu này do quan Thừa-Chí Nguyễn-Trãi soạn).</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>HVB_003_0332</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>寫所作並替代金人二軀各重二百兩至燕京陳于關下懇訴明人恨我國徵殺柳昇之故甄唾罵不問物火頴于門下外漆其兩目不許飲食</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Kèm với tờ biểu kẻ trên lại còn một hộp vàng bạc thay thế hình nhân, bên trong có đựng mỗi thứ là 100 lượng, khi tới Yên-Kinh, vua tới nhà Minh cảm thù về việc sát hại Liễu-Thăng nên chỉ quát mắng chứ không thu nhận, rồi lại bắt giam Thiếu-Đinh ở ngoài công thành, và bồi son kín cả hai mắt không cho ăn uống gì cả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>HVB_003_0333</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>時黃福八朝見之知其少穎嘗取貓餅藏穀中每過即授之三月餘不死明人以為神始受貢禮使囘復命</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>May sao lúc ấy Hoàng-Phúc vào triều biết là Thiếu-Đinh, nên thường dẫu bánh mi ở trong mũi giầy, mỗi khi đạo qua hắt cho Thiếu - Đinh, vì thế nên không chết lả. Triều thân nhà Minh thấy hơn 3 tháng mà sao Thiếu-Đinh vẫn sống như thường, thì cho là bạc thân nhân hấy giờ mới chịu nhận lễ, và cho trở về báo tin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>HVB_003_0334</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>火穎因尋父兄不知沒處至于僧奇只見一詩一畫存焉即將固本鄉虛墓之後諫太祖忤旨降禮部員外郎光貢有詩云</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Về phần Thiếu-Đinh sau khi đã được trả lại tự-do, lập tức đi đạo các nơi hỏi thăm tin tức cha anh ngày trước, nhưng cũng chẳng biết mất ở nơi nào? Sau cùng đến một người chùa thì thấy có một tập thơ để lại, ông bên mang về bồn quốc và làm ma chay theo tục hư tàng (tàng bằng quan tài không) về sau nhân việc can ngăn làm vua phật ý phải giáng chức Viên-ngoại-lạng; vì thế Quang-Bôn có thơ vịnh rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>HVB_003_0335</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>壯年表表頁高各開創寅緣際聖明</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Tên họ vang lừng lúc tuổi xanh, Gặp thời khai sáng, chúa anh mình!</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>HVB_003_0336</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>詩草預陪寫掖運垂朝先擁使花行</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Cung loạn án ngọc hằng lui tới? Xe sứ đường mây sớm khởi hành.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>HVB_003_0337</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>王臣襄惕忠兼孝天理昭明困復亨</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Nghĩa cả thờ vua trung với ái. Đạo trời qua vận bỉ sang hạnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>HVB_003_0338</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>未商于今循故轍功成事濟是前程</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Ngày nay con cháu nơi đường cũ? Xây đắp công danh sự nghiệp mình?</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>HVB_003_0339</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>其孫孫襄中狀元生下共責五歲好學人號袖童統元年號、丙辰科中黃甲仕至戶部左侍郎奉往北使時有中使輔行等寧貴物假作金銀替代潛取原物公不知之比至南寧府總督啟發見其非真遂以事聞皇帝怒其無禮命拘晉于北那官仍以蛤蜊覆公兩目以漆粘之曰瓶氣馬角方得還期</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Xét thấy hai ông Đinh và Hiền đều có công to trong việc thống nhất của vua Lê-Thái-Tổ, chỉ vì một hôm bản việc gia-dinh, không vào triều kiến, bị phạm vào lối khiếm điểm, thành thử không được phong tước công thần đó thôi. Nhắc lại khi trước ông làm Tri-phủ Tràng-An, nhân có một hôm vào yết miếu vua Đinh, ông thấy pho tượng Dương-Hậu cùng đặt ngòi chung với hai ông chồng, (tức là vua Đinh-Tiên-Hoàng và Lê-Đại-Hành) thì ông cho là hồn độn, nên có đáng bắn sỏ tàu, xin đặt Dương-Hậu vào chổ chồng sau. Nghi-luận táo bạo này được đức Thái-Tồ ban khen: Khanh quả là người trung trực, chẳng sợ quỉ thần. Rồi ngài hạ lệnh cho rước Đại-Hành và Dương-Hậu sang thờ tại ngôi miếu khác! Về sau ông được thăng chức Tuyên-Phủ-Sứ Trần Lạng - Giang châu là Tràng - Nguyễn Lê-Nại sinh ra Quang-Bôn, Quang-Bôn lúc mới lên 5 tuổi đã nỗi tiếng là thân-đồng thì đỗ Hoàng-Giáp khoa Binh-Tuất thời Lê Thống-Nguyễn, về sau làm đến Thị-Lang bộ Hộ, khi sang Sư Tẩu, có viên Trung-Sứ trong nom các thứ lễ vật đem vàng bạc giả đánh tráo mà ông không biết, khi sang đến phủ Nam-Ninh, viên Tông-Đốc bên đó mở ra kiểm điểm, biết là không phải vàng thực, lập tức báo cáo về triều, Minh triều cho là vô lễ, hạ lệnh giam cầm sứ thần, rồi viên Tông-Đốc sai lấy vở trai bịt kín hai mắt của ông, bên ngoài dùng son phủ lại, và báo cho biết: Bao giờ thấy ngựa mọc sừng thì người được trở về nước?</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>HVB_003_0340</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>公怡然自樂不少動心書於冬日出時輒圓一小床曝于日下一明人問其故公即撫其腹曰我曝腹中經笥耳</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Còn về phần ông đầu bị tai nạn bất thần như vậy, mà ông vẫn cứ thân nhiên không hề ta thân, gặp tiết mưa đông, lúc vùng Thái-dương vừa mọc ông thường nằm ngửa trên chiếc chồng, phơi dưới ánh nắng mặt trời, quan lại nhà Minh hỏi cô tại sao? thì ông vỗ bụng bảo rằng: Tôi phơi sách vở trong bụng đây mà?</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>HVB_003_0341</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>明人使讀大演義公讀了一遍不差一字明人大奇之即去其粘目甚加禮重</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Bọn quan lại nhà Minh thấy ông trả lời một cách tự phụ như vậy, liền bảo ông đọc thử một quyền Đại-học Diễn-ngiha xem sao? Biết rằng chúng muốn thử mình? ông bèn lên giọng đọc ngay một lượt chẳng hề sai một chữ nào? bọn chúng thấy vậy đem lòng kinh phục? tức thì cởi bỏ những thứ gắn mắt và để ông được tự do chứ không hành hạ như trước,</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>HVB_003_0342</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>公客旅中有撲逃本社諸先靈詩集寄歸時有葉人鄭洪震見公紫閣僕長郎八門受業癸未科中進士第除廣東知縣陞燕京重事以念其師淹晉不返即具本奏聞明帝始原之因召至京慰問二月遣還</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>thế rồi trong khi còn ở lữ điểm, ông cô soạn tập được một cuốn thơ của các Tiên hiền trong xã, đặt tên là cuốn Tư-hương Vạn-Lục gửi về nước nhà, còn ông thì phải ở lại đợi lệnh. Nhắc lại trong khi ông còn ở lại bêu Tàu, bỗng có một vị Cử-Nhân nhà Minh tên gọi là Đặng-Hồng-Chấn, vẫn thường đi lại với viên Tùy-tông của ông là Thân-khắc-Tảo vì thấy ông là người học văn yêm bác, bèn xin thụ nghiệp để học hỏi thêm? rồi sau đến khoa Kỷ-Vị thì đỗ Tấn-Sĩ, được bờ Tri-huyện Quảng-Đông, dàn dàn thăng chức Yến-Kinh Chủ-sự, nhân mới nghĩ đến thấy học của mình còn bị đây ải ở chốn tha hương, bèn dâng bản tấu kẻ rõ tình hình, được vua nhà Minh xét lại, lập tức triệu ông về Kinh an ủi, rồi tháng 3 nhuận năm ấy cho ông trở về bản quốc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>HVB_003_0343</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>洪震即設愛買斂並綵銀致饒公出侯凡十八年其家黃橋福之言始鑿金為足王是歸國陸吏部尚書蘇川侯後贈少保蘇郡公人獸武前身蓋相類者</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Trước khi lên đường Hồng-Chấn có bảy tiệc tiến hành và biểu một số bạc cùng các thứ vài vóc v. v... Tình lại ông phung mang đi Sứ vừa dùng 18 năm trời, gia đình ở bên nước nhà thấy lâu được về, bên theo như lời Hoàng-Phúc hẹn trước, đem khoét vào chỗ chân ngựa. hóa nên ông được trở lại, rồi khi về nước được thăng chức Lại-Bộ Thượng-Thư, tặng tước Thiếu-Bảo Quân-Công. người đời bảo ông là kiếp sau ông Tô-Vũ, đời nhà Hán, vì thân thể cũng giống nhau vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>HVB_003_0344</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>尚書張孚記</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Tác chiêu Sá nguy mạnh, Trương-Hoàng-Giáp nghĩa bất Mạc thần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>HVB_003_0345</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>青沔金壤断慶帝年號乙酉科中黃甲公性頗剛直統元末莫登庸欲篡位時公為吏部尚書百官以其故臣使作禮詔公張目叱之曰此何義也終不脹屈改命願公泰為之</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Ông Trương-phu-Thuyệt người làng Kim-Đầu thuộc huyện Thanh-Miện, thời Lê Uy-Mục niên hiệu Đoan - Khánh. 1505-1509 thì đã Hoàng-Giáp khoa Ất-Sửu. Ông là người có tinh cương trực cho nên vào cuối năm Thống-nguyen (1527) Mạc-Đăng-Dung muốn cướp ngôi nhà Lê, lúc ấy ông đương giữ chức Thượng-Thư bộ Lại, bá quan thấy ông là bậc nguyên lão đại-thần nhờ ông thảo cho bản chiêu nhường ngôi! Ông liên trọn mắt quát bảo: Như vậy là nghĩa lý gi? Bá quan biết rằng không thể bắt ép được ông, nên lại trao cho Nguyễn-văn-Thái (Đỗ Thám-Hoa khoa Nhâm-Tuất (1501), năm Cảnh - Thống thứ 5) đứng thảo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>HVB_003_0346</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>後公歸田里適間中館問野服乘涼與常人無異時則令偶經伊處人皆起立公獨靜坐矣之從者叱曰何人無禮將欲攻之縣令望見公駿須之異急止從者曰吾觀此鬚美且認其體構必有識字試出對句若或不成打之未晚即出對六</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Ông bèn cáo quan trở về làng cũ, trong lúc thư nhân thường ra quán ngồi chơi hóng mát, chẳng khác một người dân quê? Bồng có một hôm quan Huyện sở tại đi qua, mọi người trong quán đều đứng cả dậy, chỉ có một mình ông là vẫn ngồi yên, linh hầu của quan thấy vậy quát mắng: Người kia sao dám vô lễ? và toàn đánh đập! Quan Huyện nhìn ông thấy có bộ râu rất đẹp! vội vàng quát bảo linh hầu: Ta coi người này râu ria đạo mạo, tất nhiên là người có học? vậy để ta ra cho một vẽ đối, nếu không đối được, hãy đánh cũng chưa muốn gì, nói xong quan bên ra một vẽ đối như sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>HVB_003_0347</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>知縣青沔見無礼而欲攻</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Huyện quan Thanh-Miện kiến vờ lề nhi duc công.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>HVB_003_0348</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>公郎應之曰</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Ông liên ưng khâu đối rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>HVB_003_0349</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>進士金燭幸有珍餚而得晚賂</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Tấn-Sĩ Kim-Đầu vị hưu tu nhi đắc miễn. Nghĩa là: Quan huyện Thanh-Miện thấy kẻ vờ lề mà muốn đánh. Đối với: Tấn-Sĩ Kim-Đầu may vì có râu mà được tha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>HVB_003_0350</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>令始知其公即連遜趨拜自言途由錯誤過咎是耳幸大人見恕公笑而釋之</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Quan Huyện nghe xong câu đối mới biết chính là ông Nghè, vội vàng bài tạ, xin ông thứ lỗi, ông cũng cười xóa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>HVB_003_0351</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>公前不附偽莫後辭歸不仕蓋在節義之列云</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Xét ông không phù Mạc, thực xứng là người biết trọng tiết nghĩa vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>HVB_003_0352</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>大興候記</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>CHÍ KHÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>HVB_003_0353</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>院世儀當泰澤社一下村人中官蒞國公世恩之第附焉賜之叔也為人焉浪不循禮度而高尚志氣少善盈文尤長於文體十五歲頴鄉舉特同科諸貢士拜試場官皆用烏紗帽青吉衣公獨著紅色衣烏尾暢場官怖乃兄勢熖仍免覆問</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Nguyễn-Thế-Nghi người ở thôn hạ làng Mộ-Trạch, là em quan Đam-Quốc-Công Nguyễn-Thế-Án và là chủ họ của Phò-Mã Nguyễn-Thế-Từ, ông vốn có tính bừa bãi không giữ lễ độ, nhưng chỉ khi lại rất cao thượng, ngày từ lúc nhỏ đã giỏi văn-chương, mà lại sở trường về thế quốc âm thơ phú, khi 15 tuổi thì đã Hương-Tiến (Cử-Nhân) lúc ấy các người đồng bằng vào tạ quan trường ai cũng áo mũ màu xanh, riêng ông lại mặc màu hồng có thêu đuôi qua. Quan trường có vẻ bất mãn nhưng vì e sợ thể lực Quốc-Công, nên không phục vấn giả cả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>HVB_003_0354</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>平日共奠登庸相有交善統元間也音托不檢束也。出居京城外長生寺不求療達一月莫簽庸迫至欲加以好官公辭不受願得一爵為各稱足矣因請以大興二字為號登庸許之即拜為大興侯任行高志儀</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Nguyễn ông ngày thường chơi thân với Mạc-Đăng-Dung, đến năm Thống-Nguyễn (1527) Đặng-Dung cướp ngôi nhà Lê thì ông đương lạc lõng ở ngày Kinh thành trù ngụ trong chùa Trưởng-An, nhưng không có ý cầu cảnh. Thế mà một hôm họ Mạc biết tin muốn phong quan trước ông cũng từ chối; chỉ xin phong cho một danh hiệu mà thời. Đăng-Dung hỏi danh hiệu gi? Ông xin phong cho hai chữ Đại-Hưng, Đăng-Dung cũng bằng lòng cho để ông làm theo chí muốn,</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>HVB_003_0355</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>嘗浪吟一句云</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>rồi sau ông thường ngâm mấy câu thơ nôm, và để vào phía tả của Đại-Hưng rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>HVB_003_0356</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>英雄埃乃剝剝帝境鉅剎大興庄輪</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>?? Anh hùng ai này nhung những? Nào ai đến cửa Đại-Hưng chẳng luôn?</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>HVB_003_0357</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>題于登龍城大興門左自謂己在其上而人皆出下之意歷歷莫大李尚存</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Có ý bảo mình ngồi bên trên, mà ai cũng phải luôn cùi bên dưới vậy? hai câu này đến cuối đời nhà Mạc vẫn thấy còn để chữ không bị xóa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>HVB_003_0358</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>時莫氏荒怠政命著樂昌分鏡國語傳序陳隋奢欲事寫意諷論他亦不之悟也</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Thế rồi về sau nhà Mạc hoang dâm, trẻ nái về đường chính-trị. Ông bèn soạn ra truyện Nhạc-Xương phân kinh dùng toàn quốc âm, ngụ ý chê bài họ Mạc xa xi giống như nhà Trần nhà Tùy ngày xưa, thế mà họ Mạc vẫn không tỉnh ngộ, ông lại soạn ra bài phu Huyền-Quang-Tuyền cung nữ bằng quốc âm, rất được nhiều người truyền tụng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>HVB_003_0359</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>又嘗有北侯至途經南門聞門上題字係我國臣子各號輒停車不進要以架梯從上而行時尚書武惟斬為援伴官伴應以知命部下生一計陰取送象來從後痛刺槪大吼衝突北人叱了一驚郎撓愕走過自知墜于計中不勝慙憤至今猶傳其事云</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Đến thời Minh-Đức (1527-1529) có sứ Tàu sang, khi qua cửa Nam nhìn lên thấy có chữ đề bên trên, và là danh hiệu của một thần từ nước Nam, nên bắt dừng xe không chịu tiến nữa, và lại bắt ta phải đi lấy thang để bắc qua công thì mới chịu vào? Giữa lúc ấy có quan Thượng-Thư là Võ-Duy-Đoán hiện sung chức Bàn-Tiếp để dón sứ-giả, thấy sứ yêu sách như vậy, Ngại cũng giả ý tuân theo, nhưng mà trong tâm đã nghĩ ra được một kế, ngầm sai quan hầu di bảo quân-tượng xua voi đi qua, lúc gần đến chỗ sừ-giả thì lấy mũi nhọn chích vào lưng voi, voi bị đau buốt gãm lên rồi nhảy loạn xạ, làm cho ai này cũng phải hoảng hồn tim chở ăn nấp? chạy xô cả vào phía trong cửa nam, sừ-giả và đoàn tùy-tùng cũng thế, nhưng khi đã trót chạy vào mới biết rằng mình trúng mưu, đánh phải nuốt hận; việc ấy vẫn còn truyền ngọn cho mãi đến nay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>HVB_003_0360</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>扶擁節婦記</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>LIỆT NỮ</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>HVB_003_0361</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>上洪唐安有范氏各援者自少通穎尙間頗有姿色既加笄即歸于唐豪令族之家生下男女四人值北兵南侵夫以病死婦撫幼育孤以不一庭不雨醮自誓言其悲酸情狀缺石心腸非言語形容所莊盡</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Xã Thượng-Hồng huyện Đường-An có người con gái tên là Phạm-Noãn, lúc còn niên thiếu người rất thông minh nhân nhà lại thêm có nhan sắc đẹp, khi đến tuổi cấp kẻ kết duyên với một người cùng dòng đối danh giá ở làng Phù-ùng thuộc huyện Đường-Hào, sinh hạ được 4 con, cả trai lẫn gái. Chẳng may gặp lúc quân Tàu kéo sang xâm chiếm, người chồng lại bị ốm chết, thế mà chỉ vẫn quyết chí ở vậy để nuôi các con chứ không bước qua cầu nữa, dù rằng phải chịu trăm đáng ngàn cay, mà tấm dạ sắt gan vàng không ai có thể hình dung hết được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>HVB_003_0362</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>將當兵火人罕自全城或饑寒失守為盜賊所污者或道路流亡苟來生浩而婦周旋其間以死自誓言變容斂色不為隱暴所侵一方之人皆以故郡鄰目之</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Bởi vì trong con bình hòa, ít ai giữ được trong sạch tấm thân, nếu không vì cảnh cơ hàn, cũng bị giặc cướp hãm hiếp, hoặc giả trong bước lưu ly cũng phải bán liều danh tiết để cầu lấy sống. Thế mà riêng chị lại quyết làm cho hủy hoại nhan sắc, để bọn cưỡng đạo chẳng muốn nhìn mặt, nên mỗi giữ được trọn tấm kiên trình; vì thế cả vùng ai cũng khen là một người tiết-phụ hiếm có.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>HVB_003_0363</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>造天日明基圖復舊朝之達官鄉之豪右屢欲奪其操</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Nhất là về sau giang-son đến hồi quang phục, các quan trong triều cựng như cương hào trong xã, vi yêu danh tiết cũng muốn ép duyên, nhưng nàng đem câu đại nghĩa ra để từ chối, thì ai cũng phải kinh nê.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>HVB_003_0364</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>詔求真烈有司以名聞仍表其問曰節義門賜奉事以旌揭之年八十而終子孫累世長冠為一鄉之明王族今扶櫨社有故碑存焉</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Thế rồi vào khoảng niên hiệu Thái-Hòa đời Lê-Nhân-Tông (1443-1454) nhà vua xuống chiếu hỏi đến những người trinh-tiết, các quan địa phương cử thực tấu trình, vua bèn ban cho chiếc biển treo của có đề chữ Tiết-Phụ-Môn?, để nếu tấm gương tiết-liệt, về sau bà thọ 86 tuổi, con cháu vinh hiển nối đời, thành ra một họ danh vọng nhất xã, hiện nay tấm bia cũ ấy vẫn còn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>HVB_003_0365</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>陰境</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Chăm hậu tượng, Trần-Gia dĩ sắc đặc Thiên hạ</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>HVB_003_0366</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>陳朝之祖美禎，即墨人也。世以魚為業，南道長江一帶，到處是家焉。</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Tô tiên nhà Trần ở làng Tức-Mặc p? thuộc huyện Mỹ-Lộc nỗi đời làm nghề chài lưới, suốt cả một giải Tràng-giang ở nam đảo, tới đầu thì cũng là nhà, chừ không nhứt định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>HVB_003_0367</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>時有堪輿北客就我國相地自三島祖山從龍脈而來歷昇龍古碑至金洞縣偈州社高會社見土堆環聚即笑而言曰是也</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Lúc ấy có thấy địa lý chính tong ở bên Tàu sang nước ta tìm đất, bắt đầu từ đây tổ-son Tam-Đảo lần theo long mạch xướng khỏi Thăng-Long Cờ-Bi rồi đến các xã Kệ-Châu Cao-Xá thuộc huyện Kim-Động, thấy nhiều gò đồng tụ tập ở đó, thì thấy bảo rằng: đây là chỗ đóng bình nâu com;</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>HVB_003_0368</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>駐兵造厭旁至南昌縣芳萊社江漢沒了臨江顧望良久曰江水急流豈有六藏水底耶因過河而往至御天縣河柳社見星峯草立郎指之曰撞頭旁在是寧能適我耶遂尋至日果社起宗到太堂社阮固結苟旁續下盤針看了輒躊躇不敍去</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>đi đến xã Phương-Trà thuộc huyện Nam-Xương, không thấy vết tích long mạch đâu nữa. Thấy địa dừng lại nhìn quanh một lúc, thì lại nhầm lầm nói một mình rằng: Nước sông chảy xiết thế kia, lẽ nào huyết lại chim dưới thủy đề. Rồi lại xướng đó sang sông, đi tới đến làng Hà-Liễu thuộc huyện Ngư-Thiên. thấy một ngọn núi lù lù hiện lên. Thấy địa tỏ về mừng rõ chỉ tay nói rằng: Nó đã ngóc đầu kia rồi, thế nào lại trốn được ta? Nhận rõ long mạch rồi thấy lại tìm đến xã Nhật-Cảo là nơi khởi điểm, và xã Đại-Dương là nơi kết cục, bấy giờ mới đặt địa bàn coi thử, rồi thấy cảm thấy say mê, quanh quần mãi ở nơi đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>HVB_003_0369</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>適西衙人阮固見之問曰地仙屬意于見不知這處有吉穴耶客人仰面笑曰不謂奇王大地出平陽可笑聰勁時師都無眼力固曰果如此請以許我師謝禮如何我亦可辨客人曰爾既有福而遇我我則予之郎還謝我以百緡錢他時有國當分其半國許諾遂將祖墓葬之客人反覆謂之曰這誠大地登了必有嘉祥但於百日之內時常往來以探倘風雷之後見有異事便是剣多古少一可急殺塞之</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Chẳng ngờ giữa lúc thấy dương trù trù nghĩ ngợi ở đó, thì có một người tên gọi Nguyễn-Cố Ẩn người xã Tây-Vệ xá đi qua nom thấy, tiến lại hỏi rằng: Địa Tiên chú ý ở đây, phải chẳng chở này có ngôi quí địa sao đó. Thầy địa nghe Cố hỏi vậy, có ý tự phụ ngửa mặt cả cười: Hừ hừ! Ai biết ngôi đất để vương lại lạc xuống quảng bình điền. Từ trước đến nay các thầy địa lý thực không có mất. Chú thầy địa nói xong, Nguyễn-Cố sừng sốt hỏi: Nếu quả như vậy, xin thầy làm ơn để lại cho tôi, tôi xin biên lễ hậu tạ, bao nhiêu cũng được. Chú thầy địa đáp: Ừ, nhà người có phước nên mới gặp ta, thì ta cũng để giúp cho. Nhưng có một điều là khi tàng xong thì phải đưa trước cho ta 100 quan tiền, còn sau đến khi chiếm được nước rồi thì phải chia đôi thiên hạ. Nguyễn-Cố thấy chú khách buộc hai điều kiện trên cũng chấp thuận ngay, rồi hốt ngôi mộ Tô lên để nhờ thầy địa an táng. Thầy địa sợ Cố lật lọng nên lại hẹn rằng: kiểu đất này sau khi tàng rồi phát đạt rất lớn. Nhưng mà trong khoảng 100 ngày, phải nên thời thường thám thính, nếu sau những trận gió mưa sấm sét, mà thấy có sự gì lạ, thì sự tốt lành có ít mà sự hung dữ lại nhiều, nên kịp đời đi chỗ khác.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>HVB_003_0370</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>葬纔三日忽夜聞巨雷振起一聲所在地方人畜皆驚而次日視之見蜀會西衙太堂三社有石突出人稱貓耳石園池在在有之</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Quả nhiên vừa mới táng được 3 ngày, thì đêm hôm ấy sấm sét nỗi dậy ầm ầm, nhân dân quanh vùng thấy đều nào động, sáng sớm hôm sau, người ta thấy đã ở dưới đất trời lên, trong như thứ đá tai mèo, nhan nhãn khắp vùng 3 xã Đăng-Xá, Tây-Vệ, Thái-Đường, tất cả hồ ao vườn được chỗ nào cũng có. Ngày nay dấu tích vẫn còn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>HVB_003_0371</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>時同自知得地喜不自勝其要謂之曰此地雖然然發福但今損百緡錢如何可得又來日半分天下其所得者幾何因以是無意還謝禮錢客人問之固約以某日具還至日客抵其家固即捉來縷定乘夜救之江中惶遠而歸</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Về phần Nguyễn-Cổ thấy có sự lạ như vậy, biết rằng ngôi mộ đã kết mùng rỗ vò cùng. Nhưng vợ anh thì lại nghĩ khác, nên chị bảo khẽ anh rằng: Ngôi mộ nhà ta đã được phát phục, nhưng mà hiện nay chạy đầu cho ra 100 quan tiền lễ tạ, và lại sau này còn phải chia đôi thiên hạ, thử hỏi phần mình còn được bao nhiêu. Cố nghe vợ nói như vậy, nghĩ cũng tiếc của, anh bèn tính ngày đến việc bội sư, nên khi thấy địa đến hỏi lễ tạ, anh hẹn đúng ngày nào đó mới thấy quá bộ lại chơi, vợ chồng tôi sẽ xin giao đủ số. Thế rồi đúng hôm ước hẹn, thấy địa yên trí đến nơi, chẳng ngờ khi bước vào đến nhà trong, anh liền nhét giè vào mồm, trói gò ngay lại, rồi đến đêm khuya anh vác ra quảng xưởng giữa dòng sông cái, thì hành xong thủ đoạn anh lại đứng đình ra về, tưởng rằng không ai hay biết.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>HVB_003_0372</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>不意這處乃浮沙水漲自他將投下忽然潮水漸涸圖在沙上適陳氏魚舟過聞有人喚聲急來救之上船觧去其縫換以新衣間故客人具道由來因謝曰感君子角生之恩當以此地相報陳氏謂這地他已葬了若將之何客人曰某已先葬此地必為公有陳氏遂畱之舟中不露人聲跡客人即教以多采調器鑄為霹靂斧形及蘇木樑煮湯待有授用處</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Chẳng ngờ chỗ anh quảng thấy địa-lý phía dưới lại có con bơn (bãi cát), vì lúc thủy trào tràn ngập, nên không thấy rõ, nhưng rồi sau lúc anh quay về nhà thì nước thủy trào cũng rút. Thành ra chú thấy địa ấy lại nằm lò kho ở trên bãi cát, chứ vẫn không bị chết chim. May mắn hơn nữa là ngày lúc ấy lại có chiếc thuyền ngư phủ họ Trần đi qua, thoáng nghe thấy tiếng cầu cứu, vội vàng chèo đến, ôm xuống dưới thuyền, cởi trói cho chú, rồi hỏi duyên cớ tại sao? Chú bèn kề hết đầu đuôi câu truyện cho ngư-phủ nghe, rồi sau ngỏ lời cảm tạ: rằng tôi được ông cứu thoát, thực là ân đức tái sinh, vậy nay xin đem ngôi đất quý đó để bảo đáp lại v.v... Trần-Công hỏi: nhưng ngôi huyết ấy thầy đã đề cho người khác, biết làm thế nào? Chú thầy địa đáp: Tôi đã cân nhắc kỹ-lưỡng, biết rằng ngôi đất quý ấy, trời đã đề dành cho họ nhà ông, vậy nên tôi đã có cách xử trí... Trần-Công thấy nói vậy bèn lưu thấy địa ở ngay trong thuyền để cho khỏi lộ câu truyện, rồi chú bảo ông đi mua đồng đỏ về dúc một số lưỡi búa tâm sét, và mua Tô-mộc nấu nước để sẵn (nước vàng) đợi khi cần dùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>HVB_003_0373</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>忽是夜雷雨交作數然有雷轂手之聲，震師將雲辟雲蓋，斧穿重於墓上，面透至棺，隨以蘇木水灌下明日固往探見之以為雷打墓中流血因惧而殺去客人遂將陳家祖墓就塟焉。</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Rồi ngay đêm ấy trời bỗng nổi cơn mưa gió. Sấm sét đánh xuống âm âm, mãi đến gần sáng trời tạnh thì chú thầy địa và ông ngư-phủ họ Trần vội vàng đem các thứ ra chỗ ngôi mộ Tồ nhà Nguyễn-Cổ, cắm lưỡi tâm sét xuống chạm đến quan tài rồi đổ nước lên trên. Sáng hôm sau Nguyễn-Cổ cũng ra thăm mộ, nhìn thấy những lưỡi tâm sét còn cắm chơm chơm, và thấy nước đỏ như máu đường ở dưới mộ trào lên, anh nghĩ là bị trời đánh, nên ngay hôm ấy anh phải đào lên để đem tàng ở chỗ khác, rồi ông thầy địa bèn đem mộ Tồ họ Trần tàng vào, mà chẳng ai biết gì cả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>HVB_003_0374</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>這句前望三陵大江在美樣縣有備社格曰新巡礦後拖伏象樓壹旌劍羅劉左右穴在土腹藏金坐乾向巽事襄客人有課云彩岱黑當堤照煙花對面坐必以顏色得天下陳氏曰果如其言當分民祿之半客人得奈景須如此但君家世世享國則我家世世給足衣糧可也陳氏謹當書目伸各有書交為質</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Xét ra cục đất quỉ này, trước mặt trong ra ngã ba sông cái, thuộc xã Hữu-Bi tục gọi là của Tuần-Vàng hay Tuần-Vương, phía sau gối vào voi phục, lầu dài, cờ kiếm la liệt hai bên, huyết điểm vào chỗ Thổ-phúc Tăng-Kim tim đất giấu vàng, ngời phương can trống chư Tốn, công việc xong rồi chủ thấy địa có đoàn trước mấy câu rằng: phần đại yến hoa đối diện sinh, tất dĩ nhan sắc đặc thiên hạ, nghĩa là: Son phần yến hoa bày trước mặt, hẳn vi sắc đẹp lấy giang son. Trần-Công thấy thấy địa đoàn trước như vậy liền nói với thầy: Nếu dùng như lời sau này xin chia đôi phần lợi lộc! Thầy đáp: chẳng cần phải thế, hễ mà sau này nhà ông lấy được quốc gia, thì con cháu tôi đời đời cấp cho dữ com áo, thế cũng được rồi. Trần-Công xin vàng, rồi hai bên cùng lập khoản ước để lưu chiếu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>HVB_003_0375</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>部說客人心多機智又密寫識一道雷與彼子孫藏之嘯以異事特他如禮不替者便以冥告倘者背約即如此因與陳語曰某恐遺下二法有漆長遠來時便可造之陳氏不勝感謝至二世陳賜守度曰陳家皇族乎陳家赤族乎後遂禪位、</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Nguyên chú thầy địa đây vốn người da mưu và rất kin đáo; sau khi viết xong, chú còn viết ra 2 đạo sấm thư, trao cho con cháu cắt kỹ một chỗ, và bảo chúng rằng: vì thử sau này Trần gia xử sự trung hậu, thì nên bảo thực với họ, nhược bằng họ định bội ước, thì nên như thế như thế... rồi trước khi ra về chú lại nói với Trần-Công: Mở còn quên mất một phép có thể giữ nước lâu dài, nhưng để sau này mở sẽ chỉ bảo, Trần-Công lấy làm hân hạnh, sắm sửa lễ tạ để tiến chân chú khách về Tàu. Nhắc lại họ Trần kể từ khi tàng ngôi mộ đó cho mãi đến đời thứ 3 tức là Trần-Thừa, vào năm Duyên-Phúc thứ 8 đời nhà Lý (1218) — (có lẽ năm Kiến-Gia mới dùng) thì mới dàn sinh ra Trần-Cảnh tức là người có tướng mũi rộng mắt phương, được Lý-Chiều-Hoàng nhượng ngơi, hiệu là Thái-Tông. Bấy giờ con cháu thấy địa mới từ bên Tàu tim sang, lần nào cũng được tiền tông rất hậu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>HVB_003_0376</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>逮季世後禮日寢哀客人即進言臣先祖遺一譜囑以某年遂就黃國陳朝取讖者之見內言太堂發跡舊墳今將不旺當疏通水道遂信其言照識內書圖鑒自富初社大江而八紫囘至太堂蓋陳家享福該有此數是亦出於天命豈人力所能及</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Nhưng rồi về sau họ Trần đối đãi có phần bạc bẽo, thì con cháu thấy địa mới hiển kể rằng: Ông Tồ của thân ngày xưa có đề lại một tờ sấm, hẹn rằng năm nay thì đưa sang trình, Trần vương cảm lấy tờ sấm coi qua, thấy có những câu Ngôi mộ ở Thái-Đường là nơi phát tích, nhưng từ năm nay trở đi thì không được vương, cần phải khai thông thủy đạo thì mới giữ được lâu dài, vì quá tin ở thấy địa, nhà vua liền sai bá quan chiếu theo họa đồ trong tờ sấm đó, để đào ngay một con sông từ cửa sông cái thuộc xã Phú-Xuân kéo quanh về xã Đại-Đường (hiện nay vẫn còn di tích), chẳng ngờ vì thế mà đứt long-mạch, khiến cho nhà Trần suy yếu để Xích-Chủy-Hầu tức Hỗ-Quý-Ly ăn cướp mất ngôi. Nhưng xét cho kỹ thì nhà Trần hưởng phúc chỉ được đến đây, cũng là do ở mạng trời, chứ như nhân lực thì làm sao nổi?</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>HVB_003_0377</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>或按陳家祖墓提生天下後生仁宗火時清秀面字號金仙童子明宗清秀非允時人稱為神仙人中蓋亦土地之壇客言信不誣矣</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Hoặc xét ngôi mộ tổ nhà Trần sinh ra thiên tử, sau sinh ra Nhân Tông diện mạo thanh tú, chữ hiệu Kim Tiên đồng tử, Minh Tông thanh tú phi phàm, người đương thời gọi là bậc thần tiên trong cõi người, âu cũng là do khí thiêng của non sông đúc lại, lời của khách quả không ngoa vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>HVB_003_0378</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>詠橋祖墓記</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>VINH-KIỀU TÒ MỘ KÝ</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>HVB_003_0379</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>東崖誄橋京北阮族之祖號福過平生樂善音築木千豐盈縣東蕃社以釀酒為業傍有菩提樹為風所拔因買供新爨適極至樹根見下有銀穴約三婁許即收囘晉貯之已而撤廬去經二年餘時有北客來取銀見雀跡不存只畫空穴即聞諸旁人知這銀已為公所得遂尋至家出雀識一道示之曰某為先人遺貨跋涉而來不想天已賜公今早覓歸程所望出資路費受賜不淺而公得銀藏之不知多少至是取識者之因熙熙銀數與記不差即疑得其人謂曰聊這銀繫我取的原來收時如故不曾取用既是公家原物當盡以付還其人謂曰那物雖我家先遺一下今既為公所得是公家物倘蒙惠顧只願費路錢足矣若更以相還豈敢如命公固執不可客人曰公既有是心願頒其半公曰我不穀人情之所欲第這銀非我之財天使我為公守耳故為此以待勿復牢辭客人恐遠其意輒頒銀歸國</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Thượng-thư(thời Mạc) Nguyễn-văn-Huy xã Vinh-Kiều thuộc huyện Đông-Ngàn, Cự tổ hiệu là Phước-Mại, trong lúc ngày thường hay làm điều thiện. Cự có dựng nhà tại xã Đông-Lâu thuộc huyện An-Phong làm nghề nấu rượu, ở bên nhà có cây Bồ-đề cỏ thụ, một hôm bị bão đánh dở, Cự mua để làm cui thời, khi đào dưới gốc cây bông thấy có 3 hũ bạc, Cự bèn lẳng lặng đem về đấu kín không cho ai biết, rồi cách ít lâu Cự lại giỡ nhà thiên đi chỗ khác. Chẳng ngờ ba bốn năm sau bông có một chú ở bên Tàu sang tìm đến địa điểm chôn bạc của Tồ-tiên xưa, thì thấy đấu cũ còn đó; lỡ chôn còn đây; mà những hũ bạc đều biến đâu mất? Chú bên lân la hỏi đó những nhà bên cạnh, người ta mới đoán rằng ông nấu rượu năm trước đã lấy đi rồi. Chú bên đến thẳng nhà ông xuất trình gia phả cùng các giấy tờ, rồi mới nói để ông biết: Tồ-tiên chúng tôi ngày trước có chôn bạc ở đây, ngày nay chúng tôi sang lấy chẳng ngò bạc đó đã về tay ông. Chúng tôi không giám ươn thân chi cả, duy có một điều xin ông nghĩ lại, bởi vì nay mai chúng tôi cũng phải thu xếp trở lại cổ hương, mà túi tiền lương đã cạn, mong ông sẽ phát hàng tâm giúp cho ít chút để làm lộ phi, chúng tôi chẳng giám quên ơn. Nhắc lại ông Cụ từ khi đào được hổ bạc cho tôi ngày nay, ông vẫn dẫu kín một nơi chưa hề dùng tới, nên cũng chẳng rõ nhiều ít thế nào, nay được xem bản gia-phả Cụ mới đem ra kiểm lại, thấy đúng con số đã ghi. Cụ bèn giữ Chú ở lại cơn rượu thết dài ăn càn, rồi mới bảo thực cho các Chú biết: rằng số bạc kia quá nhiên tôi đã đào được, nhưng vẫn dẫu kín chưa hề tiêu mất ít nào, ngày nay các chú sang đây tức là chú nhân của nó, thì tôi xin tra trả hết chứ có để lại làm chi. Chú Khách nghe Cụ nói vậy, trong dạ đã thấy mờ cờ, nhưng vì chẳng dám nhận ngay nên cũng kiếm câu từ chối: Thưa Cụ mấy hũ bạc đây dẫu là bạc của Tiên Tỏ chúng tôi để lại, nhưng nay giới đã cho Cụ, tức là của Cụ, nếu Cụ ban cho ít chút để làm lộ phi, chúng tôi cũng đã hàn hạnh lắm rồi, chứ đâu lại giám nhận cả như vậy. Chú khách nói thế nhưng Cụ nhất định không nghe, về sau xin chia ra làm 2 phần Cụ cũng không thuận, bảo thực cho các Chú biết: Tôi đây hà phải con người không quí tiền bạc, chỉ vì bạc đó không phải của mình, chẳng qua giới sai giữ lại để đợi các ông đó thôi, vậy thì các ông cứ việc nhận lấy đủ số đem về thì hon. Chú khách biết chúng không thể nài ép được nữa, nên phải nhận lấy số bạc đem đi,</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>HVB_003_0380</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>後嘗以其事對北人言時有風水師者聞之曰難如此人好心我今老矣尚尚火時郎當往安南擇吉地以報其人懇之師曰我有二門弟一可遣遂與之偕往北客至詠橋社探問則念已於前年捐館矣郎辨一購禮致祭而去二月餘復至謂公之子曰我感受先人之德無以相報今帶得地師來來尋告地以謝有一處群山供伏可做一代帝王又一處緒軸花畫可做一代駙馬於二者何擇其子曰我家村鄙野人何慼望比所望者世出文儒之地不慼二地師曰苟如此在貴邑內何事遠求</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>sau khi về tới nước nhà, gặp ai Chú cũng kể lại câu chuyện ông Già nước Nam có lòng nhơn đức như vậy. Lúc ấy có một ông thầy địa lý chánh tông nghe xong câu chuyện cũng khen là người hiềm có, tiếc rằng tôi nay đã già, vì thử đường lúc thiếu trang, thì tôi quyết sang bên ấy tìm họ một ngôi huyệt kết để bảo on sau. Chú khách nghe ông Thầy Địa nói thế, khẩn khoản mời ông sang ngay, vì ông yêu quá không giám đi xa, nhưng ông cho biết: Tôi có hai anh đồ đệ cũng đã học được bí truyền, au là tôi cho cùng đi với bác một thề. Thế rồi 3 người cùng sang An-Nam tìm đến nhà Cụ bán ruộng, thì Cụ đã mất được hơn một năm, các Chú biện lễ phúng viếng xong rồi cáo từ ra đi, không biết đi đâu mà hai tháng sau thấy quay trở lại, bảo với con giai Cụ rằng: Chúng tôi đã chịu ơn Cụ ngày trước rất nhiều mà không có cách gì để báo đáp lại, vậy nay có mời được hai thầy Địa-lý cùng sang, hiện đã tìm được mấy chỗ cát địa, ngôi thứ nhất có một dãy núi châu về, sau phát Đế Vương nhưng chỉ một đôi là hết; còn ngôi thứ hai ở đóa hoa sen cũng phát 1 đôi Phò-mã, vậy Cậu muốn chấm ngôi nào? Cậu con đáp: Chúng tôi là gia đình ở nơi thôn giã, chẳng giám hy vọng cao xa, chỉ muốn được một người nào kể thế văn nho là đủ. Hai thầy Địa đáp: nếu vậy thời có khó gi, chẳng phải tìm đâu cho mệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>HVB_003_0381</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>按地自錦章社來龍屈勢如蛇形至詠橋社八首突起二小阜一阜稍大平坦一阜差小勢頗微科一地師認穴在大阜十次一地師不可即就前面澤澤處浸卧水中貼仰良久方起日我已驗之果然方在小阜二師爭辨不決因畫成一圖使人北還就諸老師取正老師曰這曷是黃鶴咱蛤其氣在耳兩阜間兩耳也大耳是等小耳是微科有氣旁必在杳其子即依言移公藝之坐恩向坤</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Tôi thấy ở Thôn nhà đây cũng có một người, long mạch tự xã Cẩm-Chương kéo đến, nó đi ướn khúc như kiểu hoàng xà, đến xã Vĩnh-Kiều thì ngóc đầu dầy, đột khởi lên 2 cái gò, gò lớn bằng phẳng, gò nhỏ thì hơi cong cong. Theo ý thầy cả thì huyết kết ở gò lớn, nhưng mà thầy hai không tin, ra cái dẫm sâu phía trước, lăn xuống dưới đây để xét khí mạch rồi quyết đoán là huyết ở gò nhỏ. Hai thầy không ai chịu thua ai, về sau phải họa kiểu đất sai người đem về Bắc quốc hỏi lại Sư-phụ. Sư-phụ coi xét bản đồ, bảo nó là kiểu Hoàng Xà thính - cáp nghĩa là con Hoàng xà lăng tiếng con ngô, lúc lăng thì tinh thần nó chú trọng cả ở lỗ tai, như vậy thì huyết kết ở tai, mà hai gò đất tức là hai tai, duy cái gò lớn bằng phẳng tức là cái tai bị điếc, còn cái gò nhỏ hơi cong, thì có tự khí, tức là tai lành, thế nào huyết cũng kết ở gò nhỏ. Hai người đồ đệ sau khi nhận được tin của Sư-phụ lập tức bảo con ông Cụ đem đi hai cha táng ở gò nhỏ, ngồi ở chữ Cẩn trong ra chữ Khôn,</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>HVB_003_0382</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>至三世文徽以明德翼登庸乙丑科中探花官至尚書致仕其三子伸調以永定奠福原丁未科中黃甲官亦至尚書日達善以光寶員乙未科中黃甲仕以淳福年考乙丑科中進士至侍郎其孫教方之文知江漢之水愈出愈奇四代孫福胡王以陽德繼中興嘉慶末科中會元再中東閣仕至都臺公坦德敦國益相鄰緒北省其苗裔商今旋中相傳諸預登紳甲者面必微科蓋地氣之所鍾也</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>rồi sau đến đời thứ 3 là ông Văn-Huy thì đổ Thám-hoa tại năm kỷ-hội trong thời nhà Mạc, làm quan đến chức Thượng-thư rồi mới trí sĩ, người con thứ ba tên là Trọng-Quỳnh thì đổ Hoàng-giáp trong năm định vị tức là niên hiệu Vĩnh-định của Mạc-phuc-Nguyên Mễ Phúc Nguyên, về sau cũng làm đến chức Thượng-thư, còn ông Đạt-Thiện tiến sĩ mới 18 tuổi cũng đỗ Hoàng-Giáp khoa kỳ-vị năm Quang-Bửu nhà Mạc, về sau cũng làm đến chức Đô-khoa và ông Hiền-Tích cũng đỗ Tấn-sĩ khoa ất-sửu, niên hiệu Thuần-phước thời Lê-trung-Hung, sau làm đến chức Thị-lạng. Nguyễn-danh-Nho đỗ Tấn-sĩ khoa canh-tuất, làm đến Đô-khoa. Trên đây là kẻ hàng con, còn hàng cháu thì có Giáo-phương cũng đỗ Hội-nguyên khoa bình-tuất niên-hiệu Đoan-Thái thời Mạc-mậu-Hiệp (1586) lúc vào thì dinh lại đỗ Thâm-hoa, trong bài đối sách được Vua khen ngợi phê rằng: Văn của Giáo-phương như nước sông Giang, sông Hán! càng viết càng lẫm thử lạ. Truyền đến hàng cháu bốn đời thì có Đức-Vọng thì đỗ Hội-nguyên khoa quí-sửu, sau lại trúng luôn Đông-các, làm quan đến chức Đô-dài. (Vào thời Lê Dương-Đức 1635-43) còn như Công-Viên, Đức-Đôn, Quốc-Ích cũng lại kế tiếp đăng khoa và cũng đều là dòng dõi họ ấy, ngày nay trong họ có truyền ngôn rằng: những người đỗ đạt nét mặt đều thót, hay là hơi lép một bên, là bởi mộ tổ nằm trên gò đất hơi cong, cho nên khí mạch chung đúc như vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>HVB_003_0383</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>卻說頭乃文微次子火領鄉舉惟善飲酒懶廢學業見海陽處隨號嘗往珥河竹木津邊明儔對飲通就河津濯行見竹筏上有紱字在焉拾而觀之乃是舊賦一箇因記之燕燭每飲酒後輒叩盤歌詠習以為常乙丑科八第一場得親朋友之助頸在中第至第二場携酒而入坐間醉酒睡著日已向暮忽大風驟至塵霧漫天續睡中驚為起輩目觀之見有數片紙字飛到其前收來紬認乃是四六體文續喜曰此天賜吾也依樣寫之已而果中至第三場賦題乃前日所得舊賦者更預中第</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Nhắc lại Hiền-Tích là con thứ của Văn-Huy, ngay lúc niên thiếu đã đỗ thi hương, chỉ vì nghiên rượu sinh ra lười biếng chẳng chịu học thêm, đến khi được sung một chức Tùy-hiệu ở xứ Hải-Dương, thời thường kéo bạn ra bãi nhà bè bên sông Nghi-hà cùng nhau chè chén, nhân có một hôm ông xuống bên tắm chợt trong thấy có một quyền vở đề ở trên bê, ông bên mở ra xem thử, thì thấy bên trong có chép một thiên phú cờ rất hay. Ông rất lấy làm thích chí, ngâm đi ngâm lại thành ra thuộc lòng. Thế rồi đến khoa ất sừ ông cũng đi thi, may sao kỳ đầu gặp bạn giúp sức nên đăng trôi chảy, đến kỳ thứ hai, ông mang theo một hồ rượu, trước khi làm bài ông đã uống say tùy lý, nằm vật xướng chống đánh một giấc ngủ cho đến xế chiều. Lúc ấy giới bồng nỗi con giống tổ, sấm chớp ầm ầm. Bấy giờ ông mới sực tỉnh, mở mắt nhìn quanh thấy có 4, 5 tờ giấy bay đến trước mặt, vội nhặt lấy coi, thì là một bài Tự lục (phủ) dùng với đề tài ấy, thì ông hết sức vui mừng, cảm ơn trời phật phù hộ nên mới có sự may mắn như vậy, rồi ông chép đúng nguyên văn đem nộp, thành ra kỳ ấy cũng được đồ cao. Đến kỳ thứ 3.là kỳ thi phủ, đầu đề lại trùng với bài phú cờ mà ông đã đọc thuộc lòng, nên ông lại được trùng luôn kỳ nữa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>HVB_003_0384</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>追至四場日學業文廢不能措一辭因取晉侯國語舊傳凡諸鄙俚者換以新聲每句撥成輒需乘醉吟詠采察官見之謂曰天日已晚入皆行文過半而新進士何乃尚番空卷而放浪酣歌乎續酩酊音落頃答之日欲寫郎寫何難遂寫了這傳授納</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Thế là do sự may mắn ông đã lọt được 3 kỳ, duy còn kỳ thứ tư (4) nữa, là kỳ khó nhất, mà ông bỏ học lâu ngày, thành ra không sao viết nổi, thế rồi nhân lúc ngồi bồn ông nhớ đến chuyện Luru-Hầu lưu, nguyên là bài phú quốc âm, ông bèn sửa lại những chữ quê kịch, sửa xong câu nào thì lại dắc ý ngâm vang cả lên, nhân viên kiểm soát thấy vậy đến hỏi: Kia quan Nghè Tân khoa, mặt giới đã xế bóng rồi, bài vô ai cũng sắp sửa viết xong, có sao Ngài còn để quyền trăng mà cứ uống rượu ngâm tràn như vậy. Ông nghe tiếng viên Giám-sát duc giả thì cũng gật gù đáp rằng: Ư muốn viết thì viết có khó chi, thế rồi ông đem quyền ra viết ngay bài phú Luru-Hâu đem nộp, rõ thực minh Sở dầu Ngọ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>HVB_003_0385</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>時同考院有知音者見其詞調清遠每得佳句郎援筆闋之因語諸同院曰這卷寧為我院獨私當送與亞覆考獻笑既而覆考官會者以為戲談大笑周一場聲聞于外采察官見問全院具道其事</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Nhưng mà may sao trong hàng Giám-khảo cũng có một vị cũng thích quốc âm, nhìn qua bài phú của ông nhận thấy lời lẽ tân kỳ, gặp những câu hay cảm bút khuyên lấy khuyên để, rồi lại nói với Khảo quan khác rằng: quyền này chúng ta không nên giữ riêng, tất phải để sang bên phòng phục-khảo để hiển các vị ấy một trận cười, quả nhiên các vị phục-khảo khi nhận được quyền của ông, tức khắc đỏ xô lại coi ai cũng ôm bụng cả cười, tưởng chúng đến vỡ cả đám! khiến cho các vị Giám-sát đương ở bên ngoài, tưởng rằng bên trong có chuyện cãi nhau chạy vào can thiệp, nhưng rồi sau khi rõ chuyện thì cũng không sao nên được trận cười.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>HVB_003_0386</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>考訖即擇諸中卷者適同候旨時上以其取中頗少亟差往命增取之諸考官對諸中官曰申格之文這等卷已盡矣其餘無足之取中官以內首見逼考官曰所存者晉侯一卷外此更無中官郎馳回具奏有首判云晉侯不取更取何人郎傳與考官批取饒而返同觀之葉已取中輒藏不匿以宣露後績仕至兵部左侍郎會我朝中興出首左遷宣光處承使魯任</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Thế là khoa thi ấy vào kỳ thứ tư, ông làm lạc đề nên phải bị rót, nhưng theo lệ thường, hễ chấm thi xong khảo quan phải chọn những quyền trung cách để cả về Kinh xét lại, khoa này Hoàng-Thượng thấy dở ít quá bèn hạ lệnh lấy thêm: Trung-quan mang lệnh ra trường thì, Khảo-quan cũng nói: Văn bài kỳ này kém quá, ngoài mấy chục quyền trung cách thì không còn quyền nào có thể lấy thêm được nữa, nhưng Trung-quan nhất định không nghe. Lúc ấy không biết vô tình hay hữu ý mà Khảo-quan lại giả nhồi rằng: Hiện đây chỉ còn 1 quyền Luru-Hầu mà thôi chứ chẳng còn quyền nào khá nữa. Trung-quan thấy vậy bèn dẹ bắn tẩu về Triều, Hoàng-Thượng xem qua bản tẩu thấy có hai chữ Luru-Hầu, Ngại liền cảm bút phê ngay mấy chữ Luru-Hầu chẳng lấy thì còn lấy ai, Luru-Hầu bất thủ cánh thủ hà nhân. Phè xong Ngại bèn truyền lệnh cho Khảo-quan phải lấy quyền đó. Đến khi dẹ quyền về Kinh thì Ngại mới biết, nhưng đã cho đồ mất rồi nên cũng đánh phải bỏ qua để khỏi lộ chuyện, về sau ông Tích cũng làm đến Bình-bộ Thị-lạng gặp lúc Triều-đình trung hung ông phải dời lên Tuyên-Quang nhưng được lưu nhiệm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>HVB_003_0387</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>按自有科目以來諸預中格者必是文理可取茲以國語傳取中頗微訛傳或者是時莫朝取士無章故有此異爭亦以見其為學在人而中否之中有天數存焉近日有監生者八省試第四場文理不成卻寫國音雜技投納試場官論以無為行仍論失監生袁訢幸免是為效類準之戒為初學</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Xét thấy nước nhà từ khi có khoa mục cho đến ngày nay, những quyền đã được trưng cách văn lý cũng đều hay cả, thế mà khoa này lại thấy 1 quyền quốc ngữ! phải chẳng là chuyện bịa đặt, hay là thời đó về việc khoa cử chưa có chương trình nhất định, cho nên mới có truyền là như vậy, nhưng nó cũng tỏ cho ta thấy rằng: học văn rộng hẹp là do ở người, còn lúc thì cử đỗ đạt hay không, hoặc giả cũng có thiên số nằm trong đó vậy. Nhưng mà việc này biết đâu chả là sự thật, bởi vì sau đó cũng có một Giám-sinh trong ngày thì ở hàng Tinh, đến kỳ thứ 4 anh cũng không làm nổi bài, nên đã phải viết những câu quốc âm làm nhảm đem nộp, Quan trường cho là vô hạnh, định truật cả chức Giám-sinh, về sau van lấy thâm thiết mới được miễn nghi. Đó cũng là một tấm gương sáng cho kẻ chỉ toàn bất chước đề cầu may vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>HVB_003_0388</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>安陽中行記</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Cát cúc thàn lưu Võ tộc, thế truyền tước lộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>HVB_003_0389</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>安陽中行有武姓者起世寒微而頗好學</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Huyện An-Dương, xã Trung-hàng có một họ Võ, nhà đầu bần hàn, nhưng tính thích làm điều thiện.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>HVB_003_0390</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>時有裴氏來風水師相地釋得地吉塗之亊襄其師謂曰之這曷世世公假未審我家能稱此否既而受神人罵日本地係我管了汝何人來塗我地不穢必有災殃其人特疑不決未幾幾舉家病作族中不寧復變神人謂曰汝福淺不堪此命我晉後待武強汝當讓與他則汝子孫亦當享他之報</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Lúc ấy trong áp có một phu-gia thường đi đón thầy phong thủy về coi đất, khi tìm được đất đem tàng xong rồi đến đêm mơ thấy có một vị thần về bảo: Địa phương đây thuộc quyền của ta cai quản, vậy mi là hàng người nào, lại dám đem mộ tàng vào địa phận của ta, muốn tốt phải bốc đi ngay, bằng không thì sẽ có tai họa đó. Nhưng mà phu ông sau khi tỉnh giấc thì lại du dự không muốn bốc đi, chẳng ngờ từ đấy người nhà bị ốm la liệt, và cả trong họ cũng mất an ninh, bấy giờ ông lại mơ thấy thần nhân về bảo: Nhà mi phước bạc không xứng đáng với ngôi đất quí ấy đâu. Vả lại ngôi ấy ta đã đề dành cho nhà họ Võ, vậy người nên nhường cho y, rồi sau con cháu nhà người cũng được y bảo đáp lại, chẳng cũng tốt hơn hay sao.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>HVB_003_0391</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>其人如言即邀武氏告之曰我有吉地一穴今許與汝來日汝家發福當無忘我子孫武氏許諸郎將先人塟之</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Về phần phu ông khi thấy thần nhân bảo mộng đến lượt thứ hai, bấy giờ ông mới quyết định theo đúng như lời trong mộng, cho mọi họ Võ đến nhà bảo cho biết là: Tôi có tìm được một ngôi đất quí, nay muốn nhường cho quí ông, ví thử sau này kết phát thì nên nhớ đến con cháu nhà tôi, ông nghĩ thế nào? Ho Võ thấy phu ông có tâm lòng tốt như vậy, nên cũng cảm tạ và nhận lời ngay, rồi đem phần mộ tiên nhân táng vào huyệt đó,</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>HVB_003_0392</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>其後武家興旺多產才藝健武的人中興問滅莫有向道功榮封功臣至今世襲典兵爵禄未次誘言安陽中行金誠璽淡蓋言世臣之多也</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>quả nhiên từ đây về sau gia-dinh mỗi ngày một thêm thịnh vượng, trong họ sản xuất được lắm nhân tài, nhất là võ nghệ, lại có nhiều tay tri đồng hơn đời, trong thời trung-hung có công hướng đạo để diệt họ Mạc, nhiều người đã được phong trước công thần, con cháu cũng được kế thế nắm giữ bình quyền, đến nay vẫn còn thịnh vượng, vì thế ngạn ngữ có câu: An-Dương nhất xã trung-hàng, Kim-Thành nhất làng Quỳnh-Khê nghĩa là nói về những xã trâm anh kế thế vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>HVB_003_0393</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>陽宅、紫泥鄧庭記</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Huyệt tại thiềm thử ảnh, bạc nghệ nhân đắc nhập vương cung</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>HVB_003_0394</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>安山縣北荒地之西有石嶺千餘峯盤桓一里許清奇可愛中有石洞</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Huyện An- Sơn địa phận xã Tứ-Trâm, có dãy núi đá cộng hơn mười ngọn quanh co hơn một dặm trường, trong rất thanh tú, bên trong có một cái động, dưới có ngôi chùa, Tiên thánh vương xây sẵn cung điện ở đó để ra ngoạn cảnh luôn luôn, nên mỗi đời tên là xã Long-Châu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>HVB_003_0395</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>舊傳有仕社人鄒庚家貧為人傭借適在田間校未有相客經過二言我有吉地一處如有何人請者我即與之度聞其言去禾而上前来拜請因邀北寒同只辨得一黍小鶴為禮前致辭曰僕候遇明師自知有福但家貧冷淡愧怍殊深倘吾師惠以福地幸來時發誓不忘恩拒人見其誠心即引在山傍蟾蜍又一指之曰此地最好當作陽宅居之必然大發富貴但得近君後急撤去之切不可要庚依言即構茅屋數間居之</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Xét thấy phía đông dãy núi có một ngọn nhỏ nhỏ lên trong giống hết như con Thiềm-thứ. Tục truyền rằng xã ấy có người tên là Đặng-Canh nhà nghèo phải đi làm mướn, một hôm anh đương nhỏ mà ở trong dãy núi, bỗng thấy có một người Tàu đi qua bảo với anh rằng: Ta đây mới tìm được ngôi đất quí, nếu ai muốn xin- thì ta cũng cho. Canh nghe thấy Tàu nói thế liền bỏ mà dấy chạy lên quy xuống trước mặt xin thấy làm ơn, rồi dồn thấy về nhà, đi xoay vát mãi mới biện được có một niêu cơm nếp để làm dò lẻ, rồi anh thú thực với thấy địa rằng: Tôi nay được gặp mình sư tử biết rằng nhà có đại hồng phúc, chỉ vì gia cảnh nghèo nàn lấy làm vô cùng hổ thẹn. Nếu thấy ra ơn giúp cho ngời huyệt quí ấy, sau này có được phát đạt, xin thề chẳng dám quên ơn. Chủ thầy địa nghe xong nhận thấy anh quả có tấm lòng thành, lập tức dẫm anh ra chỗ chân núi thiêm thử, chỉ vào núi đó bảo đây là cục đất quí lắm, nhưng nó thuộc về dương-trạch, vậy anh nên làm nhà đề ở, tất nhiên sẽ phát giàu sang. Duy có một điều hễ đến khi nào được gần vua chúa, thì phải dỡ nhà đi ở chỗ khác, chứ đừng ở lại làm chi. Canh nghe thấy địa chỉ bảo như vậy, lập tức theo đúng như lời, dựng ngay mấy gian nhà là đề ở,</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>HVB_003_0396</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>纔及三年時有打魚俗例其池在山傍宅之前長潤數大許邑人鑒網相下庚於池中忍值魚鬚斷其絕郎上池畔山邊取藤英接經束之腰間忽然陽事大舉壯硬異常原有敵樁一啟恐不敵敵因晉浸池中不敵上畔時打魚陸續而歸庭獨不見眾人意其得魚而藏匿者其母郎徙尋之見廣猶在池中仍聲以遲歸之故廣郎鮮魚共母將同襃解釋其藤陽事漸漸而倒</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>mới ở được ba năm trời, thì gặp được ngày trong áp có lệ đánh cá, ao cá ở ngay cạnh núi và ở trước mặt nhà anh, ao rộng kẻ mấy chục trượng, chẳng ngờ giữa lúc dân làng kẻ nom người vô dương mãi bất cá ở dưới ao, thì Canh hị dứt đây buộc giỏ. Anh vội lên trên bờ rào bút một sợi dây Chia-với để buộc ngang lưng rồi lại lội xuống, thì ngay lúc ấy dương vật của anh bỗng thấy thượng lên và nó cũng dẫm là thường, một đoạn khổ rách của anh chẳng còn cách nào để che kín được, vì thế anh không dám lên, cho mãi đến lúc đánh cá xong rồi người làng đã kéo lên hết, chỉ còn có một mình anh lẩn quần dưới ao, ai cũng nghĩ rằng anh bắt được cá lớn nên còn đấu điểm chi đây. Giữa lúc ấy thân mẫu của anh ở nhà, nhìn thấy dân làng đã kéo về cả mà sao anh lại chưa về, nên bà sôt ruột chạy ra xem sao, khi ra tới nơi thấy anh còn dương mò mẩm dưới ao, thi bà quát tháo dục đã, bấy giờ anh mới cỏi chiếc giỏ cá trao cho mẹ đem về trước, thì lạ thay, cái đoạn giấy ấy vừa buông ra khỏi thắt lưng, dương vật của anh nó cũng từ từ cựp xuống!</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>HVB_003_0397</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>既歸世問其故庾具以宴告母即取藤使試佩之陽輒勃起築安試箋驗母取曝乾置之灶上</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Khi về đến nhà mẹ hỏi duyên có tại sao? Anh cũng nói thực như vậy. Mẹ bên đi cắt một ít đây Chia-với đem về phơi khô, gác lên trốc bếp, muốn xem thực hư thế nào, bà mẹ thường bảo anh đem thứ đây ấy buộc vào lưng, lần nào cũng thấy hiệu nghiệm y như hôm trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>HVB_003_0398</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>時陳裕宗陽爭不舉廢罔治弗效使人禰詣國中有能治者許天下民祿之半適詣至伊社庚丹聞之曰劣陽是世之病，使者具道可其六詳母曰我家有一物必能治之母子即取而勝隨使者赴京獻上祿宗佩之忽然陽事雄壯生得二皇子以度為神醫畫之宮中侍藥賞資不可勝計寵幸無比</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Dịp đầu may mắn là nhường! vì giữa lúc ấy vua Trần-Dụ-Tông cũng dương bị chứng liệt dương, các quan thầy thuốc ra công điều trị không có hiệu quả, triều định phái viên đi khắp trong nước hỏi xem ai có món gì chữa khỏi được bệnh nhà vua, thì chia đôi quyền lợi thiên hạ. Một hôm sứ-giả về đến Tử-Trần, tuyên bố mệnh lệnh cho dân làng biết về việc tìm thầy thuốc vân vân: Bà mẹ Đặng-Canh nghe nói biết rằng cơ hội đã sắp đến nơi, bà liên xin vào yết kiến sứ-giả hỏi bệnh dương liệt nó là bệnh gì? Sứ-giả kề rõ bệnh tình như thế. Bà liền thưa rằng: Nếu như vậy nhà chúng tôi cũng có món thuốc trị được bệnh đó. Sứ-giả thấy vậy liền đưa mẹ còn bà về kinh thành tàu với nhà vua: vua cho triệu vào, bà đem những sợi Chia-với khô ấy dâng lên, nhà vua buộc thử vào người, quả nhiên thấy có công hiệu ngoài sức tưởng tượng, rồi ngài sinh luôn được hai (2) Hoàng-Tử, khen mẹ con Canh là bậc thần-y, giữ ở trong cung hầu hạ thang thuốc, luôn luôn ban thưởng, sùng hành không ai sánh tầy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>HVB_003_0399</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>廣既得君都忘客人之言不徹舊宅其後庚子通渙宮女事覺被刑庚被驅囘田產盡沒</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Riêng về phần Canh sau khi được vua sủng hành, anh liên quen bằng những lời thày địa chỉ bảo năm xưa, không chịu dỡ nhà đem đi nơi khác, rồi sau con trai của Canh, thông dâm với các cung-nữ, công việc phát giác, bị xử tử hình, và Canh cũng bị trực xuất, tịch thu hết cả gia tài, thành ra anh bị dôi rết như cũ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>HVB_003_0400</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>始曩時貧寒的人接這宅接外有高數武形如理藥刀盤以故贓得各又宅處與山相近每日月斜照山影隨下胡王之知蟾蜍在屋簷上當如身在蟾宮故得近君王出入宮掖但嫌宅在山傍地荒其適又前面卻山去來靡定以故富貴不久</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Xét thấy ngôi dương cơ này về phía trước mặt, có thửa ruộng cao ước chừng 3 mẫu, trong hình như chiếc dao câu thái thuốc, cho nên mới phát danh y. Còn chỗ nhà ở vì nó sát ngay chân núi, mặt trời mặt trăng mỗi khi ngả bóng chiếu tạt xuống nhà, trong như hình con Thiềm-thư ngồi ở trên nóc, vì như thân ở cung thêm, nên mới được ở bên cạnh quân vương, từ do ra vào cung cấm. Nhưng mà chỉ hiềm một nỗi: nhà ở bên non, địa thế bức bách, bên ngoài còn có biết bao ngọn núi phân lại, cho nên phù quái chẳng được lâu dài, đó là theo phương pháp địa lý mà nói đại khái như vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>HVB_003_0401</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>按國史記裕宗遊西湖墜水中鄒英齋之復生因陽事不舉廣請取童男肝和陽起石服之及通同胞女以助疑道乃通其端羅裕宗服之屢驗與此說不同未知孰是</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Còn như về phần sử-ký: thì trong quốc sử có chép rõ rằng: Khi vua Dụ-Tông ra chơi Tây-Hồ, đương người trên thuyền tự nhiên ngã nháo xuống nước, sau khi vót lên, Đặng-Canh dùng phép châm cứu nên ngài mới được hồi sinh, về sau ngài bị liệt dương, Đặng-Canh xin cho mở bung dựa trẻ con trai lấy gan hòa với vị Dương-khởi-Thạch để cho vua uống, và bảo vua phải thông dâm với chị em ruột để giúp thêm cho dương khi, nhà vua làm theo phương pháp quả có hiệu nghiệm, cho nên Canh mới được vua tin dùng. Nay đem sử liệu so với thuyết trên thì thấy khác hẳn, chưa rõ thực hư thế nào,</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>HVB_003_0402</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>晚斬詠史詩云</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>vì thế nhà thơ Thoát-Hiên có vinh bài thơ tứ-tuyệt như sau:</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>HVB_003_0403</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>既因薄載云要君寵又啟滯風逞已私</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Đã đem nghề mọn mua tâm chúa! Lại mở lò dâm thỏa chí ma!</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>HVB_003_0404</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>行險小人心似鬼當時謾說是神殿罔</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Hiểm thực tiểu nhân loài quỉ quốc? Ai oì đứng với tướng Hoa-Đà.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>HVB_003_0405</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>神怪厚捧光明寺</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Bật-Sô Tăng kiếp hậu vi vọng quốc Hoàng-Đế</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>HVB_003_0406</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>嘉福縣厚榛社屬海陽處有光明寺千重碧樹四面波濤里路通其前河水繞其左真禪門一勝槳也</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Huyện Gia-Phước xã Hậu-Bồng có ngôi chùa Quang-Minh từ, ngôi chùa ẩn giữa ngàn cây cổ-thụ xanh biếc, bốn bề đồng tráng nước trong, trước mặt có đường quan lộ, bên tả có sông Vĩnh-Hà, quả thực là một danh lam thắng cảnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>HVB_003_0407</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>舊傳有一婆蒼僧號玄真住持在此只誦經禮佛不營人間事業利欲卻意人皆以為禪處高僧稱許</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Chùa này nguyên trước có một nhà sư hiệu là Bật-Sô tên tư là Huyện-Minh trụ trì tại đó, ngày tháng chỉ mãi tung niệm, hầu quên thế sự, chẳng hề ham muốn lợi danh, 'ai cũng khen là một vị cao tăng hiếm có.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>HVB_003_0408</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>晚年于房後打眼忽愛彌陀伏降臨實殿邀來按前謂曰爾有功梵教委厥上有主且慈悲一點善心達于玄後劫富降生為胡王國皇帝爾其知之</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Bồng một hôm, Sư đang ngủ trưa ở chốn trai phòng, trong lúc mơ mộng thấy Đức Di-Đà hiện trước tòa sen, gọi Sư đến trước án bảo rằng: Nhà người có công đối với phật giáo, kẻ đã lâu năm, một niệm từ bi, Phật Tổ đã từng chứng giám. Vậy nên sau này hóa kiếp được làm Hoàng-Đế của một nước lớn. Người đã biết chưa?</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>HVB_003_0409</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>既醒乃召諸道場謂曰某自初出家飯依禦率每謂塵緣淨盡果福圓成寶座金蓮是我遂後身之報誼意他日迴輪都以累年或行三夫消也得塵寰一大艱難且日月國君之哲言昔人所不願也不知生前葉障其未盡除去而然耶這事現有問夜佛旨爾等同記吾言當於圓寂之後寫來數為詭以驗之也</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Về phần nhà Sư sau khi tỉnh dậy, nhớ đến những lời trong mộng, bèn triều các Đạo - Tràng đến bảo rằng: Ta từ lúc xuất gia nương nhờ của Phật, tưởng rằng tẩy hết trần duyên, tu tròn quả phúc để lên Tòa Sen, đó là hậu báo cho lúc siêu sinh, ngòi đầu đến kiếp luân hồi, thì bao công phu khở hành, lại phải dời lấy các chức vị gian nan lớn nhất ở trong trân thế. Vả lại lời thề của vua nước Nhật-Nguyệt kia, người xưa cũng còn chẳng muốn, (diễn này tham khảo ở mục Tăng-nhân-Tượng trong Minh-Kỷ) không rõ kiếp trước của ta còn có nghiệp chướng chi đây mà đến nổi thế? Thời thì việc này đêm qua đức Phật đã từng chỉ bảo, vậy thì các người hãy nên nhớ lấy những lời ta nói, đợi đến khi ta về châu Phật, các người sẽ ghi chớp lại, để xem ứng nghiệm ra sao?</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>HVB_003_0410</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>及卒後道場依其言乃朱書十字于肩上用佛家火藥法收舍利時銀瓶埋之尋藥以石庵時加供養焉</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Các Đạo-Trang theo lời di chúc trên đây, đến khi Sư mất, họ cũng lấy son viết đúng 10 chữ lên vai nhà Sư rồi theo phương pháp nhà Phật, đem xác ra thiêu, thiêu hóa xong mới lượm lấy năm than xương, dựng vào một chiếc bình bằng bạc để đem mai táng, rồi sau dựng một ngôi chùa bằng đá lên trên, tháng ngày gia công tung niệm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>HVB_003_0411</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>都說永賴縣前烈社阮自隱家貪好學及長從師長安路經予此每往返間輒檢特休息或至登臨玩賞亦不知其光明奇焉弘寳稱敬崇甲長科中進士第仕至禮部左侍郎</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Lại nói về xã Tiền-Liệt thuộc huyện Vĩnh-Lại có quan Lễ-Bộ Thị-Lang là Nguyễn-tư-Cường, lúc nhỏ nhà nghèo nhưng rất chăm học, nhận một buổi sớm cậu vào khất thực nhà ông Đô-nho, ông thấy cậu học trò nhỏ, bèn đọc một câu ngạn ngữ để điều cậu rằng: Âm vị khai nhi dương đã lộ, nguyên câu chữ nôm là Cánh cửa Hồng-môn còn khép nếp, Ngọn cò xích xí đã lăm le, rồi lấy câu đó làm để tài bảo cậu vịnh một bài thơ nghe thử. Chỉ sau giây phút câu đã làm xong, câu trạng (thứ 3-4) viết rằng:,, Hồng-môn kiểm thuận do hoài nặc, xích xí kỳ mao dĩ chỉ huy, tức là dịch câu chữ nôm ở trên, quả đã thần tình, nên được nhiều người truyền tụng. Về sau đến tuổi trưởng thành cậu ra Tràng-An du học, mỗi khi qua chùa cậu vẫn vào chơi nghỉ mát, nhưng cũng không dễ ý nhận đó chính là chùa Quang-Minh tự rồi đến niên hiệu Hoàng-Định (1600-1619), cậu đồ Tiến-Sĩ vào khoa Giáp-Thin, làm đến chức Thị-Lang,</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>HVB_003_0412</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>其後徙北使皇帝召問曰小南國陪臣未知南國各蓋何處是光明寺即跪奏曰臣本國各蓋甚矣如瓊林普明報天寵田諸古刺臣亦素聞至如光明寺各未知何處不審有何緣故願示其詳</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>cách mấy năm sau phượng mang sang sứ Bắc quốc, vua nhà Minh triều đến trước mặt hỏi rằng: Người là Sư-giả An-Nam chắc rằng biết hết những nơi danh lam bên đó. Vậy có chùa nào gọi tên là Quang-Minh tự hay không? Ông quí gọi tàu: Danh lam ở bên bồn quốc, thần biết rất nhiều, tỷ như các chùa Quỳnh-Lâm, Bão-Thiên, Phổ-Minh, Quy-Điền đều là những nơi cổ tích thần đều nghe tiếng, còn chùa Quang-Minh sự thực không biết ở đâu, thế mà ngày nay Hoàng-Đế phân hỏi, chẳng hay có duyên có gì, xin cho hạ thần được rõ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>HVB_003_0413</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>皇帝喟然曰朕生之始有上朱書痕迹冤然脫意脫是依奇僧令雖降生上國脫欲洗了字痕不知有何術公郎奏曰臣聞佛家有八水洗塵之法既是寺中降誕須取那寺中井水洗之方可耳皇帝曰爾言誠有理宜為朕亟還本國尋這奇的取井水來那時頗有授用公頒拜命謝而還且達於我國王因備行探訪不意乃原捧社寺平日素所休息處也</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Minh-Đế có về ngậm ngùi phân bảo: Trầm đây từ lúc mới sinh thấy ở bên vai có viết mấy chữ bằng son An-Nam quốc Quang-Minh tự Sa viết tự khẩu công là mươi chữ ngắn viết hãy còn rành rành. Trầm ngòi tiếp trước là một vị sư ở trong chùa đó mà sau giáng sanh sang đây; nay trầm muốn lấy những vết chữ đó, vậy người biết có phép gì màu nhiệm hay không? Ông tàu rằng: Hạ thần nghe nói phương pháp tẩy trần của nhà Phật phải dùng đến dược thủy, ngày nay Hoàng-Đế biết rõ kiếp trước ở chùa, thì nên lấy thứ nước giếng ở trong chùa đó đem về để tẩy thì mới sạch được. Minh-đế khen phải rồi bảo ông về bồn quốc tìm lấy nước giếng chùa ấy đem sang, sẽ có hậu thưởng. Ông lỉnh mang bài tạ quay về, khi về tới nước nhà, bèn đem việc ấy tàu trinh vua ta, rồi đi thăm hỏi khắp nơi, chẳng ngờ lại chính là ngôi chùa của xã Hậu-Đồng mà ngày thường ông vẫn vào đó nghỉ mát.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>HVB_003_0414</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>至來年貢部函奉命往仍取井水就京獻上皇命取來洗之果然消得舊痕書頁愈加光澤因大喜慰再召公至將大論諭曰朕得尓敵發頃悟首綠不亦終焉浪度尓宜為朕重修梵字輪矣一新俾今春勝昔春非惟副朕心之誠耳類尓國鐘靈為中花皇帝是品中之一奇也朕令付尔金三百兩銀三千兩帝同作仗奇並金銀燈擎各一樹番為奉佛之器還國之後當了此功德如朕親視否則佛家有得福果報之機須於身上與弟子孫上看</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Thế rồi cách một năm sau đến hạn công hiến, ông lại phung mang sang sử, nhân tiện đem cả nước giếng ấy sang Yên-Kinh cùng hiến một thề. Hoàng-Đế nhà Minh cả mừng, lập tức đem ra tây ngay, quả nhiên vét cũ biển đi đầu hết, da để lại được sáng bóng thêm lên. Ngài rất lấy làm hài lòng, cho triều ông vào khen ngợi. Trẫm vì có Khanh chỉ điểm chợt tình ngộ mới tiên duyên, nếu không thì thực bỏ phí cơ hội. Vậy Khanh nên vì trẫm gia sức trung tu, cửa Phật một phen đổi mới, xuân nay khác hẳn xuân xưa, làm được như thế chẳng những trọn được lòng thành bảo bồn của trẫm, mà lại còn biểu dương được rằng: nước người có cảnh linh thiêng chung đúc ra được một vị Trung-Hoa đại-đế, đối với phẩm giá thực là một việc ly kỳ. Vậy nay trẫm trao cho người 300 lạng vàng đem về xây dựng 36 tòa Phật tự và đèn cây bằng vàng bằng bạc mỗi thứ một cây để làm tự khi, sau khi về nước Khanh nên làm trọn cái công đức đó, cũng như trẫm được nhìn thấy tận nơi. Nếu không thì cơ báo ứng về sự hòa phục của Phật sẽ ở ngay bên thân của Khanh và con cháu Khanh đó nghe...</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>HVB_003_0415</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>公陛辭拜頒而歸再以這等情頭達于國王國王大奇仍許依天朝所命公即以所頒金銀市木鳴工崇修梵字一簽前後三十六連範巍哉壯麗恰似真明境界兼築浮屠一塔近百餘丈延望簷然惟金銀兩燈檠番為家用別鑄鐵器世方之</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Ông nghe lời vua nhà Minh phân bảo xong lập tức bài tạ ra về, đem câu truyện đó tàu trinh quốc vương, vương cũng lấy làm kỳ di và hứa cho ông được phép làm theo mạng lệnh Minh triều. Được quốc vương nhà cho phép xong rồi, ông bèn dem số vàng bạc ấy ra sắm sửa vật liệu, thuê mướn nhân công, dựng một tòa chùa trước sau 36 nóc, nguy nga tráng lệ như cảnh Tây-thiên; lại còn xây thêm một tháp Phù-đồ gần một trăm bậc (cấp) chót vót từng máy, duy có cây đèn vàng bạc thì ông để lại nhà dùng, rồi đúc hai cây đèn sắt thay vào tự khi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>HVB_003_0416</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>其後八朝成祖哲王聞公相人之術乘間問曰我諸子誰啟闕守王基時萬都公得寵將有儲副之命而清都位次未及公以相術直對曰諸子惟清當有天下萬都公深愠佯乃問公以他事因投以毒藥尋卒後文祖王正位公贈封太保郡公其雲仍至今猶存率皆廣賤每以兩燈敬手報應為根</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Thế rồi cách mấy năm sau, vua Thành-Tổ nghe nói ông tình về môn xem tướng, nhân lúc nhân hạ mới hỏi ông rằng: Khanh thử coi tướng các con của trẫm, xem ai xứng đáng nói ngôi? Nguyên vì lúc ấy Vạn - Quân - Công được sủng ái nhất, rất có hy vọng lên ngôi sừ nhi, còn Thanh-Đô-Vương kẻ về vị thứ hãy còn kém xa, thế mà ông giám căn cứ vào tướng mạo tàu thẳng ngay rằng: Thần xem tướng các Hoàng-tử duy có Thanh-Đô-Vương là người sẽ được thiên hạ sau này đó thôi? Chẳng ngờ câu truyện xem tướng lại lọt đến tai Quân-Công, Quân-Công biết thế, giả vờ triệu ông vào dinh để hỏi việc khác, nhưng rồi thừa cơ đầu độc nên ông bị chết. Đến sau Vãn-Tổ chính thức được lên ngôi vương, Ngài mới tặng phong cho ông trước Thái-Bửu Quân-Công và lại phong trước cho các cháu, đồng dõi họ ấy tới nay vẫn còn, nhưng đều nghèo khó, vì thế họ đều oán hận là bởi ngày trước ông đã đánh tráo hai cây đèn thơ, cho nên con cháu phải chiêu bảo ứng không hay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>HVB_003_0417</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>其寺廢經兵火付之殘灰惟浮屠一嶺巍然獨存近曰官軍進討等賊亦曾於此住焉因考僧人事跡以為慈悲中一傳奇也</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Còn như tòa chùa do ông xây dựng, trải qua bao cuộc binh hỏa, cái gì cũng biến ra tro, thế mà chỉ riêng cây tháp thì vẫn nguy nga tồn tại. Gần đây quan quân kéo đi chinh phạt cũng thường đóng quân tại đó, nhân thế mới hồi ra được sự tích cao tăng, thì ai cũng cho rằng một câu truyện lạ trong cảnh từ bi vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>HVB_003_0418</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>保伍冊郡公記</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Kim-Tông Thân miếu hội đê tỏa Điền-Quân</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>HVB_003_0419</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>細都公乃保母吳順妃之弟以故顯典兵永慶年間、公年號、大安縣、受雲社堤路水潰、珥都公奉命培築</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Huyện Thiên-Bản, xã Bảo-Ngũ, có Điền-Quận-Công, vì là em ruột bà Bảo-mẫu Mạc-Thuận-Phi, cho nên được dự binh quyền. Vào khoảng niên hiệu Vĩnh-Khánh (1729-32), nhân có khúc đê ở xã Thọ.Triền thuộc huyện Đại-An bị nước xoáy vỡ. Điền-Quận được lệnh tới đó bồi đắp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>HVB_003_0420</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>每行水次經縣內金錢河津上有水神原廟捻著靈應地方之人皆崇奉之時細郡公舟纔過廟輒不進若有沮截之者郡公指而罵曰爾在此不駐護一方之民使水常為民害今我往障頹波歇命至此尓今欲反沮我耶大罵良久忽見前出舟五艘突來跳戰</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Khi thuyền qua bên Kim-Tông, trên bên có một miếu thờ Thủy-Thần rất là linh-trùng, địa-phương sùng bài kẻ đã lâu đời. Quận-Điền bỗng thấy thuyền mình tự nhiên dừng lại, tựa hồ có gì ngăn cản. Ông liên nói giận trở lên trên miếu mảng rằng: Nhà ngươn ở đây sao chẳng bảo hộ địa hạt, để cho nước lụt thường làm hại dân. Nay ta phung mạng tới đây bồi đắp, mà ngươn lại muốn ngăn cản là có làm sao? Lạ thay ông vừa quát mắng xong, thì thấy trước mặt hiện ra 5 chiếc thuyền lớn trong có quân-sĩ khi giới, xông tới ào ào như hình khiêu chiến.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>HVB_003_0421</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>都細素精符法知是木神步見郎於船中內按劍步墨書符念呪已分而撥船夫刀搶併出兩邊鏡口對射煙霧昏黑咫尺不勝辨約一更許這出船先卻顧貯間已失所在</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Nhưng ông cũng tinh về thuật phu thủy, đoán biết ngay là Thủy-Thần hóa phép để chống lại mình, nên cũng đứng ở trong thuyền, tuốt kiếm hò thần Thiên-Cương, thư phù niệm chú, rồi mới hạ lệnh cho các tướng-sĩ cầm sản giáo mác xông lên, hai bên đều dùng hỏa pháo bắn ra, khói đen mù một phủ khắp một vùng, đứng cách chỉ một gang tấc cũng chẳng trông rõ thứ gi. Trận chiến kéo dài độ một trống canh thì thuyền bên địch bồng biển đầu mất, thế là bên ông thắng lợi hoàn toàn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>HVB_003_0422</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>細郡即順流而往至貢口誤路處與役築作土功將完問有巨魚楊鬱水次望似一小小帆以尾邀水大浪懷山堤路築復瀆裂隨難隨破如是者效次遍罰公無知之何郎暗祝于水神曰非者廟經過一時錯誤還亦衡撞神其勿以介意所胡玉餘灵默護使堤圓完一方之義受福不淺</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Đánh tan được bọn âm binh âm tướng, ông bên hạ lệnh cho thuyền cứ việc thuận dòng thẳng tiến đến nơi cửa công, rồi sai quân-sĩ dắp lại quảng đê bị vỡ, chẳng -ngờ khi dấp gần xong, thì bồng thấy một con cá lớn bơi lại, to bằng một chiếc thuyền buồm, đuôi nó vẫy vùng thành những ngọn sóng cao như trái núi, làm cho đoạn đê vừa dắp lại bị vỡ tung, vỡ rồi ông lại sai dấp, dấp xong nó lại phá luôn, trải đến mấy lần như vậy. Chẳng biết đối phó ra sao, bấy giờ ông mới làm dám khẩn vãi như sau: Kinh thưa Thủy-Thần linh-vị: Mới rồi đi qua trước miếu, tôi đây một phen lầm lỡ trót đã xúc phạm oai linh, xin Thần cũng đừng để ý, ra sức ủng hộ cho cuộc bồi dắp sớm được hoàn thành, tức là Thần đã ban phúc cho dân địa phương không phải nhỏ vậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>HVB_003_0423</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>自是堪得堅實不復潰破獨自負戲之曰我築成此堤雖百靈神亦難壞了忽然河水無故翻動狂波怒浪衝激其問這堤裂表尚一叚原來這處貢口傍出沖淵與大河密通乃俗傳淵底有神常引河水透八以故難於障塞時細都已損了許多工夫因此會怒今斂取縣內竹木環剿樹柵再取民家敗臼破礎并一切舊石煉灰投下俄見淵底瀝沸魚浮而斃者不勝其數再加培築刻衣處復完</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Khẩn Thần xong rồi ông lại ra lệnh cho quân-sĩ bắt tay vào việc, hễ dấp đến đầu thì đất chắc nich đến đó, không bị vỡ lỗ chỗ nào. Nhưng rồi sau khi dấp xong ông lại tự phụ tuyên bố ngay rằng: Khúc đê của ta dấp đây dầu có 100 vị thần linh cũng không tài nào phá được. Lạ thay lúc ấy trời dương im lặng, thế mà ông vừa nói xong mấy câu thì trên mặt nước lại thấy chuyển động, sóng lại cuộn cuộn nổi lên, đập vào chân đê phá vỡ ngay một quãng lớn, làm ông hoàng sợ, vội vàng sắm sửa lễ vật để ta thân linh rồi sai dắp lại, nhưng mà dắp mãi cũng chỉ tôn công chư không thu được kết quả. Nhưng vì chổ cửa công đây là một khúc quẹo nằm cạnh đại hà, tục truyền ở dưới đây đầm có nhiều linh vật đục lỗ phía dưới đưa nước phù sa vào trong, cho nên rất khó hàn khẩu! Nhưng riêng về Quân-Điền với quãng đê này, ông đã tổn rất nhiều công mà chẳng thành sự, nên ông lấy làm cấm gián, sai quân đi khắp huyện hạt, chặt lấy tre gỗ, và đi thâu lượm vật liệu của dân để làm đà cồn, rồi lại nhào với với đà dỡ xuống lòng sông, chỉ trong chốc lát thì thấy rùa, cá, ba ba chết nổi lên trên mặt nước nhan nhản. Cứ thế làm luôn đến nửa tháng trời thì ông bị bệnh,</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>HVB_003_0424</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>纔半月間細都忍藥不火熟病知在青火黃無灼中廢同治弗效詭病而沒</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>thân thể nóng như nước sôi, chẳng có thuốc gì chữa được, rồi ông tử trần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>HVB_003_0425</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>未幾保任邑內民富不寧邑人相與祈禱于本社廟中冀可捍災忽內有一人動而起放大聲曰我是細都公被水神黃乎抱恨而沒兮欲報仇第無象馬兵器難以相關寄達保母尊好為我辨送來不亦非推損物且將父人矣</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Nhưng rồi sau khi ông mất chưa được bao lâu, thì các gia súc trong ấp Bảo-Ngũ lại bị chết dịch, nhân dân trong ấp bàn nhau sửa lễ kỳ-an, để mong tai qua nạn khỏi. Chẳng ngợ giữa lúc đương tế ở trong đình làng, thì thấy trong đầm nhân dân bỗng có một người đứng phất ngay đây, đầu tóc dựng ngược, hai mắt trọn trừng, khóc lớn lên rằng: Ta đây là Điền-Quân-Công mới bị Thủy-Thần ám hại, ôm hận về dưới suối vàng, nay muốn phục thù chỉ hiềm không có ngựa voi khí giới, thì dịch sao nổi với Thủy-Thần. Vậy xin nhẫn lời cho chị tức là Bảo-Mẫu chuẩn bị giúp cho. Nếu không thì chẳng những sức vật bị hại, mà cả nhân mạng cũng khó bảo toàn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>HVB_003_0426</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>保母聞言即合造與器一如珥郡公生特戰具完足焚之翌日見地方一帶河波濤淘湧如牛馬爭夫岸傍聽者似有于戈交戰之聲魚鬱魚紛然而驚保母聞之度必理郡與水神交戰因祝之曰吾弟今番共他戰勝負如何倘其有靈即以相報</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Nói về bà chị tức là Bảo-Mẫu, sau khi nhận được tin ông hiện lên nhắn bảo, bà cũng theo đúng như lời, sắm sửa các thứ đồ mã, như voi, ngựa và các khí cụ bằng giấy đem đốt, rồi đến hôm sau thì một dài sông của địa phận đó, bỗng thấy sóng lớn nổi dậy như thể muốn ngựa giao tranh, nhân dân ở hai bên bờ nghe thấy những tiếng gươm giáo chạm nhau xoang-xoảng, cá tôm nổi lên mặt nước rất nhiều. Bảo-Mẫu đoán rằng: Em mình cùng Thủy-Thần giao chiến, nên bà cũng làm bảm khẩn: phen này giao chiến thắng phụ ra sao nếu em có thiêng thì báo tin ngay cho chị biết với.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>HVB_003_0427</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>忽有一人搖動躍起言曰拜上尊姊贈以兵器戰具勢顓張皇但他族類宴聚已素練習我兵新習水戰未請兼以人形都非介胄薄弱之眾難與他鱗甲相鬩纏一交鋒更被挫了今後不可與鬩當於貢口處創一新綱讓他居之竟免積弊釁族人依言而材構作不日告成自是一方河道不聞有異事焉</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Lạ thay bà vừa khẩn xong, thì hồng có một người nhà dừng phất ngay lên vừa đảo la liệt vừa nói: Xin bài tạ Chị đã cho binh mã gươm dao. Nhưng vì quân địch quá nhiều và lại tinh nhuệ. Còn binh của ta toàn là lính mới, về phần thủy chiến chưa quen; gia đĩ các đồ bằng giấy không thể thắng nổi những quân có lăn gia vậy cũng dẫm, vì thế cho nên thoát mới giao phong liên bị tan rã. Thời thì từ đây về sau đừng nên đối địch với chúng mà thêm thiệt hại. Chi bằng hãy dựng một ngôi đền mới ở trên cửa Cống, nhường cho Thủy-Thần ở đó, để khỏi tích lũy hiểm thù v. v..... Trong họ thấy ông hiện lên phân bảo như vậy, cũng theo dùng lời đi mua vật liệu xây dựng, sau khi dựng xong ngôi đền, thì quảng sông đó nghe không có truyền gì là nữa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>HVB_003_0428</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>彊暴大王記、</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Cường-bạo vương, kẻ kháng Thiên Tướng</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>HVB_003_0429</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>紂大王天本縣令改務、見縝令改人也先其母愛黑漢神謂曰托生猴焉族遂有娠而生時年將十五歲五為兒時好耕耘種樹吃然有巨人之性及長率性彊暴耿目一世都忘父母不有忘臘惟灶神朝祈又禱難得一鯨亦必熟而供之神亦知其心時加頸應</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Cường-bạo đại-vương người làng Bối-Cẩm thuộc huyện Thiên-Bản, khi trước bà mẹ nằm mộng thấy có một người mặt đen bảo cho bà biết: Thần trên núi Nhạc sẽ giáng sinh xuống họ này đây, rồi bà thụ thai, dân sinh ra ông; đến khi lớn tuổi ông rất ngổ ngưu, coi đời bằng nửa con mất, đến nỗi quên cả ngày giỗ cha mẹ, nhưng mà đối với Táo-quân thì lại sớm hôm khấn bài, dù khi bắt được một vài con tôm, cũng đem nấu nướng để cùng, cho nên thần Táo cũng thấu đến tâm lòng thành, thời thường ủng hộ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>HVB_003_0430</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>一日父母以狀罪訢于天天郎命雷神降而打之灶神密先頭告王來計灶神曰以滑物塗屋上縱有火觀石斧其盛何施王依其言遂取箝夢條日揚攢與水油相和至日直于屋上偏洒之玉潜伏暗中候視俄而風雨驟至雷神從天而下繞躡星脊上滑而墜地王從中突步揮杖擊之雷神倏然不見奪得赤銅繩長丈餘郎於靜地埋之</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Thế rồi bỗng có một hôm cha mẹ đem hết tội trạng tố cáo ở trên thiên đình. Trời bên sai ngay lời thần xuống đánh. Ông Táo biết truyền xuống trước bảo khẽ với Vương: Vương xin Táo-quân, bày kế giúp đỡ. Táo-quân báo lấy chất tròn như mổ phết lên trên mái nhà, để cho Thiên-loi không có chỗ đứng, thì dẫu roi lừa búa đá cũng khó giữ trò v.v... Vương được Táo-quân dạy cho điều kế như vậy, lập tức đi kiếm Mông-toi đem về giả lấy nước giột, và sắm các thứ dầu mỡ để sẵn, đến hôm Thiên-loi xuống đánh, thì trước giờ đó Vương đem các thứ lên trát khắp mái nhà, rồi nắp phía dưới chờ xem động tĩnh ra sao? Quả nhiên hôm ấy Vương vừa nắp được một lát, thì trời nôi con mưa gió sấm chớp ầm ầm! Thiên-lợi phượng mang Ngọc-Hoàng cởi mây nhảy xuống nóc nhà, liền bị chất tron làm cho tuột chân té nháo xuống đất. Vương ở trong nhà ngó thấy, lập tức vác gậy xông ra, đánh ngay một đòn bồ thượng. Thiên-lợi loạng choạng chạy về Thiên-đình, Vương đoạt được sợi dây đồng đỏ dài hơn một trượng, bèn đem chôn ở một nơi cao ráo sạch sẽ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>HVB_003_0431</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>雷神歸具以事奏昊天天怒謂靈神曰三才我為之尊汝震我威所擊無不摧折者何等人物乃與霹靂抗衡潛報水神以某日引水而上北固彊暴亦為魚敞之餌</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Còn phần Thiên-lợi sau khi chạy thoát trở lên tàu với Ngọc-Hoàng thì Ngài cả giận quơ mắng: Ta đây là bậc chí tôn trong hạng Tam-tái, nay cho nhà người xuống dưới hạ giới để làm vang đội oai danh, hỏi rằng đánh đầu mà chẳng nát gãy? Vậy nay tên ấy là hạng người nào lại dám chống cự thiên oai? Thế thì nhà người phải nên mặt báo với các Thủy-Thần, hẹn đúng ngày giờ, dâng nước lên bắt tên bạo tặc đó, để làm mời cho lũ cá giải, nghe!</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>HVB_003_0432</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>灶神復告之玉遂結蕉為筏取葉為旗翌日水大至浸没蘆舍王郎乘筏而出擊手鼓鳴羅織橫水面設舟震于天大言我與天交戰</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Lần này Táo-quân nghe được lệnh trên, thì lại với vàng quay xuống báo tin cho Bạo-Vương biết. Vương bèn đi đóng bè chuỗi, lấy lá làm cờ, chuẩn bị vừa xong thì sáng hôm sau tự nhiên thấy nước dâng lên, ngập cả nhà cửa. Vương ngồi trên bè chuỗi đánh trống khua chiêng, tung hoành ở trên mặt nước, miệng thì thét lớn Ta lên giao chiến với trời!</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>HVB_003_0433</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>時昊天方與群像論善惡聞之曰何處聲甚緊群像相視莫祛對雷神方候旨對曰是乃彊暴之賊向既逃罪令復于常恭望定奪昊天說思良久曰弗敬怒淪動輒抗拒是乃無天地的人今姑赦之任他長惡弗悛禍必將意至仍命水細縮水而下五竟免害</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Giữa lúc ấy trời đương cùng chư tiên phân đoàn những kẻ thiện ác ở dưới trần gian, bồng nghe phía dưới có tiếng om xóm, Ngái liên phân hỏi: Trống chiêng ở đâu mà thức dữ thế? các Tiên chưa dám tàu qua, thì Lôi-thần đứng hầu bên cạnh đã vội thưa rằng: Đó là một tên cương bạo, trước đã tránh khỏi thiên hình, nên nay mới giám cần rỡ như vậy, cúi xin Hoàng-Đế định đoạt ra sao? Ngọc-Hoàng nghe tàu xong thì Ngái trầm ngâm một lát rồi mới phân bảo: Hư! Tên kia đã chẳng kinh nề lại còn kháng cự luôn luôn, thực là một kẻ vô thiên vô địa, âu là ngày nay hãy tạm tha thứ, để nó quen thói làm can, rồi sau tai và tự nhiên sẽ đến. Phán xong Ngái liền hạ lệnh cho Thủy-Thần hãy rút nước đi, Thế là Vương lại thoát nạn lần nữa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>HVB_003_0434</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>即乃家人具道可以遙來得灶神之助允上帝一言一動必先顯告吾復何辜自是益橫其志復得一田雞自灸而食之不以獻灶神怒其忘己思中傷之</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Nhưng thoát nạn xong rồi thì Vương có về tự đắc, cho gọi tất cả người nhà tập hợp chung quanh rồi bảo cho biết: từ trước đến nay nhờ có Táo-quân ủng-hộ, phàm trên Thượng-Đế nhất cử nhất động, Ngái cũng bảo trước cho hay, thì ta còn lo gì nữa. Thế rồi từ đây Vương lại hết sức kiêu ngạo. Có hôm bắt được một con cua bẻ đem nướng ăn ngay, không cùng Táo-quân như mọi lần trước, Táo-quân tức giận về nỗi vong ân, quyết tâm tìm kế hãm hại để cho bò ghét.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>HVB_003_0435</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>一日顯告五曰來日雷神打汝五又問許灶神曰次早汝往耕于田如雷雨將至即於耕木夾處處穿車其中外用橫木裹鎖定自無事王不意一為其所賣依計而行既而雷雨漫天而至王欲斂之不脹竟被打斂頭間雨霽群牛觸土培之宛然成大阜鄉人即其土處封墳</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Thế rồi bỗng có một hôm Táo-quân hiện lên bảo với Vương rằng: Ngày mai Thiên-lợi lại xuống đánh nhà người đó. Vương hỏi có kế gì không? Táo-quân bảo: Sáng mai thì người cứ việc ra cây ngoài rương, hễ thấy trời sắp đổ mưa, sấm chớp nổ đây, thì người rủn tay vào trong chỗ kẽm chiếc cây, bên ngoài lấy đoạn cây ngang chân lên hai chân rồi khóa chặt lại, thế là sẽ được bình an. Vương thấy Táo-quân bày cho kẻ sách là lùng như vậy, cũng chẳng biết rằng Táo-quân đã nói đối mình, nên cứ lẳng lặng nghe theo. Ngờ đâu đến sáng hôm sau, lúc trời dỡ mưa, sấm chớp vang tai loe mắt! Vương muốn tháo chân chạy trốn thì đã chẳng kịp, thành ra bị sét đánh chết tươi, rồi lúc tạnh mưa dân trâu lấy sừng húc đất dắp lên tử thi thành 1 cái gò rất lớn, người làng nhân đó dắp thành phần mộ,</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>HVB_003_0436</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>數年後方民夜勤畜類不寧一日有村翁早行過予墳處見立而言曰我彊暴靈神爾立廟祀之可保無虞不卒無遺類矣將收牛者皆見之村翁歸而道其事鄕遂構祠崇奉自是始得寧居今至封為福神</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>rồi mấy năm sau địa phương bị dịch trâu bò, nhân dân rất là xao xuyến, thì hổng một hôm trong thôn có một ông già, sáng sớm đi qua phần mộ, tự nhiên đứng lại quát to lên rằng: Ta đây tức là Cường-Bạo Linh-Thần. Chúng bay biết phép lập miếu phượng thờ, thì ta phù hộ chẳng có việc chi, vì bằng không nghe Ta sẽ giết hết. Giữa lúc ấy thì có một bọn chăn trâu nghe thấy như vậy, trở về thuật truyền lại với dân làng, nhân dân bên dựng đền thờ từ đấy mới được yên ổn, đến nay được phong sắc là Phúc-Thần,</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>HVB_003_0437</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>往年有騷客過祠下題詩云</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>trước kia có một nhà thơ đi qua ngoài cửa cung vinh một bài thơ rằng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>HVB_003_0438</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>二五鍾靈象貫殊深霄黑漢應嘉符</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Lạ thay nhị ngũ khi hồn nhiều. Điểm bảo canh khuya tướng mặt đen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>HVB_003_0439</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>赤脂煉藥雷何畏白日乘桴水不虞</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Mở nhốt, Thiên-lôi không hoảng sợ. Nước dâng, bê chuối khỏi lo phiền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>HVB_003_0440</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>香火永存光祿典泰盤默祻壯玉都</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Trải bao Tự điển còn hương khói. Giúp mãi hoàng đô được vững bền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>HVB_003_0441</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>古云敬遠今臣味君子休將辨有無</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Kinh viêng đối lời nên ngầm nghĩ. Có, không đứng với nói huyền thiên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>HVB_003_0442</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>羅山阮監生記</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Nguyễn-Giám-Sinh tác vọng quốc Hoàng-đế</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>HVB_003_0443</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>羅山縣有阮姓者，生時赤光滿室，人以為失火，父視之，卒無見火而賴</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Huyện La-Son có người họ Nguyễn, lúc mới sinh, trong phòng bồng thấy đỏ rực, người nhà tưởng rằng thất hỏa, nhưng lúc vào coi thì chẳng có gì.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>HVB_003_0444</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>異性謹愿端懿常受業于本社監生之門毎日輒先至酒掃學堂坐必別席不與諸生同坐</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Rồi khi lớn lên coi rất đĩnh ngợ; tính lại ôn hòa ngay thẳng, cha mẹ cho sang thụ nghiệp một vị Giám-sinh cũng làng, hôm nào cậu cũng đến trước, quét rửa nhà trường, đến lúc vào học thì cậu ngồi riêng biệt một chiếu, chứ không ngồi chung với bạn học trò, vì thế nên vẫn được thầy chú ý hơn hết.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>HVB_003_0445</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>是年近鄉試科其師與之就憲便官析出稍通一各意使官見立命坐日縱本處取中一各亦當取許但他時得志自蒙記憶既而謂曰新貢士第出其師當番別有說詰</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Thế rồi chẳng bao lâu nữa đến khoa thi hương, thấy dấn cầu sang giới thiệu với quan Hiến-Sư xin cho được dự một tên trong kỳ xảo-thông. Hiến-Sư trong thấy vội vàng vái chào mọi người, ôn tôn nói rằng: Bồn chúc lấy đồ một tên chẳng có ngại chi, mong rằng sau này đặc chi sẽ thơ đến cho. Thời thì vị Công-Sinh mới hãy tạm ra ngoài, để thấy ở lại một lát cùng ta nói câu truyện riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>HVB_003_0446</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>憲官即以問這弟子來歷與八門父近學業如何師具道其詳</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Khi cậu lui ra ngoài rồi, Hiến-Sư bèn hỏi Giám-sinh về lai lịch của người đệ-tử, theo học đã bao lâu rồi? và sự học văn ra sao? Giám-sinh kể lại một lượt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>HVB_003_0447</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>憲官曰我昨日夜夢見一人來謁前道有銅柱斧鉞旌旗僕杖皆五者其隨從軍士約二萬人直至廳前謂曰今欲應考稍通不審官肯許一名否俄而醒覺想愛中所見端的是人不審將來做何等事業</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Hiến-Sư nghe xong bảo Giám-sinh rằng: Đêm trước tôi năm mơ thấy một người xin vào yết kiến, mà đoàn tiền đạo lại có quân sĩ vác phù việt bằng đồng, và có cờ quạt nghi về như một vương-giả, còn đoàn quân sĩ theo sau thì có đến hơn hai vạn, khi tiến vào cửa sảnh nói với tôi rằng: Muốn xin ưng cử kỳ thì xảo-thông, chẳng hay quan ngài có cho được dự một tên chẳng tá? Bây giờ nhớ lại cái người trong mộng, chính là cái cậu học sinh mới rồi, chẳng biết sau này cậu ấy làm nên sự nghiệp to tát đến đâu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>HVB_003_0448</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>是科院公八場果中第一未幾無病而終但精氣不散家人常見倏然往來猶如平日每有求必應大著靈異</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Nghè Hiến-Sử kề lại giấc mơ kỳ quặc như thế, ông Đồ cũng lấy làm lạ, cáo biết ra về, rồi trong năm ấy cậu Nguyễn vào thi trúng ngay nhất cử; nhưng mà chẳng được bao lâu thì cậu ốm chết, chết rồi mà phần tình khi vẫn chẳng tiêu tan, người nhà vẫn thường trông thấy hình bóng đi lại như lúc sinh thời, cậu khấn việc gì cũng thấy ứng nghiệm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>HVB_003_0449</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>其後有鄉人舟行至神海口於是舟中卒倒後時方頸因語人曰我見阮醫生乘舟一葉黃袍一帶侍衛甚嚴召至罰謂曰某原承上帝命降生人世作該帝王但方今收福旅方隆不可與竪立故復朝帝所別生他國今其從北去矣煩為歸報家人不必思念言詭雝然而去瞧見來乃是一魚既而振其家具以前事苦之自是不見頭應</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Thế rồi cách mấy năm sau có một người làng đi qua cửa bê Thân-phù, đương ngồi trong thuyền tự nhiên bị ngã thiếp đi hồi lâu, đến khi tỉnh dậy bảo người nhà rằng: Mới rồi ta gặp cậu Nguyễn Giám-Sinh ngồi trong một chiếc thuyền nhỏ, mình mặc hoàng-báo, lưng thắt đại ngọc, có đám thì về đi hầu, cho gọi ta đến bảo rằng: Mở đây ngày trước váng mạng Ngọc-Hoàng thác sinh xuống dưới tràn thế đẳng làm đế-vương nước này; nhưng vì quốc-vương hiện tại phục âm còn bền, vì lẽ anh hùng không thể lường lập, cho nên ta lại trở về Thiên-đình, ngày nay Ngọc-Hoàng lại sai thác sinh ở một nước khác. Vậy phiền người về nói với gia-nhân của ta cũng đừng nên thương nhớ nữa. Nói xong thì lại bay đi, đến khi người ấy chợt tỉnh mới biết là một giấc mộng, lúc về bên đêm truyền ấy kể lại cho nhà cậu nghe, rồi cũng từ đấy không thấy hiện linh như trước nữa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>HVB_003_0450</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>按此與亂鬚將見唐太宗而輒哀者乎亦相類是其神器有命不可以智力求蓋以道推之則雖天帝降生方且讓他一頭近世么麼之輩不自揣量卻于井底窺天晴圖望外亦有離身之禍世之亂賊可不成哉</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Xét ra truyện này cũng giống như truyện Cù-Tu Tướng-quân khi nhìn thấy Đường-Thái-Tông, tự nhien khóc rất thâm thiết (xuất xứ ở cuốn Hương-Đại?) như vậy mới biết ngôi báu phải có mệnh trời, không thể đem tri lực ra mà cầu cạnh được, bởi vì theo dùng đạo-lý thì dẫu trời cho giáng sinh cũng phải nhượng người có đức. Thế mà gần đây những bọn yêu quái, chẳng lượng sức mình, lại ngồi ở dưới đây giếng để tròng lên trời, lo toàn cướp ngôi tôn quỉ, chẳng sớm thì muộn rồi cũng mang lấy cái nạn diệt vong, sao chúng lại chẳng soi tấm gương đó để mà tu tỉnh vậy.</t>
         </is>
       </c>
     </row>

--- a/data/corpus/HVB_003_parallel.xlsx
+++ b/data/corpus/HVB_003_parallel.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C473"/>
+  <dimension ref="A1:C452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,8024 +436,7667 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HVB_003_0500</t>
+          <t>HVB_003_0000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>我昨日有約惠然肯來今卻忘之必被吾兄見責後清因回家途</t>
+          <t>公餘捷記</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kia tôi có hẹn Ông vào chơi, chẳng ngờ ngày nay quên</t>
+          <t>CÔNG-DƯ TIỆP-KÝ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HVB_003_0501</t>
+          <t>HVB_003_0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>經像洲郎詣公訪舊公屬家人整燕肥豬二隻又資盛二盞同坐款</t>
+          <t>世家</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>đi qua Tiên-Châu có ghé vào thăm Ông Hò, Ông bảo gia nhân giết hai con heo luộc chín, và 4 mâm xoi để</t>
+          <t>THẾ GIA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HVB_003_0502</t>
+          <t>HVB_003_0002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>待清契盡豬款各一角公契盡豬一隻又款一盤又契清新餘各一角只</t>
+          <t>慕澤武侯其先祖福建人名澤唐武宗會昌元年武代韓鈞為交州刺史愛其鄕風水之異遂卜居焉因以唐安名其縣可謂各其色中間始改為暮澤</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>về phần Ông Thanh chỉ ăn hết có 1 góc, còn Ông Hò thì ăn hết cả 3 mâm xôi và một con heo,</t>
+          <t>Gia thế họ Võ ở làng Mộ-Trạch, Tiền tổ ngày xưa tên là Hồn vốn người ở tỉnh Phúc-Kiến bên Tâu, (vào thời Đường Kinh-Tông Bửu-Nguyên năm đầu, ông được thay chân Hàn-Thiếu sang làm Đô-hộ-Sứ bên An-Nam). Đến thời Đường Võ-Tông niên hiệu năm đầu Hồi-Xương (841), lại thay Hàn-Uốc sang làm Giao-châu Thư-Sứ (có chỗ chép là Kinh lược sứ). Vì thích phong thủy tốt đẹp của làng đó, ông bên tình kế đóng ở đây, nhân thế mới lấy 2 chữ Dương-An để đặt tên huyện, và chữ Khả-Mộ để đặt tên ấp (sau mỗi đời tên là Mộ-Trạch).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HVB_003_0503</t>
+          <t>HVB_003_0003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>需其半以與狹人相吃溝大驚曰古稱慕澤先生以食為各但又于</t>
+          <t>至明宗當寧時竟佐其其弟農同登第大學並以文學稱官至內侍行遣左僕射始著宗門圖其世次科名壽爵秩自是可考</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>một nĩa cho người theo hầu, khiến cho Ông Thanh hết sức kinh ngạc nói rằng : Đời trước khen Mộ-Trạch Tiên-</t>
+          <t>Kế đến thời vua Minh-Tông (1314-23) nhà Trần thì ông Nghiêu-Lá và em là Nông cũng đều đã đạt, (chức Đại-học-sĩ đời ra Quốc-sử), cả hai cũng đều nói tiếng chữ tốt văn hay, dần dần được thăng đến chức Hành-khiển Tả-bộc-Xạ. Bấy giờ các ông mới dời lại họ hàng, xếp thành chi thứ, khoa danh phẩm trước, ghi chú phân minh, từ đó mới có thể khảo sát rõ được.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HVB_003_0504</t>
+          <t>HVB_003_0004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>十八十二之數若與兄同時適避三舍矣公大笑其後官歷左侍郎奉</t>
+          <t>時有高王七世孫各問南來徧者我國各地至邑門外</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bác đến 3 dặm vậy, Ông Hò dắc ý cả cười. Rồi sau Ông Hò làm đến chức Hữu-thị-Lang, phung</t>
+          <t>Trong thời gian này có cháu 7 đời của Cao-Vương Hao Vương, tên gọi là Lư, khi sang nước ta. Ông đi xem tất cả những nơi danh thắng nước ta khi đến công lăng Mộ-Trạch, Ông chỉ tay, bảo mọi người rằng: Đây là cái Tô Tấn sĩ đó!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HVB_003_0505</t>
+          <t>HVB_003_0005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>往北使時同縣安照社署人頗有口辨使之從行至燕京北人聞公善</t>
+          <t>己亥科四名其二各一名者從來相屬同時登用至二十員通邑皆準後裔</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mạng sang sứ Bắc quốc, lúc ấy có người lái buôn ở</t>
+          <t>Quả nhiên đến thời nhà Lê vào khoảng niên hiệu Thịnh - Đức (1653) và năm Vĩnh - Thọ (1658 - 1662) những kỳ xuân thì chiếm bằng rất nhiều, khoa bình-thân đã được 3 người, đến khoa kỷ hội đã được 4 người, còn một hai người thì chẳng khoa nào bổ trọng, đồng thời có đến 13 vị cùng ra làm quan một lúc! Toàn dân trong ấp đều là dòng dõi Ông Hồn, nguyên trước ông được tặng phong Phúc-thần, rồi sau tiếp tục được phong huy hiệu. Hiện nay sau đám rừng nhỏ, vẫn còn một năm đất, tức là ngôi mộ của ông Vũ-Hồn vậy.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HVB_003_0506</t>
+          <t>HVB_003_0006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>食因作一具十八層召公赴宴架梯而食公每吃了一層輒取鉢擲下至</t>
+          <t>推諧公道聲同往北俟約以事清後請福延一往就認武家宗派會賊挾擷阻陸路不通因徙安廣水道囘執事遂不果達</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mâm cỡ, chồng chất lên 18 từng rồi triệu Ông vào dự yến ! khi ăn phải treo lên thang, ăn hết từng trên thì</t>
+          <t>Khoảng năm Dương-Đức (1672-1674) thời vua Lê Gia-Tông, bọn ông Duy-Hải và Công-Đạo cùng sang sứ bên Tàu, các ông hẹn nhau sau khi xong việc sẽ xin 'qua thăm Phúc-Kiến một lần, để nhận dòng đội họ Vũ bên ấy! nhưng vì lúc ấy có loạn, đường bộ bị nghẽn, nên không thực hành được.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HVB_003_0507</t>
+          <t>HVB_003_0007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>最後層見一人頭在焉傷人皆掩目不敎正視公大聲喚從者來曰書我</t>
+          <t>求治間稽距崇天施屬山南土黃土黃崙尚書黃公賓又奉北使有武老爺者邀諸途而問曰使君乃安南陪臣必知本國明王族不審武潭苗裔當今闊闊如何</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quảng bát đã xuống đất rồi mới ăn đến từng dưới. Chẳng ngờ khi ăn đến từng dưới cùng thấy có một cái</t>
+          <t>Mãi đến thời vua Lê Hy-Tông khoảng niên hiệu Vĩnh-Trị (1676-80) có quan Thượng-thư là Hoàng-công-Bửu quê huyện Thổ-Hoàng thuộc phủ Thiên Thi, phượng mang sang sứ bên Tàu, hổng có ông gia họ Vũ đón ở doc đường hồi Công-Bửu rằng: Sứ thân là người An-nam biết rõ những họ có danh ở bên Quí quốc. Vây tôi xin hỏi dòng dõi của họ Vũ-Hồn hiện nay thế nào?</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HVB_003_0508</t>
+          <t>HVB_003_0008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>生不知滋味今皇帝賜我食北人頭最為佳品汝將取醋來我吃了蓋</t>
+          <t>公無道其因言武氏在天朝亦稱世科各余亨連</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lính theo hầu : Ta đây là kẻ Thư sinh chưa nếm những món ăn là bao giờ, ngày nay Hoàng - Đế cho ăn số</t>
+          <t>Công-Bửu bên kè hết chuyện họ Vũ bên này cho ông gia nghe. Ông gia nghe xong bắt giác hoa chân múa tay, luôn miệng khen tốt, rồi lại kẻ rằng: Họ Vũ chúng tôi ở bên Thiên Triều, cũng đẳng khoa danh kẻ thế, ngày nay cũng vẫn phát đạt như thường!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HVB_003_0509</t>
+          <t>HVB_003_0009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>這頭乃魚人頭與人無異世所罕見故他以此怵公今見其不懾頗有侵</t>
+          <t>既而告別以銀子十笏玄絲十匹高贈但使還間忽遇將都婁俞念我國洪澤之役事見寧相為失報仇率其徒遮截回程行裝為其所掠歸國曰鏡見道來一徧而已人言天南科第慕</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trong y như số người thực, mà đời ít khi được thấy, cho nên họ mới dùng nó để thử thách Ông, nay thấy</t>
+          <t>Thế rồi trước khi cáo biệt, ông gia đưa ra 10 hốt bạc và 10 tấm nhiều màu huyện để ghi làm quà tặng. Nhưng lúc trở về doc đường hổng gặp người vợ Đặng-Diệu nguyên là tướng của nhà Minh, năm trước bị chết tại trận Hồng-Đàm, ngày nay thị muốn báo thù cho chồng, nên mỗi đêm bọn gia nhân đón đường Sứ giả, cướp lột hết cả hành trang! Đến khi về nước, chỉ còn thuật lại câu chuyện thế thôi! Ngày nay người ta cho là: Khoa bảng nước nhà riêng làng Mộ-Trạch chiếm nhiều nhất, là nhờ vương khí của bắc phương tự tập ở đó vậy.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HVB_003_0510</t>
+          <t>HVB_003_0010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>渡之語即挈取頭去尋托以他爭篤其兩目使人撓之自曼所而往三</t>
+          <t>都探花武賊撰文會賀幀有詩讚云</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bịt mắt Ông lại, cho người công đi an trí một nơi,</t>
+          <t>Vi thế khoảng niên hiệu Vĩnh-Thịnh, khoa thi Nhâm thin (1712) Đinh-Ân thi đồ Tấn-sĩ, lúc ấy có vị Thâm-hoa Võ-Thành, là người cùng huyện, soạn bức trưởng mừng cho Văn-hội, đã có bài thơ khen ngợi như sau:</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HVB_003_0511</t>
+          <t>HVB_003_0011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>日復就這賣因問公何賣否公已默記其心郎答云乃前日賜晏賣也</t>
+          <t>八百年來通脹長各公願聖世相望</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vì Ông đã đề tâm từ trước, nên giả nhồi ngay rằng : Chính đây là chỗ ăn yến hôm</t>
+          <t>Ngàn năm đạo đức mạch truyền qua. Đời rồi vang lừng tiếng đại gia.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HVB_003_0512</t>
+          <t>HVB_003_0012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>北人謂公莊前知遂敬之時國上連月不雨仍命諸國陪臣修文橋</t>
+          <t>高曾祖考勲賢緒綿爵科各蔭澤光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trong thời gian ấy Bắc quốc đương bị hạn hàn</t>
+          <t>Sự nghiệp Tô tiên đã kẻ thế, Văn chương cháu chất nói đăng khoa!</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HVB_003_0513</t>
+          <t>HVB_003_0013</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>雨公料知天象未雨因奏曰臣小國乞後讓大國先之已而祈之皆不應</t>
+          <t>八葉華門聲來歌三槐王氏適堪芳</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>còn lâu mới mưa nên tàu rằng : Nước Thần bé nhất xin cho làm lễ đảo sau, để nhường nước lớn đảo</t>
+          <t>Tiêu đình là ngọc khoẻ tròn tâm Vương thị sản hòe sánh đủ ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HVB_003_0514</t>
+          <t>HVB_003_0014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>皇帝郎命公對曰有從人學得武公遺法嚴乎風喚雨可遣皇帝郎召</t>
+          <t>鋪張不盡君家事下筆時開翰墨香</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>trước. Quả nhiên Sư Thần các nước đảo mãi cũng đều vô hiệu, bấy giờ vua Tàu mới triệu đến Ông.</t>
+          <t>Cảnh đẹp nhà ông phó chẳng xưê. Ngạt ngào hương mực khắp gần xa.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HVB_003_0515</t>
+          <t>HVB_003_0015</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>之其人奏曰臣有一法須得吉日方可用乃潛觀櫪木根俗曰已見白父鷄</t>
+          <t>尚書曰試有記</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ông tàu rằng : Hạ thần có viên tùy tùng vốn học được phép hô phong hoán vỡ của Không-Minh ngày</t>
+          <t>THƯỢNG-THƯ VÕ-HỮU KÝ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HVB_003_0516</t>
+          <t>HVB_003_0016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>頸草俗曰鷄鵠有黠自知兩期將至即請設壇場禱之已而果得兩皇需大稱</t>
+          <t>武有慕澤人也乃竟佐之曾孫其父伯謙頒歸代路安副使參有陰德生下五男一女竝以貴顯稱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mưa đến nơi, bấy giờ anh mới tàu xin lập đàn câu đảo, quả nhiên mưa xuống âm âm, vua Tàu khen ngợi</t>
+          <t>Ông Võ-Hữu người làng Mộ-Trạch, là cháu 3 đời của Nghiêu-Tà, phụ thân ông tên là Bả-Khiêm, lãnh chức vạn-phủ-phó-Sứ tại Lộ Quy-Hóa, vì có nhiều âm đức nên sau sinh hạ được 5 con gai và 1 con gái đều hiện vinh cả!</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HVB_003_0517</t>
+          <t>HVB_003_0017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>賞封為兩國之師封公為兩國尚書公善辭命應對名聞兩朝皇帝</t>
+          <t>武有生時所居宅其後為追遠相堂堂踊有喬木古樹亭亭時立黃甲幹武詠詩云</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>phong làm Lưỡng quốc Quốc - Sư . Còn Ông thì được phong làm Lưỡng quốc Thượng-thư</t>
+          <t>Còn ngôi nhà của ông sau khi mất, học trò đặt tên là Truy Viễn-Đường, trước nhà có cây tùng cao chót vót mà Tùng-hiên Tiên-sinh (biệt hiệu của cụ Hoàng Giáp Võ-Cán) đã liệt nó vào 1 cành trong 8 cành của làng Mộ-Trạch và có vịnh bài thơ như sau:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HVB_003_0518</t>
+          <t>HVB_003_0018</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>欲晉之使教太子公難之不敬遠奏請造一新堂并備鞭模教具皇子</t>
+          <t>尚書武祖來遺種異風英香火堂前得地生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vua Tàu muốn giữ lại để dạy các Hoàng - tử ; ý Ông không muốn nhưng không giám trái lệnh, nên mới tàu</t>
+          <t>Cối phúc lưu lai tự thuở nào! Từ đường đứng trước đẹp làm sao!</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HVB_003_0519</t>
+          <t>HVB_003_0019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>出有過輒痛加筆箋矣曰先學禮後文學太後酷愛其子奏請擇導</t>
+          <t>翠華蓋參天滋粉代黑怒濤十里樹風聲</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rất đau và bảo cho biết, trước phải học lễ rồi sau mới học văn ! Hoàng-hậu vốn yêu dấu con, không thể nhận</t>
+          <t>Một trời phủ kín cây tân biếc. Mười dặm kêu vang lớp sóng đảo.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HVB_003_0520</t>
+          <t>HVB_003_0020</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>官公以是免歸國後任至尚書春江侯陸少保佀郡公致仕耳</t>
+          <t>高標挺特為人望大器軒昂爵晚成</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>được trở về nước nhà, làm đến Thượng - thư phong Xuân-Giang-Hầu và trước Thiếu-Bảo-Lữ-Quận-Công</t>
+          <t>Chót vót mây xanh người vẫn nghến! Hiện ngang bóng cả tiết càng cao!</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HVB_003_0521</t>
+          <t>HVB_003_0021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>傳公卒後國王頒以嗣棺差人會葬今村內猶有遺塚在焉其後人自	..</t>
+          <t>舊福綿洪培植厚故家喬木永</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Theo như tục truyền thì lúc Ông mất Vua ta có ban cho một cỗ áo quan bằng đồng, và vua bên Tàu cũng</t>
+          <t>Cho hay phúc hậu công bởi đắp. Nhà với cây chung chữ thế hào!</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HVB_003_0522</t>
+          <t>HVB_003_0022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>北歸國王命築室于本社寺及平置庵于其側號國師寺至今香火</t>
+          <t>醫書有為人好古執禮博學洽聞光順樣聖宗癸未科黃甲送任內外諸曹聲價盡無鹽隊五部尚書常浪吟自述詩云雀荊周年官盛踐寧牛曾有之牛耕其清介頗如此</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>danh là chùa Quốc-sur , ngày nay nhang khói</t>
+          <t>Ông Vô-Hữu là người có tánh hiểu cờ thủ lẻ, học rộng lại kiến văn nhiều. Thi đồ Hoàng-Giáp khoa Quí-vị (1463) vào thời Lê Thánh-Tông niên hiệu Quang-Thuận, khi xuất chính trái khắp trong ngoài, tôi đầu dân cũng ca ngợi, dân dân thăng đến ngữ bộ Thượng-Thư. Ông thường ngâm bài tự thuật trong có những câu: nhầm nhiểm chu niên quan lịch tiền, Tề ngưu tằng hữu pháp ngưu canh? nghĩa là: Thấm thoát năm tròn quan trái khắp! trâu mồ thi có, thiếu trâu cày, coi đó dủ biết là người thanh liêm đến như thế nào?</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HVB_003_0523</t>
+          <t>HVB_003_0023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>猶存焉在曰營接這跡內有一二事頗淡訛傳但得子公族人之言且參</t>
+          <t>尤精於筆學能立大成等法徐田載新述書行于世</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>vẫn còn. Xét sự tích này bên trong cũng có vài việc hầu như ngoa truyền, nhưng đó là những câu của người</t>
+          <t>Ngoại điểm văn chương chính sự, ông còn tinh cả toán học, đã lập ra 1 cuốn Toán pháp đại thành trong có chỉ dẫn phép tinh ruộng đất và phương pháp cấy cây, truyền bá trong khắp dân chúng.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HVB_003_0524</t>
+          <t>HVB_003_0024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>諸村邑高年所道來無異故畧記之以俟大德君子焉</t>
+          <t>將城內端門及大興東花等門自李朝營築久歷星霜漸致顔壞皇上特命增葺葺因召公謂曰爾鄉精於等術令諸門修築試等鴻尾數千完了推討規公郎相其高低廣狹等祭黃炎其陳皇上帝治任陶鎔尋命草草之依然完成不差尺寸上深嘉嘆賞日此神籌也仍賜肥田百餘畝以旌其能</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>đây để đợi các vị quan tử sau này chấp chính. CHƯ TÀO HỘI NGHI, PHÙ-KHÊ THIÊN</t>
+          <t>Giữa lúc ấy trong hoàng-thành có các cửa Đoan-môn, cửa Đại-hưng, và cửa Đông-hoa. Xây dựng từ thời nhà Lý, tới nay trải nhiều mưa nắng bị vỡ lở nhiều đoạn. Hoàng Thượng ra lệnh trùng tu, nhân triệu ông vào phân hỏi: — Trẫm nghe nhà người tinh về toán học, vậy nay công việc trùng tu, các cửa, người thử tinh xem gạch đã hết là bao nhiêu thì làm lại được. Ông lỉnh mang ra ngay các cửa do đặc tinh toán xong rồi lập thành đồ bản dâng lên. Hoàng-Thượng bèn sai thợ nung gạch ngói và các vật liệu, bắt đầu khởi công, đến lúc hoàn thành quả nhiên không thừa không thiếu! Hoàng-Thượng tẩm tắc ngợi khen là tay thân toán, rồi thưởng cho ông 100 mẫu ruộng tốt để làm tiêu biểu cho sự tài năng.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HVB_003_0525</t>
+          <t>HVB_003_0025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>范鎮杜注記</t>
+          <t>年七十來戶部尚書曰誠仕嘗作涼亭煥鬱優遊山水以樂大年所居之卷各曰鳳池</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LÀNG PHÙ-KHÊ QUÁCH-CHÚ.</t>
+          <t>Năm ông 70 tuổi, được lãnh chức Hộ bộ Thượng-thư về hưu. Trong lúc thư nhân, ông mới xây nhà nghỉ mát, ngao du sơn thủy, vui thú cảnh gia. Nơi am ông ở đặt tên là Phương-Tri.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HVB_003_0526</t>
+          <t>HVB_003_0026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>海陽之嘉福藍橋社范鎮阪林社杜汪里開相鄰舊傳杜汪邑中</t>
+          <t>後贈太保職光黃乃載六黎簿之子詠詩云</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Người làng Phù-Khê thuộc huyện</t>
+          <t>Sau ông được tặng lên chức Thái-bảo, ông Quang-Bôn có làm thơ mừng như sau:</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HVB_003_0527</t>
+          <t>HVB_003_0027</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>有女精者往往興大祟作變幻百出祈禱願有驗焉注少時臨窗閱書</t>
+          <t>豪傑初由進士科日勤日愼無他諸</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ở lân cận có một người chuyên nghề ăn trộm, bỗng có một lần mò sang bên làng Ông định kiếm một mẻ.</t>
+          <t>Hào kiệt nguyên trong Tán sĩ khoa. Chữ cần chữ thận chẳng sai qua.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HVB_003_0528</t>
+          <t>HVB_003_0028</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>夜間常見一手自窺前伸八汪知其為妖就質諸同縣老法師法師</t>
+          <t>當逃試功各著同列威推德業加</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>thiếp đi. Đến lúc gà gáy anh mới sực tỉnh xốc áo toan di, chợt nghe ở trước mặt có tiếng xôn xao.</t>
+          <t>Ty Tạo thử khắp tài năng rỏ Liêu hữu suy tôn đức nghiệp gia.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HVB_003_0529</t>
+          <t>HVB_003_0029</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>夜間常見一手自應節伸入汪知其箋效就質詣何舉才之師注師</t>
+          <t>廣相守文歆宋璟普朝強物黃張花</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>thế, đáp: Vừa rời lên châu Thượng-Đế, hội nghị với các Nam - Tào, định rằng trong đêm hôm nay sẽ cho</t>
+          <t>Đường Tướng thử văn so Tống-Cảnh Tân Triệu bác vật sánh Trương-Hoa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HVB_003_0530</t>
+          <t>HVB_003_0030</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>手果不肐縮大將曉窻下哀訴曰公當大貴我眉戲耳何忍至此極也</t>
+          <t>午門建青黃相暎映餘慶從知精善家</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>xưng chút nào, giám xin Hoàng-Đế định lại. Hoàng-Đế nghe tàu bên cầm cuốn sở coi qua một</t>
+          <t>Môn đinh rực rỡ màu xanh tía. Tích thiện cho hay bởi những nhà.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HVB_003_0531</t>
+          <t>HVB_003_0031</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>汪曰以我之果做狀元否曰狀元已有范生公當次之汪曰汝有甚灵物即共</t>
+          <t>其孫武穆為人坦蕩人少遊長安稱典兵一啟黎仁宗太祖時有通臣范屯潘般興諒山王宜氏踰牆紱逆公乃文裔謀典業者二國公假以相人之術攘刀殺得范也因急喚二稱引兵赴救收潘敬父其黨盡裁之宮庭為之南清乃遜立聖宗嗣統朝廷護其功進封明義功臣都督府左都督知禮伯尹賞肥田一百畝餘衣為世業</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hàn - Tín gởi thơ cho Yên-Vương trong có câu rằng : Bạch lộc bảo tuyên, thì sự tích ấy ra</t>
+          <t>Cháu tên là Võ-Dư là người vũ dũng can đảm là thường! lúc còn niên thiếu qua chơi Tràng-An, ban đầu được bỗ một chức Điền-binh, đến thời Lê Nhân-Tông (1413-54) có tên Phạm-Đồn và Phan-Ban cùng với Lạng-Sơn Vương Nghi-Dân trèo tường vào cung toàn bài thi nghịch, ông bèn mật muru với Sùng, Kỷ hai vị quốc công, cải trang làm thầy coi tướng, ngầm đất dao vào đâm chết Phạm-Đồn, rồi mới hò hai tướng kéo quân vào bắt sống Phan-Ban và các đồng đảng đem ra chém hết! Sau khi tạo thanh trong cung cảm, bèn đón Thánh-Tông về nỗi ngôi. Sau Triệu đình luận công ban thưởng, ông được tấn phong Minh-Nghĩa Công-Thần, Đô-Đốc Phù-Tà Đô-Đốc, Tri-Lễ-Bá, và được thưởng 100 mẫu phi diễn làm ruộng thế nghiệp.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HVB_003_0532</t>
+          <t>HVB_003_0032</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>我觀我便敵汝俄聞嘔吐聲忽見一物似玉在紋手中精光奪目汪有</t>
+          <t>光賁有詩六</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sao. Quân thần không ai đáp được, chỉ có một mình Ông đặt gởi tàu rằng: Diện tích ấy biên rỡ trong Hán-</t>
+          <t>Vì thế Quang-Bôn có thơ mừng rằng:</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HVB_003_0533</t>
+          <t>HVB_003_0033</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>取吝之師解其繫線自是天邑中不聞怪而泣嘆曰精通舟詞章一出人以</t>
+          <t>早貞才各一世豪唐安知礼擅稱廢</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>thư. Vương sai về lấy gia thư của Ông vào xem quả nhien có thực, Vương khen là người học rộng nhớ</t>
+          <t>Sớm đã tài ba nổi tiếng hào! Đường-An Tri-Lễ kém ai nào?</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HVB_003_0534</t>
+          <t>HVB_003_0034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>賞陳吐王稱之在場屋間甚有聲譽鑲常不逮光靈員員意崇年號丙辰科</t>
+          <t>卻承孔鯉廷趨訓長得曹彬世授韜</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>khiên trách, nhưng rồi chỉ sau ít lâu thì được bổ chức Đốc-đông tại tỉnh Thanh - Hóa, tức là ưu thưởng cho</t>
+          <t>Nhỏ theo của Không nên thì giáo Lớn học Tào-Bản môn lục thao</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HVB_003_0535</t>
+          <t>HVB_003_0035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>會試時年共二十四歲同年同榜至庭試日汪見全題皆素慣</t>
+          <t>許裴載武途曾至踐百年簡竹記動勞</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Triệu vua Lê - Thánh - Tông vào khoảng niên hiệu Vĩnh-Thọ ( 1658-62 tức là thời Lê-Thần-Tông thì</t>
+          <t>Mấy độ Liễu dinh từng xuất nhập. Ngàn năm sử bút nhỏ công lao.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HVB_003_0536</t>
+          <t>HVB_003_0036</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>今番首選醫我無驗時鎮在籠中彷彿見傍有兩人一稱韓琦一稱東</t>
+          <t>莫嫌世道多婉挾門望之巍巍，獨高。</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>phải), văn học nho phong dương lúc thịnh hành, riêng các sĩ tử của lang Mộ-Trạch Hải-Dương , khoa thì</t>
+          <t>Gò ghè phó mặc đời nhiều ngả! Riêng một danh môn chót vót cao.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HVB_003_0537</t>
+          <t>HVB_003_0037</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>方朔附耳讀之滔滔不竭鎮寫之不發聞靜謂琦曰須使任致病以減</t>
+          <t>旁誦言唐安知禮，此之謂也。</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>trao cho Phúc - khảo kiểm lại, xem những quyền nào văn lý đặc sắc, toàn thiên không có vết tích mới phê</t>
+          <t>Thời bấy giờ có câu ngắn gọn: Đường-An biết lễ tức là thế đó.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HVB_003_0538</t>
+          <t>HVB_003_0038</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其力俄見杜汪抱腹申吟不能下筆迨鑲過一段泣病方愈故習燕雖</t>
+          <t>按武有之，後子孫貴盛世生武將文臣永享贈太保武祿陞左府以題頒祗都督武良中進士武延臨中黃甲武仲程武延韶武延恩詭中進士武有之遠孫也</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Các quan Phúc-khảo theo lệnh chọn lọc rất kỹ được có 10 quyền đệ lên Ông xem lại, rồi thái đi 4 quyền</t>
+          <t>Xét ra con cháu ông Võ-Hữu về sau nổi đời vinh hiển, mà đời nào cũng có danh tướng, còn khoa bảng thì phát rất nhiều: ông Vĩnh-Phu được tặng đến chức Thái-Bửu, ông Dư được thăng đến chức Tâ-Phú, ông Tiệm được thăng Đề-Lãnh, ông Sa được thăng chức Tham-Đốc, ông Lương thì đỗ Tấn-sĩ, ông Đinh-Lâm thì đỗ Hoàng-giáp, các ông Trọng-Trinh, Đinh-Thiệu, Đinh-Ân đều đỗ Tấn-sĩ, và đều là cháu xa đời của ông Võ-Hữu.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HVB_003_0539</t>
+          <t>HVB_003_0039</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>多而日力不足既而臚唱鎮中獄元酒中榜眼顯喜語人曰吾今壓倒</t>
+          <t>嘗考私譜父登科錄公以年十四二十二歲中癸未科至泰帝小安年共六十四年以公年紀備之已八十七歲使共為尚有亦在休閒無用之歲</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>còn lấy được 6 quyền, thế rồi đến khi họp phách chỉ có một người đứng vào ưu hàng là Võ-Đăng-Hiền ở làng</t>
+          <t>Nay lại xét trong gia-phả riêng và trong Đặng-khoa-Lục thì ông sinh năm Tân-Dậu (1437), đến năm Quang-Thuận đời Lê-thành-Tông, thì đỗ Tấn-sĩ vào khóa Quí-vị năm ấy mới 23 tuổi, nếu tính đến khoa Đinh-hội thời Cung-Đế thì 61 năm nữa, thành ra lúc ấy đã 87 tuổi, với cái tuổi ấy mà Cụ còn sống thì cũng về hưu đã lâu.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HVB_003_0540</t>
+          <t>HVB_003_0040</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>杜注矣。	—</t>
+          <t>地先朝國史云遣松楊侯武有持節往古桑進封莫登庸為安國王這武有乃山西武人與公偶同姓字至胡公仕楊作越監據錄尋以文臣二字指為財利所喚後人因以為幕澤武公使各芳之臣久負深蚚令故辨之以俟博達君子者校正焉</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Luận-Ngữ</t>
+          <t>Thế mà cứ như quốc-sử Tiên-triệu đã chép: Vua sai Tùng-Dương Hầu Võ-Hữu mang Cờ Tiết về Cờ-Trai Tấn-phong Mạc-dăng-Dong làm An-Nam Quốc-Vương? thì Võ-Hữu ấy là người họ Võ ở tỉnh Sơn-Tây trung họ trung tên với Cụ, khiến cho ông Hò-sĩ-Dương khi soạn bộ Việt-Giám Tiệp-Lục cũng theo cái nhầm đó rồi thêm hai chữ Văn Thân, và bảo ông bị tài lợi cảm giỡ, để cho đời sau tưởng là Võ Công ở làng Mộ-Trạch. Thành ra một vị danh thần đạo đức phải chịu mỉa mai? Vậy nay chúng tôi mới khảo sát thấy, mong rằng các vị đại-nhân quân-tử sẽ định chánh cho.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HVB_003_0541</t>
+          <t>HVB_003_0041</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>汪深愬之。	—</t>
+          <t>圖景狀元記</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kiến Văn Tiêu Lục — Tây-Hồ Chí</t>
+          <t>TRẠNG-NGUYÊN CỜ, 3 VẤN ĐỀ TÊN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HVB_003_0542</t>
+          <t>HVB_003_0042</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>榮歸日驅繾綣而行。	—</t>
+          <t>武昭唐安慕澤人武悼之短也天庭中有一骨突生如棗子少有大志及長精于棊特有北國使來亦以善棊自負求共我國王開勝期以連輸三局必動兵端</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hồng-Vũ Cấm Thư ÁN-HÀNH TRONG KHUỒN-KHÒ</t>
+          <t>Ông Võ-Huyên người làng Mộ-Trạch là châu quan Nghè Võ-Đôn nguyên trên đỉnh đầu có một ngổ xương gỗ lên như cái quan cờ, lúc nhỏ đã có chí lớn, khi lớn rất tinh về môn đánh cờ. Lúc ấy có Sư tâu sang, tự phụ là tay cao cờ, muốn cùng Quốc-Vương ta đấu thử, và có hẹn rằng: Nếu Quốc-Vương thua luôn 3 ván thì bên Bắc quốc sẽ đem quân sang đánh ngay.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HVB_003_0543</t>
+          <t>HVB_003_0043</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>與鬩並驅爭先。</t>
+          <t>我國王志在勝他勢求罷者自助時臣以其各應郎召試之的是吾同手因用計瞞過他約至日中於丹墀對句各番把帕一人餘悉算去</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hội - viên IN LẦN THỨ NHẤT</t>
+          <t>Vì thế Quốc-Vương cũng muốn làm cho y phải khuất phục, nên mới sai người đi tìm tay cao về giúp, lúc ấy định thân đều tiên cử ông, Vua sai triều vào đấu thử, thấy quả là một tay cao. Ngài bên dùng kế che mất Sư giả, hẹn sẽ cùng đấu vào lúc giữa trưa ở trong sân rồng, mỗi bên chỉ đề một tên vác lọng đứng hầu, còn thì phải tránh đi hết.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HVB_003_0544</t>
+          <t>HVB_003_0044</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>不背公讓至獲</t>
+          <t>北使依克我國王以青帕徵穿上一小吼可通日影適抱之傍侍每勝局輒隱影引綦子國王以此累勝花使不覺嘆服其能</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CÔNG-DƯ TIỆP-KÝ TIẾT NGHĨA</t>
+          <t>Bắc-Sư nhận lời xong rồi bên ta mới đem chiếc lọng ra xuyên thủng một lỗ rất nhỏ có thể lọt được ánh nắng mặt trời, trao cho ông Huyên vác đề che cho vua, mỗi khi có nước hay, ông sẽ chiếu bóng nắng vào quân cờ đề chỉ nước đi, thành ra Quốc-Vương thắng luôn mấy bàn, Sư giả thán phục.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HVB_003_0545</t>
+          <t>HVB_003_0045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>澤杜蓮溪中橋人曰素聞杜范二公大各今見同日榮歸請詠橋詩一首頒</t>
+          <t>國王重其才號曰南國某紂元甚加寵幸暱自是得名人無敢與對其者</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thượng thư giao cố nhân, Lê Đại-Học-Sĩ chi tôn Nam-Quốc GỬI THƯ KHUYẾN CÓ NHÂN, LÊ ĐẠI-HỌC-SĨ</t>
+          <t>Rồi sau cuộc này ông được nhà vua trọng đại đặc biệt, ban cho danh hiệu Đấu-Kỳ Trạng-Nguyên và cũng được từ đấy nổi danh không còn ai giám đối thử.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HVB_003_0546</t>
+          <t>HVB_003_0046</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>汪相異曰橋屋十有餘間限過七間成詩詩用一句一禽先成者讓先行</t>
+          <t>諺云黃梅酒藥澤其蓋謂此也</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bồn só Thất-Trầm chữ nghĩa động tôi quỉ thần; rồi sau Văn-Hiên Vinh-Sử cũng có</t>
+          <t>Vì thế ngạn ngữ có câu: Rượu Hoàng-Mai cờ Mộ-Trạch là chỉ vào ông vậy.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HVB_003_0547</t>
+          <t>HVB_003_0047</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>不得筆道直顯如約立就詩國語八句馬上讀之人皆藥服泣曰這</t>
+          <t>交跌狀元記</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dịch Gươm dân Tương bằng một thư sinh. Câu nước trong thơ đã hiền minh ?</t>
+          <t>GIAO TRẬT TRẠNG NGUYÊN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HVB_003_0548</t>
+          <t>HVB_003_0048</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>詩已平日素成非臨時所張得吾何讓焉又齊道而行至明倫社有伊</t>
+          <t>武豊慕澤人武有之弟也相五短少善交跌賴即生宗時並長安見皇上御朝有都力士捧銅柱蕭立氣覿楊楊公問諸交曰此其人有其英才融而昂然若是</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tự lệ huyền hò tráng chỉ hàm ? Kiên kiên phi cung thành hiệp nhất.</t>
+          <t>Ông Võ-Phong người làng Mộ-Trạch là em quan Thượng Võ-Hữu, nguyên người có tướng ngũ-doàn (chân tay, tai, mắt, miệng, mũi, 5 thứ đều ngắn và nhỏ, còn người thì thấp) nhưng rất giỏi về môn đấu vật. Đời vua Lê Thánh-Tông (1460-70) nhân có một hôm ông ra kinh thành Tràng-An gặp lúc vua đương ngự triều, ông thấy có viên Đô-lực sĩ vac chiếc chày đồng dùng hầu có về đương đương tử đắc! Ông bèn quay lại hỏi bạn: này bác người kia là ai? có tài cán chi? mà giảm ngang nhiên như vậy.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HVB_003_0549</t>
+          <t>HVB_003_0049</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>社人屋字是新富途請曰鄙人再構新家幸逢兩貴台經過乞惠之</t>
+          <t>其友曰他繫是彊健的人其交踐一藝有甚於此乎？</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thế rồi cách ít lâu sau nhà Minh sai Thượng-Thư Hoàng-Phúc sang làm Đô-hộ An-Nam, Phúc liên mở</t>
+          <t>Bàn đáp: Người đó là một võ sĩ sở trường về môn đánh vật, hiện thời không ai địch nổi!</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HVB_003_0550</t>
+          <t>HVB_003_0050</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>佳句燕歌屋生輝鎮應曰年年增富貴日日壽榮花古人有此句今</t>
+          <t>夫子曰：「富貴榮辱，可以為進身之地。」</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>cảnh, buột miệng đọc một câu rằng: . Tác triều phong vũ gia gia đồi hoại cựu viên</t>
+          <t>như vậy cũng là một cách để tiến thân đó!</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HVB_003_0551</t>
+          <t>HVB_003_0051</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>日賀新家洹吟沱曰賛羙之辭此等句盡之矣豈復以加而頒矣</t>
+          <t>公曰：「吾請較藝，如何？」</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>vì thế Thúc-Hiên cũng ứng khẩu đối rằng: . Kim nhật càn khôn</t>
+          <t>Nghe bạn kề xong ông lại hỏi rằng: nếu vậy ngày nay tôi muốn cùng y so tài cao thấp phỏng có được không?</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HVB_003_0552</t>
+          <t>HVB_003_0052</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>口輒成自非神吟鬼助轟然若是自是始讓顱先行後潛至監來</t>
+          <t>交曰：「他是身材長大而公以短小較之只恐為闕場見笑</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>cháu rằng: Sau này nếu có sang Sư mà lâu không trở về, thì cứ dục khoét vào chân con ngựa ấy, tự nhiên Sư giả</t>
+          <t>Bàn nghe xong vội vàng can rằng: người ta cao lớn thế kia mà bác thì bé loắt choắt như vậy! sợ khi đối thủ lại làm trò cười cho thiên hạ đó thôi!</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HVB_003_0553</t>
+          <t>HVB_003_0053</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>杜著鎮祖墓見有二土堆俗曰兩袖童附耳泣致指之曰從來勝我數番</t>
+          <t>公曰吾技藝耳熟精無厭尚右他未逢對手故得各耳使令當番吾勝之</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>có một hôm vào yết miếu vua Đinh, ông thấy pho tượng Dương-Hậu cùng đặt ngòi chung với hai ông chồng, (tức</t>
+          <t>Ông mỉm cười đáp: điều đó xin Bác đừng ngại? tôi đây bản lĩnh rất là cao cường! từ trước đến giờ chưa ai thắng nổi. Còn y chẳng qua chưa gặp địch thủ nên mới nói danh, nhưng nay gặp tôi rồi Bác thử coi tôi sẽ thắng y một cách rất dễ đó!</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HVB_003_0554</t>
+          <t>HVB_003_0054</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>以有那神童附耳之功即用腳跟擊手土堆自是顫從耳病廢商治弗效有</t>
+          <t>即具本奏聞請與力士較勝負</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>lệnh giam cầm sứ thần, rồi viên Tông-Đốc sai lấy vở trai bịt kín hai mắt của ông, bên ngoài dùng son phủ lại, và</t>
+          <t>Nói xong ông bèn viết một bản tấu xin cùng lực sĩ so tài.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HVB_003_0555</t>
+          <t>HVB_003_0055</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>人以汪轡車土堆之事語鎮者鎮即訢于朝署朝論汪謝鎮祖墓鎮</t>
+          <t>皇上覧奏判曰吾之力士千萬中有一人耳世衆以加何人斯敵爾大膽郎六九其請試看力士如何約詞日親御視之</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kỷ-Vị thì đỗ Tấn-Sĩ, được bờ Tri-huyện Quảng-Đông, dàn dàn thăng chức Yến-Kinh Chủ-sự, nhân mới nghĩ đến thấy</t>
+          <t>Hoàng Thượng xem tấu phán rằng: lực sĩ của ta tuyên lừa trong muốn ngàn người mới dặng có một! hỏi còn ai hơn được nữa? thế mà anh kia tài nghệ ra sao lại giám to gan lớn mật như vậy? nhưng rồi Ngài cũng phê chuẩn và định ngày giờ tí thì để Ngài thân ngự ra coi.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HVB_003_0556</t>
+          <t>HVB_003_0056</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>病尋愈其後試東閣以文武並用詩題用五言三江為韻取十五韻鐵</t>
+          <t>爾邊相對公潛納沙手中揮手突八華放沙于力士面上</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(Phụ-chú : Tô-Vũ tự tên là Tứ-Khanh, làm quan Trung-Lang tướng đời Hán-Vô-Đế, phung mệnh sang sứ</t>
+          <t>Thế rồi đến hôm tì thì, trong lúc đối bên còn dương vôn nhau biểu diễn, thì ông quờ ngay xuống đất lấy một ít cát nắm kín trong lòng bàn tay, thưa lúc vô tình ném thẳng vào mặt địch thủ.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HVB_003_0557</t>
+          <t>HVB_003_0057</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>復中第一泊第二始興徵時與江對飲酒至半酣相戲為酒賛酒先</t>
+          <t>力士喊不啟開措手弗及合用。旁射格擲倒于地觀者齊聲相喝</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CHÍ KHÍ Đại Hưng-Hàu bằng huynh tử chi ĐẠI HUNG-HÀU VÌ CÓ THỂ LỰC CỦA ANH</t>
+          <t>Lực sĩ vừa nhắm mắt lại thì nhanh như chớt, ông đã dùng miệng Xuyên Trừu, một tay thọc nách một chân đệm phía sau lưng, đẩy mạnh một cái khiên cho Lực sĩ mất đã bị nằm phơi bụng ngay trên mặt đất. (Theo lệ đưa vật, hễ ai bị nằm ngửa bụng mới gọi là thua, còn nằm sấp bụng thì không kề). Thế là ông đã thắng cuộc một cách dễ dàng! khán giả hoan họ nhiệt liệt.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HVB_003_0558</t>
+          <t>HVB_003_0058</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>唱曰有潰用潰無潰用火所用咸宜無施不可頤續吟曰酒潰則歡火潰</t>
+          <t>皇上加其勇郎以所封九士者授之官至錦衣衛廷尉屬指揮使以平允称</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ông bèn soạn ra truyện Nhạc-Xương phân kinh dùng toàn quốc âm, ngụ ý chê bài họ Mạc xa</t>
+          <t>Lúc ấy Hoàng-Thượng ở trên đại trong xuống thấy ông quật đỏ Lực sĩ mau lẹ như vậy, Ngài cũng tấm tắc khen là một tay Thần dũng, rồi sai lột chức Đô Lực-sĩ để phong cho ông; dần dần ông được thăng đến Cẩm-Y-Thị-Vệ Úy-ty-Chí-huy-Sứ, nỗi tiếng là người chính trực siêng năng.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HVB_003_0559</t>
+          <t>HVB_003_0059</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>則絕有遠此言天地日月識者以是言其立志之珠其後莫七我朝中興</t>
+          <t>人言葉澤四狀元蓋指穆傳字狀元又為顧狀元武暄為葉狀元公為交跌狀元是為四狀元</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>qua cửa Nam nhìn lên thấy có chữ đề bên trên, và là danh hiệu của một thần từ nước Nam, nên bắt dừng xe không</t>
+          <t>Còn như lúc ấy thiên hạ đồn rằng: 4 Trạng của huyện Đường-An, 1 làng Mộ-Trạch chiếm cả! là chi vào ông Lê-Đinh làm Trạng-nguyên Chữ và kiêm cả Trạng-nguyên Com (ăn khỏe)! Võ-Huyên làm Trạng Cờ! còn ông thì làm Trạng đô Vật! tức là 4 Trạng!</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HVB_003_0560</t>
+          <t>HVB_003_0060</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>汪首出仕至戶部尚書封福神鎮辭歸不仕仕終承政使司</t>
+          <t>公兄弟五人竝有爵祿而公與兄有兩枝貴顯繼世登科為族中之冠</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Giữa lúc ấy có quan Thượng-Thư là Võ-Duy-Đoán hiện sung chức Bàn-Tiếp để dón sứ-giả, thấy sứ</t>
+          <t>Ông có 5 anh em thì ai cũng có phẩm tước, riêng Chi của ông và Chi anh cả thì phát đạt hơn, vì được khoa bằng nỗi đời, đứng vào hàng đầu của họ Vũ ở làng Mộ-Trạch!</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HVB_003_0561</t>
+          <t>HVB_003_0061</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>探花廓佳記</t>
+          <t>光黃有詩云</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>bui trần ?</t>
+          <t>bởi thế nên ông Quang-Bôn mới tặng thơ rằng:</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HVB_003_0562</t>
+          <t>HVB_003_0062</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>未生時有接近人以慣偷盜為業一日就公邑內</t>
+          <t>也短曾稱相顓奇、桑蓬孤矢行男兒</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>xóm làng giềng ai cũng biết cả. Sao chị lại dám cướp sống</t>
+          <t>Tương xem ngũ đoàn thực phi thường, Hồ thì làm giai chí bốn phương.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HVB_003_0563</t>
+          <t>HVB_003_0063</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>行盜會人未定時潛八廟祠後假卧不覺薰睡至鷄鳴方醒披衣徵</t>
+          <t>一門伯神光前養子載明良結主知</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bật-Sô Tăng kiếp hậu vi vọng quốc Hoàng-Đế</t>
+          <t>Nếp cũ thêm tươi hàng bá trọng, Ngàn xưa dẳng gặp chúa mình lương.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HVB_003_0564</t>
+          <t>HVB_003_0064</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>起忽聞前回喧鬧有人自廟外而入在廟內有人迎問曰今番何事遲歸</t>
+          <t>應變有才施達政稱乎各營檔于時</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bồng một hôm, Sư đang ngủ trưa ở chốn trai phòng, trong lúc mơ mộng thấy Đức Di-Đà hiện trước tòa sen, gọi</t>
+          <t>Khen tay chính trị tài thông biến. Giữ mực công minh tiếng chẳng nhường.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HVB_003_0565</t>
+          <t>HVB_003_0065</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>聞有聲曰答適朝士帝與諸曹會談夜命一探花即降伊社有員捧</t>
+          <t>無殊榮盛多非偶種德卑閥是我師</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Về phần nhà Sư sau khi tỉnh dậy, nhớ đến những lời trong mộng, bèn triều các Đạo - Tràng đến bảo rằng :</t>
+          <t>Con cháu vinh hoa âu cũng bồi, Ai giống cây đức để làm gương.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HVB_003_0566</t>
+          <t>HVB_003_0066</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>薄奏曰長按伊家福德薄恐不稱此帝命取薄觀之良久判曰雖然知此</t>
+          <t>宰相武惟志記</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ta từ lúc xuất gia nương nhờ của Phật, tưởng rằng tẩy hết trần duyên, tu tròn quả phúc để lên Tòa Sen, đó là hậu</t>
+          <t>MỘ-TRẠCH TÈ-TƯỚNG KÝ</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HVB_003_0567</t>
+          <t>HVB_003_0067</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>但業已許之不必換改如他德果薄來時更有定奪焉以此故遂歸耳時人</t>
+          <t>宰相武惟一，燕澤人也，曾祖刑部員外郎晚年二接鄰時舉社吳村教授性畏水蛭一日初有洛沂風雩庶意出村頭池塘清水麗濯綢童子五六尾之纔經伊村園處見一堆圓彙微高顧童生戲指之曰師百歲後當於此封墳則水煙不融近也</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>công phu khở hành, lại phải dời lấy các chức vị gian nan</t>
+          <t>Tè-tướng Vô-duy-Chí người làng Mộ-Trạch, Cự tam đại trước đã làm đến chức Hình-bộ Viên-ngoại-lang, đến khi già tuổi về hưu, Cự sang dạy học ở làng Thời-Cử Thôn-ngư bên cạnh làng Cự. Nguyên Cự có tính sọ địa, nhân có một hôm Cự nhớ đến cái thanh thú của đức Khổng-phu-Tử ngày trước cùng các món dẹ đi tắm sông Nghi rồi lên hông mát ở nền Vũ-Vu, Cự bên dã 5, 6 đồng sinh ra ngay cái hồ nước trong ở chỗ đầu làng, định để giặt áo, chẳng ngờ khi ra khỏi một đầm rừng cây thì thấy có một gò đất hình tròn và cũng khá cao. Cự bên trở vào mò đất nói bốn với học trò rằng: Nếu thấy trăm tuổi các anh nhớ đem tàng trên gò đất cao kia thì địa không sao lên được.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HVB_003_0568</t>
+          <t>HVB_003_0068</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>在廟後竊聞具得其詳當夜不以行為意因徧往邑中探聽何宋生子見公</t>
+          <t>及卒家人追念其言郎將伊廣塗之</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sớm cậu vào khất thực nhà ông Đô-nho, ông thấy cậu học trò nhỏ, bèn đọc một câu ngạn ngữ để điều cậu rằng:</t>
+          <t>Thế rồi cách mấy năm sau Cự mất, người nhà nhớ lại câu nói ngày trước, đem đi hai ra an táng tại đó.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HVB_003_0569</t>
+          <t>HVB_003_0069</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>生於是夜災早即公家具導前事一通預以為賀生而頴異人稱袖童及長</t>
+          <t>今按此地前接有茆浮水面桃後有升鳯郵書坐乙向辛風水師以為天蓋吉司子孫必發公候之貴</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Âm vị khai nhi dương đã lộ , nguyên câu chữ nôm là Cánh cửa Hồng-môn còn khép nếp, Ngọn</t>
+          <t>Ngày nay xét ra thì cái gò ấy có một con đất vuông vẫn mọc tại giữa hồ tức là khẩu ấn để làm tiền án, còn ở phía sau tức là hậu chẩm, thì có một con đất giống hình Đan phương hàm thư Chim phương ngậm thư, ngoài mộ ngồi vào chử Ất trong ra chử Tân, về sau các thầy Địa-lý bảo rằng: đó là cục đất trời cho, sau này sẽ phát Công hầu khanh tướng!</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HVB_003_0570</t>
+          <t>HVB_003_0070</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>以文舉子各正和年號、癸亥文科中進士第一甲三名公在朝適內閣談政事餘昭</t>
+          <t>惟志之母素有陰德少時往市間販買適有鬻綿緯者於眾人喧鬧中遺棄綿一束而去</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>(1600-1619), cậu đồ Tiến-Sĩ vào khoa Giáp-Thin, cách mấy năm sau phượng mang sang sứ Bắc quốc, vua nhà Minh triều</t>
+          <t>Nhắc lại nhà ông Duy-Chí, bà cụ thân sinh người rất hiền lành phúc hậu! khi còn ít tuổi Cụ cũng tần tảo bán buôn ở các chợ búa, một hôm dương lúc chợ đông, thấy có một chị bán hàng to lụa trong khi vội vã xếp gánh đi rồi mà còn bỏ sót lại đó một cuộn.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HVB_003_0571</t>
+          <t>HVB_003_0071</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>祖康王問侍臣曰韓信遺燕書曰有曰白鹿抱泉事跡何在卿等能知之乎</t>
+          <t>志哥已按取藏之頃之見一婦前來吐號尋覓母盡因問端的盡以付還</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ông tình về môn xem tướng, nhân lúc nhân hạ mới hỏi ông rằng : Khanh thử coi tướng các con của trẫm, xem ai</t>
+          <t>Cụ bên nhặt lấy xếp vào gánh hàng của mình, rồi một lát sau thấy chị bán to quay lại tìm kiếm không được gào khóc rất thâm thương! Cụ gọi lại hỏi chị kia mặt mát thứ gì? Thấy chị hàng to khai đúng, Cụ bên tra trả cuộn hàng cho chị,</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HVB_003_0572</t>
+          <t>HVB_003_0072</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>群臣皆莫能對公跪對曰跡詳見漢書王郎命索公家書來觀之稱其簿</t>
+          <t>賣絹婦德之以二匹致謝志哥笑曰取此二匹寧為取一束之多耶我憐汝失物囘歸必被夫兒痛責故見還耳豈望謝耶一市環視者皆稱其賢</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chẳng ngờ câu truyện xem tướng lại lọt đến tai Quân- Công, Quân-Công biết thế, giả vờ triệu ông vào dinh để hỏi</t>
+          <t>chị rất cảm ơn, rút ra 2 tấm để tạ, nhưng Cụ mỉm cười bảo rằng: nếu tôi có lòng tham của, nhận 2 tấm này chẳng tha tôi lấy cả cuộn (súc) có nhiều hơn không. Chỉ vì tôi thấy cũng chở chị em bạn hàng nay bị mất của, tất nhiên lúc trở về nhà sẽ bị chồng đánh đập tội thân, nên tôi mới tra trả lại, chứ có mong gì, tạ ơn, rồi Cụ nhất định không nhận, khiến cho các người trong chợ ai cũng ngợi khen là người phúc hậu!</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HVB_003_0573</t>
+          <t>HVB_003_0073</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>學時公方以事被遣未幾除清花聲同仕至寺癖以風疾不視朝始信從</t>
+          <t>世常愛堂前有五色雲現親自抱之俄而春紅雲光散</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mục ngưu tăng, mặc hội linh thông SU CHĂN TRÂU, HIỀU PHÉP THÂN THÔNG</t>
+          <t>Hôm ấy Cụ trở về nhà, đêm nằm mơ thấy có 5 sắc mây hiện ra trước mắt. Cụ bên ôm cả vào lòng, nhưng chỉ giây phút thì thấy mây xanh mây hồng tan ngay tức khắc.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HVB_003_0574</t>
+          <t>HVB_003_0074</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>日祠神對語之聽</t>
+          <t>後生五男其一自快少有大志年二十七適長安睹扶花公子為王所重愛人情廣明之而弘祖陽王深自韜晦每朝侍日公執就府竊視之見挾花華止言繚知其成之器一見而異之曰此聖才也即行下其後以潛邸功臣官至左侍郎忠都公</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bồ-tát chân-nhân,</t>
+          <t>Về sau Bà sinh đặng 5 con giai, ứng nghiệm với điểm 5 sắc mây trước; 5 con giai là: Người thứ nhất gọi Tự-Khoái, lúc còn thiếu niên đã có chí lớn; đến năm 17 tuổi ra thăm kinh thành Tràng-An, giữa lúc Công-lử Phù và Công-lử Hoa được Hoàng-Thượng yêu dấu đặc biệt, ai cũng trong vào. Nhưng mà Hoàng Tồ Dương-Vương thì rất kín đáo. Cứ mỗi phiên châu Cậu Khải thường vào công phủ ngô trộm, xét thấy cứ chỉ đáng điệu của hai công-tử thì Cậu đoàn biết không phải là người làm nên to tát, nhưng khi thoát nhìn thấy mặt Hoàng-Tồ thì Cậu đã lấy làm kỵ, biết rằng con người có tài thành trí, bèn xin vào làm môn hạ, rồi sau được dự vào hạng Tiêm-đề Công-Thần tức là công thần từ trong Tư thất.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HVB_003_0575</t>
+          <t>HVB_003_0075</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>參議武登顯記</t>
+          <t>其二校萃田戍科進士官至寺鄉</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vương sức tình</t>
+          <t>Người thứ hai tên gọi Bạt-Tuy, thì đồ Hoàng-giáp khoa Giáp thin (1484) làm quan đến chức Tự-khanh.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HVB_003_0576</t>
+          <t>HVB_003_0076</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>多者至八九名少者不下四五十名連名覆中率以為常而午年科保提調</t>
+          <t>其三両子皆功臣進用惟志至宰相方夫至尚書曰距封都爵其</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Về sau đến năm Giáp-Tuất, Ta vâng lệnh đi bồi đắp</t>
+          <t>Người thứ ba, tư cũng đều là bậc công thần tiến dụng; Duy-Chí làm đến Tề-tướng, Phương-Đại làm đến Thượng-thư, đều phong tước Quân.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HVB_003_0577</t>
+          <t>HVB_003_0077</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>官其左夫阮澧性頗廉直以慕澤從來多中必有私巧者在乞為海陽提</t>
+          <t>其五求諭又已亥科中進士仕至參政</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hạ-bi dị nhân toàn thuyền khước bắc binh LÀNG HẠ-BI CÓ DỊ-NHÂN, ĐỤC THỦNG THUYỀN BẦY LUI BẮC BỊCH</t>
+          <t>Người thứ năm tên gọi Cậu-Hối đồ Tấn-sĩ khoa Kỷ-hội, về sau làm đến Tham-chánh.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HVB_003_0578</t>
+          <t>HVB_003_0078</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>調以察之朝延協議考至第四場公命攝地為安合士人坐在穴中籠</t>
+          <t>自快常通六囊惟志方大皆自功成各遍相繙引年其六校萃求謝出由青紫比途而宦秩書科不異一門倡伸始信青紅先敬之聽</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>chẳng dám ở lâu, vội vàng nhổ neo đi thẳng. Còn phần Dị-nhân sau khi làm tròn nhiệm vụ cứu</t>
+          <t>Xét ra Tự-Khoái được vua tri ngộ ngay lúc thiếu thời, thế mà lương thọ cũng ngoài sáu chục (60), còn như Duy-Chí, Phương-Đại cũng đều công thành danh toại, vinh quang đến lúc tuổi già, riêng có Bạt-Tuy Cậu-Hối xuất thân trong hạng khoa cử áo tia đại xanh thì lại phẩm trước thọ khảo đều kém anh em, do đó người ta nhận thấy cái điểm mây xanh, mây vàng tan trước quả thiệt ứng nghiệm.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HVB_003_0579</t>
+          <t>HVB_003_0079</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>蓋其上防守其甚嚴迨同考院考訖送來公無嚴飾覆考官詳看文勢	..</t>
+          <t>惟志達於吏事輔以文學侍陽玉潛印頗見親幸</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>cũng Tấn phong cho trước Đại- Vương, và cho con cháu quản lãnh những chỗ cửa sông,</t>
+          <t>Nhắc lại Duy-Chí là người thông suốt việc quan và có biệt tài về văn-chương, nên khi vào giúp Dương-Vương ở trong tư phủ, được Vương tín nhiệm hơn người.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HVB_003_0580</t>
+          <t>HVB_003_0080</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>精純全篇無瑕者方得挑取而覆考擇得十卷公親自評之汰去四卷只</t>
+          <t>時廣南有阮賊高平有莫澤子公從鸞勒間多有熱勞</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kim-Tông Thân miếu hội đê tỏa Điền-Quân THÂN MIẾU XÃ KIM-TÔNG PHÁ ĐÊ, LÀM MÁT NHƯỆ KHÍ</t>
+          <t>Gặp lúc trong vùng Quảng-Nam có quân Chúa Nguyễn nỗi giây, trên vùng Cao-Băng thì có con cháu họ Mạc quấy rối, ông vẫn theo bên cạnh Vương, lập được rất nhiều công trạng.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HVB_003_0581</t>
+          <t>HVB_003_0081</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>取六卷既而呼各優頂一名皆來澤社武登顯首科纔十八歲第二名某</t>
+          <t>有駕大海調糧有險高山齊舟有隔千里陳事累差稱旨以致寵遇日隆至拜參政宰相</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ĐIỀN-QUÂN Huyện Thiên-Bản , xã Bảo-Ngũ , có Điền- Quận-Công , vì là em ruột bà Bảo-mẫu Mạc-Thuận-</t>
+          <t>Có khi vượt bê vận lương, có lúc lên rừng dốc chiến, lại còn những lúc ở xa ngàn dặm gửi kế sách về cũng đều hợp ý, nên ông lại được chúa ưu đãi hơn xưa. Chỉ sau mấy năm đã lên đến chức Tham-tung Tề-trương, khiến cho đình thần ghen tị, mà ông là Nha lại xuất thân.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HVB_003_0582</t>
+          <t>HVB_003_0082</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>澤社人第四建亦慕澤社人其三名乃永賴古庵唐安王司青林樂實人</t>
+          <t>朝臣有吏道為言王聞之即歷敘蕭曹為趙事業依鮮疑論以示群臣焉</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>trong thuyền, tuốt kiếm hò thần Thiên-Cương, thư phù niệm chú, rồi mới hạ lệnh cho các tướng-sĩ cầm</t>
+          <t>Chúa nghe thấy câu đó Ngài liền soạn lại những thiên tiêu sử nói về sự nghiệp Tiêu-Hà Tào-Tham ngày trước, để trao cho các đình-thần, cốt ý là muốn giải thích hộ ông về câu mỉa dọ. Phụ chú: Tiêu-Hà Tào-Tham nguyên trước cũng làm nha lại ấp Bái, về sau giúp Hán Cao-Tổ làm nên sự nghiệp để vương.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HVB_003_0583</t>
+          <t>HVB_003_0083</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>也一科續取六各而纂澤居其半同院取卷觀之見三卷文理各殊不相蹈</t>
+          <t>公章厚質直時春天正旦日正有旨文武殿朝禮訖各仍朝服詣政府</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sản giáo mác xông lên, hai bên đều dùng hỏa pháo bắn ra, khói đen mù một phủ khắp một vùng, đứng cách chỉ</t>
+          <t>Nguyên ông là người có tính trung hậu thắng thân, một năm nhân gặp ngày tết nguyên đán, chúa xuống chỉ du cho hà quan làm lễ triều điện xong rồi thì cứ đề nguyên áo mũ như thế vào mùng Chính-phủ.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HVB_003_0584</t>
+          <t>HVB_003_0084</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>襲深嘉嘆賞貞始細信慕澤為世尚儒流文物之地文衡公器初非本私其</t>
+          <t>道身共天道日月有光正氣崇禮言一介言青吉衣為正不宜還用朝服恐違舊制</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kinh thưa Thủy-Thần linh-vị : Mới rồi đi qua trước miếu, tôi đây một phen lầm lỡ trót đã xúc phạm oai linh,</t>
+          <t>Ông bên tâu rằng: từ trước đến nay Vương thượng vẫn giữ tắc đa tôn phu, vậy thì buổi lễ hôm nay chỉ nên vân đồ thường phục mới phải, nếu vân triều y sự nữa không hợp với chế độ cũ.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HVB_003_0585</t>
+          <t>HVB_003_0085</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>後武盞顒宏詞科中優一會試賦優士分但中三場嘗以未遊青雲為限</t>
+          <t>王從其言華為中止蓋亦有爭臣之風焉</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Khẩn Thần xong rồi ông lại ra lệnh cho quân-sĩ bắt tay vào việc, hễ dấp đến đầu thì đất chắc nich đến đó,</t>
+          <t>Chúa khen là phải thành ra việc ấy lại thôi, coi đó ta thấy ông là một người có đủ phong độ tranh thân đời cờ vậy!. Tránh thân là người bè tôi biết can gián vua,</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HVB_003_0586</t>
+          <t>HVB_003_0086</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>官至北京處參議以親老辭官歸養設場教授及其門生擢大科儒者者</t>
+          <t>後以央部尚書國者老火保致仕於彩旗對句有云一代尊臣蕭相國兩朝元老趙韓王</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>một quãng lớn, làm ông hoàng sợ, vội vàng sắm sửa lễ vật để ta thân linh rồi sai dắp lại, nhưng mà dắp mãi cũng</t>
+          <t>rồi sau ông được về hưu với chức Lại-bộ Thượng-thư Quốc-lão Thiếu-phó, trong lá cờ hiệu có theo một câu đối rằng: Nhất đại tôn thần Tiêu Tương quốc, Lưỡng triều nguyên-lão Triệu Hàn vương, để vì ông cũng như Tiêu Tương quốc với Triệu Hàn vương ngày xưa,</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HVB_003_0587</t>
+          <t>HVB_003_0087</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>稱為尊師至今猶歆為裳</t>
+          <t>詩七十五贈太傅公</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>với Thủy-Thần. Vậy xin nhẫn lời cho chị tức là Bảo-Mẫu</t>
+          <t>sau ông hưởng thọ được 75 tuổi, lúc mất lại được tặng chức Thái-phó.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HVB_003_0588</t>
+          <t>HVB_003_0088</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>節義 樑鼎景詢記附光貞</t>
+          <t>吳遼州太宰范公同時俗云慕澤寧相燕州國老蓋精權位之相軌也</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Quang côn hán trí man linh tử KẾ TRỘM KHÔN NGOAN BÁNH LỬA THÂN THÁNH</t>
+          <t>Ông cùng quan Thái-tề ở Liêu-Xuyên là Phạm-công-Trư cùng làm quan trong một triều đại, cho nên đời ấy có câu nói rằng: Tề-tướng Mộ-Trạch, Quốc-lão Liêu-Xuyên, là nói quyền vị tương đương với nhau vậy.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HVB_003_0589</t>
+          <t>HVB_003_0089</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>陳朝樁景詞其祖汝猷淳祿老疎人也為諒江知府娶唐安慕澤</t>
+          <t>其子惟諧已亥科中進士父子同朝</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>(Quỉ thân bất trắc là quỉ thân khôn lường đoán ra được). Cường-bạo vương, kẻ kháng Thiên Tướng</t>
+          <t>Còn như gia thế của ông về sau thì có con là DUY-HẢI đỗ Tấn-sĩ khoa Kỷ-hội, cha con làm quan đông triều.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HVB_003_0590</t>
+          <t>HVB_003_0090</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>武氏之女因以妻鄕居焉詢覓太學生少與青沔縣扶助社內裴伯耆</t>
+          <t>時有北國人將都鴛舟百餘艘來我國安廣之洪澤朝命宗子王都公頒水師往伐以公為勘戰官</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cường-bạo đại-vương người làng Bối-Cẩm thuộc huyện Thiên-Bản , khi trước bà mẹ nằm mộng thấy</t>
+          <t>Lúc ấy có bọn giặc Tàu tên là Đặng-Diệu kéo hơn 100 chiến thuyền vượt bể sang đánh Đầm-Hồng, Triệu đình bèn sai Vương-Tử là Ninh Quân-Công Thống lãnh Thủy sư đi đánh, còn ông thì được giữ chức Khâm chiến.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HVB_003_0591</t>
+          <t>HVB_003_0091</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>相善陳末胡墓位伯者如燕京乞師伐胡明遣張翰沐晟等分道</t>
+          <t>進討日公用出文手計編覲諸市庯花嬪有餘輩放下賊艘托為弄月醉花之歡歡陰教各犯來紅巾一幅浸之以水乘夜索艘問鏡口滴水濕之仍各依期從小舟囘去</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>đánh. Ông Táo biết truyền xuống trước bảo khẽ với Vương : Vương xin Táo-quân, bày kế giúp đỡ.</t>
+          <t>Trước khi giao phong ông bèn dùng kế mỹ nhân, sai người đi khắp các nơi mộ được 300 ả đào, cho xuống thuyền giặc ca nhạc giúp vui, nhưng trước khi xuống, ông đã chỉ bảo kẻ hoặc, trao cho mỗi chi một tấm khăn hồng, đợi đến lúc nào bọn chúng say rượu ngủ kỹ, bấy giờ mới đem thấm nước rồi nhét vô trong miệng súng thần công, làm xong nhiệm vụ thì phải trở về báo tin v.v..</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HVB_003_0592</t>
+          <t>HVB_003_0092</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>而來伯耆為先鋒向道拾逆胡父子送同明人拜伯耆為參護諭</t>
+          <t>次日交戰我即陳船排開一字交射威戰艘賊賊惶怯敗鏡應發不覺已隨計兵射不啟發將郡因縱火燼揚帆遁去官軍大捷</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>v... Vương được Táo-quân dạy cho điều kế như vậy, lập tức đi kiếm Mông-toi đem về giả lấy nước giột, và sắm các</t>
+          <t>Quả nhiên sáng sớm hôm sau các cô thiếu nữ trở về báo rằng Kế sách đã thi hành xong. Bấy giờ ông mới hạ lệnh đem hết chiến thuyền bày thành mặt trận chư nhất, cấp tốc tiến lên, các khẩu đại bác đồng thời nhả đạn. Quân giặc thấy vậy cũng với đem súng ra bắn giả nhồi, nhưng súng đều bị tắc họng, chẳng bắn được một phát nào. Bọn giặc biết mình bị trúng kế với vàng đốt thuốc hỏa mù, rồi kéo buồm lên chạy trốn, quan quân thừa thắng rượt theo,</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HVB_003_0593</t>
+          <t>HVB_003_0093</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>郎上萬言書于伯耆其畧曰若能立陳為上策僕願為佐龍中藥物</t>
+          <t>活捉得他一充子年十六姿色絕倫軍囗載還以獻</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thiên-lợi loạng choạng chạy về Thiên- đình, Vương đoạt được sợi dây đồng đỏ dài hơn một</t>
+          <t>bắt được một số tù binh trong có một thiếu nữ, tuổi mới cấp kệ thực là một trang quốc sắc, thế mà cũng đem về để hiển lên Vương chư không say dẫm (cấp kệ là đến tuổi 17-18).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HVB_003_0594</t>
+          <t>HVB_003_0094</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>任足下所用為陳辭官為中策僕願執籩籩豆奔走任足下所使</t>
+          <t>其後擇陪臣從北使奉領東牒公文公與族弟令道父會庵榜眼陶公正三名中格</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>chí tôn trong hạng Tam-tái, nay cho nhà người xuống dưới hạ giới để làm vang đội oai danh, hỏi rằng đánh đầu mà</t>
+          <t>Sau một thời gian triều đình có cuộc bang giao, muốn chọn một vị bồi thần sang sứ Bắc quốc, Vương sai đình thần thảo thử một bức công điệp, kết quả cuộc thi, ông với em họ là Công-Trực và quan Bảng-nhơn Hội-Am là Đào-công-Chánh, chỉ có 3 người được dự trúng cách,</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HVB_003_0595</t>
+          <t>HVB_003_0095</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>若貪其禄位斯為下矣則僕樂鈞耕間而已伯耆不聽父伯耆犯</t>
+          <t>再者東書字一各其門下書寫武常存以楷法道義獨在優等</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>tên bạo tặc đó, để làm mời cho lũ cá giải, nghe ! Lần này Táo-quân nghe được lệnh trên, thì lại với</t>
+          <t>lần sau lại tuyển một người chữ tốt để viết điệp văn, thì học trò ông là Võ-thường-Tôn viết lời chữ khải tốt nhất được xếp hạng ưu.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HVB_003_0596</t>
+          <t>HVB_003_0096</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>明法明人籍其家得其書目詢變姓各遊匿後明人於我國立學校諭</t>
+          <t>時有朝士數指平民論事中裴公輔曰今日中東文有三而幕澤居其二選東字有一而幕澤之優綴饒考中攬金他有兼之平民不睦措乎矣乎民俗頒廓還財物箕室公輔漸憤</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>đến thờ phượng, hương khói lưu đến đời sau, và được vinh quang trong sổ bách thần của nhà nước.</t>
+          <t>Khiến cho Triều thần lúc ấy ghen tị, thường nói dồn quan Binh-dân-Cấp-Sự Bui-công-Phụ rằng: ngày nay có 3 người văn hay thì Mộ-Trạch chiếm mất 2 suất, tuyển có 1 người chữ tốt thì Mộ-Trạch lại đứng hạng ưu. Vì thử có mở kỳ thì cướp giật, để thường Mộ-Trạch cũng chiếm cả chẳng, chứ như Binh-dân thì còn trở tay sao kip. Về phần Công-Phụ thấy bạn đồng liệu chế điều như vậy lấy làm hổ giặn,</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HVB_003_0597</t>
+          <t>HVB_003_0097</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>往觀之明人見其才學以為教授饒而知萬言書日乃誨師依郡補師</t>
+          <t>他日會朝密來社邑彼徒將朝士帽籠衣所盡陰攫之</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>viễn chi, của đức Không-Tử đã dạy, ta cũng phải nên ngầm ngợi xem đối với quỷ thần có nên kinh trọng và coi như</t>
+          <t>ông bèn bí mật cho người mọ lấy mấy tay ăn cấp thật giỏi, đem về cho sung vào toàn linh hầu, đội phiên triều hội ông cho theo vô để chúng ăn cấp hết cả các hôm áo mũ của bá quan đem dẩu vào một xó kín,</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HVB_003_0598</t>
+          <t>HVB_003_0098</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>去其三子太顚少顚叔顚皆願從行送至開門詭語之曰一當從</t>
+          <t>朝士不覺驚焉評顧謂合稱曰今日相竊非乎民而誰那睞者所言相戲耳宜急見還</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mở nhốt, Thiên-lôi không hoảng sợ. Nước dâng, bê chuối khỏi lo phiền.</t>
+          <t>sau khi tan châu bá quan thấy mất hết cả hôm dựng, ai cũng nhao nhao hỏi nhau, mà chẳng ai hiểu duyên cớ. Nhưng rồi cách một giờ lâu ai nấy nhớ lại câu chuyện hôm trước, bèn quay lại phía Công-Phụ nói với ông rằng: Việc này nếu không phải Bác Bình-dân thì còn ai nữa, thời thì hôm trước chúng tôi nói bốn, Bác cũng bỏ quá đi cho. Vậy hợp áo đầu xin Bác trả lại để ta cùng về một thề.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HVB_003_0599</t>
+          <t>HVB_003_0099</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>二次且囘已奉舉以報君父之答眾子慟哭拜別詢其太顯至北京</t>
+          <t>公輔佯為不知日比必慕澤也乎民安能如是各大笑而去</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nguyễn-Giám-Sinh tác vọng quốc Hoàng-đế NGUYỄN-GIÁM-SINH, KIẾP SAU LÀM VUA, NƯỚC LỚN</t>
+          <t>Công-Phụ lúc ấy vẫn cứ thân nhiên như không biết chuyện, thấy bá quan hỏi thì ông giả vờ đáp rằng: Việc ấy tất nhiên cũng người Mộ-Trạch, chứ bọn Bình-dân chúng tôi thì làm sao nỗi, bấy giờ mọi người mới rõ câu chuyện, trong nhau cả cười rồi cùng giải tán.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HVB_003_0600</t>
+          <t>HVB_003_0100</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>明人訝之曰爾教伯耆立陳後陰國不軌何也詢曰我南人志存南國跖狗</t>
+          <t>公奏使日與公道公正等倡和詩調頗多不嚴盡述</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nghè Hiến-Sử kề lại giấc mơ kỳ quặc như thế, ông Đồ cũng lấy làm lạ, cáo biết ra về, rồi trong năm ấy cậu</t>
+          <t>Thế rồi cách ít lâu sau, ông cùng các ông Công-Đạo, Công-Chính phượng mạng lên đường sang sứ Bắc-quốc, đi qua các nơi danh thắng, các ông cùng nhau xương họa văn thơ, không biết bao nhiêu mà kẻ,</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HVB_003_0601</t>
+          <t>HVB_003_0101</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>吠非其主又何問明人怒送于金陵獄父子皆卒于獄中掾萬言書與</t>
+          <t>陸夫部在侍師後曾禮部尚書</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>lo toàn cướp ngôi tôn quỉ, chẳng sớm thì muộn rồi cũng mang lấy cái nạn diệt vong, sao chúng lại chẳng soi tấm</t>
+          <t>đến khi xong việc trở về ông được thăng chức Thị-lạng bộ Lại, khi mất được phong Bá-tước và chức Lễ-bộ Thượng-thư.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HVB_003_0602</t>
+          <t>HVB_003_0102</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>朱安七斬疏皆忠誠所發陳樸宗先安上疏乞斬七侯臣時稱七斬疏後芸棠故胡公作</t>
+          <t>尚書武恆斷記</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>đòng suối gọi là Hán-Tuyền phát nguyên từ trong dãy núi của xã Ý-Tịch cháy qua xã đó rồi thông với</t>
+          <t>QUẾ-AM, VÕ-DUY-ĐOÁN</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HVB_003_0603</t>
+          <t>HVB_003_0103</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>越鑑有六萬言之書忠貫印月七斬之疏義動鬼神詠史詩云</t>
+          <t>尚書武惟新幕澤人也中堂甲武拔萃之子也</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Danh phần, Dương trạch quyết KIỀU BẤT VỀ MÒ MÁ VÀ HƯỚNG NHÀ</t>
+          <t>Ông Đoán người làng Mộ-Trạch là con giai quan Hoàng giáp Bạt-Tụy ngày trước,</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HVB_003_0604</t>
+          <t>HVB_003_0104</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>上庠琴劍一書生三策懐憐許國情萬里虜廷終不屈先忠十孝而成名</t>
+          <t>火極蒙晴讀書不記一行年十七乙未識字欲改別藝云</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Táng thân mã, Binh thị dĩ khác thăng nhất dư ở TÁNG MỘ VÀO CON THÂN MÃ, HỌ BÌNH THĂNG TRẦN</t>
+          <t>lúc thiếu thời tính rất lỗ độn, học suốt ngày đêm cũng không thuộc được một dòng chữ thành ra khi đã 17 tuổi đầu mà vẫn đốt đặc cán mai. Cậu thấy mình không có khiếu học nên định xoay sang nghề khác.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HVB_003_0605</t>
+          <t>HVB_003_0105</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>曾孫光貞有詩云超延詩禮講明請自勵懸壯士餌寒蹇匪朝誠協</t>
+          <t>夜受見神人騰空而降為之剖心剖去其濁既醒腹中隱然貴痛次備札橋謝之父再開心教學自此日漸開明學大進</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>THỐNG NHẤT NON SÔNG Đinh-Tiên-Hoàng người đồng Hoa-Lư hoa quan,</t>
+          <t>Chẳng ngỡ bỗng có một đêm Cậu nằm mơ thấy một vị thần nhân từ lung chùng giới giáng xuống, lấy dao rạch vào bụng Cậu, mọi trái tim ra nào hết những chất văn dục, đến khi giặt mình tỉnh giây bụng vẫn còn thấy hơi đau, nhưng Cậu cho là điểm tốt nên sáng hôm sau Cậu liền sửa lễ bài tạ, rồi cha mẹ cũng sửa lễ khai tâm để dạy Cậu học.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HVB_003_0606</t>
+          <t>HVB_003_0106</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>一拳拳許國策陳三綱常自任他奚恤鼎饒知餡死亦酣累世亦蒙</t>
+          <t>蟲宜中元二刊文章各天下</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>xưng hiệu là Vạn-Thắng-Vương , binh định</t>
+          <t>Là thay từ đấy trở đi thì Cậu học một biết mươi, dần dần nỗi tiếng là người hay chữ, rồi gặp khoa thì Cậu lại chiếm luôn cờ biên Nhi-nguyên (là 2 lần đỗ đầu), ai cũng cho rằng chuyện lạ.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HVB_003_0607</t>
+          <t>HVB_003_0107</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>忠義報光弼盡業振天南其後明人姜黃福鎮安南設場教</t>
+          <t>初昭祖康王為公子時公居門下適有間饑從星散公獨進隨</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chăm hậu tượng, Trần-Gia dĩ sắc đặc Thiên hạ</t>
+          <t>Nguyên trước khi Chiêu-Tổ Khang-Vương còn làm Công-tử, thì ông giúp việc ở trong phủ, gặp lúc hữu sự bao nhiêu thuốc hạ đều hổ chạy hết, riêng có mình ông lúc nào cũng ở bên cạnh Vương,</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HVB_003_0608</t>
+          <t>HVB_003_0108</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>學以收我國人才穎題兄弟竝往受業黃福愛之認為己子忽</t>
+          <t>迨王居節制府進徃留屯詰賊時以解元八侍帷帳事之大小王必密之當時謂之內相</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mỹ-Lộc nỗi đời làm nghề chài lưới, suốt cả một giải Tràng-giang ở nam đảo, tới đầu thì cũng là nhà, chừ</t>
+          <t>đến khi Vương được phong chức Tiết-chế tức là Trịnh-Cần 1682-1709 đem quân vào đóng ở Luru-đồn thì ông đã đã Giải-nguyên theo giúp ở nơi quân thứ, bất luận việc lớn hay nhỏ Vương cũng hỏi qua ý kiến rồi mới thi-hành, bởi thế người đời mới gọi là quan Nội-tướng,</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HVB_003_0609</t>
+          <t>HVB_003_0109</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>一夜雨電壞牆發屋明日黃福出城南玩景口占一旬云照朝風雨</t>
+          <t>徵完詞中優須甲長科中會元王賜之綵衣待以不次六部到尚書</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>thì đêm hôm ấy sấm sét nỗi dậy ầm ầm,</t>
+          <t>rồi sau thì khoa Hoành-từ ông lại được trưng ưu hạng, đến năm Giáp-thìn lại đổ Hội-nguyên, Vương ban áo mũ và trọng đài hơn mọi người. Vì thế 6 năm giới mà ông đã thăng đến chức Thượng-thư.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HVB_003_0610</t>
+          <t>HVB_003_0110</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>家家額壞舊牆垣以喻南國被侵必致額壞額頸即對云今日</t>
+          <t>言公忠剛慷慨遇事敢言常尊泰九斂之為人上金鑑錄大要勸以正心穀俗知人去讒言甚愜切王嘉納之奇以通臣自許</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ngư-phủ họ Trần vội vàng đem các thứ ra chỗ ngôi mộ Tồ nhà Nguyễn-Cổ, cắm lưỡi tâm sét xuống chạm đến quan</t>
+          <t>Xét thấy ông là người rất kiên trung và khẳng khái, gặp việc gì không hợp cũng có can đảm nói ngay. Vì ông rất hàm mộ tư cách của Trương-Cừu-Linh ngày trước cũng giống như thế. Cho nên có dáng bộ Kim-giám-lục trong đó toàn là những câu nói về Chính tâm, hậu tục biết người, xa kẻ siềm nịnh v.v... lời lẽ cực kỳ thiết đáng, được Vương khen là một vị Trực thần.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HVB_003_0611</t>
+          <t>HVB_003_0111</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>乾坤震處發榮新草木黃輝是簡高見人聞此句望天嘆曰安</t>
+          <t>時宮中有詞鷄之戲中官索鷄鷄奉進公適見問問鷄何從來中官以鷄答公作色曰昔在潛師時主上惟知有我寧知爾輩為何人今乃導之以戲樂郎立執鷄喉鷄應手而死中官馳八具告王默然而起為罷詞鷄事</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>điểm vào chỗ Thổ-phúc Tăng-Kim tim đất giấu vàng , ngời phương can trống chư Tốn, công việc</t>
+          <t>Trong thời gian ấy ở nơi cung trung thường hay có cuộc chơi gà, các vị trung - quan thấy vậy bèn sai người đi khắp các nơi để mua gà tốt về hiến, một hôm bắt gặp, ông liên quát hỏi gà này từ đâu đem đến. Trung quan cứ thực trả nhồi; ông tỏ vẻ giận dữ mắng rằng: trước kia khi còn ở nơi Tiềm-đề (tư định) Vương thượng chỉ biết có một mình ta chứ có biết đâu bọn chúng, thế mà ngày nay chúng toàn bày trò du hi để làm mê hoặc Chúa thượng hay sao, mắng xong ông bên giang lấy con gà chơi rồi bè gậy cò cho nó chết tươi. Trung-quan chạy vào trong cung tấu bày cáo, Vương lãng lăng không nói gì, rồi từ đấy về sau trò chơi chơi gà cũng không còn nữa.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HVB_003_0612</t>
+          <t>HVB_003_0112</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>南已有聖主出乾坤方南國復還南國我亦不久且歸矣二子盡往</t>
+          <t>陽德年間繫嘉宗年號有北使至公為接伴使與北使途廣和自稱河津至于殲門詩凡二十餘首應答如響北使甚敬章之</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>lộc ! Thầy đáp : chẳng cần phải thế, hễ mà sau này nhà ông lấy được quốc gia, thì con cháu tôi đời đời cấp cho</t>
+          <t>Đến năm Dương-Đức triều Lê Gia-Tông (1672-74) có sứ Tàu sang, ông được sung chức Tiếp sử, trên quãng đường trường từ ải Nam-Quan trở về, đối bên xướng họa văn thơ không biết bao nhiêu mà kẻ, ngay từ bên sông Nhi-Hà vào đến Điện-môn, Bắc-Sử cũng xướng hơn 20 bài, bài nào ông cũng họa ngay. Sư giả lấy làm kinh ngạc,</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HVB_003_0613</t>
+          <t>HVB_003_0113</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>從之以圖立功穎顯遂依報尋至愛州已見我大祖蘇山奮勵兄</t>
+          <t>至禮部設宴北使富筵索酒公應口吟曰</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>có tướng mũi rộng mắt phương, được Lý-Chiều-Hoàng nhượng ngơi, hiệu là Thái-Tông.</t>
+          <t>đến khi Lễ-bộ thết yến Sư giả hạch sách rượu dầu, ông lại ứng khẩu ngâm rằng:</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HVB_003_0614</t>
+          <t>HVB_003_0114</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>弟皆來歸附未幾大破北兵沐晟黃福等投降之和太祖縱之北還</t>
+          <t>飽吾宁道真佳味何必江亭問一盞</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>nhà Trần suy yếu để Xích-Chủy-Hầu tức Hỗ-Quý-</t>
+          <t>Bảo ngô cá đực chân nhai vị, Hà tất Giang đinh vấn nhất bồi nghĩa là Rượu ngon là đực ta say nhi, còn hỏi Giang đinh một chén chi,</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HVB_003_0615</t>
+          <t>HVB_003_0115</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>顔顔等戲師歸國至交開相告別同跪請曰儀等蒙作育久矣</t>
+          <t>北使稱賞覲成禮而去</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cát cúc thàn lưu Võ tộc, thế truyền tước lộc QUÍ ĐỊA THÂN BÊ CHO HỌ VÕ, TƯỚC LỘC BỜI BỜI</t>
+          <t>Sư giả nghe xong tấm tắc khen ngợi rồi buổi đại lễ được hoàn thành ngay. (Giang đinh là quán rượu).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HVB_003_0616</t>
+          <t>HVB_003_0116</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>未審何時復頒教誨請指示陰憤吉昌歸塟先人是吾師之賜也並福</t>
+          <t>後差往高平公幹以爲臣漢都公各居公上公杭言曰臣承嚴之備位尚書奇意主上南牙各軍不調今日使漢都公居其右臣敬不奉命</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cựu huyệt thiên táng, hàn thê dựng xuất cung phi HUYỆT SẢN TRỜI CHO, VỌ NGHÊO ĐƯƠNG CHÚA,</t>
+          <t>Cách ít lâu ông được lên công cán Cao-bằng, nhưng Vương lại cho nội thân là Hán Quân - công được ở quyền trên, nên ông kháng nghị rằng: Thần đây làm dự chức vị Thượng-thư, tưởng rằng Vương thượng cũng coi Nam nhà làm trọng, chứ có ngờ đâu Hán-Quân lại ở trên thân, vậy thân không dám phung mạng.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HVB_003_0617</t>
+          <t>HVB_003_0117</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>曰我非忘了試觀二子之志耳前日噐心一穴在亦邑兌邊桃樸頭向銀帶</t>
+          <t>時府僚或在都臺令道乃孫弟方覲奏見此命若行三都不敢秉筆</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ao rộng kẻ mấy chục trượng, chẳng ngờ giữa lúc dân làng kẻ nom người vô dương mãi bất cá ở dưới ao, thì</t>
+          <t>Giữa lúc ấy các quan đều có mặt tại phủ, Đô-Đại Công Đạo là em họ ông cũng kháng nghị rằng: Vì thử Vương bất thi hành lệnh ấy, thì Tam Đô-thân không giảm cầm bút đề ghi.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HVB_003_0618</t>
+          <t>HVB_003_0118</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>日月扶裔天馬在其西旁正乎年我已埋下木板歸而尋之囑其子孫</t>
+          <t>王怒曰若不知命且審此日向暮之黃門智俛之公道知上意不囧即以顗整柱公勃然曰王欲殺諫臣請即納還勅命</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>trăng mỗi khi ngả bóng chiếu tạt xuống nhà, trong như hình con Thiềm-thư ngồi ở trên nóc, vì như thân ở cung</t>
+          <t>Vương cả giận phân rằng: Nếu không tuân lệnh thì cứ ở lại đây, thành ra bá quan phải ở lại đến lúc gần tới. Vương sai Hoàng-môn quan ra dực, Công-Đạo xem chúng Vương không chịu thay đổi ý kiến, bèn đập đầu vào cột trụ, ông thì nói lớn lên rằng: Vương Thượng đã giết Gián Thần, vậy Thần xin nạp lại sắc lệnh!</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HVB_003_0619</t>
+          <t>HVB_003_0119</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>後有北使遲歸便可鑿這馬足郎當反轡二人拜辭而回時太祖已矣</t>
+          <t>黃門以聞王怒曰他前日斃吾良鷄我亦含忍今乃爾何疆耶誰殺諫臣而卻知此說立耶罷歸公道像他黨亦罷隨耶差往公道家追收勅命其進士科字一道公不肖納奉差索取之公堅執曰諸勅皆王之賜謹當奉還至如科字乃我才學做成不敬併納奉差不勝為而回</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Đặng-Canh dùng phép châm cứu nên ngài mới được hồi sinh, về sau ngài bị liệt dương, Đặng-Canh xin cho mở</t>
+          <t>Hoàng-môn Quan thấy vậy vội vàng vào tàu: Vương càng giận thêm! à! hôm trước đã giết gà chơi của ta, ta cũng ẩn nhẫn, chẳng ngờ ngày nay y lại quật cương đến thế thì thôi! thử hỏi ai giết Gián Thần mà y dám nói như vậy, rồi Vương hạ lệnh bãi chức ông và Công-Đạo, sau lại sai quan đến nhà thu về sắc mạng từ xưa đến nay, thử gi lòng cũng giao trả, riêng có đạo sắc Tấn-sĩ về khoa thì chữ tốt thì ông giữ lại, sai quan cố tình đời cả, ông viện lẽ rằng: những sắc lệnh kia là của Thượng ban thì tôi vàng mệnh giả về, còn đạo thì chữ là do tài tôi làm được thì tôi có quyền giữ lại làm ghi, Sai quan thấy nói hợp lẽ đánh phải trở về phục mạng.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HVB_003_0620</t>
+          <t>HVB_003_0120</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>天下擇人北使無敢行者少頴以父兄之故敵然請往太祖許之拜審</t>
+          <t>時公子推匡由庚茂科中進士同北鎮勘制司王郎召還許以少師陪從意欲用之蓋公難以舊臣然數犯顏觸諦頻見嚴憚故因忤言麗之而用其子其後公道復召用居職如原</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>bung dựa trẻ con trai lấy gan hòa với vị Dương-khởi- Thạch để cho vua uống, và bảo vua phải thông dâm với</t>
+          <t>Nhắc lại khi ông lui về vườn cũ bạn với cúc tùng, được hơn 4 tháng thì con giai là Công-Tử Duy-Khuông đỗ Tấn-sĩ tự khoa Canh-thin, hiện đương giữ chức Đông-Bắc-Trấn Khám-Chế-Ty, được Vương cho triệu về Kinh sung chức Bồi - Tung Thủy - Sur có ý muốn trọng dụng. Bởi vì ông dẫu là bậc cựu thần, nhưng đã nhiều lần làm Vương phạt ý, nên Vương mới phải xuống chỉ trực hồi, ngày nay lại muốn dùng con để tỏ ra lòng ưu đãi. Tiếc rằng Duy-Khuông vào trong Chính-phủ cũng chẳng được lâu, sự nghiệp cũng chưa thành tựu. Còn như ông Công-Đạo thì sau cũng được triệu về phục chức như xưa.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HVB_003_0621</t>
+          <t>HVB_003_0121</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>刑院事、秦陳情表于明其畧曰天地之於萬物雖有雷霆之怒而發</t>
+          <t>而公優游桑梓遂無意於當世常有范蠡五湖賦父業澤風景農家考績異聞等作皆用國音人多傳誦其詩詞銘記頗多世稱中興以前詠橋候中興以後唐川子蓋言國音文體得之清高而其學問該博故耳</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Thoát-Hiên có vinh bài thơ tứ-tuyệt như sau : Phiên âm Ký nhân bặc nghệ Yêu quân sủng !</t>
+          <t>Riêng về phần ông thì vẫn ngao du ở nơi phần tư, không đề ý đến việc đời, nhân buổi thư nhân ông có soạn ra rất nhiều thơ phú Phạm-Lãi-du-Ngũ-Hồ và cuốn Trạch-hương phong-cảnh tập Nông-gia-khảo-tích dị-văn, v.v... đặc biệt nhất là những cuốn văn ấy toàn dùng Quốc-âm, cho nên được rất nhiều người truyền tụng, ngoài ra lại còn biết bao bài mình, bài kỳ rất hay, người đời đã phải ca tụng những câu: Trung hung về trước có Vĩnh-Kiều Hầu, Trung-hung về sau có Đường Xuyên-Tử là nói thề văn quốc âm đều đã đến chỗ thanh cao lắm vậy. Lại như quan Trang họ Đặng ở làng Phù-Đồng soạn bức trướng mừng Võ Tề-Tương khi về hưu cũng có câu rằng: Châu Tương-Công có Đường-Xuyên là người đã nuốt hai kho sách Thiên-lộc Thạch-Cừ, của nhà Hán vào bụng, nghĩa là khen sức học uyên bác vậy.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HVB_003_0622</t>
+          <t>HVB_003_0122</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>生每行乎其間父母之於眾子雖有笞檳之威而鞠育常存乎其內</t>
+          <t>公雖去國而朝野皆重其各漂然起敬時有之南處意副在憲司日有武職一員以苛過被訴論失民兵其後奉侍內閣意副預焉見武官奉勵武惟斷以事忤旨囂歸至今不見召用而武職其員由該官並可濫臣等已論失民兵今復居職知原小臣敬不彈奏以嚴國典時侍臣見之無不相顧駭愕至上疑意司是公之黨為之遊說命參訊之始知共公無干郎有旨云意副小臣何敢越職言事今姑原之自後不得知此意副奉命而退</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hai mẹ con thấy mụ già xin ngủ đổ thì cũng niềm nổ cho mụ ngủ ở nhà ngoài, còn hai mẹ con thì ngủ phòng</t>
+          <t>Còn ông thì đầu thời làm quan nhưng trong triều ngoại quan thấy đều trọng danh, lúc ấy có quan Phó-hiến đến nhận chức ở Sơn-Nam, thấy có một viên quan vô bị cáo về việc hà lâm. Ông kết vào tội làm mất dân binh, đến khi ông được bỏ vào Nội-các thấy người vác kiểm đứng hầu lại chính là viên chức bị tội ngày trước. Ông liền quy xuống tàu rằng: Hạ thân thấy quan Thương-thư Võ-duy-Đoán.trước kia vi trái ý Thượng nên phải bãi chức về vườn, tôi nay chưa được phục chức, mà viên võ kia là chức cai quản hà làm, Thân đã kết tôi làm mất quân dân, có sao nay lại phục chức như cũ. Vậy nên Thân phải chất vấn đề cho quốc pháp đẳng nghiêm v.v... Giữa lúc ông kêu việc đó thì các quan hầu thấy đều đông đủ, ai cũng nhìn nhau bằng đôi con mắt kinh ngạc! Còn Vương thượng thì lại ngỏ ông về bè với Võ-Thượng-thư, nên Ngải giao cho đình thần tra xét, sau biết là không, nên được miễn nghị, nhưng Vương lại hạ dụ rằng: Hiến-ty là hạng quan nhỏ sao được nói leo. Vậy nay hãy tạm tha thứ, còn từ đây về sau thì cảm không được giữ thói ấy nữa v.v.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HVB_003_0623</t>
+          <t>HVB_003_0123</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>是以人有疾病未常不呼天地父母此臣子之歷緬陳詞以伸表籲</t>
+          <t>蓋公以正言被黜故有忠憤者亦為不平其祭文乃全平日所自作如致君期竟舜唐虞自任以身受變綫契去素蘊胸中平治欲大屢施至玄幾裏覓虛且取難宣世其盈虛付之玄機而不流於惑亦得古人忠厚之意兵壽六十四歲贈左侍郎公三世登科為武族世科之冠之始歟</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>có xảy truyền lạ, thì phải chạy với lên chỗ gò cao, chứ đừng lưu luyến gia hương mà khở.</t>
+          <t>Xét thấy ông Phó-hiến đây vì giữ chính khi mà bị truất oan, khiến cho những người có lòng ngay thẳng cũng bất bình thay, còn bài văn tế là do ông thảo tự lúc sinh thời như câu: Thờ vua thì mong Vua như Nghiêu Thuấn, sửa mình thì phải theo dấu Cao-Quy. Sẵn tấm lòng ngay, muốn đem trị bình thì thô, xem cơ tạo hóa, dám đầu tiết lộ huyền vi, câu văn thực là kín đáo nhưng mà trung hậu biết bao. Về sau ông hưởng thọ được 61 tuổi, sau khi tạ thế được tặng chức Thi-lạng, như vậy thì nhà ông đã được 3 đời đăng khoa kế tiếp, và mở đầu 4 chữ kế thế đăng khoa cho họ Vũ làng Mộ-Trạch vậy. (nguyên bản có chú rằng còn thiếu một đoạn.)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>HVB_003_0624</t>
+          <t>HVB_003_0124</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>也寫所作並替代金人二軀各重二百兩至燕京陳于關下懇訴明人恨我</t>
+          <t>尚書武公道記</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>có một cái bẻ thuộc xã Tiên-Loan chi bên tả có 2 cái bẻ thuộc xã Nam-Mẫu chỗ cùng tản bẻ lên mãi</t>
+          <t>MẠO THỦ KHOA CỬU TRÙNG ĐẶC CHỈ</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>HVB_003_0625</t>
+          <t>HVB_003_0125</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>國徵殺柳昇之故甄唾罵不問物火頴于門下外漆其兩目不許飲食</t>
+          <t>武公道一蒙澤人也其父安富侯少而總齊時有鄰右衰老儒指庭前甘燕葉取岀一曰云庭前有燕皆著紫衣父對曰池下生蓮同張青蓋來大稱賞識者知其子孫必有科第同登之兆後生公與亮公起以馮爽稱</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>THỦ LOẠI Lang đã tâm ăn đường nan tuần THI ON CÚC DỤC, DÃ TÂM CỌP CŨNG KHÓ THUẬN</t>
+          <t>Vũ-Công-Đạo người làng Mộ-Trạch phụ thân là An-phủ-Hậu. Ông vốn thông minh ngay từ thuở nhỏ, lúc ấy có một ông Đồ hàng xóm tên là Tả-Côn chỉ vào khóm mía ở trước sân ra một vẽ đối như sau: Đinh tiền hưu giá giai trước tử y, nghĩa là: mía ở trước sân đều mang áo tía. Ông đối ngay rằng: Địa hạ sinh liên đồng trương thanh cái, nghĩa là Sen sinh dưới đất cùng rán lộng xanh. Ông Đồ nghe xong tám tắc khen ngợi, còn người thức giả thì dự đoán rằng: đó là cái điểm mà con cháu về sau sẽ đổ đồng khoa, quả nhiên về sau Cụ sinh ra Ông và Công-Lượng cũng đều nổi tiếng tài hoa.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HVB_003_0626</t>
+          <t>HVB_003_0126</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>時黃福八朝見之知其少穎嘗取貓餅藏穀中每過即授之三月餘不死</t>
+          <t>丙申科會試公完赴舉時村內東亭市有老嫗于稠人廣坐中粹面撻身躍立而言曰我是儉人降下茲料進士于吾我已知之爾澤邑文星正旺天帝簡知我故來相告爾等欲聞之乎</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>giữa sân có 1 con heo, đến hôm dám ma thì lại thấy có 1 con bò, rồi sau gặp ngày tế tự cũng đều thấy có lễ vật để</t>
+          <t>Thế rồi đến năm Binh-thân gặp khoa thi hội, Công-Lượng cũng vào thi, lúc ấy ở chợ Đông-Định trong thôn bổng có một bà lão tự trong đầm đồng nhảy ra, đứng sừng trước mặt mọi người, mặt thì đỏ gay, đầu thì lão đảo, lên tiếng bảo mọi người rằng: Ta đây vốn ở Tiên cung cho nên khoa thi này được bao Tấn-sĩ ta đã biết trước, hiện nay làng Mộ-Trạch người, vẫn tinh dương vượng, đức Ngọc-Hoàng đã tuyển sẵn rồi nên mới sai Ta xướng đây bảo cho các ngươi biết rõ! Vậy thì các ngươi có muốn nghe không?</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HVB_003_0627</t>
+          <t>HVB_003_0127</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>明人以為神始受貢禮使囘復命火穎因尋父兄不知沒處至于僧奇只</t>
+          <t>村人奇之布席以坐四面還觀爭以美質當祈獻叩問之其人曰今科進士有六而幕澤居其三村人請問姓名曰登龍中再問之曰卓然牛中又問之曰公亮中眾人皆以為誣謗莫之信父後出榜率知其言識者自謂事有明定而天門放榜之事亦不託傳部說</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>đến ơn chủ, chỉ vì người trần mất thịt không hiểu thấu</t>
+          <t>Các ngươi trong thôn xóm thấy nói lạ lùng như vậy, họ bèn trái chiều mòi bà ấy ngời, rồi họ đứng bọc chung quanh và lại xô nhau đem trâu cau ra khấn vái để hỏi xem sao? Bà ấy đáp rằng: khoa này có 6 Tấn-sĩ thì làng Mộ-Trạch chiếm được 3 ngươi. Hỏi 3 ngươi ấy họ tên thế nào? Bà ấy đáp: Đặng - Long, hỏi lần thứ hai, đáp rằng: Trác-Lạc, hỏi lần thứ ba, đáp rằng: Công-Lượng. Mọi ngươi nghe xong vẫn yên trí là câu nói hoang đường chứ chẳng ai tin, nhưng rồi đến khi kéo bảng thấy đúng như vậy. Bấy giờ những ngươi thức giả mới tin là có tiền định, mà việc phóng bảng trên cửa nhà giới, cũng chẳng phải là câu nói ngoa vậy!</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HVB_003_0628</t>
+          <t>HVB_003_0128</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>見一詩一畫存焉即將固本鄉虛墓之後諫太祖忤旨降禮部員外郎光</t>
+          <t>茲科未生試一年間有北地師經登第龍祖登觀者良久曰我纏到青池縣月蓋社者阮族舊墳以為來科必發首科今按這苟不讓月蓋地脈來春亦當得者科人以爲誣朝之曰龍競假真都亂說豈有一榜二首科之理乎</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lão đáp : Mổ đây vàng mệnh Thượng-Đế sai xuống, chẳng may một sơn sa cơ, tội đáng muốn chết.</t>
+          <t>Nhắc lại khoa này một năm về trước có thầy địa-lý Tàu khi qua ngôi mộ Tồ nhà ông Đặng-Long thấy Địa xem xét hồi lâu rồi bảo mọi ngươi rằng: Khi tôi mới đến xã Nguyệt-Áng thuộc huyện Thanh-Tri đó xem lại ngôi mộ Tồ họ Nguyễn thì tôi đoán rằng: khoa thì sang năm họ ấy sẽ có người đỗ Thủ-khoa, ngày nay xem cục đất này khi mạch cũng không kèm gì Nguyệt-Áng, sang xuân thế nào cũng phát Thủ-khoa. Lúc ấy ai cũng chê điều cho rằng: Long hồ thực hư đều là những câu nói hão, chứ có lẽ đầu cùng trong một bảng mà lại có hai Thủ-khoa!</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HVB_003_0629</t>
+          <t>HVB_003_0129</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>貢有詩云壯年表表頁高各開創寅緣際聖明詩草預陪寫掖運</t>
+          <t>至是策題問以君道聖籠子敬天用人開國紀綱保功臣法度國用治道禮樂將帥賞罰中興功業國勛九十四目為問阮廷柱中會元簽籠中第二醜而八將王庭王上見簽龍相貌比廷模勝之有首判云此子不當首科耶命在天柱王右故時人稱楚樑字首科餐龍觀首科方覺北師之書亦為高見</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DANH-THẦN Phụ danh-nho danh-thần Phụ chép thêm các bậc danh-nho, danh-thần</t>
+          <t>Nhưng rồi đến khoa thì ấy thì đề tài sách vẫn lại hỏi về quân đạo Thánh học v. v... công 14 mục. Thi xong Đinh-Quế được trúng Hội - nguyên, Đặng - Long được đỡ thứ nhi, đến khi cùng vào Vương phủ dự yến, Hoàng-Thương nhìn thấy diện mạo Đặng - Long có vẻ tuần tú hơn Đinh-Quế nhiều, nên Ngai phân ngay rằng: Gã này không đáng mặt Thủ-khoa hay sao, rồi Ngai ra lệnh cho Long được đứng ở bên tay phải Đinh-Quế. Vi thế lúc ấy mới có câu rằng: Đinh - Quế là Thủ-khoa Chữ Đặng-Long là Thủ-khoa đẹp, bấy giờ người ta mới tin thấy Địa cao kiến hơn đời vậy.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HVB_003_0630</t>
+          <t>HVB_003_0130</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>垂朝先擁使花行王臣襄惕忠兼孝天理昭明困復亨未商于今循故</t>
+          <t>時入道未第吹年彼孝事偽因他適鄉試場目次點心中真更問夜為交至唐豪縣無得社行過去外聞內有聲喚曰進士何之公郎馳至三闕見闊者二人載嘆因問之曰這裏某宮人在閣者曰正中黃衣乃玉皇上帝座兩旁青衣者南曹北斗是也公進八庭前跪請曰敬問員進士何科見在旁二員面問中正知幕間之狀俄聞曰許茲科公曰來春袁經未除何能望此闡有聲曰震公再請曰臣藥已欠點知何又聞曰訴見點入受中喜不自勝急喜起趨出跌躡于地見在內老人調清水一盃灌之既而醒覺口中猶有香臭</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Mạc-Đinh-Chi, Lưỡng quốc Trang-Nguyễn, Trang-Nguyễn hai nước, (Việt-nam và Trung-</t>
+          <t>Còn như Công-Đạo lúc ấy cũng chưa dỡ đạt, rồi sang năm sau gặp việc đại tang, nhân lại có việc phải đi nơi khác, nên bị thiếu điểm ở trường thi hương, giữa lúc còn đương lo phiên thì bỗng một đêm ông nằm mơ thấy: mình đi đến xã Võ - Ngai thuộc huyện Đường-Hào, khi qua ngôi chùa chợt nghe bên trong có tiếng hỏi: Quan Nghè định đi đầu tá Ông vội chạy vào trước cửa Tam quan, thì thấy hai người cầm roi đứng canh hai bên, ông hỏi trong ấy có vị quan nào, họ đáp: Người mặc áo vàng ngồi ở chính giữa là Đức Ngọc-Hoàng, còn hai người mặc áo xanh hai bên tức là Nam-Tảo Bắc-đầu đó. Ông nghe hai người bảo thế vội tiến vào sân quy gói hỏi rằng: Khoa nào hạ thần được đổ Tấn-sĩ? Hỏi xong thì thấy hai người nhìn vào vị ngồi ở giữa hình như bẩm vấn điều chi rồi sau phân bảo: Anh sẽ đổ ngay khoa này! ông lại hỏi tiếp: Nhưng mà sang xuân thì thân còn đương mặc áo sô gấu biết làm thế nào? đáp rằng: Triền, (tức triền hạn), ông lại hỏi trước kia thân đã thiếu điểm thì sao? đáp: Tha cho điểm đó! Nghè được mấy câu phân bảo ông rất vui mừng, vội vàng chạy ra, chẳng ngờ xảy chân té nhào xuống đất, bống thấy bên trong có một ông già đem chén nước lă ra đổ vào miệng, rồi một lát sau thì ông tỉnh dậy, trong miệng vẫn còn hương thơm.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HVB_003_0631</t>
+          <t>HVB_003_0131</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>轍功成事濟是前程其孫孫襄中狀元生下共責五歲好學人號袖童</t>
+          <t>笑已科春園以有事展誠又先是各處直士徃徃潛八鄉試場代試多致大顯至是昭祖判云凡為人顯者為人代試必是有所文字應一切藏之今以是范吳科公親舅來謝族兄惟誨同色公朝四各同榜自有科目以來未之有也</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ngải vón là cháu quan Thượng-Thư Mạc-hiền-Tích</t>
+          <t>Thế rồi vừa bước sang năm Kỷ-hợi trong nước gặp lúc hữu sự, nên kỳ Xuân-thí lại phải hoãn đến mùa đông. Và lại trước kia Cống-sĩ các nơi thường hay đội quyền thì giúp trong kỳ thi hương, cho nên nhiều người thiếu điểm. Ngày nay Chiêu-Tô phán rằng: Những người đã đi thi họ tất nhiên là người học khá, vậy nay nhất thiết tha cho cái lối thiếu điểm năm xưa, vì thế ông cũng được miễn. Rồi ngày khoa ấy ông cùng Bác ruột là Cầu-Hối, em họ là Duy-Hải người cùng ấp là Công-Triều, tất cả 4 người cùng được đề danh đồng bảng. Kể từ lúc có khoa mục cho tới ngày nay chưa bao giờ thịnh đến như vậy! (Kiểm điểm cũng như kiểm diện).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>HVB_003_0632</t>
+          <t>HVB_003_0132</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>統元年號、丙辰科中黃甲仕至戶部左侍郎奉往北使時有中使輔行等</t>
+          <t>公在朝言論碌何不辟權貴常有諫闕鷄文奉進昭祖深嘉之陽德間奉往北使回至南亭遇賊依攬阻陸路不通上國給以大艘從安廣水道而回仕至都御史壹因執奏武惟斬與內臣漢都公之罪見武惟斬王不從公以頭顱系柱凜然有奸廷折楹之風時稱直御史罷歸未幾復得召用任至尚書郎八十義公之前程事築未第時一變已非見矣</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sĩ đệ nhất danh khoa Bình-Dân thời Lý Trung-Tông, làm đến Thượng-Thư bộ Lại và được nhà vua bán cho bộ áo</t>
+          <t>Xét thấy khi ông làm quan tại triều, nghị luận rất là cũng cỏi, không hề kiêng nề những chỗ quyền môn, thường tiến bài văn can gián về việc chơi gà, rất được Chiêu-Tô khen ngợi. Vào khoảng năm Dương-Đức (1672-74) ông sang sứ bên Tàu, khi về đến tỉnh Nam-Ninh thì địa phương ấy có giặc, đương bộ bị ngễn, địa phương quan phải vất 1 chiếc thuyền lớn để dưa ông về đường thủy, rồi sau ông làm đến Đô-Ngư-Sử Đại, lúc ấy ông tâu về việc Duy-Đoàn và Hán Quần-Công, thấy Vương không nghe, ông bèn dập đầu vào cột, khi phách lâm liệt chẳng khác gì người níu gãy bao lan ngày trước. Cho nên đời mới gọi ông là Trực Ngư-Sử. Tuy nhiên sau vụ ấy thì ông bị bãi chức trở về cố hương, nhưng chưa bao lâu lại được triệu dụng, rồi làm đến chức Thượng-Thư Trí-sĩ. Kể ra từ năm 18 cho đến 86 tuổi, năm nào ông cũng có thơ Tự-thuật, viết bằng quốc âm và thơ Đường-luật, thơ đều xuất khẩu thành chương, rất được nhiều người truyền tụng. (Thấy trong tập Lão-Hội) bởi vì sự nghiệp tương lai của ông thì một giấc mộng đã bảo từ trước khi đổ đạt vậy.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HVB_003_0633</t>
+          <t>HVB_003_0133</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>寧貴物假作金銀替代潛取原物公不知之比至南寧府總督啟發見</t>
+          <t>公外自風流而為行統實初為山南督同時賜夫人不在有二門下人擕一絕艶歌兒來欲其買寵公曰我自少至長未常違非已之色汝以尤物殺我平拒而遣之離居貴顯不買群妾只有微時一夫人與之緒影交常對兒孫言我雖不逮古人而未常犯奸色之或是人之所難也</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>kim-ngư (cả vàng), em là Kiến-Quan cũng đồ Tấn-Sĩ làm đến Công-bộ Thượng-Thư, còn ông Trang đây là cháu</t>
+          <t>Người ta xét thấy ông là người bên ngoài có vẻ phong tình, nhưng mà trong tâm giữ rất thuận cần, thử coi khi ông còn làm Đốc-Đồng tại xứ Sơn-Nam có viên thuộc hạ dòm lúc phu-nhân đi vắng, bèn đem một ả ca nhi tuyệt sắc vào định toan sự cầu thân. Nhưng ông bảo rằng: Ta đây từ nhỏ đến lớn chưa hề xăng bày đến cái sắc đẹp không phải của mình, vậy người toan lấy vật là để chức lay chuyện ý chí của ta đó chẳng? Thời muốn tốt thì người phải đem ngay đi chỗ khác. Chả thế mà trong lúc phu quí như vậy ông vẫn chẳng mua nàng hầu, trong phòng chỉ có mỗi một phu-nhân là người xe to kết tóc từ lúc hàn vi thôi, bởi thế nên ông thường bảo con cháu: Ta dầu không theo kip cờ nhân, nhưng cũng chưa hề phạm điều sắc giới, giữ được như thế tướng cũng khó thay.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HVB_003_0634</t>
+          <t>HVB_003_0134</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>其非真遂以事聞皇帝怒其無禮命拘晉于北那官仍以蛤蜊覆公</t>
+          <t>其平生教習多得英才如東鄰撫眼公范光宅丹輪探花武成賊楊柳會元阮各譽誼以魁科望異代見推皆公之門弟也今之學者猶尊仰焉</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nguyên-đế bèn sai ông cùng Sứ-thần Cao-Ly mỗi người</t>
+          <t>Nói tóm lại, sĩ phu thời ấy nhớ sự học vấn và đạo dức của ông đã gây nên được biết bao nhân tài. Tí như quan Bảng-nhơn Phạm-quang-Trạch ở làng Đồng-Ngạc, quan Thám-hoa Vũ-Thanh ở làng Đan-Luân và quan Hội-nguyên Nguyễn-danh-Dự ở làng Dương-Liễu, đều là các bậc khôi khoa, được đời tôn trọng và cũng đều là học trò của ông, khiến cho đời nay người ta vẫn còn ngưỡng mộ,vậy.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>HVB_003_0635</t>
+          <t>HVB_003_0135</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>兩目以漆粘之曰瓶氣馬角方得還期公怡然自樂不少動心書於冬日</t>
+          <t>廉蔣公遺記</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chu-Công ; Mưa tuyêt đầm dia, Bá-Di Thức-Tề. Ý nói mùa hạ nóng nực, thì cái quạt đắc dụng như hai ông Y-Doãn</t>
+          <t>DANH THẦN VÕ-TU.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HVB_003_0636</t>
+          <t>HVB_003_0136</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>出時輒圓一小床曝于日下一明人問其故公即撫其腹曰我曝腹中經笥耳</t>
+          <t>武娶唐安穫澤人也浙陽省洪德韜聖宗癸丑科中黃甲公性顔廉直居官清儉未嘗妄取于人時頗尚賂遺用唐太宗故事使人懲誡試之他官従従受之公獨見拒饋請人固請曰今習尚如此寢以成風且這條菲物而相公不受為傷廉也公作色曰世人比自而獨我独清豈以爾甘言而易其樑驅而出之其人固奏帝嘉其人有暮夜卻金之郎賜公廉二字許入朝黏于衣領以旌異之</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>kinh, một hôm, ông cởi lừa đi đạo phố, chẳng may con lừa của ông xó vào con</t>
+          <t>Ông Võ-Tu người làng Hoạch-Trạch huyện Đường-An thì đã Hoàng-Giáp khoa qui-sửu thời Lê Hồng-Đức, ông vốn có tánh liêm-khiết và ngay thẳng, ngay lúc làm quan cũng vẫn giữ nếp thanh bạch, không hề lấy lễ của ai, giữa lục ấy cái tệ tham những dương hoành hành. Hoàng-Đế muốn bắt chước Vua Đường Thái-Tông ngày trước, cũng sai người giả làm dân thường đem lễ đút lót các quan, quan nào cũng nhận, duy có mình ông nhất định cự tuyệt, người đưa lễ có nài nói rằng: hiện nay phong tục hối lộ đã thành thói quen, và lại một món quà đây cũng chẳng đáng giá bao nhiêu, nếu Ngài nhận cho thì cũng không hại gì đến tiếng liêm khiết. Ông thấy người kia cổ tinh nài ép thì nghiêm sắc mặt mắng rằng: nhà người nên nhớ: Thế gian đều trọc, chỉ có một mình ta thanh! nhẽ nào ta lại vi câu nói ngọt và món lễ hậu của người mà dồi tiết tháo, người phải đem đi tức khắc! Người đem lễ bị ông quát đuổi, đem lễ ra về, vào tàu với vua như thế. Vua khen là người biết trọng khí tiết cũng như các vị thanh liêm thời trước chẳng chịu nhận vàng trong lúc đêm khuya. Vì thế Ngai mới ban cho hai chữ Liêm tiết, và cho định vào cờ áo trong lúc vô triều cốt để nếu cao phẩm giá,</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HVB_003_0637</t>
+          <t>HVB_003_0137</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>明人使讀大槩演義公讀了一遍不差一字明人大奇之即去其粘目甚加</t>
+          <t>仕到刑部左侍郎廉節各良家無祖石之儲而怡然自適所得寸禄僅足代耕有薄田數高不以遺其子臨終嘆許本社為祀田蓋取白清遺子孫之意邑人重其義香火不絕至今猶存焉</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Quých đọc sách Luận-Ngữ có những tiếng Tri chi v. v... Ông liền muốn ngay mấy câu trong sách Mạnh-Tử</t>
+          <t>rồi sau ông cũng làm đến chức Thị-lạng bộ Hình, thế mà bồng lộc cũng chỉ tạm đủ chứ không dư dật, ruộng nương cũng chỉ có được 3 sao, ông cũng chẳng chia cho con, đem cùng cho xã để làm tự điển, tỏ ý chỉ để hai chữ thanh bạch lại cho con cháu mà thôi. Vì thế nhân dân trong xã thấy đều tôn kính, lập đến phung sự hương khói ngát mãi đến nay.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HVB_003_0638</t>
+          <t>HVB_003_0138</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>禮重公客旅中有撲逃本社諸先靈詩集寄歸時有葉人鄭洪震見公</t>
+          <t>火保陳瑋記</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cư quan bất cải cựu thanh bản Phiến minh hựu trọng Yên-dài dự</t>
+          <t>THỂ ĐÁO THỦ, PHONG HIẾN NHIỆP HÀO CƯỜNG TRẦN-THƯƠNG.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HVB_003_0639</t>
+          <t>HVB_003_0139</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>紫閣僕長郎八門受業癸未科中進士第除廣東知縣陞燕京重事以念</t>
+          <t>陳佛璋慕澤人也弘禎檢中興後甲長科中進士為人廉直初為乂安憲察侯時本處有國舅舅恃勢驕橫無所畏避徑徑肆行不法人奏是之其訴章堆積每有公事到輒行欺侮他官亦無知之何自公到者任他尙黠愈滋訟牒交至耶同世間清善拿回杳尋機殺之他黨聞知遂至公家圍過意欲報仇公急下漁舟倍道而去</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Nội-hành-Khiển Hữu-Ty Lang-Trung, sau lại đổi sang Tả- Ty, rồi lại thăng chức Bộc-Xạ, trong đời văn-chương, ông</t>
+          <t>Ông Thường người làng Hoạch - Trạch dỗ Tấn - sĩ khoa giáp-thin thời Lê-Kính-Tông 1600-1619 (niên-hiệu Hoàng-Định.) Ông vốn có tính liêm trục, khi làm Hiến-Sát-Sư Tỉnh Nghệ-An, trong xứ có vị Quốc-cữu ỷ thế làm can chẳng kiêng nề gi pháp luật, nhân dân bị khổ làm đơn kêu quan kẻ đến hàng tập, quan có mời đến cửa công phân xử thì ông Quốc-cữu quát tháo om xóm, Quan cũng phải nhận. Ngày nay ông vừa đảo nhậm, đã nhận được rất nhiều đơn, ông bèn thira dip bắt về công đường tra tấn đến phải bỏ mạng. Bọn gia nhân của Quốc-cữu nghe được tin này bèn kéo nhau đến vậy kín tư thất định bắt ông phải đến mạng. Ông với thoát xuống một chiếc xưởng đánh cá chạy về kinh sư,</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HVB_003_0640</t>
+          <t>HVB_003_0140</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>其師淹晉不返即具本奏聞明帝始原之因召至京慰問二月遣還洪震</t>
+          <t>既至京師即自詣政堂免冠頓首謝曰臣誠忝意司為朝守法而國舅杭弄雖行臣一時憤激不覺已過手了今伏闕待罪斧鑕是甘錦上訊問之有知其事乃獎諭曰設官以爲民風憲祛除民害可謂稱職何罪之有公拜謝而長再歸任所自是豪彊畏服境南然後奉北使仕至吏部左待郎贈少保知都公</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>chí phục thù, đến lúc Minh-đế sai Trương-Phụ đem</t>
+          <t>bỏ mũ xuống sàn chính đường khấu đầu tạ tội: Thân nay làm giữ chức vị Hiến-ty phải vi Triều-dinh thi hành pháp luật, thế mà Quốc-cữu lại dám ngang tàng khinh thường quốc pháp, vì thế trong lúc quá giận thân đã lỡ tay, vậy xin về nơi của quyết chịu tội dưới lưỡi riu búa thân cũng cam tâm! Hoàng-Thượng thấy ông tâu trình như vậy, lập tức tra hỏi nguyên do, về sau biết rõ công việc thì lại khen ngợi và dụ cho ông biết rằng: Triều đình đặt ra quan chức là để vì dân, ngày nay Hiến ty trù được mới hai cho dân thế là xưng đáng với chức vụ chứ còn tội gì. Nghè lời dụ xong ông liền bài ta lui ra rồi lại trở về Ty cũ, từ đấy về sau cương hào trong hạt thấy đều kiệp sợ, chẳng dám ho he, nhân dân nhờ được an cư lạc nghiệp, rồi cách ít lâu thì ông phượng mang sang sứ Bắc - quốc, rồi làm đến chức Tả Thị-lạng, lúc về hưu lại được tặng chức Thiếu-phó tước Hương-Quân-công.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HVB_003_0641</t>
+          <t>HVB_003_0141</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>即設愛買斂並綵銀致饒公出侯凡十八年其家黃橋福之言始鑿金為足</t>
+          <t>狀元莫擬之記</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>binh sang đánh nhà Hỏ, đại binh đóng ở Bắc ngạn sông Phú-lương , họ Hỏ bắt hết nam phụ lão ấu trong</t>
+          <t>Mạc-Đinh-Chi, Lưỡng quốc Trang-Nguyễn, Trang-Nguyễn hai nước, (Việt-nam và Trung-quốc).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HVB_003_0642</t>
+          <t>HVB_003_0142</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>王是歸國陸吏部尚書蘇川侯後贈少保蘇郡公人獸武前身蓋相類者</t>
+          <t>陳朝為國欲元首大擬之字節文至靈龐洞人也史記旁河人李朝尚書莫令徵績之孫也李仁宗廣祐二年徵績中進補翰林學士</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>bèn từ Nam-sách lên lên Tam-đôi-Châu, hiệp lực với viên Thiềm-phán Đặng-Kinh đơn hàng Trương-Phụ đề</t>
+          <t>Mạc-Công-Đinh-Chi, tên tự là Tiết-Phu, người xã Lũng-Đông thuộc huyện Chi-Linh. Sử-ký chép người xã Bàng-Hà, nhưng xét thấy từ đây Đột- Lãnh trở xuống, tất cả một dài ven sông, theo bản đồ cũ đều thuộc về xã Bàng-Hà, cho nên ngày nay ngôi chúa của làng Lễ-Xá cũng thấy kêu tên là chúa Bàng-Hà, đó cũng là một chứng có vậy. Ngải vón là cháu quan Thượng-Thư Mạc-hiền-Tích Triệu Lý ngày trước. Quan Thượng-thu thì đồ Tấn-Sĩ đệ nhất danh khoa Bình-Dân thời Lý Trung-Tông, làm đến Thượng-Thư bộ Lại và được nhà vua bán cho bộ áo kim-ngư (cả vàng), em là Kiến-Quan cũng đồ Tấn-Sĩ làm đến Công-bộ Thượng-Thư, còn ông Trang đây là cháu cụ Hiền-Tích, tên tục gọi là Sách-Tú, (vì xã Lũng- Đông quen gọi là Kẻ-Sách, cho nên mới có tục danh như thế).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HVB_003_0643</t>
+          <t>HVB_003_0143</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>尚書張孚記</t>
+          <t>世傳鄉有大陵阜林木鬱茂沐猴居之其母常往刈薪為雄猴所脅歸諸其父父遂服婦人衣懷刀往焉猴狙故態以又遂提刀擊斬殺且長從視之見土虫已將假冤墳成一堆艾異之母尊受胎暮年生公資相卑陋人以為假精之聽其父臨終遺言百塗猴墳之上至亦默會天機也其後公沒附葬其下今猶存焉</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Trương-Phụ bèn dùng</t>
+          <t>Nay cứ theo như tục truyền, thì nơi làng Ngải có một cái gò rất lớn, cây cối um tùm, tức là chỗ ở của loài khí độc. Một hôm, thân mẫu của Ngài lên đó kiếm cùi, bị con khí độc hãm hiếp, trở về thuật lại với ông (tức thân phụ Ngài), ông bèn cải trang dân bà, trong mình dẫu con dao nhọn, rồi cũng giả vờ lên núi hải cùi. Khí dục lại quen thói cũ nhảy ra, liền bị ông dâm cho một mũi dao chết ngay tại chỗ, rồi ông quay về. Sáng sớm hôm sau, ông ra coi thử thì thấy xác con khí độc đã bị mồi dùn thành một cái mò rất lớn. Ông rất lấy làm kỳ. Về phần mẫu thân, sau khi bị khí hãm hiếp chẳng ngò bà thụ thai, đủ ngày tháng sinh ra một cậu con trai, người thấp lè tè, tướng mạo trong rất xấu xí, ai cũng bảo là giống khí. Vi thế, đến lúc phụ thân sắp sửa làm chung, Cụ có di chức lại rằng: phải tàng Cụ lên trên mò con khí đó, chắc rằng Cụ cũng hiểu ngầm thiên cơ nên mới hẹn như vậy. (Rồi sau Tràng Mạc-Định-Chi, lúc mất, cũng tàng ở phía dưới chân, ngày nay vẫn còn đủ cả).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HVB_003_0644</t>
+          <t>HVB_003_0144</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>青沔金壤断慶帝年號乙酉科中黃甲公性頗剛直統元</t>
+          <t>公生而穎異資稟過人年既冠登陳英宗甲辰科中狀元上以公資質贊卑陋不欲與狀元公乃作五井蓮華賦以自祝蓋謂蓮花井中雖卑而可貴上覽之而悟遠置上第歷任各職</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bình Binh-Giao Nam-Lục của Khâu-văn-Tráng</t>
+          <t>Nói về Tràng Mạc-định-Chi, diện mạo tuy xấu nhưng rất thông minh, gặp lúc Hoàng-tử Chiêu-Quốc-Công mở rộng học đường để dạy sĩ tử, ông xin vào học, đến khi tuổi gần hai chục, thì đồ Tràng-nguyên vào khoa Giáp- Thìn đời Trần-Anh-Tông (1.304); tất cả Thái-học-sinh nội thư-gia được về đối sách, thì ông đồ đầu, chỉ vì nhà vua thấy ông tướng mạo thơ lỗ nên không muốn cho đồ Tràng. Vi thế ông mới soạn ra bài phu Ngọc-Tỉnh-Liên, để vì với mình, đại ý nói rằng: sen ở trong giếng, tuy rằng sinh ở chổ thấp nhưng nó vốn là quí vật. Nhà vua xem qua bài phu hiệu rõ thâm ý của ông, nên lại cắt lên dỡ đầu... Thi đỗ xong, ông bắt đầu xuất chính, lần lượt qua mấy chức vị,</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HVB_003_0645</t>
+          <t>HVB_003_0145</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>末莫登庸欲篡位時公為吏部尚書百官以其故臣使作禮詔公張目</t>
+          <t>往北使與北人限日至交關阻風雨失期為北人所拒公婉辭致請北人寫對句自開上板揭有曰到關邏陽陽開願過客過關</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>phong cho quan trước, Toại làm Tham-chánh, Dịch làm Chi-huy-Sứ, Viễn làm Diệm-Thiết-Sứ, về sau vua Lê Thái-</t>
+          <t>rồi phượng mang sang sứ nhà Nguyễn. Trước khi đăng trình, đã hẹn đúng ngày sẽ tới cửa ải, vì mưa gió thành sai hẹn, bị người coi giữ cửa ải chặn lại, ông phải hết sức bày tỏ duyên có, viên ấy mới thuận, nhưng bắt buộc phải đối ngay một câu thi mới mở cửa cho vào. Yế đối ấy tự trên cửa ải ném xuống như sau:. Quá quan tri, quan quan bế, nguyên quá khách quá quan.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HVB_003_0646</t>
+          <t>HVB_003_0146</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>叱之曰此何義也終不脹屈改命願公泰為之後公歸田里適間中館</t>
+          <t>公立對云出對易對對難願光生光對北人服其敏開開賜進至北朝元人以卑小陋之一日宰相召八府與坐有薄帳綿黃雀在竹枝上公以為生雀都就摘之元人笑其鄙陋公遂裂之眾人驚怪公應曰我聞古有梅雀畫未開竹雀畫夫竹君子也雀小人也寫相續此是以小人加諸君子之士上恐小人道長君子道消故為聖朝除之耳眾服其能</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Nghi-Dương rồi sanh ra nguy Thái-Tổ là Mạc- đăng-Dong , tức là cháu 7 đời của Trạng-nguyên</t>
+          <t>Ông liên đối lại rằng: Xuất đối di, đối đối nan, thính Tiên-sinh tiên đối. Nghĩa về trên: Tới quan chật, cửa quan đồng, mới quá khách qua cửa khác. Nghĩa về dưới: Ra đối dễ, đối lại khó, xin Tiên-sinh đối trước cho. Viên coi giữ cửa ải thấy ông ứng khẩu đối ngay, rất phục là nhanh, bèn sai mở rộng cửa ải đón tiếp sứ bộ.. Sang qua cửa ải Nam-Quan, ông cùng sứ bộ tiếp tục lên đường, khi tới Bắc-kinh triều thần nhà Nguyễn thấy ông thấp bé có ý kinh thường. Một hôm Tề-Tướng cho mọi vào phủ, giữa lúc đương ngồi nói chuyện, ông thấy trên bức trường gấm có thêu một con chim trước sắc vàng, đậu trên cành trúc, trông hết như con chim thực, ông tiến lại gần gior tay toan bất, các quan nhà Nguyễn cả cười, chè là ngơ ngẩn. Ông bên xe nát con chim ấy ra, khiến cho mọi người kinh ngạc, hỏi có tại sao. Ông ung dung đáp: Tôi thấy cờ nhân chỉ về Mai-Tước, chứ chưa thấy về Trúc-Tước bao giờ. Có sao bức trưởng của quan Tề-Tướng ngày nay lại thêu cái hình Trúc-Tước. (Trúc-Tước, Mai-Tước). Ôi! Trúc là bản sắc của người quân-tử! Tước là hình dáng của kẻ tiêu-nhân. Ngày nay Tề-Tướng cho thêu như vậy, thì tiêu-nhân lại dẻ lên trên quân-tử? Tôi sợ đạo của tiêu nhân lớn, thì đạo quân-tử sẽ tiêu, nên tôi phải vi Thành-đế trù khứ đi ngay. Câu giải thích đó làm cho ai cũng khiếp phục về tài hùng biện hơn đời.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HVB_003_0647</t>
+          <t>HVB_003_0147</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>問野服乘涼與常人無異時則令偶經伊處人皆起立公獨靜坐矣之</t>
+          <t>及進朝適外國進殤元帝命公與高麗使賛之高麗使先就其詞曰韞隆蟲蟲伊母周公涼雨淒淒伯夷叔齊</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ông gặp Nàng 7 dẫm xuống âm ty, câu truyện kẻ cũng hoang đường, nhưng theo lời các bậc tiên bói kẻ lại, thì</t>
+          <t>Lúc ấy lại có người ở ngoại quốc đem quạt vào dâng, Nguyên-đế bèn sai ông cùng Sứ-thần Cao-Ly mỗi người phải làm ngay một bài tán. Sứ Cao-Ly làm xong trước, có những câu rằng: Uân long trùng trùng. Y-Doãn Chu-Công; Vũ tuyêt thê thê, Bá-Di Thức-Tề. Nghĩa là: Khí nóng bùng bùng, Y-Doãn Chu-Công; Mưa tuyêt đầm dia, Bá-Di Thức-Tề. Ý nói mùa hạ nóng nực, thì cái quạt đắc dụng như hai ông Y-Doãn Chu-Công. Đến mùa đông giá rét thì cái quạt bị chết là như hai ông Bá-Di Thức-Tề.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HVB_003_0648</t>
+          <t>HVB_003_0148</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>從者叱曰何人無禮將欲攻之縣令望見公駿須之異急止從者曰吾觀此</t>
+          <t>公未哀體制望其他筆管遂因而推演之曰流金爍石天地為爐汝於斯時兮伊周臣儒北風其涼雨雪載途汝癸斯時兮夷齊戮夫隱用之則行舍之則藏惟我共爾有是夫既成竝進天子眷懷伊司嘆賞不已封兩國狀元</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cách mấy năm sau, vua Võ-vương kéo quân Chư- hầu vào đánh vua Trụ , hai ông đón đường giữ lấy</t>
+          <t>Giữa lúc ấy thì ông chưa nghĩ xong, nhưng khi liếc sang đầu quân bút của sứ Cao-Ly, ông đã biết rõ những câu như thế, ông bèn nhân cái ý đó để suy diễn thêm một bài rằng: Phiên âm: Luru kim thược thạch, thiên địa vi lò! Nhĩ ư tư thi hề, Y-Chu cự nho. Bắc phong kỳ lương, vũ tuyệt tái đồ, nhĩ ư tư thi hề, Di Tề nga phu. Y: dụng chi tắc hành, xả chi tắc tàng, duy ngã dữ nhĩ hữu thị phu? Nghĩa là: Nấu vàng nung đá, trời đất như lò, thì người lúc ấy khác gi Y-Chu nói tiếng bắc cự nho. Gió lạnh buốt xương, mưa tuyệt đầy đường! thì người lúc ấy cũng như Di Tề nhìn dồi trên núi Thu-Dương. Ôi! Dùng thì ra giúp đời, bỏ thì tạm ẩn để chờ thời, chỉ ta với người có thể ôi. Viết xong bài trên ông tiến trình lên, Thiên-Tử nhà Nguyên coi xong chợ là hay, cảm bút khuyên vào câu có chữ Y và phê 4 chữ Lưỡng-Quốc Trạng-Nguyên. Thế là bài tán đề quạt của ông dẫu rằng thoát ý và làm xong sau, nhưng mà lại được Thiên-Tử nhà Nguyên thường thức hơn bài của Sư Cao-Ly đã làm xong trước vậy.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HVB_003_0649</t>
+          <t>HVB_003_0149</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>鬚美且認其體構必有識字試出對句若或不成打之未晚即出對</t>
+          <t>其在北國與北人遇于途公乘驢觸其馬北人誦之曰觸我騎馬東夷之人也西夷之人也公應之曰遇予乘驢南方之彊戰北方之彊歟</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>cương ngựa can rằng: Con mà giết cha có đáng hay không? Bê tôi giết vua có phải đạo không?</t>
+          <t>Trong thời gian còn ở Bắc.kinh, một hôm, ông cởi lừa đi đạo phố, chẳng may con lừa của ông xó vào con ngựa của quan nhà Nguyễn. Vị quan ấy bên đọc mấy câu như sau:?? Xúc ngã ky mã, đồng di chi nhân dã? Tây di chi nhân dã? Nghĩa là: Xó vào ngựa ta? hỏi người ở Mán đồng đó hay người ở Mán tây đó? Ngài ứng khẩu đối:?? Át dư thừa lư, Nam phương chi cương du? Bắc phương chi cương du? Nghĩa là: Ngáng đầu lừa của ta, hỏi phương Nam mạnh du, hay phương Bắc mạnh du?</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HVB_003_0650</t>
+          <t>HVB_003_0150</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>六知縣青沔見无礼而欲攻公郎應之曰進士金燭幸有珍餚而得晚賂</t>
+          <t>又常共北人對答北人出對曰杞已木梧否木知何以就為稽公對曰僧曾人佛弟子人何如以僧奉佛</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nhưng vua Võ không nghe, cứ diệt vua Trụ để cướp lấy ngôi thiên-từ, dựng nên cơ nghiệp nhà Chu, vì thế</t>
+          <t>Lại có một hôm ông cùng các vị thân sĩ nhà Nguyễn bàn luận văn chương, vì muốn thử tài, họ thay phiên nhau để ra câu đối, câu thứ I là: Kỷ dĩ mộc, Bồi bất mộc, như hà dĩ kỷ vi bồi? Câu này thuộc lối chấp chữ: như chữ kỷ thì hợp 2 chữ: dĩ và mộc. Chữ Bồi thì hợp 2 chữ: bất và mộc, có sao lại dùng gố kỹ làm chén rượu, và họ ám chỉ ông cũng lùn như người nước Kỷ, có sao lại được trọng dụng? Ông đối rằng:,, Tăng tăng nhân, Phật phát nhân, vân hồ dĩ tăng sự phật. Nghĩa là: chữ Tăng thì hợp chữ Tăng với chữ nhân, chữ phật thì hợp chữ phát (là chẳng phải) với chữ nhân, có ý bảo các chú người Mông-Cổ con cháu nhà phật. Nhưng phật chẳng phải là người, nhẽ đâu lại bắt Tăng (tức chúng tôi) thờ phật.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>HVB_003_0651</t>
+          <t>HVB_003_0151</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>令始知其公即連遜趨拜自言途由錯誤過咎是耳幸大人見恕公</t>
+          <t>安者安以來為家公對曰因與人他王成國北人批云後世子孫當有王者但單字享國不長</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>kết mà Tiễn-sinh lại mượn lời của đức Không-Từ để tỏ đức độ của mình, thì quả là cao kiến hơn bài của Sư Cao-</t>
+          <t>Câu thứ II là:. An khứ nữ, dĩ thi vi gia. Nghĩa là: chử An bồ chử nữ thay chử Thi là heo vào, thành chử gia là nhà. Ông đối lại:. Tự xuất nhân, nhập vương thành quốc. Nghĩa là: chử Tự bồ chử nhân ra, cho chử Vương là vua vào, thành chử quốc là nước. Họ chịu phục câu đối này là tài, nhưng lại phê vào rằng: Con cháu sau này tất nhiên có đời làm vua. Chi hiềm chử quốc viết đơn, thì giữ nước cũng chẳng được lâu dài, (chử quốc viết kép viết đơn như ở trên).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>HVB_003_0652</t>
+          <t>HVB_003_0152</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>笑而釋之公前不附偽莫後辭歸不仕蓋在節義之列云</t>
+          <t>北人尚對曰日火雲煙白旦燒殘玉魄公對曰月弓星彈黃育射落金烏北人批云後世子孫必有慕人國</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>thiên Ly-Lâu hạ , thầy Mạnh nói rằng : Vua Thuấn sinh ở đất Chư-phùng là người</t>
+          <t>Câu thứ III:,. Nhật hỏa vàn yên, bạch trù thiếu tân ngọc thô. Nghĩa là: mặt trời là lừa, đàm mây là khói, tảng sáng đốt tan thô ngọc. Ông đối lại:,. Nguyệt cung tinh dạn, hoàng hôn xạ lạc kim ô. Nghĩa là: vành trăng là cung, sao là dạn, bóng hoàng hôn bắn rụng ác vàng. Câu này họ lại phê rằng: Đời sau con cháu tất nhiên có người cướp nước.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HVB_003_0653</t>
+          <t>HVB_003_0153</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>大興候記</t>
+          <t>北人尙對云魑魅魍魎四十四鬼蓋陋其卑小也公對曰髮鬢琵琶八大王北人北北云後世必為血食之神</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Đạo giáo gọi</t>
+          <t>Câu thứ IV:. Ly My Vọng Lạng từ tiêu quỉ. Nghĩa là: 4 con quỉ nhỏ trên đều có chử quỉ một bên. Ông đối lại:. Cầm sắt Tỳ-bà bát đại vương. Nghĩa là: 4 cây đàn trên đều có 8 chử vương. Câu này họ phê rằng: Về sau sẽ được làm phúc thần.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HVB_003_0654</t>
+          <t>HVB_003_0154</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>院世儀當泰澤社一下村人中官蒞國公世恩之第附焉賜之叔也為人焉</t>
+          <t>北人對云鳥呼枝頭談嘗論知為知爭知為不知是知蓋以默音譏南人也公以類蛙聲應之曰蛙鳴池上讀鄒書樂獨樂樂共飛樂樂亂樂</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>là núi Thiên-Trụ thuộc tỉnh Thiềm-Tây , khi Chu Thái-Vương trấn nại Di-Địch đem dân sang</t>
+          <t>Câu thứ V:. Quách tại tường đầu dâm lỗ luận: Tri chi vi tri chi, bất tri vi bất tri, thị tri. Nghĩa là: Con chim quách đậu ở đầu tường, nó học đòi nói những câu sách Luận-ngữ: Biết thì bảo là biết, không biết bảo là không biết, ấy là biết. (để ngụ ý chê ông cũng như con chim học nói). Ông liền mượn ngay mấy câu trong sách Mạnh-Tử cũng có những tiếng đối lại rằng:. Oa cư trì để độc Trâu thư: Nhạc dữ thiểu lạc nhạc, nhạc dữ chúng lạc nhạc thực lạc. Nghĩa là: Con ếch ngồi đáy giếng đọc sách của ông Mạnh-Đức (Trâu thư): Vui với người ít cũng vui, vui với người nhiều lại càng vui thực. (lấy tiếng ộp oạp của ếch để đối với tiếng lích chích của quách, thành ra âm thanh đối với âm thanh).</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HVB_003_0655</t>
+          <t>HVB_003_0155</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>浪不循禮度而高尚志氣少善盈文尤長於文體十五歲頴鄉舉</t>
+          <t>北人吾對云洛水神邕單應兆天效五地效五也五十五效效威混三大道道合元始天尊一誠有感公對曰峻山靈鳳兩星神雄聲六雌聲十六聲徽九章大天生嘉靖皇帝萬壽節無疆其對答出只成章無少為者</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tĩnh là yên tĩnh, chứ không phải năm Gia-</t>
+          <t>Câu thứ VI:,,,,,,. Lạc thủy thần qui đơn ứng triệu, thiên số cửu, địa số cửu, cửu cửu bát thập nhất số, số số hỗn thành tam đại đạo, đạo hợp nguyên thủy thiên tôn nhất thành hữu cảm. Nghĩa là: Thần qui ở sông Lạc hiện ra điểm tốt, số trời là 9, số đất là 9, 9 lần 9 là 81 số, số số hỗn thành 3 đạo lớn, đạo hợp với đức Nguyên-thủy Thiên-tôn do một tấm lòng thành cảm ứng. Đối lại rằng:,,,,,,. Kỳ-Sơn minh phượng lưỡng trình tường, hùng thanh lục, thư thanh lục, lục lục tam thập lục thanh, thanh thanh hưởng triệt cửu trùng thiên, thiên sinh gia tĩnh Hoàng-đế vạn thọ vô cương. Nghĩa là: Chim phượng hót ở núi Kỳ-Sơn hiện hai điểm tốt, tiếng chim đực là 6, tiếng chim cái là 6, 6 lần 6 là 36 tiếng, tiếng tiếng vang suốt chín từng trời, trời sinh vua Gia-tĩnh muôn tuổi khôn cùng. Trải qua bao câu đối đáp, Thân Sĩ triều Nguyên biết rằng không thể áp đảo được ông,</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>HVB_003_0656</t>
+          <t>HVB_003_0156</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>特同科諸貢士拜試場官皆用烏紗帽青吉衣公獨著紅色衣烏尾</t>
+          <t>又北朝后妃薨臨簽命公讀祝就讀但見空紙紙上有遺一字公即哭而讀之其词曰天上一朶雲空中一點雲子閾苑一枝花廣寒一片月噫雲散雪消花殘月缺北人大談焉異嘆服其文</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>con hổ lớn, sắc vàng, đầu trắng, sừng sọc nhảy vào, trên lưng có công một người đem quảng vào giữa đồng xương</t>
+          <t>rồi sau mấy bữa, nhân gặp tang lễ bà Hậu phi, họ bèn tâu với vua nhà Nguyên cử ông vào đọc văn tế. Khi vào quỳ trước linh-vị, nghe tiếng xướng xong, mở tờ chúc văn ra đọc, chỉ thấy có 4 chữ nhất là một. Ông biết họ chực thử mình, nhưng văn trình trong đọc ngay lên rằng: Thanh-thiên nhất đóa vân, hồng-lò nhất điểm tuyết; Thượng-uyển nhất chi hoa, Quảng-hàn nhất phiên nguyệt. Y! Vân tán tuyêt tiêu, hoa tàn nguyệt khuyet. Dịch nghĩa: Trời xanh 1 đám mây, Lò hồng 1 điểm tuyệt; Thượng-uyên một cảnh họa, Cung quảng một vùng nguyệt. Ơi! Mây tân tuyệt tiêu, hoa tân, giăng khuyết. (Bốn câu trên đều có 4 chữ nhất là một). Đọc xong bài văn tế trên, tất cả vua tôi nhà Nguyễn đều phục là bức thiên tài! (bài văn ấy vẫn còn ghi trong bắc-sử, thế mà về sau lại có người bảo: bài ấy là của Lý-Bạch, nhưng ta xét kỹ về lời và ý, thì thấy giống như văn thể của ông. Tuy thế chưa chắc đã phải, bởi vì bài thơ đề quạt dịch là của ông. Thế mà trong sách Thuyết-Linh lại chép là của Phương-hiệu-Nho, lấy đó suy ra, thì sử sách bên Tàu chép về việc ấy chắc gì đã dùng vậy).</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HVB_003_0657</t>
+          <t>HVB_003_0157</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>暢場官怖乃兄勢熖仍免覆問平日共奠登庸相有交善統元間</t>
+          <t>公在北朝北人大奇其才而察相貌無可責者乃直公出則潛往視之見便薺分方謂公有隱相所貴在此分還北人往我國認其墳塋稱公乃禀生之地但水不亭留故不富耳</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>khác gì treo một sợi tóc, biết tình sao đây? Ngờ đâu giữa lúc nguy nan như thế thì chú bỗng nhó</t>
+          <t>Nhắc lại trong khi ông ở bắc-triều thì người nhà Nguyễn thấy có kỳ tài, nhưng xét tướng mạo không thấy có gì đáng quí. Họ bèn đợi lúc ông đi sau xong trở vào, họ mới lên ra quan sát thấy những hòn phân, vuông như quan cơ, bấy giờ họ mới bảo nhau: đó là ẩn tướng rất quí. Nhưng rồi sau khi công việc xuất sứ hoàn hảo, ông trở về nước, họ còn phải thấy địa-lý theo sang để xem phong thủy đều ta, nhân tiện ông có dẫn họ xem lại phần mộ tò tiên, ngôi nào họ cũng lắc đầu bảo rằng không được, sau cùng dẫn đến ngôi mộ phụ thân, thì họ tấm tắc khen ngôi bảo rằng: đây mới chính là ngôi mộ phát tích. Nay ta xét lại hình thế, thì ngôi mộ ấy quả nhiên đẹp thực, đầu đến các thầy địa-lý tầm thường cũng biết là qui cách. (cục này chép kỹ ở sách địa-lý ông Hòa-Thúc). Hiểm rằng thủy không tu mấy, nên chỉ phát quí mà thôi, chứ không phát phú.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>HVB_003_0658</t>
+          <t>HVB_003_0158</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>也音托不檢束也。</t>
+          <t>公為官廉潔薄於自奉故其慶番後人于各覩員外郎孫各迪各遂各遠皆有執力共列顯貴其後吳平亦不父難莫遂子孫綏濟青河廣漢三世乂綏居宜陽蘇古齋社生莫太祖登庸篆織而有天下實狀元五世孫也</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>cũng chẳng còn kể gì.</t>
+          <t>Xét thấy trong đời làm quan của ông rất trong sạch, về cách cư xử âm-thực cũng chỉ giữ mực thường thường, vua Trần Minh-Tông hiểu rõ tinh tinh của ông, nên có sai người đem 10 bó tiền, rinh lúc đêm khuya thanh vắng bỏ vào trong cửa, sáng sớm hôm sau, khi ông thức dậy không biết là tiền của ai, vội vàng vào triều tàu để vua biết. Vua phân rằng: Tiền không có chủ thì khanh cứ việc nhận lấy chứ có hề chi; đức tinh thanh liêm của ông đại đề là như thế đó. Cho nên về sau Văn-hiên tiên-sinh có làm bài thơ tứ tuyệt để ca ngợi rằng: Phiên âm Đệ nhất khôi nguyên tạo trí thân Cư quan bất cải cựu thanh bản Phiến minh hựu trọng Yên-dài dự Sử tiết phương tri quốc hữu nhân Dịch Chiếm giải khôi nguyên tự thiếu thời, Quan sang vẫn giữ nếp nghèo thời, Yên-kính đã trọng thơ để quạt, Cò Sứ nếu cao, nước có người. Nói về đức tánh thì trong lúc qui hiền, ông vẫn giữ được nếp thanh bần, nên mới dễ phước lại cho con cháu. Con trai như các ông Khẩn và Trực; cũng đều làm đến Viên-ngoại. Cháu là Dịch, Toại, Viễn,, đều có sức khỏe, gặp lúc nhà Hỏ cướp ngôi, nhân thấy cha ông ngày trước làm tới nhà Trần, nên vẫn ôm chí phục thù, đến lúc Minh-đế sai Trương-Phụ đem binh sang đánh nhà Hỏ, đại binh đóng ở Bắc ngạn sông Phú-lương, họ Hỏ bắt hết nam phụ lão ấu trong nước ra để cố thủ. Trương-Phụ không rõ hư thực ra sao, nên không dám vượt sang sông. Lúc ấy anh em ông Dịch nhận thấy có cơ báo thù, bèn từ Nam-sách lên lên Tam-đôi-Châu, hiệp lực với viên Thiềm-phán Đặng-Kinh đơn hàng Trương-Phụ đề báo-cáo tình-hình họ Hỏ. Vì thế quân Minh mới dám qua sông tiến đánh, luôn luôn thắng lợi. Trương-Phụ bèn dùng làm Hướng-đạo quan, rồi sau cùng với viên Hạ-hòa-mục là Võ-Thạch-Khanh, bắt được Hán-Thương và con là Nhưế ở núi Cao-Vọng. (việc còn ghi rõ trong Bình Binh-Giao Nam-Lục của Khâu-văn-Tráng biên soạn,). Vì có công lớn nên được nhà Minh phong cho quan trước, Toại làm Tham-chánh, Dịch làm Chi-huy-Sứ, Viễn làm Diệm-Thiết-Sứ, về sau vua Lê Thái-Tổ bình được Ngọ, các ông cũng không mắc nạn... Riêng về phần Toại sau khi mất rồi, con cháu di cư vào vùng Ma-Khê thuộc huyện Thanh-Hà,, đến đời thứ 3 lại đi về làng Cổ-Trai cổ xã thuộc huyện Nghi-Dương rồi sanh ra nguy Thái-Tổ là Mạc-đăng-Dong, tức là cháu 7 đời của Trạng-nguyên Mạc-định-Chi vậy.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>HVB_003_0659</t>
+          <t>HVB_003_0159</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>出居京城外長生寺不求療</t>
+          <t>樗眼鄭鐵長記</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>da mà cũng không hóa đi được. Hưởng chi ngày nay lão</t>
+          <t>ĐA NĂNG TẠI HẠ TRỊNH BẰNG-NHỜN</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>HVB_003_0660</t>
+          <t>HVB_003_0160</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>達一月莫簽庸迫至欲加以好官公辭不受願得一爵為各稱足矣</t>
+          <t>鄭鐵安矣東十里人也生而顴異少蓄與五六童子戲作大眾公以詡蝶為耳水蛭為鼻宛如真形適有府官經過而異之因出對云</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Lão đáp : Mổ đây vàng mệnh Thượng-Đế sai xuống, chẳng may một sơn sa cơ, tội đáng muốn chết.</t>
+          <t>TRỊNH THIẾT-TRƯỜNG người làng Đông-Lý thuộc huyện An-Định về người coi rất dĩnh ngọ, lúc còn thơ ấu chơi dưa với trẻ, cậu biết nặn con voi đất, rồi lấy bướm bướm làm tai, lấy dìa làm voi, hoạt động như con voi thực. Lúc ấy có ông quan phủ đi qua cũng lấy làm kỳ, nhân tiện có ra cho cậu một về đối rằng: Ngũ lục đồng vò như nhi xảo?</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HVB_003_0661</t>
+          <t>HVB_003_0161</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>因請以大興二字為號登庸許之即拜為大興侯任行高志儀嘗</t>
+          <t>童子五人六無知汝巧公曰敢問公是何官府官曰我是當今太守也</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DANH-THẦN Phụ danh-nho danh-thần Phụ chép thêm các bậc danh-nho, danh-thần</t>
+          <t>Cậu liền hỏi lại: Vậy Ngài là quan chức gì? Quan đáp: ta đây là dường kim Thái-thủ ăn lương 2000 thạch đó;</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HVB_003_0662</t>
+          <t>HVB_003_0162</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>浪吟一句云英雄埃乃剝剝帝境鉅剎大興庄輪題于登龍城大興門</t>
+          <t>公郎對云太守二千石莫若公府官曰欠一字省請賞府官曰汝對不發至何賞之有公曰太守二千石莫若公貪府官命賜綺錢公即改對曰莫大公若廉府官大奇之因喚公母至曰此子俊才當勉以學業必中魁元</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Quan Thượng-thu thì đồ Tấn- Sĩ đệ nhất danh khoa Bình-Dân thời Lý Trung-Tông, làm</t>
+          <t>nghe xong Cậu đối ngay rằng:. Nhị thiên thạch mạc nhược công: Quan hỏi sao còn thiếu một chữ cuối? Cậu thưa rằng xin quan thường tiên rồi con sẽ có đủ. Quan bảo my đối không chính còn thường nói gì. Cậu bèn thêm ngay chữ tham tức là mạc nhược công tham, thành ra câu đối như sau: Năm sáu bê con chi có mây khéo, hai ngàn thùng thóc quả thực ông tham. Quan phủ nghe xong bên thường cho một quan tiên thi cậu lập tức dời ngay chữ tham ra chữ liêm, Quan phủ càng lấy làm la! sai người đi gọi mẹ cậu đến bảo: Con bà là một đứa bé tuần tù thông minh! Bà nên có gắng cho cháu đi học sau này thế nào nó cũng chiếm bằng khôi nguyên đó.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HVB_003_0663</t>
+          <t>HVB_003_0163</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>左自謂己在其上而人皆出下之意歷歴莫大李尚存時莫氏荒怠政命</t>
+          <t>母依教遂勤以刻意讀書父長博學多能以文章名天下</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>cụ Hiền-Tích, tên tục gọi là Sách-Tú , (vì xã Lũng- Đông quen gọi là Kẻ-Sách, cho nên mới có tục danh</t>
+          <t>Bà mẹ thấy Quan bảo thế nên cũng tìm thấy cho cậu học hành, đến khi lớn lên học rộng lại nhiều tài năng, văn chương lừng lẫy khắp cả thiên hạ!</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HVB_003_0664</t>
+          <t>HVB_003_0164</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>著樂昌分鏡國語傳序陳隋奢欲事寫意諷論他亦不之悟也又嘗</t>
+          <t>太寶篤志崇子虞科中進士使人來迎母赴京母不肯曰我從來望汝帶得魁元二字來明令都在人下任汝自為之我決不往</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>thấy ông tướng mạo thơ lỗ nên không muốn cho đồ Tràng. Vi thế ông mới soạn ra bài phu (1) Ngọc-Tỉnh-</t>
+          <t>rồi đến niên hiệu Đại-Bảo (1440-42 Lê-Thái-tông) khoa thi nhâm tuất ông dỡ Đồng Tấn-sĩ, sai người về đón thân mẫu ra kinh thành, bà không chịu đi, bảo rằng trước đây ta vẫn mong rằng nó sẽ đoạt lấy hai chữ Khôi-nguyên đem về. Chờ còn ngày nay lại phải ở dưới người khác, thì mặc y nó, ta đây còn ra làm chi?</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>HVB_003_0665</t>
+          <t>HVB_003_0165</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>有北侯至途經</t>
+          <t>其後與狀元青威且溪人同往北使公郎辭歸固學太和橘仁戊辰科再試遂中榜眼</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ông liên đối lại rằng: Xuất đối</t>
+          <t>Ông thấy mẹ già nói nhẫn như vậy lập tức từ giã kinh thành trở về học thêm, thế rồi đến khoa mẫu thin (1448) niên-hiệu Thái-Hòa, ông vào thi lại được trúng Bảng-Nhữn,</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HVB_003_0666</t>
+          <t>HVB_003_0166</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>南門聞門上題字係我國臣子各號輒停車不進要以架梯從上而行	.</t>
+          <t>其後與狀元青威且溪人同往北使適天朝有會試科命諸國陪臣與中國舉人一體應試公與阮直入試文漸至半篇乃私與阮直語曰今審舊得先篤時惟我與兄耳觀我文辭有起鳳騰蛟之勢未易與爭第思本朝間兄是狀元我是榜眼今以壓倒得兄則我國王必有選擇不精之吾兄意料如何</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sang qua cửa ải Nam-Quan, ông cùng sứ bộ tiếp tục lên đường, khi tới Bắc-kinh triều thần nhà Nguyễn thấy</t>
+          <t>rồi sau cùng với Trạng-Nguyên Nguyễn-Trực (người ở Bối-Khê thuộc huyện Thanh-Oai) đỗ trạng năm nhâm-tuất, (1442) vang mệnh sang sứ Bắc-quốc, gặp lúc bên ấy mở khoa thi Hội, có lệnh cho các Sư thần cũng được vào thi với các Cử-nhan, Trung-quốc, hai ông cũng vào dự thi. Trong khi làm được nửa bài, ông bèn nói nhỏ với Nguyễn-công rằng: Cử chỗ tôi biết, phen này đoạt được giải nhất thì chỉ có tôi và quan bác đó thôi, nhưng văn từ của tôi có về rồng bay phương mùa, khó lòng có ai địch nổi. Tôi tự nghĩ rằng: khi ở nước nhà bác là Tràng-Nguyên Tôi đây chỉ là Băng - Nhơn, vì bẳng ngày nay tôi lại ở trên quan Bắc, thì chẳng hóa ra Quốc-Vương tuyển lựa không tinh! vậy Bác định liệu thế nào xin cho đệ biết?</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>HVB_003_0667</t>
+          <t>HVB_003_0167</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>時尚書武惟斬為援伴官伴應以知命部下生一計陰取送象來從</t>
+          <t>阮直曰仕公規之既有遜讓之誠乞減其力俾我復欲元公復次檮眼可也</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Nghĩa là : Khí nóng bùng bùng, Y-Doãn Chu-Công ; Mưa tuyêt đầm dia, Bá-Di Thức-Tề.</t>
+          <t>Nguyễn công đáp: Việc ấy tùy anh định đoạt. Vi thì anh có thành tâm nhượng lại, thì anh nên giảm bớt sức văn, để cho Ta vẫn giữ được Tràng-Nguyên, còn Anh vẫn giữ Băng-Nhơn là được.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HVB_003_0668</t>
+          <t>HVB_003_0168</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>後痛刺槪大吼衝突北人叱了一驚郎撓愕走過自知墜于計中不勝</t>
+          <t>鄭公首肯既而行文有南之舟北之馬之句都塗馬字改寫予外馬有四點只見三點盡有司衡文鄭公宣猷充院道宣場眼但見鄭公寫自一字以北為為三足是蹤焉也似有輕中國之意即點一次乃許阮君為兩國狀元鄭公為兩國榜眼並賜榮歸本國使回日頒賜錦袍金笏兩袖廝馬儀用榮觀命防直前道簽程鄭公競自馬字其所頒廝馬仍簽一尺任使上轄簽程否則責留中國</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Nhĩ ư tư thi hề, Y-Chu cự nho. Bắc phong kỳ lương, vũ tuyệt tái đồ, nhĩ ư tư thi hề,</t>
+          <t>Trịnh công thấy Trạng đã vui lòng nhận lời, ông bèn trở lại chỗ ngồi đem quyền ra viết, khi viết đến câu: Nam chi chu bắc chi mã, nghĩa là phương nam giới nghề bơi thuyền phương bắc giới nghề côi ngựa, ông bèn xóa nhoe chữ mã rồi viết chữ khác một bên, chữ ấy lại chỉ chấm có 3 nét. Đến khi chấm bài Quan trưởng xét thấy văn của Trịnh công đáng dỡ Trạng-Nguyên còn văn của Nguyễn công thì đáng Băng-Nhơn, nhưng vì chữ mã trong bài Trịnh công thiếu mất một nét chấm tức là ngựa có 3 chân, khác chi ngựa què, có ý coi thường Bắc - quốc nên bị truất xuống một bực, rồi cho Nguyễn công được làm Lưỡng quốc Tràng-Nguyên Trịnh công thì làm Lưỡng quốc Băng-Nhơn! đều ban áo mũ vinh quí. Thế rồi đến hôm ra về, Vua Tàu lại còn ban thêm bào gấm hốt vàng và ngựa thiên lý, để cho tăng phần vinh diệu, và lại xuống lệnh cho Nguyễn công phải đăng trình trước, còn phần Trịnh công vì có chữ mã 3 châu, nên con ngựa ban cũng bị treo lên 1 cảng, buộc phải lên yên cởi về, nếu không cởi được thì phải ở lại thượng quốc.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HVB_003_0669</t>
+          <t>HVB_003_0169</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>慙憤至今猶傳其事云</t>
+          <t>公即生下一計急命行人造一片木狀如馬足毒加以鐵索穿一下用異條經之擇起蹶足仍痛加鞭打這馬三足奔馳一足與之相依賴以不墜</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>An khứ nữ, dĩ thi</t>
+          <t>Tiếp được mệnh trên và thấy cơ sự như vậy, Trịnh công bèn nghĩ ngay một kế, sai người theo hầu chế tạo ngay một cái chân ngựa gỗ, ruồn dây thép vào rồi buộc chằng lên chỗ chân bị treo bằng sợi dây đen, đợi khi ông ngồi lên yên đang hoàng, rồi mới dùng roi vứt mạnh một cái, tức thì ngựa chạy như bay! Vì có chân nọ giữa vào chân kia nên không bị ngã.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HVB_003_0670</t>
+          <t>HVB_003_0170</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>扶擁節婦記</t>
+          <t>繞過一里許、天朝志務其有應命又機思客即命解其索定乃與阮公依次而行</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cầm sắt Tỷ bà bát đại vương.</t>
+          <t>Rồi sau cứ thế đi được đến hơn một dặm, thiên triều thấy vậy khen ông có tài làm cơ ứng biến! lập tức hạ lệnh cho cởi chiếc chân treo, để cùng đi với Trạng-Nguyên một thề.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HVB_003_0671</t>
+          <t>HVB_003_0171</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>上洪唐安有范氏各援者自少通穎尙間頗有姿色既加笄即歸于唐	.</t>
+          <t>歸國後防公仕至尚書鄭公亦仕至尚書封濟國禽渾北朝題載南文獻之邦緯莫公疑之之後二公其次也為公克寬亦踵其後壘</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Kỷ-Sơn minh phương lưỡng trình trường, hùng</t>
+          <t>Rồi khi về nước hai ông làm đến chức Thượng-thư rồi mới chỉ sĩ, Trịnh công được phong là Nghi-Quốc-Công tiếng tăm lừng lẫy cả bên Bắc-Quốc! làm thêm rang về vấn hiến nước nhà! như vậy thì sau Mạc-Đinh-Chi ta thấy chỉ có hai ông, mà người kế tiếp được hai ông thì có Phùng Khắc-Khoan tức là Trạng Phùng vậy.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HVB_003_0672</t>
+          <t>HVB_003_0172</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>豪令族之家生下男女四人值北兵南侵夫以病死婦撫幼育孤以不一</t>
+          <t>黃田武瓊記</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>thanh lục, thư thanh lục, lục lục tam thập lục thanh, thanh thanh hưởng triệt cừu trung thiên, thiên sinh gia tinh</t>
+          <t>DANH NHO VÕ - QUỲNH.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HVB_003_0673</t>
+          <t>HVB_003_0173</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>庭不雨醮自誓言其悲酸情狀缺石心腸非言語形容所莊盡將當</t>
+          <t>武瓊唐安慕澤人也洪德縣聖宗戊戌科由三黃甲公博學好古為世導師在長於模迹嘗業曰大官都總裁有大越通鹽通考迹自洪厽氏至十二侯君以前為外紀自丁天皇至朝繙太祖大受初年為本紀异譯錄歷代紀年九十二卷行于世</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Phiên âm : Thanh-thiên nhất đóa văn, hồng-lò nhất điểm tuyêt ; Thượng-uyên nhất chi hoa, Quảng-hàn nhất</t>
+          <t>Ông vốn là người Mộ-Trạch thi đỗ Hoàng-Giáp khoa Mậu-tuất thời Lê Hồng-Đức (1478), là người học rộng có tánh hiểu cờ lại sở trường về soạn thuật, lúc làm quan thường được kiêm cả chức Sư-quán-Đô-Tông-tái, đã soạn ra các bộ Đại-Việt Thông-Giám, và Thông-Khảo, thuật lại từ đời Hồng-Bàng xuống đến đời Thập Nhị Sứ-quân, từ đây trở về trước gọi là Ngoại-kỷ, còn từ Đinh-tiên-Hoàng xuống đến Bồn Triều Lê Thái-Tổ đại định năm đầu, gọi là Bồn-kỷ, và lại biên kỷ những niên kỷ của từng Triều đại, hợp thành 26 quyển truyền bá cho đời.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HVB_003_0674</t>
+          <t>HVB_003_0174</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>兵火人罕自全城或饑寒失守為盜賊所污者或道路流亡苟來生</t>
+          <t>又嘗接蘋南摭卦集仕至兵部尚書時有賊至遇害其壻狀元黎鶴卿有祭文曰</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Dịch nghĩa : Trời xanh 1 đám mây, Lò hồng 1 điểm tuyệt; Thượng-uyên một cảnh họa, Cung quảng một vùng</t>
+          <t>Ngoài ra ông lại cùng với Trần-thế-Pháp soạn tập Lãnh-Nam-Chích Quái rồi sau làm đến Binh-bộ Thượng-thư, chẳng may gặp thời loạn lạc nên ông bị chết, con rể là Trạng-Nguyễn Lê-Đình có văn tế rằng;</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HVB_003_0675</t>
+          <t>HVB_003_0175</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>浩而婦周旋其間以死自誓言變容斂色不為隱暴所侵一方之人皆</t>
+          <t>羅先生道大矣學統而貫擬像風道骨之姿為君子善人之冠躬行而口不言教稱而人無間行惠之和而合犯之時得參之曾而非由之噫意井顔之德行粹然知玉之無瑕游真文章渾然大櫟之未散光風霽月兮滿胸懷攬影翻江兮何影靜</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>phong thủy đều ta, nhân tiện ông có dẫn họ xem lại phần mộ tò tiên, ngôi nào họ cũng lắc đầu bảo rằng không</t>
+          <t>Nhớ Tiên - sinh xưa: Đạo đã cao siêu, học càng thông suốt, đứng đầu quân tử thiên nhân, định dạc tiên phong đạo cốt! làm nhiều nói ít, hiểu hành khôn chê, ôn hòa giống ông Huệ xưa, Thời Trung theo thánh Khổng trước, như Tăng-Sâm lỗ đọn mà chẳng ương gần như thê Trọng-Do. Đức hạnh giống thầy Nhiệm thầy Nhan, ngọc lành không vết, văn chương như Tử-Du Tử-Hạ chất ngọc chưa tan, gió mát giảng thanh hề đầy túi, vượt bề cội sống hề mệnh mang!</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HVB_003_0676</t>
+          <t>HVB_003_0176</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>以故郡鄰目之造天日明基圖復舊朝之達官鄉之豪右屢欲奪其操</t>
+          <t>洪德間策舉追士時則先生峻危擢科馳名壹諫</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Phiên âm Đệ nhất khôi nguyên tạo trí thân Cư quan bất cải cựu thanh bản</t>
+          <t>Khoa Tấn-sĩ năm Hồng-đức đã chiếm Khói-nguyen danh vang trong đại Ngự-Sử.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HVB_003_0677</t>
+          <t>HVB_003_0177</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>詔求真烈有司以名聞</t>
+          <t>景綬纂宗詔初求遺逸時則先生首應義旗張聲史館</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Phiến minh hựu trọng Yên-dài dự Sử tiết phương tri quốc hữu nhân</t>
+          <t>Chiếu cầu hiện năm Cảnh-Thống kéo cờ khởi nghĩa công rạng trong viện tu-thư.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HVB_003_0678</t>
+          <t>HVB_003_0178</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>仍表其問曰節義門賜奉事以旌揭之年八十而終子孫累世長冠</t>
+          <t>窮通隨所遇而安著述異乎人之模</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Dịch Chiếm giải khôi nguyên tự thiếu thời, Quan sang vẫn giữ nếp nghèo thời,</t>
+          <t>Mới biết cùng Thông đầu phải theo thời, trước thuật không ai sánh kịp.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HVB_003_0679</t>
+          <t>HVB_003_0179</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>為一鄉之明王族今扶櫨社有故碑存焉</t>
+          <t>通考紀元崔備史得經史之規模耕籍侍學諸書得史中經之體</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Yên-kính đã trọng thơ để quạt, Cò Sứ nếu cao, nước có người.</t>
+          <t>Thứ coi: Thông Khảo-kỷ-Nguyên cựu sử chép đúng quy mô, lại như Canh-Tịch Thị học chư biên. Chia trường thề đoạn,</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HVB_003_0680</t>
+          <t>HVB_003_0180</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>陰境 陳朝祖墓記</t>
+          <t>既師儒希楊震之鱉堂政事萬李宏之山判</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Giải nghĩa</t>
+          <t>sư nho suy tôn Dương-Chấn, Chánh-sự theo kip Lý-Hoàng,</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HVB_003_0681</t>
+          <t>HVB_003_0181</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>陳朝之祖美禎，即墨人也。</t>
+          <t>蒼東海則以恩信撫韓乎邊氓戮北乎則以恬靜鎮安平邊患</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>cũng đều làm đến Viên-ngoại. Cháu là Dịch, Toại, Viễn , ,</t>
+          <t>khi ra Đông-Hải khéo lấy án tín vỗ về, lúc đến Bắc-binh lại thì chính sách điểm tính.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HVB_003_0682</t>
+          <t>HVB_003_0182</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>世以魚為業，南道長江一帶，到處是家焉。</t>
+          <t>醒聖王圖任舊人越朋背蹤登頭窟業曳履於楓宸作元龜於弈泮</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Trương-Phụ không rõ hư thực ra sao, nên không dám vượt sang sông.</t>
+          <t>Vua dùng người cũ, đặt lên chức cao, chống gây trúc vào trước sân rồng, nếu guong sáng trong nền Quốc-học,</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HVB_003_0683</t>
+          <t>HVB_003_0183</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>時有堪輿北客就我國相地自三島祖山從龍脈而來歷昇龍古</t>
+          <t>其八侍經筵也堂堂焉輔成君德之程頗其總裁國史也致成焉志春秋之胡旦</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>bèn từ Nam-sách lên lên Tam-đôi-Châu, hiệp lực với viên</t>
+          <t>ở chức Kinh-Duyên gần gui, giúp vua thành dức như ông Trinh-Dy, ở nơi Quốc-sử Tông-tái, lại tu Xuan thu như ông Hồ-Đán.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HVB_003_0684</t>
+          <t>HVB_003_0184</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>碑至金洞縣偈州社高會社見土堆環聚即笑而言曰是也</t>
+          <t>心忠義兮有天知萬古太和子恩日賞險功多在於斯文</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Thiềm-phán Đặng-Kinh đơn hàng Trương-Phụ đề báo-cáo tình-hình họ Hỏ.</t>
+          <t>Một tấm lòng son trời có biết? Muôn đời thịnh trị bút còn ghi, những tưởng âm công chưa chất, sẽ hưởng thọ toàn lâu dài.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HVB_003_0685</t>
+          <t>HVB_003_0185</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>駐兵造厭旁至南昌縣芳萊社江漢沒了臨江顧望良久曰江水</t>
+          <t>陽報期年於京尊胡皇天不假於愁遺致暮夜垂懸於難受易纏柱下之魄筆寫難常中之讚顏梁興冬士之嗟之強起九壹之嘆聞哀之中侯甫三慰吊之金餞臣萬</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>làm Hướng-đạo quan, rồi sau cùng với viên Hạ-hòa-mục là Võ-Thạch-Khanh , bắt được Hán-Thương</t>
+          <t>Cờ sao hoàng thiên chẳng dễ, khiến cho đêm tối làm nguy. Hồn còn phảng phát đầu đây, bút khó điểm tò nên chử. Thái-Sơn khi dò sĩ phu lương những ngâm ngùi! cừu trùng xiết bao ta thân, sai quan thăm viếng sau trước mấy lần, ăn huệ ban cho bạc tiền hàng vạn.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HVB_003_0686</t>
+          <t>HVB_003_0186</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>急流豈有六藏水底耶因過河而往至御天縣河柳社見星峯草</t>
+          <t>時先生之不幸乃史書之不幸必使天下之人見其目睹耳聞莫不痛心之扼腕</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bình Binh-Giao Nam-Lục của Khâu-văn-Tráng</t>
+          <t>Than ôi! Tiên sinh bất hạnh là không may cho Sứ quân nước nhà, những người mất thấy tai nghe ai không thương tiếc!</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HVB_003_0687</t>
+          <t>HVB_003_0187</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>立郎指之曰撞頭旁在是寧能適我耶遂尋至日果社起宗到太堂社</t>
+          <t>況某也義重臣三情深于半愴一刑之長終恨百年莫換器</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>phong cho quan trước, Toại làm Tham-chánh, Dịch làm Chi-huy-Sứ, Viễn làm Diệm-Thiết-Sứ, về sau vua Lê Thái-</t>
+          <t>Hương chi tôi đây, nghĩa nặng nào khác cha sinh. Tinh sâu lại là con rẻ, biệt ly một phút, uất hận trăm năm!</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HVB_003_0688</t>
+          <t>HVB_003_0188</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>阮固結苟旁續下盤針看了輒躊躇不敍去適西衙人阮固見之問曰地仙</t>
+          <t>聞此日僅得備會禮而正是衣冠在續權時不得設几筵而奠是酒鬱</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Nghi-Dương rồi sanh ra nguy Thái-Tổ là Mạc- đăng-Dong , tức là cháu 7 đời của Trạng-nguyên</t>
+          <t>Cáo phó hôm nào may được y quan vào liệm, những ngày quan thần chẳng được giang rượu mấy tuần,</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HVB_003_0689</t>
+          <t>HVB_003_0189</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>屬意于見不知這處有吉穴耶客人仰面笑曰不謂奇王大地出平陽</t>
+          <t>魯城靈墓兮恨無由從厚血壠兮增感嘆</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>cao để làm nơi tế lễ, các quan nhà Mạc đi qua nơi đó đều đến bái vọng, hai chỗ hiện nay vẫn còn (Điện ở bản</t>
+          <t>làm nhà bên mộ khôn hay, gò đống ngồn ngang thêm cảm,</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HVB_003_0690</t>
+          <t>HVB_003_0190</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>可笑聰勁時師都無眼力固曰果如此請以許我師謝禮如何我亦可</t>
+          <t>將欲收先生之遺篇則某也以文章倥傯總覩筆夕踈不莊集昌樑之遺文而為唐李漢</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Nay tôi là kẻ hậu sinh, kiến văn dẫu rằng thiên lậu, cũng xin tạm thuật một cách đại lược ra đây.</t>
+          <t>cũng muốn thu thập di cảo, then mình nghiên bút sơ sai,</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HVB_003_0691</t>
+          <t>HVB_003_0191</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>辨客人曰爾既有福而遇我我則予之郎還謝我以百緡錢他時有	,</t>
+          <t>將欲紡先生之道派則某也以見聞淺陋政事紛紜不罷榻老亭之遺蹤而為泉之黃幹</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>vua Thành-Thang biết có tài đức, sai sứ đem lễ đến đón trước sau 3 lần, ông mới chịu ra làm tướng,</t>
+          <t>cũng muốn diễn lại dư ba! thẹn mình kiến văn nồng cạn, nhớ nét bằng thanh thường: phảng phát.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>HVB_003_0692</t>
+          <t>HVB_003_0192</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>國當分其半國許諾遂將祖墓葬之客人反覆謂之曰這誠大地</t>
+          <t>水清玉潤兮想無忘萬里接遲兮空望新惡一酌以將愧寫百年之哀怒</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>đánh tan vua Kiệt nhà Hạ lập nên cơ nghiệp nhà Thương . Chu-Công là em vua Vũ-Vương nhà Chu ,</t>
+          <t>Trong với Cáo - lý những bảng khuang, gọi là một chén kinh dâng, khôn tả trăm năm ai oán</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>HVB_003_0693</t>
+          <t>HVB_003_0193</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>登了必有嘉祥但於百日之內時常往來以探倘風雷之後見有異事</t>
+          <t>魏朝嘆詠詩云</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>dám nhận, rồi sau cũng bỏ trốn đi nơi khác. Cách mấy năm sau, vua Võ-vương kéo quân Chư-</t>
+          <t>bởi thế nên trong tập Lê-Triệu khiếu Vinh đã có thơ rằng:</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>HVB_003_0694</t>
+          <t>HVB_003_0194</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>便是剣多古少一可急殺塞之葬纔三日忽夜聞巨雷振起一聲所在</t>
+          <t>儒科早擢際明時學道尊為國學師</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>hầu vào đánh vua Trụ , hai ông đón đường giữ lấy cương ngựa can rằng: Con mà giết cha có đáng hay</t>
+          <t>Sớm chiếm cao khoa buổi thịnh thi. Đạo cao quốc học bậc Tôn sư (si)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HVB_003_0695</t>
+          <t>HVB_003_0195</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>地方人畜皆驚而次日視之見蜀會西衙太堂三社有石突出人稱貓耳石</t>
+          <t>越考一為真可法休談撫怪謾傳奇</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>lấy ngôi thiên-từ, dựng nên cơ nghiệp nhà Chu, vì thế hai ông không thêm ăn thóc nhà Chu, rồi cùng lên núi</t>
+          <t>Một Thiên Việt khảo phương châm đủ. Trích quái bản chi những truyện kỳ.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HVB_003_0696</t>
+          <t>HVB_003_0196</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>園池在在皆有時同自知得地喜不自勝其要謂之曰此地雖然然發</t>
+          <t>繡光貢有詩云</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>cháy đá, bài Chiêu-Hồn trong Sổ-Từ có nói rằng : ở phương đông có cây Phù-tang, phát ra khí nóng</t>
+          <t>QUANG-BÔN CÓ THƠ RẰNG:</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HVB_003_0697</t>
+          <t>HVB_003_0197</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>福但今損百緡錢如何可得又來日半分天下其所得者幾何因以是無意還謝禮錢客人問之固約以某日具還至日客抵其家固即捉</t>
+          <t>堂堂聖世一洪儒 仕士隨時任自由 天上麗儒稱。骨相人間話佛見心頭嘉言善行諸賢慈大典高文萬古彌斯道巍然山奇在後人無不企企前修傳奇唐安之武者是也</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Phong. Đại ý nói rằng : gặp thời nóng nực thì cái quạt đặc dụng như ông Y-Đoãn ông Chu-công ; gặp buổi rét mướt thì cái</t>
+          <t>Một vị hồng nho giữa Thánh trào. Tùy thời tần thoái tự do sao. Tiên còn thượng thế coi như đúc? Phật sống nhân gian ngầm khác nào? Ngôn hạnh đối đương ai sánh kịp. Văn chương muốn thuở giá càng cao. Non xanh cùng đạo nguy nga mãi Hậu thế ai người chẳng ước ao? Nay ta xét thấy trong tập Truyền - Kỷ có chép họ Vũ ở Đường-An, chính là họ Vũ này vậy.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HVB_003_0698</t>
+          <t>HVB_003_0198</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>來縷定乘夜救之江中惶遠而歸不意這處乃浮沙水漲自他將投下</t>
+          <t>公子幹生而頴異博極群書景綿稱德士寅科中黃甲性愛松故以松軒自號文章行當代推尊雖家素清貧而恬然自適凡遇物即事輒隨意興吟矢口成章揮毫立就日積月累遂成一家機軸</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>quạt thành ra vô dụng, bị bỏ chết đối như ông Bả-Di, ông Thúc-Tê. Dụng chi tắc hành xả chi</t>
+          <t>Còn những con giai của ông tên là Cán, lúc nhỏ cũng rất thông minh nói tiếng là người bác học, thì đồ Hoàng-giáp vào khoa nhâm tuất thời Lê-Cảnh-Thống năm ấy mới 28 tuổi vì tánh yêu tùng nên mới lấy hiệu là Tùng-Hiên, về phần văn chương đức hạnh người đời rất là kinh mến, nhà vốn thanh bản thế mà lúc nào ông cũng thân nhiên, gặp khi cao hứng xuất khẩu thành chương, ngày tháng tích lại đóng thành một tập.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HVB_003_0699</t>
+          <t>HVB_003_0199</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>忽然潮水漸涸圖在沙上適陳氏魚舟過聞有人喚聲急來救之上</t>
+          <t>典永賴古庵程國公相善其詩詞偈經往復如懷鄉綠蒿艾虎等首見白雲庵詩集未澤鄉八景等首見品景詩集又有松軒詩集并四六備覧覧傳于世</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>tắc tang, câu này ở thiên Thuật-Nhi trong sách Luận- Ngữ , đức Không-Từ bảo ông Nhan-Uyên</t>
+          <t>Ngoài ra ông lại cùng với bạn thân là Trinh-quốc-Công ở Trung-Am thuộc huyện Vĩnh-Lại xướng họa rất nhiều, tỷ như các bài thơ Hoài-hương Chi-duyên Một - hở v. v. hiện nay có chép trong Bạch Vân-Am Thi tập và các bài Tiêu-Tương-bát-Thủ thấy ở trong tập Phẩm-Vưng, lại còn Tùng-hiên tập và Tập Tứ-lục-bị-lâm truyền bá cho đời,</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HVB_003_0700</t>
+          <t>HVB_003_0200</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>船觧去其縫換以新衣間故客人具道由來因謝曰感君子角生之恩</t>
+          <t>仕禮部尚書禮度伯光賁詩云</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>dám nhận, rồi sau cũng bỏ trốn đi nơi khác. Cách mấy năm sau, vua Võ-vương kéo quân Chư-</t>
+          <t>về sau ông cùng làm đến Lễ-bộ Thượng-thư và được phong tước Lễ-Độ-Bá. Cho nên ông Quang-Bồn có thơ vinh rằng:</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HVB_003_0701</t>
+          <t>HVB_003_0201</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>當以此地相報陳氏謂這地他已葬了若將之何客人曰某已先葬此</t>
+          <t>早擢危科副上來文章德業依飾模</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ly vậy. (4) Đông-di Tây-di, câu này ở sách Mạnh-Từ thiên Ly-Lâu hạ , thầy Mạnh nói rằng :</t>
+          <t>Sớm đỗ cao khoa đẹp ý vua. Văn chương đức nghiệp đang sư mô.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HVB_003_0702</t>
+          <t>HVB_003_0202</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>地必為公有陳氏遂畱之舟中不露人聲跡客人即教以多采調器</t>
+          <t>半天載上扶興運三十年餘歷要途</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Vua Thuấn sinh ở đất Chư-phùng là người</t>
+          <t>Nửa ngàn năm trước phò hưng vạn. Ba chục niên sau trái hoàn đồ.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>HVB_003_0703</t>
+          <t>HVB_003_0203</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>鑄為霹靂斧形及蘇木樑煮湯待有授用處忽是夜雷雨交作數</t>
+          <t>驚龜冕躬主新好爵青燈黃老舊寒儒</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Trâu-Thu là sách Mạnh-Tử , vi thầy Mạnh sinh ở Ấp Trâu, lúc thầy Mạnh vào yết kiến vua Lương-</t>
+          <t>Áo tía đại vàng Quan tốt phẩm. Đèn xanh Ấn tuyệt cảnh hàn nho.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HVB_003_0704</t>
+          <t>HVB_003_0204</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>然有雷轂手之聲，震師將雲辟雲蓋，斧穿重於墓上，面透至棺，隨以蘇</t>
+          <t>清貧誰哉為家計焦地詩書有道腹</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Lạc, có con Rùa-thần nổi lên, trên mo có 9 vạch, dưới bụng có 9 vạch, vua bèn suy diễn ra thiên Hồng-Phạm-</t>
+          <t>Phí gia kề ấy không mang tới, Rượng cấy thi thư chẳng mất mùa.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HVB_003_0705</t>
+          <t>HVB_003_0205</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>木水灌下明日固往探見之以為雷打墓中流血因惧而殺去客人遂將</t>
+          <t>樗眼阮全安記</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>là núi Thiên-Trụ thuộc tỉnh Thiềm-Tây , khi Chu Thái-Vương trấn nại Di-Địch đem dân sang</t>
+          <t>LÁNH HIỆU BAN THI, NGUYỄN BẢNG-NHÂN</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>HVB_003_0706</t>
+          <t>HVB_003_0206</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>陳家祖墓就塟焉。</t>
+          <t>阮全安唐安時舉人也洪德間充另兵常守殿前判草適中秋朝侍間夜月昏曉御題中秋無月詩班列中吟咏未竟公詩先就跪而上之在坐笑曰另兵亦有詩乎母乃雷門擊手鼓命取觀之落句若曰</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Thám-hoa Đặng-đình-Bảo ! Thiên hạ cộng tri danh.</t>
+          <t>Nguyễn-Toàn-An, người làng Thời-Cử tham thuộc huyện Dương-An vào khoảng niên hiệu Lê-Hồng-đức ông phải sung vào ngạch lính, giữ việc cắt cỏ ở trong sân điện, một đêm gặp tiết trung thu, bá quan được vào thường giang trong điện, đêm ấy giáng mờ, Hoàng thượng bên lấy 4 chữ Trung thu vô Nguyệt làm đầu đề, bắt các văn thần vinh thi, giữa lúc mọi người còn dương thời xao, chẳng ngờ chú lính Toàn-An đã làm xong trước, qui gởi dâng lên! cứ tỏ ai cũng cười rằng: binh lính cũng biết làm thơ đó chẳng? rỡ thật đánh trọng qua cửa nhà sắm, Hoàng thượng thấy vậy phân bảo đưa lên Ngai coi. Thấy câu kết viết:</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>HVB_003_0707</t>
+          <t>HVB_003_0207</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>這句前望三陵大江在美樣縣有備社格曰新巡礦後拖伏象樓壹</t>
+          <t>莫把今番閒視月來秋望月月彌高</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Đời trước truyền ngon lại rằng : Lúc ông ra Kinh ứng thí phải qua sông Uông , khi ấy sông còn nhỏ hẹp</t>
+          <t>. Chớ thấy phen này mà để nguyệt? Thu sau trông nguyệt nguyệt càng cao.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>HVB_003_0708</t>
+          <t>HVB_003_0208</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>旌劍羅劉左右穴在土腹藏金坐乾向巽事襄客人有課云彩岱黑當堤</t>
+          <t>觀者嘆服仍具奏敬因全寅科貳拾歲一舉中鄉試會廷試中榜眼合菜歸</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>có thể bắc cầu qua được, nên ông khẩn thâm xin giang thần phù hộ cho ông đỗ Trạng-Nguyên, thì ông bắc cầu</t>
+          <t>ai cũng tóm tắc khen ngợi rồi tâu vua xá tội cho về, đến năm nhâm-thin thì ông mới 23 tuổi, gặp có khoa thì ông vào ứng cử đỗ thi Hương xong, lại đỗ cả thi Hội; lúc vào thì Đinh được đỗ Bảng-nhãn, vinh quí bài tỏ vừa xong</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HVB_003_0709</t>
+          <t>HVB_003_0209</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>陳氏曰果如其言當分民祿之半客人</t>
+          <t>未幾適值家憂時朝制孔嚴係憂中要憂孕者不盡仕刻公守制三年不敬近女色服闕尋卒無嗣皇上聞而憐之自是居喪言月之極亦始除之</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>con ông dự hưởng ở nơi đền thờ. Thám-Hoa Đinh-công-Lưu</t>
+          <t>chẳng may lại gặp gia biến, theo như chế độ hiện hành, nghiêm cấm những người trong lúc có tang cha mẹ mà vợ thụ thai, thì không được kẻ vào hàng thân sĩ, bởi thế trong vòng 3 năm cư tang, ông phải lánh xa thế thiếp, rồi khi hết tang ông bị ốm chết, thành ra vô tự!</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HVB_003_0710</t>
+          <t>HVB_003_0210</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>顏色得天下陳氏曰果如其言當分民祿之半客人</t>
+          <t>光真有詩云</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>biểu-diễn đến mấy trăm lần. Hoàng-thượng thấy vậy cười</t>
+          <t>vì thế Quang-Bôn có thơ khóc rằng:</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HVB_003_0711</t>
+          <t>HVB_003_0211</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>照煙花對面坐必以顏色得天下陳氏曰果如其言當分民祿之半客人</t>
+          <t>森然美玉為聖河莫狀良工妙琢磨</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>câu: Tam-đô đắc thiên-hạ nghĩa là : Tam-đô lấy được thiên-hạ, đến khi tinh dầy Ngài bên nghi</t>
+          <t>Sáng choang ngọc bích giữa trần ai, Khôn tỏ lương công cách giữa mái.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HVB_003_0712</t>
+          <t>HVB_003_0212</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>得奈 景須如此但君家世世享國則我家世世給足衣糧可也陳氏謹當書目伸</t>
+          <t>辛苦十年劬勞九寅綠一拳權危科</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>trong số Tam-đô, và lại có con lối lạc, nên mới ra lệnh cho Cự và ông thứ nhi phải tự tử, mà không để ý đến vị</t>
+          <t>Đèn sách mười niên công chẳng quản, Khoa danh nhất cử gia chưa hai.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HVB_003_0713</t>
+          <t>HVB_003_0213</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>各有書交為質部說客人心多機智又密寫識一道雷與彼子孫藏之</t>
+          <t>方施心上經綸用莫測裘中愁恨交</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>quan rất thanh liêm ngay thẳng, gặp những vụ án uẩn khúc, có tài xét đoán như thần, vì thế ông ở trong đại</t>
+          <t>Kinh luận mở túi toàn gia sức, Luật pháp cư tang cảm thụ thai.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HVB_003_0714</t>
+          <t>HVB_003_0214</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>嘯以異事特他如禮不替者便以冥告倘者背約即如此因與陳語曰</t>
+          <t>地下修文知有命豐才普壽奈天何</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>quan văn cho được kiện, nhưng sau đến lượt ông xét thì ông lại xử cho thua, từ đấy về sau không đi kiện cáo</t>
+          <t>Này chức tu văn nọ địa hạ, Ông xanh bớt thọ bồi thêm lại.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HVB_003_0715</t>
+          <t>HVB_003_0215</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>某恐遺下二法有漆長遠來時便可造之陳氏不勝感謝至二世陳賜</t>
+          <t>狀元綬帶記</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ông là một vị liêm chính tài năng, nên lại cho sứ về triều để ra cảm đầu trong đại Ngự-Sử, dần dần thăng đến</t>
+          <t>HUYNH DƯ ĐỆ THI LÊ TRANG-NGUYÊN</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HVB_003_0716</t>
+          <t>HVB_003_0216</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>守度曰陳家皇族乎陳家赤族乎後遂禪位、</t>
+          <t>敬賀眾唐安幕澤人也少助于紫鮮元時二十七歲同邑尚書狄瓊以女妻之出贅復終日間居不以書籍意瑤文怪之以問於公之艾曰素問言吾瑤力學邇來無事不曾見讀書父曰兒自過貴庭相公每食之如何瓊曰儒家清淡所食者其肱幾何父曰老子異夫人的食而公以尋常視之安巧有不滿處璣間言食每飯必加飯倍之</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>nuôi, rồi sau lại được người cùng họ là Thường-quốc- Công xin lại, nuôi làm nghĩa tử (Quốc-Công cũng</t>
+          <t>Tràng-Nguyên Lê-Nại. (có chỗ viết là Đinh) Ông Nại Người làng Mộ-Trạch lúc nhỏ rất chăm học, năm đỗ giải nguyên mới 27 tuổi, được quan Thượng Võ-Quỳnh là người cùng làng gà con gái cho, khi ở gùi rẽ ông chỉ thơ thân tới ngày không để ý gì đến sách vở. Cụ Thượng lấy làm là hỏi phụ thân ông rằng: Tôi thường nghe nói Cậu ấy chăm học, thế mà từ khi sang bên nhà tôi thì Cậu không hề nhìn đến sách vở là có làm sao? Thân phụ ông hỏi lại: Thưa Ngài vậy từ khi cháu sang ở bên quí phụ thì sự ẩm thực thế nào? Cụ Thượng đáp: Theo lời thanh đạm của nhà nho, thì mỗi bữa ăn cũng chẳng mấy tí! Phụ thân ông đáp: Sức ăn của cháu khác với người thường, thế mà Tương-Công cho ăn ít ỏi như vậy, hoặc giả châu không vừa lòng đó chăng? Cụ Thượng Quỳnh thấy ông dâu gia nói vậy bên bảo người nhà cứ mỗi bữa ăn của Cậu sẽ tăng gấp đôi,</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HVB_003_0717</t>
+          <t>HVB_003_0217</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>逮季世後禮日寢哀客人即進言臣先祖遺一譜囑以某年遂就黃國</t>
+          <t>自是公始開卷讀一二篇尋加三歲謁飯公漸讀章三鼓又加以四歲錫公郎讀至四鼓還曰吾謂誠能過人矣更加以五歲錫為度誠觀知何是後讀書終夜不絕微常有賛云</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>quan nhà Mạc phong chức Đại Nguyên-Soái Tổng quốc chánh trước là Thanh-Vương, về sau nhà Mạc mất thì tự</t>
+          <t>từ đấy Cậu mới cảm sách đọc vài lượt, tăng đến nỗi ba (3) thì Cậu học đến trống tư (4)! bấy giờ Cụ Thượng mới biết con rể của mình ăn khỏe quá xá! rồi sau mỗi bữa ăn cứ lấy nỗi 5 làm mục để thử xem sao? quả nhiên Cậu học suốt đêm không hề nhắm mắt! và thường tán tụng mình rằng:</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HVB_003_0718</t>
+          <t>HVB_003_0218</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>陳朝取讖者之見內言太堂發跡舊墳今將不旺當疏通水道</t>
+          <t>曾來潭先生以食為名十八肆飯十二餌羹魅荒次第各冠群英富之也鉅談之也宏</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>dinh vẫn cứ thanh bạch, bởi thế ông mới thảo ra những bài phú như : Thái-Môn-Nhân-Túc nghĩa là</t>
+          <t>Mộ-Trạch Tiên-Sinh, ăn khỏe nỗi danh! mười tám bát cơm! mười hai bát canh! Khởi nguyên chiếm bảng, trên cả quân anh! bởi nhiều sức tích, nên phát tung hoành!</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HVB_003_0719</t>
+          <t>HVB_003_0219</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>遂信其言照識內書圖鑒自富初社大江而八紫囘至太堂</t>
+          <t>端變年間乙丑科會試四六中第二義經賦文策並第一廷試文中狀元往至戶部左侍郎</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Linh Phong-Thổ ký và bài Vương-Thăng-Truyện , với bài phú Ngư-Tiều Canh-Mục, đều được</t>
+          <t>Thế rồi đến khoa ất Sứu (1504) niên hiệu Đoan-Khánh Triều Lệ Uy-Mục-Đế ông vào thi hội, về văn Tự lục ông dùng thứ nhi, còn kinh nghĩa, phủ sách, thì đều. thứ nhất, khi vào thì Đinh liên đồ Trạng-Nguyễn, lúc ra làm quan dàn dàn đến chức Tả-thị-Lang bộ Hộ,</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HVB_003_0720</t>
+          <t>HVB_003_0220</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>蓋陳家享福該有此數是亦出於天命豈人力所能及或按陳家祖墓提生</t>
+          <t>其子光貞有詩云、</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>cả môn Địa-lý, người ta đồn rằng: chính ngôi mộ Tò của nhà Trang-nguyên ở Hùng-Khê cũng là tự ông coi đất điểm</t>
+          <t>con là Quang-Bôn có thơ vịnh rằng:</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HVB_003_0721</t>
+          <t>HVB_003_0221</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>天下後生仁宗火時清秀面字號金仙童子明宗清秀非允時人</t>
+          <t>局度寬洪操履純天才定賦晚逢長</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Quan Thương-Thư trức Nghiêm-Sơn Hầu Nguyễn-công Doãn-Khâm, ở làng Kiệt-Đặc, huyện Chi-Linh</t>
+          <t>Rộng rãi còn thêm tính nét thuần. Thiên tài muốn phát chắc mười phân.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HVB_003_0722</t>
+          <t>HVB_003_0222</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>稱為神仙人中蓋亦土地之壇客言信不誣矣	—</t>
+          <t>曾將各望魁天下又把詩書還萬民</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Quốc-triệu đáng-khoa-lýc — Những suy-niệm siêu-hình-học</t>
+          <t>Đã đem danh vọng trùm thiên hạ. Còn lấy thì thư hóa vạn dân.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HVB_003_0723</t>
+          <t>HVB_003_0223</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>詠橋祖墓記</t>
+          <t>陰德足徵來世及危科繼擢一門春</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Lê-dinh-Huyền Bài-văn-Bảo</t>
+          <t>Cây đực tốt tươi đời hai quả. Bằng vàng nối đời của đầy xuân!</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HVB_003_0724</t>
+          <t>HVB_003_0224</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>東崖誄橋京北阮族之祖號福過平生樂善音築木千豐盈縣東蕃社以</t>
+          <t>永垂者一無窮慶漢義於公宋當見</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Nguyên trước Trị-sở Thừa-Ty của tỉnh Hải-dương</t>
+          <t>Cho hay phúc trạch bao giờ can? Hán vi Vu-Công, Tống Đậu-Quân.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HVB_003_0725</t>
+          <t>HVB_003_0225</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>釀酒為業傍有菩提樹為風所拔因買供新爨適極至樹根見下有</t>
+          <t>嗣公第大調以袖童稱少年激發之氣公奇抑之</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>giải võ của Ty, đánh 3 hồi trống, các quan trong Ty ngò có việc công, vội vã khẩn áo chính tề tới họp.</t>
+          <t>Nguyễn ông còn có một người em giai tên gọi là Tài Thần, lúc nhỏ nỗi tiếng thân đồng! nên hay có tánh tự phụ ông phải tìm cách để nên bớt đi!</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HVB_003_0726</t>
+          <t>HVB_003_0226</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>銀穴約三婁許即收囘晉貯之已而撤廬去經二年餘時有北客來取銀見</t>
+          <t>乙丑科八第一場有錯誤處以問子公公答之曰今番與正第試若以相告更將誰誘郎鼎怒曰今科讓兄光簽討撤籠而出郎日歸本鄉乘夜而行致家時以三鼓不敵呵門因憇卧于軒之檐處</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>quan ngạc nhiên hỏi vậy: Cớ sao lại dám đánh trống? Ông đáp: Tới đây là kẻ hàn-sĩ muốn đến để xin lương</t>
+          <t>Vi thế nên khoa ất sử, anh em cùng vào ứng thí, giữa kỳ đệ nhất, ông Tài quên sách đến hồi thì ông bảo rằng: chuyện này tôi thi với chú, nếu lại bảo chú thì còn thì cử với ai? Ông Tài tức giận đáp: Thôi thì khoa này tôi để cho anh chiếm giải trước vậy nói xong giỡ phẳng lều chống ra về, đi thẳng một mạch đến trông canh ba thì về tới nhà, nhưng lại không giám gọi cửa, dành nằm ngủ ở ngoài hiên.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HVB_003_0727</t>
+          <t>HVB_003_0227</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>雀跡不存只畫空穴即聞諸旁人知這銀已為公所得遂尋至家出雀</t>
+          <t>是夜其母愛袖人謂軒前有黃甲在何不開門接入俄醒覧覧私自怵曰今日八會試場二子皆京城應舉部有何黨甲在我家軒誠尚親焉見壚外有人熹睡喚而起之乃晨才鼎其母愕然問故才鼎以實對母曰曾學未到勸再加功才得郎點燈索書觀之母笑而言曰覆落第歸斯爾愼激只恐此志難持鼎曰自今而後母觀如何自是日夜攻書手不釋卷</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Mọi người lấy làm khâm phục, đem cấp cho 5 quan tiền và 1 thùng gạo; thế mới biết ông quả là một kỳ tài.</t>
+          <t>Giữa lúc ấy thân mẫu ngủ trong nhà mờ thấy thân nhân đến báo: Ngoài hiên có Ông Hoàng-giáp, sao không mở cửa đón vào. Bà cụ sức tình nghĩ rằng: Ngày nay đương kỳ thi Hội, hai con của mình đều ở trong kinh, thử hội còn Hoàng-giáp nào ngủ ở ngoài hiên. Nghĩ thế rồi bà mở cửa ra coi, bỗng thấy một người dương nằm ngủ lăn ra đó. Bà đánh thức đây thì lại chính là cậu Tài, làm bà hết sức ngạc nhiên! Cậu bèn kể lại câu chuyện như thế. Nghe xong bà mới báo rằng: Đó là tại con học chưa đến nơi đến chốn, vậy thì từ nay con phải gắng công v. v. Cậu nghe lời mẹ dạy bảo với theo vào ngay trong nhà, đốt đèn mở sách ra đọc. Bà cụ thấy vậy mỉm cười bảo rằng: vừa mới thì hồng cho nên phần khích nhất thôi, chỉ sợ không giữ mãi được như thế đó thôi Ông đáp: Thưa mẹ, từ này về sau rồi mẹ sẽ thấy, thế rồi từ đây ông học suốt cả ngày đêm, tay không hề rời quyển sách.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HVB_003_0728</t>
+          <t>HVB_003_0228</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>識一道示之曰某為先人遺貨跋涉而來不想天已賜公今早覓歸程所</t>
+          <t>是科兄鶴中狀元帝以爲監司月講官作成人才鼎尋赴京邀訓學從謂曰經営司是我的有如問其書首從毛聽講來學者素聞其各試往觀才學知何至鄕市處士人特書來問才兼隨問答之滔滔不絕至有以外書諸子問之亦淡練應答人皆發為服爭來觀咱而盟胃為之一空</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Theo lời truyền lại thì ông sinh trưởng trong một gia- đình nghèo túng, phải ở gửi rể nhà một phù ông cùng</t>
+          <t>Còn phần ông Nại lúc ấy đã đồ Trạng-Nguyên vua cho giữ chức Giảng-quan trong Quốc-tử-Giám, biết bao sĩ tử được ông tác thành, rồi ngay khi đó ông Tài cũng ra kinh đó, đón đường bảo các sĩ tử rằng: Ta đây tức là bồ chư? các anh muốn hỏi chư gi? hãy cứ đem sách lại đây rồi ta sẽ bảo? Về phần sĩ tử trước kia vẫn thường nghe tiếng, ngày nay cũng muốn xem tài học ra sao? nên họ rủ nhau đến chỗ chợ Dừa thị để hỏi nghĩa sách, hỏi đâu đáp đây, thao thao bất tuyệt! Có người đem cả ngoại thư và sách chư từ ra hỏi, ông cũng giảng giải rất là tinh tường! Khiến cho mọi người đều phải khấp phục, rồi sau kéo đến cảng đông thành ra trường Giám vãng teo.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HVB_003_0729</t>
+          <t>HVB_003_0229</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>望出資路費受賜不淺而公得銀藏之不知多少至是取識者之因熙熙</t>
+          <t>兄鼐即歎諧之曰吾弟之才何直受於高選不宜如此孟浪邀學者義嚴談使譽席欲講這是關風教焉。</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>nhẫn phi Hằng thì Trí; vì thấy tài học của ông còn hon Phạm-Công xa lắm, thế mà về sau ông chẳng</t>
+          <t>Ông Nại thấy vậy phải can em rằng: Cứ như tài học của chú lo gì chẳng đồ cao? mà đi làm việc vô ích, đón học giả về bàn suông để cho trường Giám không ai đến học. Tôi thấy việc này có quan hệ đến nên giáo hóa, vậy khuyên chú nên định chỉ thi hơn.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HVB_003_0730</t>
+          <t>HVB_003_0230</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>銀數與記不差即疑得其人謂曰聊這銀繫我取的原來收時如故不曾取</t>
+          <t>才眾郎輿歸至洪順三年，穆襄翼帝年號，辛未科果中黃甲嘗以不得大科為根仕經免部給事中短光責有詩云</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Nhắc lại khoa trước mà ông bị hỏng, thì lại chính là cái khoa mà ông tin chắc thập phần, vì thế trước khi</t>
+          <t>Ông nghe lời anh lập tức trở về. Đến khoa Tân-Vị (1140) ông đồ Nhị-giáp, lấy làm uất hận vì không chiếm giải khối nguyên, sau ra làm quan cũng chỉ đến Lại Bộ Cấp Sự-Trung rồi mất! vì thế Quang-Bôn là cháu có thơ rằng:</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HVB_003_0731</t>
+          <t>HVB_003_0231</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>用既是公家原物當盡以付還其人謂曰那物雖我家先遺一下今既為公所</t>
+          <t>確句奇男的壯懷一門兄弟應花開</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>nộp quyền đi thì, ông đã xin với nhạc-gia cho mở 1 trâu đề ăn khoa trước, và hẹn người làng chặt tre làm sẵn</t>
+          <t>Lỗi lạc nam nhi có đủ tài? Sao khuê ưng cả một nhà Ngài?</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HVB_003_0732</t>
+          <t>HVB_003_0232</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>得是公家物倘蒙惠顧只願費路錢足矣若更以相還豈敢如命公固執</t>
+          <t>青鐵萬中登高遠蘋案曾趨預密陪</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ông gia nghe xong bảo rằng : Nếu ông bỏ ra thì ai là người đáng mặt ở lại thì cứ ?</t>
+          <t>Vẫn như tiên đúc luôn tranh giải? Chức cũng xu bồi thoát ghế vai?</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HVB_003_0733</t>
+          <t>HVB_003_0233</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>不可客人曰公既有是心願頒其半公曰我不穀人情之所欲第這銀非我</t>
+          <t>幼學壯行初得遂有才無壽盡堪哀</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Nhẽ nào khói-nguyên mà phải ăn cấp chữ của người khác, vừa nói vừa dáo bước đi, không thêm ngoài cờ trở lại.</t>
+          <t>Ngầm sự học hành khi thiếu tráng? Xem cơ thọ đoàn thực bi ai?</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HVB_003_0734</t>
+          <t>HVB_003_0234</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>之財天使我為公守耳故為此以待勿復牢辭客人恐遠其意輒</t>
+          <t>九重莫謂三光滿已送文星八夜臺</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Ông Đắc nói : Chương ấy em vẫn thuộc lòng, vậy xin anh cứ ở lại, em sẽ đọc cho mà nghe.</t>
+          <t>Cửu trùng chớ tưởng Tam quang đủ? Đã tiến sao vẫn xống Dạ-đài!</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HVB_003_0735</t>
+          <t>HVB_003_0235</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>頒銀歸國後嘗以其事對北人言時有風水師者聞之曰難如此</t>
+          <t>狀元程國公記</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Câu Tự thấy anh bảo vậy, quyết chí học thêm rồi sau cũng dỡ đại-khoa, anh em đều được vinh hiền, sự</t>
+          <t>BẠCH-VÂN-AM CƯ-SĨ NGUYỄN-CÔNG-VĂN-ĐẠT PHỔ-KÝ</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HVB_003_0736</t>
+          <t>HVB_003_0236</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>人好心我今老矣尚尚火時郎當往安南擇吉地以報其人懇之</t>
+          <t>公字秉謙道號自雲居士永賴中庵人也先世皆有隱德不可考其祖文靖始卜陽宅山水週环暗兮高王錮記父文英有學行亮太學生母慈淑夫人光明妾子下人戶尚部書汝文瀾相公之女世聽聲通經史善文章尤精風鑑曉術戴方洪德盛時而知四十年後炎運當微慨然有大夫夫改物之志擇對不嫁幾十年一見文定知其有貴兒相逐歸焉</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Ông người làng Hùng-Khê , huyện Chi-linh , thân phụ mất từ khi ông còn thơ ấu, chỉ nhớ</t>
+          <t>Ông Nguyễn-bỉnh-Khiêm đạo hiệu là Bạch-Vân cư-sĩ, người làng Trung-Am huyện Vĩnh-Lại, tiền tổ ngày xưa tu nhân tích đức đã nhiều, (nay không thể khảo cứu được) chỉ biết từ đời cụ Tổ thì được tập phong Thiếu-bảo Tư-quận-Công mĩ tự là Văn-Tính, Cụ bà được phong Chính phu-nhân Phạm-thị Trinh-Huệ, nguyên trước các cụ lập gia cư ở nơi có núi sông bao bọc, hợp với kiểu đất của Cao-Biền. Phụ-thân được tặng phong Thái-bửu Nghiêm Quận-Công, mĩ tự là Văn-Định, đạo hiệu là Cù-Xuyên Tiên-Sinh, nguyên người học rộng tài cao, lại có đức tốt, được sung chức Thái-học-sinh. Thân mẫu họ Nhữ được phong Từ-Thục phu-nhân, nguyên người ở An-Tử hạ thuộc huyện Tiên-Minh, là con gái quan Hộ-bộ Thượng-thư Nhữ-Văn-Lan. Bà vốn là người thông minh, học rộng văn hay; lại tinh cả môn tướng số, ngay thời Hồng-Đức mà Bà đã tính được rằng; vận mệnh nhà Lê chỉ sau 40 năm nữa thì sẽ suy đồi. Vì có một chí hướng phò vua giúp nước của bậc trượng phu, muốn chọn một người vừa ý mới chịu kết duyên, nên đã chờ đợi đến ngót 20 năm trời, khi gặp Cù-Xuyên Tiên-sinh biết là có tướng sinh quý tử mới chịu lấy.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HVB_003_0737</t>
+          <t>HVB_003_0237</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>師曰我有二門弟一可遣遂與之偕往北客至詠橋社探問則念已</t>
+          <t>後遇一少年過雪江寒度頭愕然嘆曰火時何不相遇今日到此何為從者比而顓之夫人徐詢姓名知是登庸恨悔者絞日</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>tế Tiên-sư cho cháu nhập học mới phải.</t>
+          <t>Sau bà gặp một thiếu niên đi qua bến đò Hàn bên sông Tuyết-giang, bà kinh ngạc than rằng: «Sao lúc trước không gặp, nay tới đây làm chi?» Người nhà nghe lén hỏi tên họ, mới biết đó là Mạc-Đăng-Dung, bà lấy làm tiếc nuối.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HVB_003_0738</t>
+          <t>HVB_003_0238</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>於前年捐館矣郎辨一購禮致祭而去二月餘復至謂公之子曰我感</t>
+          <t>公以洪德二十一年幸亥生身體長大容貌英偉未周歲能言一日昧爽文定抱諸卷忽語曰日出東方考大驚異</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Nguyên trước có lần Tiên-sinh mơ thấy mình dỡ, mà trong lên bằng thấy người được dỡ thứ nhất tên là</t>
+          <t>Ông sinh năm Tân-Hợi niên hiệu Hồng-Đức thứ 22, thân hình cao lớn dung mạo khôi ngô, chưa đầy tuổi đã biết nói. Một hôm sáng sớm, thân phụ bế ông, bỗng ông cất tiếng: «Nhật xuất đông phương». Thân phụ rất kinh ngạc.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HVB_003_0739</t>
+          <t>HVB_003_0239</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>受先人之德無以相報今帶得地師來來尋告地以謝有一處群山</t>
+          <t>年四歲夫人誦以經傳王義即能誦新口頭又暗讀諸國詩數十首</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>sĩ ngày nay mà mình quen biết, chẳng có tên ai như vậy. Cho nên ông đã mượn nghề dạy học đi khắp đó</t>
+          <t>Năm 4 tuổi, mẹ dạy kinh truyện, đọc đến đâu ông nhớ đến đó, lại đọc thuộc hàng chục bài thơ Nôm.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HVB_003_0740</t>
+          <t>HVB_003_0240</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>供伏可做一代帝王又一處緒軸花畫可做一代駙馬於二者何擇其</t>
+          <t>時夫人他為文矣因拽竹權弄兒戲吟國語詩曰月撿弓月撿弓下句未就公在竹樞中郎和云撥魏例忍忍容文武喜以示夫人夫人恚曰月臣象也汝何以此命兒考大慚謝然恨終不釋竟辭歸於父家</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>muốn mấy. Quả nhiên cách mấy năm sau, giữa khoa nhâm tuất (1562) niên hiệu Quang-Bửu nhà Mạc, thầy trò cùng dỡ</t>
+          <t>Một hôm mẹ kéo chiếc que tre chơi với ông, ngâm câu thơ Nôm: «Nguyệt như cung, nguyệt như cung», chưa kịp ngâm câu dưới thì ông ở trong cũi tre liền ứng khẩu họa lại: «Bát nguyệt sơ tam nguyệt lãng dung». Thân phụ mừng rỡ đem khoe với phu nhân, phu nhân giận bảo: «Trăng là tượng của bề tôi, sao ông lại dạy con như thế?» Thân phụ hổ thẹn tạ lỗi, nhưng bà giận không nguôi, bỏ về nhà cha đẻ.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HVB_003_0741</t>
+          <t>HVB_003_0241</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>子曰我家村鄙野人何慼望比所望者世出文儒之地不慼二地</t>
+          <t>公總角時群見洛於寒度南艏北人始相之曰王及諦視又曰惜彼粗只存做狀元宰相故人皆知其為公韓器</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>sinh bảo nhỏ Cậu rằng: Trạng-nguyên khoa này phải nhượng phần thầy đấy nhé, cậu Trĩ cui đầu dạ, dạ.</t>
+          <t>Thuở nhỏ ông chăn trâu ở bến đò Hàn, có khách phương Bắc trông thấy bảo rằng: Cậu bé này có tướng rất quý, chỉ hiềm một nỗi là da hơi thô, về sau chỉ làm đến Trạng-nguyên Tể-tướng mà thôi, vì thế nên ai cũng đoán chắc rằng: ông sẽ là bậc tể-phụ của quốc gia sau này.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HVB_003_0742</t>
+          <t>HVB_003_0242</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>師曰苟如此在貴邑內何事遠求按地自錦章社來龍屈勢如蛇</t>
+          <t>自少時講學家吏既長聞榜眼梁得交文章各世負笈從從之梁公弘化會朝人奉使如明得太乙神經族人梁汝笏之後仍以授公公既造諸玄理見道遂東後染師病篤嘆其子有慶於公公撫之如子教以成名</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>triều : Trạng-nguyên khoa này thế nào cũng lọt vào tay học trò của tôi tên là Duy-Trí đó.</t>
+          <t>Như ông lúc còn niên thiếu, học văn sở đắc ngay từ gia đình, đến khi lớn tuổi, nghe nói có quan Bảng-nhãn Lương-đắc-Bằng, nổi tiếng văn chương quán thế, ông bèn tìm đến để xin nhập học. Lương-Công là người ở làng Hội-Trào thuộc huyện Hoằng-Hóa lúc Ngài phụng mệnh sang sứ nhà Minh, có học được phép Thái-ất-thần-kinh của người cùng họ, tức là dòng dõi của Lương-nhữ-Hốt. Lương-Công rất tinh thông về lẽ huyền vi, đem truyền lại cho ông, đến khi Ngài bị ốm nặng, lại đem con là Lương-hữu-Khánh ký thác với ông, ông săn sóc dạy dỗ chẳng khác con mình, sau này ông Khánh cũng được thành đạt.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HVB_003_0743</t>
+          <t>HVB_003_0243</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>形至詠橋社八首突起二小阜一阜稍大平坦一阜差小勢頗微科一地師</t>
+          <t>光紹間兵變起公隱居教授抱道自樂不求聞達綿元帝皇初年鄭綾公莫登庸皆有挾天子会諸侯之志類年構兵境內大亂公感懸興詩云</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>sách địa-lý đi, chứ để làm gì cho nhầm lấy đến người khác? Quả nhiên năm ấy Phạm-Công được dỡ khỏi</t>
+          <t>Năm Quang-thiệu gặp lúc loạn lạc, ông về ẩn cư để dạy học trò, lấy đạo làm vui, chẳng cầu danh tiếng, nhưng sang đến thời đầu niên hiệu Thống-nguyên thì Trịnh-Tuy và Mạc-đăng-Dung cũng đều có ý hiệp chế Thiên tử để sai khiến chư hầu, hai bên gây cuộc nội chiến khiến cho trong nước chịu cảnh lầm than, lúc ấy ông có cảm hứng một bài thơ rằng:</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HVB_003_0744</t>
+          <t>HVB_003_0244</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>認穴在大阜十次一地師不可即就前面澤澤處浸卧水中貼仰良久方</t>
+          <t>泰和宇宙不虞周五戰交爭笑商答</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Tân kéo đến, 9 khúc triều về trước mặt, huyết kết tại nơi khe nhỏ nhất, lại có cái gò cao đứng cách trước mặt</t>
+          <t>Thái hòa vũ trụ bất ngu chu, Ngũ chiến giao tranh tiếu thượng thu.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>HVB_003_0745</t>
+          <t>HVB_003_0245</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>起日我已驗之果然方在小阜二師爭辨不決因畫成一圖使人北還就諸老師取正老師曰這曷是黃鶴咱蛤其氣在耳兩阜間兩耳也大耳是</t>
+          <t>川血山骸淵魚羊殼雀為誰驅</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>quyết khoa, còn ông thầy Tàu vì lập sai hướng, nên tuy</t>
+          <t>Xuyên huyết sơn hài tùy xứ hữu, Uyên ngư tằng trước vị thùy khu?</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HVB_003_0746</t>
+          <t>HVB_003_0246</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>等小耳是微科有氣旁必在杳其子即依言移公藝之坐恩向坤至三世</t>
+          <t>重興巴下渡江馬後憲應防八室龜</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>tương kỳ, vật đã tiêu hiềm giới ý, Nghĩa là: Kẻ trượng phu chỉ khí hẹn hò, truyền nhỏ nhất đừng nên để ý.</t>
+          <t>Trùng hưng Ba Hạ độ giang mã, Hậu hoạn ưng phòng nhập thất quy.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HVB_003_0747</t>
+          <t>HVB_003_0247</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>文徽以明德翼登庸乙丑科中探花官至尚書致仕其三子伸調以永定</t>
+          <t>世事到頭休說著醉吟澤畔為閒這</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Thái-Bửu, sinh hạ được 3 con giao, con trưởng làm chức Tri-huyện Gia-định, con út làm Tri-bạ, được phong chức</t>
+          <t>Thế sự đáo đầu hưu thuyết trước, Túy ngâm trạch phán vị nhàn du.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HVB_003_0748</t>
+          <t>HVB_003_0248</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>奠福原丁未科中黃甲官亦至尚書日達善以光寶員乙未科中黃甲仕</t>
+          <t>蓋知教民當復與始雖備安終必復興國而室韜其隱語也</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Ngưỡng hậu thô giám làm hâm nạp, Tí vong hồn phần mộ</t>
+          <t>Sở dĩ có bài thơ trên, vì ông biết rõ nhà Lê sẽ được trung hưng, dẫu rằng ngày nay tạm phải tìm kế an thân, nhưng rồi sau đây tất nhiên sẽ lại khôi phục được nước.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HVB_003_0749</t>
+          <t>HVB_003_0249</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>以淳福年考乙丑科中進士至侍郎其孫教方</t>
+          <t>阮鼎革偸檄四方乎親明委勸之仕公元四十始就鄉試領首選莫大正六年癸巳未春公年四十五赴會試四場並第壹廷對擢進士及第授東閣校書和莫太宗所制表春天御講二詩皆頒優等刑部左侍郎俄遷吏部左侍郎業東閣大學士在朝八年疏劾弄臣阮世小者十八人請悉誅之其志欲使萬物各得其所微而致慧亦比自授以敬卜葉恐值壇防端貴橫恐累連姻遂托病致仕時公元五十二</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Truyền gia kẻ gia, lộc thêm đưa nò. Xuất tướng nhập tướng, tài được nỗi sinh.</t>
+          <t>Quả nhiên về sau nhà Lê trung-hưng, bốn phương trở lại yên tĩnh, bấy giờ bạn hữu đều khuyên ông ra làm quan, đến năm 44 tuổi ông mới chịu ra ứng thí, khoa hương thí ấy ông được đỗ đầu, rồi năm sau tức là năm thứ 6 đời nhà Mạc, lại ra tỉnh thi được đỗ thứ nhất, khi vào đình đối lại đỗ Tấn-sĩ đệ nhất danh, được bổ chức Đông-Các Hiệu-Thư, trong thời Thái-Tông nhà Mạc, ông có làm hai bài thơ Xuân-thiên ngự-tứ, đều dự hạng ưu, rồi thăng chức Hữu-Thị-Lang Hình-bộ, sau thời gian ngắn lại thăng chức Tả-Thị-Lang, kiêm chức Đông-Các Đại-học-sĩ. Trong 8 năm ở triều, ông có dâng sớ hạch tội 18 kẻ nịnh thần, xin đem chém để làm gương, nhưng rồi gặp phải sự cản trở, vì sợ liên lụy đến mình, nên ông cáo quan xin về trí sĩ. Thế là giữa năm Quảng-Hòa thứ 2 ông mới 52 tuổi đã xin trí sĩ, treo mũ về làng, dựng am Bạch-Vân ở phía tả chỗ làng ông ở, và vẫn lấy hiệu là Bạch-Vân Cư-sĩ.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HVB_003_0750</t>
+          <t>HVB_003_0250</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>之文知江漢之水愈出愈奇四代孫福胡王以陽德繼中興嘉慶末科</t>
+          <t>既歸田里起白雲庵於鄉之士仍號名士起逐風長春等橋歲時遊態築中津館於雪江之津作碑以記其父又修葺佛寺構老僧同遊時或扁舟泛金海郁海觀魚宴子卧雲散主塗山諸各山皆自杖履登臨適意嘆咏往來或徜徉終日每遇樹木青幽時鳥變聲輒欣然自得公雖在家莫事以師礼國有大政事輒遣使就訪或時徵至京詢以大計從容規畫禪蓋弘多尋復還庵頤志後以功封程川候累陞夫部尚書太傅程國公</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Quang-Hung năm thứ 16 đời Lê-Thế-Tông (1596), Mạc-Khang-Hựu chiếm đóng thành Phao-Sơn</t>
+          <t>Khi ấy ông có bắc hai chiếc cầu Nghinh-Phong và Trường-Xuân để khi hóng mát, dựng một ngôi quán gọi là Trung-Tân ở bên Tuyết-Giang, có bia để ghi sự thực. Ngoài ra ông còn tu bổ chùa chiền, có lúc cùng các lão tăng đàm luận, có khi thả một con thuyền dạo chơi Kim-hải Úc-hải để xem đánh cá. Còn chỗ danh sơn thắng cảnh, như núi An-Tử, Ngọa-Vân, Kính-Chủ, Đồ-Sơn, nơi nào ông cũng chống gậy trèo lên, thừa hứng ngâm vịnh quên cả sớm chiều, mỗi khi thấy chỗ rừng cây xanh tốt, chim đổi giọng ca, thì ông hớn hở tự đắc, quả là một vị Lục-địa Thần-tiên. Nhưng trong thời gian dưỡng lão ở chốn gia hương, tuy rằng không dự quốc chính, thế mà họ Mạc vẫn phải kính trọng như một ông thầy, những việc trọng đại thường sai sứ giả về hỏi, có khi lại đón lên kinh thành để hỏi, ông đều ung dung chỉ dẫn, nhờ được bổ ích rất nhiều. Xong rồi ông lại trở về am cũ, về sau được phong tước là Trình-Tuyền-Hầu, dần dần thăng đến Lại-bộ Thượng-Thư Thái-phó Trình-Quốc-Công.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HVB_003_0751</t>
+          <t>HVB_003_0251</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>中會元再中東閣仕至都臺公坦德敦國益相鄰緒北省其苗裔商今</t>
+          <t>公博極聲書深明易理雨暘水旱禍福災祥存亡得喪之因無不前知常與門人張時舉卜易則乾卦而知八世之後起戈千其神祕淵奧不能盡述授徒甚眾惟馮克寬篤有慶阮璽張時舉最著</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>thư, Đông-Các học-sĩ, Quốc-từ-Giám, Tế-Từ, Thiếu-báo</t>
+          <t>Nói về môn sinh của ông sự thực không biết bao nhiêu mà kể, nhưng nói riêng về những người đã có tiếng tăm lừng lẫy thì có những ông như Phùng-khắc-Khoan, như Lương-hữu-Khánh, Nguyễn-Dữ và Trương-thời-Cử, đều đã nhờ ơn truyền thụ.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HVB_003_0752</t>
+          <t>HVB_003_0252</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>旋中相傳諸預登紳甲者面必微科蓋地氣之所鍾也卻說頭乃文微</t>
+          <t>初克寬假館遊學事既卒業公夜叩門語之曰鷄鳴矣夜既明矣何不起而作食堅固何為寬悟遂請八清仕歸阮氏後扶樑中興為各臣興隱居不仕作傳奇謾錄公亥為斧正遂為千古奇筆</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>phủ đầu để là Quang-võ được mã phú , ông</t>
+          <t>Nhắc lại khi Phùng-khắc-Khoan còn theo học Bạch-Vân Tiên-sinh, lúc thành tài rồi bỗng có một đêm Tiên-sinh đến chỗ nhà trọ của ông, gõ cửa bảo rằng: «Gà gáy rồi đây, sao anh chưa dậy nấu ăn, mà còn nằm ỳ ở đó», Khắc-Khoan hiểu rõ ý thầy nên vội thu xếp vào vùng Thanh-hóa, cùng ẩn cư với ông Nguyễn-Dữ, trong thời gian ấy Nguyễn-Dữ có soạn ra bộ Truyền-Kỳ-Mạn-Lục, được ông phủ chính rất nhiều, cho nên mới thành một cuốn Thiên cổ Kỳ bút.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HVB_003_0753</t>
+          <t>HVB_003_0253</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>次子火領鄉舉惟善飲酒懶廢學業見海陽處隨號嘗往珥</t>
+          <t>時阮太祖曰我兵大振數戰神符讙王莫敬兵敗世祖因進兵由西山累京北中外皇皇誠獻以實虛計境內靳日寧我朝順平八年中宗崩無嗣太祖有特疑意詢之焉竟寘不詔決因使寬家人饗厚禮潛往海陽訪之公弗答但顧家童曰方今不穩在於粟穀不奸爾等可覓雀鴉穀種種之又命鳥遊寺僧童酒榼焚香餘無所及蓋徵示以事佛獎綿底意寬具馳苦太祖乃悟遂立英宗</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Thể sau ông phê hai chữ minh khoái , nghĩa là : sáng sửa khoái hoạt, nhưng</t>
+          <t>Năm Thuận-bình thứ 8 Lê Trung-Tông mất, không có hoàng nam nối ngôi. Thế-Tổ do dự không biết lập ai, hỏi Trạng-nguyên Phùng-khắc-Khoan, cũng không quyết định nổi, nên mới phải sai gia nhân ngầm đem lễ vật về tận Hải-dương để hỏi, ông không trả lời mà chỉ quay lại bảo các gia nhân rằng: «Vụ này lúa không được mẩy, chỉ tại thóc giống không tốt, vậy các người phải đi tìm giống cũ để mà gieo mạ». Nói xong ông lại lên xe ra chùa, sai các chú tiểu quét dọn đốt nhang, ngoài ra không hề đả động gì đến chuyện khác, bởi vì ông đã hé mở cho biết cái thâm ý là «cứ việc thờ phật thì được ăn oản». Rồi Trạng Phùng thấy thế vội vàng về báo, Thế-Tổ hiểu ngay, bèn đón Anh-Tông về lập, tình thế trong nước mới được ổn định.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HVB_003_0754</t>
+          <t>HVB_003_0254</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>河竹木津邊明儔對飲通就河津濯行見竹筏上有紱字在焉拾而</t>
+          <t>范舍人與公又同鄉誼嘗密使人請公為子求一條生路使者以銀一包為贄拜祈不已。如適策杖後圍圍後有數十石塊答石嵌出橫繞軒前有群議縁石而行公徐目蟻而矢曰橫山一帶足以容身使者悟其意歸以告洪洪乃以計頴廣順遂蟠撫焉為隂氏</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>trong Hàn-uynh tập và Ky-anh tập, cùng hơn 10 bài thơ mừng Đạo-phái Hầu đạo ấp sang sử Bắc quốc, lời văn</t>
+          <t>Trong thời gian ấy Đoan Quốc-Công Nguyễn-Hoàng là con Chiêu-Huân Tĩnh-Vương, đương lúc ở trong tình thế nguy ngập vì sợ không thoát khỏi tay Trịnh-Kiểm, thân mẫu của người vốn là chỗ đồng hương, nên thường bí mật sai người về làng nhờ ông chỉ giúp cho con giai bà một đường sống. Sứ giả đặt gói bạc nén ở trước mặt ông, rồi bái lạy lia lịa. Ông thấy sứ giả năn nỉ xin mãi nhưng vẫn không nói gì, rồi đứng phắt lên, tay cầm chiếc gậy thủng thỉnh ra lối vườn sau, là nơi có hơn 10 tảng đá xanh xếp thành một dãy núi giả quanh co, trước núi lúc ấy có những đàn kiến đương men tảng đá leo lên, ông ngắm nghía chúng một lát rồi mỉm cười và đọc một câu: «Hoành-sơn nhất đới khả dĩ dung thân», nghĩa là một dãy Hoành-Sơn có thể dung thân được đó. Sứ giả hiểu ý trở về thuật lại với Nguyễn-Hoàng, Hoàng bèn xin vào trấn thủ Quảng-Nam.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HVB_003_0755</t>
+          <t>HVB_003_0255</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>觀之乃是舊賦一箇因記之燕燭每飲酒後輒叩盤歌詠習以為常乙丑</t>
+          <t>莫延歲八年發洽年號乙酉十一月公寢疾莫蒼治使人心問且語以國事公但曰他日國有事故高平難小可延數世福他無所言後七年莫之乾統隆泰順德永昌退保高平歷三世四十七十年而後泯其言無不騐類如此</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>danh nho của một thời đại vậy! Ngày nay xét lại sự tích của ông, trước kia cũng có</t>
+          <t>Mạc Mậu-Hiệp năm Diên-Thành thứ 8 tức năm Ất Dậu tháng 11 thì ông lâm bệnh, Mậu-Hiệp sai sứ đến vấn an và hỏi về quốc sự. Ông chỉ trả lời rằng: «Sau này quốc gia hữu sự thì đất Cao-bằng tuy nhỏ cũng giữ thêm được mấy đời», ngoài ra không nói gì nữa. Quả nhiên cách 7 năm sau thì họ Mạc mất, rồi rút lui lên giữ Cao-bằng được 70 năm, nghĩa là sau 3, 4 đời thì mới hoàn toàn bị diệt, coi đó thì lời của ông dự đoán chẳng sai chút nào.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HVB_003_0756</t>
+          <t>HVB_003_0256</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>科八第一場得親朋友之助頸在中第至第二場携酒而入坐間醉酒睡著</t>
+          <t>是月二十八日公薨于家壽九十五學者尊為雪江夫子葬于鄉之原</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bài số 22 Giải nghĩa Câu 1: Ngô: ta, hà: cái gì, Ái: yêu, Ái: yêu, duy: chỉ</t>
+          <t>Nhưng rồi trong tháng ấy giữa ngày 28 thì ông tạ thế, hưởng thọ 95 tuổi, học trò suy tôn hiệu là Tuyết-giang phu-tử phần mộ ở trên một cái gò đất trong làng.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HVB_003_0757</t>
+          <t>HVB_003_0257</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>日已向暮忽大風驟至塵霧漫天續睡中驚為起輩目觀之見有數片</t>
+          <t>公胸依酒落天資極高而充養補裨渾然不露圭角人不問則不言言則必中從容就事不見其有為居家四十四年而其心未嘗一日而亡世憂時愼俗一發於詩文章出於自然天口輒成不事雕琢簡而暢淡而味皆有觀於世教所依國語詩賦甚多著日雲詩集未千餘首今行于世者百餘首父中津賦而止然觀其大略齊月光風千古猶可想見公嘗有詩云高潔誰為天一士安閒我是地行行傳蓋自言其志也妻二人子十六男女五長子號寒江魏士蔭受惠員夫大生切德切德生道進道進生道通道通生登瀛登瀛生時當時當年六院十五有男子效人皆八世孫也按廣鄉之西南潭淤四五聚高亦可數四敵深泓一大許同光照鍾秀毓英宜其達人者尚焉古鉗云研池水暎豈不信然其後清使周粲謂嶺南人物理學有程泉筆之於書而傳於中土公詡宮國</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>vân: mây, sắc: màu sắc, lão: già, âm đạm. Ngước mắt trông lên giới thấy có màu âm đạm của mây.</t>
+          <t>Xét thấy ông là người khơi ngoan tuấn, học hết các kinh sách lại rất tinh về lý thuyết kinh dịch, phạm việc mưa nắng, lụt hạn, hoa phúc, điểm dữ điểm lành cơ suy cơ thịnh v.v... việc gì ông cũng biết trước. Ngay trong lúc ông còn mở trường dạy học có một học sinh họ Bùi người xã Trung-hàng thuộc huyện An- dương, là người rất thạo về văn án. Ông bảo hậu vận của anh thế nào cũng được giàu sang. Nhưng mãi đến khi tuổi gần 70 mà bước công danh vẫn thấy chất vật như thường, nên anh nói nhỏ với các bạn rằng : Lý sở của thầy thân điều đến thế, mà cũng có chỗ sai nhầm hay sao. Ông thấy học trò bàn mảnh với nhau như vậy thì cũng mỉm cười chứ không nói gì. Nhưng rồi bỗng có một hôm ông bảo trò Bùi đi thuê lấy 10 chiếc thuyền đánh cá, kéo buồm vượt thắng ra cửa Vạn-Ninh rồi rẽ vào đầu ở trong khoảng Đàm-hồng, đợi đến đúng hôm nào đó, hễ thấy vật gì cứ vớt đem về, tất nhiên sẽ được trọng thưởng? (Mạn sự Tản , Vạn-Ninh, Đàm-hồng). Trò Bùi thấy thấy đây bảo như vậy hơn hổ vui mừng, theo đúng như lời, chuẩn bị thuyền ghe kéo ra Đàm- hồng chờ đợi. Bỗng thấy một chiếc thuyền dương bị sóng gió dồn dập. Anh với cùng đoàn thủy thủ lướt sóng tiến ra, nhìn vào trong khoang chỉ thấy có một bà lão ẩn vận ra dáng cung phi, đương nằm ngất xỉu! Anh bảo gia nhân đỡ sang thuyền mình đưa về tìm phương cứu tính rồi anh đưa về phượng sự như thế mẹ già. Sau một thời gian thì viên Tổng-đốc Quảng-dong có sai sứ giả sang ta nói rằng: Vì Thái-phu-nhân một hôm đáp thuyền ra bể, chẳng may bị nạn phong ba, nay coi thiên văn biết rằng Bà hãy còn sống, hiện ở địa phận nước Nam. Vậy xin qui quốc vì nghĩa lân bang, sai người tim hộ, bồn chức không giám quên ơn v.v.. Lúc ấy triều đình nhà Mạc tiếp được thư trên, cho thông sức đi khắp các nơi, hứa rằng hễ ai tìm thấy sẽ được hậu thưởng. Nhận thấy lệnh trên, anh liền sắm sửa xe vồng đưa Bà ra hiện tại kinh thành, Mạc chưa ban thường rất hậu, và lại được bồ quan chức, về sau phong tước đến Thao-Quốc-Công! . Năm Thuận-bình thứ 8 (1556) Lê Trung-Tông mất, không có hoàng nam nối ngôi. Thế-Tồ</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HVB_003_0758</t>
+          <t>HVB_003_0258</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>紙字飛到其前收來紬認乃是四六體文續喜曰此天賜吾也依樣寫</t>
+          <t>進士繚如虎記</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Câu 6: Bá: cây Bách-diệp, lặp: đứng, đồng: phương đông, phong: gió, mậu: tươi tốt, tuế: năm, hàn :</t>
+          <t>ĐỒNG NIÊN SONG TẤN THOẠI GIA TƯ?</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HVB_003_0759</t>
+          <t>HVB_003_0259</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>之已而果中至第三場賦題乃前日所得舊賦者更預中第追至四</t>
+          <t>黎胡燕仙侶仙洲人也少南處生而岐嶷及長體大過人高五尺五寸家貧好學性善飯父母嘗羹七歲餳飯公食無餘學得半年以家計不贍出為善片社富家贅婦翁食以五歲鍋飯輒嗜臥廢學亦公疑之以問公之父曰聶聞君言有佳婿是好學的人而今懶廢不知有何緣故父曰兒自蒙托愛公毋食之知何翁曰飯五歲鍋矣父曰無雖家用不數此兒尚有七歲餌之食今如此相待其不學也固宜爾聞言輒加倍焉</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Câu 3: Thiên : giới, hạ : dưới, hữu : có, thiên : giới, xuân : mưa xuân, bất lão : chẳng già.</t>
+          <t>Ông Lê-như-Hồ (triều nhà Mạc) người xã Tiên - Châu thuộc huyện Tiên-Lữ lúc mới sinh ra trong rất vạm vỡ, đến khi lớn lên, thì người cao tới 5 thước 5 tấc, khoảng lưng chu vi đến một thước năm, Ông vốn có tính chăm học chỉ phải cái tật ăn khố mà nhà thì nghèo. Mỗi bữa cha mẹ nấu cho đến nồi 7 cơn mà Ông cũng ăn hết nhẫn. Vì thế cha mẹ chỉ cho theo học được đến nửa năm thì hết lượng thực, đánh phải cho sang gửi rể ở nhà phù Ông bên xã Thiện - Phiên, cha vợ cho ăn một nồi 5 cơn, thì ông chỉ nằm suốt ngày không hề mò đến quyền sách. Cha vợ lấy làm nghi hoặc hỏi cha để rằng: Trước kia tôi thấy Ông bảo Cậu nó là người chăm học, mà nay lười biếng như vậy, là có làm sao? Cha để hỏi lại: Được Ông quá yêu cho cháu sang ở bên ấy, vậy thì mỗi bữa Ông cho cháu ăn bao nhiêu? Cha vợ đáp: Mỗi bữa một nồi 5 com cơ đấy! Cha để mỉm cười nói: nhà tôi dẫu tùng cũng phải cho cháu ăn 1 nồi 7 com! Ngày nay Ông cho ăn ít như thế thảo nào nó chả nhắc học. Cha vợ biết thế cho ăn tăng lên ti chút.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HVB_003_0760</t>
+          <t>HVB_003_0260</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>場日學業文廢不能措一辭因取晉侯國語舊傳凡諸鄙俚者換</t>
+          <t>公自是始索書目讀一二歲耳安世有不足處謂顧曰擇得一好婿來雖勉強讀書只要善食終焉做得何事辦鮮之曰他食兼人之食必有兼人之勇母曰苟如此我有田草始無試使他刲了公聞之郎取刀出林頭榕樹下假臥速象母牲市同見而嗔之郎歸告其六翁曰今猶多造飯與他吃否託言刈草自旦至歸市猶在一處打眼因橋翁手往想不意自岳母歸後公郎就田刈之神觀瞻息間效敵草間俱盡魚走之不及所浮邀收換不可勝計地舅媽來見之因嗟訝不已</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ông Dương-công-Tôn người xã Lục-Dương huyện Chi-linh về văn học đáng được người đời</t>
+          <t>Bấy giờ cậu mới tìm sách để đọc qua loa, mẹ vợ thấy vậy có ý bất mãn bảo với Ông rằng: Ông khéo kén chọn con rể, chỉ được cái nết ăn khỏe mà thôi, còn sự học hành như thế, thì sau nó làm nên được những trò trống gì. Ông giải thích rằng: Điều đó bà đừng lo ngại, vì nó ăn khỏe hơn người, tất nhiên nó cũng có sức hơn người đây chứ. Bà đáp ừ nếu quả như vậy, thì nhà ta đây hiện có mấy mẫu ruộng rẫm, thử bảo nó ra phát có xem sao. Cậu thấy cha mẹ vợ bàn mảnh với nhau như vậy, sáng sớm hôm sau Cậu liền vác một con dao thật lớn xin ra phát có ngoài đồng, nhưng ra đến nơi thì Cậu lại nằm giả ngủ dưới gốc cây bàng. Đến khi mẹ vợ đi chợ về trông thấy tức giận dấy ruột, chạy về la lối om xóm: Ông oi từ nay Ông còn bảo nấu thêm com cho nó ăn nữa hay thôi. Hôm nay nó muốn tiếng ra phát cổ, thế mà từ sáng sớm cho đến lúc tôi về chợ, nó vẫn còn nằm ngủ dài ở dưới gốc cây. Chá tin thì Ông ra mà coi thử. Thế rồi bà tóm lấy tay dẫm ông ra thẳng cánh đồng. Nhưng bà có biết đâu rằng con rể của Bà vẫn nằm giả ngủ, đợi Bà đi khuất thì Cậu lập tức vác dao xuống ruộng phát lấy phát đẻ, chỉ trong chốc lát thì mấy mẫu cỏ đều đã quang lăng! đến cả tôm cá đều không chạy kip nên bị chết nỗi nhan nhân vót được rất nhiều. Khi hai Ông bà tới nơi, cũng phải hết sức kinh ngạc.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HVB_003_0761</t>
+          <t>HVB_003_0261</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>以新聲每句撥成輒需乘醉吟詠采察官見之謂曰天日已晚入皆</t>
+          <t>其後穀嘉時岳母使公往市喚傭工來公乍出輒囘報云其小已喚之無肯行者時家中已養二十歲鵠飯以待工人而無有二公輒取餌來食之殆盡吾母喚之曰這飯吃了不幾成賜破那腹耶公曰媽媽不須委惱今番經刈某請獨當遂袖弄一大段為俗曰：槴乾，幷參大繩以往繞半月，復餘二畝，殆盡，各束為四捆而回，每捆由是愛之仍許以飽食就學</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>bài Cao-Tổ-Kiểm phú , bài Ngọa-Long phú , bài Bạch-Y-son nhân , bài Áp-tử từ-kê-</t>
+          <t>Rồi sau đến mùa lúa chín mẹ vợ sai Cậu đi mướn thợ gặt, Cậu đi một lát quay về bảo chẳng mướn được ai cả, nhưng mà lúc ấy nhà đã nấu sẵn nồi hai mươi com, Cậu bèn đón com ra ăn hết quen, mẹ vợ lắc đầu báo: Con ăn nhiều quá như vậy, chẳng sợ vỡ bụng hay sao, Cậu thưa: mà đừng ngại! công việc gặt thóc hôm nay con xin đảm đang hết thầy. Ăn uống xong rồi Cậu liền dẫn hai đoạn tre lớn để làm đòn xóc, và chẻ một bó lạt dài quầy ra ngoài ruộng, gặt đến quá trưa thì xong cả hai mẫu lúa! bó thành bốn bó lững thừng quầy về! từ đấy mẹ vợ mới tổ thực tình yêu mến, cho ăn đầy đủ để chuyên vào việc học hành,</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HVB_003_0762</t>
+          <t>HVB_003_0262</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>行文過半而新進士何乃尚番空卷而放浪酣歌乎續酩酊音落頃答</t>
+          <t>公當學時每得紙千張讀了即焚之傍縣有交跌場公郎往取第一標都力士亦不敵較以其有力故各知亮年立辛丑科一舉中進士</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>bài Nghinh-xuân Uyền , và bài Cương-Thổ-phục- Hán-Đường cựu đĩ-Thiên-hạ vi-tâm ,</t>
+          <t>nhưng lạ thay! trong khi học tập, hễ Cậu viết xong trang nào, thì lại đốt ngay tức khắc. Trong thời gian ấy, các vùng lân cận thường hay mở đám hội hè, đám nào có treo giải vật, Cậu cũng xin giữ giải nhất, bao nhiêu lực sĩ đó vật, vi đã biết sức của Cậu nên chẳng ai dám so tài! cho nên người ta mới tặng tên là (Như-Hồ). Thế rồi cách mấy năm sau, khi vừa đúng 30 tuổi thì đã nổi tiếng văn chương, bấy giờ đương triều nhà Mạc niên hiệu Quảng-Hòa (1541 - 46), Ông ra ứng thí được đỗ Tán-sĩ vào khoa Tán-Sửu,</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>HVB_003_0763</t>
+          <t>HVB_003_0263</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>之日欲寫郎寫何難遂寫了這傳授納時同考院有知音者見其</t>
+          <t>時同科有同年阮清弘化人也嘗與公語及家計公戲之曰兄之家資僅足供我一月粮清曰請供三月之頓會不須三月斬請許一頓如何清曰諾約以某日辰臨至</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ở bên cạnh nhà ông Tới đây Cậu muốn nhắn gì? Cậu sỡ sàng đáp: Nhờ bác về báo ông Tới : Thiên</t>
+          <t>lúc ấy có người đồng bảng là Nguyễn - Thanh Ẩn người xã Bột - Thái thuộc huyện Hoằng - Hóa thường khoe nhà mình giàu có. Ông nói bốn rằng: Gia tài của Ông, chỉ đủ dải tôi một tháng là cùng? Thanh đáp: Nếu vậy mời Bác quá bộ vào chơi, tôi xin cung phượng ba tháng là ít, Ông đáp: thời khởi cần nói chi ba tháng, hôm nào tiện dip xin Bác hãy tạm thiết tôi một bữa xem sao? Ông Thanh nhận lời, hẹn dùng hôm nào sẽ xin đón tiếp.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>HVB_003_0764</t>
+          <t>HVB_003_0264</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>詞調清遠每得佳句郎援筆闋之因語諸同院曰這卷寧為我</t>
+          <t>公遂與一僕徒諳清家不意清有事他適公使達于夫人我與兄有舊偶因公事往過有隨從三十餘人須許一頓夫人即喚家童煮十歲鶴飯者三并物食五六盤聚了進之公佯謂其仆曰爾忘喚請從者來既而不見一人公就取盤鍋并物食吃都盡了因致謝而去</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Đại nhân ất tị, tư văn tại ti, thành tập đại kim thanh ngọc chấn, đức hạnh thảo an hành sinh tri.</t>
+          <t>Rồi ít lâu sau, đúng ngày ước hẹn, Ông cùng với 1 tiểu học tới nhà Ông Thanh, chẳng ngờ Ông Thanh đi vắng, ông bèn nói với phu nhân: Tôi là bạn cũ của Bác trai đây, nhân có việc đi qua ghế vào thăm Bác, chẳng may Bác lại đi khỏi, vậy nay có hơn 30 tùy tùng, phiền Bác cho ăn một bữa, phòng có được chẳng. Phu nhân thấy nói là bạn của chồng, với bảo người nhà nấu ngày 3 nồi 10 com và đóng 5, 6 mâm cỗ chính đón bụng ra. Ông bèn giả tăng bảo đưa tiểu học: my ra gọi chúng vào đây, nhưng rồi chẳng thấy có một tên nào. Duy chỉ có mỗi mình Ông ngồi ăn, ăn hết mâm này lại đến mâm khác, khi ăn quan cả bấy nhiêu mâm rồi Ông mới cáo biệt ra đi.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>HVB_003_0765</t>
+          <t>HVB_003_0265</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>院獨私當送與亞覆考獻笑既而覆考官會者以為戲談大笑</t>
+          <t>逮暮清歸夫人語之曰我家今日有一事好笑請問故夫人笑道早有一人自稱與君相善多帶從人者來求獵予一頓妻發並辨以待不謂只有一酌人坐吃妄自竊視見一碗數口恰似風捲雲殘三盞飯並五六食盤一時俱盡不知是人是怪清悔之曰此必我同年儒洲人也我昨日有約惠然肯來今卻忘之必被吾兄見責</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Quan trường thấy vậy không dám lấy dỡ</t>
+          <t>Chiều hôm ấy Ông Thanh thoát về đến cửa, phu nhân với ra nói ngay: Cậu ơi: nhà ta hôm nay có một câu chuyện rất là buồn cười; Ông hỏi chuyện gì? phu nhân mỉm cười đáp: Sáng sớm hôm nay có một ông khách đến chơi, nói là bạn thân của Cậu, nhân đi công cán qua đây, hiện có đem theo mấy chục tùy tùng, nhờ tôi sửa giúp cho một bữa cơm. Chẳng ngờ đến khi làm xong bụng lên, thì lại chỉ có một mình ông ấy ngồi ăn hết cả. Lúc ấy tôi ở trong phòng nhìn ra thấy mỗi tò com lớn ông chỉ và có hai miếng! ăn mau như thế gió cuốn mấy bay! chỉ trong một lát, ăn hết cả ba nồi 10 com và 5, 6 mâm cỡ. Chẳng biết là người hay quí? mà lại ăn khỏe lạ lùng như vậy. Ông Thanh nghe vọ kề xong tỏ vẻ hối hận nói rằng: Thôi thôi! chính là Ông bạn quê ở Tiên-Châu, trước kia tôi có hẹn Ông vào chơi, chẳng ngờ ngày nay quên bằng đi mất, thế nào anh ấy cũng trách là kẻ vô tình?</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HVB_003_0766</t>
+          <t>HVB_003_0266</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>周一場聲聞于外采察官見問全院具道其事考訖即擇諸中</t>
+          <t>後清因回家途經像洲郎詣公訪舊公屬家人整燕肥豬二隻又資盛二盞同坐款待清契盡豬款各一角公契盡豬一隻又款一盤又契清新餘各一角只需其半以與狹人相吃溝大驚曰古稱慕澤先生以食為各但又于十八十二之數若與兄同時適避三舍矣公大笑</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Quan trường thưa rằng: Chỉ còn có mỗi</t>
+          <t>Thế rồi cách ít lâu sau, Ông Thanh nhân lúc về quê đi qua Tiên-Châu có ghé vào thăm Ông Hò, Ông bảo gia nhân giết hai con heo luộc chín, và 4 mâm xoi để thết đài bạn! về phần Ông Thanh chỉ ăn hết có 1 góc, còn Ông Hò thì ăn hết cả 3 mâm xôi và một con heo, rồi lại ăn sang một góc của Ông Thanh, chỉ còn để lại một nĩa cho người theo hầu, khiến cho Ông Thanh hết sức kinh ngạc nói rằng: Đời trước khen Mộ-Trạch Tiên-Sinh là người ăn khỏe, nhưng chỉ đến số 12 (cạnh) 18 (cơm) mà thôi, vì thử đồng thời với Bác thì còn kém Bác đến 3 dặm vậy, Ông Hò dắc ý cả cười.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>HVB_003_0767</t>
+          <t>HVB_003_0267</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>卷者適同候旨時上以其取中頗少亟差往命增取之諸考官對</t>
+          <t>其後官歷左侍郎奉往北使時同縣安照社署人頗有口辨使之從行</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Khảo quan lại thưa: Cứ ý Thần đăng: Quyền ấy không lấy thì thôi, nếu lấy thì nên cho dỡ Thủ-khoa</t>
+          <t>Rồi sau Ông Hò làm đến chức Hữu-thị-Lang, phung mạng sang sứ Bắc quốc, lúc ấy có người lái buôn ở xã An-Chiều an cung huyện, vốn là một người có tài khẩu thiệt, Ông cho đi theo.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>HVB_003_0768</t>
+          <t>HVB_003_0268</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>諸中官曰申格之文這等卷已盡矣其餘無足之取中官以內首見逼</t>
+          <t>至燕京北人聞公善食因作一具十八層召公赴宴架梯而食公每吃了一層輒取鉢擲下至最後層見一人頭在焉傷人皆掩目不敎正視公大聲喚從者來曰書我生不知滋味今皇帝賜我食北人頭最為佳品汝將取醋來我吃了蓋這頭乃魚人頭與人無異世所罕見故他以此怵公今見其不懾頗有侵渡之語即挈取頭去</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>mới xưng. Vương Thượng phán: Chư khanh xét thấy có thể cho dỡ Thủ-khoa thì cứ việc cho, còn ngò chi nữa.</t>
+          <t>Khi tới Yên Kinh, Bắc triều vốn đã nghe tiếng Ông ăn khỏe nhất, nên có sửa một mâm cỡ, chồng chất lên 18 từng rồi triệu Ông vào dự yến! khi ăn phải treo lên thang, ăn hết từng trên thì quảng bát đã xuống đất rồi mới ăn đến từng dưới. Chẳng ngờ khi ăn đến từng dưới cùng thấy có một cái đầu người. Ông bèn lấy dưa xuyên vào hai mắt rồi giao cao lên, làm cho những người chung quanh đều phải bịt mắt chó không giám nhìn. Ông bèn thét bảo quân lính theo hầu: Ta đây là kẻ Thư sinh chưa nếm những món ăn là bao giờ, ngày nay Hoàng - Đế cho ăn số người Bắc quốc! hẳn là món ăn rất ngon. Vậy thì các chủ kip đem tương dẫm lại đây để cho ta chén nghe. Nguyên cái số ấy tức là số con nhân ngư (cả người) trong y như số người thực, mà đời ít khi được thấy, cho nên họ mới dùng nó để thử thách Ông, nay thấy Ông đã chẳng sợ lại còn nói xược như vậy. Họ liền xách ngay cái số ấy đi,</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>HVB_003_0769</t>
+          <t>HVB_003_0269</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>考官曰所存者晉侯一卷外此更無中官郎馳回具奏有首判云晉侯</t>
+          <t>尋托以他爭篤其兩目使人撓之自曼所而往三日復就這賣因問公何賣否公已默記其心郎答云乃前日賜晏賣也北人謂公莊前知遂敬之</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Thượng-Thư, Thượng nghe lời lập tức thăng ông chức Thượng-Thư Công-bộ, tước Đinh-xuyên-hầu, để bưng sách</t>
+          <t>rồi vùn vào một cờ khác để bịt mắt Ông lại, cho người công đi an trí một nơi, sau một vài hôm chúng lại đưa về chỗ cũ, hỏi Ông có biết đây là nơi nào. Vì Ông đã đề tâm từ trước, nên giả nhồi ngay rằng: Chính đây là chỗ ăn yến hôm trước chứ còn nơi nào. Người Tàu tưởng Ông là bậc tiên-tri, nên mới tha cho lối trước.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>HVB_003_0770</t>
+          <t>HVB_003_0270</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>不取更取何人郎傳與考官批取饒而返同觀之葉已取中輒藏不匿以宣</t>
+          <t>時國上連月不雨仍命諸國陪臣修文橋雨公料知天象未雨因奏曰臣小國乞後讓大國先之已而祈之皆不應皇帝郎命公對曰有從人學得武公遺法嚴乎風喚雨可遣皇帝郎召之其人奏曰臣有一法須得吉日方可用乃潛觀櫪木根俗曰已見白父鷄頸草俗曰鷄鵠有黠自知兩期將至即請設壇場禱之已而果得兩皇需大稱賞封為兩國之師封公為兩國尚書</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>sao được. Vi ông vừa mới bị Thượng giữ lại, không dám xin nữa, cho nên ông mới giả nhồi bằng câu hải</t>
+          <t>Trong thời gian ấy Bắc quốc đương bị hạn hàn luôn mấy tháng giới! Vua Tàu ra lệnh cho Sư-Thần các nước đều phải viết văn đảo vỡ. Ông thấy điểm giới còn lâu mới mưa nên tàu rằng: Nước Thần bé nhất xin cho làm lễ đảo sau, để nhường nước lớn đảo trước. Quả nhiên Sư Thần các nước đảo mãi cũng đều vô hiệu, bấy giờ vua Tàu mới triệu đến Ông. Ông tàu rằng: Hạ thần có viên tùy tùng vốn học được phép hô phong hoán vỡ của Không-Minh ngày xưa, nếu sai người ấy cầu đảo tất nhiên sẽ có công biểu, vua bèn cho đi triệu ngay, người ấy (tức anh lái buôn chè) tàu rằng: Thần có một phép nhưng cần phải chọn ngày tốt thì mới ứng nghiệm. Rồi anh lên đi các nơi để xem triệu chúng ra sao. Sau khi nhìn thấy gốc si đã đâm rễ trắng, cỏ gà cũng điểm lóm đốm, biết rằng sập mưa đến nơi, bấy giờ anh mới tàu xin lập đàn câu đảo, quả nhiên mưa xuống âm âm, vua Tàu khen ngợi phong làm Lưỡng quốc Quốc - Sư. Còn Ông thì được phong làm Lưỡng quốc Thượng-thư.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>HVB_003_0771</t>
+          <t>HVB_003_0271</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>露後績仕至兵部左侍郎會我朝中興出首左遷宣光處承使魯任按</t>
+          <t>公善辭命應對名聞兩朝皇帝欲晉之使教太子公難之不敬遠奏請造一新堂并備鞭模教具皇子出有過輒痛加筆箋矣曰先學禮後文學太後酷愛其子奏請擇導官公以是免歸</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Rồi sau đến ngoại 80 tuổi ông mới trí sĩ với chức Công-bộ Thượng-Thư và tước Thiếu-bảo Cẩm-</t>
+          <t>Riêng Ông sở trường về từ mạnh ứng đối, vua Tàu muốn giữ lại để dạy các Hoàng - tử; ý Ông không muốn nhưng không giám trái lệnh, nên mới tàu xin cho đặt học đường riêng ra một chỗ, rồi sai sắm sửa các thứ roi vọt, hễ Hoàng-tử nào có lỗi Ông đánh rất đau và bảo cho biết, trước phải học lễ rồi sau mới học văn! Hoàng-hậu vốn yêu dấu con, không thể nhận được bên xin vua chọn thầy giáo khác, thành ra Ông được trở về nước nhà,</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>HVB_003_0772</t>
+          <t>HVB_003_0272</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>自有科目以來諸預中格者必是文理可取茲以國語傳取中頗微訛</t>
+          <t>國後任至尚書春江侯陸少保佀郡公致仕耳</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>tục, tạo riêng khuôn mẫu văn học của một nhà nho, bao nhiêu văn tự ứng chế trong triều cũng do một tay ông</t>
+          <t>làm đến Thượng - thư phong Xuân-Giang-Hầu và trước Thiếu-Bảo-Lữ-Quận-Công rồi mới Tri-sĩ hưởng thọ 72 tuổi...</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>HVB_003_0773</t>
+          <t>HVB_003_0273</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>傳或者是時莫朝取士無章故有此異爭亦以見其為學在人而中否</t>
+          <t>傳公卒後國王頒以嗣棺差人會葬今村內猶有遺塚在焉其後人自北歸國王命築室于本社寺及平置庵于其側號國師寺至今香火猶存焉</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>thảo. Lúc về tri sĩ ông soạn 3 thể tạ văn, mỗi thể một khác chứ không trùng điệp, hiện còn ghi cả trong tập</t>
+          <t>Theo như tục truyền thì lúc Ông mất Vua ta có ban cho một cỗ áo quan bằng đồng, và vua bên Tàu cũng sai quan sang đưa dặm, hiện nay mồ mà vẫn còn thấy ở trong thôn. Còn anh lái buồn theo Ông khi ở Tàu về Vua ta cũng sai dựng nhà ở bên cạnh ch a của làng ấy, và lấy danh là chùa Quốc-sur, ngày nay nhang khói vẫn còn.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>HVB_003_0774</t>
+          <t>HVB_003_0274</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>之中有天數存焉近日有監生者八省試第四場文理不成卻寫國</t>
+          <t>在曰營接這跡內有一二事頗淡訛傳但得子公族人之言且參諸村邑高年所道來無異故畧記之以俟大德君子焉</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Nhưng nay chỉ còn thấy có mấy bài, như là bài phu Duy nghĩa-lý phong niên phú ; và bài văn-</t>
+          <t>Xét sự tích này bên trong cũng có vài việc hầu như ngoa truyền, nhưng đó là những câu của người trong họ Ông sau này thuật lại. Và các bô lão ở vùng lân cận cũng đều kể lại như thế. Cho nên mới ghi lại đây để đợi các vị quan tử sau này chấp chính.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>HVB_003_0775</t>
+          <t>HVB_003_0275</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>音雜技投納試場官論以無為行仍論失監生袁訢幸免是為</t>
+          <t>范鎮杜注記</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>khứ-Tật, Hoặc-khứ-Bệnh, tật bệnh khứ trừ, đối với Hán- duyên-Thọ, Đỗ-duyên-Niên, thọ niên duyên vĩnh.</t>
+          <t>LIÊN LUYẾN LƯỢNG KHÔI TRANH TỔ ĐẠO,</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>HVB_003_0776</t>
+          <t>HVB_003_0276</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>效類準之戒為初學</t>
+          <t>海陽之嘉福藍橋社范鎮阪林社杜汪里開相鄰舊傳杜汪邑中有女精者往往興大祟作變幻百出祈禱願有驗焉注少時臨窗閱書夜間常見一手自窺前伸八汪知其為妖就質諸同縣老法師法師夜間常見一手自應節伸入汪知其箋效就質詣何舉才之師注師手果不肐縮大將曉窻下哀訴曰公當大貴我眉戲耳何忍至此極也</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Tiên sinh vốn là bạn</t>
+          <t>Phạm-Trần ở xã Lam-Kiều thuộc huyện Gia-Phúc và Đỗ - Uông ở xã Đoàn - Lâm hai làng giáp với nhau. Tục truyền rằng: trong ấp Ông Uông có một con nữ yêu tình thời thường hiện hiện, tác yêu tác quái biến ảo khôn lương! dân làng yểm đảo mãi mà vẫn vô hiệu. Về phần Ông Uông lúc còn niên thiếu, một đêm đường ngời đọc sách ở trong cửa sổ, bỗng thấy phía ngoài có một cánh tay thò vào. Ông đoán biết là tay con nữ yêu, sáng sớm hôm sau đến hỏi Ông pháp sư già cùng làng. Pháp sư ấy bảo: Từ nay về sau hễ thấy nó thò tay vào thì cậu lấy chỉ ngũ sắc buộc lại, tất nhien nó không biến được. Uông nghe pháp sư bảo thế với về sắm sửa đội đến canh khuya lại thấy con yêu thò cánh tay vào. Cậu liên lấy chỉ ngũ sắc buộc ngay vào song cửa sổ, tư nhien tay nó cưng dò, không sao rút ra được nữa, cho mãi đến lúc gần sáng. Nó đứng bên ngoài khóc lóc van lon. Tôi thấy ông sắp trở nên đại qui, nên mới đưa bốn thế thôi, sao mà ông lại nhẫn tâm như vậy?</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HVB_003_0777</t>
+          <t>HVB_003_0277</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>安陽中行記</t>
+          <t>汪曰以我之果做狀元否曰狀元已有范生公當次之汪曰汝有甚灵物即共我觀我便敵汝俄聞嘔吐聲忽見一物似玉在紋手中精光奪目汪有取吝之師解其繫線自是天邑中不聞怪而泣嘆曰精通舟詞章一出人以賞陳吐王稱之在場屋間甚有聲譽鑲常不逮</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>NGUYỄN-CÔNG-DĂNG</t>
+          <t>Ông hỏi: vậy như tài của Ta đây thì có dỡ được Trang-Nguyen hay không? Nó đáp: Trang-nguyen thì đã về họ Phạm, còn ông chỉ dỡ thứ hai mà thôi! Lại hỏi: vậy mi có vật gì thiêng liêng hãy đưa đây ta coi thử, rồi ta sẽ cởi trói cho. Ông vừa hỏi xong thì thấy nó thở ra một vật gì ở giữa bàn tay trong như viên ngọc sáng chói cả mắt. Ông liền cảm lấy bỏ ngay vào mồm nuốt trúng, rồi mới cởi trói cho nó biến đi. Về sau không thấy tác quái gì nữa, mà ông thì cũng từ đấy về sau học một biết mươi, vẫn chương lại càng xuất sắc, ai cũng khen tài nhà ngọc phun châu, khi cùng tập ở các trường ông Trần vẫn không theo kịp.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>HVB_003_0778</t>
+          <t>HVB_003_0278</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>安陽中行有武姓者起世寒微而頗好學時有裴氏來風水師相地釋得</t>
+          <t>光靈員員意崇年號丙辰科會試時年共二十四歲同年同榜至庭試日汪見全題皆素慣今番首選醫我無驗</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>người xã Đại-Tôi thuộc huyện Quế-Dương là người quán quân về từ phú lúc bấy giờ, mà đến cả</t>
+          <t>Thế rồi đến năm Quang-Bửu thời Mạc Phúc-Nguyên (1554-61) gặp khoa thi hội năm Bình-thin, hai ông cùng 34 tuổi, là bạn đồng niên đồng bằng, đến hôm cùng vào thi đình, ông Uông nhận thấy đầu bài nào mình cũng thuộc lòng hết thấy, tin chắc phen này sẽ nắm vững giải khơi - nguyên.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>HVB_003_0779</t>
+          <t>HVB_003_0279</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>地吉塗之亊襄其師謂曰之這曷世世公假未審我家能稱此否既而</t>
+          <t>時鎮在籠中彷彿見傍有兩人一稱韓琦一稱東方朔附耳讀之滔滔不竭鎮寫之不發聞靜謂琦曰須使任致病以減其力俄見杜汪抱腹申吟不能下筆迨鑲過一段泣病方愈故習燕雖多而日力不足既而臚唱鎮中獄元酒中榜眼顯喜語人曰吾今壓倒杜注矣。汪深愬之。</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>làm bài phú Tu-thán Trị-quốc để chê bai vua Thái-Tông và Cao-Tông ngày trước, từ ý rất là</t>
+          <t>Còn phần ông Trần lúc đương viết bài ở trong lều, bồng thấy thấp thoáng có hai bóng người đứng ở bên cạnh, một người tự xưng là Đông - phương - Sóc một người tự xưng là Hán-Kỳ (có bốn chép là Phú bất và Phạm-trọng-Am) ghé vào bên tai đọc lên thao thao bất tuyệt, khiến ông Trần không sao chép kịp. Thấy vậy ông Sóc bảo ông Kỳ rằng: chúng ta phải làm thế nào cho Uông bị ốm để giảm sức văn thì mới thắng nói. Thế rồi chỉ trong chớp mắt ông Uông ốm bụng kêu đau, không sao cảm được bút viết, cho mãi đến khi ông Trần viết xong một đoạn, bấy giờ ông Uông mới khỏi, thành ra sách vở văn thuốc, nhưng lại không đủ thì giờ, cho nên sức văn hơi kém. Đến khi truyền lò (xương danh) ông Trần đỗ Trạng-nguyen, Ông Uông phải đứng thứ nhì tức là Bảng-Nhơn. Ông Trần tỏ vẻ hoan hỉ nói rằng: phen này ta đã đề nói Đỗ-Uông. Làm cho ông Uông tức bực vô cùng.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HVB_003_0780</t>
+          <t>HVB_003_0280</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>受神人罵日本地係我管了汝何人來塗我地不穢必有災殃其人特</t>
+          <t>榮歸日驅繾綣而行。與鬩並驅爭先。不背公讓至獲澤杜蓮溪中橋人曰素聞杜范二公大各今見同日榮歸請詠橋詩一首頒汪相異曰橋屋十有餘間限過七間成詩詩用一句一禽先成者讓先行不得筆道直顯如約立就詩國語八句馬上讀之人皆藥服泣曰這詩已平日素成非臨時所張得吾何讓焉又齊道而行</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>sông Lạc đời vua Hạ-Vũ, rồng ở sông Hà đời vua Phục- Hy, mà đây chính là ông Hoàng-đế nối đời trị nước</t>
+          <t>Đến hôm hai người cùng về vinh quí bài tờ, Uông vẫn đóng ngựa đi ngang với Trần, chứ không chịu nhường, khi về đến chợ Bồng - Khê thuộc xã Hoạch-Trạch, người ở bên cầu thường vẫn nghe tiếng hai ông, ngày nay thấy cùng vinh quí, nên họ xin một bài thơ vinh cầu để làm kỷ niệm. Hai ông thấy dân sở tại xin thơ, lập tức giao hẹn với nhau rằng: chiếc cầu có hơn 10 gian, vậy khi qua được 7 gian thì phải làm xong bài thơ, mà thể thơ thì mỗi câu có một giống cảm, nếu ai xong trước thì sẽ đi trước, còn xong sau thì không được phép tranh cạnh. Hai ông đặt điều kiện xong rồi cùng tiến bước, chẳng ngờ ông Trần ngồi trên lưng ngựa đọc luôn ngay được 8 câu, khiến cho ai cũng kinh phục, riêng có ông Uông thì lại bảo rằng: Thơ ấy làm sẵn từ lúc ngày thường, chứ lúc làm thời thì làm sao nỗi, tôi chẳng chiều nhường. Nói xong ông lại cứ đi ngang hàng,</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HVB_003_0781</t>
+          <t>HVB_003_0281</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>疑不決未幾幾舉家病作族中不寧復變神人謂曰汝福淺不堪此命</t>
+          <t>至明倫社有伊社人屋字是新富途請曰鄙人再構新家幸逢兩貴台經過乞惠之佳句燕歌屋生輝鎮應曰</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ba ông văn-sĩ thoạt nhìn mấy câu phá đề biết rằng không thể dịch nói, vội vàng gác bút xin lui.</t>
+          <t>khi về đến xã Minh-Luân, trong xã có người vừa làm được ngôi nhà mới, đón đường thưa rằng: chúng tôi mới dùng xong nhà, may gặp được hai quý vị qua đây, giảm xin hai vị ban cho mấy câu để tặng về đẹp. Ông Trần ứng khẩu đọc luôn:</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HVB_003_0782</t>
+          <t>HVB_003_0282</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>我晉後待武強汝當讓與他則汝子孫亦當享他之報其人如言即</t>
+          <t>年年增富貴日日壽榮花</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>hiệu Hoằng-định tam niên (1603) đời Lê-Kinh-Tông , mới đỗ, sau cùng với quan Thượng Lưu-</t>
+          <t>Năm năm tặng phu quý ngày ngày hưởng vinh hoa</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>HVB_003_0783</t>
+          <t>HVB_003_0283</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>邀武氏告之曰我有吉地一穴今許與汝來日汝家發福當無忘我</t>
+          <t>古人有此句今日賀新家</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>đêm gót giữa thật là đặc ý, rồi hôm đến chùa, Lưu-Công giả vờ xin ông Tới vịnh một bài phú tức cảnh.</t>
+          <t>người xưa có câu ấy nay mừng mới làm nhà,</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>HVB_003_0784</t>
+          <t>HVB_003_0284</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>子孫武氏許諸郎將先人塟之其後武家興旺多產才藝健武的人中</t>
+          <t>洹吟沱曰賛羙之辭此等句盡之矣豈復以加而頒矣口輒成自非神吟鬼助轟然若是自是始讓顱先行</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Quan Thám-hoa Đong-Các Nguyễn-dăng-Cảo người xã Hoài-bảo huyện Tiên-du , lúc nhỏ đã</t>
+          <t>ông Trần vừa mới ngâm xong, ông Uông nói chận ngay rằng: đó là những chữ tân tung, chỉ dùng nửa câu cũng đủ can chi mà phải làm nhiều, rồi ông cũng vẫn không phục, Nghè ông Trần ngâm xong bài thơ trên đây, ông Uông mới đặt này mình nói rằng: quả thực xuất khẩu thành chương, nếu không có quỉ thần trợ lực thì làm sao nổi, từ đấy chịu nhường để cho ông Trần đi trước chó không đi ngang hàng nữa.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>HVB_003_0785</t>
+          <t>HVB_003_0285</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>興問滅莫有向道功榮封功臣至今世襲典兵爵禄未次誘言安陽</t>
+          <t>後潛至監來杜著鎮祖墓見有二土堆俗曰兩袖童附耳泣致指之曰從來勝我數番以有那神童附耳之功即用腳跟擊手土堆自是顫從耳病廢商治弗效有人以汪轡車土堆之事語鎮者鎮即訢于朝署朝論汪謝鎮祖墓鎮病尋愈</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>May sao giữa lúc ấy thì có quan Phó-đô là Nhữ-đình- Hiến, vẫn thường trọng ông như bậc cha chú,</t>
+          <t>Nhưng rồi về sau ông Uông lên đến Lam-Kiều xem ngôi mộ tò của nhà ông Trần, thấy có hai cái gò đất ở sát hai bên, tục gọi là đống thần ẩn ẩn thần đồng phụ nhi, ông bên chi vào đống đất bảo rằng, trước đây y thằng nói ta mấy phen là nhờ cái đống đất này. Nói xong ông lấy gót chân nện vào hai đống đất ấy thế mà không biết tại sao cũng từ hôm ấy ông Trần bị chứng điếc tai, thuốc thang chạy chữa vẫn không công hiệu, về sau cò người dem viêc ông Uông dập vào gò đất thân đồng mách với ông Trần, ông bèn tố cáo lên vua. Vua bắt ông Uông phải làm lễ tạ long thần, bấy giờ ông Trần mới khỏi,</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>HVB_003_0786</t>
+          <t>HVB_003_0286</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>中行金誠璽淡蓋言世臣之多也</t>
+          <t>其後試東閣以文武並用詩題用五言三江為韻取十五韻鐵復中第一泊第二始興徵時與江對飲酒至半酣相戲為酒賛酒先唱曰</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>than thở mà thôi. Đô đức độ của ông đại loại như thế,</t>
+          <t>rồi sau Triệu dinh có mở khoa thì Đông-Các, đầu đề tho là (Văn-Võ,Tinh-Dụng), dùng thể ngữ ngôn, hạn 15 văn, trong thơ Ông Trần có hai câu rằng:. Xưng Cao phong tự khỏi. Diệt Hạng diuh năng giang, nghĩa là khen Cao-Tô giấy tư ấp phong, Diệp Hạng quân sức hay cử đỉnh. Kỷ này Ông Trần lại được đứng hàng nhất, mà Ông Uông vẫn phải thứ hai. Nhắc lại lúc chưa đỗ đạt, có hôm hai Ông cùng ngồi uống rượu, khi đã giờ say, thách nhau làm bài. Từ-Tán, Ông Uông đọc trước:</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>HVB_003_0787</t>
+          <t>HVB_003_0287</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>陽宅、紫泥鄧庭記</t>
+          <t>有潰用潰無潰用火所用咸宜無施不可</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>NGUYỄN-CÔNG QUÍ-ĐỨC</t>
+          <t>Hữu huynh dụng huynh, vô huynh dụng hòa. dụng tắc hàm nghi thì vô bất khả: Có huynh thì uống rượu huynh, không huynh thì uống rượu hòa, uống đều say xưa gặp chẳng hay chớ.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>HVB_003_0788</t>
+          <t>HVB_003_0288</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>安山縣北荒地之西有石嶺千餘峯盤桓一里許清奇可愛中有石洞</t>
+          <t>頤續吟曰</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Ông Nguyễn-Quí-Đức người làng Thiên-mụ huyện Tứ-Liêm , lúc còn ít tuổi theo học ở hạt</t>
+          <t>Ông Trần lại đọc tiếp rằng:</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>HVB_003_0789</t>
+          <t>HVB_003_0289</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>安山鼎北。</t>
+          <t>酒潰則歡火潰則絕有遠此言天地日月</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Đông-ngạc.</t>
+          <t>,, Từ hoang tắc âm, từ hòa tắc tuyệt, hữu vi thử ngôn thiên địa nhất nguyệt. Rượu vàng thì uống, rượu hòa thì thôi, vì chẳng như lời, có đất trời soi,</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>HVB_003_0790</t>
+          <t>HVB_003_0290</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>江左之。</t>
+          <t>識者以是言其立志之珠其後莫七我朝中興汪首出仕至戶部尚書封福神鎮辭歸不仕仕終承政使司</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Y, Phó, dĩ phụ vương.</t>
+          <t>xem hai bài tán trên người ta nhận thấy hai Ông lập chí vẫn khác nhau xa. Quả nhiên rồi sau họ Mạc mất rồi. Bản Triệu trung hung thì Ông Uông ra làm quan trước được thăng đến chức Hộ-Bộ Thượng-Thư và phong sắc phục Thần, còn Ông Trần thì không chịu ra cho nên chỉ làm đến chức Thừa-Chính-Sư mà thôi.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>HVB_003_0791</t>
+          <t>HVB_003_0291</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>有大。</t>
+          <t>探花廓佳記</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Cự ý chuẩn sơ kiến hạ.</t>
+          <t>CHƯ TÀO HỘI NGHI, PHÙ-KHÊ THIÊN QUÁCH-CHÚ.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>HVB_003_0792</t>
+          <t>HVB_003_0292</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>有。下有禪。</t>
+          <t>未生時有接近人以慣偷盜為業一日就公邑內行盜會人未定時潛八廟祠後假卧不覺薰睡至鷄鳴方醒披衣徵起忽聞前回喧鬧有人自廟外而入在廟內有人迎問曰今番何事遲歸</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Sào Do di ân.</t>
+          <t>Người làng Phù-Khê thuộc huyện Đông-Ngan. Nói về lúc Ông chưa sinh ra đời, thì ở lân cận có một người chuyên nghề ăn trộm, bỗng có một lần mò sang bên làng Ông định kiếm một mẻ. Nhưng vì lúc ấy nhà nào cũng còn thức, nên anh lên vào nằm ở trong miếu, để đợi, chẳng ngòi lại ngủ thiếp đi. Đến lúc gà gáy anh mới sực tỉnh xốc áo toan di, chợt nghe ở trước mặt có tiếng xôn xao. Và thấy có người từ ở phía ngoài đi vào trong miếu, bên trong có người ra đón hỏi rằng: Phiên này sao về trẻ thế,</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>HVB_003_0793</t>
+          <t>HVB_003_0293</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>高陳先聖。</t>
+          <t>聞有聲曰答適朝士帝與諸曹會談夜命一探花即降伊社有員捧薄奏曰長按伊家福德薄恐不稱此帝命取薄觀之良久判曰雖然知此但業已許之不必換改如他德果薄來時更有定奪焉以此故遂歸耳</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Phó giúp vua.</t>
+          <t>đáp: Vừa rời lên châu Thượng-Đế, hội nghị với các Nam - Tào, định rằng trong đêm hôm nay sẽ cho một vị Thám - Hoa giáng sinh ngay ở xã này. Rồi lại thấy một viên quan tay nàng quyền sở tàu rằng Hạ: thần xét thấy phúc đức nhà ấy mông lẫm sợ không xưng chút nào, giám xin Hoàng-Đế định lại. Hoàng-Đế nghe tàu bên cầm cuốn sở coi qua một lát rồi mới phân rằng: đầu thế nhưng mà đã cho rồi, nhẽ nào lại còn canh cãi. Vì thử nhà ấy quả nhiên phúc bạc, rồi sẽ định đoạt về sau v. v. Vì thế cho nên hôm nay tôi về hỏi trẻ một chút.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>HVB_003_0794</t>
+          <t>HVB_003_0294</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>宗築宮於此。</t>
+          <t>時人在廟後竊聞具得其詳當夜不以行為意因徧往邑中探聽何宋生子見公生於是夜災早即公家具導前事一通預以為賀</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>cho nhà Ân.</t>
+          <t>Lúc ấy anh kẻ trộm ta hãy còn nụ ở trong miếu, nghe lồm được bấy nhiêu câu. Anh bên bỏ ngay ý định ăn trộm, rồi vào trong ấp để thám thính xem trong đêm ấy nhà nào sinh đẳng con trai. Khi thấy chỉ có nhà Ông, thì sáng hôm sau nữa anh đến tận nhà kẻ lại câu truyện như thế.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>HVB_003_0795</t>
+          <t>HVB_003_0295</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>屢臨幸。</t>
+          <t>生而頴異人稱袖童及長以文舉子各正和年號、癸亥文科中進士第一甲三名</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>tùng bộ khan.</t>
+          <t>Còn về phần Ông ngay lúc mới sinh trong đã rình ngộ rồi sau nói tiếng Thần-đồng! Đến khi lớn lên vẫn học lại thêm lừng lẫy! Vào khoảng niên-hiệu Chính-Hòa (1680 - 1705) khoa thi năm Quí-Hợi, thì đồ Tấn-sĩ đệ Nhất giáp đệ Tam danh.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>HVB_003_0796</t>
+          <t>HVB_003_0296</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>焉。始改為龍珠社。</t>
+          <t>公在朝適內閣談政事餘昭祖康王問侍臣曰韓信遺燕書曰有曰白鹿抱泉事跡何在卿等能知之乎群臣皆莫能對公跪對曰跡詳見漢書王郎命索公家書來觀之稱其簿學</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>nguyệt tự nhân.</t>
+          <t>Đến khi làm quan tại triều, nhân lúc nhân đàm ở trong Nội-các Chiêu-tổ Khang-Vương (Trinh-Cần) hỏi các quan hầu về việc ngày trước Hàn - Tín gởi thơ cho Yên-Vương trong có câu rằng: Bạch lộc bảo tuyên, thì sự tích ấy ra sao. Quân thần không ai đáp được, chỉ có một mình Ông đặt gởi tàu rằng: Diện tích ấy biên rỡ trong Hán-thư. Vương sai về lấy gia thư của Ông vào xem quả nhien có thực, Vương khen là người học rộng nhớ nhiều.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>HVB_003_0797</t>
+          <t>HVB_003_0297</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>按山之東。</t>
+          <t>時公方以事被遣未幾除清花聲同仕至寺癖以風疾不視朝始信從日祠神對語之聽</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>từ rất nhiều.</t>
+          <t>Giữa lúc ấy Ông đương mắc phải việc gì nên bị khiên trách, nhưng rồi chỉ sau ít lâu thì được bổ chức Đốc-đông tại tỉnh Thanh - Hóa, tức là ưu thưởng cho Ông về điểm bác học. Rồi sau Ông làm đến chức Thị-lang, vì có bình phong nên không vào triều chính, bấy giờ mới rỡ câu chuyện trong miếu ngày trước quả nhien có ứng nghiệm vậy.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>HVB_003_0798</t>
+          <t>HVB_003_0298</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>有 一石突起酷類蠅餘舊傳有仕社人鄒庚家貧為人傭借適在田間</t>
+          <t>參議武登顯記</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chánh-Phủ, nhân gặp được hôm rồi rải, ông cùng với các quan lên du ngoạn ở chùa Sài-son thì vừa</t>
+          <t>MỖI KHOA LIÊN ĐĂNG, MỘ-TRẠCH ĐẠI</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>HVB_003_0799</t>
+          <t>HVB_003_0299</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>校未有相客經過二言我有吉地一處如有何人請者我即與之度聞其</t>
+          <t>多者至八九名少者不下四五十名連名覆中率以為常而午年科保提調官其左夫阮澧性頗廉直以慕澤從來多中必有私巧者在乞為海陽提調以察之朝延協議考至第四場公命攝地為安合士人坐在穴中籠蓋其上防守其甚嚴</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>gặp lúc hai vị triều-sĩ là Nguyễn-Xá và Nguyễn-Côn đi trợ tế cho một gia-đình nào đó, nhân tiện có ít</t>
+          <t>Triệu vua Lê - Thánh - Tông vào khoảng niên hiệu Vĩnh-Thọ (1658-62 tức là thời Lê-Thần-Tông thì phải), văn học nho phong dương lúc thịnh hành, riêng các sĩ tử của lang Mộ-Trạch Hải-Dương, khoa thì Hương nào cũng đỗ đến 8, 9 người, ít nhất cũng 4, 5 người, chẳng một khoa nào bỏ trống; cho nên cũng lấy làm thường. Nhưng rồi đến khoa Binh-Ngo, có quan Tả-sử là Nguyễn-văn-Phong giữ chức Đề-diệu Trưởng thì, tính Ông thanh liêm và rất ngay thẳng, nay Ông xét thấy khoa nào Mộ-Trạch cũng đỗ đạt nhiều, ngòi rằng họ có mánh lới gì chẳng, nên khoa thì này Ông xin làm Đề-diệu Hải - Dương để kiểm soát thử. Được Triệu-đình chuẩn y, Ông ra tới nơi chấm xong 3 kỳ đến kỳ thứ 4, Ông sai đào riêng từng lỗ rồi dựng nhà lên trên, để cho sĩ-tư ngồi ở dưới lỗ, trên miệng lỗ đều có chụp chiếc lồng thưa, phòng thủ rất là nghiêm mật.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>HVB_003_0800</t>
+          <t>HVB_003_0300</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>言去禾而上前来拜請因邀北寒同只辨得一黍小鶴為禮前致辭曰</t>
+          <t>迨同考院考訖送來公無嚴飾覆考官詳看文勢精純全篇無瑕者方得挑取而覆考擇得十卷公親自評之汰去四卷只取六卷</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>phần biểu đem về, bèn sai người nhà mua một be rượu đặt cả lên bàn để mời các ông thụ lộc.</t>
+          <t>Đợi khi các quan So-khảo chấm xong đệ văn bài đến, Ông lại trao cho Phúc - khảo kiểm lại, xem những quyền nào văn lý đặc sắc, toàn thiên không có vết tích mới phê cho đồ v. v. Các quan Phúc-khảo theo lệnh chọn lọc rất kỹ được có 10 quyền đệ lên Ông xem lại, rồi thái đi 4 quyền còn lấy được 6 quyền,</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>HVB_003_0801</t>
+          <t>HVB_003_0301</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>僕候遇明師自知有福但家貧冷淡愧怍殊深倘吾師惠以福地幸</t>
+          <t>既而呼各優頂一名皆來澤社武登顯首科纔十八歲第二名某澤社人第四建亦慕澤社人其三名乃永賴古庵唐安王司青林樂實人也一科續取六各而纂澤居其半同院取卷觀之見三卷文理各殊不相蹈襲深嘉嘆賞貞始細信慕澤為世尚儒流文物之地文衡公器初非本私</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>nhận thấy Văn-Miếu nước nhà chỉ giữ hình-thức bề ngoại, còn ở bên trong thì để um-tùm lạnh lẽo, mà việc</t>
+          <t>thế rồi đến khi họp phách chỉ có một người đứng vào ưu hàng là Võ-Đăng-Hiền ở làng Mộ-Trạch được đỗ Thủ - khoa, năm ấy mới 18 tuổi. Đến người được đỗ thứ nhi và người thứ tư cũng đều quê ở Mộ-Trạch. Còn người thứ 3 thứ 5 thứ 6, quê ở Cờ-Am thuộc phủ Vĩnh - Lại và làng Ngọc-Cục huyện Đường-An, cùng xã Lạc-Thực huyện Thanh-Lâm. Thế là Khoa ấy có 6 người đỗ thì làng Mộ-Trạch chiếm được 3! Khảo quan đem quyền xét lại thấy văn các quyền chẳng hề giống nhau chút nào. Bấy giờ Ông mới tin rằng Mộ - Trạch quả là một nơi danh nho kể thế, mà văn chương có mục thước chung, trước kia không hề tư vị,</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>HVB_003_0802</t>
+          <t>HVB_003_0302</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>來時發誓不忘恩拒人見其誠心即引在山傍蟾蜍又一指之曰此地最</t>
+          <t>其後武盞顒宏詞科中優一會試賦優士分但中三場嘗以未遊青雲為限官至北京處參議以親老辭官歸養設場教授及其門生擢大科儒者者稱為尊師至今猶歆為裳</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Xét thấy việc này ông đứng độc công thực đã hết lòng hết sức, thế mà cũng đến hai năm mới được hoàn-</t>
+          <t>rồi sau Ông Đăng-Hiền lại trùng ưu hàng, khoa Hoành-từ, 10 khoa luôn trùng tam trường lấy làm chưa thỏa chí nguyện sau làm đến Kinh-Bắc Tham-nghi, rồi vi có cha mẹ già xin từ quan về phượng dưỡng, học trò rất đông mà đồ đại khoa cũng nhiều. Vi thế học giả lúc ấy đều coi như bậc Tôn-sư vậy.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>HVB_003_0803</t>
+          <t>HVB_003_0303</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>好當作陽宅居之必然大發富貴但得近君後急撤去之切不可要庚</t>
+          <t>節義</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>thành, tồn phí có tới hàng vạn, mà tiền Vua ban chỉ được một ngàn quan, còn thiếu bao nhiêu riêng một mình</t>
+          <t>TIẾT NGHĨA</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>HVB_003_0804</t>
+          <t>HVB_003_0304</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>依言即構茅屋數間居之纔及三年時有打魚俗例其池在山傍宅之前長</t>
+          <t>陳朝樁景詞其祖汝猷淳祿老疎人也為諒江知府娶唐安慕澤武氏之女因以妻鄕居焉</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Trong thời-gian ở nhà, ông vẫn giữ lễ mỗi tháng hai kỳ sóc vọng (rằm và mồng một), cũng tới trường giám</t>
+          <t>Lê-Cảnh-Tuân.— Triệu nhà Trần có Lê-Cảnh-Tuân, ông nọi tên là Nhữ-Du người huyện Thuần-Phước xã Lão-Lạt; khi làm Tri-Phủ Lạng-Giang kết duyên với con gái họ Vũ của làng Mộ-Trạch thuộc huyện Đường-An, nhân thế, mới lập gia-cư ngay ở làng vợ, tức là Thê hương.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>HVB_003_0805</t>
+          <t>HVB_003_0305</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>潤數大許邑人鑒網相下庚於池中忍值魚鬚斷其絕郎上池畔山邊取藤英</t>
+          <t>詢覓太學生少與青沔縣扶助社內裴伯耆相善陳末胡墓位伯者如燕京乞師伐胡明遣張翰沐晟等分道而來伯耆為先鋒向道拾逆胡父子送同明人拜伯耆為參護</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Bài thơ quốc-âm trên đây, đề tài là thân mẫu ông Vương- Lãng nhân lời sử giả nhà Hán, về bảo cho ông biết nông-</t>
+          <t>Đến thời ông Tuân, khi đã sung chức Đại-Học-Sĩ, vì lúc còn nhỏ có quen với Bùi-Bá-Kỳ người xã Phù-Nội thuộc huyện Thanh-Miện, gặp lúc cuối đời nhà Trần bị Hổ-Quý-Ly cướp ngôi, Bá-Kỳ sang bên Yên-Kinh xin quân về đánh họ Hổ. Nhà Minh bên sai Truong-Phu và Mộc-Thanh chia đường kéo sang, Bá-Kỳ nhận chức Tiên-phong để hướng đạo. Sau khi bắt sống được cha con họ Hồ đem về bên Bắc quốc, nhà Minh bên cho Bá-Kỳ giữ chức Tham-Nghi,</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>HVB_003_0806</t>
+          <t>HVB_003_0306</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>接經束之腰間忽然陽事大舉壯硬異常原有敵樁一啟恐不敵敵因晉浸池</t>
+          <t>諭郎上萬言書于伯耆其畧曰</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Chú thích Vương-Lãng sinh đời nhà Tiền — Hán, quê ở ấp Bái nguyên trước làm chức Huyện - hào, Lực Hán - Cao - Tô</t>
+          <t>lúc ấy ông Tuân có gửi cho Bá-Kỳ một bức Vạn ngôn thư (bức thư có hơn một vạn chữ) đại lược như sau:</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>HVB_003_0807</t>
+          <t>HVB_003_0307</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>中不敵上畔時打魚陸續而歸庭獨不見眾人意其得魚而藏匿者其母郎</t>
+          <t>若能立陳為上策僕願為佐龍中藥物任足下所用</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>đánh nhau với Hạng-Vũ , Vũ thấy Lãng có tướng tài, bèn sai người đi bắt cóc thân mẫu của Lãng, Lãng được tin</t>
+          <t>Nếu ông có thể lập lại dòng dõi nhà Trần? Đó là thượng sách, thì tôi xin làm các vị thuốc ở trong tử để ông sử dụng!</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>HVB_003_0808</t>
+          <t>HVB_003_0308</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>徙尋之見廣猶在池中仍聲以遲歸之故廣郎鮮魚共母將同襃解釋其</t>
+          <t>為陳辭官為中策僕願執籩籩豆奔走任足下所使</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>cho sứ sang thâm, Hạng-Vương bắt buộc Bà phải gọi Lãng về bên Sở. Bà bảo riêng với sứ giả rằng: Tôi nhớ sứ quân về</t>
+          <t>Hai là: Nếu ông nghĩ đến nhà Trần, mà giả chức vị cho nhà Minh, đó là trung sách, thì tôi xin cầm trở đầu (dở thờ) chạy theo, để tùy ý ông sai khiến!</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>HVB_003_0809</t>
+          <t>HVB_003_0309</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>藤陽事漸漸而倒既歸世問其故庾具以宴告母即取藤使試佩之陽輒勃</t>
+          <t>若貪其禄位斯為下矣則僕樂鈞耕間而已</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Từ-Thú? Vì Bà còn du dự đến nỗi mắc mưu Tào-Tháo, dùng bức thư giả để triệu Từ-Thú sang Tào, rồi khi trông</t>
+          <t>Ba là: Nếu ông còn tham tước lộc nhà Minh, đó là hạ sách, thì tôi sẽ đi câu cá hoặc đi cày ruộng mà thôi!</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>HVB_003_0810</t>
+          <t>HVB_003_0310</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>起築安試箋驗母取曝乾置之灶上時陳裕宗陽爭不舉廢罔治弗效使人</t>
+          <t>伯耆不聽父伯耆犯明法明人籍其家得其書目詢變姓各遊匿後明人於我國立學校諭往觀之明人見其才學以為教授饒而知萬言書日乃誨師依郡補師去其三子太顚少顚叔顚皆願從行送至開門詭語之曰一當從二次且囘已奉舉以報君父之答眾子慟哭拜別</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>thơ Tam-kiệt-thi bài thơ của một vị túc nho là Đồng-Bình-Quân được khảo quan xếp vào</t>
+          <t>Bá-Kỳ chưa kịp dùng. Cách ít lâu Bá-Kỳ phạm pháp bị quan nhà Minh tịch biên gia sản, bắt được bức thư ấy, nhưng ông đã thay đổi họ tên lánh đi nơi khác, về sau nhà Minh đặt xong nên thống trị nước ta, rồi mới thiết lập ra các học xã, bấy giờ ông mới ra để xem việc giáo hóa thế nào? Chẳng ngờ các quan nhà Minh thấy ông là người có tài văn học liên cho ông làm Giáo-Thụ, nhưng rồi chúng biết chính ông đã viết bức thư vạn ngôn, nên chúng bắt ông giải về bên Tàu. Lúc ấy ba người con trai của ông tên là Thái-Điên Thiếu-Đinh Thúc-Hiên đều xin đi theo, khi tiến đến Âi Nam-Quan, ông bảo các con: Thời để cho một mình con trưởng theo ta là đủ, còn hai con thứ thì nên trở về trong nom hướng khỏi để bảo thù cho Vua, cha! hai con vàng lời bài biệt rồi quay trở lại.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>HVB_003_0811</t>
+          <t>HVB_003_0311</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>禰詣國中有能治者許天下民祿之半適詣至伊社庚丹聞之曰劣陽</t>
+          <t>詢其太顯至北京明人訝之曰爾教伯耆立陳後陰國不軌何也詢曰我南人志存南國跖狗吠非其主又何問明人怒送于金陵獄父子皆卒于獄中</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>phạm nan phù vong Sở quốc, bách tham thực dữ sáng Luru-</t>
+          <t>Khi ông cùng Thái-Điên sang tới Yên-Kinh, các quan nhà Minh hỏi rằng: My xui Bá-Kỷ lập lại con cháu nhà Trần, âm mưu làm việc phi pháp là cờ làm sao? Ông đáp: Ta đây là người nước Nam, nên phải quyết chí bảo tồn Nam quốc, con chó của tên Đạo-Chích (kẻ trộm) còn biết cẩn người không phải chủ nó? Vậy thì các ngươn còn hỏi làm chi. Quan Minh nghe xong lấy làm tức giận bên đem giam ông vào nơi ngục thất ở Thanh Kim-Lăng, rồi hai cha con bị chết ở đó!</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>HVB_003_0812</t>
+          <t>HVB_003_0312</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>是世之病，使者具道可其六詳母曰我家有一物必能治之母子即取而勝隨</t>
+          <t>掾萬言書與朱安七斬疏皆忠誠所發陳樸宗先安上疏乞斬七侯臣時稱七斬疏後芸棠故胡公作越鑑有六萬言之書忠貫印月七斬之疏義動鬼神</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>co (Ky), nghĩa là : Một Phạm-Tăng khôn phù được vạn nước Sở cho khói mất, dẫu có Trẫm Tào-tham, cũng</t>
+          <t>Xét thấy bức Vạn-ngôn-Thư của ông cùng với bản Thất-Trầm-Sơ của Chu-Văn-An đều do một tấm trung thành phát biểu ra ngoài cho nên trong bộ Việt- Giám của Tương-Công mới có câu rằng:,! Vạn ngôn chi thư Trung quân nhật nguyệt. Thất-Trầm chi só nghĩa động quỉ thần. Nghĩa là: bức thư Vạn-ngôn lòng Trung soi thấu nhật nguyệt! Bồn só Thất-Trầm chữ nghĩa động tôi quỉ thần;</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>HVB_003_0813</t>
+          <t>HVB_003_0313</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>使者赴京獻上祿宗佩之忽然陽事雄壯生得二皇子以度為神醫</t>
+          <t>詠史詩云</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Tin . Phạm-Tăng , Tăng là quân-sur của Tây Sở. Tào-Tham là Đại tướng của Hán Vương Luru-</t>
+          <t>rồi sau Văn-Hiên Vinh-Sử cũng có thơ rằng:</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>HVB_003_0814</t>
+          <t>HVB_003_0314</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>畫之宮中侍藥賞資不可勝計寵幸無比廣既得君都忘客人</t>
+          <t>上庠琴劍一書生三策懐憐許國情</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>vẫn làm tướng rằng văn-học của các Tấn-sĩ cũng tẩm thường thời, chẳng ngò ngày nay được thấy thơ của</t>
+          <t>Gươm dân Tương bằng một thư sinh. Câu nước trong thơ đã hiền minh?</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>HVB_003_0815</t>
+          <t>HVB_003_0315</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>之言不徹舊宅其後庚子通渙宮女事覺被刑庚被驅囘田產盡沒</t>
+          <t>萬里虜廷終不屈先忠十孝而成名</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Quan Thượng-thư Lê Công-Hy người làng Thạch-Khê huyện Đông-Sơn, Đông khi thảo tờ chế đến câu</t>
+          <t>Muốn dặm trước thù không chịu khuất? Cha trung con hiếu thấy lừng danh.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>HVB_003_0816</t>
+          <t>HVB_003_0316</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>始曩時貧寒的人接這宅接外有高數武形如理藥刀盤以故贓得</t>
+          <t>曾孫光貞有詩云</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Nguyễn Lê-Công lúc cầm chính quyền, rất là khắc- nghiệt ghen ngừơi hiền, ghét ngừơi tài năng, ai có danh</t>
+          <t>Ông Quang-Bôn cũng có thơ rằng:</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>HVB_003_0817</t>
+          <t>HVB_003_0317</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>各又宅處與山相近每日月斜照山影隨下胡王之知蟾蜍在屋簷上當如</t>
+          <t>超延詩禮講明請自勵懸壯士餌寒蹇</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>vọng, ông cũng tìm cách mạt sát đến cùng, vì thế thiên hạ đều phải khiếp oai!</t>
+          <t>Trước sân thì lẽ đã từng qua? Tráng chi say sưa tự nhủ mà?</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>HVB_003_0818</t>
+          <t>HVB_003_0318</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>身在蟾宮故得近君王出入宮掖但嫌宅在山傍地荒其適又前面卻</t>
+          <t>匪朝誠協一拳拳許國策陳三綱常自任</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>là Nguyễn-quán-Nho đồng thời làm quan ở trong chánh phủ, nhưng lại nổi tiếng là người có đức độ, nên</t>
+          <t>Bằng bằng quên mình thành giữ một? Luôn luôn vì nước kẻ đáng ba?</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>HVB_003_0819</t>
+          <t>HVB_003_0319</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>山去來靡定以故富貴不久按國史記裕宗遊西湖墜水中鄒英齋</t>
+          <t>他奚恤鼎饒知餡死亦酣累世亦蒙忠義報光弼盡業振天南</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>người đời mới có câu rằng: Tề tướng Lê-Hy thiên hạ sầu bi; Tề tướng Văn-Hà, thiên hạ âu ca.</t>
+          <t>Cương thường phải nhớ, ngoài chi kẻ? Bình vạc như du, chết cũng thả? Trung nghĩa nói đời cơ bảo ưng? Về vang sự nghiệp nước Nam nhà.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>HVB_003_0820</t>
+          <t>HVB_003_0320</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>之復生因陽事不舉廣請取童男肝和陽起石服之及通同胞女以助</t>
+          <t>其後明人姜黃福鎮安南設場教學以收我國人才穎題兄弟竝往受業黃福愛之認為己子</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Ông Lương-Hữu-Khánh quê xã Hội-trào là con trai quan Bảng-nhân Lương-dắc-Bảng ở huyện</t>
+          <t>Thế rồi cách ít lâu sau nhà Minh sai Thượng-Thư Hoàng-Phúc sang làm Đô-hộ An-Nam, Phúc liên mở trường dạy học để thu nhân tài, bấy giờ anh em Thúc-Đinh cũng xin nhập học, được Phúc yêu mến nhận làm con nuôi.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>HVB_003_0821</t>
+          <t>HVB_003_0321</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>疑道乃通其端羅裕宗服之屢驗與此說不同未知孰是晚斬詠史詩云</t>
+          <t>忽一夜雨電壞牆發屋明日黃福出城南玩景口占一旬云</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Còn Kế- Khê-Công thì cũng dự đoán ý ông như vậy, nhưng chưa chắc hẳn. Bổng một hôm thấy bài phú Tần-quan-văn-kê</t>
+          <t>Rồi bỗng một đêm mưa bão làm đổ nhà cửa! sáng sớm hôm sau, Hoàng-Phúc thân ra ngoài thành để xem quang cảnh, buột miệng đọc một câu rằng:</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>HVB_003_0822</t>
+          <t>HVB_003_0322</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>既因薄載云要君寵又啟滯風逞已私行險小人心似鬼當時謾說是神殿罔</t>
+          <t>照朝風雨家家額壞舊牆垣</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Luru khách phiền thành khứ khách, thì mới ngạc</t>
+          <t>. Tác triều phong vũ gia gia đồi hoại cựu viên tường? Nghĩa là: hôm qua gió mưa, tường vách muốn nha cùng đổ la liệt.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>HVB_003_0823</t>
+          <t>HVB_003_0323</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>神怪厚捧光明寺</t>
+          <t>以喻南國被侵必致額壞額頸即對云</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>VÕ - DUY - ĐOÁN</t>
+          <t>Xét thấy câu thơ ứng khẩu trên đây, Hoàng-Phúc có ý nói nước Nam ta đã bị xâm chiếm thế tất là phải tan hoang? vì thế Thúc-Hiên cũng ứng khẩu đối rằng:</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>HVB_003_0824</t>
+          <t>HVB_003_0324</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>嘉福縣厚榛社屬海陽處有光明寺千重碧樹四面波濤里路通其前河水</t>
+          <t>今日乾坤震處發榮新草木</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Tràng-nguyên Giáp-Hải người làng Sinh-Kế Túy Tín huyện Phương-nhẫn Phù Lạc, lúc nhỏ theo học tại một</t>
+          <t>. Kim nhật càn khôn xử xử phát vinh tán thảo mộc. Nghĩa là: Hôm nay trời đất cô cây bốn mặt càng thêm tỏ vẻ tốt tươi.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>HVB_003_0825</t>
+          <t>HVB_003_0325</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>繞其左真禪門一勝槳也舊傳有一婆蒼僧號玄真住持在此只誦經</t>
+          <t>黃輝是簡高見人聞此句望天嘆曰安南已有聖主出乾坤方南國復還南國我亦不久且歸矣二子盡往從之以圖立功穎顯遂依報尋至愛州已見我大祖蘇山奮勵兄弟皆來歸附未幾大破北兵沐晟黃福等投降之和太祖縱之北還</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>như sau : Xảo tràng xảo đoạn đoạn xảo tràng, rồi đảo ngược lại rằng: Xảo đoạn xảo tràng tràng xảo đoạn v.</t>
+          <t>Hoàng-Phúc là người cao kiến khi nghe học trò đối lại như vậy, thốt nhiên ngửa mặt lên trời than rằng: Thôi! An-Nam đã có Thánh chúa giáng sinh tại phương càn khôn (dong nam) nước Nam lại được trả về cho người nước Nam, chẳng bao lâu nữa ta cũng trở về Bắc quốc? vậy thì hai con sao chả đi tìm người đó để lập công danh? Anh em Thúc-Hiên nghe lời Hoàng-Phúc chỉ giáo ưư vậy, bèn từ biệt thầy để vào Ái-Châu dăng tìm Thánh chúa? khi vào tới nơi thì Lê-Thái-Tổ đã khởi nghĩa ở Lam-Sơn rồi. Anh em bèn xin ở lại phò tá, rồi chẳng bao lâu, quân Minh bị bại, Mộc-Thanh Hoàng-Phúc xin hòa. Thái-Tổ tha cho trở về Bắc quốc,</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>HVB_003_0826</t>
+          <t>HVB_003_0326</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>禮佛不營人間事業利欲卻意人皆以為禪處高僧稱許晚年于房後</t>
+          <t>顔顔等戲師歸國至交開相告別同跪請曰儀等蒙作育久矣未審何時復頒教誨請指示陰憤吉昌歸塟先人是吾師之賜也</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Quan Bảng-nhân Ha-Tôn-Huân người xã Kim- Thanh huyện An-định , là người thông</t>
+          <t>lúc ấy anh em Đinh-Hiên xin tiến chân thầy đến Ái Nam-Quan rồi mới thưa rằng: Chúng con nhớ ơn chỉ giáo đã lâu, ngày nay Tôn-sur trở về cớ quốc, chẳng biết bao giờ lại sang? vậy xin Tôn-sur chỉ bảo cho mấy người đất đề táng Tô tiên? đó là cái ơn đặc biệt vậy.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>HVB_003_0827</t>
+          <t>HVB_003_0327</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>打眼忽愛彌陀伏降臨實殿邀來按前謂曰爾有功梵教委厥上有主</t>
+          <t>並福曰我非忘了試觀二子之志耳前日噐心一穴在亦邑兌邊桃樸頭向銀帶日月扶裔天馬在其西旁正乎年我已埋下木板歸而尋之囑其子孫後有北使遲歸便可鑿這馬足郎當反轡二人拜辭而回</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>lãng huyện An-lãng, khi chưa đỗ có đến chùa Xuân-loi huyện An-phong để cầu thần báo</t>
+          <t>Hoàng-Phúc đáp rằng: Việc đó nhẽ nào Thầy lại không nhớ? chẳng qua là muốn thử gia các anh đó thôi? vậy nay Thầy bảo cho các anh biết, nguyên trước Thầy đã lưu tâm một huyết ở ngay phía bắc làng anh, cục ấy gởi vào chiếc mũ trong ra chiếc dai vàng, nhật nguyệt đóng ở hai vai, ngựa đi sứ đông tại phía Tây, còn mộ thì toạ chữ Tỷ hướng chữ ngo, phía dưới Thầy đã chọn sẵn một mảnh vân gỗ làm ghi, vậy khi trở về các anh nên tìm ngay đến chỗ đó, và nhớ hẹn con' cháu rằng: Sau này nếu có sang Sư mà lâu không trở về, thì cứ dục khoét vào chân con ngựa ấy, tự nhiên Sư giả sẽ được về ngay? Hai người nghe xong bài từ Hoàng-Phúc rồi quay trở lại.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>HVB_003_0828</t>
+          <t>HVB_003_0328</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>且慈悲一點善心達于玄後劫富降生為胡王國皇帝爾其知之既</t>
+          <t>時太祖已矣天下擇人北使無敢行者少頴以父兄之故敵然請往太祖許之拜審刑院事、秦陳情表于明其畧曰</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>ông đỗ Hoàng-giáp, rồi sung chức trong chính-phủ, có công trù được nội nạn, dần dần thăng đến Lục-bộ Thượng</t>
+          <t>Lúc ấy Thái-Tổ đã bình định xong thiên hạ, Ngái muốn tuyển một Sư bộ sang Tâu nhưng chẳng ai dám xin đi, riêng có Thúc-Định vì muốn tiện thể thăm đó tin tức phụ huynh nên mới khẳng khái tình nguyện, Thái-Tổ bèn phong cho chức Thâm-Hình Viện-Sự để mang tờ biểu trần tình sang nộp tờ biểu đại lược như sau:</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>HVB_003_0829</t>
+          <t>HVB_003_0329</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>醒乃召諸道場謂曰某自初出家飯依禦率每謂塵緣淨盡果</t>
+          <t>天地之於萬物雖有雷霆之怒而發生每行乎其間</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Bất dĩ Bồi-lăng thung nhất đầu , Thầy học</t>
+          <t>Trời đất đối với muốn loài, mỗi khi giạn dữ đầu có ra oai sấm sét, nhưng mà bên trong vẫn ngụ sẵn đức hiểu sinh?</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>HVB_003_0830</t>
+          <t>HVB_003_0330</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>福圓成寶座金蓮是我遂後身之報誼意他日迴輪都以累年或</t>
+          <t>父母之於眾子雖有笞檳之威而鞠育常存乎其內</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Võ Thám-hoa gửi thơ thành lời sám Thám - hoa Võ - Tôn - Sur người xã Đan - loan</t>
+          <t>Cha mẹ đối với các con, đầu có dùng đến roi vọt mà on cục dục vẫn dễ trong lòng,</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>HVB_003_0831</t>
+          <t>HVB_003_0331</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>行三夫消也得塵寰一大艱難且日月國君之哲言昔人所不願也不知</t>
+          <t>是以人有疾病未常不呼天地父母此臣子之歷緬陳詞以伸表籲也</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Gió đưa muốn dặm trời coi hẹp, Chim-chích len</t>
+          <t>chả thể mà con người ta mỗi khi gặp sự đau đớn lại kêu trời đất cha mẹ? cho nên ngày nay Thần phải đem câu tâm huyết giải bày để mong soi xét v.v... (Tờ biểu này do quan Thừa-Chí Nguyễn-Trãi soạn).</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>HVB_003_0832</t>
+          <t>HVB_003_0332</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>生前葉障其未盡除去而然耶這事現有問夜佛旨爾等同記吾</t>
+          <t>寫所作並替代金人二軀各重二百兩至燕京陳于關下懇訴明人恨我國徵殺柳昇之故甄唾罵不問物火頴于門下外漆其兩目不許飲食</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Rồi sau người ấy quả nhiên dỡ đạt, còn người kia thì lưu lạc suốt đời, khác nhau như thế</t>
+          <t>Kèm với tờ biểu kẻ trên lại còn một hộp vàng bạc thay thế hình nhân, bên trong có đựng mỗi thứ là 100 lượng, khi tới Yên-Kinh, vua tới nhà Minh cảm thù về việc sát hại Liễu-Thăng nên chỉ quát mắng chứ không thu nhận, rồi lại bắt giam Thiếu-Đinh ở ngoài công thành, và bồi son kín cả hai mắt không cho ăn uống gì cả.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>HVB_003_0833</t>
+          <t>HVB_003_0333</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>言當於圓寂之後寫來數為詭以驗之也及卒後道場依其言乃朱</t>
+          <t>時黃福八朝見之知其少穎嘗取貓餅藏穀中每過即授之三月餘不死明人以為神始受貢禮使囘復命</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Hầu, rồi ông tự hiệu là Đại-hung Hầu , và có đề</t>
+          <t>May sao lúc ấy Hoàng-Phúc vào triều biết là Thiếu-Đinh, nên thường dẫu bánh mi ở trong mũi giầy, mỗi khi đạo qua hắt cho Thiếu - Đinh, vì thế nên không chết lả. Triều thân nhà Minh thấy hơn 3 tháng mà sao Thiếu-Đinh vẫn sống như thường, thì cho là bạc thân nhân hấy giờ mới chịu nhận lễ, và cho trở về báo tin.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>HVB_003_0834</t>
+          <t>HVB_003_0334</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>書十字于肩上用佛家火藥法收舍利時銀瓶埋之尋藥以石庵時加</t>
+          <t>火穎因尋父兄不知沒處至于僧奇只見一詩一畫存焉即將固本鄉虛墓之後諫太祖忤旨降禮部員外郎光貢有詩云</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>hoang dâm, bỏ bê chính sự, ông có soạn ra một truyện Lạc-xương phân-kính bằng chữ quốc âm chè</t>
+          <t>Về phần Thiếu-Đinh sau khi đã được trả lại tự-do, lập tức đi đạo các nơi hỏi thăm tin tức cha anh ngày trước, nhưng cũng chẳng biết mất ở nơi nào? Sau cùng đến một người chùa thì thấy có một tập thơ để lại, ông bên mang về bồn quốc và làm ma chay theo tục hư tàng (tàng bằng quan tài không) về sau nhân việc can ngăn làm vua phật ý phải giáng chức Viên-ngoại-lạng; vì thế Quang-Bôn có thơ vịnh rằng:</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>HVB_003_0835</t>
+          <t>HVB_003_0335</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>供養焉都說永賴縣前烈社阮自隱家貪好學及長從師長安路</t>
+          <t>壯年表表頁高各開創寅緣際聖明</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Ông Thượng người xã Bao-Trung huyện Gia- Phước vốn người mãn tiếp, thi dỗ Tấn-sĩ khoa</t>
+          <t>Tên họ vang lừng lúc tuổi xanh, Gặp thời khai sáng, chúa anh mình!</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>HVB_003_0836</t>
+          <t>HVB_003_0336</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>經予此每往返間輒檢特休息或至登臨玩賞亦不知其光明奇焉</t>
+          <t>詩草預陪寫掖運垂朝先擁使花行</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>lối văn hai hước của ông đại khái như vậy. Lại có một lần, ông ra ngoài chợ chóng gheọ con</t>
+          <t>Cung loạn án ngọc hằng lui tới? Xe sứ đường mây sớm khởi hành.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>HVB_003_0837</t>
+          <t>HVB_003_0337</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>弘寳稱敬崇甲長科中進士第仕至禮部左侍郎其後徙北使皇帝召</t>
+          <t>王臣襄惕忠兼孝天理昭明困復亨</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>TRUNG - HUNG HẬU VĂN THỂ ÍCH TÍ Sau thời Trung-hung văn càng thấp kém</t>
+          <t>Nghĩa cả thờ vua trung với ái. Đạo trời qua vận bỉ sang hạnh.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>HVB_003_0838</t>
+          <t>HVB_003_0338</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>問曰小南國陪臣未知南國各蓋何處是光明寺即跪奏曰臣本國各蓋</t>
+          <t>未商于今循故轍功成事濟是前程</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Nghĩa là: Ông Giả-Phục được làm Dao-dong- Hâu, ăn lộc 4 huyện, thế mà trong trường có bao nhiêu</t>
+          <t>Ngày nay con cháu nơi đường cũ? Xây đắp công danh sự nghiệp mình?</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>HVB_003_0839</t>
+          <t>HVB_003_0339</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>甚矣如瓊林普明報天寵田諸古刺臣亦素聞至如光明寺各未知</t>
+          <t>其孫孫襄中狀元生下共責五歲好學人號袖童統元年號、丙辰科中黃甲仕至戶部左侍郎奉往北使時有中使輔行等寧貴物假作金銀替代潛取原物公不知之比至南寧府總督啟發見其非真遂以事聞皇帝怒其無禮命拘晉于北那官仍以蛤蜊覆公兩目以漆粘之曰瓶氣馬角方得還期</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Tích thi kỳ trước gian nan, kim nhật nghi đồng phú</t>
+          <t>Xét thấy hai ông Đinh và Hiền đều có công to trong việc thống nhất của vua Lê-Thái-Tổ, chỉ vì một hôm bản việc gia-dinh, không vào triều kiến, bị phạm vào lối khiếm điểm, thành thử không được phong tước công thần đó thôi. Nhắc lại khi trước ông làm Tri-phủ Tràng-An, nhân có một hôm vào yết miếu vua Đinh, ông thấy pho tượng Dương-Hậu cùng đặt ngòi chung với hai ông chồng, (tức là vua Đinh-Tiên-Hoàng và Lê-Đại-Hành) thì ông cho là hồn độn, nên có đáng bắn sỏ tàu, xin đặt Dương-Hậu vào chổ chồng sau. Nghi-luận táo bạo này được đức Thái-Tồ ban khen: Khanh quả là người trung trực, chẳng sợ quỉ thần. Rồi ngài hạ lệnh cho rước Đại-Hành và Dương-Hậu sang thờ tại ngôi miếu khác! Về sau ông được thăng chức Tuyên-Phủ-Sứ Trần Lạng - Giang châu là Tràng - Nguyễn Lê-Nại sinh ra Quang-Bôn, Quang-Bôn lúc mới lên 5 tuổi đã nỗi tiếng là thân-đồng thì đỗ Hoàng-Giáp khoa Binh-Tuất thời Lê Thống-Nguyễn, về sau làm đến Thị-Lang bộ Hộ, khi sang Sư Tẩu, có viên Trung-Sứ trong nom các thứ lễ vật đem vàng bạc giả đánh tráo mà ông không biết, khi sang đến phủ Nam-Ninh, viên Tông-Đốc bên đó mở ra kiểm điểm, biết là không phải vàng thực, lập tức báo cáo về triều, Minh triều cho là vô lễ, hạ lệnh giam cầm sứ thần, rồi viên Tông-Đốc sai lấy vở trai bịt kín hai mắt của ông, bên ngoài dùng son phủ lại, và báo cho biết: Bao giờ thấy ngựa mọc sừng thì người được trở về nước?</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>HVB_003_0840</t>
+          <t>HVB_003_0340</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>何處不審有何緣故願示其詳皇帝喟然曰朕生之始有上朱書</t>
+          <t>公怡然自樂不少動心書於冬日出時輒圓一小床曝于日下一明人問其故公即撫其腹曰我曝腹中經笥耳</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Vì chữ quan trên là nói vào hoàng thượng vua Lê ; còn chữ quan dưới là nói vào vương thượng</t>
+          <t>Còn về phần ông đầu bị tai nạn bất thần như vậy, mà ông vẫn cứ thân nhiên không hề ta thân, gặp tiết mưa đông, lúc vùng Thái-dương vừa mọc ông thường nằm ngửa trên chiếc chồng, phơi dưới ánh nắng mặt trời, quan lại nhà Minh hỏi cô tại sao? thì ông vỗ bụng bảo rằng: Tôi phơi sách vở trong bụng đây mà?</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>HVB_003_0841</t>
+          <t>HVB_003_0341</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>痕迹冤</t>
+          <t>明人使讀大演義公讀了一遍不差一字明人大奇之即去其粘目甚加禮重</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>máu bà đẻ.</t>
+          <t>Bọn quan lại nhà Minh thấy ông trả lời một cách tự phụ như vậy, liền bảo ông đọc thử một quyền Đại-học Diễn-ngiha xem sao? Biết rằng chúng muốn thử mình? ông bèn lên giọng đọc ngay một lượt chẳng hề sai một chữ nào? bọn chúng thấy vậy đem lòng kinh phục? tức thì cởi bỏ những thứ gắn mắt và để ông được tự do chứ không hành hạ như trước,</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>HVB_003_0842</t>
+          <t>HVB_003_0342</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>然脫意脫是依奇僧令雖降生上國脫欲洗了字痕不知有何術公郎</t>
+          <t>公客旅中有撲逃本社諸先靈詩集寄歸時有葉人鄭洪震見公紫閣僕長郎八門受業癸未科中進士第除廣東知縣陞燕京重事以念其師淹晉不返即具本奏聞明帝始原之因召至京慰問二月遣還</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Vì thế sau khi chết, hồn ma của y mới đi khắp cả trong nước, tìm để hút máu dân bà, nếu ai mắc</t>
+          <t>thế rồi trong khi còn ở lữ điểm, ông cô soạn tập được một cuốn thơ của các Tiên hiền trong xã, đặt tên là cuốn Tư-hương Vạn-Lục gửi về nước nhà, còn ông thì phải ở lại đợi lệnh. Nhắc lại trong khi ông còn ở lại bêu Tàu, bỗng có một vị Cử-Nhân nhà Minh tên gọi là Đặng-Hồng-Chấn, vẫn thường đi lại với viên Tùy-tông của ông là Thân-khắc-Tảo vì thấy ông là người học văn yêm bác, bèn xin thụ nghiệp để học hỏi thêm? rồi sau đến khoa Kỷ-Vị thì đỗ Tấn-Sĩ, được bờ Tri-huyện Quảng-Đông, dàn dàn thăng chức Yến-Kinh Chủ-sự, nhân mới nghĩ đến thấy học của mình còn bị đây ải ở chốn tha hương, bèn dâng bản tấu kẻ rõ tình hình, được vua nhà Minh xét lại, lập tức triệu ông về Kinh an ủi, rồi tháng 3 nhuận năm ấy cho ông trở về bản quốc.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>HVB_003_0843</t>
+          <t>HVB_003_0343</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>奏曰臣聞佛家有八水洗塵之法既是寺中降誕須取那寺中井水洗之</t>
+          <t>洪震即設愛買斂並綵銀致饒公出侯凡十八年其家黃橋福之言始鑿金為足王是歸國陸吏部尚書蘇川侯後贈少保蘇郡公人獸武前身蓋相類者</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Trong truyền rằng: đền thờ Phạm-Nhan ngày trước ở trong Tự-diễn được đặt lên hàng Thượng đẳng, chỉ vì</t>
+          <t>Trước khi lên đường Hồng-Chấn có bảy tiệc tiến hành và biểu một số bạc cùng các thứ vài vóc v. v... Tình lại ông phung mang đi Sứ vừa dùng 18 năm trời, gia đình ở bên nước nhà thấy lâu được về, bên theo như lời Hoàng-Phúc hẹn trước, đem khoét vào chỗ chân ngựa. hóa nên ông được trở lại, rồi khi về nước được thăng chức Lại-Bộ Thượng-Thư, tặng tước Thiếu-Bảo Quân-Công. người đời bảo ông là kiếp sau ông Tô-Vũ, đời nhà Hán, vì thân thể cũng giống nhau vậy.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>HVB_003_0844</t>
+          <t>HVB_003_0344</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>方可耳皇帝曰爾言誠有理宜為朕亟還本國尋這奇的取井水來</t>
+          <t>尚書張孚記</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>cửa miếu thì thuyền của hậu-cung không tiến lên được. Hoàng-Thượng cả giận, hạ lệnh cho quan hậu đem súng</t>
+          <t>Tác chiêu Sá nguy mạnh, Trương-Hoàng-Giáp nghĩa bất Mạc thần.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>HVB_003_0845</t>
+          <t>HVB_003_0345</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>那時頗有授用公頒拜命謝而還且達於我國王因備行探訪不意乃原</t>
+          <t>青沔金壤断慶帝年號乙酉科中黃甲公性頗剛直統元末莫登庸欲篡位時公為吏部尚書百官以其故臣使作禮詔公張目叱之曰此何義也終不脹屈改命願公泰為之</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Nam-Chân , có quan Tràng-nguyên Đào-Công Sư- Tích , khi vào kinh thi hội, vừa bước chân ra</t>
+          <t>Ông Trương-phu-Thuyệt người làng Kim-Đầu thuộc huyện Thanh-Miện, thời Lê Uy-Mục niên hiệu Đoan - Khánh. 1505-1509 thì đã Hoàng-Giáp khoa Ất-Sửu. Ông là người có tinh cương trực cho nên vào cuối năm Thống-nguyen (1527) Mạc-Đăng-Dung muốn cướp ngôi nhà Lê, lúc ấy ông đương giữ chức Thượng-Thư bộ Lại, bá quan thấy ông là bậc nguyên lão đại-thần nhờ ông thảo cho bản chiêu nhường ngôi! Ông liên trọn mắt quát bảo: Như vậy là nghĩa lý gi? Bá quan biết rằng không thể bắt ép được ông, nên lại trao cho Nguyễn-văn-Thái (Đỗ Thám-Hoa khoa Nhâm-Tuất (1501), năm Cảnh - Thống thứ 5) đứng thảo.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>HVB_003_0846</t>
+          <t>HVB_003_0346</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>捧社寺平日素所休息處也至來年貢部函奉命往仍取井水就京</t>
+          <t>後公歸田里適間中館問野服乘涼與常人無異時則令偶經伊處人皆起立公獨靜坐矣之從者叱曰何人無禮將欲攻之縣令望見公駿須之異急止從者曰吾觀此鬚美且認其體構必有識字試出對句若或不成打之未晚即出對六</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Lại như trước đây ở làng Phù-Chân thuộc huyện Đông-Ngàn có một Cống-Sĩ thường soạn</t>
+          <t>Ông bèn cáo quan trở về làng cũ, trong lúc thư nhân thường ra quán ngồi chơi hóng mát, chẳng khác một người dân quê? Bồng có một hôm quan Huyện sở tại đi qua, mọi người trong quán đều đứng cả dậy, chỉ có một mình ông là vẫn ngồi yên, linh hầu của quan thấy vậy quát mắng: Người kia sao dám vô lễ? và toàn đánh đập! Quan Huyện nhìn ông thấy có bộ râu rất đẹp! vội vàng quát bảo linh hầu: Ta coi người này râu ria đạo mạo, tất nhiên là người có học? vậy để ta ra cho một vẽ đối, nếu không đối được, hãy đánh cũng chưa muốn gì, nói xong quan bên ra một vẽ đối như sau:</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>HVB_003_0847</t>
+          <t>HVB_003_0347</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>獻上皇命取來洗之果然消得舊痕書頁愈加光澤因大喜慰再</t>
+          <t>知縣青沔見無礼而欲攻</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Kham ta ân thiêu Cao-hoàng; nhẫn phụ công cao tướng- quốc. Nghĩa là: đáng buồn cho đức Cao-Hoàng ít ra ân</t>
+          <t>Huyện quan Thanh-Miện kiến vờ lề nhi duc công.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>HVB_003_0848</t>
+          <t>HVB_003_0348</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>召公至將大論諭曰朕得尓敵發頃悟首綠不亦終焉浪度尓宜為朕重</t>
+          <t>公郎應之曰</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Ngò đầu Cống-sinh dùng dùng nói giận, chửi bới cha ông chú lái rồi bảo: Tấn-sĩ Ta đây không thêm !</t>
+          <t>Ông liên ưng khâu đối rằng:</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>HVB_003_0849</t>
+          <t>HVB_003_0349</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>修梵字輪矣一新俾今春勝昔春非惟副朕心之誠耳類尓國鐘靈為</t>
+          <t>進士金燭幸有珍餚而得晚賂</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Tấn-sĩ, còn ông Thánh non, thì lại bị rớt, mà cứ rớt hoài! Như vậy chẳng đúng như câu tục ngữ là linh linh thân</t>
+          <t>Tấn-Sĩ Kim-Đầu vị hưu tu nhi đắc miễn. Nghĩa là: Quan huyện Thanh-Miện thấy kẻ vờ lề mà muốn đánh. Đối với: Tấn-Sĩ Kim-Đầu may vì có râu mà được tha.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>HVB_003_0850</t>
+          <t>HVB_003_0350</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>中花皇帝是品中之一奇也朕令付尔金三百兩銀三千兩帝同作</t>
+          <t>令始知其公即連遜趨拜自言途由錯誤過咎是耳幸大人見恕公笑而釋之</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>thế. Triệu-sĩ đáp: Vàng vàng; Thế rồi khoa ấy quả nhien ông đầu Tấn-sĩ.</t>
+          <t>Quan Huyện nghe xong câu đối mới biết chính là ông Nghè, vội vàng bài tạ, xin ông thứ lỗi, ông cũng cười xóa.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>HVB_003_0851</t>
+          <t>HVB_003_0351</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>仗奇並金銀燈擎各一樹番為奉佛之器還國之後當了此功</t>
+          <t>公前不附偽莫後辭歸不仕蓋在節義之列云</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Thượng ngự ở trên điện để nghe xướng danh các vị Tấn sĩ, trong đó có người tên gọi là Nguyễn-công-Phái</t>
+          <t>Xét ông không phù Mạc, thực xứng là người biết trọng tiết nghĩa vậy.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>HVB_003_0852</t>
+          <t>HVB_003_0352</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>德如朕親視否則佛家有得福果報之機須於身上與弟子孫上</t>
+          <t>大興候記</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mụ lại nói tiếp: Tôi thấy trên diện xướng danh rất lâu, có lễ khoa này được nhiều Tấn-sĩ.</t>
+          <t>CHÍ KHÍ</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>HVB_003_0853</t>
+          <t>HVB_003_0353</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>看公陛辭拜頒而歸再以這等情頭達于國王國王大奇仍許依天</t>
+          <t>院世儀當泰澤社一下村人中官蒞國公世恩之第附焉賜之叔也為人焉浪不循禮度而高尚志氣少善盈文尤長於文體十五歲頴鄉舉特同科諸貢士拜試場官皆用烏紗帽青吉衣公獨著紅色衣烏尾暢場官怖乃兄勢熖仍免覆問</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>mang vào đây Sư-vương (Thái-tử), vì có công ấy được tiền làm Triều-sĩ, dần dần thắng đến Công-bộ Tả-thị-</t>
+          <t>Nguyễn-Thế-Nghi người ở thôn hạ làng Mộ-Trạch, là em quan Đam-Quốc-Công Nguyễn-Thế-Án và là chủ họ của Phò-Mã Nguyễn-Thế-Từ, ông vốn có tính bừa bãi không giữ lễ độ, nhưng chỉ khi lại rất cao thượng, ngày từ lúc nhỏ đã giỏi văn-chương, mà lại sở trường về thế quốc âm thơ phú, khi 15 tuổi thì đã Hương-Tiến (Cử-Nhân) lúc ấy các người đồng bằng vào tạ quan trường ai cũng áo mũ màu xanh, riêng ông lại mặc màu hồng có thêu đuôi qua. Quan trường có vẻ bất mãn nhưng vì e sợ thể lực Quốc-Công, nên không phục vấn giả cả.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>HVB_003_0854</t>
+          <t>HVB_003_0354</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>朝所命公即以所頒金銀市木鳴工崇修梵字一簽前後三十六連範</t>
+          <t>平日共奠登庸相有交善統元間也音托不檢束也。出居京城外長生寺不求療達一月莫簽庸迫至欲加以好官公辭不受願得一爵為各稱足矣因請以大興二字為號登庸許之即拜為大興侯任行高志儀</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Lang rồi mới tri-sĩ, hưởng thọ đến ngoài 80, khi mất, được tặng phong đến chức Thượng-Thư.</t>
+          <t>Nguyễn ông ngày thường chơi thân với Mạc-Đăng-Dung, đến năm Thống-Nguyễn (1527) Đặng-Dung cướp ngôi nhà Lê thì ông đương lạc lõng ở ngày Kinh thành trù ngụ trong chùa Trưởng-An, nhưng không có ý cầu cảnh. Thế mà một hôm họ Mạc biết tin muốn phong quan trước ông cũng từ chối; chỉ xin phong cho một danh hiệu mà thời. Đăng-Dung hỏi danh hiệu gi? Ông xin phong cho hai chữ Đại-Hưng, Đăng-Dung cũng bằng lòng cho để ông làm theo chí muốn,</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>HVB_003_0855</t>
+          <t>HVB_003_0355</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>巍哉壯麗恰似真明境界兼築浮屠一塔近百餘丈延望簷然惟</t>
+          <t>嘗浪吟一句云</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Than ôi! như ông về đường quan giai phục lộc, tìm</t>
+          <t>rồi sau ông thường ngâm mấy câu thơ nôm, và để vào phía tả của Đại-Hưng rằng:</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>HVB_003_0856</t>
+          <t>HVB_003_0356</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>金銀兩燈檠番為家用別鑄鐵器世方之其後八朝成祖哲王聞公相人</t>
+          <t>英雄埃乃剝剝帝境鉅剎大興庄輪</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>người mơ thấy Thiên-quan đương ngồi đề xếp thứ tự người đỗ, đầu tiên đã định lấy ông Đăng-dinh-Tương</t>
+          <t>?? Anh hùng ai này nhung những? Nào ai đến cửa Đại-Hưng chẳng luôn?</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>HVB_003_0857</t>
+          <t>HVB_003_0357</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>之術乘間問曰我諸子誰啟闕守王基時萬都公得寵將有儲副之命</t>
+          <t>題于登龍城大興門左自謂己在其上而人皆出下之意歷歷莫大李尚存</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Thiên-quan bên đời ý kiến rồi viện lẽ rằng : hể nhìn thấy mặt ai trước thì cho người ấy</t>
+          <t>Có ý bảo mình ngồi bên trên, mà ai cũng phải luôn cùi bên dưới vậy? hai câu này đến cuối đời nhà Mạc vẫn thấy còn để chữ không bị xóa.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>HVB_003_0858</t>
+          <t>HVB_003_0358</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>而清都位次未及公以相術直對曰諸子惟清當有天下萬都公深愠</t>
+          <t>時莫氏荒怠政命著樂昌分鏡國語傳序陳隋奢欲事寫意諷論他亦不之悟也</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Còn phần Đặng-Công thì làm đến chức Thái-phó Quốc- bảo rồi mới trí-sĩ, nhưng sau vua lại triệu ra, làm đến</t>
+          <t>Thế rồi về sau nhà Mạc hoang dâm, trẻ nái về đường chính-trị. Ông bèn soạn ra truyện Nhạc-Xương phân kinh dùng toàn quốc âm, ngụ ý chê bài họ Mạc xa xi giống như nhà Trần nhà Tùy ngày xưa, thế mà họ Mạc vẫn không tỉnh ngộ, ông lại soạn ra bài phu Huyền-Quang-Tuyền cung nữ bằng quốc âm, rất được nhiều người truyền tụng.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>HVB_003_0859</t>
+          <t>HVB_003_0359</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>佯乃問公以他事因投以毒藥尋卒後文祖王正位公贈封太保</t>
+          <t>又嘗有北侯至途經南門聞門上題字係我國臣子各號輒停車不進要以架梯從上而行時尚書武惟斬為援伴官伴應以知命部下生一計陰取送象來從後痛刺槪大吼衝突北人叱了一驚郎撓愕走過自知墜于計中不勝慙憤至今猶傳其事云</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>chức Đại-Tư-Không, hơn 10 năm nữa rồi mới trí-sĩ, hưởng thọ 86 tuổi ; con cháu 4 người được lấy Công-chúa, đại</t>
+          <t>Đến thời Minh-Đức (1527-1529) có sứ Tàu sang, khi qua cửa Nam nhìn lên thấy có chữ đề bên trên, và là danh hiệu của một thần từ nước Nam, nên bắt dừng xe không chịu tiến nữa, và lại bắt ta phải đi lấy thang để bắc qua công thì mới chịu vào? Giữa lúc ấy có quan Thượng-Thư là Võ-Duy-Đoán hiện sung chức Bàn-Tiếp để dón sứ-giả, thấy sứ yêu sách như vậy, Ngại cũng giả ý tuân theo, nhưng mà trong tâm đã nghĩ ra được một kế, ngầm sai quan hầu di bảo quân-tượng xua voi đi qua, lúc gần đến chỗ sừ-giả thì lấy mũi nhọn chích vào lưng voi, voi bị đau buốt gãm lên rồi nhảy loạn xạ, làm cho ai này cũng phải hoảng hồn tim chở ăn nấp? chạy xô cả vào phía trong cửa nam, sừ-giả và đoàn tùy-tùng cũng thế, nhưng khi đã trót chạy vào mới biết rằng mình trúng mưu, đánh phải nuốt hận; việc ấy vẫn còn truyền ngọn cho mãi đến nay.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>HVB_003_0860</t>
+          <t>HVB_003_0360</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>郡公其雲仍至今猶存率皆廣賤每以兩燈敬手報應為根其寺廢經</t>
+          <t>扶擁節婦記</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>thứ cao cả nhất xưa nay, thực chẳng sai vậy. Lại truyền ngọn rằng : lúc ấy có quan Thượng-thư,</t>
+          <t>LIỆT NỮ</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>HVB_003_0861</t>
+          <t>HVB_003_0361</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>兵火付之殘灰惟浮屠一嶺巍然獨存近曰官軍進討等賊亦曾</t>
+          <t>上洪唐安有范氏各援者自少通穎尙間頗有姿色既加笄即歸于唐豪令族之家生下男女四人值北兵南侵夫以病死婦撫幼育孤以不一庭不雨醮自誓言其悲酸情狀缺石心腸非言語形容所莊盡</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>như sau : Tấn-sĩ khoa này ta lấy tươi. Sợ chi mà đội đến ba</t>
+          <t>Xã Thượng-Hồng huyện Đường-An có người con gái tên là Phạm-Noãn, lúc còn niên thiếu người rất thông minh nhân nhà lại thêm có nhan sắc đẹp, khi đến tuổi cấp kẻ kết duyên với một người cùng dòng đối danh giá ở làng Phù-ùng thuộc huyện Đường-Hào, sinh hạ được 4 con, cả trai lẫn gái. Chẳng may gặp lúc quân Tàu kéo sang xâm chiếm, người chồng lại bị ốm chết, thế mà chỉ vẫn quyết chí ở vậy để nuôi các con chứ không bước qua cầu nữa, dù rằng phải chịu trăm đáng ngàn cay, mà tấm dạ sắt gan vàng không ai có thể hình dung hết được.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>HVB_003_0862</t>
+          <t>HVB_003_0362</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>於此住焉因考僧人事跡以為慈悲中一傳奇也</t>
+          <t>將當兵火人罕自全城或饑寒失守為盜賊所污者或道路流亡苟來生浩而婦周旋其間以死自誓言變容斂色不為隱暴所侵一方之人皆以故郡鄰目之</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Huyện Chi-Linh xã Kiết-dặc có viên Diên-bạ họ Nguyễn, thiên tư thuần túy, về phần đức hạnh</t>
+          <t>Bởi vì trong con bình hòa, ít ai giữ được trong sạch tấm thân, nếu không vì cảnh cơ hàn, cũng bị giặc cướp hãm hiếp, hoặc giả trong bước lưu ly cũng phải bán liều danh tiết để cầu lấy sống. Thế mà riêng chị lại quyết làm cho hủy hoại nhan sắc, để bọn cưỡng đạo chẳng muốn nhìn mặt, nên mỗi giữ được trọn tấm kiên trình; vì thế cả vùng ai cũng khen là một người tiết-phụ hiếm có.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>HVB_003_0863</t>
+          <t>HVB_003_0363</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>保伍冊郡公記</t>
+          <t>造天日明基圖復舊朝之達官鄉之豪右屢欲奪其操</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>hiệu Bửu-Thái (1720-1728), Hoàng-thượng ra ơn cho bá quan. Nguyễn-công-Hãng đương ở chức Binh-bộ-</t>
+          <t>Nhất là về sau giang-son đến hồi quang phục, các quan trong triều cựng như cương hào trong xã, vi yêu danh tiết cũng muốn ép duyên, nhưng nàng đem câu đại nghĩa ra để từ chối, thì ai cũng phải kinh nê.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>HVB_003_0864</t>
+          <t>HVB_003_0364</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>細都公乃保母吳順妃之弟以故顯典</t>
+          <t>詔求真烈有司以名聞仍表其問曰節義門賜奉事以旌揭之年八十而終子孫累世長冠為一鄉之明王族今扶櫨社有故碑存焉</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Vương-An-Thạch ở đời nhà Tống</t>
+          <t>Thế rồi vào khoảng niên hiệu Thái-Hòa đời Lê-Nhân-Tông (1443-1454) nhà vua xuống chiếu hỏi đến những người trinh-tiết, các quan địa phương cử thực tấu trình, vua bèn ban cho chiếc biển treo của có đề chữ Tiết-Phụ-Môn?, để nếu tấm gương tiết-liệt, về sau bà thọ 86 tuổi, con cháu vinh hiển nối đời, thành ra một họ danh vọng nhất xã, hiện nay tấm bia cũ ấy vẫn còn.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>HVB_003_0865</t>
+          <t>HVB_003_0365</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>兵永慶年間、公年號、大安縣、受雲社堤路水潰、</t>
+          <t>陰境</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>thứ nhất là viên Huấn-đạo tên là Dương-Mô , người đổ thứ nhi là viên Giám-sinh Nguyễn-Tôn-Cổ , khi</t>
+          <t>Chăm hậu tượng, Trần-Gia dĩ sắc đặc Thiên hạ</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>HVB_003_0866</t>
+          <t>HVB_003_0366</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>珥都公奉命培築</t>
+          <t>陳朝之祖美禎，即墨人也。世以魚為業，南道長江一帶，到處是家焉。</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Nhị niên từ tam</t>
+          <t>Tô tiên nhà Trần ở làng Tức-Mặc p? thuộc huyện Mỹ-Lộc nỗi đời làm nghề chài lưới, suốt cả một giải Tràng-giang ở nam đảo, tới đầu thì cũng là nhà, chừ không nhứt định.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>HVB_003_0867</t>
+          <t>HVB_003_0367</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>每行水次經縣內金錢河津上有水神原廟捻著靈應地方之人皆崇</t>
+          <t>時有堪輿北客就我國相地自三島祖山從龍脈而來歷昇龍古碑至金洞縣偈州社高會社見土堆環聚即笑而言曰是也</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Đến hôm Triều-sĩ sắp sửa lai kinh, bà con đem tiền đến tặng, riêng có Xã-trưởng thì không giúp đỡ đồng</t>
+          <t>Lúc ấy có thấy địa lý chính tong ở bên Tàu sang nước ta tìm đất, bắt đầu từ đây tổ-son Tam-Đảo lần theo long mạch xướng khỏi Thăng-Long Cờ-Bi rồi đến các xã Kệ-Châu Cao-Xá thuộc huyện Kim-Động, thấy nhiều gò đồng tụ tập ở đó, thì thấy bảo rằng: đây là chỗ đóng bình nâu com;</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>HVB_003_0868</t>
+          <t>HVB_003_0368</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>奉之時細郡公舟纔過廟輒不進若有沮截之者郡公指而罵曰爾</t>
+          <t>駐兵造厭旁至南昌縣芳萊社江漢沒了臨江顧望良久曰江水急流豈有六藏水底耶因過河而往至御天縣河柳社見星峯草立郎指之曰撞頭旁在是寧能適我耶遂尋至日果社起宗到太堂社阮固結苟旁續下盤針看了輒躊躇不敍去</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>nào, đến hôm được tin báo tiếp, dân làng kéo đến đồng đủ, Xã-Trưởng cũng không tới thăm, hôm vinh quí bài tở,</t>
+          <t>đi đến xã Phương-Trà thuộc huyện Nam-Xương, không thấy vết tích long mạch đâu nữa. Thấy địa dừng lại nhìn quanh một lúc, thì lại nhầm lầm nói một mình rằng: Nước sông chảy xiết thế kia, lẽ nào huyết lại chim dưới thủy đề. Rồi lại xướng đó sang sông, đi tới đến làng Hà-Liễu thuộc huyện Ngư-Thiên. thấy một ngọn núi lù lù hiện lên. Thấy địa tỏ về mừng rõ chỉ tay nói rằng: Nó đã ngóc đầu kia rồi, thế nào lại trốn được ta? Nhận rõ long mạch rồi thấy lại tìm đến xã Nhật-Cảo là nơi khởi điểm, và xã Đại-Dương là nơi kết cục, bấy giờ mới đặt địa bàn coi thử, rồi thấy cảm thấy say mê, quanh quần mãi ở nơi đó.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>HVB_003_0869</t>
+          <t>HVB_003_0369</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>在此不駐護一方之民使水常為民害今我往障頹波歇命至此尓今</t>
+          <t>適西衙人阮固見之問曰地仙屬意于見不知這處有吉穴耶客人仰面笑曰不謂奇王大地出平陽可笑聰勁時師都無眼力固曰果如此請以許我師謝禮如何我亦可辨客人曰爾既有福而遇我我則予之郎還謝我以百緡錢他時有國當分其半國許諾遂將祖墓葬之客人反覆謂之曰這誠大地登了必有嘉祥但於百日之內時常往來以探倘風雷之後見有異事便是剣多古少一可急殺塞之</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>một mâm rượu, cho mỗi y đến hỏi rằng : Tôi đây với ông vốn không có sự thù oán, có sao ngày nay tôi được hiện</t>
+          <t>Chẳng ngờ giữa lúc thấy dương trù trù nghĩ ngợi ở đó, thì có một người tên gọi Nguyễn-Cố Ẩn người xã Tây-Vệ xá đi qua nom thấy, tiến lại hỏi rằng: Địa Tiên chú ý ở đây, phải chẳng chở này có ngôi quí địa sao đó. Thầy địa nghe Cố hỏi vậy, có ý tự phụ ngửa mặt cả cười: Hừ hừ! Ai biết ngôi đất để vương lại lạc xuống quảng bình điền. Từ trước đến nay các thầy địa lý thực không có mất. Chú thầy địa nói xong, Nguyễn-Cố sừng sốt hỏi: Nếu quả như vậy, xin thầy làm ơn để lại cho tôi, tôi xin biên lễ hậu tạ, bao nhiêu cũng được. Chú thầy địa đáp: Ừ, nhà người có phước nên mới gặp ta, thì ta cũng để giúp cho. Nhưng có một điều là khi tàng xong thì phải đưa trước cho ta 100 quan tiền, còn sau đến khi chiếm được nước rồi thì phải chia đôi thiên hạ. Nguyễn-Cố thấy chú khách buộc hai điều kiện trên cũng chấp thuận ngay, rồi hốt ngôi mộ Tô lên để nhờ thầy địa an táng. Thầy địa sợ Cố lật lọng nên lại hẹn rằng: kiểu đất này sau khi tàng rồi phát đạt rất lớn. Nhưng mà trong khoảng 100 ngày, phải nên thời thường thám thính, nếu sau những trận gió mưa sấm sét, mà thấy có sự gì lạ, thì sự tốt lành có ít mà sự hung dữ lại nhiều, nên kịp đời đi chỗ khác.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>HVB_003_0870</t>
+          <t>HVB_003_0370</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>欲反沮我耶大罵良久忽見前出舟五艘突來跳戰都細素精符法</t>
+          <t>葬纔三日忽夜聞巨雷振起一聲所在地方人畜皆驚而次日視之見蜀會西衙太堂三社有石突出人稱貓耳石園池在在有之</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ngoài bái phục xuống đất, để nghe Thổ-công phân bảo. Thổ-công bên cất tiếng hỏi : Ta hiện về đây báo cho</t>
+          <t>Quả nhiên vừa mới táng được 3 ngày, thì đêm hôm ấy sấm sét nỗi dậy ầm ầm, nhân dân quanh vùng thấy đều nào động, sáng sớm hôm sau, người ta thấy đã ở dưới đất trời lên, trong như thứ đá tai mèo, nhan nhãn khắp vùng 3 xã Đăng-Xá, Tây-Vệ, Thái-Đường, tất cả hồ ao vườn được chỗ nào cũng có. Ngày nay dấu tích vẫn còn.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>HVB_003_0871</t>
+          <t>HVB_003_0371</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>知是木神步見郎於船中內按劍步墨書符念呪已分而撥船夫刀搶併</t>
+          <t>時同自知得地喜不自勝其要謂之曰此地雖然然發福但今損百緡錢如何可得又來日半分天下其所得者幾何因以是無意還謝禮錢客人問之固約以某日具還至日客抵其家固即捉來縷定乘夜救之江中惶遠而歸</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Triều-sĩ vâng lời cảm bút viết ngay mấy câu : Cung viết : Đăn vi khí bảm sở câu, vật dục sở tể, tắc</t>
+          <t>Về phần Nguyễn-Cổ thấy có sự lạ như vậy, biết rằng ngôi mộ đã kết mùng rỗ vò cùng. Nhưng vợ anh thì lại nghĩ khác, nên chị bảo khẽ anh rằng: Ngôi mộ nhà ta đã được phát phục, nhưng mà hiện nay chạy đầu cho ra 100 quan tiền lễ tạ, và lại sau này còn phải chia đôi thiên hạ, thử hỏi phần mình còn được bao nhiêu. Cố nghe vợ nói như vậy, nghĩ cũng tiếc của, anh bèn tính ngày đến việc bội sư, nên khi thấy địa đến hỏi lễ tạ, anh hẹn đúng ngày nào đó mới thấy quá bộ lại chơi, vợ chồng tôi sẽ xin giao đủ số. Thế rồi đúng hôm ước hẹn, thấy địa yên trí đến nơi, chẳng ngờ khi bước vào đến nhà trong, anh liền nhét giè vào mồm, trói gò ngay lại, rồi đến đêm khuya anh vác ra quảng xưởng giữa dòng sông cái, thì hành xong thủ đoạn anh lại đứng đình ra về, tưởng rằng không ai hay biết.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>HVB_003_0872</t>
+          <t>HVB_003_0372</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>出兩邊鏡口對射煙霧昏黑咫尺不勝辨約一更許這出船先卻顧</t>
+          <t>不意這處乃浮沙水漲自他將投下忽然潮水漸涸圖在沙上適陳氏魚舟過聞有人喚聲急來救之上船觧去其縫換以新衣間故客人具道由來因謝曰感君子角生之恩當以此地相報陳氏謂這地他已葬了若將之何客人曰某已先葬此地必為公有陳氏遂畱之舟中不露人聲跡客人即教以多采調器鑄為霹靂斧形及蘇木樑煮湯待有授用處</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Quắc chi hình tùng lục, Uu hi thiết hổ tuy. Tích giã Tứ Thái Tử, Kim Yến Tứ-bá-Ky.</t>
+          <t>Chẳng ngờ chỗ anh quảng thấy địa-lý phía dưới lại có con bơn (bãi cát), vì lúc thủy trào tràn ngập, nên không thấy rõ, nhưng rồi sau lúc anh quay về nhà thì nước thủy trào cũng rút. Thành ra chú thấy địa ấy lại nằm lò kho ở trên bãi cát, chứ vẫn không bị chết chim. May mắn hơn nữa là ngày lúc ấy lại có chiếc thuyền ngư phủ họ Trần đi qua, thoáng nghe thấy tiếng cầu cứu, vội vàng chèo đến, ôm xuống dưới thuyền, cởi trói cho chú, rồi hỏi duyên cớ tại sao? Chú bèn kề hết đầu đuôi câu truyện cho ngư-phủ nghe, rồi sau ngỏ lời cảm tạ: rằng tôi được ông cứu thoát, thực là ân đức tái sinh, vậy nay xin đem ngôi đất quý đó để bảo đáp lại v.v... Trần-Công hỏi: nhưng ngôi huyết ấy thầy đã đề cho người khác, biết làm thế nào? Chú thầy địa đáp: Tôi đã cân nhắc kỹ-lưỡng, biết rằng ngôi đất quý ấy, trời đã đề dành cho họ nhà ông, vậy nên tôi đã có cách xử trí... Trần-Công thấy nói vậy bèn lưu thấy địa ở ngay trong thuyền để cho khỏi lộ câu truyện, rồi chú bảo ông đi mua đồng đỏ về dúc một số lưỡi búa tâm sét, và mua Tô-mộc nấu nước để sẵn (nước vàng) đợi khi cần dùng.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>HVB_003_0873</t>
+          <t>HVB_003_0373</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>貯間已失所在細郡即順流而往至貢口誤路處與役築作土功將完</t>
+          <t>忽是夜雷雨交作數然有雷轂手之聲，震師將雲辟雲蓋，斧穿重於墓上，面透至棺，隨以蘇木水灌下明日固往探見之以為雷打墓中流血因惧而殺去客人遂將陳家祖墓就塟焉。</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Thúc-Độ người huyện Đỗ-Lãng , thi đỗ Mậu- Tài, làm quan Thái-Thú Thực-quận , nguyên trước quan</t>
+          <t>Rồi ngay đêm ấy trời bỗng nổi cơn mưa gió. Sấm sét đánh xuống âm âm, mãi đến gần sáng trời tạnh thì chú thầy địa và ông ngư-phủ họ Trần vội vàng đem các thứ ra chỗ ngôi mộ Tồ nhà Nguyễn-Cổ, cắm lưỡi tâm sét xuống chạm đến quan tài rồi đổ nước lên trên. Sáng hôm sau Nguyễn-Cổ cũng ra thăm mộ, nhìn thấy những lưỡi tâm sét còn cắm chơm chơm, và thấy nước đỏ như máu đường ở dưới mộ trào lên, anh nghĩ là bị trời đánh, nên ngay hôm ấy anh phải đào lên để đem tàng ở chỗ khác, rồi ông thầy địa bèn đem mộ Tồ họ Trần tàng vào, mà chẳng ai biết gì cả.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>HVB_003_0874</t>
+          <t>HVB_003_0374</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>問有巨魚楊鬱水次望似一小小帆以尾邀水大浪懷山堤路築復瀆</t>
+          <t>這句前望三陵大江在美樣縣有備社格曰新巡礦後拖伏象樓壹旌劍羅劉左右穴在土腹藏金坐乾向巽事襄客人有課云彩岱黑當堤照煙花對面坐必以顏色得天下陳氏曰果如其言當分民祿之半客人得奈景須如此但君家世世享國則我家世世給足衣糧可也陳氏謹當書目伸各有書交為質</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Bắt cấm hỏa, dân an tọ, bình nhật vô nhu, kim ngũ khở.</t>
+          <t>Xét ra cục đất quỉ này, trước mặt trong ra ngã ba sông cái, thuộc xã Hữu-Bi tục gọi là của Tuần-Vàng hay Tuần-Vương, phía sau gối vào voi phục, lầu dài, cờ kiếm la liệt hai bên, huyết điểm vào chỗ Thổ-phúc Tăng-Kim tim đất giấu vàng, ngời phương can trống chư Tốn, công việc xong rồi chủ thấy địa có đoàn trước mấy câu rằng: phần đại yến hoa đối diện sinh, tất dĩ nhan sắc đặc thiên hạ, nghĩa là: Son phần yến hoa bày trước mặt, hẳn vi sắc đẹp lấy giang son. Trần-Công thấy thấy địa đoàn trước như vậy liền nói với thầy: Nếu dùng như lời sau này xin chia đôi phần lợi lộc! Thầy đáp: chẳng cần phải thế, hễ mà sau này nhà ông lấy được quốc gia, thì con cháu tôi đời đời cấp cho dữ com áo, thế cũng được rồi. Trần-Công xin vàng, rồi hai bên cùng lập khoản ước để lưu chiếu.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>HVB_003_0875</t>
+          <t>HVB_003_0375</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>裂隨難隨破如是者效次遍罰公無知之何郎暗祝于水神曰非者廟經</t>
+          <t>部說客人心多機智又密寫識一道雷與彼子孫藏之嘯以異事特他如禮不替者便以冥告倘者背約即如此因與陳語曰某恐遺下二法有漆長遠來時便可造之陳氏不勝感謝至二世陳賜守度曰陳家皇族乎陳家赤族乎後遂禪位、</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>bao vây. Nghĩa là: năm Kiền-Trung đời Đường Đức-Tông, bị Chu-Tỷ bao vây thật chặt như cái đại lưng, sau nhờ Lý,</t>
+          <t>Nguyên chú thầy địa đây vốn người da mưu và rất kin đáo; sau khi viết xong, chú còn viết ra 2 đạo sấm thư, trao cho con cháu cắt kỹ một chỗ, và bảo chúng rằng: vì thử sau này Trần gia xử sự trung hậu, thì nên bảo thực với họ, nhược bằng họ định bội ước, thì nên như thế như thế... rồi trước khi ra về chú lại nói với Trần-Công: Mở còn quên mất một phép có thể giữ nước lâu dài, nhưng để sau này mở sẽ chỉ bảo, Trần-Công lấy làm hân hạnh, sắm sửa lễ tạ để tiến chân chú khách về Tàu. Nhắc lại họ Trần kể từ khi tàng ngôi mộ đó cho mãi đến đời thứ 3 tức là Trần-Thừa, vào năm Duyên-Phúc thứ 8 đời nhà Lý (1218) — (có lẽ năm Kiến-Gia mới dùng) thì mới dàn sinh ra Trần-Cảnh tức là người có tướng mũi rộng mắt phương, được Lý-Chiều-Hoàng nhượng ngơi, hiệu là Thái-Tông. Bấy giờ con cháu thấy địa mới từ bên Tàu tim sang, lần nào cũng được tiền tông rất hậu.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>HVB_003_0876</t>
+          <t>HVB_003_0376</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>過一時錯誤還亦衡撞神其勿以介意所胡玉餘灵默護使堤圓</t>
+          <t>逮季世後禮日寢哀客人即進言臣先祖遺一譜囑以某年遂就黃國陳朝取讖者之見內言太堂發跡舊墳今將不旺當疏通水道遂信其言照識內書圖鑒自富初社大江而八紫囘至太堂蓋陳家享福該有此數是亦出於天命豈人力所能及</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>chưa chắc đã đúng, vậy mong Thức-giả sẽ bỏ cứu cho. Một vị Triều-sĩ trong ngày lai kinh để dự khoa thi</t>
+          <t>Nhưng rồi về sau họ Trần đối đãi có phần bạc bẽo, thì con cháu thấy địa mới hiển kể rằng: Ông Tồ của thân ngày xưa có đề lại một tờ sấm, hẹn rằng năm nay thì đưa sang trình, Trần vương cảm lấy tờ sấm coi qua, thấy có những câu Ngôi mộ ở Thái-Đường là nơi phát tích, nhưng từ năm nay trở đi thì không được vương, cần phải khai thông thủy đạo thì mới giữ được lâu dài, vì quá tin ở thấy địa, nhà vua liền sai bá quan chiếu theo họa đồ trong tờ sấm đó, để đào ngay một con sông từ cửa sông cái thuộc xã Phú-Xuân kéo quanh về xã Đại-Đường (hiện nay vẫn còn di tích), chẳng ngờ vì thế mà đứt long-mạch, khiến cho nhà Trần suy yếu để Xích-Chủy-Hầu tức Hỗ-Quý-Ly ăn cướp mất ngôi. Nhưng xét cho kỹ thì nhà Trần hưởng phúc chỉ được đến đây, cũng là do ở mạng trời, chứ như nhân lực thì làm sao nổi?</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>HVB_003_0877</t>
+          <t>HVB_003_0377</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>完一方之義受福不淺自是堪得堅實不復潰破獨自負戲之曰我築</t>
+          <t>或按陳家祖墓提生天下後生仁宗火時清秀面字號金仙童子明宗清秀非允時人稱為神仙人中蓋亦土地之壇客言信不誣矣</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Đại hiền đối thời nhân ngôn : sở suc giả cư, sở phát tất hoảng giả : Cái sở suc ký cư, Tắc sở phát an dắc nhi</t>
+          <t>Hoặc xét ngôi mộ tổ nhà Trần sinh ra thiên tử, sau sinh ra Nhân Tông diện mạo thanh tú, chữ hiệu Kim Tiên đồng tử, Minh Tông thanh tú phi phàm, người đương thời gọi là bậc thần tiên trong cõi người, âu cũng là do khí thiêng của non sông đúc lại, lời của khách quả không ngoa vậy.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>HVB_003_0878</t>
+          <t>HVB_003_0378</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>成此堤雖百靈神亦難壞了忽然河水無故翻動狂波怒浪衝激其</t>
+          <t>詠橋祖墓記</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Bồn múa suối chảy chẳng hay mòn. Le te vó cật bên kia suối.</t>
+          <t>VINH-KIỀU TÒ MỘ KÝ</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>HVB_003_0879</t>
+          <t>HVB_003_0379</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>問這堤裂表尚一叚原來這處貢口傍出沖淵與大河密通乃俗傳淵底</t>
+          <t>東崖誄橋京北阮族之祖號福過平生樂善音築木千豐盈縣東蕃社以釀酒為業傍有菩提樹為風所拔因買供新爨適極至樹根見下有銀穴約三婁許即收囘晉貯之已而撤廬去經二年餘時有北客來取銀見雀跡不存只畫空穴即聞諸旁人知這銀已為公所得遂尋至家出雀識一道示之曰某為先人遺貨跋涉而來不想天已賜公今早覓歸程所望出資路費受賜不淺而公得銀藏之不知多少至是取識者之因熙熙銀數與記不差即疑得其人謂曰聊這銀繫我取的原來收時如故不曾取用既是公家原物當盡以付還其人謂曰那物雖我家先遺一下今既為公所得是公家物倘蒙惠顧只願費路錢足矣若更以相還豈敢如命公固執不可客人曰公既有是心願頒其半公曰我不穀人情之所欲第這銀非我之財天使我為公守耳故為此以待勿復牢辭客人恐遠其意輒頒銀歸國</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Đứng đinh chảy dám mái nọ non Cảm nhớ đầu ghenh sào một cọc.</t>
+          <t>Thượng-thư(thời Mạc) Nguyễn-văn-Huy xã Vinh-Kiều thuộc huyện Đông-Ngàn, Cự tổ hiệu là Phước-Mại, trong lúc ngày thường hay làm điều thiện. Cự có dựng nhà tại xã Đông-Lâu thuộc huyện An-Phong làm nghề nấu rượu, ở bên nhà có cây Bồ-đề cỏ thụ, một hôm bị bão đánh dở, Cự mua để làm cui thời, khi đào dưới gốc cây bông thấy có 3 hũ bạc, Cự bèn lẳng lặng đem về đấu kín không cho ai biết, rồi cách ít lâu Cự lại giỡ nhà thiên đi chỗ khác. Chẳng ngờ ba bốn năm sau bông có một chú ở bên Tàu sang tìm đến địa điểm chôn bạc của Tồ-tiên xưa, thì thấy đấu cũ còn đó; lỡ chôn còn đây; mà những hũ bạc đều biến đâu mất? Chú bên lân la hỏi đó những nhà bên cạnh, người ta mới đoán rằng ông nấu rượu năm trước đã lấy đi rồi. Chú bên đến thẳng nhà ông xuất trình gia phả cùng các giấy tờ, rồi mới nói để ông biết: Tồ-tiên chúng tôi ngày trước có chôn bạc ở đây, ngày nay chúng tôi sang lấy chẳng ngò bạc đó đã về tay ông. Chúng tôi không giám ươn thân chi cả, duy có một điều xin ông nghĩ lại, bởi vì nay mai chúng tôi cũng phải thu xếp trở lại cổ hương, mà túi tiền lương đã cạn, mong ông sẽ phát hàng tâm giúp cho ít chút để làm lộ phi, chúng tôi chẳng giám quên ơn. Nhắc lại ông Cụ từ khi đào được hổ bạc cho tôi ngày nay, ông vẫn dẫu kín một nơi chưa hề dùng tới, nên cũng chẳng rõ nhiều ít thế nào, nay được xem bản gia-phả Cụ mới đem ra kiểm lại, thấy đúng con số đã ghi. Cụ bèn giữ Chú ở lại cơn rượu thết dài ăn càn, rồi mới bảo thực cho các Chú biết: rằng số bạc kia quá nhiên tôi đã đào được, nhưng vẫn dẫu kín chưa hề tiêu mất ít nào, ngày nay các chú sang đây tức là chú nhân của nó, thì tôi xin tra trả hết chứ có để lại làm chi. Chú Khách nghe Cụ nói vậy, trong dạ đã thấy mờ cờ, nhưng vì chẳng dám nhận ngay nên cũng kiếm câu từ chối: Thưa Cụ mấy hũ bạc đây dẫu là bạc của Tiên Tỏ chúng tôi để lại, nhưng nay giới đã cho Cụ, tức là của Cụ, nếu Cụ ban cho ít chút để làm lộ phi, chúng tôi cũng đã hàn hạnh lắm rồi, chứ đâu lại giám nhận cả như vậy. Chú khách nói thế nhưng Cụ nhất định không nghe, về sau xin chia ra làm 2 phần Cụ cũng không thuận, bảo thực cho các Chú biết: Tôi đây hà phải con người không quí tiền bạc, chỉ vì bạc đó không phải của mình, chẳng qua giới sai giữ lại để đợi các ông đó thôi, vậy thì các ông cứ việc nhận lấy đủ số đem về thì hon. Chú khách biết chúng không thể nài ép được nữa, nên phải nhận lấy số bạc đem đi,</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>HVB_003_0880</t>
+          <t>HVB_003_0380</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>有神常引河水透八以故難於障塞時細都已損了許多工夫因此會怒</t>
+          <t>後嘗以其事對北人言時有風水師者聞之曰難如此人好心我今老矣尚尚火時郎當往安南擇吉地以報其人懇之師曰我有二門弟一可遣遂與之偕往北客至詠橋社探問則念已於前年捐館矣郎辨一購禮致祭而去二月餘復至謂公之子曰我感受先人之德無以相報今帶得地師來來尋告地以謝有一處群山供伏可做一代帝王又一處緒軸花畫可做一代駙馬於二者何擇其子曰我家村鄙野人何慼望比所望者世出文儒之地不慼二地師曰苟如此在貴邑內何事遠求</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Quan lớn cả giận cho là có ý hỗn xược, bèn sai gia nhân</t>
+          <t>sau khi về tới nước nhà, gặp ai Chú cũng kể lại câu chuyện ông Già nước Nam có lòng nhơn đức như vậy. Lúc ấy có một ông thầy địa lý chánh tông nghe xong câu chuyện cũng khen là người hiềm có, tiếc rằng tôi nay đã già, vì thử đường lúc thiếu trang, thì tôi quyết sang bên ấy tìm họ một ngôi huyệt kết để bảo on sau. Chú khách nghe ông Thầy Địa nói thế, khẩn khoản mời ông sang ngay, vì ông yêu quá không giám đi xa, nhưng ông cho biết: Tôi có hai anh đồ đệ cũng đã học được bí truyền, au là tôi cho cùng đi với bác một thề. Thế rồi 3 người cùng sang An-Nam tìm đến nhà Cụ bán ruộng, thì Cụ đã mất được hơn một năm, các Chú biện lễ phúng viếng xong rồi cáo từ ra đi, không biết đi đâu mà hai tháng sau thấy quay trở lại, bảo với con giai Cụ rằng: Chúng tôi đã chịu ơn Cụ ngày trước rất nhiều mà không có cách gì để báo đáp lại, vậy nay có mời được hai thầy Địa-lý cùng sang, hiện đã tìm được mấy chỗ cát địa, ngôi thứ nhất có một dãy núi châu về, sau phát Đế Vương nhưng chỉ một đôi là hết; còn ngôi thứ hai ở đóa hoa sen cũng phát 1 đôi Phò-mã, vậy Cậu muốn chấm ngôi nào? Cậu con đáp: Chúng tôi là gia đình ở nơi thôn giã, chẳng giám hy vọng cao xa, chỉ muốn được một người nào kể thế văn nho là đủ. Hai thầy Địa đáp: nếu vậy thời có khó gi, chẳng phải tìm đâu cho mệt.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>HVB_003_0881</t>
+          <t>HVB_003_0381</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>今斂取縣內竹木環剿樹柵再取民家敗臼破礎并一切舊石煉灰投下俄見</t>
+          <t>按地自錦章社來龍屈勢如蛇形至詠橋社八首突起二小阜一阜稍大平坦一阜差小勢頗微科一地師認穴在大阜十次一地師不可即就前面澤澤處浸卧水中貼仰良久方起日我已驗之果然方在小阜二師爭辨不決因畫成一圖使人北還就諸老師取正老師曰這曷是黃鶴咱蛤其氣在耳兩阜間兩耳也大耳是等小耳是微科有氣旁必在杳其子即依言移公藝之坐恩向坤</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>của hàn-sĩ trước, làm quan đã hao thêm 10 đầu gạo, khiến cho Ngài lại giận dữ, quát tháo gia nhân phét thêm 10</t>
+          <t>Tôi thấy ở Thôn nhà đây cũng có một người, long mạch tự xã Cẩm-Chương kéo đến, nó đi ướn khúc như kiểu hoàng xà, đến xã Vĩnh-Kiều thì ngóc đầu dầy, đột khởi lên 2 cái gò, gò lớn bằng phẳng, gò nhỏ thì hơi cong cong. Theo ý thầy cả thì huyết kết ở gò lớn, nhưng mà thầy hai không tin, ra cái dẫm sâu phía trước, lăn xuống dưới đây để xét khí mạch rồi quyết đoán là huyết ở gò nhỏ. Hai thầy không ai chịu thua ai, về sau phải họa kiểu đất sai người đem về Bắc quốc hỏi lại Sư-phụ. Sư-phụ coi xét bản đồ, bảo nó là kiểu Hoàng Xà thính - cáp nghĩa là con Hoàng xà lăng tiếng con ngô, lúc lăng thì tinh thần nó chú trọng cả ở lỗ tai, như vậy thì huyết kết ở tai, mà hai gò đất tức là hai tai, duy cái gò lớn bằng phẳng tức là cái tai bị điếc, còn cái gò nhỏ hơi cong, thì có tự khí, tức là tai lành, thế nào huyết cũng kết ở gò nhỏ. Hai người đồ đệ sau khi nhận được tin của Sư-phụ lập tức bảo con ông Cụ đem đi hai cha táng ở gò nhỏ, ngồi ở chữ Cẩn trong ra chữ Khôn,</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>HVB_003_0882</t>
+          <t>HVB_003_0382</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>淵底瀝沸魚浮而斃者不勝其數再加培築刻衣處復完纔半月間</t>
+          <t>至三世文徽以明德翼登庸乙丑科中探花官至尚書致仕其三子伸調以永定奠福原丁未科中黃甲官亦至尚書日達善以光寶員乙未科中黃甲仕以淳福年考乙丑科中進士至侍郎其孫教方之文知江漢之水愈出愈奇四代孫福胡王以陽德繼中興嘉慶末科中會元再中東閣仕至都臺公坦德敦國益相鄰緒北省其苗裔商今旋中相傳諸預登紳甲者面必微科蓋地氣之所鍾也</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>sư-ni đương đọc bài kệ, tiếng trong văng văng lên tới từng mây! lúc xa giá trở về, Ngai ghé vào chùa, sư-ni</t>
+          <t>rồi sau đến đời thứ 3 là ông Văn-Huy thì đổ Thám-hoa tại năm kỷ-hội trong thời nhà Mạc, làm quan đến chức Thượng-thư rồi mới trí sĩ, người con thứ ba tên là Trọng-Quỳnh thì đổ Hoàng-giáp trong năm định vị tức là niên hiệu Vĩnh-định của Mạc-phuc-Nguyên Mễ Phúc Nguyên, về sau cũng làm đến chức Thượng-thư, còn ông Đạt-Thiện tiến sĩ mới 18 tuổi cũng đỗ Hoàng-Giáp khoa kỳ-vị năm Quang-Bửu nhà Mạc, về sau cũng làm đến chức Đô-khoa và ông Hiền-Tích cũng đỗ Tấn-sĩ khoa ất-sửu, niên hiệu Thuần-phước thời Lê-trung-Hung, sau làm đến chức Thị-lạng. Nguyễn-danh-Nho đỗ Tấn-sĩ khoa canh-tuất, làm đến Đô-khoa. Trên đây là kẻ hàng con, còn hàng cháu thì có Giáo-phương cũng đỗ Hội-nguyên khoa bình-tuất niên-hiệu Đoan-Thái thời Mạc-mậu-Hiệp (1586) lúc vào thì dinh lại đỗ Thâm-hoa, trong bài đối sách được Vua khen ngợi phê rằng: Văn của Giáo-phương như nước sông Giang, sông Hán! càng viết càng lẫm thử lạ. Truyền đến hàng cháu bốn đời thì có Đức-Vọng thì đỗ Hội-nguyên khoa quí-sửu, sau lại trúng luôn Đông-các, làm quan đến chức Đô-dài. (Vào thời Lê Dương-Đức 1635-43) còn như Công-Viên, Đức-Đôn, Quốc-Ích cũng lại kế tiếp đăng khoa và cũng đều là dòng dõi họ ấy, ngày nay trong họ có truyền ngôn rằng: những người đỗ đạt nét mặt đều thót, hay là hơi lép một bên, là bởi mộ tổ nằm trên gò đất hơi cong, cho nên khí mạch chung đúc như vậy.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>HVB_003_0883</t>
+          <t>HVB_003_0383</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>細都忍藥不火熟病知在青火黃無灼中廢同治弗效詭病而沒未幾保任</t>
+          <t>卻說頭乃文微次子火領鄉舉惟善飲酒懶廢學業見海陽處隨號嘗往珥河竹木津邊明儔對飲通就河津濯行見竹筏上有紱字在焉拾而觀之乃是舊賦一箇因記之燕燭每飲酒後輒叩盤歌詠習以為常乙丑科八第一場得親朋友之助頸在中第至第二場携酒而入坐間醉酒睡著日已向暮忽大風驟至塵霧漫天續睡中驚為起輩目觀之見有數片紙字飛到其前收來紬認乃是四六體文續喜曰此天賜吾也依樣寫之已而果中至第三場賦題乃前日所得舊賦者更預中第</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>rằng không làm nỗi, Ngài lại sai quan Phó Nguyễn-Soái là Thân-Nhân-Trung-Công làm, ông vâng mạng</t>
+          <t>Nhắc lại Hiền-Tích là con thứ của Văn-Huy, ngay lúc niên thiếu đã đỗ thi hương, chỉ vì nghiên rượu sinh ra lười biếng chẳng chịu học thêm, đến khi được sung một chức Tùy-hiệu ở xứ Hải-Dương, thời thường kéo bạn ra bãi nhà bè bên sông Nghi-hà cùng nhau chè chén, nhân có một hôm ông xuống bên tắm chợt trong thấy có một quyền vở đề ở trên bê, ông bên mở ra xem thử, thì thấy bên trong có chép một thiên phú cờ rất hay. Ông rất lấy làm thích chí, ngâm đi ngâm lại thành ra thuộc lòng. Thế rồi đến khoa ất sừ ông cũng đi thi, may sao kỳ đầu gặp bạn giúp sức nên đăng trôi chảy, đến kỳ thứ hai, ông mang theo một hồ rượu, trước khi làm bài ông đã uống say tùy lý, nằm vật xướng chống đánh một giấc ngủ cho đến xế chiều. Lúc ấy giới bồng nỗi con giống tổ, sấm chớp ầm ầm. Bấy giờ ông mới sực tỉnh, mở mắt nhìn quanh thấy có 4, 5 tờ giấy bay đến trước mặt, vội nhặt lấy coi, thì là một bài Tự lục (phủ) dùng với đề tài ấy, thì ông hết sức vui mừng, cảm ơn trời phật phù hộ nên mới có sự may mắn như vậy, rồi ông chép đúng nguyên văn đem nộp, thành ra kỳ ấy cũng được đồ cao. Đến kỳ thứ 3.là kỳ thi phủ, đầu đề lại trùng với bài phú cờ mà ông đã đọc thuộc lòng, nên ông lại được trùng luôn kỳ nữa.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>HVB_003_0884</t>
+          <t>HVB_003_0384</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>邑內民富不寧邑人相與祈禱于本社廟中冀可捍災忽內有一人</t>
+          <t>追至四場日學業文廢不能措一辭因取晉侯國語舊傳凡諸鄙俚者換以新聲每句撥成輒需乘醉吟詠采察官見之謂曰天日已晚入皆行文過半而新進士何乃尚番空卷而放浪酣歌乎續酩酊音落頃答之日欲寫郎寫何難遂寫了這傳授納</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Sắc không tay bự hối lòng người. Chày kinh một tiếng tan niềm tục,</t>
+          <t>Thế là do sự may mắn ông đã lọt được 3 kỳ, duy còn kỳ thứ tư (4) nữa, là kỳ khó nhất, mà ông bỏ học lâu ngày, thành ra không sao viết nổi, thế rồi nhân lúc ngồi bồn ông nhớ đến chuyện Luru-Hầu lưu, nguyên là bài phú quốc âm, ông bèn sửa lại những chữ quê kịch, sửa xong câu nào thì lại dắc ý ngâm vang cả lên, nhân viên kiểm soát thấy vậy đến hỏi: Kia quan Nghè Tân khoa, mặt giới đã xế bóng rồi, bài vô ai cũng sắp sửa viết xong, có sao Ngài còn để quyền trăng mà cứ uống rượu ngâm tràn như vậy. Ông nghe tiếng viên Giám-sát duc giả thì cũng gật gù đáp rằng: Ư muốn viết thì viết có khó chi, thế rồi ông đem quyền ra viết ngay bài phú Luru-Hâu đem nộp, rõ thực minh Sở dầu Ngọ.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>HVB_003_0885</t>
+          <t>HVB_003_0385</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>動而起放大聲曰我是細都公被水神黃乎抱恨而沒兮欲報仇</t>
+          <t>時同考院有知音者見其詞調清遠每得佳句郎援筆闋之因語諸同院曰這卷寧為我院獨私當送與亞覆考獻笑既而覆考官會者以為戲談大笑周一場聲聞于外采察官見問全院具道其事</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Công thảo xong dâng lên, Hoàng-Thượng sai sư-ni</t>
+          <t>Nhưng mà may sao trong hàng Giám-khảo cũng có một vị cũng thích quốc âm, nhìn qua bài phú của ông nhận thấy lời lẽ tân kỳ, gặp những câu hay cảm bút khuyên lấy khuyên để, rồi lại nói với Khảo quan khác rằng: quyền này chúng ta không nên giữ riêng, tất phải để sang bên phòng phục-khảo để hiển các vị ấy một trận cười, quả nhiên các vị phục-khảo khi nhận được quyền của ông, tức khắc đỏ xô lại coi ai cũng ôm bụng cả cười, tưởng chúng đến vỡ cả đám! khiến cho các vị Giám-sát đương ở bên ngoài, tưởng rằng bên trong có chuyện cãi nhau chạy vào can thiệp, nhưng rồi sau khi rõ chuyện thì cũng không sao nên được trận cười.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>HVB_003_0886</t>
+          <t>HVB_003_0386</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>第無象馬兵器難以相關寄達保母尊好為我辨送來不亦非推</t>
+          <t>考訖即擇諸中卷者適同候旨時上以其取中頗少亟差往命增取之諸考官對諸中官曰申格之文這等卷已盡矣其餘無足之取中官以內首見逼考官曰所存者晉侯一卷外此更無中官郎馳回具奏有首判云晉侯不取更取何人郎傳與考官批取饒而返同觀之葉已取中輒藏不匿以宣露後績仕至兵部左侍郎會我朝中興出首左遷宣光處承使魯任</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Thượng lạy làm vừa ý hạ lệnh cho chở sư-ni</t>
+          <t>Thế là khoa thi ấy vào kỳ thứ tư, ông làm lạc đề nên phải bị rót, nhưng theo lệ thường, hễ chấm thi xong khảo quan phải chọn những quyền trung cách để cả về Kinh xét lại, khoa này Hoàng-Thượng thấy dở ít quá bèn hạ lệnh lấy thêm: Trung-quan mang lệnh ra trường thì, Khảo-quan cũng nói: Văn bài kỳ này kém quá, ngoài mấy chục quyền trung cách thì không còn quyền nào có thể lấy thêm được nữa, nhưng Trung-quan nhất định không nghe. Lúc ấy không biết vô tình hay hữu ý mà Khảo-quan lại giả nhồi rằng: Hiện đây chỉ còn 1 quyền Luru-Hầu mà thôi chứ chẳng còn quyền nào khá nữa. Trung-quan thấy vậy bèn dẹ bắn tẩu về Triều, Hoàng-Thượng xem qua bản tẩu thấy có hai chữ Luru-Hầu, Ngại liền cảm bút phê ngay mấy chữ Luru-Hầu chẳng lấy thì còn lấy ai, Luru-Hầu bất thủ cánh thủ hà nhân. Phè xong Ngại bèn truyền lệnh cho Khảo-quan phải lấy quyền đó. Đến khi dẹ quyền về Kinh thì Ngại mới biết, nhưng đã cho đồ mất rồi nên cũng đánh phải bỏ qua để khỏi lộ chuyện, về sau ông Tích cũng làm đến Bình-bộ Thị-lạng gặp lúc Triều-đình trung hung ông phải dời lên Tuyên-Quang nhưng được lưu nhiệm.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>HVB_003_0887</t>
+          <t>HVB_003_0387</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>損物且將父人矣保母聞言即合造與器一如珥郡公生特戰具完足</t>
+          <t>按自有科目以來諸預中格者必是文理可取茲以國語傳取中頗微訛傳或者是時莫朝取士無章故有此異爭亦以見其為學在人而中否之中有天數存焉近日有監生者八省試第四場文理不成卻寫國音雜技投納試場官論以無為行仍論失監生袁訢幸免是為效類準之戒為初學</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Thiên vi khâm chẩm địa vi chiến, nhật nguyệt đồng song đối ngã miên, Gia thâm bất cảm thân trường túc,</t>
+          <t>Xét thấy nước nhà từ khi có khoa mục cho đến ngày nay, những quyền đã được trưng cách văn lý cũng đều hay cả, thế mà khoa này lại thấy 1 quyền quốc ngữ! phải chẳng là chuyện bịa đặt, hay là thời đó về việc khoa cử chưa có chương trình nhất định, cho nên mới có truyền là như vậy, nhưng nó cũng tỏ cho ta thấy rằng: học văn rộng hẹp là do ở người, còn lúc thì cử đỗ đạt hay không, hoặc giả cũng có thiên số nằm trong đó vậy. Nhưng mà việc này biết đâu chả là sự thật, bởi vì sau đó cũng có một Giám-sinh trong ngày thì ở hàng Tinh, đến kỳ thứ 4 anh cũng không làm nổi bài, nên đã phải viết những câu quốc âm làm nhảm đem nộp, Quan trường cho là vô hạnh, định truật cả chức Giám-sinh, về sau van lấy thâm thiết mới được miễn nghi. Đó cũng là một tấm gương sáng cho kẻ chỉ toàn bất chước đề cầu may vậy.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>HVB_003_0888</t>
+          <t>HVB_003_0388</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>焚之翌日見地方一帶河波濤淘湧如牛馬爭夫岸傍聽者似有于戈</t>
+          <t>安陽中行記</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>gối, đất làm mền, nhật nguyệt châu ta giấc ngủ yên, Đêm khuya đôi cẳng dành co vậy, đuổi, sọ son hà bị đảo điền.</t>
+          <t>Cát cúc thàn lưu Võ tộc, thế truyền tước lộc</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>HVB_003_0889</t>
+          <t>HVB_003_0389</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>交戰之聲魚鬱魚紛然而驚保母聞之度必理郡與水神交戰因祝之曰</t>
+          <t>安陽中行有武姓者起世寒微而頗好學</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Anh kép tàu rằng: Khi thân xuống dưới Thủy quốc bổng gặp ngay quan Tam-Lư Đại-phu ( tức là</t>
+          <t>Huyện An-Dương, xã Trung-hàng có một họ Võ, nhà đầu bần hàn, nhưng tính thích làm điều thiện.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>HVB_003_0890</t>
+          <t>HVB_003_0390</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>吾弟今番共他戰勝負如何倘其有靈即以相報忽有一人搖動躍起</t>
+          <t>時有裴氏來風水師相地釋得地吉塗之亊襄其師謂曰之這曷世世公假未審我家能稱此否既而受神人罵日本地係我管了汝何人來塗我地不穢必有災殃其人特疑不決未幾幾舉家病作族中不寧復變神人謂曰汝福淺不堪此命我晉後待武強汝當讓與他則汝子孫亦當享他之報</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ta gặp phải vị hôn quân nên mới chịu xuống dưới này, chứ như chú mình ngày nay, đã gặp mình chưa, có sao</t>
+          <t>Lúc ấy trong áp có một phu-gia thường đi đón thầy phong thủy về coi đất, khi tìm được đất đem tàng xong rồi đến đêm mơ thấy có một vị thần về bảo: Địa phương đây thuộc quyền của ta cai quản, vậy mi là hàng người nào, lại dám đem mộ tàng vào địa phận của ta, muốn tốt phải bốc đi ngay, bằng không thì sẽ có tai họa đó. Nhưng mà phu ông sau khi tỉnh giấc thì lại du dự không muốn bốc đi, chẳng ngờ từ đấy người nhà bị ốm la liệt, và cả trong họ cũng mất an ninh, bấy giờ ông lại mơ thấy thần nhân về bảo: Nhà mi phước bạc không xứng đáng với ngôi đất quí ấy đâu. Vả lại ngôi ấy ta đã đề dành cho nhà họ Võ, vậy người nên nhường cho y, rồi sau con cháu nhà người cũng được y bảo đáp lại, chẳng cũng tốt hơn hay sao.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>HVB_003_0891</t>
+          <t>HVB_003_0391</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>言曰拜上尊姊贈以兵器戰具勢顓張皇但他族類宴聚已素</t>
+          <t>其人如言即邀武氏告之曰我有吉地一穴今許與汝來日汝家發福當無忘我子孫武氏許諸郎將先人塟之</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>kéo đại binh sang sát biên cảnh, tuyên ngôn là sang đánh họ Mạc, Mạc-Thái-Tổ cùng với triều thần lên</t>
+          <t>Về phần phu ông khi thấy thần nhân bảo mộng đến lượt thứ hai, bấy giờ ông mới quyết định theo đúng như lời trong mộng, cho mọi họ Võ đến nhà bảo cho biết là: Tôi có tìm được một ngôi đất quí, nay muốn nhường cho quí ông, ví thử sau này kết phát thì nên nhớ đến con cháu nhà tôi, ông nghĩ thế nào? Ho Võ thấy phu ông có tâm lòng tốt như vậy, nên cũng cảm tạ và nhận lời ngay, rồi đem phần mộ tiên nhân táng vào huyệt đó,</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>HVB_003_0892</t>
+          <t>HVB_003_0392</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>練習我兵新習水戰未請兼以人形都非介胄薄弱之眾難與他</t>
+          <t>其後武家興旺多產才藝健武的人中興問滅莫有向道功榮封功臣至今世襲典兵爵禄未次誘言安陽中行金誠璽淡蓋言世臣之多也</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Vị tiểu quốc bất học võ nhân, lễ nghĩa hà tức thâm trách. Mẫn An-Nam vô có xích tử, phong nhận nhẫn</t>
+          <t>quả nhiên từ đây về sau gia-dinh mỗi ngày một thêm thịnh vượng, trong họ sản xuất được lắm nhân tài, nhất là võ nghệ, lại có nhiều tay tri đồng hơn đời, trong thời trung-hung có công hướng đạo để diệt họ Mạc, nhiều người đã được phong trước công thần, con cháu cũng được kế thế nắm giữ bình quyền, đến nay vẫn còn thịnh vượng, vì thế ngạn ngữ có câu: An-Dương nhất xã trung-hàng, Kim-Thành nhất làng Quỳnh-Khê nghĩa là nói về những xã trâm anh kế thế vậy.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>HVB_003_0893</t>
+          <t>HVB_003_0393</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>鱗甲相鬩纏一交鋒更被挫了今後不可與鬩當於貢口處創一新</t>
+          <t>陽宅、紫泥鄧庭記</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mao-bá-Ôn xem xong bài biểu cảm vi lời lề câu văn đến nỗi sa lẻ, rồi họp các tướng thương nghị để rút binh về.</t>
+          <t>Huyệt tại thiềm thử ảnh, bạc nghệ nhân đắc nhập vương cung</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>HVB_003_0894</t>
+          <t>HVB_003_0394</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>綱讓他居之竟免積弊釁族人依言而材構作不日告成自是一方河</t>
+          <t>安山縣北荒地之西有石嶺千餘峯盤桓一里許清奇可愛中有石洞</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Tràng-nguyên Ngô-Công Miễn-Thiệu người làng</t>
+          <t>Huyện An- Sơn địa phận xã Tứ-Trâm, có dãy núi đá cộng hơn mười ngọn quanh co hơn một dặm trường, trong rất thanh tú, bên trong có một cái động, dưới có ngôi chùa, Tiên thánh vương xây sẵn cung điện ở đó để ra ngoạn cảnh luôn luôn, nên mỗi đời tên là xã Long-Châu.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>HVB_003_0895</t>
+          <t>HVB_003_0395</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>道不聞有異事焉</t>
+          <t>舊傳有仕社人鄒庚家貧為人傭借適在田間校未有相客經過二言我有吉地一處如有何人請者我即與之度聞其言去禾而上前来拜請因邀北寒同只辨得一黍小鶴為禮前致辭曰僕候遇明師自知有福但家貧冷淡愧怍殊深倘吾師惠以福地幸來時發誓不忘恩拒人見其誠心即引在山傍蟾蜍又一指之曰此地最好當作陽宅居之必然大發富貴但得近君後急撤去之切不可要庚依言即構茅屋數間居之</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>không được vô lễ.</t>
+          <t>Xét thấy phía đông dãy núi có một ngọn nhỏ nhỏ lên trong giống hết như con Thiềm-thứ. Tục truyền rằng xã ấy có người tên là Đặng-Canh nhà nghèo phải đi làm mướn, một hôm anh đương nhỏ mà ở trong dãy núi, bỗng thấy có một người Tàu đi qua bảo với anh rằng: Ta đây mới tìm được ngôi đất quí, nếu ai muốn xin- thì ta cũng cho. Canh nghe thấy Tàu nói thế liền bỏ mà dấy chạy lên quy xuống trước mặt xin thấy làm ơn, rồi dồn thấy về nhà, đi xoay vát mãi mới biện được có một niêu cơm nếp để làm dò lẻ, rồi anh thú thực với thấy địa rằng: Tôi nay được gặp mình sư tử biết rằng nhà có đại hồng phúc, chỉ vì gia cảnh nghèo nàn lấy làm vô cùng hổ thẹn. Nếu thấy ra ơn giúp cho ngời huyệt quí ấy, sau này có được phát đạt, xin thề chẳng dám quên ơn. Chủ thầy địa nghe xong nhận thấy anh quả có tấm lòng thành, lập tức dẫm anh ra chỗ chân núi thiêm thử, chỉ vào núi đó bảo đây là cục đất quí lắm, nhưng nó thuộc về dương-trạch, vậy anh nên làm nhà đề ở, tất nhiên sẽ phát giàu sang. Duy có một điều hễ đến khi nào được gần vua chúa, thì phải dỡ nhà đi ở chỗ khác, chứ đừng ở lại làm chi. Canh nghe thấy địa chỉ bảo như vậy, lập tức theo đúng như lời, dựng ngay mấy gian nhà là đề ở,</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>HVB_003_0896</t>
+          <t>HVB_003_0396</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>彊暴大王記、</t>
+          <t>纔及三年時有打魚俗例其池在山傍宅之前長潤數大許邑人鑒網相下庚於池中忍值魚鬚斷其絕郎上池畔山邊取藤英接經束之腰間忽然陽事大舉壯硬異常原有敵樁一啟恐不敵敵因晉浸池中不敵上畔時打魚陸續而歸庭獨不見眾人意其得魚而藏匿者其母郎徙尋之見廣猶在池中仍聲以遲歸之故廣郎鮮魚共母將同襃解釋其藤陽事漸漸而倒</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Vương cho triệu</t>
+          <t>mới ở được ba năm trời, thì gặp được ngày trong áp có lệ đánh cá, ao cá ở ngay cạnh núi và ở trước mặt nhà anh, ao rộng kẻ mấy chục trượng, chẳng ngờ giữa lúc dân làng kẻ nom người vô dương mãi bất cá ở dưới ao, thì Canh hị dứt đây buộc giỏ. Anh vội lên trên bờ rào bút một sợi dây Chia-với để buộc ngang lưng rồi lại lội xuống, thì ngay lúc ấy dương vật của anh bỗng thấy thượng lên và nó cũng dẫm là thường, một đoạn khổ rách của anh chẳng còn cách nào để che kín được, vì thế anh không dám lên, cho mãi đến lúc đánh cá xong rồi người làng đã kéo lên hết, chỉ còn có một mình anh lẩn quần dưới ao, ai cũng nghĩ rằng anh bắt được cá lớn nên còn đấu điểm chi đây. Giữa lúc ấy thân mẫu của anh ở nhà, nhìn thấy dân làng đã kéo về cả mà sao anh lại chưa về, nên bà sôt ruột chạy ra xem sao, khi ra tới nơi thấy anh còn dương mò mẩm dưới ao, thi bà quát tháo dục đã, bấy giờ anh mới cỏi chiếc giỏ cá trao cho mẹ đem về trước, thì lạ thay, cái đoạn giấy ấy vừa buông ra khỏi thắt lưng, dương vật của anh nó cũng từ từ cựp xuống!</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>HVB_003_0897</t>
+          <t>HVB_003_0397</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>紂大王天本縣令改務</t>
+          <t>既歸世問其故庾具以宴告母即取藤使試佩之陽輒勃起築安試箋驗母取曝乾置之灶上</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>duyên Hán-hoàng,</t>
+          <t>Khi về đến nhà mẹ hỏi duyên có tại sao? Anh cũng nói thực như vậy. Mẹ bên đi cắt một ít đây Chia-với đem về phơi khô, gác lên trốc bếp, muốn xem thực hư thế nào, bà mẹ thường bảo anh đem thứ đây ấy buộc vào lưng, lần nào cũng thấy hiệu nghiệm y như hôm trước.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>HVB_003_0898</t>
+          <t>HVB_003_0398</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>、見縝令改</t>
+          <t>時陳裕宗陽爭不舉廢罔治弗效使人禰詣國中有能治者許天下民祿之半適詣至伊社庚丹聞之曰劣陽是世之病，使者具道可其六詳母曰我家有一物必能治之母子即取而勝隨使者赴京獻上祿宗佩之忽然陽事雄壯生得二皇子以度為神醫畫之宮中侍藥賞資不可勝計寵幸無比</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Hoàng-Hậu. TIỀN THÍCH</t>
+          <t>Dịp đầu may mắn là nhường! vì giữa lúc ấy vua Trần-Dụ-Tông cũng dương bị chứng liệt dương, các quan thầy thuốc ra công điều trị không có hiệu quả, triều định phái viên đi khắp trong nước hỏi xem ai có món gì chữa khỏi được bệnh nhà vua, thì chia đôi quyền lợi thiên hạ. Một hôm sứ-giả về đến Tử-Trần, tuyên bố mệnh lệnh cho dân làng biết về việc tìm thầy thuốc vân vân: Bà mẹ Đặng-Canh nghe nói biết rằng cơ hội đã sắp đến nơi, bà liên xin vào yết kiến sứ-giả hỏi bệnh dương liệt nó là bệnh gì? Sứ-giả kề rõ bệnh tình như thế. Bà liền thưa rằng: Nếu như vậy nhà chúng tôi cũng có món thuốc trị được bệnh đó. Sứ-giả thấy vậy liền đưa mẹ còn bà về kinh thành tàu với nhà vua: vua cho triệu vào, bà đem những sợi Chia-với khô ấy dâng lên, nhà vua buộc thử vào người, quả nhiên thấy có công hiệu ngoài sức tưởng tượng, rồi ngài sinh luôn được hai (2) Hoàng-Tử, khen mẹ con Canh là bậc thần-y, giữ ở trong cung hầu hạ thang thuốc, luôn luôn ban thưởng, sùng hành không ai sánh tầy.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>HVB_003_0899</t>
+          <t>HVB_003_0399</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>人也先其母愛黑漢神謂曰托生猴</t>
+          <t>廣既得君都忘客人之言不徹舊宅其後庚子通渙宮女事覺被刑庚被驅囘田產盡沒</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>HUONG-HẢI TỰ, DU LINH TÚC TRÚ Chúa Hương-hải vẫn anh-linh</t>
+          <t>Riêng về phần Canh sau khi được vua sủng hành, anh liên quen bằng những lời thày địa chỉ bảo năm xưa, không chịu dỡ nhà đem đi nơi khác, rồi sau con trai của Canh, thông dâm với các cung-nữ, công việc phát giác, bị xử tử hình, và Canh cũng bị trực xuất, tịch thu hết cả gia tài, thành ra anh bị dôi rết như cũ.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>HVB_003_0900</t>
+          <t>HVB_003_0400</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>族遂有娠而生時年將十五歲五為兒時好耕耘種樹吃然有巨人之性</t>
+          <t>始曩時貧寒的人接這宅接外有高數武形如理藥刀盤以故贓得各又宅處與山相近每日月斜照山影隨下胡王之知蟾蜍在屋簷上當如身在蟾宮故得近君王出入宮掖但嫌宅在山傍地荒其適又前面卻山去來靡定以故富貴不久</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Trúc-Lâm đệ nhị đại Tô-Sư hiệu là Pháp-Loa Tôn- Giả sinh vào niên hiệu Thiệu-Long năm thứ 6</t>
+          <t>Xét thấy ngôi dương cơ này về phía trước mặt, có thửa ruộng cao ước chừng 3 mẫu, trong hình như chiếc dao câu thái thuốc, cho nên mới phát danh y. Còn chỗ nhà ở vì nó sát ngay chân núi, mặt trời mặt trăng mỗi khi ngả bóng chiếu tạt xuống nhà, trong như hình con Thiềm-thư ngồi ở trên nóc, vì như thân ở cung thêm, nên mới được ở bên cạnh quân vương, từ do ra vào cung cấm. Nhưng mà chỉ hiềm một nỗi: nhà ở bên non, địa thế bức bách, bên ngoài còn có biết bao ngọn núi phân lại, cho nên phù quái chẳng được lâu dài, đó là theo phương pháp địa lý mà nói đại khái như vậy.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>HVB_003_0901</t>
+          <t>HVB_003_0401</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>及長率性彊暴耿目一世都忘父母不有忘臘惟灶神朝祈又禱難得</t>
+          <t>按國史記裕宗遊西湖墜水中鄒英齋之復生因陽事不舉廣請取童男肝和陽起石服之及通同胞女以助疑道乃通其端羅裕宗服之屢驗與此說不同未知孰是</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Long, chính tay Sư-Tổ rước long thể vào trong an trí, rồi sư Huyền-Quang theo người để học đạo, lúc nào cũng</t>
+          <t>Còn như về phần sử-ký: thì trong quốc sử có chép rõ rằng: Khi vua Dụ-Tông ra chơi Tây-Hồ, đương người trên thuyền tự nhiên ngã nháo xuống nước, sau khi vót lên, Đặng-Canh dùng phép châm cứu nên ngài mới được hồi sinh, về sau ngài bị liệt dương, Đặng-Canh xin cho mở bung dựa trẻ con trai lấy gan hòa với vị Dương-khởi-Thạch để cho vua uống, và bảo vua phải thông dâm với chị em ruột để giúp thêm cho dương khi, nhà vua làm theo phương pháp quả có hiệu nghiệm, cho nên Canh mới được vua tin dùng. Nay đem sử liệu so với thuyết trên thì thấy khác hẳn, chưa rõ thực hư thế nào,</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>HVB_003_0902</t>
+          <t>HVB_003_0402</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>一鯨亦必熟而供之神亦知其心時加頸應一日父母以狀罪訢于天天郎</t>
+          <t>晚斬詠史詩云</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Vạn duyên triệt đoạn nhất thân nhân, Tứ thập dư niên mộng huyền gian, Trần trọng chư nhân hưu tá vấn?</t>
+          <t>vì thế nhà thơ Thoát-Hiên có vinh bài thơ tứ-tuyệt như sau:</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>HVB_003_0903</t>
+          <t>HVB_003_0403</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>命雷神降而打之灶神密先頭告王來計灶神曰以滑物塗屋上縱有火</t>
+          <t>既因薄載云要君寵又啟滯風逞已私</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>dẫn dẫn trở thành một chốn danh lam, trong triều nhà Trần quan Đại Tu-đồ hiệu là Băng-Hồ Tướng-công</t>
+          <t>Đã đem nghề mọn mua tâm chúa! Lại mở lò dâm thỏa chí ma!</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>HVB_003_0904</t>
+          <t>HVB_003_0404</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>觀石斧其盛何施王依其言遂取箝夢條日揚攢與水油相和至日</t>
+          <t>行險小人心似鬼當時謾說是神殿罔</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Một trời cây cỏ trong ngâm vịnh Bồn mạt non sông dưới chi huy.</t>
+          <t>Hiểm thực tiểu nhân loài quỉ quốc? Ai oì đứng với tướng Hoa-Đà.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>HVB_003_0905</t>
+          <t>HVB_003_0405</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>直于屋上偏洒之玉潜伏暗中候視俄而風雨驟至雷神從天而下繞</t>
+          <t>神怪厚捧光明寺</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Lưu-quang diện hạ tùng thiên thu, Tận thi kinh thiên</t>
+          <t>Bật-Sô Tăng kiếp hậu vi vọng quốc Hoàng-Đế</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>HVB_003_0906</t>
+          <t>HVB_003_0406</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>躡星脊上滑而墜地王從中突步揮杖擊之雷神倏然不見奪得赤銅繩長丈餘郎於靜地埋之雷神歸具以事奏昊天天怒</t>
+          <t>嘉福縣厚榛社屬海陽處有光明寺千重碧樹四面波濤里路通其前河水繞其左真禪門一勝槳也</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Giang kéo ra, hợp thành ngã ba, rồi lại 1 chi từ sông Như-Nguyệt kéo ra, một chi từ Thanh-Giang đổ</t>
+          <t>Huyện Gia-Phước xã Hậu-Bồng có ngôi chùa Quang-Minh từ, ngôi chùa ẩn giữa ngàn cây cổ-thụ xanh biếc, bốn bề đồng tráng nước trong, trước mặt có đường quan lộ, bên tả có sông Vĩnh-Hà, quả thực là một danh lam thắng cảnh.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>HVB_003_0907</t>
+          <t>HVB_003_0407</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>謂靈神曰三才我為之尊汝震我威所擊無不摧折者何等人物</t>
+          <t>舊傳有一婆蒼僧號玄真住持在此只誦經禮佛不營人間事業利欲卻意人皆以為禪處高僧稱許</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>tập phong Thiếu-bảo Tư-quân-Công mĩ tự là Văn-Tính , Cụ bà được phong Chính phu-nhận Phạm-</t>
+          <t>Chùa này nguyên trước có một nhà sư hiệu là Bật-Sô tên tư là Huyện-Minh trụ trì tại đó, ngày tháng chỉ mãi tung niệm, hầu quên thế sự, chẳng hề ham muốn lợi danh, 'ai cũng khen là một vị cao tăng hiếm có.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>HVB_003_0908</t>
+          <t>HVB_003_0408</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>乃與霹靂抗衡潛報水神以某日引水而上北固彊暴亦為魚</t>
+          <t>晚年于房後打眼忽愛彌陀伏降臨實殿邀來按前謂曰爾有功梵教委厥上有主且慈悲一點善心達于玄後劫富降生為胡王國皇帝爾其知之</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Xuyên huyết son hải tùy xứ hữu Uyên ngư từng trước vị thủy khu</t>
+          <t>Bồng một hôm, Sư đang ngủ trưa ở chốn trai phòng, trong lúc mơ mộng thấy Đức Di-Đà hiện trước tòa sen, gọi Sư đến trước án bảo rằng: Nhà người có công đối với phật giáo, kẻ đã lâu năm, một niệm từ bi, Phật Tổ đã từng chứng giám. Vậy nên sau này hóa kiếp được làm Hoàng-Đế của một nước lớn. Người đã biết chưa?</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>HVB_003_0909</t>
+          <t>HVB_003_0409</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>敞之餌灶神復告之玉遂結蕉為筏取葉為旗翌日水大至浸没</t>
+          <t>既醒乃召諸道場謂曰某自初出家飯依禦率每謂塵緣淨盡果福圓成寶座金蓮是我遂後身之報誼意他日迴輪都以累年或行三夫消也得塵寰一大艱難且日月國君之哲言昔人所不願也不知生前葉障其未盡除去而然耶這事現有問夜佛旨爾等同記吾言當於圓寂之後寫來數為詭以驗之也</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Trung hung dưới ngựa qua sông trước, Hậu hoàn phong beo tiên cửa sau</t>
+          <t>Về phần nhà Sư sau khi tỉnh dậy, nhớ đến những lời trong mộng, bèn triều các Đạo - Tràng đến bảo rằng: Ta từ lúc xuất gia nương nhờ của Phật, tưởng rằng tẩy hết trần duyên, tu tròn quả phúc để lên Tòa Sen, đó là hậu báo cho lúc siêu sinh, ngòi đầu đến kiếp luân hồi, thì bao công phu khở hành, lại phải dời lấy các chức vị gian nan lớn nhất ở trong trân thế. Vả lại lời thề của vua nước Nhật-Nguyệt kia, người xưa cũng còn chẳng muốn, (diễn này tham khảo ở mục Tăng-nhân-Tượng trong Minh-Kỷ) không rõ kiếp trước của ta còn có nghiệp chướng chi đây mà đến nổi thế? Thời thì việc này đêm qua đức Phật đã từng chỉ bảo, vậy thì các người hãy nên nhớ lấy những lời ta nói, đợi đến khi ta về châu Phật, các người sẽ ghi chớp lại, để xem ứng nghiệm ra sao?</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>HVB_003_0910</t>
+          <t>HVB_003_0410</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>蘆舍王郎乘筏而出擊手鼓鳴羅織橫水面設舟震于天大言我與天</t>
+          <t>及卒後道場依其言乃朱書十字于肩上用佛家火藥法收舍利時銀瓶埋之尋藥以石庵時加供養焉</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>cảnh, như núi An-Từ, Ngoa-Vân, Kinh-Chú, Đồ-Sơn, nơi nào ông cũng chống gậy treo lên, thưa hưng ngâm vịnh</t>
+          <t>Các Đạo-Trang theo lời di chúc trên đây, đến khi Sư mất, họ cũng lấy son viết đúng 10 chữ lên vai nhà Sư rồi theo phương pháp nhà Phật, đem xác ra thiêu, thiêu hóa xong mới lượm lấy năm than xương, dựng vào một chiếc bình bằng bạc để đem mai táng, rồi sau dựng một ngôi chùa bằng đá lên trên, tháng ngày gia công tung niệm.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>HVB_003_0911</t>
+          <t>HVB_003_0411</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>交戰時昊天方與群像論善惡聞之曰何處聲甚緊群像相視莫</t>
+          <t>都說永賴縣前烈社阮自隱家貪好學及長從師長安路經予此每往返間輒檢特休息或至登臨玩賞亦不知其光明奇焉弘寳稱敬崇甲長科中進士第仕至禮部左侍郎</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>thần, phong trước là Trinh-Tuyên-Hầu , dần dần thăng đến Lại-bộ Thượng-Thư Thái-phó Trinh-Quốc-Công,</t>
+          <t>Lại nói về xã Tiền-Liệt thuộc huyện Vĩnh-Lại có quan Lễ-Bộ Thị-Lang là Nguyễn-tư-Cường, lúc nhỏ nhà nghèo nhưng rất chăm học, nhận một buổi sớm cậu vào khất thực nhà ông Đô-nho, ông thấy cậu học trò nhỏ, bèn đọc một câu ngạn ngữ để điều cậu rằng: Âm vị khai nhi dương đã lộ, nguyên câu chữ nôm là Cánh cửa Hồng-môn còn khép nếp, Ngọn cò xích xí đã lăm le, rồi lấy câu đó làm để tài bảo cậu vịnh một bài thơ nghe thử. Chỉ sau giây phút câu đã làm xong, câu trạng (thứ 3-4) viết rằng:,, Hồng-môn kiểm thuận do hoài nặc, xích xí kỳ mao dĩ chỉ huy, tức là dịch câu chữ nôm ở trên, quả đã thần tình, nên được nhiều người truyền tụng. Về sau đến tuổi trưởng thành cậu ra Tràng-An du học, mỗi khi qua chùa cậu vẫn vào chơi nghỉ mát, nhưng cũng không dễ ý nhận đó chính là chùa Quang-Minh tự rồi đến niên hiệu Hoàng-Định (1600-1619), cậu đồ Tiến-Sĩ vào khoa Giáp-Thin, làm đến chức Thị-Lang,</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>HVB_003_0912</t>
+          <t>HVB_003_0412</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>祛對雷神方候旨對曰是乃彊暴之賊向既逃罪令復于常恭望定</t>
+          <t>其後徙北使皇帝召問曰小南國陪臣未知南國各蓋何處是光明寺即跪奏曰臣本國各蓋甚矣如瓊林普明報天寵田諸古刺臣亦素聞至如光明寺各未知何處不審有何緣故願示其詳</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Phiên : Cổ ngã tồn cô duy nghĩa tại, Tri quân xử</t>
+          <t>cách mấy năm sau phượng mang sang sứ Bắc quốc, vua nhà Minh triều đến trước mặt hỏi rằng: Người là Sư-giả An-Nam chắc rằng biết hết những nơi danh lam bên đó. Vậy có chùa nào gọi tên là Quang-Minh tự hay không? Ông quí gọi tàu: Danh lam ở bên bồn quốc, thần biết rất nhiều, tỷ như các chùa Quỳnh-Lâm, Bão-Thiên, Phổ-Minh, Quy-Điền đều là những nơi cổ tích thần đều nghe tiếng, còn chùa Quang-Minh sự thực không biết ở đâu, thế mà ngày nay Hoàng-Đế phân hỏi, chẳng hay có duyên có gì, xin cho hạ thần được rõ?</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>HVB_003_0913</t>
+          <t>HVB_003_0413</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>奪昊天說思良久曰弗敬怒淪動輒抗拒是乃無天地的人今姑赦</t>
+          <t>皇帝喟然曰朕生之始有上朱書痕迹冤然脫意脫是依奇僧令雖降生上國脫欲洗了字痕不知有何術公郎奏曰臣聞佛家有八水洗塵之法既是寺中降誕須取那寺中井水洗之方可耳皇帝曰爾言誠有理宜為朕亟還本國尋這奇的取井水來那時頗有授用公頒拜命謝而還且達於我國王因備行探訪不意乃原捧社寺平日素所休息處也</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Cha Quyền với Thần là chỗ hạn thân từ trước, và đã ở trong nhà thần, hiện nay được ra trấn thủ Thiên-Trường.</t>
+          <t>Minh-Đế có về ngậm ngùi phân bảo: Trầm đây từ lúc mới sinh thấy ở bên vai có viết mấy chữ bằng son An-Nam quốc Quang-Minh tự Sa viết tự khẩu công là mươi chữ ngắn viết hãy còn rành rành. Trầm ngòi tiếp trước là một vị sư ở trong chùa đó mà sau giáng sanh sang đây; nay trầm muốn lấy những vết chữ đó, vậy người biết có phép gì màu nhiệm hay không? Ông tàu rằng: Hạ thần nghe nói phương pháp tẩy trần của nhà Phật phải dùng đến dược thủy, ngày nay Hoàng-Đế biết rõ kiếp trước ở chùa, thì nên lấy thứ nước giếng ở trong chùa đó đem về để tẩy thì mới sạch được. Minh-đế khen phải rồi bảo ông về bồn quốc tìm lấy nước giếng chùa ấy đem sang, sẽ có hậu thưởng. Ông lỉnh mang bài tạ quay về, khi về tới nước nhà, bèn đem việc ấy tàu trinh vua ta, rồi đi thăm hỏi khắp nơi, chẳng ngờ lại chính là ngôi chùa của xã Hậu-Đồng mà ngày thường ông vẫn vào đó nghỉ mát.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>HVB_003_0914</t>
+          <t>HVB_003_0414</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>之任他長惡弗悛禍必將意至仍命水細縮水而下五竟免害即乃</t>
+          <t>至來年貢部函奉命往仍取井水就京獻上皇命取來洗之果然消得舊痕書頁愈加光澤因大喜慰再召公至將大論諭曰朕得尓敵發頃悟首綠不亦終焉浪度尓宜為朕重修梵字輪矣一新俾今春勝昔春非惟副朕心之誠耳類尓國鐘靈為中花皇帝是品中之一奇也朕令付尔金三百兩銀三千兩帝同作仗奇並金銀燈擎各一樹番為奉佛之器還國之後當了此功德如朕親視否則佛家有得福果報之機須於身上與弟子孫上看</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>sĩ, sai đi phục sẫn ở bên bắc ngạn, ông gửi thư cho Quyền, hẹn sang bên thuyền nâng chén rượu nhạt kẻ lại</t>
+          <t>Thế rồi cách một năm sau đến hạn công hiến, ông lại phung mang sang sử, nhân tiện đem cả nước giếng ấy sang Yên-Kinh cùng hiến một thề. Hoàng-Đế nhà Minh cả mừng, lập tức đem ra tây ngay, quả nhiên vét cũ biển đi đầu hết, da để lại được sáng bóng thêm lên. Ngài rất lấy làm hài lòng, cho triều ông vào khen ngợi. Trẫm vì có Khanh chỉ điểm chợt tình ngộ mới tiên duyên, nếu không thì thực bỏ phí cơ hội. Vậy Khanh nên vì trẫm gia sức trung tu, cửa Phật một phen đổi mới, xuân nay khác hẳn xuân xưa, làm được như thế chẳng những trọn được lòng thành bảo bồn của trẫm, mà lại còn biểu dương được rằng: nước người có cảnh linh thiêng chung đúc ra được một vị Trung-Hoa đại-đế, đối với phẩm giá thực là một việc ly kỳ. Vậy nay trẫm trao cho người 300 lạng vàng đem về xây dựng 36 tòa Phật tự và đèn cây bằng vàng bằng bạc mỗi thứ một cây để làm tự khi, sau khi về nước Khanh nên làm trọn cái công đức đó, cũng như trẫm được nhìn thấy tận nơi. Nếu không thì cơ báo ứng về sự hòa phục của Phật sẽ ở ngay bên thân của Khanh và con cháu Khanh đó nghe...</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>HVB_003_0915</t>
+          <t>HVB_003_0415</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>家人具道可以遙來得灶神之助允上帝一言一動必先顯告吾復何辜</t>
+          <t>公陛辭拜頒而歸再以這等情頭達于國王國王大奇仍許依天朝所命公即以所頒金銀市木鳴工崇修梵字一簽前後三十六連範巍哉壯麗恰似真明境界兼築浮屠一塔近百餘丈延望簷然惟金銀兩燈檠番為家用別鑄鐵器世方之</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>thanh thế vang khắp xa gần, đánh nhau mấy trận ở cửa Thần-phù thần , Kiêm-Vương Mạc-Kinh-Điên</t>
+          <t>Ông nghe lời vua nhà Minh phân bảo xong lập tức bài tạ ra về, đem câu truyện đó tàu trinh quốc vương, vương cũng lấy làm kỳ di và hứa cho ông được phép làm theo mạng lệnh Minh triều. Được quốc vương nhà cho phép xong rồi, ông bèn dem số vàng bạc ấy ra sắm sửa vật liệu, thuê mướn nhân công, dựng một tòa chùa trước sau 36 nóc, nguy nga tráng lệ như cảnh Tây-thiên; lại còn xây thêm một tháp Phù-đồ gần một trăm bậc (cấp) chót vót từng máy, duy có cây đèn vàng bạc thì ông để lại nhà dùng, rồi đúc hai cây đèn sắt thay vào tự khi.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>HVB_003_0916</t>
+          <t>HVB_003_0416</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>自是益橫其志復得一田雞自灸而食之不以獻灶神怒其忘己思</t>
+          <t>其後八朝成祖哲王聞公相人之術乘間問曰我諸子誰啟闕守王基時萬都公得寵將有儲副之命而清都位次未及公以相術直對曰諸子惟清當有天下萬都公深愠佯乃問公以他事因投以毒藥尋卒後文祖王正位公贈封太保郡公其雲仍至今猶存率皆廣賤每以兩燈敬手報應為根</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>đại bại, Thế-Tô thừa cơ tiến binh theo đường Tây-Sơn ra đánh kinh bắc, khiến cho trong ngoài nom nọ lo sợ,</t>
+          <t>Thế rồi cách mấy năm sau, vua Thành-Tổ nghe nói ông tình về môn xem tướng, nhân lúc nhân hạ mới hỏi ông rằng: Khanh thử coi tướng các con của trẫm, xem ai xứng đáng nói ngôi? Nguyên vì lúc ấy Vạn - Quân - Công được sủng ái nhất, rất có hy vọng lên ngôi sừ nhi, còn Thanh-Đô-Vương kẻ về vị thứ hãy còn kém xa, thế mà ông giám căn cứ vào tướng mạo tàu thẳng ngay rằng: Thần xem tướng các Hoàng-tử duy có Thanh-Đô-Vương là người sẽ được thiên hạ sau này đó thôi? Chẳng ngờ câu truyện xem tướng lại lọt đến tai Quân-Công, Quân-Công biết thế, giả vờ triệu ông vào dinh để hỏi việc khác, nhưng rồi thừa cơ đầu độc nên ông bị chết. Đến sau Vãn-Tổ chính thức được lên ngôi vương, Ngài mới tặng phong cho ông trước Thái-Bửu Quân-Công và lại phong trước cho các cháu, đồng dõi họ ấy tới nay vẫn còn, nhưng đều nghèo khó, vì thế họ đều oán hận là bởi ngày trước ông đã đánh tráo hai cây đèn thơ, cho nên con cháu phải chiêu bảo ứng không hay.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>HVB_003_0917</t>
+          <t>HVB_003_0417</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>中傷之一日顯告五曰來日雷神打汝五又問許灶神曰次早汝往耕于</t>
+          <t>其寺廢經兵火付之殘灰惟浮屠一嶺巍然獨存近曰官軍進討等賊亦曾於此住焉因考僧人事跡以為慈悲中一傳奇也</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>sai sứ giả sang ta nói rằng: Vì Thái-phu-nhân một hôm đáp thuyền ra bể, chẳng may bị nạn phong ba, nay coi</t>
+          <t>Còn như tòa chùa do ông xây dựng, trải qua bao cuộc binh hỏa, cái gì cũng biến ra tro, thế mà chỉ riêng cây tháp thì vẫn nguy nga tồn tại. Gần đây quan quân kéo đi chinh phạt cũng thường đóng quân tại đó, nhân thế mới hồi ra được sự tích cao tăng, thì ai cũng cho rằng một câu truyện lạ trong cảnh từ bi vậy.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>HVB_003_0918</t>
+          <t>HVB_003_0418</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>田如雷雨將至即於耕木夾處處穿車其中外用橫木裹鎖定自無事</t>
+          <t>保伍冊郡公記</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Nhận thấy lệnh trên, anh liền sắm sửa xe vồng đưa Bà ra hiện tại kinh thành, Mạc chưa ban</t>
+          <t>Kim-Tông Thân miếu hội đê tỏa Điền-Quân</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>HVB_003_0919</t>
+          <t>HVB_003_0419</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>王不意一為其所賣依計而行既而雷雨漫天而至王欲斂之不脹竟被打</t>
+          <t>細都公乃保母吳順妃之弟以故顯典兵永慶年間、公年號、大安縣、受雲社堤路水潰、珥都公奉命培築</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>là con Chiêu-Huân Tĩnh-Vương, đương lúc ở trong tinh-thế nguy-ngập vì sợ không thoát khỏi tay Trịnh-</t>
+          <t>Huyện Thiên-Bản, xã Bảo-Ngũ, có Điền-Quận-Công, vì là em ruột bà Bảo-mẫu Mạc-Thuận-Phi, cho nên được dự binh quyền. Vào khoảng niên hiệu Vĩnh-Khánh (1729-32), nhân có khúc đê ở xã Thọ.Triền thuộc huyện Đại-An bị nước xoáy vỡ. Điền-Quận được lệnh tới đó bồi đắp.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>HVB_003_0920</t>
+          <t>HVB_003_0420</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>斂頭間雨霽群牛觸土培之宛然成大阜鄉人即其土處封墳數年</t>
+          <t>每行水次經縣內金錢河津上有水神原廟捻著靈應地方之人皆崇奉之時細郡公舟纔過廟輒不進若有沮截之者郡公指而罵曰爾在此不駐護一方之民使水常為民害今我往障頹波歇命至此尓今欲反沮我耶大罵良久忽見前出舟五艘突來跳戰</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>tôn là Thánh-mẫu, nguyên quán ở làng Phạm-Xá thuộc huyện Tứ-Kỷ , với ông là chỗ đồng hương, nên</t>
+          <t>Khi thuyền qua bên Kim-Tông, trên bên có một miếu thờ Thủy-Thần rất là linh-trùng, địa-phương sùng bài kẻ đã lâu đời. Quận-Điền bỗng thấy thuyền mình tự nhiên dừng lại, tựa hồ có gì ngăn cản. Ông liên nói giận trở lên trên miếu mảng rằng: Nhà ngươn ở đây sao chẳng bảo hộ địa hạt, để cho nước lụt thường làm hại dân. Nay ta phung mạng tới đây bồi đắp, mà ngươn lại muốn ngăn cản là có làm sao? Lạ thay ông vừa quát mắng xong, thì thấy trước mặt hiện ra 5 chiếc thuyền lớn trong có quân-sĩ khi giới, xông tới ào ào như hình khiêu chiến.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>HVB_003_0921</t>
+          <t>HVB_003_0421</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>後方民夜勤畜類不寧一日有村翁早行過予墳處見立而言曰我</t>
+          <t>都細素精符法知是木神步見郎於船中內按劍步墨書符念呪已分而撥船夫刀搶併出兩邊鏡口對射煙霧昏黑咫尺不勝辨約一更許這出船先卻顧貯間已失所在</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>một dãy núi giả (non bộ) quanh co, trước núi lúc ấy có những đàn kiến dương men tầng đá lco lên, ông ngắm</t>
+          <t>Nhưng ông cũng tinh về thuật phu thủy, đoán biết ngay là Thủy-Thần hóa phép để chống lại mình, nên cũng đứng ở trong thuyền, tuốt kiếm hò thần Thiên-Cương, thư phù niệm chú, rồi mới hạ lệnh cho các tướng-sĩ cầm sản giáo mác xông lên, hai bên đều dùng hỏa pháo bắn ra, khói đen mù một phủ khắp một vùng, đứng cách chỉ một gang tấc cũng chẳng trông rõ thứ gi. Trận chiến kéo dài độ một trống canh thì thuyền bên địch bồng biển đầu mất, thế là bên ông thắng lợi hoàn toàn.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>HVB_003_0922</t>
+          <t>HVB_003_0422</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>彊暴靈神爾立廟祀之可保無虞不卒無遺類矣將收牛者皆</t>
+          <t>細郡即順流而往至貢口誤路處與役築作土功將完問有巨魚楊鬱水次望似一小小帆以尾邀水大浪懷山堤路築復瀆裂隨難隨破如是者效次遍罰公無知之何郎暗祝于水神曰非者廟經過一時錯誤還亦衡撞神其勿以介意所胡玉餘灵默護使堤圓完一方之義受福不淺</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Hoành-son nhất đại khả dĩ dung thân,</t>
+          <t>Đánh tan được bọn âm binh âm tướng, ông bên hạ lệnh cho thuyền cứ việc thuận dòng thẳng tiến đến nơi cửa công, rồi sai quân-sĩ dắp lại quảng đê bị vỡ, chẳng -ngờ khi dấp gần xong, thì bồng thấy một con cá lớn bơi lại, to bằng một chiếc thuyền buồm, đuôi nó vẫy vùng thành những ngọn sóng cao như trái núi, làm cho đoạn đê vừa dắp lại bị vỡ tung, vỡ rồi ông lại sai dấp, dấp xong nó lại phá luôn, trải đến mấy lần như vậy. Chẳng biết đối phó ra sao, bấy giờ ông mới làm dám khẩn vãi như sau: Kinh thưa Thủy-Thần linh-vị: Mới rồi đi qua trước miếu, tôi đây một phen lầm lỡ trót đã xúc phạm oai linh, xin Thần cũng đừng để ý, ra sức ủng hộ cho cuộc bồi dắp sớm được hoàn thành, tức là Thần đã ban phúc cho dân địa phương không phải nhỏ vậy.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>HVB_003_0923</t>
+          <t>HVB_003_0423</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>見之村翁歸而道其事鄕遂構祠崇奉自是始得寧居今至封為</t>
+          <t>自是堪得堅實不復潰破獨自負戲之曰我築成此堤雖百靈神亦難壞了忽然河水無故翻動狂波怒浪衝激其問這堤裂表尚一叚原來這處貢口傍出沖淵與大河密通乃俗傳淵底有神常引河水透八以故難於障塞時細都已損了許多工夫因此會怒今斂取縣內竹木環剿樹柵再取民家敗臼破礎并一切舊石煉灰投下俄見淵底瀝沸魚浮而斃者不勝其數再加培築刻衣處復完</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Thứ phu-nhân họ Nguyễn hiệu là Nhu-Tính Á-phu-nhân họ Nguyễn hiệu là Vi-Tính , Tự tức cộng</t>
+          <t>Khẩn Thần xong rồi ông lại ra lệnh cho quân-sĩ bắt tay vào việc, hễ dấp đến đầu thì đất chắc nich đến đó, không bị vỡ lỗ chỗ nào. Nhưng rồi sau khi dấp xong ông lại tự phụ tuyên bố ngay rằng: Khúc đê của ta dấp đây dầu có 100 vị thần linh cũng không tài nào phá được. Lạ thay lúc ấy trời dương im lặng, thế mà ông vừa nói xong mấy câu thì trên mặt nước lại thấy chuyển động, sóng lại cuộn cuộn nổi lên, đập vào chân đê phá vỡ ngay một quãng lớn, làm ông hoàng sợ, vội vàng sắm sửa lễ vật để ta thân linh rồi sai dắp lại, nhưng mà dắp mãi cũng chỉ tôn công chư không thu được kết quả. Nhưng vì chổ cửa công đây là một khúc quẹo nằm cạnh đại hà, tục truyền ở dưới đây đầm có nhiều linh vật đục lỗ phía dưới đưa nước phù sa vào trong, cho nên rất khó hàn khẩu! Nhưng riêng về Quân-Điền với quãng đê này, ông đã tổn rất nhiều công mà chẳng thành sự, nên ông lấy làm cấm gián, sai quân đi khắp huyện hạt, chặt lấy tre gỗ, và đi thâu lượm vật liệu của dân để làm đà cồn, rồi lại nhào với với đà dỡ xuống lòng sông, chỉ trong chốc lát thì thấy rùa, cá, ba ba chết nổi lên trên mặt nước nhan nhản. Cứ thế làm luôn đến nửa tháng trời thì ông bị bệnh,</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>HVB_003_0924</t>
+          <t>HVB_003_0424</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>福神往年有騷客過祠下題詩云二五鍾靈象貫殊深霄黑漢應</t>
+          <t>纔半月間細都忍藥不火熟病知在青火黃無灼中廢同治弗效詭病而沒</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Sinh phong hàm Triệu-Liệt Đại-Phu, trước Quảng-nghĩa-Hâu, Con thứ III phong hàm Hiền-Cung Đại-</t>
+          <t>thân thể nóng như nước sôi, chẳng có thuốc gì chữa được, rồi ông tử trần.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>HVB_003_0925</t>
+          <t>HVB_003_0425</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>嘉符赤脂煉藥雷何畏白日乘桴水不虞香火永存光祿典泰</t>
+          <t>未幾保任邑內民富不寧邑人相與祈禱于本社廟中冀可捍災忽內有一人動而起放大聲曰我是細都公被水神黃乎抱恨而沒兮欲報仇第無象馬兵器難以相關寄達保母尊好為我辨送來不亦非推損物且將父人矣</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>sinh ra Thiết-Đức Thiết-Đức sinh ra Đạo-Tấn , Tấn sinh ra Đạo-Thông , Thống sinh Đặng-Doanh</t>
+          <t>Nhưng rồi sau khi ông mất chưa được bao lâu, thì các gia súc trong ấp Bảo-Ngũ lại bị chết dịch, nhân dân trong ấp bàn nhau sửa lễ kỳ-an, để mong tai qua nạn khỏi. Chẳng ngợ giữa lúc đương tế ở trong đình làng, thì thấy trong đầm nhân dân bỗng có một người đứng phất ngay đây, đầu tóc dựng ngược, hai mắt trọn trừng, khóc lớn lên rằng: Ta đây là Điền-Quân-Công mới bị Thủy-Thần ám hại, ôm hận về dưới suối vàng, nay muốn phục thù chỉ hiềm không có ngựa voi khí giới, thì dịch sao nổi với Thủy-Thần. Vậy xin nhẫn lời cho chị tức là Bảo-Mẫu chuẩn bị giúp cho. Nếu không thì chẳng những sức vật bị hại, mà cả nhân mạng cũng khó bảo toàn.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>HVB_003_0926</t>
+          <t>HVB_003_0426</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>盤默祻壯玉都古云敬遠今臣味君子休將辨有無</t>
+          <t>保母聞言即合造與器一如珥郡公生特戰具完足焚之翌日見地方一帶河波濤淘湧如牛馬爭夫岸傍聽者似有于戈交戰之聲魚鬱魚紛然而驚保母聞之度必理郡與水神交戰因祝之曰吾弟今番共他戰勝負如何倘其有靈即以相報</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Xích - Tùng - Tử làm quan Vũ-Sư ở đời vua Thán- Nông . Dục hổ Nghi phong hổ Vũ-Vu, là</t>
+          <t>Nói về bà chị tức là Bảo-Mẫu, sau khi nhận được tin ông hiện lên nhắn bảo, bà cũng theo đúng như lời, sắm sửa các thứ đồ mã, như voi, ngựa và các khí cụ bằng giấy đem đốt, rồi đến hôm sau thì một dài sông của địa phận đó, bỗng thấy sóng lớn nổi dậy như thể muốn ngựa giao tranh, nhân dân ở hai bên bờ nghe thấy những tiếng gươm giáo chạm nhau xoang-xoảng, cá tôm nổi lên mặt nước rất nhiều. Bảo-Mẫu đoán rằng: Em mình cùng Thủy-Thần giao chiến, nên bà cũng làm bảm khẩn: phen này giao chiến thắng phụ ra sao nếu em có thiêng thì báo tin ngay cho chị biết với.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>HVB_003_0927</t>
+          <t>HVB_003_0427</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>羅山阮監生記</t>
+          <t>忽有一人搖動躍起言曰拜上尊姊贈以兵器戰具勢顓張皇但他族類宴聚已素練習我兵新習水戰未請兼以人形都非介胄薄弱之眾難與他鱗甲相鬩纏一交鋒更被挫了今後不可與鬩當於貢口處創一新綱讓他居之竟免積弊釁族人依言而材構作不日告成自是一方河道不聞有異事焉</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Vị Thang Vũ</t>
+          <t>Lạ thay bà vừa khẩn xong, thì hồng có một người nhà dừng phất ngay lên vừa đảo la liệt vừa nói: Xin bài tạ Chị đã cho binh mã gươm dao. Nhưng vì quân địch quá nhiều và lại tinh nhuệ. Còn binh của ta toàn là lính mới, về phần thủy chiến chưa quen; gia đĩ các đồ bằng giấy không thể thắng nổi những quân có lăn gia vậy cũng dẫm, vì thế cho nên thoát mới giao phong liên bị tan rã. Thời thì từ đây về sau đừng nên đối địch với chúng mà thêm thiệt hại. Chi bằng hãy dựng một ngôi đền mới ở trên cửa Cống, nhường cho Thủy-Thần ở đó, để khỏi tích lũy hiểm thù v. v..... Trong họ thấy ông hiện lên phân bảo như vậy, cũng theo dùng lời đi mua vật liệu xây dựng, sau khi dựng xong ngôi đền, thì quảng sông đó nghe không có truyền gì là nữa.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>HVB_003_0928</t>
+          <t>HVB_003_0428</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>羅山縣有阮姓者，生時赤光滿室，人以為失火，父視之，卒無見火而賴</t>
+          <t>彊暴大王記、</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Xương tiếng Giống Gian, biết là hào kiệt Ngày xưa có nhà phú hộ hay đi thưa kiện người làng,</t>
+          <t>Cường-bạo vương, kẻ kháng Thiên Tướng</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>HVB_003_0929</t>
+          <t>HVB_003_0429</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>異性謹愿端懿常受業于本社監生之門毎日輒先至酒掃學堂坐</t>
+          <t>紂大王天本縣令改務、見縝令改人也先其母愛黑漢神謂曰托生猴焉族遂有娠而生時年將十五歲五為兒時好耕耘種樹吃然有巨人之性及長率性彊暴耿目一世都忘父母不有忘臘惟灶神朝祈又禱難得一鯨亦必熟而供之神亦知其心時加頸應</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Rõ thực ngày thường thì coi các ông</t>
+          <t>Cường-bạo đại-vương người làng Bối-Cẩm thuộc huyện Thiên-Bản, khi trước bà mẹ nằm mộng thấy có một người mặt đen bảo cho bà biết: Thần trên núi Nhạc sẽ giáng sinh xuống họ này đây, rồi bà thụ thai, dân sinh ra ông; đến khi lớn tuổi ông rất ngổ ngưu, coi đời bằng nửa con mất, đến nỗi quên cả ngày giỗ cha mẹ, nhưng mà đối với Táo-quân thì lại sớm hôm khấn bài, dù khi bắt được một vài con tôm, cũng đem nấu nướng để cùng, cho nên thần Táo cũng thấu đến tâm lòng thành, thời thường ủng hộ.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>HVB_003_0930</t>
+          <t>HVB_003_0430</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>必別席不與諸生同坐是年近鄉試科其師與之就憲便官析出稍</t>
+          <t>一日父母以狀罪訢于天天郎命雷神降而打之灶神密先頭告王來計灶神曰以滑物塗屋上縱有火觀石斧其盛何施王依其言遂取箝夢條日揚攢與水油相和至日直于屋上偏洒之玉潜伏暗中候視俄而風雨驟至雷神從天而下繞躡星脊上滑而墜地王從中突步揮杖擊之雷神倏然不見奪得赤銅繩長丈餘郎於靜地埋之</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>coi, hôm ấy các quan Phủ huyện Thừa Ty đều vào hành lễ, anh phú hộ đứng bên thấy viên diễn lễ, xướng rằng :</t>
+          <t>Thế rồi bỗng có một hôm cha mẹ đem hết tội trạng tố cáo ở trên thiên đình. Trời bên sai ngay lời thần xuống đánh. Ông Táo biết truyền xuống trước bảo khẽ với Vương: Vương xin Táo-quân, bày kế giúp đỡ. Táo-quân báo lấy chất tròn như mổ phết lên trên mái nhà, để cho Thiên-loi không có chỗ đứng, thì dẫu roi lừa búa đá cũng khó giữ trò v.v... Vương được Táo-quân dạy cho điều kế như vậy, lập tức đi kiếm Mông-toi đem về giả lấy nước giột, và sắm các thứ dầu mỡ để sẵn, đến hôm Thiên-loi xuống đánh, thì trước giờ đó Vương đem các thứ lên trát khắp mái nhà, rồi nắp phía dưới chờ xem động tĩnh ra sao? Quả nhiên hôm ấy Vương vừa nắp được một lát, thì trời nôi con mưa gió sấm chớp ầm ầm! Thiên-lợi phượng mang Ngọc-Hoàng cởi mây nhảy xuống nóc nhà, liền bị chất tron làm cho tuột chân té nháo xuống đất. Vương ở trong nhà ngó thấy, lập tức vác gậy xông ra, đánh ngay một đòn bồ thượng. Thiên-lợi loạng choạng chạy về Thiên-đình, Vương đoạt được sợi dây đồng đỏ dài hơn một trượng, bèn đem chôn ở một nơi cao ráo sạch sẽ.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>HVB_003_0931</t>
+          <t>HVB_003_0431</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>通一各意使官見立命坐日縱本處取中一各亦當取許但他時得志自</t>
+          <t>雷神歸具以事奏昊天天怒謂靈神曰三才我為之尊汝震我威所擊無不摧折者何等人物乃與霹靂抗衡潛報水神以某日引水而上北固彊暴亦為魚敞之餌</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Bá Quan tự vị (Trẫm quan tới chỗ mình đứng) Anh cũng xướng tiếp ngay rằng: Giống gian tự</t>
+          <t>Còn phần Thiên-lợi sau khi chạy thoát trở lên tàu với Ngọc-Hoàng thì Ngài cả giận quơ mắng: Ta đây là bậc chí tôn trong hạng Tam-tái, nay cho nhà người xuống dưới hạ giới để làm vang đội oai danh, hỏi rằng đánh đầu mà chẳng nát gãy? Vậy nay tên ấy là hạng người nào lại dám chống cự thiên oai? Thế thì nhà người phải nên mặt báo với các Thủy-Thần, hẹn đúng ngày giờ, dâng nước lên bắt tên bạo tặc đó, để làm mời cho lũ cá giải, nghe!</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>HVB_003_0932</t>
+          <t>HVB_003_0432</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>蒙記憶既而謂曰新貢士第出其師當番別有說詰憲官即以問這</t>
+          <t>灶神復告之玉遂結蕉為筏取葉為旗翌日水大至浸没蘆舍王郎乘筏而出擊手鼓鳴羅織橫水面設舟震于天大言我與天交戰</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>xướng sau đó tức là người đưa hỏi lộ cho mình ngày trước, thì chẳng còn ai dám nói năng gì, như vậy thì</t>
+          <t>Lần này Táo-quân nghe được lệnh trên, thì lại với vàng quay xuống báo tin cho Bạo-Vương biết. Vương bèn đi đóng bè chuỗi, lấy lá làm cờ, chuẩn bị vừa xong thì sáng hôm sau tự nhiên thấy nước dâng lên, ngập cả nhà cửa. Vương ngồi trên bè chuỗi đánh trống khua chiêng, tung hoành ở trên mặt nước, miệng thì thét lớn Ta lên giao chiến với trời!</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>HVB_003_0933</t>
+          <t>HVB_003_0433</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>弟子來歷與八門父近學業如何師具道其詳憲官曰我昨日夜夢</t>
+          <t>時昊天方與群像論善惡聞之曰何處聲甚緊群像相視莫祛對雷神方候旨對曰是乃彊暴之賊向既逃罪令復于常恭望定奪昊天說思良久曰弗敬怒淪動輒抗拒是乃無天地的人今姑赦之任他長惡弗悛禍必將意至仍命水細縮水而下五竟免害</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Linh , quốc triều niên hiệu Thái-Hòa, Trưởng-Lão Thuyền-Sư từ núi Đông-Cứu thường qua chơi</t>
+          <t>Giữa lúc ấy trời đương cùng chư tiên phân đoàn những kẻ thiện ác ở dưới trần gian, bồng nghe phía dưới có tiếng om xóm, Ngái liên phân hỏi: Trống chiêng ở đâu mà thức dữ thế? các Tiên chưa dám tàu qua, thì Lôi-thần đứng hầu bên cạnh đã vội thưa rằng: Đó là một tên cương bạo, trước đã tránh khỏi thiên hình, nên nay mới giám cần rỡ như vậy, cúi xin Hoàng-Đế định đoạt ra sao? Ngọc-Hoàng nghe tàu xong thì Ngái trầm ngâm một lát rồi mới phân bảo: Hư! Tên kia đã chẳng kinh nề lại còn kháng cự luôn luôn, thực là một kẻ vô thiên vô địa, âu là ngày nay hãy tạm tha thứ, để nó quen thói làm can, rồi sau tai và tự nhiên sẽ đến. Phán xong Ngái liền hạ lệnh cho Thủy-Thần hãy rút nước đi, Thế là Vương lại thoát nạn lần nữa.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>HVB_003_0934</t>
+          <t>HVB_003_0434</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>見一人來謁前道有銅柱斧鉞旌旗僕杖皆五者其隨從軍士約</t>
+          <t>即乃家人具道可以遙來得灶神之助允上帝一言一動必先顯告吾復何辜自是益橫其志復得一田雞自灸而食之不以獻灶神怒其忘己思中傷之</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>cây cột phía trước có 2 hàng chữ cờ, 1 hàng viết 4 chữ Đại-bi-thuyền-Tự , 1 hàng viết</t>
+          <t>Nhưng thoát nạn xong rồi thì Vương có về tự đắc, cho gọi tất cả người nhà tập hợp chung quanh rồi bảo cho biết: từ trước đến nay nhờ có Táo-quân ủng-hộ, phàm trên Thượng-Đế nhất cử nhất động, Ngái cũng bảo trước cho hay, thì ta còn lo gì nữa. Thế rồi từ đây Vương lại hết sức kiêu ngạo. Có hôm bắt được một con cua bẻ đem nướng ăn ngay, không cùng Táo-quân như mọi lần trước, Táo-quân tức giận về nỗi vong ân, quyết tâm tìm kế hãm hại để cho bò ghét.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>HVB_003_0935</t>
+          <t>HVB_003_0435</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>二萬人直至廳前謂曰今欲應考稍通不審官肯許一名否俄而醒</t>
+          <t>一日顯告五曰來日雷神打汝五又問許灶神曰次早汝往耕于田如雷雨將至即於耕木夾處處穿車其中外用橫木裹鎖定自無事王不意一為其所賣依計而行既而雷雨漫天而至王欲斂之不脹竟被打斂頭間雨霽群牛觸土培之宛然成大阜鄉人即其土處封墳</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PHAO SON HUYẾT ÁN TRIỀU BẠCH NHÂN Huyệt ở Phao son trước mặt có nhận tráng châu về</t>
+          <t>Thế rồi bỗng có một hôm Táo-quân hiện lên bảo với Vương rằng: Ngày mai Thiên-lợi lại xuống đánh nhà người đó. Vương hỏi có kế gì không? Táo-quân bảo: Sáng mai thì người cứ việc ra cây ngoài rương, hễ thấy trời sắp đổ mưa, sấm chớp nổ đây, thì người rủn tay vào trong chỗ kẽm chiếc cây, bên ngoài lấy đoạn cây ngang chân lên hai chân rồi khóa chặt lại, thế là sẽ được bình an. Vương thấy Táo-quân bày cho kẻ sách là lùng như vậy, cũng chẳng biết rằng Táo-quân đã nói đối mình, nên cứ lẳng lặng nghe theo. Ngờ đâu đến sáng hôm sau, lúc trời dỡ mưa, sấm chớp vang tai loe mắt! Vương muốn tháo chân chạy trốn thì đã chẳng kịp, thành ra bị sét đánh chết tươi, rồi lúc tạnh mưa dân trâu lấy sừng húc đất dắp lên tử thi thành 1 cái gò rất lớn, người làng nhân đó dắp thành phần mộ,</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>HVB_003_0936</t>
+          <t>HVB_003_0436</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>覺想愛中所見端的是人不審將來做何等事業是科院公八場果中第一未幾無病而終但精氣不散家人常見倏然往來猶如平日每有求必應大著靈異其後有鄉人舟行至神海口於是舟中</t>
+          <t>數年後方民夜勤畜類不寧一日有村翁早行過予墳處見立而言曰我彊暴靈神爾立廟祀之可保無虞不卒無遺類矣將收牛者皆見之村翁歸而道其事鄕遂構祠崇奉自是始得寧居今至封為福神</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>trường thi hương, tới khoảng niên hiệu Hồng-Đức Lã- dương Tiên-sinh khi nhậm chức Tham-chánh-</t>
+          <t>rồi mấy năm sau địa phương bị dịch trâu bò, nhân dân rất là xao xuyến, thì hổng một hôm trong thôn có một ông già, sáng sớm đi qua phần mộ, tự nhiên đứng lại quát to lên rằng: Ta đây tức là Cường-Bạo Linh-Thần. Chúng bay biết phép lập miếu phượng thờ, thì ta phù hộ chẳng có việc chi, vì bằng không nghe Ta sẽ giết hết. Giữa lúc ấy thì có một bọn chăn trâu nghe thấy như vậy, trở về thuật truyền lại với dân làng, nhân dân bên dựng đền thờ từ đấy mới được yên ổn, đến nay được phong sắc là Phúc-Thần,</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>HVB_003_0937</t>
+          <t>HVB_003_0437</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>卒倒後時方頸因語人曰我見阮醫生乘舟一葉黃袍一帶侍衛甚</t>
+          <t>往年有騷客過祠下題詩云</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>truyền là do thầy Tàu tàng hộ, có dự đoán rằng: , . Bạch nhạn sinh mao, sản tận anh hào,</t>
+          <t>trước kia có một nhà thơ đi qua ngoài cửa cung vinh một bài thơ rằng:</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>HVB_003_0938</t>
+          <t>HVB_003_0438</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>嚴召至罰謂曰某原承上帝命降生人世作該帝王但方今收福旅</t>
+          <t>二五鍾靈象貫殊深霄黑漢應嘉符</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>tục gọi là huyết khai oa, nhưng nay đã mất tích, bên</t>
+          <t>Lạ thay nhị ngũ khi hồn nhiều. Điểm bảo canh khuya tướng mặt đen.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>HVB_003_0939</t>
+          <t>HVB_003_0439</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>方隆不可與竪立故復朝帝所別生他國今其從北去矣煩為歸報</t>
+          <t>赤脂煉藥雷何畏白日乘桴水不虞</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>lay chuyển, can qua đời chiến quốc cũng vẫn vững vàng. Tần đột không cháy, Hán phả không tan, khôn biến ra</t>
+          <t>Mở nhốt, Thiên-lôi không hoảng sợ. Nước dâng, bê chuối khỏi lo phiền.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>HVB_003_0940</t>
+          <t>HVB_003_0440</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>家人不必思念言詭雝然而去瞧見來乃是一魚既而振其家具以</t>
+          <t>香火永存光祿典泰盤默祻壯玉都</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>chỉ riêng có cửa nhà họ Phạm mà thôi đâu. Thế thì những ai đi qua mà nhìn vào cái biển ấy</t>
+          <t>Trải bao Tự điển còn hương khói. Giúp mãi hoàng đô được vững bền.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>HVB_003_0941</t>
+          <t>HVB_003_0441</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>前事苦之自是不見頭應按此與亂鬚將見唐太宗而輒哀者乎	, ,</t>
+          <t>古云敬遠今臣味君子休將辨有無</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Đường Ngu trước đúc, Co-son tiết, để dĩ chi, Tiên-sinh dĩ chi.</t>
+          <t>Kinh viêng đối lời nên ngầm nghĩ. Có, không đứng với nói huyền thiên.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>HVB_003_0942</t>
+          <t>HVB_003_0442</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>亦相類是其神器有命不可以智力求蓋以道推之則雖天帝降生</t>
+          <t>羅山阮監生記</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>giữ vĩng tiết thảo, ngày nay Hoàng-đế cũng thế mà Tiên-sinh cũng giống như thế.</t>
+          <t>Nguyễn-Giám-Sinh tác vọng quốc Hoàng-đế</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>HVB_003_0943</t>
+          <t>HVB_003_0443</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>方且讓他一頭近世么麼之輩不自揣量卻于井底窺天晴圖望</t>
+          <t>羅山縣有阮姓者，生時赤光滿室，人以為失火，父視之，卒無見火而賴</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Luật Thương-mãi toát-yêu (tập II) Lé-tài-Triển 60 Đạo-đức-kinh — Lão-tử Nghiêm Toàn 70</t>
+          <t>Huyện La-Son có người họ Nguyễn, lúc mới sinh, trong phòng bồng thấy đỏ rực, người nhà tưởng rằng thất hỏa, nhưng lúc vào coi thì chẳng có gì.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>HVB_003_0944</t>
+          <t>HVB_003_0444</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>外亦有離身之禍世之亂賊可不成哉</t>
+          <t>異性謹愿端懿常受業于本社監生之門毎日輒先至酒掃學堂坐必別席不與諸生同坐</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Danh-từ ký-thuật Bộ Công Chánh 30 Thế-giới Sư Đệ Nhất Tăng-xuân-An 50</t>
+          <t>Rồi khi lớn lên coi rất đĩnh ngợ; tính lại ôn hòa ngay thẳng, cha mẹ cho sang thụ nghiệp một vị Giám-sinh cũng làng, hôm nào cậu cũng đến trước, quét rửa nhà trường, đến lúc vào học thì cậu ngồi riêng biệt một chiếu, chứ không ngồi chung với bạn học trò, vì thế nên vẫn được thầy chú ý hơn hết.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>HVB_003_0945</t>
+          <t>HVB_003_0445</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>槪記字數共五十小張</t>
+          <t>是年近鄉試科其師與之就憲便官析出稍通一各意使官見立命坐日縱本處取中一各亦當取許但他時得志自蒙記憶既而謂曰新貢士第出其師當番別有說詰</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Nguyễn-nam-Châu Cao-hữu-Hoành</t>
+          <t>Thế rồi chẳng bao lâu nữa đến khoa thi hương, thấy dấn cầu sang giới thiệu với quan Hiến-Sư xin cho được dự một tên trong kỳ xảo-thông. Hiến-Sư trong thấy vội vàng vái chào mọi người, ôn tôn nói rằng: Bồn chúc lấy đồ một tên chẳng có ngại chi, mong rằng sau này đặc chi sẽ thơ đến cho. Thời thì vị Công-Sinh mới hãy tạm ra ngoài, để thấy ở lại một lát cùng ta nói câu truyện riêng.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>HVB_003_0946</t>
+          <t>HVB_003_0446</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>三名鹹敬自跡</t>
+          <t>憲官即以問這弟子來歷與八門父近學業如何師具道其詳</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Lê-xuân-Khoa Trần-trọng-San</t>
+          <t>Khi cậu lui ra ngoài rồi, Hiến-Sư bèn hỏi Giám-sinh về lai lịch của người đệ-tử, theo học đã bao lâu rồi? và sự học văn ra sao? Giám-sinh kể lại một lượt.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>HVB_003_0947</t>
+          <t>HVB_003_0447</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>昔我越紹基南服自雄朝十八世都是雄王玉帛事</t>
+          <t>憲官曰我昨日夜夢見一人來謁前道有銅柱斧鉞旌旗僕杖皆五者其隨從軍士約二萬人直至廳前謂曰今欲應考稍通不審官肯許一名否俄而醒覺想愛中所見端的是人不審將來做何等事業</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Nữ thi-hào Việt-Nam Phạm-xuân-Độ 22 Văn-học Việt-Nam Dương-quảng-Hàm 35</t>
+          <t>Hiến-Sư nghe xong bảo Giám-sinh rằng: Đêm trước tôi năm mơ thấy một người xin vào yết kiến, mà đoàn tiền đạo lại có quân sĩ vác phù việt bằng đồng, và có cờ quạt nghi về như một vương-giả, còn đoàn quân sĩ theo sau thì có đến hơn hai vạn, khi tiến vào cửa sảnh nói với tôi rằng: Muốn xin ưng cử kỳ thì xảo-thông, chẳng hay quan ngài có cho được dự một tên chẳng tá? Bây giờ nhớ lại cái người trong mộng, chính là cái cậu học sinh mới rồi, chẳng biết sau này cậu ấy làm nên sự nghiệp to tát đến đâu.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>HVB_003_0948</t>
+          <t>HVB_003_0448</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>書山河一統是為百越之祖焉長値朝雄傳至蜀</t>
+          <t>是科院公八場果中第一未幾無病而終但精氣不散家人常見倏然往來猶如平日每有求必應大著靈異</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Thiên-văn học Đệ Nhất Đặng-văn-Nhân 30</t>
+          <t>Nghè Hiến-Sử kề lại giấc mơ kỳ quặc như thế, ông Đồ cũng lấy làm lạ, cáo biết ra về, rồi trong năm ấy cậu Nguyễn vào thi trúng ngay nhất cử; nhưng mà chẳng được bao lâu thì cậu ốm chết, chết rồi mà phần tình khi vẫn chẳng tiêu tan, người nhà vẫn thường trông thấy hình bóng đi lại như lúc sinh thời, cậu khấn việc gì cũng thấy ứng nghiệm.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>HVB_003_0949</t>
+          <t>HVB_003_0449</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>王蜀王乃傳順王順王娶乎章縣洞為社後</t>
+          <t>其後有鄉人舟行至神海口於是舟中卒倒後時方頸因語人曰我見阮醫生乘舟一葉黃袍一帶侍衛甚嚴召至罰謂曰某原承上帝命降生人世作該帝王但方今收福旅方隆不可與竪立故復朝帝所別生他國今其從北去矣煩為歸報家人不必思念言詭雝然而去瞧見來乃是一魚既而振其家具以前事苦之自是不見頭應</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Nguyễn-văn-Chính 15 Anh-văn Đệ Thất</t>
+          <t>Thế rồi cách mấy năm sau có một người làng đi qua cửa bê Thân-phù, đương ngồi trong thuyền tự nhiên bị ngã thiếp đi hồi lâu, đến khi tỉnh dậy bảo người nhà rằng: Mới rồi ta gặp cậu Nguyễn Giám-Sinh ngồi trong một chiếc thuyền nhỏ, mình mặc hoàng-báo, lưng thắt đại ngọc, có đám thì về đi hầu, cho gọi ta đến bảo rằng: Mở đây ngày trước váng mạng Ngọc-Hoàng thác sinh xuống dưới tràn thế đẳng làm đế-vương nước này; nhưng vì quốc-vương hiện tại phục âm còn bền, vì lẽ anh hùng không thể lường lập, cho nên ta lại trở về Thiên-đình, ngày nay Ngọc-Hoàng lại sai thác sinh ở một nước khác. Vậy phiền người về nói với gia-nhân của ta cũng đừng nên thương nhớ nữa. Nói xong thì lại bay đi, đến khi người ấy chợt tỉnh mới biết là một giấc mộng, lúc về bên đêm truyền ấy kể lại cho nhà cậu nghe, rồi cũng từ đấy không thấy hiện linh như trước nữa.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>HVB_003_0950</t>
+          <t>HVB_003_0450</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>改洞蒙社明氏女經十三年而未見熊羆之兆乃</t>
+          <t>按此與亂鬚將見唐太宗而輒哀者乎亦相類是其神器有命不可以智力求蓋以道推之則雖天帝降生方且讓他一頭近世么麼之輩不自揣量卻于井底窺天晴圖望外亦有離身之禍世之亂賊可不成哉</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Thượng-chi văn tập II — nt — 35 Thượng-chi văn tập III — nt — 35</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>HVB_003_0951</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>立炫場祈禱感動天庭至六月二十一日明代協孕</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>SÁCH DỊCH Cung-oán ngâm-khúc T.L. Huỳnh-k-Dụng 28</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>HVB_003_0952</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>後生一胞外六十人頭甚其怪異郎將深莖子本</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>Chinh-phụ ngâm-khúc — nt — 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>HVB_003_0953</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>社三岐大路至三月初十日玉皇急差鬼王降鑒</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>M. Hoàng-q-Trương 6 (A frightful Discovery from Typee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>HVB_003_0954</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>墳墓及都憲都承都司尽鉴感照王情上奏天</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>Lễ-triệu giáo-hóa điều luật — Tự thập thật điều Trần-Khải-Văn 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>HVB_003_0955</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>庭下令給許就伊總社迎杜氏名璣現八為君以</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>Lê-triệu lịch-khoa tiên- si để danh bi ký (tập I) Võ-Oanh 85</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>HVB_003_0956</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>維治天下又催本社胄氏名琚現八為文臣以贊</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>Lê-Triệu lịch-khoa tiên-si để danh bi ký (tập II) —nt— 75</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>HVB_003_0957</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>治化再催朋氏之人名瓊現八為武將以董兵催三</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>Công-dư tiếp-ký (tập I) Nguyễn-dinh-Điệm 50 Quốc Triều đăng-khoa lục Lê-mạnh-Liều 80</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>HVB_003_0958</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>名號曰三彭同八明氏克家之子以治天下於雄</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>M. Trần-thái-Đinh 50 Luận-ngữ Lê-phục-Thiện 95</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>HVB_003_0959</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>朝既熾之秋自此朋氏依貽至來年亦三月初十</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>Tang-thương ngẫu-lục Đạm-Nguyên 75 Tân-biên Truyền-ký mạn-lục Bùi-xuân-Trang 80</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>HVB_003_0960</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>日挺生一胞子廚王地分第一員生則無面第二員</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>Công-dư tiếp-ký (tập II) Nguyễn-dinh-Điệm 40 Lê-triệu lịch-khoa tiên-si để</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>HVB_003_0961</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>生則無手第三員者無頭乃三名號三彭一胞之</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>danh bi ký (tập III) Võ-Oanh 70</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>HVB_003_0962</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>子也。</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>Bên bờ sông xanh Nguyễn-văn-Mừng 22 Công-dân Đệ Tứ Phạm-thị-Tự — Trần-t.</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>HVB_003_0963</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>其順王見此遂驚乃移萃三員于三牛中一牛在</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>San 10 Công-dân Đệ Nhị Lè-xuân-Khoa 25 Mũi tên đen Nguyễn-dáng-Hải 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>HVB_003_0964</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>後廟二井在路旁三井在上鄕以不存形跡滿百日妙</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>Vật-lý Đệ Tam A B Bùi-phương-Chi 38 Hóa-học Đệ Nhị Phạm-dinh-Ái 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>HVB_003_0965</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>其変化萬千逐打城隍各道第一名無面有救封二</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>Tom Walker với quỷ sứ Nguyễn-văn-Tạo 8 Silas Marner Nguyễn-văn-Tạo 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>HVB_003_0966</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>字足有四縱五橫宇天下莫不重足以居順王意無以</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>Quan-sát lớp Ba Một nhóm giáo-viên 10 Toán-pháp lớp Nhật — nt — 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>HVB_003_0967</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>敵乃親出為駕就洞為左諭以相安之術乃通說其</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>Địa-lý lớp Tư Huỳnh-văn-Đổ 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>HVB_003_0968</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>各景臣者乃皸皸皸也前日臣為三世都次日為孤	.</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>13 — Thượng-thư trí-sĩ Toàn-quận-Công. . 18 — Dương - Công - Tôn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>HVB_003_0969</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>魂將今夭心弗佑雄朝臣等卽爲三名鬼將明君欲安	.</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>77 — Chỉ-khi dừ Thượng-Thư Nghiêm-Son-Hâu — Võ Thám-Hoa Ký thi thành sầm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>HVB_003_0970</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>天下者每日賜祭一筵粥米大盛卽変化無誠妨矣	—</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>Chung gian lễ xướng tri hào-kiệt. . . 161 — Trần-Quốc lão, thề xưng di thuật.</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>HVB_003_0971</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>自此傳本縣與本總及本社設設嗚盡則生事矣。	. .</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>163 — Lệ-Kỳ linh Cổ Chung hiện-di. . . . 165 — Đại bị tự bắc nhân sở kiến.</t>
+          <t>Xét ra truyện này cũng giống như truyện Cù-Tu Tướng-quân khi nhìn thấy Đường-Thái-Tông, tự nhien khóc rất thâm thiết (xuất xứ ở cuốn Hương-Đại?) như vậy mới biết ngôi báu phải có mệnh trời, không thể đem tri lực ra mà cầu cạnh được, bởi vì theo dùng đạo-lý thì dẫu trời cho giáng sinh cũng phải nhượng người có đức. Thế mà gần đây những bọn yêu quái, chẳng lượng sức mình, lại ngồi ở dưới đây giếng để tròng lên trời, lo toàn cướp ngôi tôn quỉ, chẳng sớm thì muộn rồi cũng mang lấy cái nạn diệt vong, sao chúng lại chẳng soi tấm gương đó để mà tu tỉnh vậy.</t>
         </is>
       </c>
     </row>
